--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -4469,7 +4469,7 @@
         <v>0.118</v>
       </c>
       <c r="K308" t="n">
-        <v>0.501</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="309">
@@ -4911,7 +4911,7 @@
         <v>-0.122</v>
       </c>
       <c r="K342" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="343">
@@ -6861,7 +6861,7 @@
         <v>0.724</v>
       </c>
       <c r="K492" t="n">
-        <v>0.842</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="493">
@@ -8603,7 +8603,7 @@
         <v>0.46</v>
       </c>
       <c r="K626" t="n">
-        <v>-0.17</v>
+        <v>-0.169</v>
       </c>
     </row>
   </sheetData>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.205</v>
+        <v>10.189</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.085</v>
+        <v>1.08</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.92</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="14">
@@ -34435,10 +34435,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.085</v>
+        <v>1.0797</v>
       </c>
       <c r="H634" t="n">
-        <v>10.2049</v>
+        <v>10.1887</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -37181,7 +37181,7 @@
         <v>-1.4179</v>
       </c>
       <c r="C167" t="n">
-        <v>-3.1728</v>
+        <v>-3.1729</v>
       </c>
       <c r="D167" t="n">
         <v>-2.2954</v>
@@ -37190,13 +37190,13 @@
         <v>-1.4179</v>
       </c>
       <c r="F167" t="n">
-        <v>-3.1728</v>
+        <v>-3.1729</v>
       </c>
       <c r="G167" t="n">
         <v>-1.4179</v>
       </c>
       <c r="M167" t="n">
-        <v>-3.1728</v>
+        <v>-3.1729</v>
       </c>
     </row>
     <row r="168">
@@ -37825,7 +37825,7 @@
         <v>-0.8606</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3753</v>
+        <v>-0.3754</v>
       </c>
       <c r="D190" t="n">
         <v>-0.618</v>
@@ -37834,13 +37834,13 @@
         <v>-0.8606</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.3753</v>
+        <v>-0.3754</v>
       </c>
       <c r="G190" t="n">
         <v>-0.8606</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.3753</v>
+        <v>-0.3754</v>
       </c>
     </row>
     <row r="191">
@@ -37937,7 +37937,7 @@
         <v>-1.2593</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.7313</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="D194" t="n">
         <v>-0.9953</v>
@@ -37946,13 +37946,13 @@
         <v>-1.2593</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.7313</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="G194" t="n">
         <v>-1.2593</v>
       </c>
       <c r="M194" t="n">
-        <v>-0.7313</v>
+        <v>-0.7314000000000001</v>
       </c>
     </row>
     <row r="195">
@@ -38584,7 +38584,7 @@
         <v>-0.0901</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.7631</v>
+        <v>-0.7632</v>
       </c>
       <c r="E217" t="n">
         <v>-1.4362</v>
@@ -38836,7 +38836,7 @@
         <v>-0.0033</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.2515</v>
+        <v>-0.2516</v>
       </c>
       <c r="E226" t="n">
         <v>-0.4998</v>
@@ -39561,7 +39561,7 @@
         <v>-0.6702</v>
       </c>
       <c r="C252" t="n">
-        <v>-1.0832</v>
+        <v>-1.0833</v>
       </c>
       <c r="D252" t="n">
         <v>-0.8767</v>
@@ -39570,13 +39570,13 @@
         <v>-0.6702</v>
       </c>
       <c r="F252" t="n">
-        <v>-1.0832</v>
+        <v>-1.0833</v>
       </c>
       <c r="G252" t="n">
         <v>-0.6702</v>
       </c>
       <c r="M252" t="n">
-        <v>-1.0832</v>
+        <v>-1.0833</v>
       </c>
     </row>
     <row r="253">
@@ -40569,7 +40569,7 @@
         <v>1.0712</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.1078</v>
+        <v>-0.1079</v>
       </c>
       <c r="D288" t="n">
         <v>0.4817</v>
@@ -40578,13 +40578,13 @@
         <v>1.0712</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.1078</v>
+        <v>-0.1079</v>
       </c>
       <c r="G288" t="n">
         <v>1.0712</v>
       </c>
       <c r="M288" t="n">
-        <v>-0.1078</v>
+        <v>-0.1079</v>
       </c>
     </row>
     <row r="289">
@@ -40625,7 +40625,7 @@
         <v>0.9968</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.1245</v>
+        <v>-0.1246</v>
       </c>
       <c r="D290" t="n">
         <v>0.4361</v>
@@ -40634,13 +40634,13 @@
         <v>0.9968</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.1245</v>
+        <v>-0.1246</v>
       </c>
       <c r="G290" t="n">
         <v>0.9968</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.1245</v>
+        <v>-0.1246</v>
       </c>
     </row>
     <row r="291">
@@ -40852,7 +40852,7 @@
         <v>-0.1635</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.1369</v>
+        <v>-0.137</v>
       </c>
       <c r="E298" t="n">
         <v>-0.1104</v>
@@ -41216,7 +41216,7 @@
         <v>-1.0241</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.418</v>
+        <v>-0.4181</v>
       </c>
       <c r="E311" t="n">
         <v>0.188</v>
@@ -41384,7 +41384,7 @@
         <v>0.7655</v>
       </c>
       <c r="D317" t="n">
-        <v>0.4396</v>
+        <v>0.4397</v>
       </c>
       <c r="E317" t="n">
         <v>0.1138</v>
@@ -41549,7 +41549,7 @@
         <v>-0.2258</v>
       </c>
       <c r="C323" t="n">
-        <v>0.303</v>
+        <v>0.3029</v>
       </c>
       <c r="D323" t="n">
         <v>0.0386</v>
@@ -41558,13 +41558,13 @@
         <v>-0.2258</v>
       </c>
       <c r="F323" t="n">
-        <v>0.303</v>
+        <v>0.3029</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2258</v>
       </c>
       <c r="M323" t="n">
-        <v>0.303</v>
+        <v>0.3029</v>
       </c>
     </row>
     <row r="324">
@@ -41633,7 +41633,7 @@
         <v>-0.2564</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1854</v>
+        <v>0.1853</v>
       </c>
       <c r="D326" t="n">
         <v>-0.0355</v>
@@ -41642,13 +41642,13 @@
         <v>-0.2564</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1854</v>
+        <v>0.1853</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2564</v>
       </c>
       <c r="M326" t="n">
-        <v>0.1854</v>
+        <v>0.1853</v>
       </c>
     </row>
     <row r="327">
@@ -41717,7 +41717,7 @@
         <v>-0.1292</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0298</v>
+        <v>0.0297</v>
       </c>
       <c r="D329" t="n">
         <v>-0.0497</v>
@@ -41726,13 +41726,13 @@
         <v>-0.1292</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0298</v>
+        <v>0.0297</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1292</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0298</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="330">
@@ -41745,7 +41745,7 @@
         <v>-0.2151</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1376</v>
+        <v>-0.1377</v>
       </c>
       <c r="D330" t="n">
         <v>-0.1764</v>
@@ -41754,13 +41754,13 @@
         <v>-0.2151</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1376</v>
+        <v>-0.1377</v>
       </c>
       <c r="G330" t="n">
         <v>-0.2151</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1376</v>
+        <v>-0.1377</v>
       </c>
     </row>
     <row r="331">
@@ -41776,7 +41776,7 @@
         <v>-0.1221</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1445</v>
+        <v>-0.1446</v>
       </c>
       <c r="E331" t="n">
         <v>-0.167</v>
@@ -41829,7 +41829,7 @@
         <v>-0.1717</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.2402</v>
+        <v>-0.2403</v>
       </c>
       <c r="D333" t="n">
         <v>-0.206</v>
@@ -41838,13 +41838,13 @@
         <v>-0.1717</v>
       </c>
       <c r="F333" t="n">
-        <v>-0.2402</v>
+        <v>-0.2403</v>
       </c>
       <c r="G333" t="n">
         <v>-0.1717</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.2402</v>
+        <v>-0.2403</v>
       </c>
     </row>
     <row r="334">
@@ -41885,7 +41885,7 @@
         <v>-0.07290000000000001</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2615</v>
+        <v>-0.2616</v>
       </c>
       <c r="D335" t="n">
         <v>-0.1672</v>
@@ -41894,13 +41894,13 @@
         <v>-0.07290000000000001</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2615</v>
+        <v>-0.2616</v>
       </c>
       <c r="G335" t="n">
         <v>-0.07290000000000001</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2615</v>
+        <v>-0.2616</v>
       </c>
     </row>
     <row r="336">
@@ -41913,7 +41913,7 @@
         <v>-0.1207</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.204</v>
+        <v>-0.2041</v>
       </c>
       <c r="D336" t="n">
         <v>-0.1624</v>
@@ -41922,13 +41922,13 @@
         <v>-0.1207</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.204</v>
+        <v>-0.2041</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1207</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.204</v>
+        <v>-0.2041</v>
       </c>
     </row>
     <row r="337">
@@ -41997,7 +41997,7 @@
         <v>-0.1227</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2085</v>
+        <v>-0.2086</v>
       </c>
       <c r="D339" t="n">
         <v>-0.1656</v>
@@ -42006,13 +42006,13 @@
         <v>-0.1227</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2085</v>
+        <v>-0.2086</v>
       </c>
       <c r="G339" t="n">
         <v>-0.1227</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2085</v>
+        <v>-0.2086</v>
       </c>
     </row>
     <row r="340">
@@ -42053,7 +42053,7 @@
         <v>-0.1681</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1765</v>
+        <v>0.1764</v>
       </c>
       <c r="D341" t="n">
         <v>0.0042</v>
@@ -42062,13 +42062,13 @@
         <v>-0.1681</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1765</v>
+        <v>0.1764</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1681</v>
       </c>
       <c r="M341" t="n">
-        <v>0.1765</v>
+        <v>0.1764</v>
       </c>
     </row>
     <row r="342">
@@ -42109,7 +42109,7 @@
         <v>-0.1208</v>
       </c>
       <c r="C343" t="n">
-        <v>0.3411</v>
+        <v>0.341</v>
       </c>
       <c r="D343" t="n">
         <v>0.1101</v>
@@ -42118,13 +42118,13 @@
         <v>-0.1208</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3411</v>
+        <v>0.341</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1208</v>
       </c>
       <c r="M343" t="n">
-        <v>0.3411</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="344">
@@ -42168,7 +42168,7 @@
         <v>0.4448</v>
       </c>
       <c r="D345" t="n">
-        <v>0.1398</v>
+        <v>0.1397</v>
       </c>
       <c r="E345" t="n">
         <v>-0.1653</v>
@@ -42193,7 +42193,7 @@
         <v>-0.1658</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5241</v>
+        <v>0.524</v>
       </c>
       <c r="D346" t="n">
         <v>0.1791</v>
@@ -42202,13 +42202,13 @@
         <v>-0.1658</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5241</v>
+        <v>0.524</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1658</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5241</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="347">
@@ -42221,7 +42221,7 @@
         <v>-0.1659</v>
       </c>
       <c r="C347" t="n">
-        <v>0.351</v>
+        <v>0.3509</v>
       </c>
       <c r="D347" t="n">
         <v>0.0925</v>
@@ -42230,13 +42230,13 @@
         <v>-0.1659</v>
       </c>
       <c r="F347" t="n">
-        <v>0.351</v>
+        <v>0.3509</v>
       </c>
       <c r="G347" t="n">
         <v>-0.1659</v>
       </c>
       <c r="M347" t="n">
-        <v>0.351</v>
+        <v>0.3509</v>
       </c>
     </row>
     <row r="348">
@@ -42252,7 +42252,7 @@
         <v>0.5121</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1966</v>
+        <v>0.1965</v>
       </c>
       <c r="E348" t="n">
         <v>-0.119</v>
@@ -42280,7 +42280,7 @@
         <v>0.508</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2183</v>
+        <v>0.2182</v>
       </c>
       <c r="E349" t="n">
         <v>-0.07149999999999999</v>
@@ -42588,7 +42588,7 @@
         <v>-0.0186</v>
       </c>
       <c r="D360" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="E360" t="n">
         <v>0.2137</v>
@@ -42675,7 +42675,7 @@
         <v>-0.2216</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.3613</v>
+        <v>-0.3614</v>
       </c>
       <c r="E363" t="n">
         <v>-0.5011</v>
@@ -42706,7 +42706,7 @@
         <v>-0.0677</v>
       </c>
       <c r="D364" t="n">
-        <v>-0.2752</v>
+        <v>-0.2753</v>
       </c>
       <c r="E364" t="n">
         <v>-0.4828</v>
@@ -42827,7 +42827,7 @@
         <v>-0.4761</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.1071</v>
+        <v>-0.1072</v>
       </c>
       <c r="D368" t="n">
         <v>-0.2916</v>
@@ -42836,7 +42836,7 @@
         <v>-0.4761</v>
       </c>
       <c r="F368" t="n">
-        <v>-0.1071</v>
+        <v>-0.1072</v>
       </c>
       <c r="G368" t="n">
         <v>0.1603</v>
@@ -42845,7 +42845,7 @@
         <v>-1.1125</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.1071</v>
+        <v>-0.1072</v>
       </c>
     </row>
     <row r="369">
@@ -42858,7 +42858,7 @@
         <v>-0.4497</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.4019</v>
+        <v>-0.402</v>
       </c>
       <c r="D369" t="n">
         <v>-0.4258</v>
@@ -42867,7 +42867,7 @@
         <v>-0.4497</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.4019</v>
+        <v>-0.402</v>
       </c>
       <c r="G369" t="n">
         <v>0.1635</v>
@@ -42876,7 +42876,7 @@
         <v>-1.063</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.4019</v>
+        <v>-0.402</v>
       </c>
     </row>
     <row r="370">
@@ -42889,7 +42889,7 @@
         <v>-0.4054</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3736</v>
+        <v>-0.3737</v>
       </c>
       <c r="D370" t="n">
         <v>-0.3895</v>
@@ -42898,7 +42898,7 @@
         <v>-0.4054</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3736</v>
+        <v>-0.3737</v>
       </c>
       <c r="G370" t="n">
         <v>0.2606</v>
@@ -42907,7 +42907,7 @@
         <v>-1.0714</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3736</v>
+        <v>-0.3737</v>
       </c>
     </row>
     <row r="371">
@@ -42951,7 +42951,7 @@
         <v>-0.5492</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3353</v>
+        <v>-0.3354</v>
       </c>
       <c r="D372" t="n">
         <v>-0.4423</v>
@@ -42960,7 +42960,7 @@
         <v>-0.5492</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3353</v>
+        <v>-0.3354</v>
       </c>
       <c r="G372" t="n">
         <v>0.1678</v>
@@ -42969,7 +42969,7 @@
         <v>-1.2662</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3353</v>
+        <v>-0.3354</v>
       </c>
     </row>
     <row r="373">
@@ -42982,7 +42982,7 @@
         <v>-0.5374</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2944</v>
+        <v>-0.2945</v>
       </c>
       <c r="D373" t="n">
         <v>-0.4159</v>
@@ -42991,7 +42991,7 @@
         <v>-0.5374</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2944</v>
+        <v>-0.2945</v>
       </c>
       <c r="G373" t="n">
         <v>0.1683</v>
@@ -43000,7 +43000,7 @@
         <v>-1.2431</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2944</v>
+        <v>-0.2945</v>
       </c>
     </row>
     <row r="374">
@@ -43142,7 +43142,7 @@
         <v>-0.5411</v>
       </c>
       <c r="C377" t="n">
-        <v>0.3535</v>
+        <v>0.3534</v>
       </c>
       <c r="D377" t="n">
         <v>-0.09379999999999999</v>
@@ -43151,7 +43151,7 @@
         <v>-0.5411</v>
       </c>
       <c r="F377" t="n">
-        <v>0.3535</v>
+        <v>0.3534</v>
       </c>
       <c r="G377" t="n">
         <v>0.2646</v>
@@ -43215,7 +43215,7 @@
         <v>0.731</v>
       </c>
       <c r="M378" t="n">
-        <v>0.7518</v>
+        <v>0.7517</v>
       </c>
     </row>
     <row r="379">
@@ -43400,7 +43400,7 @@
         <v>-0.4241</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.0799</v>
+        <v>-0.08</v>
       </c>
       <c r="D383" t="n">
         <v>-0.252</v>
@@ -43409,7 +43409,7 @@
         <v>-0.4241</v>
       </c>
       <c r="F383" t="n">
-        <v>-0.0799</v>
+        <v>-0.08</v>
       </c>
       <c r="G383" t="n">
         <v>0.2029</v>
@@ -43446,7 +43446,7 @@
         <v>-0.132</v>
       </c>
       <c r="D384" t="n">
-        <v>-0.2827</v>
+        <v>-0.2828</v>
       </c>
       <c r="E384" t="n">
         <v>-0.4335</v>
@@ -44462,7 +44462,7 @@
         <v>-1.9109</v>
       </c>
       <c r="M407" t="n">
-        <v>-0.1641</v>
+        <v>-0.1642</v>
       </c>
     </row>
     <row r="408">
@@ -44505,7 +44505,7 @@
         <v>-1.9276</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.1735</v>
+        <v>-0.1736</v>
       </c>
     </row>
     <row r="409">
@@ -45507,7 +45507,7 @@
         <v>-0.7232</v>
       </c>
       <c r="C432" t="n">
-        <v>0.0868</v>
+        <v>0.0867</v>
       </c>
       <c r="D432" t="n">
         <v>-0.3182</v>
@@ -45516,7 +45516,7 @@
         <v>-0.7232</v>
       </c>
       <c r="F432" t="n">
-        <v>0.0868</v>
+        <v>0.0867</v>
       </c>
       <c r="G432" t="n">
         <v>-0.5622</v>
@@ -45666,7 +45666,7 @@
         <v>-0.0377</v>
       </c>
       <c r="M435" t="n">
-        <v>0.4094</v>
+        <v>0.4093</v>
       </c>
     </row>
     <row r="436">
@@ -45725,7 +45725,7 @@
         <v>0.2228</v>
       </c>
       <c r="D437" t="n">
-        <v>-0.2093</v>
+        <v>-0.2094</v>
       </c>
       <c r="E437" t="n">
         <v>-0.6415</v>
@@ -45980,7 +45980,7 @@
         <v>-0.6115</v>
       </c>
       <c r="C443" t="n">
-        <v>0.2956</v>
+        <v>0.2955</v>
       </c>
       <c r="D443" t="n">
         <v>-0.158</v>
@@ -45989,7 +45989,7 @@
         <v>-0.6115</v>
       </c>
       <c r="F443" t="n">
-        <v>0.2956</v>
+        <v>0.2955</v>
       </c>
       <c r="G443" t="n">
         <v>-0.1662</v>
@@ -46367,7 +46367,7 @@
         <v>-0.3037</v>
       </c>
       <c r="C452" t="n">
-        <v>0.2787</v>
+        <v>0.2786</v>
       </c>
       <c r="D452" t="n">
         <v>-0.0125</v>
@@ -46376,7 +46376,7 @@
         <v>-0.3037</v>
       </c>
       <c r="F452" t="n">
-        <v>0.2787</v>
+        <v>0.2786</v>
       </c>
       <c r="G452" t="n">
         <v>0.271</v>
@@ -46397,7 +46397,7 @@
         <v>0.1787</v>
       </c>
       <c r="M452" t="n">
-        <v>0.1858</v>
+        <v>0.1857</v>
       </c>
     </row>
     <row r="453">
@@ -46539,7 +46539,7 @@
         <v>-0.3855</v>
       </c>
       <c r="C456" t="n">
-        <v>0.3124</v>
+        <v>0.3123</v>
       </c>
       <c r="D456" t="n">
         <v>-0.0366</v>
@@ -46548,7 +46548,7 @@
         <v>-0.3855</v>
       </c>
       <c r="F456" t="n">
-        <v>0.3124</v>
+        <v>0.3123</v>
       </c>
       <c r="G456" t="n">
         <v>0.1245</v>
@@ -46741,7 +46741,7 @@
         <v>0.3105</v>
       </c>
       <c r="M460" t="n">
-        <v>0.3726</v>
+        <v>0.3725</v>
       </c>
     </row>
     <row r="461">
@@ -46827,7 +46827,7 @@
         <v>0.3018</v>
       </c>
       <c r="M462" t="n">
-        <v>0.3912</v>
+        <v>0.3911</v>
       </c>
     </row>
     <row r="463">
@@ -46870,7 +46870,7 @@
         <v>0.4368</v>
       </c>
       <c r="M463" t="n">
-        <v>0.333</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="464">
@@ -46929,7 +46929,7 @@
         <v>0.3575</v>
       </c>
       <c r="D465" t="n">
-        <v>-0.0623</v>
+        <v>-0.0624</v>
       </c>
       <c r="E465" t="n">
         <v>-0.4822</v>
@@ -47042,7 +47042,7 @@
         <v>0.441</v>
       </c>
       <c r="M467" t="n">
-        <v>0.3804</v>
+        <v>0.3803</v>
       </c>
     </row>
     <row r="468">
@@ -47214,7 +47214,7 @@
         <v>0.6054</v>
       </c>
       <c r="M471" t="n">
-        <v>0.3037</v>
+        <v>0.3036</v>
       </c>
     </row>
     <row r="472">
@@ -47257,7 +47257,7 @@
         <v>0.6002999999999999</v>
       </c>
       <c r="M472" t="n">
-        <v>0.2852</v>
+        <v>0.2851</v>
       </c>
     </row>
     <row r="473">
@@ -47356,7 +47356,7 @@
         <v>0.481</v>
       </c>
       <c r="C475" t="n">
-        <v>1.0087</v>
+        <v>1.0086</v>
       </c>
       <c r="D475" t="n">
         <v>0.7448</v>
@@ -47365,7 +47365,7 @@
         <v>0.481</v>
       </c>
       <c r="F475" t="n">
-        <v>1.0087</v>
+        <v>1.0086</v>
       </c>
       <c r="G475" t="n">
         <v>0.3733</v>
@@ -47429,7 +47429,7 @@
         <v>0.6847</v>
       </c>
       <c r="M476" t="n">
-        <v>0.3135</v>
+        <v>0.3134</v>
       </c>
     </row>
     <row r="477">
@@ -47472,7 +47472,7 @@
         <v>0.5770999999999999</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2799</v>
+        <v>0.2798</v>
       </c>
     </row>
     <row r="478">
@@ -47687,7 +47687,7 @@
         <v>0.6862</v>
       </c>
       <c r="M482" t="n">
-        <v>0.2446</v>
+        <v>0.2445</v>
       </c>
     </row>
     <row r="483">
@@ -48219,7 +48219,7 @@
         <v>0.8484</v>
       </c>
       <c r="D495" t="n">
-        <v>0.8799</v>
+        <v>0.8798</v>
       </c>
       <c r="E495" t="n">
         <v>0.9113</v>
@@ -48375,7 +48375,7 @@
         <v>0.5169</v>
       </c>
       <c r="M498" t="n">
-        <v>0.6905</v>
+        <v>0.6904</v>
       </c>
     </row>
     <row r="499">
@@ -50925,7 +50925,7 @@
         <v>0.5974</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.3941</v>
+        <v>-0.394</v>
       </c>
       <c r="D558" t="n">
         <v>0.1017</v>
@@ -50934,7 +50934,7 @@
         <v>0.5974</v>
       </c>
       <c r="F558" t="n">
-        <v>-0.3941</v>
+        <v>-0.394</v>
       </c>
       <c r="G558" t="n">
         <v>0.2698</v>
@@ -50955,7 +50955,7 @@
         <v>-0.8518</v>
       </c>
       <c r="M558" t="n">
-        <v>-0.2737</v>
+        <v>-0.2736</v>
       </c>
     </row>
     <row r="559">
@@ -52073,7 +52073,7 @@
         <v>0.6975</v>
       </c>
       <c r="M584" t="n">
-        <v>-0.4657</v>
+        <v>-0.4658</v>
       </c>
     </row>
     <row r="585">
@@ -52202,7 +52202,7 @@
         <v>0.5306</v>
       </c>
       <c r="M587" t="n">
-        <v>-0.8593</v>
+        <v>-0.8594000000000001</v>
       </c>
     </row>
     <row r="588">
@@ -52215,7 +52215,7 @@
         <v>0.6444</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.3168</v>
+        <v>-0.3169</v>
       </c>
       <c r="D588" t="n">
         <v>0.1638</v>
@@ -52224,7 +52224,7 @@
         <v>0.6444</v>
       </c>
       <c r="F588" t="n">
-        <v>-0.3168</v>
+        <v>-0.3169</v>
       </c>
       <c r="G588" t="n">
         <v>2.024</v>
@@ -52288,7 +52288,7 @@
         <v>0.5178</v>
       </c>
       <c r="M589" t="n">
-        <v>-1.0445</v>
+        <v>-1.0446</v>
       </c>
     </row>
     <row r="590">
@@ -52374,7 +52374,7 @@
         <v>0.5157</v>
       </c>
       <c r="M591" t="n">
-        <v>-1.0594</v>
+        <v>-1.0595</v>
       </c>
     </row>
     <row r="592">
@@ -52503,7 +52503,7 @@
         <v>0.4914</v>
       </c>
       <c r="M594" t="n">
-        <v>-1.0487</v>
+        <v>-1.0488</v>
       </c>
     </row>
     <row r="595">
@@ -52817,7 +52817,7 @@
         <v>0.5528</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.2248</v>
+        <v>-0.2249</v>
       </c>
       <c r="D602" t="n">
         <v>0.164</v>
@@ -52826,7 +52826,7 @@
         <v>0.5528</v>
       </c>
       <c r="F602" t="n">
-        <v>-0.2248</v>
+        <v>-0.2249</v>
       </c>
       <c r="G602" t="n">
         <v>1.2189</v>
@@ -52860,7 +52860,7 @@
         <v>0.6578000000000001</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.2148</v>
+        <v>-0.2149</v>
       </c>
       <c r="D603" t="n">
         <v>0.2215</v>
@@ -52869,7 +52869,7 @@
         <v>0.6578000000000001</v>
       </c>
       <c r="F603" t="n">
-        <v>-0.2148</v>
+        <v>-0.2149</v>
       </c>
       <c r="G603" t="n">
         <v>1.5694</v>
@@ -52949,7 +52949,7 @@
         <v>-0.1475</v>
       </c>
       <c r="D605" t="n">
-        <v>0.2166</v>
+        <v>0.2165</v>
       </c>
       <c r="E605" t="n">
         <v>0.5806</v>
@@ -53148,7 +53148,7 @@
         <v>0.4739</v>
       </c>
       <c r="M609" t="n">
-        <v>-0.3641</v>
+        <v>-0.3642</v>
       </c>
     </row>
     <row r="610">
@@ -53422,7 +53422,7 @@
         <v>-0.1414</v>
       </c>
       <c r="D616" t="n">
-        <v>0.1978</v>
+        <v>0.1977</v>
       </c>
       <c r="E616" t="n">
         <v>0.5369</v>
@@ -53492,7 +53492,7 @@
         <v>0.425</v>
       </c>
       <c r="M617" t="n">
-        <v>-0.1074</v>
+        <v>-0.1075</v>
       </c>
     </row>
     <row r="618">
@@ -53535,7 +53535,7 @@
         <v>0.4181</v>
       </c>
       <c r="M618" t="n">
-        <v>-0.1046</v>
+        <v>-0.1047</v>
       </c>
     </row>
     <row r="619">
@@ -53621,7 +53621,7 @@
         <v>0.3891</v>
       </c>
       <c r="M620" t="n">
-        <v>-0.1262</v>
+        <v>-0.1263</v>
       </c>
     </row>
     <row r="621">
@@ -53763,7 +53763,7 @@
         <v>0.5455</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.248</v>
+        <v>-0.2481</v>
       </c>
       <c r="D624" t="n">
         <v>0.1487</v>
@@ -53772,7 +53772,7 @@
         <v>0.5455</v>
       </c>
       <c r="F624" t="n">
-        <v>-0.248</v>
+        <v>-0.2481</v>
       </c>
       <c r="G624" t="n">
         <v>1.3915</v>
@@ -54008,7 +54008,7 @@
         <v>0.3526</v>
       </c>
       <c r="M629" t="n">
-        <v>0.0689</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="630">
@@ -54051,7 +54051,7 @@
         <v>0.4614</v>
       </c>
       <c r="M630" t="n">
-        <v>-0.003</v>
+        <v>-0.0031</v>
       </c>
     </row>
     <row r="631">
@@ -54193,16 +54193,16 @@
         <v>0.4602</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1701</v>
+        <v>-0.169</v>
       </c>
       <c r="D634" t="n">
-        <v>0.1451</v>
+        <v>0.1456</v>
       </c>
       <c r="E634" t="n">
         <v>0.4602</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1701</v>
+        <v>-0.169</v>
       </c>
       <c r="G634" t="n">
         <v>0.5974</v>
@@ -54223,7 +54223,7 @@
         <v>0.4206</v>
       </c>
       <c r="M634" t="n">
-        <v>0.3983</v>
+        <v>0.4014</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>+0.15  Broadly neutral</t>
+          <t>+0.14  Broadly neutral</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Monetary conditions score +0.46 (mildly accommodative) and liquidity conditions -0.17 (mildly restrictive); the combined index is +0.15 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-8.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
+          <t>Monetary conditions score +0.46 (mildly accommodative) and liquidity conditions -0.17 (mildly restrictive); the combined index is +0.14 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-8.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2701,7 +2701,7 @@
         <v>-1.295</v>
       </c>
       <c r="K172" t="n">
-        <v>-1.932</v>
+        <v>-1.931</v>
       </c>
     </row>
     <row r="173">
@@ -3195,7 +3195,7 @@
         <v>-1.15</v>
       </c>
       <c r="K210" t="n">
-        <v>-0.151</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="211">
@@ -3221,7 +3221,7 @@
         <v>-1.13</v>
       </c>
       <c r="K212" t="n">
-        <v>-0.015</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="213">
@@ -3325,7 +3325,7 @@
         <v>-0.443</v>
       </c>
       <c r="K220" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="221">
@@ -3338,7 +3338,7 @@
         <v>-0.899</v>
       </c>
       <c r="K221" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="222">
@@ -3377,7 +3377,7 @@
         <v>-0.39</v>
       </c>
       <c r="K224" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="225">
@@ -3455,7 +3455,7 @@
         <v>-0.431</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.403</v>
+        <v>-0.402</v>
       </c>
     </row>
     <row r="231">
@@ -3572,7 +3572,7 @@
         <v>-0.355</v>
       </c>
       <c r="K239" t="n">
-        <v>-1.264</v>
+        <v>-1.263</v>
       </c>
     </row>
     <row r="240">
@@ -3585,7 +3585,7 @@
         <v>-0.382</v>
       </c>
       <c r="K240" t="n">
-        <v>-1.177</v>
+        <v>-1.176</v>
       </c>
     </row>
     <row r="241">
@@ -3611,7 +3611,7 @@
         <v>-0.594</v>
       </c>
       <c r="K242" t="n">
-        <v>-1.307</v>
+        <v>-1.306</v>
       </c>
     </row>
     <row r="243">
@@ -3728,7 +3728,7 @@
         <v>-0.386</v>
       </c>
       <c r="K251" t="n">
-        <v>-1.096</v>
+        <v>-1.095</v>
       </c>
     </row>
     <row r="252">
@@ -3832,7 +3832,7 @@
         <v>0.025</v>
       </c>
       <c r="K259" t="n">
-        <v>-1.087</v>
+        <v>-1.086</v>
       </c>
     </row>
     <row r="260">
@@ -3962,7 +3962,7 @@
         <v>1.043</v>
       </c>
       <c r="K269" t="n">
-        <v>0.152</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="270">
@@ -3975,7 +3975,7 @@
         <v>0.317</v>
       </c>
       <c r="K270" t="n">
-        <v>0.411</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="271">
@@ -4131,7 +4131,7 @@
         <v>0.997</v>
       </c>
       <c r="K282" t="n">
-        <v>-0.125</v>
+        <v>-0.124</v>
       </c>
     </row>
     <row r="283">
@@ -4196,7 +4196,7 @@
         <v>0.068</v>
       </c>
       <c r="K287" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="288">
@@ -4313,7 +4313,7 @@
         <v>0.163</v>
       </c>
       <c r="K296" t="n">
-        <v>-1.577</v>
+        <v>-1.576</v>
       </c>
     </row>
     <row r="297">
@@ -4391,7 +4391,7 @@
         <v>0.23</v>
       </c>
       <c r="K302" t="n">
-        <v>-1.122</v>
+        <v>-1.123</v>
       </c>
     </row>
     <row r="303">
@@ -4404,7 +4404,7 @@
         <v>0.188</v>
       </c>
       <c r="K303" t="n">
-        <v>-1.024</v>
+        <v>-1.025</v>
       </c>
     </row>
     <row r="304">
@@ -4417,7 +4417,7 @@
         <v>0.135</v>
       </c>
       <c r="K304" t="n">
-        <v>-0.872</v>
+        <v>-0.873</v>
       </c>
     </row>
     <row r="305">
@@ -4443,7 +4443,7 @@
         <v>0.126</v>
       </c>
       <c r="K306" t="n">
-        <v>-0.128</v>
+        <v>-0.129</v>
       </c>
     </row>
     <row r="307">
@@ -4482,7 +4482,7 @@
         <v>0.114</v>
       </c>
       <c r="K309" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
     </row>
     <row r="310">
@@ -4508,7 +4508,7 @@
         <v>0.112</v>
       </c>
       <c r="K311" t="n">
-        <v>0.902</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="312">
@@ -4521,7 +4521,7 @@
         <v>0.099</v>
       </c>
       <c r="K312" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="313">
@@ -4560,7 +4560,7 @@
         <v>-0.226</v>
       </c>
       <c r="K315" t="n">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="316">
@@ -4586,7 +4586,7 @@
         <v>-0.18</v>
       </c>
       <c r="K317" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="318">
@@ -4612,7 +4612,7 @@
         <v>-0.24</v>
       </c>
       <c r="K319" t="n">
-        <v>0.411</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="320">
@@ -4638,7 +4638,7 @@
         <v>-0.129</v>
       </c>
       <c r="K321" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="322">
@@ -4664,7 +4664,7 @@
         <v>-0.167</v>
       </c>
       <c r="K323" t="n">
-        <v>-0.122</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="324">
@@ -4677,7 +4677,7 @@
         <v>-0.17</v>
       </c>
       <c r="K324" t="n">
-        <v>-0.255</v>
+        <v>-0.256</v>
       </c>
     </row>
     <row r="325">
@@ -4690,7 +4690,7 @@
         <v>-0.172</v>
       </c>
       <c r="K325" t="n">
-        <v>-0.24</v>
+        <v>-0.241</v>
       </c>
     </row>
     <row r="326">
@@ -4703,7 +4703,7 @@
         <v>-0.119</v>
       </c>
       <c r="K326" t="n">
-        <v>-0.115</v>
+        <v>-0.116</v>
       </c>
     </row>
     <row r="327">
@@ -4716,7 +4716,7 @@
         <v>-0.073</v>
       </c>
       <c r="K327" t="n">
-        <v>-0.262</v>
+        <v>-0.263</v>
       </c>
     </row>
     <row r="328">
@@ -4729,7 +4729,7 @@
         <v>-0.121</v>
       </c>
       <c r="K328" t="n">
-        <v>-0.204</v>
+        <v>-0.205</v>
       </c>
     </row>
     <row r="329">
@@ -4742,7 +4742,7 @@
         <v>-0.171</v>
       </c>
       <c r="K329" t="n">
-        <v>-0.283</v>
+        <v>-0.284</v>
       </c>
     </row>
     <row r="330">
@@ -4755,7 +4755,7 @@
         <v>-0.124</v>
       </c>
       <c r="K330" t="n">
-        <v>-0.246</v>
+        <v>-0.247</v>
       </c>
     </row>
     <row r="331">
@@ -4781,7 +4781,7 @@
         <v>-0.075</v>
       </c>
       <c r="K332" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="333">
@@ -4807,7 +4807,7 @@
         <v>-0.12</v>
       </c>
       <c r="K334" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="335">
@@ -4846,7 +4846,7 @@
         <v>-0.165</v>
       </c>
       <c r="K337" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="338">
@@ -4872,7 +4872,7 @@
         <v>-0.166</v>
       </c>
       <c r="K339" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="340">
@@ -4911,7 +4911,7 @@
         <v>-0.122</v>
       </c>
       <c r="K342" t="n">
-        <v>0.805</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="343">
@@ -4963,7 +4963,7 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="K346" t="n">
-        <v>1.253</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="347">
@@ -5106,7 +5106,7 @@
         <v>-0.529</v>
       </c>
       <c r="K357" t="n">
-        <v>-0.214</v>
+        <v>-0.215</v>
       </c>
     </row>
     <row r="358">
@@ -5145,7 +5145,7 @@
         <v>-0.476</v>
       </c>
       <c r="K360" t="n">
-        <v>-0.107</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="361">
@@ -5158,7 +5158,7 @@
         <v>-0.45</v>
       </c>
       <c r="K361" t="n">
-        <v>-0.402</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="362">
@@ -5184,7 +5184,7 @@
         <v>-0.453</v>
       </c>
       <c r="K363" t="n">
-        <v>-0.308</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="364">
@@ -5197,7 +5197,7 @@
         <v>-0.549</v>
       </c>
       <c r="K364" t="n">
-        <v>-0.335</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="365">
@@ -5210,7 +5210,7 @@
         <v>-0.537</v>
       </c>
       <c r="K365" t="n">
-        <v>-0.294</v>
+        <v>-0.295</v>
       </c>
     </row>
     <row r="366">
@@ -5223,7 +5223,7 @@
         <v>-0.541</v>
       </c>
       <c r="K366" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="367">
@@ -5275,7 +5275,7 @@
         <v>-0.576</v>
       </c>
       <c r="K370" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="371">
@@ -5938,7 +5938,7 @@
         <v>-0.583</v>
       </c>
       <c r="K421" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="422">
@@ -6029,7 +6029,7 @@
         <v>-0.716</v>
       </c>
       <c r="K428" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="429">
@@ -6120,7 +6120,7 @@
         <v>-0.611</v>
       </c>
       <c r="K435" t="n">
-        <v>0.296</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="436">
@@ -6133,7 +6133,7 @@
         <v>-0.61</v>
       </c>
       <c r="K436" t="n">
-        <v>0.276</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="437">
@@ -6211,7 +6211,7 @@
         <v>-0.399</v>
       </c>
       <c r="K442" t="n">
-        <v>0.296</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="443">
@@ -6406,7 +6406,7 @@
         <v>-0.482</v>
       </c>
       <c r="K457" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="458">
@@ -6471,7 +6471,7 @@
         <v>-0.047</v>
       </c>
       <c r="K462" t="n">
-        <v>0.67</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="463">
@@ -6835,7 +6835,7 @@
         <v>0.794</v>
       </c>
       <c r="K490" t="n">
-        <v>0.901</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="491">
@@ -7992,7 +7992,7 @@
         <v>0.647</v>
       </c>
       <c r="K579" t="n">
-        <v>-0.277</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="580">
@@ -8408,7 +8408,7 @@
         <v>0.533</v>
       </c>
       <c r="K611" t="n">
-        <v>-0.22</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="612">
@@ -8421,7 +8421,7 @@
         <v>0.51</v>
       </c>
       <c r="K612" t="n">
-        <v>-0.229</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="613">
@@ -8499,7 +8499,7 @@
         <v>0.432</v>
       </c>
       <c r="K618" t="n">
-        <v>-0.265</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="619">
@@ -8512,7 +8512,7 @@
         <v>0.386</v>
       </c>
       <c r="K619" t="n">
-        <v>-0.307</v>
+        <v>-0.308</v>
       </c>
     </row>
     <row r="620">
@@ -8525,7 +8525,7 @@
         <v>0.429</v>
       </c>
       <c r="K620" t="n">
-        <v>-0.277</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="621">
@@ -8577,7 +8577,7 @@
         <v>0.425</v>
       </c>
       <c r="K624" t="n">
-        <v>-0.211</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="625">
@@ -8590,7 +8590,7 @@
         <v>0.419</v>
       </c>
       <c r="K625" t="n">
-        <v>-0.192</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="626">
@@ -8603,7 +8603,7 @@
         <v>0.46</v>
       </c>
       <c r="K626" t="n">
-        <v>-0.169</v>
+        <v>-0.171</v>
       </c>
     </row>
   </sheetData>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.189</v>
+        <v>10.608</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.08</v>
+        <v>1.077</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.9</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="14">
@@ -34295,10 +34295,10 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="G632" t="n">
-        <v>1.1567</v>
+        <v>1.14</v>
       </c>
       <c r="H632" t="n">
-        <v>10.3951</v>
+        <v>10.4066</v>
       </c>
       <c r="I632" t="n">
         <v>1.3419</v>
@@ -34365,10 +34365,10 @@
         <v>0.0067</v>
       </c>
       <c r="G633" t="n">
-        <v>1.1442</v>
+        <v>1.0749</v>
       </c>
       <c r="H633" t="n">
-        <v>10.2998</v>
+        <v>10.3669</v>
       </c>
       <c r="I633" t="n">
         <v>1.2575</v>
@@ -34435,10 +34435,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.0797</v>
+        <v>1.0769</v>
       </c>
       <c r="H634" t="n">
-        <v>10.1887</v>
+        <v>10.608</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -37100,7 +37100,7 @@
         <v>-2.871</v>
       </c>
       <c r="D164" t="n">
-        <v>-2.0424</v>
+        <v>-2.0423</v>
       </c>
       <c r="E164" t="n">
         <v>-1.2137</v>
@@ -37181,7 +37181,7 @@
         <v>-1.4179</v>
       </c>
       <c r="C167" t="n">
-        <v>-3.1729</v>
+        <v>-3.1728</v>
       </c>
       <c r="D167" t="n">
         <v>-2.2954</v>
@@ -37190,13 +37190,13 @@
         <v>-1.4179</v>
       </c>
       <c r="F167" t="n">
-        <v>-3.1729</v>
+        <v>-3.1728</v>
       </c>
       <c r="G167" t="n">
         <v>-1.4179</v>
       </c>
       <c r="M167" t="n">
-        <v>-3.1729</v>
+        <v>-3.1728</v>
       </c>
     </row>
     <row r="168">
@@ -37405,7 +37405,7 @@
         <v>-1.2863</v>
       </c>
       <c r="C175" t="n">
-        <v>-3.924</v>
+        <v>-3.9241</v>
       </c>
       <c r="D175" t="n">
         <v>-2.6052</v>
@@ -37414,13 +37414,13 @@
         <v>-1.2863</v>
       </c>
       <c r="F175" t="n">
-        <v>-3.924</v>
+        <v>-3.9241</v>
       </c>
       <c r="G175" t="n">
         <v>-1.2863</v>
       </c>
       <c r="M175" t="n">
-        <v>-3.924</v>
+        <v>-3.9241</v>
       </c>
     </row>
     <row r="176">
@@ -37517,7 +37517,7 @@
         <v>-1.4402</v>
       </c>
       <c r="C179" t="n">
-        <v>-2.7856</v>
+        <v>-2.7855</v>
       </c>
       <c r="D179" t="n">
         <v>-2.1129</v>
@@ -37526,13 +37526,13 @@
         <v>-1.4402</v>
       </c>
       <c r="F179" t="n">
-        <v>-2.7856</v>
+        <v>-2.7855</v>
       </c>
       <c r="G179" t="n">
         <v>-1.4402</v>
       </c>
       <c r="M179" t="n">
-        <v>-2.7856</v>
+        <v>-2.7855</v>
       </c>
     </row>
     <row r="180">
@@ -37629,22 +37629,22 @@
         <v>-1.2675</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.9796</v>
+        <v>-0.9795</v>
       </c>
       <c r="D183" t="n">
-        <v>-1.1236</v>
+        <v>-1.1235</v>
       </c>
       <c r="E183" t="n">
         <v>-1.2675</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.9796</v>
+        <v>-0.9795</v>
       </c>
       <c r="G183" t="n">
         <v>-1.2675</v>
       </c>
       <c r="M183" t="n">
-        <v>-0.9796</v>
+        <v>-0.9795</v>
       </c>
     </row>
     <row r="184">
@@ -37657,22 +37657,22 @@
         <v>-1.2863</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.9123</v>
+        <v>-0.9122</v>
       </c>
       <c r="D184" t="n">
-        <v>-1.0993</v>
+        <v>-1.0992</v>
       </c>
       <c r="E184" t="n">
         <v>-1.2863</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.9123</v>
+        <v>-0.9122</v>
       </c>
       <c r="G184" t="n">
         <v>-1.2863</v>
       </c>
       <c r="M184" t="n">
-        <v>-0.9123</v>
+        <v>-0.9122</v>
       </c>
     </row>
     <row r="185">
@@ -37685,22 +37685,22 @@
         <v>-0.7036</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.8892</v>
+        <v>-0.8891</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.7964</v>
+        <v>-0.7963</v>
       </c>
       <c r="E185" t="n">
         <v>-0.7036</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.8892</v>
+        <v>-0.8891</v>
       </c>
       <c r="G185" t="n">
         <v>-0.7036</v>
       </c>
       <c r="M185" t="n">
-        <v>-0.8892</v>
+        <v>-0.8891</v>
       </c>
     </row>
     <row r="186">
@@ -37713,7 +37713,7 @@
         <v>-0.6945</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.7699</v>
+        <v>-0.7698</v>
       </c>
       <c r="D186" t="n">
         <v>-0.7322</v>
@@ -37722,13 +37722,13 @@
         <v>-0.6945</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.7699</v>
+        <v>-0.7698</v>
       </c>
       <c r="G186" t="n">
         <v>-0.6945</v>
       </c>
       <c r="M186" t="n">
-        <v>-0.7699</v>
+        <v>-0.7698</v>
       </c>
     </row>
     <row r="187">
@@ -37741,7 +37741,7 @@
         <v>-0.786</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.7325</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="D187" t="n">
         <v>-0.7592</v>
@@ -37750,13 +37750,13 @@
         <v>-0.786</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.7325</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="G187" t="n">
         <v>-0.786</v>
       </c>
       <c r="M187" t="n">
-        <v>-0.7325</v>
+        <v>-0.7324000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -37769,7 +37769,7 @@
         <v>-0.7713</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.4738</v>
+        <v>-0.4737</v>
       </c>
       <c r="D188" t="n">
         <v>-0.6225000000000001</v>
@@ -37778,13 +37778,13 @@
         <v>-0.7713</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.4738</v>
+        <v>-0.4737</v>
       </c>
       <c r="G188" t="n">
         <v>-0.7713</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.4738</v>
+        <v>-0.4737</v>
       </c>
     </row>
     <row r="189">
@@ -37797,22 +37797,22 @@
         <v>-0.8016</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.4729</v>
+        <v>-0.4728</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.6373</v>
+        <v>-0.6372</v>
       </c>
       <c r="E189" t="n">
         <v>-0.8016</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.4729</v>
+        <v>-0.4728</v>
       </c>
       <c r="G189" t="n">
         <v>-0.8016</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.4729</v>
+        <v>-0.4728</v>
       </c>
     </row>
     <row r="190">
@@ -37825,22 +37825,22 @@
         <v>-0.8606</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3754</v>
+        <v>-0.3753</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.618</v>
+        <v>-0.6179</v>
       </c>
       <c r="E190" t="n">
         <v>-0.8606</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.3754</v>
+        <v>-0.3753</v>
       </c>
       <c r="G190" t="n">
         <v>-0.8606</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.3754</v>
+        <v>-0.3753</v>
       </c>
     </row>
     <row r="191">
@@ -37853,7 +37853,7 @@
         <v>-1.0599</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.2022</v>
+        <v>-0.2021</v>
       </c>
       <c r="D191" t="n">
         <v>-0.631</v>
@@ -37862,13 +37862,13 @@
         <v>-1.0599</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.2022</v>
+        <v>-0.2021</v>
       </c>
       <c r="G191" t="n">
         <v>-1.0599</v>
       </c>
       <c r="M191" t="n">
-        <v>-0.2022</v>
+        <v>-0.2021</v>
       </c>
     </row>
     <row r="192">
@@ -37881,22 +37881,22 @@
         <v>-1.2335</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.097</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.6653</v>
+        <v>-0.6652</v>
       </c>
       <c r="E192" t="n">
         <v>-1.2335</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.097</v>
       </c>
       <c r="G192" t="n">
         <v>-1.2335</v>
       </c>
       <c r="M192" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.097</v>
       </c>
     </row>
     <row r="193">
@@ -37909,7 +37909,7 @@
         <v>-1.4151</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0896</v>
+        <v>0.0898</v>
       </c>
       <c r="D193" t="n">
         <v>-0.6627</v>
@@ -37918,13 +37918,13 @@
         <v>-1.4151</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0896</v>
+        <v>0.0898</v>
       </c>
       <c r="G193" t="n">
         <v>-1.4151</v>
       </c>
       <c r="M193" t="n">
-        <v>0.0896</v>
+        <v>0.0898</v>
       </c>
     </row>
     <row r="194">
@@ -37937,7 +37937,7 @@
         <v>-1.2593</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.7313</v>
       </c>
       <c r="D194" t="n">
         <v>-0.9953</v>
@@ -37946,13 +37946,13 @@
         <v>-1.2593</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.7313</v>
       </c>
       <c r="G194" t="n">
         <v>-1.2593</v>
       </c>
       <c r="M194" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.7313</v>
       </c>
     </row>
     <row r="195">
@@ -37965,22 +37965,22 @@
         <v>-1.3702</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7199</v>
+        <v>-0.7198</v>
       </c>
       <c r="D195" t="n">
-        <v>-1.0451</v>
+        <v>-1.045</v>
       </c>
       <c r="E195" t="n">
         <v>-1.3702</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7199</v>
+        <v>-0.7198</v>
       </c>
       <c r="G195" t="n">
         <v>-1.3702</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7199</v>
+        <v>-0.7198</v>
       </c>
     </row>
     <row r="196">
@@ -37993,22 +37993,22 @@
         <v>-1.4857</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.8718</v>
+        <v>-0.8717</v>
       </c>
       <c r="D196" t="n">
-        <v>-1.1788</v>
+        <v>-1.1787</v>
       </c>
       <c r="E196" t="n">
         <v>-1.4857</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.8718</v>
+        <v>-0.8717</v>
       </c>
       <c r="G196" t="n">
         <v>-1.4857</v>
       </c>
       <c r="M196" t="n">
-        <v>-0.8718</v>
+        <v>-0.8717</v>
       </c>
     </row>
     <row r="197">
@@ -38024,7 +38024,7 @@
         <v>-0.82</v>
       </c>
       <c r="D197" t="n">
-        <v>-1.448</v>
+        <v>-1.4479</v>
       </c>
       <c r="E197" t="n">
         <v>-2.0759</v>
@@ -38049,7 +38049,7 @@
         <v>-2.0185</v>
       </c>
       <c r="C198" t="n">
-        <v>-1.1529</v>
+        <v>-1.1528</v>
       </c>
       <c r="D198" t="n">
         <v>-1.5857</v>
@@ -38058,13 +38058,13 @@
         <v>-2.0185</v>
       </c>
       <c r="F198" t="n">
-        <v>-1.1529</v>
+        <v>-1.1528</v>
       </c>
       <c r="G198" t="n">
         <v>-2.0185</v>
       </c>
       <c r="M198" t="n">
-        <v>-1.1529</v>
+        <v>-1.1528</v>
       </c>
     </row>
     <row r="199">
@@ -38105,7 +38105,7 @@
         <v>-2.1567</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.0841</v>
+        <v>-1.084</v>
       </c>
       <c r="D200" t="n">
         <v>-1.6204</v>
@@ -38114,13 +38114,13 @@
         <v>-2.1567</v>
       </c>
       <c r="F200" t="n">
-        <v>-1.0841</v>
+        <v>-1.084</v>
       </c>
       <c r="G200" t="n">
         <v>-2.1567</v>
       </c>
       <c r="M200" t="n">
-        <v>-1.0841</v>
+        <v>-1.084</v>
       </c>
     </row>
     <row r="201">
@@ -38133,7 +38133,7 @@
         <v>-2.2366</v>
       </c>
       <c r="C201" t="n">
-        <v>-1.4038</v>
+        <v>-1.4037</v>
       </c>
       <c r="D201" t="n">
         <v>-1.8202</v>
@@ -38142,13 +38142,13 @@
         <v>-2.2366</v>
       </c>
       <c r="F201" t="n">
-        <v>-1.4038</v>
+        <v>-1.4037</v>
       </c>
       <c r="G201" t="n">
         <v>-2.2366</v>
       </c>
       <c r="M201" t="n">
-        <v>-1.4038</v>
+        <v>-1.4037</v>
       </c>
     </row>
     <row r="202">
@@ -38161,7 +38161,7 @@
         <v>-2.3232</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.4421</v>
+        <v>-1.442</v>
       </c>
       <c r="D202" t="n">
         <v>-1.8826</v>
@@ -38170,13 +38170,13 @@
         <v>-2.3232</v>
       </c>
       <c r="F202" t="n">
-        <v>-1.4421</v>
+        <v>-1.442</v>
       </c>
       <c r="G202" t="n">
         <v>-2.3232</v>
       </c>
       <c r="M202" t="n">
-        <v>-1.4421</v>
+        <v>-1.442</v>
       </c>
     </row>
     <row r="203">
@@ -38189,22 +38189,22 @@
         <v>-2.0213</v>
       </c>
       <c r="C203" t="n">
-        <v>-1.84</v>
+        <v>-1.8399</v>
       </c>
       <c r="D203" t="n">
-        <v>-1.9307</v>
+        <v>-1.9306</v>
       </c>
       <c r="E203" t="n">
         <v>-2.0213</v>
       </c>
       <c r="F203" t="n">
-        <v>-1.84</v>
+        <v>-1.8399</v>
       </c>
       <c r="G203" t="n">
         <v>-2.0213</v>
       </c>
       <c r="M203" t="n">
-        <v>-1.84</v>
+        <v>-1.8399</v>
       </c>
     </row>
     <row r="204">
@@ -38469,7 +38469,7 @@
         <v>-1.6224</v>
       </c>
       <c r="C213" t="n">
-        <v>-1.3152</v>
+        <v>-1.3151</v>
       </c>
       <c r="D213" t="n">
         <v>-1.4688</v>
@@ -38478,13 +38478,13 @@
         <v>-1.6224</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.3152</v>
+        <v>-1.3151</v>
       </c>
       <c r="G213" t="n">
         <v>-1.6224</v>
       </c>
       <c r="M213" t="n">
-        <v>-1.3152</v>
+        <v>-1.3151</v>
       </c>
     </row>
     <row r="214">
@@ -38500,7 +38500,7 @@
         <v>-0.7331</v>
       </c>
       <c r="D214" t="n">
-        <v>-1.1178</v>
+        <v>-1.1177</v>
       </c>
       <c r="E214" t="n">
         <v>-1.5024</v>
@@ -38525,7 +38525,7 @@
         <v>-1.5327</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.6752</v>
+        <v>-0.6751</v>
       </c>
       <c r="D215" t="n">
         <v>-1.1039</v>
@@ -38534,13 +38534,13 @@
         <v>-1.5327</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.6752</v>
+        <v>-0.6751</v>
       </c>
       <c r="G215" t="n">
         <v>-1.5327</v>
       </c>
       <c r="M215" t="n">
-        <v>-0.6752</v>
+        <v>-0.6751</v>
       </c>
     </row>
     <row r="216">
@@ -38553,22 +38553,22 @@
         <v>-1.4424</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.5052</v>
+        <v>-0.5051</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.9738</v>
+        <v>-0.9737</v>
       </c>
       <c r="E216" t="n">
         <v>-1.4424</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.5052</v>
+        <v>-0.5051</v>
       </c>
       <c r="G216" t="n">
         <v>-1.4424</v>
       </c>
       <c r="M216" t="n">
-        <v>-0.5052</v>
+        <v>-0.5051</v>
       </c>
     </row>
     <row r="217">
@@ -38581,22 +38581,22 @@
         <v>-1.4362</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.0901</v>
+        <v>-0.09</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.7632</v>
+        <v>-0.7631</v>
       </c>
       <c r="E217" t="n">
         <v>-1.4362</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.0901</v>
+        <v>-0.09</v>
       </c>
       <c r="G217" t="n">
         <v>-1.4362</v>
       </c>
       <c r="M217" t="n">
-        <v>-0.0901</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="218">
@@ -38609,22 +38609,22 @@
         <v>-1.1496</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1505</v>
+        <v>-0.1504</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.6501</v>
+        <v>-0.65</v>
       </c>
       <c r="E218" t="n">
         <v>-1.1496</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.1505</v>
+        <v>-0.1504</v>
       </c>
       <c r="G218" t="n">
         <v>-1.1496</v>
       </c>
       <c r="M218" t="n">
-        <v>-0.1505</v>
+        <v>-0.1504</v>
       </c>
     </row>
     <row r="219">
@@ -38637,22 +38637,22 @@
         <v>-1.0911</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.2079</v>
+        <v>-0.2078</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.6495</v>
+        <v>-0.6494</v>
       </c>
       <c r="E219" t="n">
         <v>-1.0911</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.2079</v>
+        <v>-0.2078</v>
       </c>
       <c r="G219" t="n">
         <v>-1.0911</v>
       </c>
       <c r="M219" t="n">
-        <v>-0.2079</v>
+        <v>-0.2078</v>
       </c>
     </row>
     <row r="220">
@@ -38665,7 +38665,7 @@
         <v>-1.1299</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.0146</v>
+        <v>-0.0145</v>
       </c>
       <c r="D220" t="n">
         <v>-0.5722</v>
@@ -38674,13 +38674,13 @@
         <v>-1.1299</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.0146</v>
+        <v>-0.0145</v>
       </c>
       <c r="G220" t="n">
         <v>-1.1299</v>
       </c>
       <c r="M220" t="n">
-        <v>-0.0146</v>
+        <v>-0.0145</v>
       </c>
     </row>
     <row r="221">
@@ -38693,7 +38693,7 @@
         <v>-0.6687</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.1351</v>
+        <v>-0.135</v>
       </c>
       <c r="D221" t="n">
         <v>-0.4019</v>
@@ -38702,13 +38702,13 @@
         <v>-0.6687</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.1351</v>
+        <v>-0.135</v>
       </c>
       <c r="G221" t="n">
         <v>-0.6687</v>
       </c>
       <c r="M221" t="n">
-        <v>-0.1351</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="222">
@@ -38721,22 +38721,22 @@
         <v>-0.7229</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.1517</v>
+        <v>-0.1516</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.4373</v>
+        <v>-0.4372</v>
       </c>
       <c r="E222" t="n">
         <v>-0.7229</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.1517</v>
+        <v>-0.1516</v>
       </c>
       <c r="G222" t="n">
         <v>-0.7229</v>
       </c>
       <c r="M222" t="n">
-        <v>-0.1517</v>
+        <v>-0.1516</v>
       </c>
     </row>
     <row r="223">
@@ -38749,22 +38749,22 @@
         <v>-0.7151</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.0035</v>
+        <v>-0.0034</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.3593</v>
+        <v>-0.3592</v>
       </c>
       <c r="E223" t="n">
         <v>-0.7151</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.0035</v>
+        <v>-0.0034</v>
       </c>
       <c r="G223" t="n">
         <v>-0.7151</v>
       </c>
       <c r="M223" t="n">
-        <v>-0.0035</v>
+        <v>-0.0034</v>
       </c>
     </row>
     <row r="224">
@@ -38777,7 +38777,7 @@
         <v>-0.7131</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.0439</v>
+        <v>-0.0438</v>
       </c>
       <c r="D224" t="n">
         <v>-0.3785</v>
@@ -38786,13 +38786,13 @@
         <v>-0.7131</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.0439</v>
+        <v>-0.0438</v>
       </c>
       <c r="G224" t="n">
         <v>-0.7131</v>
       </c>
       <c r="M224" t="n">
-        <v>-0.0439</v>
+        <v>-0.0438</v>
       </c>
     </row>
     <row r="225">
@@ -38805,7 +38805,7 @@
         <v>-0.4995</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="D225" t="n">
         <v>-0.2903</v>
@@ -38814,13 +38814,13 @@
         <v>-0.4995</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="G225" t="n">
         <v>-0.4995</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="226">
@@ -38833,22 +38833,22 @@
         <v>-0.4998</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.0033</v>
+        <v>-0.0032</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.2516</v>
+        <v>-0.2515</v>
       </c>
       <c r="E226" t="n">
         <v>-0.4998</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.0033</v>
+        <v>-0.0032</v>
       </c>
       <c r="G226" t="n">
         <v>-0.4998</v>
       </c>
       <c r="M226" t="n">
-        <v>-0.0033</v>
+        <v>-0.0032</v>
       </c>
     </row>
     <row r="227">
@@ -38861,22 +38861,22 @@
         <v>-0.4962</v>
       </c>
       <c r="C227" t="n">
-        <v>0.0048</v>
+        <v>0.0049</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.2457</v>
+        <v>-0.2456</v>
       </c>
       <c r="E227" t="n">
         <v>-0.4962</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0048</v>
+        <v>0.0049</v>
       </c>
       <c r="G227" t="n">
         <v>-0.4962</v>
       </c>
       <c r="M227" t="n">
-        <v>0.0048</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="228">
@@ -38889,7 +38889,7 @@
         <v>-0.4433</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0174</v>
+        <v>0.0176</v>
       </c>
       <c r="D228" t="n">
         <v>-0.2129</v>
@@ -38898,13 +38898,13 @@
         <v>-0.4433</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0174</v>
+        <v>0.0176</v>
       </c>
       <c r="G228" t="n">
         <v>-0.4433</v>
       </c>
       <c r="M228" t="n">
-        <v>0.0174</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="229">
@@ -38917,7 +38917,7 @@
         <v>-0.8986</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0244</v>
+        <v>0.0245</v>
       </c>
       <c r="D229" t="n">
         <v>-0.4371</v>
@@ -38926,13 +38926,13 @@
         <v>-0.8986</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0244</v>
+        <v>0.0245</v>
       </c>
       <c r="G229" t="n">
         <v>-0.8986</v>
       </c>
       <c r="M229" t="n">
-        <v>0.0244</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="230">
@@ -38945,7 +38945,7 @@
         <v>-0.6155</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0718</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="D230" t="n">
         <v>-0.2718</v>
@@ -38954,13 +38954,13 @@
         <v>-0.6155</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0718</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G230" t="n">
         <v>-0.6155</v>
       </c>
       <c r="M230" t="n">
-        <v>0.0718</v>
+        <v>0.07190000000000001</v>
       </c>
     </row>
     <row r="231">
@@ -38973,22 +38973,22 @@
         <v>-0.4068</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.2036</v>
+        <v>-0.2035</v>
       </c>
       <c r="E231" t="n">
         <v>-0.4068</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="G231" t="n">
         <v>-0.4068</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
     </row>
     <row r="232">
@@ -39001,22 +39001,22 @@
         <v>-0.3898</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.0025</v>
+        <v>-0.0024</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.1962</v>
+        <v>-0.1961</v>
       </c>
       <c r="E232" t="n">
         <v>-0.3898</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.0025</v>
+        <v>-0.0024</v>
       </c>
       <c r="G232" t="n">
         <v>-0.3898</v>
       </c>
       <c r="M232" t="n">
-        <v>-0.0025</v>
+        <v>-0.0024</v>
       </c>
     </row>
     <row r="233">
@@ -39029,7 +39029,7 @@
         <v>-0.5581</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.1151</v>
+        <v>-0.115</v>
       </c>
       <c r="D233" t="n">
         <v>-0.3366</v>
@@ -39038,13 +39038,13 @@
         <v>-0.5581</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.1151</v>
+        <v>-0.115</v>
       </c>
       <c r="G233" t="n">
         <v>-0.5581</v>
       </c>
       <c r="M233" t="n">
-        <v>-0.1151</v>
+        <v>-0.115</v>
       </c>
     </row>
     <row r="234">
@@ -39057,7 +39057,7 @@
         <v>-0.6117</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.3814</v>
+        <v>-0.3813</v>
       </c>
       <c r="D234" t="n">
         <v>-0.4965</v>
@@ -39066,13 +39066,13 @@
         <v>-0.6117</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.3814</v>
+        <v>-0.3813</v>
       </c>
       <c r="G234" t="n">
         <v>-0.6117</v>
       </c>
       <c r="M234" t="n">
-        <v>-0.3814</v>
+        <v>-0.3813</v>
       </c>
     </row>
     <row r="235">
@@ -39085,7 +39085,7 @@
         <v>-0.592</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.3814</v>
+        <v>-0.3813</v>
       </c>
       <c r="D235" t="n">
         <v>-0.4867</v>
@@ -39094,13 +39094,13 @@
         <v>-0.592</v>
       </c>
       <c r="F235" t="n">
-        <v>-0.3814</v>
+        <v>-0.3813</v>
       </c>
       <c r="G235" t="n">
         <v>-0.592</v>
       </c>
       <c r="M235" t="n">
-        <v>-0.3814</v>
+        <v>-0.3813</v>
       </c>
     </row>
     <row r="236">
@@ -39113,7 +39113,7 @@
         <v>-0.5683</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.4533</v>
+        <v>-0.4532</v>
       </c>
       <c r="D236" t="n">
         <v>-0.5108</v>
@@ -39122,13 +39122,13 @@
         <v>-0.5683</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.4533</v>
+        <v>-0.4532</v>
       </c>
       <c r="G236" t="n">
         <v>-0.5683</v>
       </c>
       <c r="M236" t="n">
-        <v>-0.4533</v>
+        <v>-0.4532</v>
       </c>
     </row>
     <row r="237">
@@ -39141,7 +39141,7 @@
         <v>-0.5061</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.3537</v>
+        <v>-0.3536</v>
       </c>
       <c r="D237" t="n">
         <v>-0.4299</v>
@@ -39150,13 +39150,13 @@
         <v>-0.5061</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.3537</v>
+        <v>-0.3536</v>
       </c>
       <c r="G237" t="n">
         <v>-0.5061</v>
       </c>
       <c r="M237" t="n">
-        <v>-0.3537</v>
+        <v>-0.3536</v>
       </c>
     </row>
     <row r="238">
@@ -39169,7 +39169,7 @@
         <v>-0.4305</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.4026</v>
+        <v>-0.4025</v>
       </c>
       <c r="D238" t="n">
         <v>-0.4165</v>
@@ -39178,13 +39178,13 @@
         <v>-0.4305</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.4026</v>
+        <v>-0.4025</v>
       </c>
       <c r="G238" t="n">
         <v>-0.4305</v>
       </c>
       <c r="M238" t="n">
-        <v>-0.4026</v>
+        <v>-0.4025</v>
       </c>
     </row>
     <row r="239">
@@ -39197,7 +39197,7 @@
         <v>-0.2922</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.4433</v>
+        <v>-0.4432</v>
       </c>
       <c r="D239" t="n">
         <v>-0.3677</v>
@@ -39206,13 +39206,13 @@
         <v>-0.2922</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.4433</v>
+        <v>-0.4432</v>
       </c>
       <c r="G239" t="n">
         <v>-0.2922</v>
       </c>
       <c r="M239" t="n">
-        <v>-0.4433</v>
+        <v>-0.4432</v>
       </c>
     </row>
     <row r="240">
@@ -39225,7 +39225,7 @@
         <v>-0.3254</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.4707</v>
+        <v>-0.4706</v>
       </c>
       <c r="D240" t="n">
         <v>-0.398</v>
@@ -39234,13 +39234,13 @@
         <v>-0.3254</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.4707</v>
+        <v>-0.4706</v>
       </c>
       <c r="G240" t="n">
         <v>-0.3254</v>
       </c>
       <c r="M240" t="n">
-        <v>-0.4707</v>
+        <v>-0.4706</v>
       </c>
     </row>
     <row r="241">
@@ -39253,7 +39253,7 @@
         <v>-0.4323</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.5108</v>
+        <v>-0.5107</v>
       </c>
       <c r="D241" t="n">
         <v>-0.4715</v>
@@ -39262,13 +39262,13 @@
         <v>-0.4323</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.5108</v>
+        <v>-0.5107</v>
       </c>
       <c r="G241" t="n">
         <v>-0.4323</v>
       </c>
       <c r="M241" t="n">
-        <v>-0.5108</v>
+        <v>-0.5107</v>
       </c>
     </row>
     <row r="242">
@@ -39281,7 +39281,7 @@
         <v>-0.2545</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.7211</v>
+        <v>-0.721</v>
       </c>
       <c r="D242" t="n">
         <v>-0.4878</v>
@@ -39290,13 +39290,13 @@
         <v>-0.2545</v>
       </c>
       <c r="F242" t="n">
-        <v>-0.7211</v>
+        <v>-0.721</v>
       </c>
       <c r="G242" t="n">
         <v>-0.2545</v>
       </c>
       <c r="M242" t="n">
-        <v>-0.7211</v>
+        <v>-0.721</v>
       </c>
     </row>
     <row r="243">
@@ -39309,22 +39309,22 @@
         <v>-0.3303</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.9363</v>
+        <v>-0.9362</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.6333</v>
+        <v>-0.6332</v>
       </c>
       <c r="E243" t="n">
         <v>-0.3303</v>
       </c>
       <c r="F243" t="n">
-        <v>-0.9363</v>
+        <v>-0.9362</v>
       </c>
       <c r="G243" t="n">
         <v>-0.3303</v>
       </c>
       <c r="M243" t="n">
-        <v>-0.9363</v>
+        <v>-0.9362</v>
       </c>
     </row>
     <row r="244">
@@ -39365,7 +39365,7 @@
         <v>-0.3567</v>
       </c>
       <c r="C245" t="n">
-        <v>-1.1923</v>
+        <v>-1.1922</v>
       </c>
       <c r="D245" t="n">
         <v>-0.7745</v>
@@ -39374,13 +39374,13 @@
         <v>-0.3567</v>
       </c>
       <c r="F245" t="n">
-        <v>-1.1923</v>
+        <v>-1.1922</v>
       </c>
       <c r="G245" t="n">
         <v>-0.3567</v>
       </c>
       <c r="M245" t="n">
-        <v>-1.1923</v>
+        <v>-1.1922</v>
       </c>
     </row>
     <row r="246">
@@ -39393,7 +39393,7 @@
         <v>-0.247</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.075</v>
+        <v>-1.0749</v>
       </c>
       <c r="D246" t="n">
         <v>-0.661</v>
@@ -39402,13 +39402,13 @@
         <v>-0.247</v>
       </c>
       <c r="F246" t="n">
-        <v>-1.075</v>
+        <v>-1.0749</v>
       </c>
       <c r="G246" t="n">
         <v>-0.247</v>
       </c>
       <c r="M246" t="n">
-        <v>-1.075</v>
+        <v>-1.0749</v>
       </c>
     </row>
     <row r="247">
@@ -39421,7 +39421,7 @@
         <v>-0.3549</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.2635</v>
+        <v>-1.2634</v>
       </c>
       <c r="D247" t="n">
         <v>-0.8092</v>
@@ -39430,13 +39430,13 @@
         <v>-0.3549</v>
       </c>
       <c r="F247" t="n">
-        <v>-1.2635</v>
+        <v>-1.2634</v>
       </c>
       <c r="G247" t="n">
         <v>-0.3549</v>
       </c>
       <c r="M247" t="n">
-        <v>-1.2635</v>
+        <v>-1.2634</v>
       </c>
     </row>
     <row r="248">
@@ -39449,22 +39449,22 @@
         <v>-0.3822</v>
       </c>
       <c r="C248" t="n">
-        <v>-1.1766</v>
+        <v>-1.1765</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.7794</v>
+        <v>-0.7793</v>
       </c>
       <c r="E248" t="n">
         <v>-0.3822</v>
       </c>
       <c r="F248" t="n">
-        <v>-1.1766</v>
+        <v>-1.1765</v>
       </c>
       <c r="G248" t="n">
         <v>-0.3822</v>
       </c>
       <c r="M248" t="n">
-        <v>-1.1766</v>
+        <v>-1.1765</v>
       </c>
     </row>
     <row r="249">
@@ -39477,22 +39477,22 @@
         <v>-0.4611</v>
       </c>
       <c r="C249" t="n">
-        <v>-1.3611</v>
+        <v>-1.361</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.9111</v>
+        <v>-0.911</v>
       </c>
       <c r="E249" t="n">
         <v>-0.4611</v>
       </c>
       <c r="F249" t="n">
-        <v>-1.3611</v>
+        <v>-1.361</v>
       </c>
       <c r="G249" t="n">
         <v>-0.4611</v>
       </c>
       <c r="M249" t="n">
-        <v>-1.3611</v>
+        <v>-1.361</v>
       </c>
     </row>
     <row r="250">
@@ -39533,7 +39533,7 @@
         <v>-0.6722</v>
       </c>
       <c r="C251" t="n">
-        <v>-1.1926</v>
+        <v>-1.1925</v>
       </c>
       <c r="D251" t="n">
         <v>-0.9324</v>
@@ -39542,13 +39542,13 @@
         <v>-0.6722</v>
       </c>
       <c r="F251" t="n">
-        <v>-1.1926</v>
+        <v>-1.1925</v>
       </c>
       <c r="G251" t="n">
         <v>-0.6722</v>
       </c>
       <c r="M251" t="n">
-        <v>-1.1926</v>
+        <v>-1.1925</v>
       </c>
     </row>
     <row r="252">
@@ -39561,7 +39561,7 @@
         <v>-0.6702</v>
       </c>
       <c r="C252" t="n">
-        <v>-1.0833</v>
+        <v>-1.0832</v>
       </c>
       <c r="D252" t="n">
         <v>-0.8767</v>
@@ -39570,13 +39570,13 @@
         <v>-0.6702</v>
       </c>
       <c r="F252" t="n">
-        <v>-1.0833</v>
+        <v>-1.0832</v>
       </c>
       <c r="G252" t="n">
         <v>-0.6702</v>
       </c>
       <c r="M252" t="n">
-        <v>-1.0833</v>
+        <v>-1.0832</v>
       </c>
     </row>
     <row r="253">
@@ -39589,7 +39589,7 @@
         <v>-0.7845</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.806</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="D253" t="n">
         <v>-0.7952</v>
@@ -39598,13 +39598,13 @@
         <v>-0.7845</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.806</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G253" t="n">
         <v>-0.7845</v>
       </c>
       <c r="M253" t="n">
-        <v>-0.806</v>
+        <v>-0.8058999999999999</v>
       </c>
     </row>
     <row r="254">
@@ -39617,22 +39617,22 @@
         <v>-0.5672</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.7788</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="D254" t="n">
-        <v>-0.673</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="E254" t="n">
         <v>-0.5672</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.7788</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="G254" t="n">
         <v>-0.5672</v>
       </c>
       <c r="M254" t="n">
-        <v>-0.7788</v>
+        <v>-0.7786999999999999</v>
       </c>
     </row>
     <row r="255">
@@ -39645,22 +39645,22 @@
         <v>-0.5938</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.6897</v>
+        <v>-0.6896</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.6418</v>
+        <v>-0.6417</v>
       </c>
       <c r="E255" t="n">
         <v>-0.5938</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.6897</v>
+        <v>-0.6896</v>
       </c>
       <c r="G255" t="n">
         <v>-0.5938</v>
       </c>
       <c r="M255" t="n">
-        <v>-0.6897</v>
+        <v>-0.6896</v>
       </c>
     </row>
     <row r="256">
@@ -39673,7 +39673,7 @@
         <v>-0.6084000000000001</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.7715</v>
+        <v>-0.7714</v>
       </c>
       <c r="D256" t="n">
         <v>-0.6899</v>
@@ -39682,13 +39682,13 @@
         <v>-0.6084000000000001</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.7715</v>
+        <v>-0.7714</v>
       </c>
       <c r="G256" t="n">
         <v>-0.6084000000000001</v>
       </c>
       <c r="M256" t="n">
-        <v>-0.7715</v>
+        <v>-0.7714</v>
       </c>
     </row>
     <row r="257">
@@ -39704,7 +39704,7 @@
         <v>-1.1859</v>
       </c>
       <c r="D257" t="n">
-        <v>-0.824</v>
+        <v>-0.8239</v>
       </c>
       <c r="E257" t="n">
         <v>-0.462</v>
@@ -39757,7 +39757,7 @@
         <v>-0.3861</v>
       </c>
       <c r="C259" t="n">
-        <v>-1.0956</v>
+        <v>-1.0955</v>
       </c>
       <c r="D259" t="n">
         <v>-0.7408</v>
@@ -39766,13 +39766,13 @@
         <v>-0.3861</v>
       </c>
       <c r="F259" t="n">
-        <v>-1.0956</v>
+        <v>-1.0955</v>
       </c>
       <c r="G259" t="n">
         <v>-0.3861</v>
       </c>
       <c r="M259" t="n">
-        <v>-1.0956</v>
+        <v>-1.0955</v>
       </c>
     </row>
     <row r="260">
@@ -39785,7 +39785,7 @@
         <v>-0.2116</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.9984</v>
+        <v>-0.9983</v>
       </c>
       <c r="D260" t="n">
         <v>-0.605</v>
@@ -39794,13 +39794,13 @@
         <v>-0.2116</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.9984</v>
+        <v>-0.9983</v>
       </c>
       <c r="G260" t="n">
         <v>-0.2116</v>
       </c>
       <c r="M260" t="n">
-        <v>-0.9984</v>
+        <v>-0.9983</v>
       </c>
     </row>
     <row r="261">
@@ -39813,22 +39813,22 @@
         <v>-0.2101</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.844</v>
+        <v>-0.8439</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.5271</v>
+        <v>-0.527</v>
       </c>
       <c r="E261" t="n">
         <v>-0.2101</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.844</v>
+        <v>-0.8439</v>
       </c>
       <c r="G261" t="n">
         <v>-0.2101</v>
       </c>
       <c r="M261" t="n">
-        <v>-0.844</v>
+        <v>-0.8439</v>
       </c>
     </row>
     <row r="262">
@@ -39841,7 +39841,7 @@
         <v>0.0747</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.8841</v>
+        <v>-0.884</v>
       </c>
       <c r="D262" t="n">
         <v>-0.4047</v>
@@ -39850,13 +39850,13 @@
         <v>0.0747</v>
       </c>
       <c r="F262" t="n">
-        <v>-0.8841</v>
+        <v>-0.884</v>
       </c>
       <c r="G262" t="n">
         <v>0.0747</v>
       </c>
       <c r="M262" t="n">
-        <v>-0.8841</v>
+        <v>-0.884</v>
       </c>
     </row>
     <row r="263">
@@ -39869,22 +39869,22 @@
         <v>0.1559</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.7604</v>
+        <v>-0.7603</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.3023</v>
+        <v>-0.3022</v>
       </c>
       <c r="E263" t="n">
         <v>0.1559</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.7604</v>
+        <v>-0.7603</v>
       </c>
       <c r="G263" t="n">
         <v>0.1559</v>
       </c>
       <c r="M263" t="n">
-        <v>-0.7604</v>
+        <v>-0.7603</v>
       </c>
     </row>
     <row r="264">
@@ -39897,22 +39897,22 @@
         <v>0.1099</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.8346</v>
+        <v>-0.8345</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.3624</v>
+        <v>-0.3623</v>
       </c>
       <c r="E264" t="n">
         <v>0.1099</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.8346</v>
+        <v>-0.8345</v>
       </c>
       <c r="G264" t="n">
         <v>0.1099</v>
       </c>
       <c r="M264" t="n">
-        <v>-0.8346</v>
+        <v>-0.8345</v>
       </c>
     </row>
     <row r="265">
@@ -39925,7 +39925,7 @@
         <v>0.2201</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.8693</v>
+        <v>-0.8692</v>
       </c>
       <c r="D265" t="n">
         <v>-0.3246</v>
@@ -39934,13 +39934,13 @@
         <v>0.2201</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.8693</v>
+        <v>-0.8692</v>
       </c>
       <c r="G265" t="n">
         <v>0.2201</v>
       </c>
       <c r="M265" t="n">
-        <v>-0.8693</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="266">
@@ -39956,7 +39956,7 @@
         <v>-1.0161</v>
       </c>
       <c r="D266" t="n">
-        <v>-0.5291</v>
+        <v>-0.529</v>
       </c>
       <c r="E266" t="n">
         <v>-0.042</v>
@@ -39981,7 +39981,7 @@
         <v>0.0251</v>
       </c>
       <c r="C267" t="n">
-        <v>-1.0865</v>
+        <v>-1.0864</v>
       </c>
       <c r="D267" t="n">
         <v>-0.5306999999999999</v>
@@ -39990,13 +39990,13 @@
         <v>0.0251</v>
       </c>
       <c r="F267" t="n">
-        <v>-1.0865</v>
+        <v>-1.0864</v>
       </c>
       <c r="G267" t="n">
         <v>0.0251</v>
       </c>
       <c r="M267" t="n">
-        <v>-1.0865</v>
+        <v>-1.0864</v>
       </c>
     </row>
     <row r="268">
@@ -40009,7 +40009,7 @@
         <v>0.0421</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.8895</v>
+        <v>-0.8894</v>
       </c>
       <c r="D268" t="n">
         <v>-0.4237</v>
@@ -40018,13 +40018,13 @@
         <v>0.0421</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.8895</v>
+        <v>-0.8894</v>
       </c>
       <c r="G268" t="n">
         <v>0.0421</v>
       </c>
       <c r="M268" t="n">
-        <v>-0.8895</v>
+        <v>-0.8894</v>
       </c>
     </row>
     <row r="269">
@@ -40037,7 +40037,7 @@
         <v>0.0542</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.4208</v>
+        <v>-0.4207</v>
       </c>
       <c r="D269" t="n">
         <v>-0.1833</v>
@@ -40046,13 +40046,13 @@
         <v>0.0542</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.4208</v>
+        <v>-0.4207</v>
       </c>
       <c r="G269" t="n">
         <v>0.0542</v>
       </c>
       <c r="M269" t="n">
-        <v>-0.4208</v>
+        <v>-0.4207</v>
       </c>
     </row>
     <row r="270">
@@ -40065,22 +40065,22 @@
         <v>0.0444</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.3335</v>
+        <v>-0.3334</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.1446</v>
+        <v>-0.1445</v>
       </c>
       <c r="E270" t="n">
         <v>0.0444</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.3335</v>
+        <v>-0.3334</v>
       </c>
       <c r="G270" t="n">
         <v>0.0444</v>
       </c>
       <c r="M270" t="n">
-        <v>-0.3335</v>
+        <v>-0.3334</v>
       </c>
     </row>
     <row r="271">
@@ -40093,22 +40093,22 @@
         <v>0.1095</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.0417</v>
+        <v>-0.0416</v>
       </c>
       <c r="D271" t="n">
-        <v>0.0339</v>
+        <v>0.034</v>
       </c>
       <c r="E271" t="n">
         <v>0.1095</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.0417</v>
+        <v>-0.0416</v>
       </c>
       <c r="G271" t="n">
         <v>0.1095</v>
       </c>
       <c r="M271" t="n">
-        <v>-0.0417</v>
+        <v>-0.0416</v>
       </c>
     </row>
     <row r="272">
@@ -40121,22 +40121,22 @@
         <v>0.1298</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.0178</v>
+        <v>-0.0176</v>
       </c>
       <c r="D272" t="n">
-        <v>0.056</v>
+        <v>0.0561</v>
       </c>
       <c r="E272" t="n">
         <v>0.1298</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.0178</v>
+        <v>-0.0176</v>
       </c>
       <c r="G272" t="n">
         <v>0.1298</v>
       </c>
       <c r="M272" t="n">
-        <v>-0.0178</v>
+        <v>-0.0176</v>
       </c>
     </row>
     <row r="273">
@@ -40149,7 +40149,7 @@
         <v>0.1281</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1324</v>
+        <v>0.1325</v>
       </c>
       <c r="D273" t="n">
         <v>0.1303</v>
@@ -40158,13 +40158,13 @@
         <v>0.1281</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1324</v>
+        <v>0.1325</v>
       </c>
       <c r="G273" t="n">
         <v>0.1281</v>
       </c>
       <c r="M273" t="n">
-        <v>0.1324</v>
+        <v>0.1325</v>
       </c>
     </row>
     <row r="274">
@@ -40177,22 +40177,22 @@
         <v>0.1599</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2272</v>
+        <v>0.2273</v>
       </c>
       <c r="D274" t="n">
-        <v>0.1935</v>
+        <v>0.1936</v>
       </c>
       <c r="E274" t="n">
         <v>0.1599</v>
       </c>
       <c r="F274" t="n">
-        <v>0.2272</v>
+        <v>0.2273</v>
       </c>
       <c r="G274" t="n">
         <v>0.1599</v>
       </c>
       <c r="M274" t="n">
-        <v>0.2272</v>
+        <v>0.2273</v>
       </c>
     </row>
     <row r="275">
@@ -40205,7 +40205,7 @@
         <v>0.1674</v>
       </c>
       <c r="C275" t="n">
-        <v>0.1657</v>
+        <v>0.1658</v>
       </c>
       <c r="D275" t="n">
         <v>0.1666</v>
@@ -40214,13 +40214,13 @@
         <v>0.1674</v>
       </c>
       <c r="F275" t="n">
-        <v>0.1657</v>
+        <v>0.1658</v>
       </c>
       <c r="G275" t="n">
         <v>0.1674</v>
       </c>
       <c r="M275" t="n">
-        <v>0.1657</v>
+        <v>0.1658</v>
       </c>
     </row>
     <row r="276">
@@ -40233,22 +40233,22 @@
         <v>0.2689</v>
       </c>
       <c r="C276" t="n">
-        <v>0.1691</v>
+        <v>0.1692</v>
       </c>
       <c r="D276" t="n">
-        <v>0.219</v>
+        <v>0.2191</v>
       </c>
       <c r="E276" t="n">
         <v>0.2689</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1691</v>
+        <v>0.1692</v>
       </c>
       <c r="G276" t="n">
         <v>0.2689</v>
       </c>
       <c r="M276" t="n">
-        <v>0.1691</v>
+        <v>0.1692</v>
       </c>
     </row>
     <row r="277">
@@ -40261,22 +40261,22 @@
         <v>1.0427</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1524</v>
+        <v>0.1525</v>
       </c>
       <c r="D277" t="n">
-        <v>0.5975</v>
+        <v>0.5976</v>
       </c>
       <c r="E277" t="n">
         <v>1.0427</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1524</v>
+        <v>0.1525</v>
       </c>
       <c r="G277" t="n">
         <v>1.0427</v>
       </c>
       <c r="M277" t="n">
-        <v>0.1524</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="278">
@@ -40289,22 +40289,22 @@
         <v>0.3174</v>
       </c>
       <c r="C278" t="n">
-        <v>0.4115</v>
+        <v>0.4116</v>
       </c>
       <c r="D278" t="n">
-        <v>0.3644</v>
+        <v>0.3645</v>
       </c>
       <c r="E278" t="n">
         <v>0.3174</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4115</v>
+        <v>0.4116</v>
       </c>
       <c r="G278" t="n">
         <v>0.3174</v>
       </c>
       <c r="M278" t="n">
-        <v>0.4115</v>
+        <v>0.4116</v>
       </c>
     </row>
     <row r="279">
@@ -40317,22 +40317,22 @@
         <v>0.2691</v>
       </c>
       <c r="C279" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5017</v>
       </c>
       <c r="D279" t="n">
-        <v>0.3853</v>
+        <v>0.3854</v>
       </c>
       <c r="E279" t="n">
         <v>0.2691</v>
       </c>
       <c r="F279" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5017</v>
       </c>
       <c r="G279" t="n">
         <v>0.2691</v>
       </c>
       <c r="M279" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5017</v>
       </c>
     </row>
     <row r="280">
@@ -40345,7 +40345,7 @@
         <v>0.296</v>
       </c>
       <c r="C280" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="D280" t="n">
         <v>0.4033</v>
@@ -40354,13 +40354,13 @@
         <v>0.296</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="G280" t="n">
         <v>0.296</v>
       </c>
       <c r="M280" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5107</v>
       </c>
     </row>
     <row r="281">
@@ -40373,7 +40373,7 @@
         <v>0.9436</v>
       </c>
       <c r="C281" t="n">
-        <v>0.5727</v>
+        <v>0.5729</v>
       </c>
       <c r="D281" t="n">
         <v>0.7582</v>
@@ -40382,13 +40382,13 @@
         <v>0.9436</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5727</v>
+        <v>0.5729</v>
       </c>
       <c r="G281" t="n">
         <v>0.9436</v>
       </c>
       <c r="M281" t="n">
-        <v>0.5727</v>
+        <v>0.5729</v>
       </c>
     </row>
     <row r="282">
@@ -40401,22 +40401,22 @@
         <v>0.9459</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="D282" t="n">
-        <v>0.4352</v>
+        <v>0.4353</v>
       </c>
       <c r="E282" t="n">
         <v>0.9459</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="G282" t="n">
         <v>0.9459</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.07530000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -40429,7 +40429,7 @@
         <v>0.907</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="D283" t="n">
         <v>0.4178</v>
@@ -40438,13 +40438,13 @@
         <v>0.907</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="G283" t="n">
         <v>0.907</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
     </row>
     <row r="284">
@@ -40457,7 +40457,7 @@
         <v>0.9891</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0641</v>
       </c>
       <c r="D284" t="n">
         <v>0.4625</v>
@@ -40466,13 +40466,13 @@
         <v>0.9891</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0641</v>
       </c>
       <c r="G284" t="n">
         <v>0.9891</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0641</v>
       </c>
     </row>
     <row r="285">
@@ -40485,22 +40485,22 @@
         <v>1.058</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.1</v>
+        <v>-0.0998</v>
       </c>
       <c r="D285" t="n">
-        <v>0.479</v>
+        <v>0.4791</v>
       </c>
       <c r="E285" t="n">
         <v>1.058</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.1</v>
+        <v>-0.0998</v>
       </c>
       <c r="G285" t="n">
         <v>1.058</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.1</v>
+        <v>-0.0998</v>
       </c>
     </row>
     <row r="286">
@@ -40513,22 +40513,22 @@
         <v>1.1509</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.032</v>
+        <v>-0.0319</v>
       </c>
       <c r="D286" t="n">
-        <v>0.5594</v>
+        <v>0.5595</v>
       </c>
       <c r="E286" t="n">
         <v>1.1509</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.032</v>
+        <v>-0.0319</v>
       </c>
       <c r="G286" t="n">
         <v>1.1509</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.032</v>
+        <v>-0.0319</v>
       </c>
     </row>
     <row r="287">
@@ -40541,7 +40541,7 @@
         <v>1.155</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.1074</v>
+        <v>-0.1073</v>
       </c>
       <c r="D287" t="n">
         <v>0.5238</v>
@@ -40550,13 +40550,13 @@
         <v>1.155</v>
       </c>
       <c r="F287" t="n">
-        <v>-0.1074</v>
+        <v>-0.1073</v>
       </c>
       <c r="G287" t="n">
         <v>1.155</v>
       </c>
       <c r="M287" t="n">
-        <v>-0.1074</v>
+        <v>-0.1073</v>
       </c>
     </row>
     <row r="288">
@@ -40569,7 +40569,7 @@
         <v>1.0712</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.1079</v>
+        <v>-0.1077</v>
       </c>
       <c r="D288" t="n">
         <v>0.4817</v>
@@ -40578,13 +40578,13 @@
         <v>1.0712</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.1079</v>
+        <v>-0.1077</v>
       </c>
       <c r="G288" t="n">
         <v>1.0712</v>
       </c>
       <c r="M288" t="n">
-        <v>-0.1079</v>
+        <v>-0.1077</v>
       </c>
     </row>
     <row r="289">
@@ -40597,22 +40597,22 @@
         <v>0.2048</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.111</v>
+        <v>-0.1109</v>
       </c>
       <c r="D289" t="n">
-        <v>0.0469</v>
+        <v>0.047</v>
       </c>
       <c r="E289" t="n">
         <v>0.2048</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.111</v>
+        <v>-0.1109</v>
       </c>
       <c r="G289" t="n">
         <v>0.2048</v>
       </c>
       <c r="M289" t="n">
-        <v>-0.111</v>
+        <v>-0.1109</v>
       </c>
     </row>
     <row r="290">
@@ -40625,22 +40625,22 @@
         <v>0.9968</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.1246</v>
+        <v>-0.1244</v>
       </c>
       <c r="D290" t="n">
-        <v>0.4361</v>
+        <v>0.4362</v>
       </c>
       <c r="E290" t="n">
         <v>0.9968</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.1246</v>
+        <v>-0.1244</v>
       </c>
       <c r="G290" t="n">
         <v>0.9968</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.1246</v>
+        <v>-0.1244</v>
       </c>
     </row>
     <row r="291">
@@ -40653,22 +40653,22 @@
         <v>0.8967000000000001</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.133</v>
+        <v>-0.1329</v>
       </c>
       <c r="D291" t="n">
-        <v>0.3818</v>
+        <v>0.3819</v>
       </c>
       <c r="E291" t="n">
         <v>0.8967000000000001</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.133</v>
+        <v>-0.1329</v>
       </c>
       <c r="G291" t="n">
         <v>0.8967000000000001</v>
       </c>
       <c r="M291" t="n">
-        <v>-0.133</v>
+        <v>-0.1329</v>
       </c>
     </row>
     <row r="292">
@@ -40681,22 +40681,22 @@
         <v>0.9155</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1409</v>
+        <v>-0.1408</v>
       </c>
       <c r="D292" t="n">
-        <v>0.3873</v>
+        <v>0.3874</v>
       </c>
       <c r="E292" t="n">
         <v>0.9155</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.1409</v>
+        <v>-0.1408</v>
       </c>
       <c r="G292" t="n">
         <v>0.9155</v>
       </c>
       <c r="M292" t="n">
-        <v>-0.1409</v>
+        <v>-0.1408</v>
       </c>
     </row>
     <row r="293">
@@ -40709,22 +40709,22 @@
         <v>0.1414</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.1257</v>
+        <v>-0.1256</v>
       </c>
       <c r="D293" t="n">
-        <v>0.0078</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="E293" t="n">
         <v>0.1414</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.1257</v>
+        <v>-0.1256</v>
       </c>
       <c r="G293" t="n">
         <v>0.1414</v>
       </c>
       <c r="M293" t="n">
-        <v>-0.1257</v>
+        <v>-0.1256</v>
       </c>
     </row>
     <row r="294">
@@ -40737,7 +40737,7 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="C294" t="n">
-        <v>0.3809</v>
+        <v>0.381</v>
       </c>
       <c r="D294" t="n">
         <v>0.2284</v>
@@ -40746,13 +40746,13 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="F294" t="n">
-        <v>0.3809</v>
+        <v>0.381</v>
       </c>
       <c r="G294" t="n">
         <v>0.07580000000000001</v>
       </c>
       <c r="M294" t="n">
-        <v>0.3809</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="295">
@@ -40765,22 +40765,22 @@
         <v>0.0684</v>
       </c>
       <c r="C295" t="n">
-        <v>0.3804</v>
+        <v>0.3805</v>
       </c>
       <c r="D295" t="n">
-        <v>0.2244</v>
+        <v>0.2245</v>
       </c>
       <c r="E295" t="n">
         <v>0.0684</v>
       </c>
       <c r="F295" t="n">
-        <v>0.3804</v>
+        <v>0.3805</v>
       </c>
       <c r="G295" t="n">
         <v>0.0684</v>
       </c>
       <c r="M295" t="n">
-        <v>0.3804</v>
+        <v>0.3805</v>
       </c>
     </row>
     <row r="296">
@@ -40793,7 +40793,7 @@
         <v>0.0164</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1696</v>
+        <v>0.1697</v>
       </c>
       <c r="D296" t="n">
         <v>0.093</v>
@@ -40802,13 +40802,13 @@
         <v>0.0164</v>
       </c>
       <c r="F296" t="n">
-        <v>0.1696</v>
+        <v>0.1697</v>
       </c>
       <c r="G296" t="n">
         <v>0.0164</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1696</v>
+        <v>0.1697</v>
       </c>
     </row>
     <row r="297">
@@ -40821,7 +40821,7 @@
         <v>0.0221</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1653</v>
+        <v>0.1654</v>
       </c>
       <c r="D297" t="n">
         <v>0.09370000000000001</v>
@@ -40830,13 +40830,13 @@
         <v>0.0221</v>
       </c>
       <c r="F297" t="n">
-        <v>0.1653</v>
+        <v>0.1654</v>
       </c>
       <c r="G297" t="n">
         <v>0.0221</v>
       </c>
       <c r="M297" t="n">
-        <v>0.1653</v>
+        <v>0.1654</v>
       </c>
     </row>
     <row r="298">
@@ -40849,22 +40849,22 @@
         <v>-0.1104</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.1635</v>
+        <v>-0.1634</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.137</v>
+        <v>-0.1369</v>
       </c>
       <c r="E298" t="n">
         <v>-0.1104</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.1635</v>
+        <v>-0.1634</v>
       </c>
       <c r="G298" t="n">
         <v>-0.1104</v>
       </c>
       <c r="M298" t="n">
-        <v>-0.1635</v>
+        <v>-0.1634</v>
       </c>
     </row>
     <row r="299">
@@ -40877,22 +40877,22 @@
         <v>-0.036</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.1279</v>
+        <v>-0.1278</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.082</v>
+        <v>-0.0819</v>
       </c>
       <c r="E299" t="n">
         <v>-0.036</v>
       </c>
       <c r="F299" t="n">
-        <v>-0.1279</v>
+        <v>-0.1278</v>
       </c>
       <c r="G299" t="n">
         <v>-0.036</v>
       </c>
       <c r="M299" t="n">
-        <v>-0.1279</v>
+        <v>-0.1278</v>
       </c>
     </row>
     <row r="300">
@@ -40905,22 +40905,22 @@
         <v>0.0383</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.1948</v>
+        <v>-0.1947</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E300" t="n">
         <v>0.0383</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.1948</v>
+        <v>-0.1947</v>
       </c>
       <c r="G300" t="n">
         <v>0.0383</v>
       </c>
       <c r="M300" t="n">
-        <v>-0.1948</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="301">
@@ -40933,7 +40933,7 @@
         <v>-0.0259</v>
       </c>
       <c r="C301" t="n">
-        <v>-1.0457</v>
+        <v>-1.0456</v>
       </c>
       <c r="D301" t="n">
         <v>-0.5358000000000001</v>
@@ -40942,13 +40942,13 @@
         <v>-0.0259</v>
       </c>
       <c r="F301" t="n">
-        <v>-1.0457</v>
+        <v>-1.0456</v>
       </c>
       <c r="G301" t="n">
         <v>-0.0259</v>
       </c>
       <c r="M301" t="n">
-        <v>-1.0457</v>
+        <v>-1.0456</v>
       </c>
     </row>
     <row r="302">
@@ -40989,22 +40989,22 @@
         <v>0.0931</v>
       </c>
       <c r="C303" t="n">
-        <v>-1.4292</v>
+        <v>-1.4291</v>
       </c>
       <c r="D303" t="n">
-        <v>-0.6681</v>
+        <v>-0.668</v>
       </c>
       <c r="E303" t="n">
         <v>0.0931</v>
       </c>
       <c r="F303" t="n">
-        <v>-1.4292</v>
+        <v>-1.4291</v>
       </c>
       <c r="G303" t="n">
         <v>0.0931</v>
       </c>
       <c r="M303" t="n">
-        <v>-1.4292</v>
+        <v>-1.4291</v>
       </c>
     </row>
     <row r="304">
@@ -41045,7 +41045,7 @@
         <v>0.175</v>
       </c>
       <c r="C305" t="n">
-        <v>-1.6608</v>
+        <v>-1.6607</v>
       </c>
       <c r="D305" t="n">
         <v>-0.7429</v>
@@ -41054,13 +41054,13 @@
         <v>0.175</v>
       </c>
       <c r="F305" t="n">
-        <v>-1.6608</v>
+        <v>-1.6607</v>
       </c>
       <c r="G305" t="n">
         <v>0.175</v>
       </c>
       <c r="M305" t="n">
-        <v>-1.6608</v>
+        <v>-1.6607</v>
       </c>
     </row>
     <row r="306">
@@ -41073,22 +41073,22 @@
         <v>0.2387</v>
       </c>
       <c r="C306" t="n">
-        <v>-1.6373</v>
+        <v>-1.6372</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.6993</v>
+        <v>-0.6992</v>
       </c>
       <c r="E306" t="n">
         <v>0.2387</v>
       </c>
       <c r="F306" t="n">
-        <v>-1.6373</v>
+        <v>-1.6372</v>
       </c>
       <c r="G306" t="n">
         <v>0.2387</v>
       </c>
       <c r="M306" t="n">
-        <v>-1.6373</v>
+        <v>-1.6372</v>
       </c>
     </row>
     <row r="307">
@@ -41101,7 +41101,7 @@
         <v>0.232</v>
       </c>
       <c r="C307" t="n">
-        <v>-1.7959</v>
+        <v>-1.7958</v>
       </c>
       <c r="D307" t="n">
         <v>-0.7819</v>
@@ -41110,13 +41110,13 @@
         <v>0.232</v>
       </c>
       <c r="F307" t="n">
-        <v>-1.7959</v>
+        <v>-1.7958</v>
       </c>
       <c r="G307" t="n">
         <v>0.232</v>
       </c>
       <c r="M307" t="n">
-        <v>-1.7959</v>
+        <v>-1.7958</v>
       </c>
     </row>
     <row r="308">
@@ -41129,7 +41129,7 @@
         <v>0.218</v>
       </c>
       <c r="C308" t="n">
-        <v>-1.7675</v>
+        <v>-1.7674</v>
       </c>
       <c r="D308" t="n">
         <v>-0.7747000000000001</v>
@@ -41138,13 +41138,13 @@
         <v>0.218</v>
       </c>
       <c r="F308" t="n">
-        <v>-1.7675</v>
+        <v>-1.7674</v>
       </c>
       <c r="G308" t="n">
         <v>0.218</v>
       </c>
       <c r="M308" t="n">
-        <v>-1.7675</v>
+        <v>-1.7674</v>
       </c>
     </row>
     <row r="309">
@@ -41157,7 +41157,7 @@
         <v>0.2204</v>
       </c>
       <c r="C309" t="n">
-        <v>-1.7388</v>
+        <v>-1.7387</v>
       </c>
       <c r="D309" t="n">
         <v>-0.7592</v>
@@ -41166,13 +41166,13 @@
         <v>0.2204</v>
       </c>
       <c r="F309" t="n">
-        <v>-1.7388</v>
+        <v>-1.7387</v>
       </c>
       <c r="G309" t="n">
         <v>0.2204</v>
       </c>
       <c r="M309" t="n">
-        <v>-1.7388</v>
+        <v>-1.7387</v>
       </c>
     </row>
     <row r="310">
@@ -41185,22 +41185,22 @@
         <v>0.2303</v>
       </c>
       <c r="C310" t="n">
-        <v>-1.1223</v>
+        <v>-1.1231</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.446</v>
+        <v>-0.4464</v>
       </c>
       <c r="E310" t="n">
         <v>0.2303</v>
       </c>
       <c r="F310" t="n">
-        <v>-1.1223</v>
+        <v>-1.1231</v>
       </c>
       <c r="G310" t="n">
         <v>0.2303</v>
       </c>
       <c r="M310" t="n">
-        <v>-1.1223</v>
+        <v>-1.1231</v>
       </c>
     </row>
     <row r="311">
@@ -41213,22 +41213,22 @@
         <v>0.188</v>
       </c>
       <c r="C311" t="n">
-        <v>-1.0241</v>
+        <v>-1.0248</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.4181</v>
+        <v>-0.4184</v>
       </c>
       <c r="E311" t="n">
         <v>0.188</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.0241</v>
+        <v>-1.0248</v>
       </c>
       <c r="G311" t="n">
         <v>0.188</v>
       </c>
       <c r="M311" t="n">
-        <v>-1.0241</v>
+        <v>-1.0248</v>
       </c>
     </row>
     <row r="312">
@@ -41241,22 +41241,22 @@
         <v>0.1355</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.8723</v>
+        <v>-0.8728</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3684</v>
+        <v>-0.3687</v>
       </c>
       <c r="E312" t="n">
         <v>0.1355</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.8723</v>
+        <v>-0.8728</v>
       </c>
       <c r="G312" t="n">
         <v>0.1355</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.8723</v>
+        <v>-0.8728</v>
       </c>
     </row>
     <row r="313">
@@ -41269,22 +41269,22 @@
         <v>0.1744</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.5008</v>
+        <v>-0.5012</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.1632</v>
+        <v>-0.1634</v>
       </c>
       <c r="E313" t="n">
         <v>0.1744</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.5008</v>
+        <v>-0.5012</v>
       </c>
       <c r="G313" t="n">
         <v>0.1744</v>
       </c>
       <c r="M313" t="n">
-        <v>-0.5008</v>
+        <v>-0.5012</v>
       </c>
     </row>
     <row r="314">
@@ -41297,22 +41297,22 @@
         <v>0.126</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.1284</v>
+        <v>-0.1285</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.0012</v>
+        <v>-0.0013</v>
       </c>
       <c r="E314" t="n">
         <v>0.126</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.1284</v>
+        <v>-0.1285</v>
       </c>
       <c r="G314" t="n">
         <v>0.126</v>
       </c>
       <c r="M314" t="n">
-        <v>-0.1284</v>
+        <v>-0.1285</v>
       </c>
     </row>
     <row r="315">
@@ -41325,22 +41325,22 @@
         <v>0.171</v>
       </c>
       <c r="C315" t="n">
-        <v>0.1317</v>
+        <v>0.1318</v>
       </c>
       <c r="D315" t="n">
-        <v>0.1513</v>
+        <v>0.1514</v>
       </c>
       <c r="E315" t="n">
         <v>0.171</v>
       </c>
       <c r="F315" t="n">
-        <v>0.1317</v>
+        <v>0.1318</v>
       </c>
       <c r="G315" t="n">
         <v>0.171</v>
       </c>
       <c r="M315" t="n">
-        <v>0.1317</v>
+        <v>0.1318</v>
       </c>
     </row>
     <row r="316">
@@ -41353,22 +41353,22 @@
         <v>0.1181</v>
       </c>
       <c r="C316" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5019</v>
       </c>
       <c r="D316" t="n">
-        <v>0.3098</v>
+        <v>0.31</v>
       </c>
       <c r="E316" t="n">
         <v>0.1181</v>
       </c>
       <c r="F316" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5019</v>
       </c>
       <c r="G316" t="n">
         <v>0.1181</v>
       </c>
       <c r="M316" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5019</v>
       </c>
     </row>
     <row r="317">
@@ -41381,22 +41381,22 @@
         <v>0.1138</v>
       </c>
       <c r="C317" t="n">
-        <v>0.7655</v>
+        <v>0.7661</v>
       </c>
       <c r="D317" t="n">
-        <v>0.4397</v>
+        <v>0.44</v>
       </c>
       <c r="E317" t="n">
         <v>0.1138</v>
       </c>
       <c r="F317" t="n">
-        <v>0.7655</v>
+        <v>0.7661</v>
       </c>
       <c r="G317" t="n">
         <v>0.1138</v>
       </c>
       <c r="M317" t="n">
-        <v>0.7655</v>
+        <v>0.7661</v>
       </c>
     </row>
     <row r="318">
@@ -41409,22 +41409,22 @@
         <v>0.1704</v>
       </c>
       <c r="C318" t="n">
-        <v>0.6536</v>
+        <v>0.6539</v>
       </c>
       <c r="D318" t="n">
-        <v>0.412</v>
+        <v>0.4122</v>
       </c>
       <c r="E318" t="n">
         <v>0.1704</v>
       </c>
       <c r="F318" t="n">
-        <v>0.6536</v>
+        <v>0.6539</v>
       </c>
       <c r="G318" t="n">
         <v>0.1704</v>
       </c>
       <c r="M318" t="n">
-        <v>0.6536</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="319">
@@ -41437,22 +41437,22 @@
         <v>0.1123</v>
       </c>
       <c r="C319" t="n">
-        <v>0.9022</v>
+        <v>0.9025</v>
       </c>
       <c r="D319" t="n">
-        <v>0.5072</v>
+        <v>0.5074</v>
       </c>
       <c r="E319" t="n">
         <v>0.1123</v>
       </c>
       <c r="F319" t="n">
-        <v>0.9022</v>
+        <v>0.9025</v>
       </c>
       <c r="G319" t="n">
         <v>0.1123</v>
       </c>
       <c r="M319" t="n">
-        <v>0.9022</v>
+        <v>0.9025</v>
       </c>
     </row>
     <row r="320">
@@ -41465,22 +41465,22 @@
         <v>0.0993</v>
       </c>
       <c r="C320" t="n">
-        <v>0.8033</v>
+        <v>0.8035</v>
       </c>
       <c r="D320" t="n">
-        <v>0.4513</v>
+        <v>0.4514</v>
       </c>
       <c r="E320" t="n">
         <v>0.0993</v>
       </c>
       <c r="F320" t="n">
-        <v>0.8033</v>
+        <v>0.8035</v>
       </c>
       <c r="G320" t="n">
         <v>0.0993</v>
       </c>
       <c r="M320" t="n">
-        <v>0.8033</v>
+        <v>0.8035</v>
       </c>
     </row>
     <row r="321">
@@ -41493,22 +41493,22 @@
         <v>0.1454</v>
       </c>
       <c r="C321" t="n">
-        <v>0.875</v>
+        <v>0.8752</v>
       </c>
       <c r="D321" t="n">
-        <v>0.5102</v>
+        <v>0.5103</v>
       </c>
       <c r="E321" t="n">
         <v>0.1454</v>
       </c>
       <c r="F321" t="n">
-        <v>0.875</v>
+        <v>0.8752</v>
       </c>
       <c r="G321" t="n">
         <v>0.1454</v>
       </c>
       <c r="M321" t="n">
-        <v>0.875</v>
+        <v>0.8752</v>
       </c>
     </row>
     <row r="322">
@@ -41549,22 +41549,22 @@
         <v>-0.2258</v>
       </c>
       <c r="C323" t="n">
-        <v>0.3029</v>
+        <v>0.3024</v>
       </c>
       <c r="D323" t="n">
-        <v>0.0386</v>
+        <v>0.0383</v>
       </c>
       <c r="E323" t="n">
         <v>-0.2258</v>
       </c>
       <c r="F323" t="n">
-        <v>0.3029</v>
+        <v>0.3024</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2258</v>
       </c>
       <c r="M323" t="n">
-        <v>0.3029</v>
+        <v>0.3024</v>
       </c>
     </row>
     <row r="324">
@@ -41577,22 +41577,22 @@
         <v>-0.1752</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2112</v>
+        <v>0.2105</v>
       </c>
       <c r="D324" t="n">
-        <v>0.018</v>
+        <v>0.0176</v>
       </c>
       <c r="E324" t="n">
         <v>-0.1752</v>
       </c>
       <c r="F324" t="n">
-        <v>0.2112</v>
+        <v>0.2105</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1752</v>
       </c>
       <c r="M324" t="n">
-        <v>0.2112</v>
+        <v>0.2105</v>
       </c>
     </row>
     <row r="325">
@@ -41605,22 +41605,22 @@
         <v>-0.1799</v>
       </c>
       <c r="C325" t="n">
-        <v>0.191</v>
+        <v>0.1904</v>
       </c>
       <c r="D325" t="n">
-        <v>0.0056</v>
+        <v>0.0052</v>
       </c>
       <c r="E325" t="n">
         <v>-0.1799</v>
       </c>
       <c r="F325" t="n">
-        <v>0.191</v>
+        <v>0.1904</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1799</v>
       </c>
       <c r="M325" t="n">
-        <v>0.191</v>
+        <v>0.1904</v>
       </c>
     </row>
     <row r="326">
@@ -41633,22 +41633,22 @@
         <v>-0.2564</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1853</v>
+        <v>0.1847</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.0355</v>
+        <v>-0.0358</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2564</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1853</v>
+        <v>0.1847</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2564</v>
       </c>
       <c r="M326" t="n">
-        <v>0.1853</v>
+        <v>0.1847</v>
       </c>
     </row>
     <row r="327">
@@ -41661,22 +41661,22 @@
         <v>-0.2402</v>
       </c>
       <c r="C327" t="n">
-        <v>0.4109</v>
+        <v>0.4105</v>
       </c>
       <c r="D327" t="n">
-        <v>0.0853</v>
+        <v>0.0851</v>
       </c>
       <c r="E327" t="n">
         <v>-0.2402</v>
       </c>
       <c r="F327" t="n">
-        <v>0.4109</v>
+        <v>0.4105</v>
       </c>
       <c r="G327" t="n">
         <v>-0.2402</v>
       </c>
       <c r="M327" t="n">
-        <v>0.4109</v>
+        <v>0.4105</v>
       </c>
     </row>
     <row r="328">
@@ -41689,22 +41689,22 @@
         <v>-0.2121</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4498</v>
+        <v>0.4496</v>
       </c>
       <c r="D328" t="n">
-        <v>0.1189</v>
+        <v>0.1188</v>
       </c>
       <c r="E328" t="n">
         <v>-0.2121</v>
       </c>
       <c r="F328" t="n">
-        <v>0.4498</v>
+        <v>0.4496</v>
       </c>
       <c r="G328" t="n">
         <v>-0.2121</v>
       </c>
       <c r="M328" t="n">
-        <v>0.4498</v>
+        <v>0.4496</v>
       </c>
     </row>
     <row r="329">
@@ -41717,22 +41717,22 @@
         <v>-0.1292</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0297</v>
+        <v>0.0292</v>
       </c>
       <c r="D329" t="n">
-        <v>-0.0497</v>
+        <v>-0.05</v>
       </c>
       <c r="E329" t="n">
         <v>-0.1292</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0297</v>
+        <v>0.0292</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1292</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0297</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="330">
@@ -41745,22 +41745,22 @@
         <v>-0.2151</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1377</v>
+        <v>-0.1385</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.1764</v>
+        <v>-0.1768</v>
       </c>
       <c r="E330" t="n">
         <v>-0.2151</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1377</v>
+        <v>-0.1385</v>
       </c>
       <c r="G330" t="n">
         <v>-0.2151</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1377</v>
+        <v>-0.1385</v>
       </c>
     </row>
     <row r="331">
@@ -41773,22 +41773,22 @@
         <v>-0.167</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.1221</v>
+        <v>-0.1229</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1446</v>
+        <v>-0.1449</v>
       </c>
       <c r="E331" t="n">
         <v>-0.167</v>
       </c>
       <c r="F331" t="n">
-        <v>-0.1221</v>
+        <v>-0.1229</v>
       </c>
       <c r="G331" t="n">
         <v>-0.167</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.1221</v>
+        <v>-0.1229</v>
       </c>
     </row>
     <row r="332">
@@ -41801,22 +41801,22 @@
         <v>-0.1701</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.2553</v>
+        <v>-0.2562</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.2127</v>
+        <v>-0.2131</v>
       </c>
       <c r="E332" t="n">
         <v>-0.1701</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2553</v>
+        <v>-0.2562</v>
       </c>
       <c r="G332" t="n">
         <v>-0.1701</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.2553</v>
+        <v>-0.2562</v>
       </c>
     </row>
     <row r="333">
@@ -41829,22 +41829,22 @@
         <v>-0.1717</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.2403</v>
+        <v>-0.2411</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.206</v>
+        <v>-0.2064</v>
       </c>
       <c r="E333" t="n">
         <v>-0.1717</v>
       </c>
       <c r="F333" t="n">
-        <v>-0.2403</v>
+        <v>-0.2411</v>
       </c>
       <c r="G333" t="n">
         <v>-0.1717</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.2403</v>
+        <v>-0.2411</v>
       </c>
     </row>
     <row r="334">
@@ -41857,22 +41857,22 @@
         <v>-0.1192</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1152</v>
+        <v>-0.1159</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1172</v>
+        <v>-0.1176</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1192</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1152</v>
+        <v>-0.1159</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1192</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1152</v>
+        <v>-0.1159</v>
       </c>
     </row>
     <row r="335">
@@ -41885,22 +41885,22 @@
         <v>-0.07290000000000001</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2616</v>
+        <v>-0.2625</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.1672</v>
+        <v>-0.1677</v>
       </c>
       <c r="E335" t="n">
         <v>-0.07290000000000001</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2616</v>
+        <v>-0.2625</v>
       </c>
       <c r="G335" t="n">
         <v>-0.07290000000000001</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2616</v>
+        <v>-0.2625</v>
       </c>
     </row>
     <row r="336">
@@ -41913,22 +41913,22 @@
         <v>-0.1207</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.2041</v>
+        <v>-0.2049</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.1624</v>
+        <v>-0.1628</v>
       </c>
       <c r="E336" t="n">
         <v>-0.1207</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.2041</v>
+        <v>-0.2049</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1207</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.2041</v>
+        <v>-0.2049</v>
       </c>
     </row>
     <row r="337">
@@ -41941,22 +41941,22 @@
         <v>-0.1707</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2831</v>
+        <v>-0.2841</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.2269</v>
+        <v>-0.2274</v>
       </c>
       <c r="E337" t="n">
         <v>-0.1707</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.2831</v>
+        <v>-0.2841</v>
       </c>
       <c r="G337" t="n">
         <v>-0.1707</v>
       </c>
       <c r="M337" t="n">
-        <v>-0.2831</v>
+        <v>-0.2841</v>
       </c>
     </row>
     <row r="338">
@@ -41969,22 +41969,22 @@
         <v>-0.1235</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2463</v>
+        <v>-0.2473</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.1849</v>
+        <v>-0.1854</v>
       </c>
       <c r="E338" t="n">
         <v>-0.1235</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2463</v>
+        <v>-0.2473</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1235</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2463</v>
+        <v>-0.2473</v>
       </c>
     </row>
     <row r="339">
@@ -41997,22 +41997,22 @@
         <v>-0.1227</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2086</v>
+        <v>-0.2095</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.1656</v>
+        <v>-0.1661</v>
       </c>
       <c r="E339" t="n">
         <v>-0.1227</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2086</v>
+        <v>-0.2095</v>
       </c>
       <c r="G339" t="n">
         <v>-0.1227</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2086</v>
+        <v>-0.2095</v>
       </c>
     </row>
     <row r="340">
@@ -42025,22 +42025,22 @@
         <v>-0.07480000000000001</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0521</v>
+        <v>0.0513</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.0113</v>
+        <v>-0.0117</v>
       </c>
       <c r="E340" t="n">
         <v>-0.07480000000000001</v>
       </c>
       <c r="F340" t="n">
-        <v>0.0521</v>
+        <v>0.0513</v>
       </c>
       <c r="G340" t="n">
         <v>-0.07480000000000001</v>
       </c>
       <c r="M340" t="n">
-        <v>0.0521</v>
+        <v>0.0513</v>
       </c>
     </row>
     <row r="341">
@@ -42053,22 +42053,22 @@
         <v>-0.1681</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1764</v>
+        <v>0.1757</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0042</v>
+        <v>0.0038</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1681</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1764</v>
+        <v>0.1757</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1681</v>
       </c>
       <c r="M341" t="n">
-        <v>0.1764</v>
+        <v>0.1757</v>
       </c>
     </row>
     <row r="342">
@@ -42081,22 +42081,22 @@
         <v>-0.1203</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2256</v>
+        <v>0.2249</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0526</v>
+        <v>0.0523</v>
       </c>
       <c r="E342" t="n">
         <v>-0.1203</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2256</v>
+        <v>0.2249</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1203</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2256</v>
+        <v>0.2249</v>
       </c>
     </row>
     <row r="343">
@@ -42109,22 +42109,22 @@
         <v>-0.1208</v>
       </c>
       <c r="C343" t="n">
-        <v>0.341</v>
+        <v>0.3405</v>
       </c>
       <c r="D343" t="n">
-        <v>0.1101</v>
+        <v>0.1098</v>
       </c>
       <c r="E343" t="n">
         <v>-0.1208</v>
       </c>
       <c r="F343" t="n">
-        <v>0.341</v>
+        <v>0.3405</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1208</v>
       </c>
       <c r="M343" t="n">
-        <v>0.341</v>
+        <v>0.3405</v>
       </c>
     </row>
     <row r="344">
@@ -42137,22 +42137,22 @@
         <v>-0.1216</v>
       </c>
       <c r="C344" t="n">
-        <v>0.5604</v>
+        <v>0.5601</v>
       </c>
       <c r="D344" t="n">
-        <v>0.2194</v>
+        <v>0.2192</v>
       </c>
       <c r="E344" t="n">
         <v>-0.1216</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5604</v>
+        <v>0.5601</v>
       </c>
       <c r="G344" t="n">
         <v>-0.1216</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5604</v>
+        <v>0.5601</v>
       </c>
     </row>
     <row r="345">
@@ -42165,22 +42165,22 @@
         <v>-0.1653</v>
       </c>
       <c r="C345" t="n">
-        <v>0.4448</v>
+        <v>0.4443</v>
       </c>
       <c r="D345" t="n">
-        <v>0.1397</v>
+        <v>0.1395</v>
       </c>
       <c r="E345" t="n">
         <v>-0.1653</v>
       </c>
       <c r="F345" t="n">
-        <v>0.4448</v>
+        <v>0.4443</v>
       </c>
       <c r="G345" t="n">
         <v>-0.1653</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4448</v>
+        <v>0.4443</v>
       </c>
     </row>
     <row r="346">
@@ -42193,22 +42193,22 @@
         <v>-0.1658</v>
       </c>
       <c r="C346" t="n">
-        <v>0.524</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="D346" t="n">
-        <v>0.1791</v>
+        <v>0.1789</v>
       </c>
       <c r="E346" t="n">
         <v>-0.1658</v>
       </c>
       <c r="F346" t="n">
-        <v>0.524</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1658</v>
       </c>
       <c r="M346" t="n">
-        <v>0.524</v>
+        <v>0.5237000000000001</v>
       </c>
     </row>
     <row r="347">
@@ -42221,22 +42221,22 @@
         <v>-0.1659</v>
       </c>
       <c r="C347" t="n">
-        <v>0.3509</v>
+        <v>0.3504</v>
       </c>
       <c r="D347" t="n">
-        <v>0.0925</v>
+        <v>0.0922</v>
       </c>
       <c r="E347" t="n">
         <v>-0.1659</v>
       </c>
       <c r="F347" t="n">
-        <v>0.3509</v>
+        <v>0.3504</v>
       </c>
       <c r="G347" t="n">
         <v>-0.1659</v>
       </c>
       <c r="M347" t="n">
-        <v>0.3509</v>
+        <v>0.3504</v>
       </c>
     </row>
     <row r="348">
@@ -42249,22 +42249,22 @@
         <v>-0.119</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5121</v>
+        <v>0.5117</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1965</v>
+        <v>0.1964</v>
       </c>
       <c r="E348" t="n">
         <v>-0.119</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5121</v>
+        <v>0.5117</v>
       </c>
       <c r="G348" t="n">
         <v>-0.119</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5121</v>
+        <v>0.5117</v>
       </c>
     </row>
     <row r="349">
@@ -42277,22 +42277,22 @@
         <v>-0.07149999999999999</v>
       </c>
       <c r="C349" t="n">
-        <v>0.508</v>
+        <v>0.5077</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2182</v>
+        <v>0.2181</v>
       </c>
       <c r="E349" t="n">
         <v>-0.07149999999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>0.508</v>
+        <v>0.5077</v>
       </c>
       <c r="G349" t="n">
         <v>-0.07149999999999999</v>
       </c>
       <c r="M349" t="n">
-        <v>0.508</v>
+        <v>0.5077</v>
       </c>
     </row>
     <row r="350">
@@ -42333,7 +42333,7 @@
         <v>-0.07489999999999999</v>
       </c>
       <c r="C351" t="n">
-        <v>0.9315</v>
+        <v>0.9316</v>
       </c>
       <c r="D351" t="n">
         <v>0.4283</v>
@@ -42342,13 +42342,13 @@
         <v>-0.07489999999999999</v>
       </c>
       <c r="F351" t="n">
-        <v>0.9315</v>
+        <v>0.9316</v>
       </c>
       <c r="G351" t="n">
         <v>-0.07489999999999999</v>
       </c>
       <c r="M351" t="n">
-        <v>0.9315</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="352">
@@ -42361,22 +42361,22 @@
         <v>-0.0265</v>
       </c>
       <c r="C352" t="n">
-        <v>1.0239</v>
+        <v>1.0241</v>
       </c>
       <c r="D352" t="n">
-        <v>0.4987</v>
+        <v>0.4988</v>
       </c>
       <c r="E352" t="n">
         <v>-0.0265</v>
       </c>
       <c r="F352" t="n">
-        <v>1.0239</v>
+        <v>1.0241</v>
       </c>
       <c r="G352" t="n">
         <v>-0.0265</v>
       </c>
       <c r="M352" t="n">
-        <v>1.0239</v>
+        <v>1.0241</v>
       </c>
     </row>
     <row r="353">
@@ -42389,22 +42389,22 @@
         <v>0.06850000000000001</v>
       </c>
       <c r="C353" t="n">
-        <v>1.2337</v>
+        <v>1.2342</v>
       </c>
       <c r="D353" t="n">
-        <v>0.6511</v>
+        <v>0.6513</v>
       </c>
       <c r="E353" t="n">
         <v>0.06850000000000001</v>
       </c>
       <c r="F353" t="n">
-        <v>1.2337</v>
+        <v>1.2342</v>
       </c>
       <c r="G353" t="n">
         <v>0.06850000000000001</v>
       </c>
       <c r="M353" t="n">
-        <v>1.2337</v>
+        <v>1.2342</v>
       </c>
     </row>
     <row r="354">
@@ -42417,22 +42417,22 @@
         <v>0.0716</v>
       </c>
       <c r="C354" t="n">
-        <v>1.2533</v>
+        <v>1.2538</v>
       </c>
       <c r="D354" t="n">
-        <v>0.6625</v>
+        <v>0.6627</v>
       </c>
       <c r="E354" t="n">
         <v>0.0716</v>
       </c>
       <c r="F354" t="n">
-        <v>1.2533</v>
+        <v>1.2538</v>
       </c>
       <c r="G354" t="n">
         <v>0.0716</v>
       </c>
       <c r="M354" t="n">
-        <v>1.2533</v>
+        <v>1.2538</v>
       </c>
     </row>
     <row r="355">
@@ -42445,22 +42445,22 @@
         <v>0.0721</v>
       </c>
       <c r="C355" t="n">
-        <v>1.0922</v>
+        <v>1.0924</v>
       </c>
       <c r="D355" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5823</v>
       </c>
       <c r="E355" t="n">
         <v>0.0721</v>
       </c>
       <c r="F355" t="n">
-        <v>1.0922</v>
+        <v>1.0924</v>
       </c>
       <c r="G355" t="n">
         <v>0.0721</v>
       </c>
       <c r="M355" t="n">
-        <v>1.0922</v>
+        <v>1.0924</v>
       </c>
     </row>
     <row r="356">
@@ -42473,7 +42473,7 @@
         <v>0.168</v>
       </c>
       <c r="C356" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
       <c r="D356" t="n">
         <v>0.2355</v>
@@ -42482,13 +42482,13 @@
         <v>0.168</v>
       </c>
       <c r="F356" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
       <c r="G356" t="n">
         <v>0.168</v>
       </c>
       <c r="M356" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="357">
@@ -42501,7 +42501,7 @@
         <v>0.2148</v>
       </c>
       <c r="C357" t="n">
-        <v>0.1628</v>
+        <v>0.1627</v>
       </c>
       <c r="D357" t="n">
         <v>0.1888</v>
@@ -42510,13 +42510,13 @@
         <v>0.2148</v>
       </c>
       <c r="F357" t="n">
-        <v>0.1628</v>
+        <v>0.1627</v>
       </c>
       <c r="G357" t="n">
         <v>0.2148</v>
       </c>
       <c r="M357" t="n">
-        <v>0.1628</v>
+        <v>0.1627</v>
       </c>
     </row>
     <row r="358">
@@ -42529,22 +42529,22 @@
         <v>0.2092</v>
       </c>
       <c r="C358" t="n">
-        <v>0.265</v>
+        <v>0.2653</v>
       </c>
       <c r="D358" t="n">
-        <v>0.2371</v>
+        <v>0.2372</v>
       </c>
       <c r="E358" t="n">
         <v>0.2092</v>
       </c>
       <c r="F358" t="n">
-        <v>0.265</v>
+        <v>0.2653</v>
       </c>
       <c r="G358" t="n">
         <v>0.2092</v>
       </c>
       <c r="M358" t="n">
-        <v>0.265</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="359">
@@ -42585,7 +42585,7 @@
         <v>0.2137</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0186</v>
+        <v>-0.0187</v>
       </c>
       <c r="D360" t="n">
         <v>0.0975</v>
@@ -42594,13 +42594,13 @@
         <v>0.2137</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.0186</v>
+        <v>-0.0187</v>
       </c>
       <c r="G360" t="n">
         <v>0.2137</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.0186</v>
+        <v>-0.0187</v>
       </c>
     </row>
     <row r="361">
@@ -42613,7 +42613,7 @@
         <v>0.2627</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0154</v>
+        <v>0.0153</v>
       </c>
       <c r="D361" t="n">
         <v>0.139</v>
@@ -42622,13 +42622,13 @@
         <v>0.2627</v>
       </c>
       <c r="F361" t="n">
-        <v>0.0154</v>
+        <v>0.0153</v>
       </c>
       <c r="G361" t="n">
         <v>0.2627</v>
       </c>
       <c r="M361" t="n">
-        <v>0.0154</v>
+        <v>0.0153</v>
       </c>
     </row>
     <row r="362">
@@ -42641,16 +42641,16 @@
         <v>-0.5438</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0207</v>
+        <v>0.0206</v>
       </c>
       <c r="D362" t="n">
-        <v>-0.2615</v>
+        <v>-0.2616</v>
       </c>
       <c r="E362" t="n">
         <v>-0.5438</v>
       </c>
       <c r="F362" t="n">
-        <v>0.0207</v>
+        <v>0.0206</v>
       </c>
       <c r="G362" t="n">
         <v>0.2144</v>
@@ -42659,7 +42659,7 @@
         <v>-1.302</v>
       </c>
       <c r="M362" t="n">
-        <v>0.0207</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="363">
@@ -42672,16 +42672,16 @@
         <v>-0.5011</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.2216</v>
+        <v>-0.222</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.3614</v>
+        <v>-0.3616</v>
       </c>
       <c r="E363" t="n">
         <v>-0.5011</v>
       </c>
       <c r="F363" t="n">
-        <v>-0.2216</v>
+        <v>-0.222</v>
       </c>
       <c r="G363" t="n">
         <v>0.2627</v>
@@ -42690,7 +42690,7 @@
         <v>-1.2649</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.2216</v>
+        <v>-0.222</v>
       </c>
     </row>
     <row r="364">
@@ -42703,7 +42703,7 @@
         <v>-0.4828</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.0677</v>
+        <v>-0.0679</v>
       </c>
       <c r="D364" t="n">
         <v>-0.2753</v>
@@ -42712,7 +42712,7 @@
         <v>-0.4828</v>
       </c>
       <c r="F364" t="n">
-        <v>-0.0677</v>
+        <v>-0.0679</v>
       </c>
       <c r="G364" t="n">
         <v>0.2151</v>
@@ -42721,7 +42721,7 @@
         <v>-1.1806</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.0677</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="365">
@@ -42734,16 +42734,16 @@
         <v>-0.5291</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.2141</v>
+        <v>-0.2145</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.3716</v>
+        <v>-0.3718</v>
       </c>
       <c r="E365" t="n">
         <v>-0.5291</v>
       </c>
       <c r="F365" t="n">
-        <v>-0.2141</v>
+        <v>-0.2145</v>
       </c>
       <c r="G365" t="n">
         <v>0.1664</v>
@@ -42752,7 +42752,7 @@
         <v>-1.2246</v>
       </c>
       <c r="M365" t="n">
-        <v>-0.2141</v>
+        <v>-0.2145</v>
       </c>
     </row>
     <row r="366">
@@ -42765,16 +42765,16 @@
         <v>-0.4434</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.2347</v>
+        <v>-0.2352</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.3391</v>
+        <v>-0.3393</v>
       </c>
       <c r="E366" t="n">
         <v>-0.4434</v>
       </c>
       <c r="F366" t="n">
-        <v>-0.2347</v>
+        <v>-0.2352</v>
       </c>
       <c r="G366" t="n">
         <v>0.1179</v>
@@ -42783,7 +42783,7 @@
         <v>-1.0047</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.2347</v>
+        <v>-0.2352</v>
       </c>
     </row>
     <row r="367">
@@ -42796,16 +42796,16 @@
         <v>-0.4661</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.1057</v>
+        <v>-0.106</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.2859</v>
+        <v>-0.2861</v>
       </c>
       <c r="E367" t="n">
         <v>-0.4661</v>
       </c>
       <c r="F367" t="n">
-        <v>-0.1057</v>
+        <v>-0.106</v>
       </c>
       <c r="G367" t="n">
         <v>0.2112</v>
@@ -42814,7 +42814,7 @@
         <v>-1.1434</v>
       </c>
       <c r="M367" t="n">
-        <v>-0.1057</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="368">
@@ -42827,16 +42827,16 @@
         <v>-0.4761</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.1072</v>
+        <v>-0.1076</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.2916</v>
+        <v>-0.2919</v>
       </c>
       <c r="E368" t="n">
         <v>-0.4761</v>
       </c>
       <c r="F368" t="n">
-        <v>-0.1072</v>
+        <v>-0.1076</v>
       </c>
       <c r="G368" t="n">
         <v>0.1603</v>
@@ -42845,7 +42845,7 @@
         <v>-1.1125</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.1072</v>
+        <v>-0.1076</v>
       </c>
     </row>
     <row r="369">
@@ -42858,16 +42858,16 @@
         <v>-0.4497</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.402</v>
+        <v>-0.4027</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.4258</v>
+        <v>-0.4262</v>
       </c>
       <c r="E369" t="n">
         <v>-0.4497</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.402</v>
+        <v>-0.4027</v>
       </c>
       <c r="G369" t="n">
         <v>0.1635</v>
@@ -42876,7 +42876,7 @@
         <v>-1.063</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.402</v>
+        <v>-0.4027</v>
       </c>
     </row>
     <row r="370">
@@ -42889,16 +42889,16 @@
         <v>-0.4054</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3737</v>
+        <v>-0.3745</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.3895</v>
+        <v>-0.3899</v>
       </c>
       <c r="E370" t="n">
         <v>-0.4054</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3737</v>
+        <v>-0.3745</v>
       </c>
       <c r="G370" t="n">
         <v>0.2606</v>
@@ -42907,7 +42907,7 @@
         <v>-1.0714</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3737</v>
+        <v>-0.3745</v>
       </c>
     </row>
     <row r="371">
@@ -42920,16 +42920,16 @@
         <v>-0.4533</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.3078</v>
+        <v>-0.3085</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.3805</v>
+        <v>-0.3809</v>
       </c>
       <c r="E371" t="n">
         <v>-0.4533</v>
       </c>
       <c r="F371" t="n">
-        <v>-0.3078</v>
+        <v>-0.3085</v>
       </c>
       <c r="G371" t="n">
         <v>0.2125</v>
@@ -42938,7 +42938,7 @@
         <v>-1.119</v>
       </c>
       <c r="M371" t="n">
-        <v>-0.3078</v>
+        <v>-0.3085</v>
       </c>
     </row>
     <row r="372">
@@ -42951,16 +42951,16 @@
         <v>-0.5492</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3354</v>
+        <v>-0.3361</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.4423</v>
+        <v>-0.4426</v>
       </c>
       <c r="E372" t="n">
         <v>-0.5492</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3354</v>
+        <v>-0.3361</v>
       </c>
       <c r="G372" t="n">
         <v>0.1678</v>
@@ -42969,7 +42969,7 @@
         <v>-1.2662</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3354</v>
+        <v>-0.3361</v>
       </c>
     </row>
     <row r="373">
@@ -42982,16 +42982,16 @@
         <v>-0.5374</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2945</v>
+        <v>-0.2951</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.4159</v>
+        <v>-0.4163</v>
       </c>
       <c r="E373" t="n">
         <v>-0.5374</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2945</v>
+        <v>-0.2951</v>
       </c>
       <c r="G373" t="n">
         <v>0.1683</v>
@@ -43000,7 +43000,7 @@
         <v>-1.2431</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2945</v>
+        <v>-0.2951</v>
       </c>
     </row>
     <row r="374">
@@ -43013,16 +43013,16 @@
         <v>-0.5414</v>
       </c>
       <c r="C374" t="n">
-        <v>0.4906</v>
+        <v>0.4905</v>
       </c>
       <c r="D374" t="n">
-        <v>-0.0254</v>
+        <v>-0.0255</v>
       </c>
       <c r="E374" t="n">
         <v>-0.5414</v>
       </c>
       <c r="F374" t="n">
-        <v>0.4906</v>
+        <v>0.4905</v>
       </c>
       <c r="G374" t="n">
         <v>0.3133</v>
@@ -43043,7 +43043,7 @@
         <v>1.052</v>
       </c>
       <c r="M374" t="n">
-        <v>0.8242</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="375">
@@ -43056,16 +43056,16 @@
         <v>-0.5754</v>
       </c>
       <c r="C375" t="n">
-        <v>0.4564</v>
+        <v>0.4563</v>
       </c>
       <c r="D375" t="n">
-        <v>-0.0595</v>
+        <v>-0.0596</v>
       </c>
       <c r="E375" t="n">
         <v>-0.5754</v>
       </c>
       <c r="F375" t="n">
-        <v>0.4564</v>
+        <v>0.4563</v>
       </c>
       <c r="G375" t="n">
         <v>0.1676</v>
@@ -43086,7 +43086,7 @@
         <v>1.0318</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8172</v>
+        <v>0.8169</v>
       </c>
     </row>
     <row r="376">
@@ -43099,7 +43099,7 @@
         <v>-0.6573</v>
       </c>
       <c r="C376" t="n">
-        <v>0.3864</v>
+        <v>0.3863</v>
       </c>
       <c r="D376" t="n">
         <v>-0.1355</v>
@@ -43108,7 +43108,7 @@
         <v>-0.6573</v>
       </c>
       <c r="F376" t="n">
-        <v>0.3864</v>
+        <v>0.3863</v>
       </c>
       <c r="G376" t="n">
         <v>0.2158</v>
@@ -43129,7 +43129,7 @@
         <v>0.8966</v>
       </c>
       <c r="M376" t="n">
-        <v>0.8534</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="377">
@@ -43142,16 +43142,16 @@
         <v>-0.5411</v>
       </c>
       <c r="C377" t="n">
-        <v>0.3534</v>
+        <v>0.3533</v>
       </c>
       <c r="D377" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0939</v>
       </c>
       <c r="E377" t="n">
         <v>-0.5411</v>
       </c>
       <c r="F377" t="n">
-        <v>0.3534</v>
+        <v>0.3533</v>
       </c>
       <c r="G377" t="n">
         <v>0.2646</v>
@@ -43172,7 +43172,7 @@
         <v>0.9024</v>
       </c>
       <c r="M377" t="n">
-        <v>0.8351</v>
+        <v>0.8348</v>
       </c>
     </row>
     <row r="378">
@@ -43185,16 +43185,16 @@
         <v>-0.576</v>
       </c>
       <c r="C378" t="n">
-        <v>0.2296</v>
+        <v>0.2295</v>
       </c>
       <c r="D378" t="n">
-        <v>-0.1732</v>
+        <v>-0.1733</v>
       </c>
       <c r="E378" t="n">
         <v>-0.576</v>
       </c>
       <c r="F378" t="n">
-        <v>0.2296</v>
+        <v>0.2295</v>
       </c>
       <c r="G378" t="n">
         <v>0.3129</v>
@@ -43215,7 +43215,7 @@
         <v>0.731</v>
       </c>
       <c r="M378" t="n">
-        <v>0.7517</v>
+        <v>0.7514</v>
       </c>
     </row>
     <row r="379">
@@ -43228,16 +43228,16 @@
         <v>-0.5566</v>
       </c>
       <c r="C379" t="n">
-        <v>0.196</v>
+        <v>0.1959</v>
       </c>
       <c r="D379" t="n">
-        <v>-0.1803</v>
+        <v>-0.1804</v>
       </c>
       <c r="E379" t="n">
         <v>-0.5566</v>
       </c>
       <c r="F379" t="n">
-        <v>0.196</v>
+        <v>0.1959</v>
       </c>
       <c r="G379" t="n">
         <v>0.1679</v>
@@ -43258,7 +43258,7 @@
         <v>0.7181999999999999</v>
       </c>
       <c r="M379" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7441</v>
       </c>
     </row>
     <row r="380">
@@ -43271,7 +43271,7 @@
         <v>-0.4259</v>
       </c>
       <c r="C380" t="n">
-        <v>0.1259</v>
+        <v>0.1258</v>
       </c>
       <c r="D380" t="n">
         <v>-0.15</v>
@@ -43280,7 +43280,7 @@
         <v>-0.4259</v>
       </c>
       <c r="F380" t="n">
-        <v>0.1259</v>
+        <v>0.1258</v>
       </c>
       <c r="G380" t="n">
         <v>0.1669</v>
@@ -43301,7 +43301,7 @@
         <v>0.6002999999999999</v>
       </c>
       <c r="M380" t="n">
-        <v>0.7605</v>
+        <v>0.7602</v>
       </c>
     </row>
     <row r="381">
@@ -43314,16 +43314,16 @@
         <v>-0.4767</v>
       </c>
       <c r="C381" t="n">
-        <v>0.0372</v>
+        <v>0.0371</v>
       </c>
       <c r="D381" t="n">
-        <v>-0.2197</v>
+        <v>-0.2198</v>
       </c>
       <c r="E381" t="n">
         <v>-0.4767</v>
       </c>
       <c r="F381" t="n">
-        <v>0.0372</v>
+        <v>0.0371</v>
       </c>
       <c r="G381" t="n">
         <v>0.1652</v>
@@ -43344,7 +43344,7 @@
         <v>0.4722</v>
       </c>
       <c r="M381" t="n">
-        <v>0.7191</v>
+        <v>0.7187</v>
       </c>
     </row>
     <row r="382">
@@ -43360,7 +43360,7 @@
         <v>-0.0217</v>
       </c>
       <c r="D382" t="n">
-        <v>-0.2548</v>
+        <v>-0.2549</v>
       </c>
       <c r="E382" t="n">
         <v>-0.488</v>
@@ -43387,7 +43387,7 @@
         <v>0.3513</v>
       </c>
       <c r="M382" t="n">
-        <v>0.7851</v>
+        <v>0.7849</v>
       </c>
     </row>
     <row r="383">
@@ -43403,7 +43403,7 @@
         <v>-0.08</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.252</v>
+        <v>-0.2521</v>
       </c>
       <c r="E383" t="n">
         <v>-0.4241</v>
@@ -43430,7 +43430,7 @@
         <v>0.2908</v>
       </c>
       <c r="M383" t="n">
-        <v>0.7627</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="384">
@@ -43443,7 +43443,7 @@
         <v>-0.4335</v>
       </c>
       <c r="C384" t="n">
-        <v>-0.132</v>
+        <v>-0.1321</v>
       </c>
       <c r="D384" t="n">
         <v>-0.2828</v>
@@ -43452,7 +43452,7 @@
         <v>-0.4335</v>
       </c>
       <c r="F384" t="n">
-        <v>-0.132</v>
+        <v>-0.1321</v>
       </c>
       <c r="G384" t="n">
         <v>0.1958</v>
@@ -43473,7 +43473,7 @@
         <v>0.2207</v>
       </c>
       <c r="M384" t="n">
-        <v>0.7544</v>
+        <v>0.7542</v>
       </c>
     </row>
     <row r="385">
@@ -43486,7 +43486,7 @@
         <v>-0.3656</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.2081</v>
+        <v>-0.2082</v>
       </c>
       <c r="D385" t="n">
         <v>-0.2869</v>
@@ -43495,7 +43495,7 @@
         <v>-0.3656</v>
       </c>
       <c r="F385" t="n">
-        <v>-0.2081</v>
+        <v>-0.2082</v>
       </c>
       <c r="G385" t="n">
         <v>0.1996</v>
@@ -43516,7 +43516,7 @@
         <v>0.1421</v>
       </c>
       <c r="M385" t="n">
-        <v>0.7148</v>
+        <v>0.7146</v>
       </c>
     </row>
     <row r="386">
@@ -43559,7 +43559,7 @@
         <v>-0.022</v>
       </c>
       <c r="M386" t="n">
-        <v>0.7811</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="387">
@@ -43615,7 +43615,7 @@
         <v>-0.5713</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.3558</v>
+        <v>-0.3557</v>
       </c>
       <c r="D388" t="n">
         <v>-0.4635</v>
@@ -43624,7 +43624,7 @@
         <v>-0.5713</v>
       </c>
       <c r="F388" t="n">
-        <v>-0.3558</v>
+        <v>-0.3557</v>
       </c>
       <c r="G388" t="n">
         <v>0.2643</v>
@@ -43645,7 +43645,7 @@
         <v>-0.1737</v>
       </c>
       <c r="M388" t="n">
-        <v>0.9076</v>
+        <v>0.9078000000000001</v>
       </c>
     </row>
     <row r="389">
@@ -43658,16 +43658,16 @@
         <v>-0.6967</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.4261</v>
+        <v>-0.426</v>
       </c>
       <c r="D389" t="n">
-        <v>-0.5614</v>
+        <v>-0.5613</v>
       </c>
       <c r="E389" t="n">
         <v>-0.6967</v>
       </c>
       <c r="F389" t="n">
-        <v>-0.4261</v>
+        <v>-0.426</v>
       </c>
       <c r="G389" t="n">
         <v>0.1511</v>
@@ -43688,7 +43688,7 @@
         <v>-0.2322</v>
       </c>
       <c r="M389" t="n">
-        <v>0.8169</v>
+        <v>0.8171</v>
       </c>
     </row>
     <row r="390">
@@ -43731,7 +43731,7 @@
         <v>-0.2991</v>
       </c>
       <c r="M390" t="n">
-        <v>0.734</v>
+        <v>0.7341</v>
       </c>
     </row>
     <row r="391">
@@ -43774,7 +43774,7 @@
         <v>-0.4894</v>
       </c>
       <c r="M391" t="n">
-        <v>0.7099</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="392">
@@ -43860,7 +43860,7 @@
         <v>-0.6489</v>
       </c>
       <c r="M393" t="n">
-        <v>0.4025</v>
+        <v>0.4024</v>
       </c>
     </row>
     <row r="394">
@@ -43903,7 +43903,7 @@
         <v>-0.6498</v>
       </c>
       <c r="M394" t="n">
-        <v>0.3753</v>
+        <v>0.3752</v>
       </c>
     </row>
     <row r="395">
@@ -43916,7 +43916,7 @@
         <v>-0.9292</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.6914</v>
+        <v>-0.6915</v>
       </c>
       <c r="D395" t="n">
         <v>-0.8103</v>
@@ -43925,7 +43925,7 @@
         <v>-0.9292</v>
       </c>
       <c r="F395" t="n">
-        <v>-0.6914</v>
+        <v>-0.6915</v>
       </c>
       <c r="G395" t="n">
         <v>0.1393</v>
@@ -43946,7 +43946,7 @@
         <v>-0.805</v>
       </c>
       <c r="M395" t="n">
-        <v>0.3647</v>
+        <v>0.3646</v>
       </c>
     </row>
     <row r="396">
@@ -43989,7 +43989,7 @@
         <v>-0.8401999999999999</v>
       </c>
       <c r="M396" t="n">
-        <v>0.3617</v>
+        <v>0.3616</v>
       </c>
     </row>
     <row r="397">
@@ -44032,7 +44032,7 @@
         <v>-0.9742</v>
       </c>
       <c r="M397" t="n">
-        <v>0.3531</v>
+        <v>0.3532</v>
       </c>
     </row>
     <row r="398">
@@ -44075,7 +44075,7 @@
         <v>-1.0455</v>
       </c>
       <c r="M398" t="n">
-        <v>0.2701</v>
+        <v>0.2702</v>
       </c>
     </row>
     <row r="399">
@@ -44217,7 +44217,7 @@
         <v>-0.6224</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.6921</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="D402" t="n">
         <v>-0.6572</v>
@@ -44226,7 +44226,7 @@
         <v>-0.6224</v>
       </c>
       <c r="F402" t="n">
-        <v>-0.6921</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="G402" t="n">
         <v>-0.0621</v>
@@ -44247,7 +44247,7 @@
         <v>-1.4616</v>
       </c>
       <c r="M402" t="n">
-        <v>0.2564</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="403">
@@ -44260,7 +44260,7 @@
         <v>-0.5518</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.6776</v>
+        <v>-0.6775</v>
       </c>
       <c r="D403" t="n">
         <v>-0.6147</v>
@@ -44269,7 +44269,7 @@
         <v>-0.5518</v>
       </c>
       <c r="F403" t="n">
-        <v>-0.6776</v>
+        <v>-0.6775</v>
       </c>
       <c r="G403" t="n">
         <v>-0.08649999999999999</v>
@@ -44290,7 +44290,7 @@
         <v>-1.4908</v>
       </c>
       <c r="M403" t="n">
-        <v>0.2116</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="404">
@@ -44346,7 +44346,7 @@
         <v>-0.4275</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.8011</v>
+        <v>-0.8012</v>
       </c>
       <c r="D405" t="n">
         <v>-0.6143</v>
@@ -44355,7 +44355,7 @@
         <v>-0.4275</v>
       </c>
       <c r="F405" t="n">
-        <v>-0.8011</v>
+        <v>-0.8012</v>
       </c>
       <c r="G405" t="n">
         <v>-0.0624</v>
@@ -44376,7 +44376,7 @@
         <v>-1.6774</v>
       </c>
       <c r="M405" t="n">
-        <v>-0.002</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="406">
@@ -44462,7 +44462,7 @@
         <v>-1.9109</v>
       </c>
       <c r="M407" t="n">
-        <v>-0.1642</v>
+        <v>-0.1643</v>
       </c>
     </row>
     <row r="408">
@@ -44505,7 +44505,7 @@
         <v>-1.9276</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.1736</v>
+        <v>-0.1737</v>
       </c>
     </row>
     <row r="409">
@@ -44548,7 +44548,7 @@
         <v>-1.9972</v>
       </c>
       <c r="M409" t="n">
-        <v>-0.2826</v>
+        <v>-0.2827</v>
       </c>
     </row>
     <row r="410">
@@ -44561,7 +44561,7 @@
         <v>-0.2579</v>
       </c>
       <c r="C410" t="n">
-        <v>-1.0299</v>
+        <v>-1.03</v>
       </c>
       <c r="D410" t="n">
         <v>-0.6439</v>
@@ -44570,7 +44570,7 @@
         <v>-0.2579</v>
       </c>
       <c r="F410" t="n">
-        <v>-1.0299</v>
+        <v>-1.03</v>
       </c>
       <c r="G410" t="n">
         <v>0.4149</v>
@@ -44591,7 +44591,7 @@
         <v>-2.1231</v>
       </c>
       <c r="M410" t="n">
-        <v>-0.3737</v>
+        <v>-0.3739</v>
       </c>
     </row>
     <row r="411">
@@ -44604,7 +44604,7 @@
         <v>-0.2395</v>
       </c>
       <c r="C411" t="n">
-        <v>-1.0756</v>
+        <v>-1.0757</v>
       </c>
       <c r="D411" t="n">
         <v>-0.6576</v>
@@ -44613,7 +44613,7 @@
         <v>-0.2395</v>
       </c>
       <c r="F411" t="n">
-        <v>-1.0756</v>
+        <v>-1.0757</v>
       </c>
       <c r="G411" t="n">
         <v>0.5139</v>
@@ -44634,7 +44634,7 @@
         <v>-2.278</v>
       </c>
       <c r="M411" t="n">
-        <v>-0.367</v>
+        <v>-0.3672</v>
       </c>
     </row>
     <row r="412">
@@ -44647,16 +44647,16 @@
         <v>-0.2238</v>
       </c>
       <c r="C412" t="n">
-        <v>-1.1511</v>
+        <v>-1.1512</v>
       </c>
       <c r="D412" t="n">
-        <v>-0.6874</v>
+        <v>-0.6875</v>
       </c>
       <c r="E412" t="n">
         <v>-0.2238</v>
       </c>
       <c r="F412" t="n">
-        <v>-1.1511</v>
+        <v>-1.1512</v>
       </c>
       <c r="G412" t="n">
         <v>0.6071</v>
@@ -44677,7 +44677,7 @@
         <v>-2.3073</v>
       </c>
       <c r="M412" t="n">
-        <v>-0.6059</v>
+        <v>-0.6063</v>
       </c>
     </row>
     <row r="413">
@@ -44720,7 +44720,7 @@
         <v>-2.4503</v>
       </c>
       <c r="M413" t="n">
-        <v>-0.5274</v>
+        <v>-0.5276</v>
       </c>
     </row>
     <row r="414">
@@ -44806,7 +44806,7 @@
         <v>-2.6195</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.6224</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="416">
@@ -44819,16 +44819,16 @@
         <v>0.011</v>
       </c>
       <c r="C416" t="n">
-        <v>-1.304</v>
+        <v>-1.3041</v>
       </c>
       <c r="D416" t="n">
-        <v>-0.6465</v>
+        <v>-0.6466</v>
       </c>
       <c r="E416" t="n">
         <v>0.011</v>
       </c>
       <c r="F416" t="n">
-        <v>-1.304</v>
+        <v>-1.3041</v>
       </c>
       <c r="G416" t="n">
         <v>1.1086</v>
@@ -44849,7 +44849,7 @@
         <v>-2.7731</v>
       </c>
       <c r="M416" t="n">
-        <v>-0.672</v>
+        <v>-0.6721</v>
       </c>
     </row>
     <row r="417">
@@ -44892,7 +44892,7 @@
         <v>-2.8579</v>
       </c>
       <c r="M417" t="n">
-        <v>-0.7228</v>
+        <v>-0.723</v>
       </c>
     </row>
     <row r="418">
@@ -44935,7 +44935,7 @@
         <v>-2.9258</v>
       </c>
       <c r="M418" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.669</v>
       </c>
     </row>
     <row r="419">
@@ -44978,7 +44978,7 @@
         <v>-2.9947</v>
       </c>
       <c r="M419" t="n">
-        <v>-0.7301</v>
+        <v>-0.7302</v>
       </c>
     </row>
     <row r="420">
@@ -45021,7 +45021,7 @@
         <v>-2.8066</v>
       </c>
       <c r="M420" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6236</v>
       </c>
     </row>
     <row r="421">
@@ -45064,7 +45064,7 @@
         <v>-2.5738</v>
       </c>
       <c r="M421" t="n">
-        <v>-0.4443</v>
+        <v>-0.4445</v>
       </c>
     </row>
     <row r="422">
@@ -45193,7 +45193,7 @@
         <v>-1.4901</v>
       </c>
       <c r="M424" t="n">
-        <v>0.1369</v>
+        <v>0.1368</v>
       </c>
     </row>
     <row r="425">
@@ -45236,7 +45236,7 @@
         <v>-1.2112</v>
       </c>
       <c r="M425" t="n">
-        <v>0.313</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="426">
@@ -45322,7 +45322,7 @@
         <v>-0.4667</v>
       </c>
       <c r="M427" t="n">
-        <v>0.6268</v>
+        <v>0.6267</v>
       </c>
     </row>
     <row r="428">
@@ -45365,7 +45365,7 @@
         <v>-0.3771</v>
       </c>
       <c r="M428" t="n">
-        <v>0.6803</v>
+        <v>0.6802</v>
       </c>
     </row>
     <row r="429">
@@ -45378,16 +45378,16 @@
         <v>-0.5832000000000001</v>
       </c>
       <c r="C429" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="D429" t="n">
-        <v>-0.2743</v>
+        <v>-0.2744</v>
       </c>
       <c r="E429" t="n">
         <v>-0.5832000000000001</v>
       </c>
       <c r="F429" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="G429" t="n">
         <v>-0.93</v>
@@ -45408,7 +45408,7 @@
         <v>-0.3155</v>
       </c>
       <c r="M429" t="n">
-        <v>0.5572</v>
+        <v>0.5569</v>
       </c>
     </row>
     <row r="430">
@@ -45421,7 +45421,7 @@
         <v>-0.6768999999999999</v>
       </c>
       <c r="C430" t="n">
-        <v>0.0631</v>
+        <v>0.063</v>
       </c>
       <c r="D430" t="n">
         <v>-0.3069</v>
@@ -45430,7 +45430,7 @@
         <v>-0.6768999999999999</v>
       </c>
       <c r="F430" t="n">
-        <v>0.0631</v>
+        <v>0.063</v>
       </c>
       <c r="G430" t="n">
         <v>-0.8796</v>
@@ -45451,7 +45451,7 @@
         <v>-0.2178</v>
       </c>
       <c r="M430" t="n">
-        <v>0.524</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="431">
@@ -45494,7 +45494,7 @@
         <v>-0.241</v>
       </c>
       <c r="M431" t="n">
-        <v>0.5665</v>
+        <v>0.5663</v>
       </c>
     </row>
     <row r="432">
@@ -45510,7 +45510,7 @@
         <v>0.0867</v>
       </c>
       <c r="D432" t="n">
-        <v>-0.3182</v>
+        <v>-0.3183</v>
       </c>
       <c r="E432" t="n">
         <v>-0.7232</v>
@@ -45537,7 +45537,7 @@
         <v>-0.1577</v>
       </c>
       <c r="M432" t="n">
-        <v>0.458</v>
+        <v>0.4577</v>
       </c>
     </row>
     <row r="433">
@@ -45550,7 +45550,7 @@
         <v>-0.6498</v>
       </c>
       <c r="C433" t="n">
-        <v>0.1184</v>
+        <v>0.1183</v>
       </c>
       <c r="D433" t="n">
         <v>-0.2657</v>
@@ -45559,7 +45559,7 @@
         <v>-0.6498</v>
       </c>
       <c r="F433" t="n">
-        <v>0.1184</v>
+        <v>0.1183</v>
       </c>
       <c r="G433" t="n">
         <v>-0.4106</v>
@@ -45580,7 +45580,7 @@
         <v>-0.1139</v>
       </c>
       <c r="M433" t="n">
-        <v>0.5111</v>
+        <v>0.5109</v>
       </c>
     </row>
     <row r="434">
@@ -45593,7 +45593,7 @@
         <v>-0.5634</v>
       </c>
       <c r="C434" t="n">
-        <v>0.1461</v>
+        <v>0.146</v>
       </c>
       <c r="D434" t="n">
         <v>-0.2087</v>
@@ -45602,7 +45602,7 @@
         <v>-0.5634</v>
       </c>
       <c r="F434" t="n">
-        <v>0.1461</v>
+        <v>0.146</v>
       </c>
       <c r="G434" t="n">
         <v>-0.2666</v>
@@ -45623,7 +45623,7 @@
         <v>-0.0446</v>
       </c>
       <c r="M434" t="n">
-        <v>0.4525</v>
+        <v>0.4522</v>
       </c>
     </row>
     <row r="435">
@@ -45636,16 +45636,16 @@
         <v>-0.5977</v>
       </c>
       <c r="C435" t="n">
-        <v>0.1366</v>
+        <v>0.1365</v>
       </c>
       <c r="D435" t="n">
-        <v>-0.2305</v>
+        <v>-0.2306</v>
       </c>
       <c r="E435" t="n">
         <v>-0.5977</v>
       </c>
       <c r="F435" t="n">
-        <v>0.1366</v>
+        <v>0.1365</v>
       </c>
       <c r="G435" t="n">
         <v>-0.2179</v>
@@ -45666,7 +45666,7 @@
         <v>-0.0377</v>
       </c>
       <c r="M435" t="n">
-        <v>0.4093</v>
+        <v>0.4091</v>
       </c>
     </row>
     <row r="436">
@@ -45679,16 +45679,16 @@
         <v>-0.7156</v>
       </c>
       <c r="C436" t="n">
-        <v>0.1895</v>
+        <v>0.1894</v>
       </c>
       <c r="D436" t="n">
-        <v>-0.263</v>
+        <v>-0.2631</v>
       </c>
       <c r="E436" t="n">
         <v>-0.7156</v>
       </c>
       <c r="F436" t="n">
-        <v>0.1895</v>
+        <v>0.1894</v>
       </c>
       <c r="G436" t="n">
         <v>-0.2639</v>
@@ -45709,7 +45709,7 @@
         <v>0.092</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4169</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="437">
@@ -45752,7 +45752,7 @@
         <v>0.1713</v>
       </c>
       <c r="M437" t="n">
-        <v>0.4078</v>
+        <v>0.4076</v>
       </c>
     </row>
     <row r="438">
@@ -45765,7 +45765,7 @@
         <v>-0.6207</v>
       </c>
       <c r="C438" t="n">
-        <v>0.2801</v>
+        <v>0.28</v>
       </c>
       <c r="D438" t="n">
         <v>-0.1703</v>
@@ -45774,7 +45774,7 @@
         <v>-0.6207</v>
       </c>
       <c r="F438" t="n">
-        <v>0.2801</v>
+        <v>0.28</v>
       </c>
       <c r="G438" t="n">
         <v>-0.2181</v>
@@ -45795,7 +45795,7 @@
         <v>0.2607</v>
       </c>
       <c r="M438" t="n">
-        <v>0.4638</v>
+        <v>0.4636</v>
       </c>
     </row>
     <row r="439">
@@ -45811,7 +45811,7 @@
         <v>0.244</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.2081</v>
+        <v>-0.2082</v>
       </c>
       <c r="E439" t="n">
         <v>-0.6603</v>
@@ -45838,7 +45838,7 @@
         <v>0.2502</v>
       </c>
       <c r="M439" t="n">
-        <v>0.3245</v>
+        <v>0.3243</v>
       </c>
     </row>
     <row r="440">
@@ -45851,7 +45851,7 @@
         <v>-0.7383999999999999</v>
       </c>
       <c r="C440" t="n">
-        <v>0.2827</v>
+        <v>0.2826</v>
       </c>
       <c r="D440" t="n">
         <v>-0.2279</v>
@@ -45860,7 +45860,7 @@
         <v>-0.7383999999999999</v>
       </c>
       <c r="F440" t="n">
-        <v>0.2827</v>
+        <v>0.2826</v>
       </c>
       <c r="G440" t="n">
         <v>-0.3169</v>
@@ -45881,7 +45881,7 @@
         <v>0.2617</v>
       </c>
       <c r="M440" t="n">
-        <v>0.4023</v>
+        <v>0.4022</v>
       </c>
     </row>
     <row r="441">
@@ -45937,7 +45937,7 @@
         <v>-0.7405</v>
       </c>
       <c r="C442" t="n">
-        <v>0.2536</v>
+        <v>0.2535</v>
       </c>
       <c r="D442" t="n">
         <v>-0.2435</v>
@@ -45946,7 +45946,7 @@
         <v>-0.7405</v>
       </c>
       <c r="F442" t="n">
-        <v>0.2536</v>
+        <v>0.2535</v>
       </c>
       <c r="G442" t="n">
         <v>-0.3597</v>
@@ -45967,7 +45967,7 @@
         <v>0.2877</v>
       </c>
       <c r="M442" t="n">
-        <v>0.2328</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="443">
@@ -46010,7 +46010,7 @@
         <v>0.3262</v>
       </c>
       <c r="M443" t="n">
-        <v>0.2774</v>
+        <v>0.2771</v>
       </c>
     </row>
     <row r="444">
@@ -46053,7 +46053,7 @@
         <v>0.2379</v>
       </c>
       <c r="M444" t="n">
-        <v>0.2897</v>
+        <v>0.2896</v>
       </c>
     </row>
     <row r="445">
@@ -46066,7 +46066,7 @@
         <v>-0.6667999999999999</v>
       </c>
       <c r="C445" t="n">
-        <v>0.2375</v>
+        <v>0.2374</v>
       </c>
       <c r="D445" t="n">
         <v>-0.2147</v>
@@ -46075,7 +46075,7 @@
         <v>-0.6667999999999999</v>
       </c>
       <c r="F445" t="n">
-        <v>0.2375</v>
+        <v>0.2374</v>
       </c>
       <c r="G445" t="n">
         <v>-0.1277</v>
@@ -46096,7 +46096,7 @@
         <v>0.1918</v>
       </c>
       <c r="M445" t="n">
-        <v>0.1834</v>
+        <v>0.1832</v>
       </c>
     </row>
     <row r="446">
@@ -46109,7 +46109,7 @@
         <v>-0.6778999999999999</v>
       </c>
       <c r="C446" t="n">
-        <v>0.2772</v>
+        <v>0.2771</v>
       </c>
       <c r="D446" t="n">
         <v>-0.2004</v>
@@ -46118,7 +46118,7 @@
         <v>-0.6778999999999999</v>
       </c>
       <c r="F446" t="n">
-        <v>0.2772</v>
+        <v>0.2771</v>
       </c>
       <c r="G446" t="n">
         <v>-0.1745</v>
@@ -46139,7 +46139,7 @@
         <v>0.2401</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2394</v>
+        <v>0.2392</v>
       </c>
     </row>
     <row r="447">
@@ -46152,16 +46152,16 @@
         <v>-0.6881</v>
       </c>
       <c r="C447" t="n">
-        <v>0.2627</v>
+        <v>0.2626</v>
       </c>
       <c r="D447" t="n">
-        <v>-0.2127</v>
+        <v>-0.2128</v>
       </c>
       <c r="E447" t="n">
         <v>-0.6881</v>
       </c>
       <c r="F447" t="n">
-        <v>0.2627</v>
+        <v>0.2626</v>
       </c>
       <c r="G447" t="n">
         <v>-0.1809</v>
@@ -46182,7 +46182,7 @@
         <v>0.2046</v>
       </c>
       <c r="M447" t="n">
-        <v>0.1859</v>
+        <v>0.1857</v>
       </c>
     </row>
     <row r="448">
@@ -46195,7 +46195,7 @@
         <v>-0.4027</v>
       </c>
       <c r="C448" t="n">
-        <v>0.2404</v>
+        <v>0.2403</v>
       </c>
       <c r="D448" t="n">
         <v>-0.08119999999999999</v>
@@ -46204,7 +46204,7 @@
         <v>-0.4027</v>
       </c>
       <c r="F448" t="n">
-        <v>0.2404</v>
+        <v>0.2403</v>
       </c>
       <c r="G448" t="n">
         <v>-0.0814</v>
@@ -46225,7 +46225,7 @@
         <v>0.2011</v>
       </c>
       <c r="M448" t="n">
-        <v>0.1202</v>
+        <v>0.1199</v>
       </c>
     </row>
     <row r="449">
@@ -46238,16 +46238,16 @@
         <v>-0.2793</v>
       </c>
       <c r="C449" t="n">
-        <v>0.2659</v>
+        <v>0.2658</v>
       </c>
       <c r="D449" t="n">
-        <v>-0.0067</v>
+        <v>-0.0068</v>
       </c>
       <c r="E449" t="n">
         <v>-0.2793</v>
       </c>
       <c r="F449" t="n">
-        <v>0.2659</v>
+        <v>0.2658</v>
       </c>
       <c r="G449" t="n">
         <v>0.0731</v>
@@ -46268,7 +46268,7 @@
         <v>0.1767</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1538</v>
+        <v>0.1535</v>
       </c>
     </row>
     <row r="450">
@@ -46281,16 +46281,16 @@
         <v>-0.3994</v>
       </c>
       <c r="C450" t="n">
-        <v>0.2956</v>
+        <v>0.2955</v>
       </c>
       <c r="D450" t="n">
-        <v>-0.0519</v>
+        <v>-0.052</v>
       </c>
       <c r="E450" t="n">
         <v>-0.3994</v>
       </c>
       <c r="F450" t="n">
-        <v>0.2956</v>
+        <v>0.2955</v>
       </c>
       <c r="G450" t="n">
         <v>0.1192</v>
@@ -46311,7 +46311,7 @@
         <v>0.2255</v>
       </c>
       <c r="M450" t="n">
-        <v>0.1826</v>
+        <v>0.1824</v>
       </c>
     </row>
     <row r="451">
@@ -46324,16 +46324,16 @@
         <v>-0.3444</v>
       </c>
       <c r="C451" t="n">
-        <v>0.2823</v>
+        <v>0.2822</v>
       </c>
       <c r="D451" t="n">
-        <v>-0.031</v>
+        <v>-0.0311</v>
       </c>
       <c r="E451" t="n">
         <v>-0.3444</v>
       </c>
       <c r="F451" t="n">
-        <v>0.2823</v>
+        <v>0.2822</v>
       </c>
       <c r="G451" t="n">
         <v>0.1231</v>
@@ -46354,7 +46354,7 @@
         <v>0.1736</v>
       </c>
       <c r="M451" t="n">
-        <v>0.1684</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="452">
@@ -46370,7 +46370,7 @@
         <v>0.2786</v>
       </c>
       <c r="D452" t="n">
-        <v>-0.0125</v>
+        <v>-0.0126</v>
       </c>
       <c r="E452" t="n">
         <v>-0.3037</v>
@@ -46397,7 +46397,7 @@
         <v>0.1787</v>
       </c>
       <c r="M452" t="n">
-        <v>0.1857</v>
+        <v>0.1855</v>
       </c>
     </row>
     <row r="453">
@@ -46413,7 +46413,7 @@
         <v>0.2503</v>
       </c>
       <c r="D453" t="n">
-        <v>-0.0409</v>
+        <v>-0.041</v>
       </c>
       <c r="E453" t="n">
         <v>-0.3322</v>
@@ -46440,7 +46440,7 @@
         <v>0.143</v>
       </c>
       <c r="M453" t="n">
-        <v>0.197</v>
+        <v>0.1968</v>
       </c>
     </row>
     <row r="454">
@@ -46453,7 +46453,7 @@
         <v>-0.3582</v>
       </c>
       <c r="C454" t="n">
-        <v>0.2751</v>
+        <v>0.275</v>
       </c>
       <c r="D454" t="n">
         <v>-0.0416</v>
@@ -46462,7 +46462,7 @@
         <v>-0.3582</v>
       </c>
       <c r="F454" t="n">
-        <v>0.2751</v>
+        <v>0.275</v>
       </c>
       <c r="G454" t="n">
         <v>0.3201</v>
@@ -46483,7 +46483,7 @@
         <v>0.2323</v>
       </c>
       <c r="M454" t="n">
-        <v>0.2554</v>
+        <v>0.2552</v>
       </c>
     </row>
     <row r="455">
@@ -46496,7 +46496,7 @@
         <v>-0.478</v>
       </c>
       <c r="C455" t="n">
-        <v>0.2618</v>
+        <v>0.2617</v>
       </c>
       <c r="D455" t="n">
         <v>-0.1081</v>
@@ -46505,7 +46505,7 @@
         <v>-0.478</v>
       </c>
       <c r="F455" t="n">
-        <v>0.2618</v>
+        <v>0.2617</v>
       </c>
       <c r="G455" t="n">
         <v>0.1734</v>
@@ -46526,7 +46526,7 @@
         <v>0.1678</v>
       </c>
       <c r="M455" t="n">
-        <v>0.3112</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="456">
@@ -46569,7 +46569,7 @@
         <v>0.2683</v>
       </c>
       <c r="M456" t="n">
-        <v>0.3921</v>
+        <v>0.3919</v>
       </c>
     </row>
     <row r="457">
@@ -46582,7 +46582,7 @@
         <v>-0.3795</v>
       </c>
       <c r="C457" t="n">
-        <v>0.2216</v>
+        <v>0.2215</v>
       </c>
       <c r="D457" t="n">
         <v>-0.079</v>
@@ -46591,7 +46591,7 @@
         <v>-0.3795</v>
       </c>
       <c r="F457" t="n">
-        <v>0.2216</v>
+        <v>0.2215</v>
       </c>
       <c r="G457" t="n">
         <v>0.1729</v>
@@ -46612,7 +46612,7 @@
         <v>0.1279</v>
       </c>
       <c r="M457" t="n">
-        <v>0.3514</v>
+        <v>0.3511</v>
       </c>
     </row>
     <row r="458">
@@ -46625,16 +46625,16 @@
         <v>-0.4569</v>
       </c>
       <c r="C458" t="n">
-        <v>0.2474</v>
+        <v>0.2473</v>
       </c>
       <c r="D458" t="n">
-        <v>-0.1047</v>
+        <v>-0.1048</v>
       </c>
       <c r="E458" t="n">
         <v>-0.4569</v>
       </c>
       <c r="F458" t="n">
-        <v>0.2474</v>
+        <v>0.2473</v>
       </c>
       <c r="G458" t="n">
         <v>0.2205</v>
@@ -46655,7 +46655,7 @@
         <v>0.1919</v>
       </c>
       <c r="M458" t="n">
-        <v>0.3892</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="459">
@@ -46668,7 +46668,7 @@
         <v>-0.3435</v>
       </c>
       <c r="C459" t="n">
-        <v>0.2584</v>
+        <v>0.2583</v>
       </c>
       <c r="D459" t="n">
         <v>-0.0426</v>
@@ -46677,7 +46677,7 @@
         <v>-0.3435</v>
       </c>
       <c r="F459" t="n">
-        <v>0.2584</v>
+        <v>0.2583</v>
       </c>
       <c r="G459" t="n">
         <v>0.2701</v>
@@ -46698,7 +46698,7 @@
         <v>0.243</v>
       </c>
       <c r="M459" t="n">
-        <v>0.4033</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="460">
@@ -46741,7 +46741,7 @@
         <v>0.3105</v>
       </c>
       <c r="M460" t="n">
-        <v>0.3725</v>
+        <v>0.3723</v>
       </c>
     </row>
     <row r="461">
@@ -46754,7 +46754,7 @@
         <v>-0.4059</v>
       </c>
       <c r="C461" t="n">
-        <v>0.2684</v>
+        <v>0.2683</v>
       </c>
       <c r="D461" t="n">
         <v>-0.0688</v>
@@ -46763,7 +46763,7 @@
         <v>-0.4059</v>
       </c>
       <c r="F461" t="n">
-        <v>0.2684</v>
+        <v>0.2683</v>
       </c>
       <c r="G461" t="n">
         <v>0.3221</v>
@@ -46784,7 +46784,7 @@
         <v>0.3765</v>
       </c>
       <c r="M461" t="n">
-        <v>0.3938</v>
+        <v>0.3935</v>
       </c>
     </row>
     <row r="462">
@@ -46797,7 +46797,7 @@
         <v>-0.5039</v>
       </c>
       <c r="C462" t="n">
-        <v>0.2186</v>
+        <v>0.2185</v>
       </c>
       <c r="D462" t="n">
         <v>-0.1427</v>
@@ -46806,7 +46806,7 @@
         <v>-0.5039</v>
       </c>
       <c r="F462" t="n">
-        <v>0.2186</v>
+        <v>0.2185</v>
       </c>
       <c r="G462" t="n">
         <v>0.1739</v>
@@ -46827,7 +46827,7 @@
         <v>0.3018</v>
       </c>
       <c r="M462" t="n">
-        <v>0.3911</v>
+        <v>0.3909</v>
       </c>
     </row>
     <row r="463">
@@ -46840,16 +46840,16 @@
         <v>-0.4258</v>
       </c>
       <c r="C463" t="n">
-        <v>0.221</v>
+        <v>0.2208</v>
       </c>
       <c r="D463" t="n">
-        <v>-0.1024</v>
+        <v>-0.1025</v>
       </c>
       <c r="E463" t="n">
         <v>-0.4258</v>
       </c>
       <c r="F463" t="n">
-        <v>0.221</v>
+        <v>0.2208</v>
       </c>
       <c r="G463" t="n">
         <v>0.1278</v>
@@ -46870,7 +46870,7 @@
         <v>0.4368</v>
       </c>
       <c r="M463" t="n">
-        <v>0.3329</v>
+        <v>0.3326</v>
       </c>
     </row>
     <row r="464">
@@ -46883,7 +46883,7 @@
         <v>-0.4738</v>
       </c>
       <c r="C464" t="n">
-        <v>0.2787</v>
+        <v>0.2786</v>
       </c>
       <c r="D464" t="n">
         <v>-0.09760000000000001</v>
@@ -46892,7 +46892,7 @@
         <v>-0.4738</v>
       </c>
       <c r="F464" t="n">
-        <v>0.2787</v>
+        <v>0.2786</v>
       </c>
       <c r="G464" t="n">
         <v>0.07679999999999999</v>
@@ -46913,7 +46913,7 @@
         <v>0.3657</v>
       </c>
       <c r="M464" t="n">
-        <v>0.3718</v>
+        <v>0.3715</v>
       </c>
     </row>
     <row r="465">
@@ -46926,7 +46926,7 @@
         <v>-0.4822</v>
       </c>
       <c r="C465" t="n">
-        <v>0.3575</v>
+        <v>0.3574</v>
       </c>
       <c r="D465" t="n">
         <v>-0.0624</v>
@@ -46935,7 +46935,7 @@
         <v>-0.4822</v>
       </c>
       <c r="F465" t="n">
-        <v>0.3575</v>
+        <v>0.3574</v>
       </c>
       <c r="G465" t="n">
         <v>0.1263</v>
@@ -46956,7 +46956,7 @@
         <v>0.4497</v>
       </c>
       <c r="M465" t="n">
-        <v>0.3814</v>
+        <v>0.3811</v>
       </c>
     </row>
     <row r="466">
@@ -46969,16 +46969,16 @@
         <v>-0.4002</v>
       </c>
       <c r="C466" t="n">
-        <v>0.3963</v>
+        <v>0.3962</v>
       </c>
       <c r="D466" t="n">
-        <v>-0.0019</v>
+        <v>-0.002</v>
       </c>
       <c r="E466" t="n">
         <v>-0.4002</v>
       </c>
       <c r="F466" t="n">
-        <v>0.3963</v>
+        <v>0.3962</v>
       </c>
       <c r="G466" t="n">
         <v>0.2242</v>
@@ -46999,7 +46999,7 @@
         <v>0.4648</v>
       </c>
       <c r="M466" t="n">
-        <v>0.3246</v>
+        <v>0.3242</v>
       </c>
     </row>
     <row r="467">
@@ -47012,7 +47012,7 @@
         <v>-0.2589</v>
       </c>
       <c r="C467" t="n">
-        <v>0.471</v>
+        <v>0.4708</v>
       </c>
       <c r="D467" t="n">
         <v>0.106</v>
@@ -47021,7 +47021,7 @@
         <v>-0.2589</v>
       </c>
       <c r="F467" t="n">
-        <v>0.471</v>
+        <v>0.4708</v>
       </c>
       <c r="G467" t="n">
         <v>0.2243</v>
@@ -47042,7 +47042,7 @@
         <v>0.441</v>
       </c>
       <c r="M467" t="n">
-        <v>0.3803</v>
+        <v>0.3799</v>
       </c>
     </row>
     <row r="468">
@@ -47055,16 +47055,16 @@
         <v>-0.3495</v>
       </c>
       <c r="C468" t="n">
-        <v>0.5621</v>
+        <v>0.5619</v>
       </c>
       <c r="D468" t="n">
-        <v>0.1063</v>
+        <v>0.1062</v>
       </c>
       <c r="E468" t="n">
         <v>-0.3495</v>
       </c>
       <c r="F468" t="n">
-        <v>0.5621</v>
+        <v>0.5619</v>
       </c>
       <c r="G468" t="n">
         <v>0.2241</v>
@@ -47085,7 +47085,7 @@
         <v>0.5666</v>
       </c>
       <c r="M468" t="n">
-        <v>0.3652</v>
+        <v>0.3647</v>
       </c>
     </row>
     <row r="469">
@@ -47098,7 +47098,7 @@
         <v>-0.142</v>
       </c>
       <c r="C469" t="n">
-        <v>0.6041</v>
+        <v>0.604</v>
       </c>
       <c r="D469" t="n">
         <v>0.231</v>
@@ -47107,7 +47107,7 @@
         <v>-0.142</v>
       </c>
       <c r="F469" t="n">
-        <v>0.6041</v>
+        <v>0.604</v>
       </c>
       <c r="G469" t="n">
         <v>0.5673</v>
@@ -47128,7 +47128,7 @@
         <v>0.4979</v>
       </c>
       <c r="M469" t="n">
-        <v>0.3939</v>
+        <v>0.3935</v>
       </c>
     </row>
     <row r="470">
@@ -47141,16 +47141,16 @@
         <v>-0.047</v>
       </c>
       <c r="C470" t="n">
-        <v>0.6696</v>
+        <v>0.6694</v>
       </c>
       <c r="D470" t="n">
-        <v>0.3113</v>
+        <v>0.3112</v>
       </c>
       <c r="E470" t="n">
         <v>-0.047</v>
       </c>
       <c r="F470" t="n">
-        <v>0.6696</v>
+        <v>0.6694</v>
       </c>
       <c r="G470" t="n">
         <v>0.0803</v>
@@ -47171,7 +47171,7 @@
         <v>0.5364</v>
       </c>
       <c r="M470" t="n">
-        <v>0.3832</v>
+        <v>0.3827</v>
       </c>
     </row>
     <row r="471">
@@ -47184,16 +47184,16 @@
         <v>-0.0159</v>
       </c>
       <c r="C471" t="n">
-        <v>0.7269</v>
+        <v>0.7267</v>
       </c>
       <c r="D471" t="n">
-        <v>0.3555</v>
+        <v>0.3554</v>
       </c>
       <c r="E471" t="n">
         <v>-0.0159</v>
       </c>
       <c r="F471" t="n">
-        <v>0.7269</v>
+        <v>0.7267</v>
       </c>
       <c r="G471" t="n">
         <v>0.0842</v>
@@ -47214,7 +47214,7 @@
         <v>0.6054</v>
       </c>
       <c r="M471" t="n">
-        <v>0.3036</v>
+        <v>0.3031</v>
       </c>
     </row>
     <row r="472">
@@ -47227,16 +47227,16 @@
         <v>0.0743</v>
       </c>
       <c r="C472" t="n">
-        <v>0.7711</v>
+        <v>0.7709</v>
       </c>
       <c r="D472" t="n">
-        <v>0.4227</v>
+        <v>0.4226</v>
       </c>
       <c r="E472" t="n">
         <v>0.0743</v>
       </c>
       <c r="F472" t="n">
-        <v>0.7711</v>
+        <v>0.7709</v>
       </c>
       <c r="G472" t="n">
         <v>-0.0065</v>
@@ -47257,7 +47257,7 @@
         <v>0.6002999999999999</v>
       </c>
       <c r="M472" t="n">
-        <v>0.2851</v>
+        <v>0.2847</v>
       </c>
     </row>
     <row r="473">
@@ -47270,7 +47270,7 @@
         <v>0.2305</v>
       </c>
       <c r="C473" t="n">
-        <v>0.9117</v>
+        <v>0.9116</v>
       </c>
       <c r="D473" t="n">
         <v>0.5711000000000001</v>
@@ -47279,7 +47279,7 @@
         <v>0.2305</v>
       </c>
       <c r="F473" t="n">
-        <v>0.9117</v>
+        <v>0.9116</v>
       </c>
       <c r="G473" t="n">
         <v>0.033</v>
@@ -47300,7 +47300,7 @@
         <v>0.6629</v>
       </c>
       <c r="M473" t="n">
-        <v>0.4931</v>
+        <v>0.4929</v>
       </c>
     </row>
     <row r="474">
@@ -47316,7 +47316,7 @@
         <v>0.9523</v>
       </c>
       <c r="D474" t="n">
-        <v>0.6978</v>
+        <v>0.6977</v>
       </c>
       <c r="E474" t="n">
         <v>0.4432</v>
@@ -47343,7 +47343,7 @@
         <v>0.6934</v>
       </c>
       <c r="M474" t="n">
-        <v>0.4037</v>
+        <v>0.4036</v>
       </c>
     </row>
     <row r="475">
@@ -47386,7 +47386,7 @@
         <v>0.7379</v>
       </c>
       <c r="M475" t="n">
-        <v>0.3763</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="476">
@@ -47399,7 +47399,7 @@
         <v>0.6325</v>
       </c>
       <c r="C476" t="n">
-        <v>1.0342</v>
+        <v>1.0341</v>
       </c>
       <c r="D476" t="n">
         <v>0.8333</v>
@@ -47408,7 +47408,7 @@
         <v>0.6325</v>
       </c>
       <c r="F476" t="n">
-        <v>1.0342</v>
+        <v>1.0341</v>
       </c>
       <c r="G476" t="n">
         <v>0.5196</v>
@@ -47429,7 +47429,7 @@
         <v>0.6847</v>
       </c>
       <c r="M476" t="n">
-        <v>0.3134</v>
+        <v>0.3131</v>
       </c>
     </row>
     <row r="477">
@@ -47442,16 +47442,16 @@
         <v>0.6539</v>
       </c>
       <c r="C477" t="n">
-        <v>1.0471</v>
+        <v>1.047</v>
       </c>
       <c r="D477" t="n">
-        <v>0.8505</v>
+        <v>0.8504</v>
       </c>
       <c r="E477" t="n">
         <v>0.6539</v>
       </c>
       <c r="F477" t="n">
-        <v>1.0471</v>
+        <v>1.047</v>
       </c>
       <c r="G477" t="n">
         <v>0.5696</v>
@@ -47472,7 +47472,7 @@
         <v>0.5770999999999999</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2798</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="478">
@@ -47485,16 +47485,16 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="C478" t="n">
-        <v>1.1124</v>
+        <v>1.1123</v>
       </c>
       <c r="D478" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9117</v>
       </c>
       <c r="E478" t="n">
         <v>0.7112000000000001</v>
       </c>
       <c r="F478" t="n">
-        <v>1.1124</v>
+        <v>1.1123</v>
       </c>
       <c r="G478" t="n">
         <v>0.5206</v>
@@ -47515,7 +47515,7 @@
         <v>0.6845</v>
       </c>
       <c r="M478" t="n">
-        <v>0.2136</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="479">
@@ -47528,7 +47528,7 @@
         <v>0.7681</v>
       </c>
       <c r="C479" t="n">
-        <v>1.1932</v>
+        <v>1.1931</v>
       </c>
       <c r="D479" t="n">
         <v>0.9806</v>
@@ -47537,7 +47537,7 @@
         <v>0.7681</v>
       </c>
       <c r="F479" t="n">
-        <v>1.1932</v>
+        <v>1.1931</v>
       </c>
       <c r="G479" t="n">
         <v>0.622</v>
@@ -47558,7 +47558,7 @@
         <v>0.6926</v>
       </c>
       <c r="M479" t="n">
-        <v>0.2585</v>
+        <v>0.2582</v>
       </c>
     </row>
     <row r="480">
@@ -47571,16 +47571,16 @@
         <v>0.8911</v>
       </c>
       <c r="C480" t="n">
-        <v>1.2027</v>
+        <v>1.2026</v>
       </c>
       <c r="D480" t="n">
-        <v>1.0469</v>
+        <v>1.0468</v>
       </c>
       <c r="E480" t="n">
         <v>0.8911</v>
       </c>
       <c r="F480" t="n">
-        <v>1.2027</v>
+        <v>1.2026</v>
       </c>
       <c r="G480" t="n">
         <v>0.768</v>
@@ -47601,7 +47601,7 @@
         <v>0.5778</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2488</v>
+        <v>0.2485</v>
       </c>
     </row>
     <row r="481">
@@ -47614,7 +47614,7 @@
         <v>1.0906</v>
       </c>
       <c r="C481" t="n">
-        <v>1.2863</v>
+        <v>1.2862</v>
       </c>
       <c r="D481" t="n">
         <v>1.1884</v>
@@ -47623,7 +47623,7 @@
         <v>1.0906</v>
       </c>
       <c r="F481" t="n">
-        <v>1.2863</v>
+        <v>1.2862</v>
       </c>
       <c r="G481" t="n">
         <v>1.5423</v>
@@ -47644,7 +47644,7 @@
         <v>0.6435999999999999</v>
       </c>
       <c r="M481" t="n">
-        <v>0.2395</v>
+        <v>0.2392</v>
       </c>
     </row>
     <row r="482">
@@ -47657,16 +47657,16 @@
         <v>0.9982</v>
       </c>
       <c r="C482" t="n">
-        <v>1.2407</v>
+        <v>1.2406</v>
       </c>
       <c r="D482" t="n">
-        <v>1.1195</v>
+        <v>1.1194</v>
       </c>
       <c r="E482" t="n">
         <v>0.9982</v>
       </c>
       <c r="F482" t="n">
-        <v>1.2407</v>
+        <v>1.2406</v>
       </c>
       <c r="G482" t="n">
         <v>0.8703</v>
@@ -47687,7 +47687,7 @@
         <v>0.6862</v>
       </c>
       <c r="M482" t="n">
-        <v>0.2445</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="483">
@@ -47700,16 +47700,16 @@
         <v>0.9845</v>
       </c>
       <c r="C483" t="n">
-        <v>1.1607</v>
+        <v>1.1606</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0726</v>
+        <v>1.0725</v>
       </c>
       <c r="E483" t="n">
         <v>0.9845</v>
       </c>
       <c r="F483" t="n">
-        <v>1.1607</v>
+        <v>1.1606</v>
       </c>
       <c r="G483" t="n">
         <v>0.8702</v>
@@ -47730,7 +47730,7 @@
         <v>0.61</v>
       </c>
       <c r="M483" t="n">
-        <v>0.2283</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="484">
@@ -47743,7 +47743,7 @@
         <v>0.9379</v>
       </c>
       <c r="C484" t="n">
-        <v>1.1434</v>
+        <v>1.1432</v>
       </c>
       <c r="D484" t="n">
         <v>1.0406</v>
@@ -47752,7 +47752,7 @@
         <v>0.9379</v>
       </c>
       <c r="F484" t="n">
-        <v>1.1434</v>
+        <v>1.1432</v>
       </c>
       <c r="G484" t="n">
         <v>0.8731</v>
@@ -47773,7 +47773,7 @@
         <v>0.6838</v>
       </c>
       <c r="M484" t="n">
-        <v>0.2414</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="485">
@@ -47786,7 +47786,7 @@
         <v>1.0379</v>
       </c>
       <c r="C485" t="n">
-        <v>1.0808</v>
+        <v>1.0806</v>
       </c>
       <c r="D485" t="n">
         <v>1.0593</v>
@@ -47795,7 +47795,7 @@
         <v>1.0379</v>
       </c>
       <c r="F485" t="n">
-        <v>1.0808</v>
+        <v>1.0806</v>
       </c>
       <c r="G485" t="n">
         <v>1.7483</v>
@@ -47816,7 +47816,7 @@
         <v>0.6618000000000001</v>
       </c>
       <c r="M485" t="n">
-        <v>0.2107</v>
+        <v>0.2103</v>
       </c>
     </row>
     <row r="486">
@@ -47829,16 +47829,16 @@
         <v>0.9735</v>
       </c>
       <c r="C486" t="n">
-        <v>1.0255</v>
+        <v>1.0254</v>
       </c>
       <c r="D486" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="E486" t="n">
         <v>0.9735</v>
       </c>
       <c r="F486" t="n">
-        <v>1.0255</v>
+        <v>1.0254</v>
       </c>
       <c r="G486" t="n">
         <v>1.7932</v>
@@ -47859,7 +47859,7 @@
         <v>0.5447</v>
       </c>
       <c r="M486" t="n">
-        <v>0.3388</v>
+        <v>0.3384</v>
       </c>
     </row>
     <row r="487">
@@ -47872,16 +47872,16 @@
         <v>0.9487</v>
       </c>
       <c r="C487" t="n">
-        <v>0.9633</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="D487" t="n">
-        <v>0.956</v>
+        <v>0.9559</v>
       </c>
       <c r="E487" t="n">
         <v>0.9487</v>
       </c>
       <c r="F487" t="n">
-        <v>0.9633</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G487" t="n">
         <v>1.7933</v>
@@ -47902,7 +47902,7 @@
         <v>0.5776</v>
       </c>
       <c r="M487" t="n">
-        <v>0.2612</v>
+        <v>0.2608</v>
       </c>
     </row>
     <row r="488">
@@ -47915,16 +47915,16 @@
         <v>0.9189000000000001</v>
       </c>
       <c r="C488" t="n">
-        <v>0.9494</v>
+        <v>0.9493</v>
       </c>
       <c r="D488" t="n">
-        <v>0.9342</v>
+        <v>0.9341</v>
       </c>
       <c r="E488" t="n">
         <v>0.9189000000000001</v>
       </c>
       <c r="F488" t="n">
-        <v>0.9494</v>
+        <v>0.9493</v>
       </c>
       <c r="G488" t="n">
         <v>1.7969</v>
@@ -47945,7 +47945,7 @@
         <v>0.584</v>
       </c>
       <c r="M488" t="n">
-        <v>0.2476</v>
+        <v>0.2472</v>
       </c>
     </row>
     <row r="489">
@@ -47958,16 +47958,16 @@
         <v>0.8653</v>
       </c>
       <c r="C489" t="n">
-        <v>0.9121</v>
+        <v>0.9119</v>
       </c>
       <c r="D489" t="n">
-        <v>0.8887</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="E489" t="n">
         <v>0.8653</v>
       </c>
       <c r="F489" t="n">
-        <v>0.9121</v>
+        <v>0.9119</v>
       </c>
       <c r="G489" t="n">
         <v>1.6948</v>
@@ -47988,7 +47988,7 @@
         <v>0.5092</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2671</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="490">
@@ -48001,7 +48001,7 @@
         <v>0.8836000000000001</v>
       </c>
       <c r="C490" t="n">
-        <v>0.9011</v>
+        <v>0.901</v>
       </c>
       <c r="D490" t="n">
         <v>0.8923</v>
@@ -48010,7 +48010,7 @@
         <v>0.8836000000000001</v>
       </c>
       <c r="F490" t="n">
-        <v>0.9011</v>
+        <v>0.901</v>
       </c>
       <c r="G490" t="n">
         <v>1.6467</v>
@@ -48031,7 +48031,7 @@
         <v>0.5525</v>
       </c>
       <c r="M490" t="n">
-        <v>0.2441</v>
+        <v>0.2437</v>
       </c>
     </row>
     <row r="491">
@@ -48044,16 +48044,16 @@
         <v>0.8941</v>
       </c>
       <c r="C491" t="n">
-        <v>0.8922</v>
+        <v>0.892</v>
       </c>
       <c r="D491" t="n">
-        <v>0.8932</v>
+        <v>0.8931</v>
       </c>
       <c r="E491" t="n">
         <v>0.8941</v>
       </c>
       <c r="F491" t="n">
-        <v>0.8922</v>
+        <v>0.892</v>
       </c>
       <c r="G491" t="n">
         <v>1.6021</v>
@@ -48074,7 +48074,7 @@
         <v>0.595</v>
       </c>
       <c r="M491" t="n">
-        <v>0.2427</v>
+        <v>0.2423</v>
       </c>
     </row>
     <row r="492">
@@ -48087,16 +48087,16 @@
         <v>0.9697</v>
       </c>
       <c r="C492" t="n">
-        <v>0.8806</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="D492" t="n">
-        <v>0.9252</v>
+        <v>0.9251</v>
       </c>
       <c r="E492" t="n">
         <v>0.9697</v>
       </c>
       <c r="F492" t="n">
-        <v>0.8806</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="G492" t="n">
         <v>1.4585</v>
@@ -48117,7 +48117,7 @@
         <v>0.5249</v>
       </c>
       <c r="M492" t="n">
-        <v>0.3191</v>
+        <v>0.3188</v>
       </c>
     </row>
     <row r="493">
@@ -48130,16 +48130,16 @@
         <v>0.7104</v>
       </c>
       <c r="C493" t="n">
-        <v>0.8658</v>
+        <v>0.8657</v>
       </c>
       <c r="D493" t="n">
-        <v>0.7881</v>
+        <v>0.788</v>
       </c>
       <c r="E493" t="n">
         <v>0.7104</v>
       </c>
       <c r="F493" t="n">
-        <v>0.8658</v>
+        <v>0.8657</v>
       </c>
       <c r="G493" t="n">
         <v>0.252</v>
@@ -48160,7 +48160,7 @@
         <v>0.5299</v>
       </c>
       <c r="M493" t="n">
-        <v>0.3282</v>
+        <v>0.3279</v>
       </c>
     </row>
     <row r="494">
@@ -48173,16 +48173,16 @@
         <v>0.9415</v>
       </c>
       <c r="C494" t="n">
-        <v>0.8913</v>
+        <v>0.8912</v>
       </c>
       <c r="D494" t="n">
-        <v>0.9164</v>
+        <v>0.9163</v>
       </c>
       <c r="E494" t="n">
         <v>0.9415</v>
       </c>
       <c r="F494" t="n">
-        <v>0.8913</v>
+        <v>0.8912</v>
       </c>
       <c r="G494" t="n">
         <v>1.3195</v>
@@ -48203,7 +48203,7 @@
         <v>0.5125999999999999</v>
       </c>
       <c r="M494" t="n">
-        <v>0.4554</v>
+        <v>0.4552</v>
       </c>
     </row>
     <row r="495">
@@ -48216,7 +48216,7 @@
         <v>0.9113</v>
       </c>
       <c r="C495" t="n">
-        <v>0.8484</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="D495" t="n">
         <v>0.8798</v>
@@ -48225,7 +48225,7 @@
         <v>0.9113</v>
       </c>
       <c r="F495" t="n">
-        <v>0.8484</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="G495" t="n">
         <v>1.2155</v>
@@ -48246,7 +48246,7 @@
         <v>0.5885</v>
       </c>
       <c r="M495" t="n">
-        <v>0.3092</v>
+        <v>0.3088</v>
       </c>
     </row>
     <row r="496">
@@ -48289,7 +48289,7 @@
         <v>0.528</v>
       </c>
       <c r="M496" t="n">
-        <v>0.7318</v>
+        <v>0.7316</v>
       </c>
     </row>
     <row r="497">
@@ -48302,16 +48302,16 @@
         <v>0.7696</v>
       </c>
       <c r="C497" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9329</v>
       </c>
       <c r="D497" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8512</v>
       </c>
       <c r="E497" t="n">
         <v>0.7696</v>
       </c>
       <c r="F497" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9329</v>
       </c>
       <c r="G497" t="n">
         <v>0.4393</v>
@@ -48332,7 +48332,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="M497" t="n">
-        <v>0.7381</v>
+        <v>0.7378</v>
       </c>
     </row>
     <row r="498">
@@ -48345,16 +48345,16 @@
         <v>0.7936</v>
       </c>
       <c r="C498" t="n">
-        <v>0.9005</v>
+        <v>0.9004</v>
       </c>
       <c r="D498" t="n">
-        <v>0.8471</v>
+        <v>0.847</v>
       </c>
       <c r="E498" t="n">
         <v>0.7936</v>
       </c>
       <c r="F498" t="n">
-        <v>0.9005</v>
+        <v>0.9004</v>
       </c>
       <c r="G498" t="n">
         <v>0.3442</v>
@@ -48375,7 +48375,7 @@
         <v>0.5169</v>
       </c>
       <c r="M498" t="n">
-        <v>0.6904</v>
+        <v>0.6902</v>
       </c>
     </row>
     <row r="499">
@@ -48388,7 +48388,7 @@
         <v>0.7819</v>
       </c>
       <c r="C499" t="n">
-        <v>0.831</v>
+        <v>0.8309</v>
       </c>
       <c r="D499" t="n">
         <v>0.8064</v>
@@ -48397,7 +48397,7 @@
         <v>0.7819</v>
       </c>
       <c r="F499" t="n">
-        <v>0.831</v>
+        <v>0.8309</v>
       </c>
       <c r="G499" t="n">
         <v>0.2961</v>
@@ -48418,7 +48418,7 @@
         <v>0.4824</v>
       </c>
       <c r="M499" t="n">
-        <v>0.5827</v>
+        <v>0.5825</v>
       </c>
     </row>
     <row r="500">
@@ -48431,7 +48431,7 @@
         <v>0.7237</v>
       </c>
       <c r="C500" t="n">
-        <v>0.8415</v>
+        <v>0.8414</v>
       </c>
       <c r="D500" t="n">
         <v>0.7826</v>
@@ -48440,7 +48440,7 @@
         <v>0.7237</v>
       </c>
       <c r="F500" t="n">
-        <v>0.8415</v>
+        <v>0.8414</v>
       </c>
       <c r="G500" t="n">
         <v>0.2002</v>
@@ -48461,7 +48461,7 @@
         <v>0.5273</v>
       </c>
       <c r="M500" t="n">
-        <v>0.5985</v>
+        <v>0.5982</v>
       </c>
     </row>
     <row r="501">
@@ -48504,7 +48504,7 @@
         <v>0.478</v>
       </c>
       <c r="M501" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5456</v>
       </c>
     </row>
     <row r="502">
@@ -48517,7 +48517,7 @@
         <v>0.6452</v>
       </c>
       <c r="C502" t="n">
-        <v>0.7441</v>
+        <v>0.744</v>
       </c>
       <c r="D502" t="n">
         <v>0.6946</v>
@@ -48526,7 +48526,7 @@
         <v>0.6452</v>
       </c>
       <c r="F502" t="n">
-        <v>0.7441</v>
+        <v>0.744</v>
       </c>
       <c r="G502" t="n">
         <v>0.1533</v>
@@ -48547,7 +48547,7 @@
         <v>0.4749</v>
       </c>
       <c r="M502" t="n">
-        <v>0.4578</v>
+        <v>0.4575</v>
       </c>
     </row>
     <row r="503">
@@ -48590,7 +48590,7 @@
         <v>0.4547</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4343</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="504">
@@ -48603,7 +48603,7 @@
         <v>0.5724</v>
       </c>
       <c r="C504" t="n">
-        <v>0.6887</v>
+        <v>0.6886</v>
       </c>
       <c r="D504" t="n">
         <v>0.6304999999999999</v>
@@ -48612,7 +48612,7 @@
         <v>0.5724</v>
       </c>
       <c r="F504" t="n">
-        <v>0.6887</v>
+        <v>0.6886</v>
       </c>
       <c r="G504" t="n">
         <v>0.2485</v>
@@ -48633,7 +48633,7 @@
         <v>0.4472</v>
       </c>
       <c r="M504" t="n">
-        <v>0.4244</v>
+        <v>0.4241</v>
       </c>
     </row>
     <row r="505">
@@ -48646,16 +48646,16 @@
         <v>0.5433</v>
       </c>
       <c r="C505" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6496</v>
       </c>
       <c r="D505" t="n">
-        <v>0.5965</v>
+        <v>0.5964</v>
       </c>
       <c r="E505" t="n">
         <v>0.5433</v>
       </c>
       <c r="F505" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6496</v>
       </c>
       <c r="G505" t="n">
         <v>0.2554</v>
@@ -48676,7 +48676,7 @@
         <v>0.4077</v>
       </c>
       <c r="M505" t="n">
-        <v>0.3748</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="506">
@@ -48689,16 +48689,16 @@
         <v>0.4896</v>
       </c>
       <c r="C506" t="n">
-        <v>0.6263</v>
+        <v>0.6262</v>
       </c>
       <c r="D506" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5579</v>
       </c>
       <c r="E506" t="n">
         <v>0.4896</v>
       </c>
       <c r="F506" t="n">
-        <v>0.6263</v>
+        <v>0.6262</v>
       </c>
       <c r="G506" t="n">
         <v>0.2564</v>
@@ -48719,7 +48719,7 @@
         <v>0.4757</v>
       </c>
       <c r="M506" t="n">
-        <v>0.3153</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="507">
@@ -48732,16 +48732,16 @@
         <v>0.4606</v>
       </c>
       <c r="C507" t="n">
-        <v>0.5868</v>
+        <v>0.5867</v>
       </c>
       <c r="D507" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5236</v>
       </c>
       <c r="E507" t="n">
         <v>0.4606</v>
       </c>
       <c r="F507" t="n">
-        <v>0.5868</v>
+        <v>0.5867</v>
       </c>
       <c r="G507" t="n">
         <v>0.298</v>
@@ -48762,7 +48762,7 @@
         <v>0.4013</v>
       </c>
       <c r="M507" t="n">
-        <v>0.314</v>
+        <v>0.3137</v>
       </c>
     </row>
     <row r="508">
@@ -48848,7 +48848,7 @@
         <v>0.417</v>
       </c>
       <c r="M509" t="n">
-        <v>0.5486</v>
+        <v>0.5488</v>
       </c>
     </row>
     <row r="510">
@@ -48891,7 +48891,7 @@
         <v>0.4044</v>
       </c>
       <c r="M510" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5712</v>
       </c>
     </row>
     <row r="511">
@@ -48934,7 +48934,7 @@
         <v>0.3745</v>
       </c>
       <c r="M511" t="n">
-        <v>0.6311</v>
+        <v>0.6312</v>
       </c>
     </row>
     <row r="512">
@@ -48947,7 +48947,7 @@
         <v>0.3167</v>
       </c>
       <c r="C512" t="n">
-        <v>0.6271</v>
+        <v>0.6272</v>
       </c>
       <c r="D512" t="n">
         <v>0.4719</v>
@@ -48956,7 +48956,7 @@
         <v>0.3167</v>
       </c>
       <c r="F512" t="n">
-        <v>0.6271</v>
+        <v>0.6272</v>
       </c>
       <c r="G512" t="n">
         <v>0.1156</v>
@@ -48977,7 +48977,7 @@
         <v>0.437</v>
       </c>
       <c r="M512" t="n">
-        <v>0.6435</v>
+        <v>0.6438</v>
       </c>
     </row>
     <row r="513">
@@ -48990,7 +48990,7 @@
         <v>0.2714</v>
       </c>
       <c r="C513" t="n">
-        <v>0.5878</v>
+        <v>0.5879</v>
       </c>
       <c r="D513" t="n">
         <v>0.4296</v>
@@ -48999,7 +48999,7 @@
         <v>0.2714</v>
       </c>
       <c r="F513" t="n">
-        <v>0.5878</v>
+        <v>0.5879</v>
       </c>
       <c r="G513" t="n">
         <v>0.089</v>
@@ -49020,7 +49020,7 @@
         <v>0.3664</v>
       </c>
       <c r="M513" t="n">
-        <v>0.5959</v>
+        <v>0.5961</v>
       </c>
     </row>
     <row r="514">
@@ -49063,7 +49063,7 @@
         <v>0.3239</v>
       </c>
       <c r="M514" t="n">
-        <v>0.4975</v>
+        <v>0.4976</v>
       </c>
     </row>
     <row r="515">
@@ -49106,7 +49106,7 @@
         <v>0.2758</v>
       </c>
       <c r="M515" t="n">
-        <v>0.5457</v>
+        <v>0.5458</v>
       </c>
     </row>
     <row r="516">
@@ -49149,7 +49149,7 @@
         <v>0.308</v>
       </c>
       <c r="M516" t="n">
-        <v>0.5345</v>
+        <v>0.5346</v>
       </c>
     </row>
     <row r="517">
@@ -49278,7 +49278,7 @@
         <v>0.287</v>
       </c>
       <c r="M519" t="n">
-        <v>0.4422</v>
+        <v>0.4421</v>
       </c>
     </row>
     <row r="520">
@@ -49321,7 +49321,7 @@
         <v>0.2884</v>
       </c>
       <c r="M520" t="n">
-        <v>0.4386</v>
+        <v>0.4385</v>
       </c>
     </row>
     <row r="521">
@@ -49364,7 +49364,7 @@
         <v>0.2351</v>
       </c>
       <c r="M521" t="n">
-        <v>0.4077</v>
+        <v>0.4076</v>
       </c>
     </row>
     <row r="522">
@@ -49536,7 +49536,7 @@
         <v>0.1585</v>
       </c>
       <c r="M525" t="n">
-        <v>0.3922</v>
+        <v>0.3921</v>
       </c>
     </row>
     <row r="526">
@@ -49592,16 +49592,16 @@
         <v>0.4338</v>
       </c>
       <c r="C527" t="n">
-        <v>0.3025</v>
+        <v>0.3024</v>
       </c>
       <c r="D527" t="n">
-        <v>0.3682</v>
+        <v>0.3681</v>
       </c>
       <c r="E527" t="n">
         <v>0.4338</v>
       </c>
       <c r="F527" t="n">
-        <v>0.3025</v>
+        <v>0.3024</v>
       </c>
       <c r="G527" t="n">
         <v>0.6864</v>
@@ -49622,7 +49622,7 @@
         <v>0.2102</v>
       </c>
       <c r="M527" t="n">
-        <v>0.3663</v>
+        <v>0.3662</v>
       </c>
     </row>
     <row r="528">
@@ -49665,7 +49665,7 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="M528" t="n">
-        <v>0.3614</v>
+        <v>0.3613</v>
       </c>
     </row>
     <row r="529">
@@ -49708,7 +49708,7 @@
         <v>0.1209</v>
       </c>
       <c r="M529" t="n">
-        <v>0.3482</v>
+        <v>0.3481</v>
       </c>
     </row>
     <row r="530">
@@ -49923,7 +49923,7 @@
         <v>0.033</v>
       </c>
       <c r="M534" t="n">
-        <v>0.2845</v>
+        <v>0.2844</v>
       </c>
     </row>
     <row r="535">
@@ -50009,7 +50009,7 @@
         <v>-0.0072</v>
       </c>
       <c r="M536" t="n">
-        <v>0.2574</v>
+        <v>0.2575</v>
       </c>
     </row>
     <row r="537">
@@ -50022,7 +50022,7 @@
         <v>0.3064</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.0255</v>
+        <v>-0.0256</v>
       </c>
       <c r="D537" t="n">
         <v>0.1404</v>
@@ -50031,7 +50031,7 @@
         <v>0.3064</v>
       </c>
       <c r="F537" t="n">
-        <v>-0.0255</v>
+        <v>-0.0256</v>
       </c>
       <c r="G537" t="n">
         <v>0.7305</v>
@@ -50108,7 +50108,7 @@
         <v>0.3108</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.0599</v>
+        <v>-0.06</v>
       </c>
       <c r="D539" t="n">
         <v>0.1254</v>
@@ -50117,7 +50117,7 @@
         <v>0.3108</v>
       </c>
       <c r="F539" t="n">
-        <v>-0.0599</v>
+        <v>-0.06</v>
       </c>
       <c r="G539" t="n">
         <v>0.7813</v>
@@ -50138,7 +50138,7 @@
         <v>-0.0314</v>
       </c>
       <c r="M539" t="n">
-        <v>0.1051</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="540">
@@ -50224,7 +50224,7 @@
         <v>-0.0895</v>
       </c>
       <c r="M541" t="n">
-        <v>0.0008</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="542">
@@ -50310,7 +50310,7 @@
         <v>-0.2796</v>
       </c>
       <c r="M543" t="n">
-        <v>0.0453</v>
+        <v>0.0454</v>
       </c>
     </row>
     <row r="544">
@@ -50396,7 +50396,7 @@
         <v>-0.3111</v>
       </c>
       <c r="M545" t="n">
-        <v>-0.0192</v>
+        <v>-0.0191</v>
       </c>
     </row>
     <row r="546">
@@ -50412,7 +50412,7 @@
         <v>-0.2466</v>
       </c>
       <c r="D546" t="n">
-        <v>-0.0223</v>
+        <v>-0.0222</v>
       </c>
       <c r="E546" t="n">
         <v>0.2021</v>
@@ -50482,7 +50482,7 @@
         <v>-0.4569</v>
       </c>
       <c r="M547" t="n">
-        <v>-0.0468</v>
+        <v>-0.0467</v>
       </c>
     </row>
     <row r="548">
@@ -50495,7 +50495,7 @@
         <v>0.2004</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.3276</v>
+        <v>-0.3275</v>
       </c>
       <c r="D548" t="n">
         <v>-0.0636</v>
@@ -50504,7 +50504,7 @@
         <v>0.2004</v>
       </c>
       <c r="F548" t="n">
-        <v>-0.3276</v>
+        <v>-0.3275</v>
       </c>
       <c r="G548" t="n">
         <v>0.606</v>
@@ -50525,7 +50525,7 @@
         <v>-0.5861</v>
       </c>
       <c r="M548" t="n">
-        <v>-0.0593</v>
+        <v>-0.0592</v>
       </c>
     </row>
     <row r="549">
@@ -50538,7 +50538,7 @@
         <v>0.1829</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.3683</v>
+        <v>-0.3682</v>
       </c>
       <c r="D549" t="n">
         <v>-0.0927</v>
@@ -50547,7 +50547,7 @@
         <v>0.1829</v>
       </c>
       <c r="F549" t="n">
-        <v>-0.3683</v>
+        <v>-0.3682</v>
       </c>
       <c r="G549" t="n">
         <v>0.5631</v>
@@ -50568,7 +50568,7 @@
         <v>-0.6701</v>
       </c>
       <c r="M549" t="n">
-        <v>-0.1088</v>
+        <v>-0.1087</v>
       </c>
     </row>
     <row r="550">
@@ -50581,16 +50581,16 @@
         <v>0.2275</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.362</v>
+        <v>-0.3619</v>
       </c>
       <c r="D550" t="n">
-        <v>-0.0673</v>
+        <v>-0.0672</v>
       </c>
       <c r="E550" t="n">
         <v>0.2275</v>
       </c>
       <c r="F550" t="n">
-        <v>-0.362</v>
+        <v>-0.3619</v>
       </c>
       <c r="G550" t="n">
         <v>0.5271</v>
@@ -50611,7 +50611,7 @@
         <v>-0.6618000000000001</v>
       </c>
       <c r="M550" t="n">
-        <v>-0.1468</v>
+        <v>-0.1466</v>
       </c>
     </row>
     <row r="551">
@@ -50654,7 +50654,7 @@
         <v>-0.7244</v>
       </c>
       <c r="M551" t="n">
-        <v>-0.2195</v>
+        <v>-0.2194</v>
       </c>
     </row>
     <row r="552">
@@ -50667,16 +50667,16 @@
         <v>0.3283</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.3968</v>
+        <v>-0.3967</v>
       </c>
       <c r="D552" t="n">
-        <v>-0.0343</v>
+        <v>-0.0342</v>
       </c>
       <c r="E552" t="n">
         <v>0.3283</v>
       </c>
       <c r="F552" t="n">
-        <v>-0.3968</v>
+        <v>-0.3967</v>
       </c>
       <c r="G552" t="n">
         <v>0.5508</v>
@@ -50697,7 +50697,7 @@
         <v>-0.7461</v>
       </c>
       <c r="M552" t="n">
-        <v>-0.2308</v>
+        <v>-0.2306</v>
       </c>
     </row>
     <row r="553">
@@ -50710,16 +50710,16 @@
         <v>0.3303</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.424</v>
+        <v>-0.4239</v>
       </c>
       <c r="D553" t="n">
-        <v>-0.0469</v>
+        <v>-0.0468</v>
       </c>
       <c r="E553" t="n">
         <v>0.3303</v>
       </c>
       <c r="F553" t="n">
-        <v>-0.424</v>
+        <v>-0.4239</v>
       </c>
       <c r="G553" t="n">
         <v>0.4446</v>
@@ -50740,7 +50740,7 @@
         <v>-0.8743</v>
       </c>
       <c r="M553" t="n">
-        <v>-0.2004</v>
+        <v>-0.2002</v>
       </c>
     </row>
     <row r="554">
@@ -50753,7 +50753,7 @@
         <v>0.4282</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.4518</v>
+        <v>-0.4517</v>
       </c>
       <c r="D554" t="n">
         <v>-0.0118</v>
@@ -50762,7 +50762,7 @@
         <v>0.4282</v>
       </c>
       <c r="F554" t="n">
-        <v>-0.4518</v>
+        <v>-0.4517</v>
       </c>
       <c r="G554" t="n">
         <v>0.6754</v>
@@ -50783,7 +50783,7 @@
         <v>-0.9601</v>
       </c>
       <c r="M554" t="n">
-        <v>-0.2282</v>
+        <v>-0.2281</v>
       </c>
     </row>
     <row r="555">
@@ -50826,7 +50826,7 @@
         <v>-1.0419</v>
       </c>
       <c r="M555" t="n">
-        <v>-0.3185</v>
+        <v>-0.3184</v>
       </c>
     </row>
     <row r="556">
@@ -50869,7 +50869,7 @@
         <v>-1.0524</v>
       </c>
       <c r="M556" t="n">
-        <v>-0.287</v>
+        <v>-0.2868</v>
       </c>
     </row>
     <row r="557">
@@ -50912,7 +50912,7 @@
         <v>-0.9431</v>
       </c>
       <c r="M557" t="n">
-        <v>-0.329</v>
+        <v>-0.3288</v>
       </c>
     </row>
     <row r="558">
@@ -50955,7 +50955,7 @@
         <v>-0.8518</v>
       </c>
       <c r="M558" t="n">
-        <v>-0.2736</v>
+        <v>-0.2735</v>
       </c>
     </row>
     <row r="559">
@@ -50998,7 +50998,7 @@
         <v>-0.7127</v>
       </c>
       <c r="M559" t="n">
-        <v>-0.2883</v>
+        <v>-0.2881</v>
       </c>
     </row>
     <row r="560">
@@ -51011,7 +51011,7 @@
         <v>0.8132</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.2225</v>
+        <v>-0.2224</v>
       </c>
       <c r="D560" t="n">
         <v>0.2954</v>
@@ -51020,7 +51020,7 @@
         <v>0.8132</v>
       </c>
       <c r="F560" t="n">
-        <v>-0.2225</v>
+        <v>-0.2224</v>
       </c>
       <c r="G560" t="n">
         <v>0.3102</v>
@@ -51041,7 +51041,7 @@
         <v>-0.4747</v>
       </c>
       <c r="M560" t="n">
-        <v>-0.269</v>
+        <v>-0.2689</v>
       </c>
     </row>
     <row r="561">
@@ -51084,7 +51084,7 @@
         <v>-0.265</v>
       </c>
       <c r="M561" t="n">
-        <v>-0.1859</v>
+        <v>-0.1858</v>
       </c>
     </row>
     <row r="562">
@@ -51097,7 +51097,7 @@
         <v>0.8752</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.0665</v>
+        <v>-0.0664</v>
       </c>
       <c r="D562" t="n">
         <v>0.4044</v>
@@ -51106,7 +51106,7 @@
         <v>0.8752</v>
       </c>
       <c r="F562" t="n">
-        <v>-0.0665</v>
+        <v>-0.0664</v>
       </c>
       <c r="G562" t="n">
         <v>0.1253</v>
@@ -51127,7 +51127,7 @@
         <v>-0.1923</v>
       </c>
       <c r="M562" t="n">
-        <v>-0.2402</v>
+        <v>-0.2401</v>
       </c>
     </row>
     <row r="563">
@@ -51213,7 +51213,7 @@
         <v>0.1579</v>
       </c>
       <c r="M564" t="n">
-        <v>-0.1553</v>
+        <v>-0.1552</v>
       </c>
     </row>
     <row r="565">
@@ -51256,7 +51256,7 @@
         <v>0.3208</v>
       </c>
       <c r="M565" t="n">
-        <v>-0.1445</v>
+        <v>-0.1444</v>
       </c>
     </row>
     <row r="566">
@@ -51315,7 +51315,7 @@
         <v>0.2876</v>
       </c>
       <c r="D567" t="n">
-        <v>0.5602</v>
+        <v>0.5603</v>
       </c>
       <c r="E567" t="n">
         <v>0.8329</v>
@@ -51342,7 +51342,7 @@
         <v>0.381</v>
       </c>
       <c r="M567" t="n">
-        <v>-0.029</v>
+        <v>-0.0289</v>
       </c>
     </row>
     <row r="568">
@@ -51355,7 +51355,7 @@
         <v>0.7518</v>
       </c>
       <c r="C568" t="n">
-        <v>0.2996</v>
+        <v>0.2997</v>
       </c>
       <c r="D568" t="n">
         <v>0.5256999999999999</v>
@@ -51364,7 +51364,7 @@
         <v>0.7518</v>
       </c>
       <c r="F568" t="n">
-        <v>0.2996</v>
+        <v>0.2997</v>
       </c>
       <c r="G568" t="n">
         <v>0.1129</v>
@@ -51385,7 +51385,7 @@
         <v>0.3564</v>
       </c>
       <c r="M568" t="n">
-        <v>0.0408</v>
+        <v>0.0409</v>
       </c>
     </row>
     <row r="569">
@@ -51471,7 +51471,7 @@
         <v>0.4545</v>
       </c>
       <c r="M570" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0808</v>
       </c>
     </row>
     <row r="571">
@@ -51514,7 +51514,7 @@
         <v>0.4716</v>
       </c>
       <c r="M571" t="n">
-        <v>0.1193</v>
+        <v>0.1194</v>
       </c>
     </row>
     <row r="572">
@@ -51600,7 +51600,7 @@
         <v>0.4791</v>
       </c>
       <c r="M573" t="n">
-        <v>0.1124</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="574">
@@ -51613,7 +51613,7 @@
         <v>0.247</v>
       </c>
       <c r="C574" t="n">
-        <v>0.2612</v>
+        <v>0.2613</v>
       </c>
       <c r="D574" t="n">
         <v>0.2541</v>
@@ -51622,7 +51622,7 @@
         <v>0.247</v>
       </c>
       <c r="F574" t="n">
-        <v>0.2612</v>
+        <v>0.2613</v>
       </c>
       <c r="G574" t="n">
         <v>0.3448</v>
@@ -51643,7 +51643,7 @@
         <v>0.4919</v>
       </c>
       <c r="M574" t="n">
-        <v>0.0083</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="575">
@@ -51815,7 +51815,7 @@
         <v>0.5018</v>
       </c>
       <c r="M578" t="n">
-        <v>-0.0209</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="579">
@@ -51871,7 +51871,7 @@
         <v>0.3092</v>
       </c>
       <c r="C580" t="n">
-        <v>0.0767</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="D580" t="n">
         <v>0.193</v>
@@ -51880,7 +51880,7 @@
         <v>0.3092</v>
       </c>
       <c r="F580" t="n">
-        <v>0.0767</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G580" t="n">
         <v>0.6553</v>
@@ -51987,7 +51987,7 @@
         <v>0.665</v>
       </c>
       <c r="M582" t="n">
-        <v>-0.1747</v>
+        <v>-0.1748</v>
       </c>
     </row>
     <row r="583">
@@ -52030,7 +52030,7 @@
         <v>0.6339</v>
       </c>
       <c r="M583" t="n">
-        <v>-0.3324</v>
+        <v>-0.3325</v>
       </c>
     </row>
     <row r="584">
@@ -52043,16 +52043,16 @@
         <v>0.5351</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="D584" t="n">
-        <v>0.2316</v>
+        <v>0.2315</v>
       </c>
       <c r="E584" t="n">
         <v>0.5351</v>
       </c>
       <c r="F584" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G584" t="n">
         <v>1.4156</v>
@@ -52073,7 +52073,7 @@
         <v>0.6975</v>
       </c>
       <c r="M584" t="n">
-        <v>-0.4658</v>
+        <v>-0.466</v>
       </c>
     </row>
     <row r="585">
@@ -52086,16 +52086,16 @@
         <v>0.5171</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.1254</v>
+        <v>-0.1255</v>
       </c>
       <c r="D585" t="n">
-        <v>0.1959</v>
+        <v>0.1958</v>
       </c>
       <c r="E585" t="n">
         <v>0.5171</v>
       </c>
       <c r="F585" t="n">
-        <v>-0.1254</v>
+        <v>-0.1255</v>
       </c>
       <c r="G585" t="n">
         <v>1.5592</v>
@@ -52116,7 +52116,7 @@
         <v>0.5831</v>
       </c>
       <c r="M585" t="n">
-        <v>-0.4854</v>
+        <v>-0.4856</v>
       </c>
     </row>
     <row r="586">
@@ -52129,7 +52129,7 @@
         <v>0.5704</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.1938</v>
+        <v>-0.1939</v>
       </c>
       <c r="D586" t="n">
         <v>0.1883</v>
@@ -52138,7 +52138,7 @@
         <v>0.5704</v>
       </c>
       <c r="F586" t="n">
-        <v>-0.1938</v>
+        <v>-0.1939</v>
       </c>
       <c r="G586" t="n">
         <v>1.7534</v>
@@ -52159,7 +52159,7 @@
         <v>0.6586</v>
       </c>
       <c r="M586" t="n">
-        <v>-0.7399</v>
+        <v>-0.7402</v>
       </c>
     </row>
     <row r="587">
@@ -52172,7 +52172,7 @@
         <v>0.6474</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.2774</v>
+        <v>-0.2775</v>
       </c>
       <c r="D587" t="n">
         <v>0.185</v>
@@ -52181,7 +52181,7 @@
         <v>0.6474</v>
       </c>
       <c r="F587" t="n">
-        <v>-0.2774</v>
+        <v>-0.2775</v>
       </c>
       <c r="G587" t="n">
         <v>1.9343</v>
@@ -52202,7 +52202,7 @@
         <v>0.5306</v>
       </c>
       <c r="M587" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.8597</v>
       </c>
     </row>
     <row r="588">
@@ -52215,16 +52215,16 @@
         <v>0.6444</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.3169</v>
+        <v>-0.317</v>
       </c>
       <c r="D588" t="n">
-        <v>0.1638</v>
+        <v>0.1637</v>
       </c>
       <c r="E588" t="n">
         <v>0.6444</v>
       </c>
       <c r="F588" t="n">
-        <v>-0.3169</v>
+        <v>-0.317</v>
       </c>
       <c r="G588" t="n">
         <v>2.024</v>
@@ -52245,7 +52245,7 @@
         <v>0.5526</v>
       </c>
       <c r="M588" t="n">
-        <v>-0.9601</v>
+        <v>-0.9604</v>
       </c>
     </row>
     <row r="589">
@@ -52258,16 +52258,16 @@
         <v>0.507</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.3643</v>
+        <v>-0.3644</v>
       </c>
       <c r="D589" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="E589" t="n">
         <v>0.507</v>
       </c>
       <c r="F589" t="n">
-        <v>-0.3643</v>
+        <v>-0.3644</v>
       </c>
       <c r="G589" t="n">
         <v>1.6062</v>
@@ -52288,7 +52288,7 @@
         <v>0.5178</v>
       </c>
       <c r="M589" t="n">
-        <v>-1.0446</v>
+        <v>-1.0448</v>
       </c>
     </row>
     <row r="590">
@@ -52301,16 +52301,16 @@
         <v>0.6985</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.422</v>
+        <v>-0.4221</v>
       </c>
       <c r="D590" t="n">
-        <v>0.1383</v>
+        <v>0.1382</v>
       </c>
       <c r="E590" t="n">
         <v>0.6985</v>
       </c>
       <c r="F590" t="n">
-        <v>-0.422</v>
+        <v>-0.4221</v>
       </c>
       <c r="G590" t="n">
         <v>2.2292</v>
@@ -52331,7 +52331,7 @@
         <v>0.4095</v>
       </c>
       <c r="M590" t="n">
-        <v>-1.0745</v>
+        <v>-1.0747</v>
       </c>
     </row>
     <row r="591">
@@ -52344,16 +52344,16 @@
         <v>0.5921999999999999</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.3771</v>
+        <v>-0.3772</v>
       </c>
       <c r="D591" t="n">
-        <v>0.1076</v>
+        <v>0.1075</v>
       </c>
       <c r="E591" t="n">
         <v>0.5921999999999999</v>
       </c>
       <c r="F591" t="n">
-        <v>-0.3771</v>
+        <v>-0.3772</v>
       </c>
       <c r="G591" t="n">
         <v>1.7263</v>
@@ -52374,7 +52374,7 @@
         <v>0.5157</v>
       </c>
       <c r="M591" t="n">
-        <v>-1.0595</v>
+        <v>-1.0597</v>
       </c>
     </row>
     <row r="592">
@@ -52387,7 +52387,7 @@
         <v>0.5724</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.4324</v>
+        <v>-0.4325</v>
       </c>
       <c r="D592" t="n">
         <v>0.07000000000000001</v>
@@ -52396,7 +52396,7 @@
         <v>0.5724</v>
       </c>
       <c r="F592" t="n">
-        <v>-0.4324</v>
+        <v>-0.4325</v>
       </c>
       <c r="G592" t="n">
         <v>1.7692</v>
@@ -52417,7 +52417,7 @@
         <v>0.4589</v>
       </c>
       <c r="M592" t="n">
-        <v>-1.1653</v>
+        <v>-1.1655</v>
       </c>
     </row>
     <row r="593">
@@ -52430,7 +52430,7 @@
         <v>0.608</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.4151</v>
+        <v>-0.4152</v>
       </c>
       <c r="D593" t="n">
         <v>0.0964</v>
@@ -52439,7 +52439,7 @@
         <v>0.608</v>
       </c>
       <c r="F593" t="n">
-        <v>-0.4151</v>
+        <v>-0.4152</v>
       </c>
       <c r="G593" t="n">
         <v>1.8542</v>
@@ -52460,7 +52460,7 @@
         <v>0.525</v>
       </c>
       <c r="M593" t="n">
-        <v>-1.148</v>
+        <v>-1.1482</v>
       </c>
     </row>
     <row r="594">
@@ -52519,7 +52519,7 @@
         <v>-0.3413</v>
       </c>
       <c r="D595" t="n">
-        <v>0.1601</v>
+        <v>0.16</v>
       </c>
       <c r="E595" t="n">
         <v>0.6614</v>
@@ -52546,7 +52546,7 @@
         <v>0.4914</v>
       </c>
       <c r="M595" t="n">
-        <v>-0.8429</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="596">
@@ -52632,7 +52632,7 @@
         <v>0.4469</v>
       </c>
       <c r="M597" t="n">
-        <v>-0.8001</v>
+        <v>-0.8002</v>
       </c>
     </row>
     <row r="598">
@@ -52648,7 +52648,7 @@
         <v>-0.2536</v>
       </c>
       <c r="D598" t="n">
-        <v>0.2469</v>
+        <v>0.2468</v>
       </c>
       <c r="E598" t="n">
         <v>0.7473</v>
@@ -52675,7 +52675,7 @@
         <v>0.4833</v>
       </c>
       <c r="M598" t="n">
-        <v>-0.5686</v>
+        <v>-0.5687</v>
       </c>
     </row>
     <row r="599">
@@ -52688,7 +52688,7 @@
         <v>0.7677</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.2288</v>
+        <v>-0.2289</v>
       </c>
       <c r="D599" t="n">
         <v>0.2694</v>
@@ -52697,7 +52697,7 @@
         <v>0.7677</v>
       </c>
       <c r="F599" t="n">
-        <v>-0.2288</v>
+        <v>-0.2289</v>
       </c>
       <c r="G599" t="n">
         <v>1.6339</v>
@@ -52718,7 +52718,7 @@
         <v>0.5221</v>
       </c>
       <c r="M599" t="n">
-        <v>-0.5626</v>
+        <v>-0.5627</v>
       </c>
     </row>
     <row r="600">
@@ -52731,7 +52731,7 @@
         <v>0.7216</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.2815</v>
+        <v>-0.2816</v>
       </c>
       <c r="D600" t="n">
         <v>0.22</v>
@@ -52740,7 +52740,7 @@
         <v>0.7216</v>
       </c>
       <c r="F600" t="n">
-        <v>-0.2815</v>
+        <v>-0.2816</v>
       </c>
       <c r="G600" t="n">
         <v>1.4473</v>
@@ -52761,7 +52761,7 @@
         <v>0.5309</v>
       </c>
       <c r="M600" t="n">
-        <v>-0.7221</v>
+        <v>-0.7223000000000001</v>
       </c>
     </row>
     <row r="601">
@@ -52774,7 +52774,7 @@
         <v>0.6691</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.2484</v>
+        <v>-0.2485</v>
       </c>
       <c r="D601" t="n">
         <v>0.2103</v>
@@ -52783,7 +52783,7 @@
         <v>0.6691</v>
       </c>
       <c r="F601" t="n">
-        <v>-0.2484</v>
+        <v>-0.2485</v>
       </c>
       <c r="G601" t="n">
         <v>1.5078</v>
@@ -52804,7 +52804,7 @@
         <v>0.4849</v>
       </c>
       <c r="M601" t="n">
-        <v>-0.5676</v>
+        <v>-0.5678</v>
       </c>
     </row>
     <row r="602">
@@ -52820,7 +52820,7 @@
         <v>-0.2249</v>
       </c>
       <c r="D602" t="n">
-        <v>0.164</v>
+        <v>0.1639</v>
       </c>
       <c r="E602" t="n">
         <v>0.5528</v>
@@ -52847,7 +52847,7 @@
         <v>0.4865</v>
       </c>
       <c r="M602" t="n">
-        <v>-0.5079</v>
+        <v>-0.5081</v>
       </c>
     </row>
     <row r="603">
@@ -52863,7 +52863,7 @@
         <v>-0.2149</v>
       </c>
       <c r="D603" t="n">
-        <v>0.2215</v>
+        <v>0.2214</v>
       </c>
       <c r="E603" t="n">
         <v>0.6578000000000001</v>
@@ -52890,7 +52890,7 @@
         <v>0.478</v>
       </c>
       <c r="M603" t="n">
-        <v>-0.494</v>
+        <v>-0.4942</v>
       </c>
     </row>
     <row r="604">
@@ -52933,7 +52933,7 @@
         <v>0.4493</v>
       </c>
       <c r="M604" t="n">
-        <v>-0.3359</v>
+        <v>-0.3361</v>
       </c>
     </row>
     <row r="605">
@@ -52946,7 +52946,7 @@
         <v>0.5806</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.1475</v>
+        <v>-0.1476</v>
       </c>
       <c r="D605" t="n">
         <v>0.2165</v>
@@ -52955,7 +52955,7 @@
         <v>0.5806</v>
       </c>
       <c r="F605" t="n">
-        <v>-0.1475</v>
+        <v>-0.1476</v>
       </c>
       <c r="G605" t="n">
         <v>1.2534</v>
@@ -52976,7 +52976,7 @@
         <v>0.4828</v>
       </c>
       <c r="M605" t="n">
-        <v>-0.306</v>
+        <v>-0.3062</v>
       </c>
     </row>
     <row r="606">
@@ -53019,7 +53019,7 @@
         <v>0.4807</v>
       </c>
       <c r="M606" t="n">
-        <v>-0.2783</v>
+        <v>-0.2785</v>
       </c>
     </row>
     <row r="607">
@@ -53032,16 +53032,16 @@
         <v>0.6535</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.1264</v>
+        <v>-0.1265</v>
       </c>
       <c r="D607" t="n">
-        <v>0.2636</v>
+        <v>0.2635</v>
       </c>
       <c r="E607" t="n">
         <v>0.6535</v>
       </c>
       <c r="F607" t="n">
-        <v>-0.1264</v>
+        <v>-0.1265</v>
       </c>
       <c r="G607" t="n">
         <v>1.4515</v>
@@ -53062,7 +53062,7 @@
         <v>0.4844</v>
       </c>
       <c r="M607" t="n">
-        <v>-0.2548</v>
+        <v>-0.2551</v>
       </c>
     </row>
     <row r="608">
@@ -53075,16 +53075,16 @@
         <v>0.6832</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.1577</v>
+        <v>-0.1578</v>
       </c>
       <c r="D608" t="n">
-        <v>0.2628</v>
+        <v>0.2627</v>
       </c>
       <c r="E608" t="n">
         <v>0.6832</v>
       </c>
       <c r="F608" t="n">
-        <v>-0.1577</v>
+        <v>-0.1578</v>
       </c>
       <c r="G608" t="n">
         <v>1.4938</v>
@@ -53105,7 +53105,7 @@
         <v>0.4705</v>
       </c>
       <c r="M608" t="n">
-        <v>-0.2893</v>
+        <v>-0.2896</v>
       </c>
     </row>
     <row r="609">
@@ -53118,7 +53118,7 @@
         <v>0.5908</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.1835</v>
+        <v>-0.1836</v>
       </c>
       <c r="D609" t="n">
         <v>0.2036</v>
@@ -53127,7 +53127,7 @@
         <v>0.5908</v>
       </c>
       <c r="F609" t="n">
-        <v>-0.1835</v>
+        <v>-0.1836</v>
       </c>
       <c r="G609" t="n">
         <v>1.4808</v>
@@ -53148,7 +53148,7 @@
         <v>0.4739</v>
       </c>
       <c r="M609" t="n">
-        <v>-0.3642</v>
+        <v>-0.3645</v>
       </c>
     </row>
     <row r="610">
@@ -53161,7 +53161,7 @@
         <v>0.5163</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.1642</v>
+        <v>-0.1643</v>
       </c>
       <c r="D610" t="n">
         <v>0.176</v>
@@ -53170,7 +53170,7 @@
         <v>0.5163</v>
       </c>
       <c r="F610" t="n">
-        <v>-0.1642</v>
+        <v>-0.1643</v>
       </c>
       <c r="G610" t="n">
         <v>1.2597</v>
@@ -53191,7 +53191,7 @@
         <v>0.4776</v>
       </c>
       <c r="M610" t="n">
-        <v>-0.2754</v>
+        <v>-0.2758</v>
       </c>
     </row>
     <row r="611">
@@ -53204,7 +53204,7 @@
         <v>0.5303</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.1753</v>
+        <v>-0.1754</v>
       </c>
       <c r="D611" t="n">
         <v>0.1775</v>
@@ -53213,7 +53213,7 @@
         <v>0.5303</v>
       </c>
       <c r="F611" t="n">
-        <v>-0.1753</v>
+        <v>-0.1754</v>
       </c>
       <c r="G611" t="n">
         <v>1.2024</v>
@@ -53234,7 +53234,7 @@
         <v>0.4612</v>
       </c>
       <c r="M611" t="n">
-        <v>-0.2412</v>
+        <v>-0.2416</v>
       </c>
     </row>
     <row r="612">
@@ -53247,7 +53247,7 @@
         <v>0.5806</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.1597</v>
+        <v>-0.1598</v>
       </c>
       <c r="D612" t="n">
         <v>0.2104</v>
@@ -53256,7 +53256,7 @@
         <v>0.5806</v>
       </c>
       <c r="F612" t="n">
-        <v>-0.1597</v>
+        <v>-0.1598</v>
       </c>
       <c r="G612" t="n">
         <v>1.3456</v>
@@ -53277,7 +53277,7 @@
         <v>0.4633</v>
       </c>
       <c r="M612" t="n">
-        <v>-0.1961</v>
+        <v>-0.1965</v>
       </c>
     </row>
     <row r="613">
@@ -53290,7 +53290,7 @@
         <v>0.5888</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.1646</v>
+        <v>-0.1647</v>
       </c>
       <c r="D613" t="n">
         <v>0.2121</v>
@@ -53299,7 +53299,7 @@
         <v>0.5888</v>
       </c>
       <c r="F613" t="n">
-        <v>-0.1646</v>
+        <v>-0.1647</v>
       </c>
       <c r="G613" t="n">
         <v>1.4018</v>
@@ -53320,7 +53320,7 @@
         <v>0.3826</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1028</v>
+        <v>-0.1031</v>
       </c>
     </row>
     <row r="614">
@@ -53363,7 +53363,7 @@
         <v>0.39</v>
       </c>
       <c r="M614" t="n">
-        <v>-0.0379</v>
+        <v>-0.0381</v>
       </c>
     </row>
     <row r="615">
@@ -53406,7 +53406,7 @@
         <v>0.3968</v>
       </c>
       <c r="M615" t="n">
-        <v>0.016</v>
+        <v>0.0158</v>
       </c>
     </row>
     <row r="616">
@@ -53449,7 +53449,7 @@
         <v>0.3761</v>
       </c>
       <c r="M616" t="n">
-        <v>0.0623</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="617">
@@ -53462,16 +53462,16 @@
         <v>0.5463</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.1873</v>
+        <v>-0.1875</v>
       </c>
       <c r="D617" t="n">
-        <v>0.1795</v>
+        <v>0.1794</v>
       </c>
       <c r="E617" t="n">
         <v>0.5463</v>
       </c>
       <c r="F617" t="n">
-        <v>-0.1873</v>
+        <v>-0.1875</v>
       </c>
       <c r="G617" t="n">
         <v>1.6836</v>
@@ -53492,7 +53492,7 @@
         <v>0.425</v>
       </c>
       <c r="M617" t="n">
-        <v>-0.1075</v>
+        <v>-0.1078</v>
       </c>
     </row>
     <row r="618">
@@ -53505,16 +53505,16 @@
         <v>0.5769</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.198</v>
+        <v>-0.1982</v>
       </c>
       <c r="D618" t="n">
-        <v>0.1895</v>
+        <v>0.1894</v>
       </c>
       <c r="E618" t="n">
         <v>0.5769</v>
       </c>
       <c r="F618" t="n">
-        <v>-0.198</v>
+        <v>-0.1982</v>
       </c>
       <c r="G618" t="n">
         <v>1.7157</v>
@@ -53535,7 +53535,7 @@
         <v>0.4181</v>
       </c>
       <c r="M618" t="n">
-        <v>-0.1047</v>
+        <v>-0.1051</v>
       </c>
     </row>
     <row r="619">
@@ -53548,16 +53548,16 @@
         <v>0.5334</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.2205</v>
+        <v>-0.2206</v>
       </c>
       <c r="D619" t="n">
-        <v>0.1565</v>
+        <v>0.1564</v>
       </c>
       <c r="E619" t="n">
         <v>0.5334</v>
       </c>
       <c r="F619" t="n">
-        <v>-0.2205</v>
+        <v>-0.2206</v>
       </c>
       <c r="G619" t="n">
         <v>1.5795</v>
@@ -53578,7 +53578,7 @@
         <v>0.3694</v>
       </c>
       <c r="M619" t="n">
-        <v>-0.1011</v>
+        <v>-0.1016</v>
       </c>
     </row>
     <row r="620">
@@ -53591,16 +53591,16 @@
         <v>0.5105</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.2293</v>
+        <v>-0.2295</v>
       </c>
       <c r="D620" t="n">
-        <v>0.1406</v>
+        <v>0.1405</v>
       </c>
       <c r="E620" t="n">
         <v>0.5105</v>
       </c>
       <c r="F620" t="n">
-        <v>-0.2293</v>
+        <v>-0.2295</v>
       </c>
       <c r="G620" t="n">
         <v>1.4321</v>
@@ -53621,7 +53621,7 @@
         <v>0.3891</v>
       </c>
       <c r="M620" t="n">
-        <v>-0.1263</v>
+        <v>-0.1268</v>
       </c>
     </row>
     <row r="621">
@@ -53634,7 +53634,7 @@
         <v>0.484</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.2419</v>
+        <v>-0.242</v>
       </c>
       <c r="D621" t="n">
         <v>0.121</v>
@@ -53643,7 +53643,7 @@
         <v>0.484</v>
       </c>
       <c r="F621" t="n">
-        <v>-0.2419</v>
+        <v>-0.242</v>
       </c>
       <c r="G621" t="n">
         <v>1.2465</v>
@@ -53664,7 +53664,7 @@
         <v>0.4098</v>
       </c>
       <c r="M621" t="n">
-        <v>-0.1045</v>
+        <v>-0.105</v>
       </c>
     </row>
     <row r="622">
@@ -53677,7 +53677,7 @@
         <v>0.4746</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.2339</v>
+        <v>-0.234</v>
       </c>
       <c r="D622" t="n">
         <v>0.1203</v>
@@ -53686,7 +53686,7 @@
         <v>0.4746</v>
       </c>
       <c r="F622" t="n">
-        <v>-0.2339</v>
+        <v>-0.234</v>
       </c>
       <c r="G622" t="n">
         <v>1.3678</v>
@@ -53707,7 +53707,7 @@
         <v>0.4629</v>
       </c>
       <c r="M622" t="n">
-        <v>-0.1104</v>
+        <v>-0.1109</v>
       </c>
     </row>
     <row r="623">
@@ -53720,16 +53720,16 @@
         <v>0.5211</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.2687</v>
+        <v>-0.2688</v>
       </c>
       <c r="D623" t="n">
-        <v>0.1262</v>
+        <v>0.1261</v>
       </c>
       <c r="E623" t="n">
         <v>0.5211</v>
       </c>
       <c r="F623" t="n">
-        <v>-0.2687</v>
+        <v>-0.2688</v>
       </c>
       <c r="G623" t="n">
         <v>1.3974</v>
@@ -53750,7 +53750,7 @@
         <v>0.3654</v>
       </c>
       <c r="M623" t="n">
-        <v>-0.0871</v>
+        <v>-0.0876</v>
       </c>
     </row>
     <row r="624">
@@ -53763,16 +53763,16 @@
         <v>0.5455</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.2481</v>
+        <v>-0.2482</v>
       </c>
       <c r="D624" t="n">
-        <v>0.1487</v>
+        <v>0.1486</v>
       </c>
       <c r="E624" t="n">
         <v>0.5455</v>
       </c>
       <c r="F624" t="n">
-        <v>-0.2481</v>
+        <v>-0.2482</v>
       </c>
       <c r="G624" t="n">
         <v>1.3915</v>
@@ -53793,7 +53793,7 @@
         <v>0.4504</v>
       </c>
       <c r="M624" t="n">
-        <v>-0.0596</v>
+        <v>-0.0601</v>
       </c>
     </row>
     <row r="625">
@@ -53806,7 +53806,7 @@
         <v>0.2323</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.2776</v>
+        <v>-0.2777</v>
       </c>
       <c r="D625" t="n">
         <v>-0.0227</v>
@@ -53815,7 +53815,7 @@
         <v>0.2323</v>
       </c>
       <c r="F625" t="n">
-        <v>-0.2776</v>
+        <v>-0.2777</v>
       </c>
       <c r="G625" t="n">
         <v>0.1559</v>
@@ -53836,7 +53836,7 @@
         <v>0.3825</v>
       </c>
       <c r="M625" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0709</v>
       </c>
     </row>
     <row r="626">
@@ -53849,7 +53849,7 @@
         <v>0.4317</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.2654</v>
+        <v>-0.2655</v>
       </c>
       <c r="D626" t="n">
         <v>0.08309999999999999</v>
@@ -53858,7 +53858,7 @@
         <v>0.4317</v>
       </c>
       <c r="F626" t="n">
-        <v>-0.2654</v>
+        <v>-0.2655</v>
       </c>
       <c r="G626" t="n">
         <v>0.8129</v>
@@ -53879,7 +53879,7 @@
         <v>0.4379</v>
       </c>
       <c r="M626" t="n">
-        <v>-0.0409</v>
+        <v>-0.0413</v>
       </c>
     </row>
     <row r="627">
@@ -53892,16 +53892,16 @@
         <v>0.3858</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.3075</v>
+        <v>-0.3076</v>
       </c>
       <c r="D627" t="n">
-        <v>0.0392</v>
+        <v>0.0391</v>
       </c>
       <c r="E627" t="n">
         <v>0.3858</v>
       </c>
       <c r="F627" t="n">
-        <v>-0.3075</v>
+        <v>-0.3076</v>
       </c>
       <c r="G627" t="n">
         <v>0.5855</v>
@@ -53922,7 +53922,7 @@
         <v>0.3662</v>
       </c>
       <c r="M627" t="n">
-        <v>-0.0613</v>
+        <v>-0.0618</v>
       </c>
     </row>
     <row r="628">
@@ -53935,16 +53935,16 @@
         <v>0.4287</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.2774</v>
+        <v>-0.2775</v>
       </c>
       <c r="D628" t="n">
-        <v>0.0757</v>
+        <v>0.0756</v>
       </c>
       <c r="E628" t="n">
         <v>0.4287</v>
       </c>
       <c r="F628" t="n">
-        <v>-0.2774</v>
+        <v>-0.2775</v>
       </c>
       <c r="G628" t="n">
         <v>0.6657999999999999</v>
@@ -53965,7 +53965,7 @@
         <v>0.4414</v>
       </c>
       <c r="M628" t="n">
-        <v>-0.002</v>
+        <v>-0.0023</v>
       </c>
     </row>
     <row r="629">
@@ -53978,16 +53978,16 @@
         <v>0.3905</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.29</v>
+        <v>-0.2901</v>
       </c>
       <c r="D629" t="n">
-        <v>0.0503</v>
+        <v>0.0502</v>
       </c>
       <c r="E629" t="n">
         <v>0.3905</v>
       </c>
       <c r="F629" t="n">
-        <v>-0.29</v>
+        <v>-0.2901</v>
       </c>
       <c r="G629" t="n">
         <v>0.5208</v>
@@ -54008,7 +54008,7 @@
         <v>0.3526</v>
       </c>
       <c r="M629" t="n">
-        <v>0.0688</v>
+        <v>0.06859999999999999</v>
       </c>
     </row>
     <row r="630">
@@ -54021,7 +54021,7 @@
         <v>0.3871</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.2899</v>
+        <v>-0.29</v>
       </c>
       <c r="D630" t="n">
         <v>0.0486</v>
@@ -54030,7 +54030,7 @@
         <v>0.3871</v>
       </c>
       <c r="F630" t="n">
-        <v>-0.2899</v>
+        <v>-0.29</v>
       </c>
       <c r="G630" t="n">
         <v>0.5153</v>
@@ -54051,7 +54051,7 @@
         <v>0.4614</v>
       </c>
       <c r="M630" t="n">
-        <v>-0.0031</v>
+        <v>-0.0034</v>
       </c>
     </row>
     <row r="631">
@@ -54064,16 +54064,16 @@
         <v>0.3914</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.2038</v>
+        <v>-0.2039</v>
       </c>
       <c r="D631" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="E631" t="n">
         <v>0.3914</v>
       </c>
       <c r="F631" t="n">
-        <v>-0.2038</v>
+        <v>-0.2039</v>
       </c>
       <c r="G631" t="n">
         <v>0.5193</v>
@@ -54094,7 +54094,7 @@
         <v>0.4852</v>
       </c>
       <c r="M631" t="n">
-        <v>0.2712</v>
+        <v>0.2709</v>
       </c>
     </row>
     <row r="632">
@@ -54107,16 +54107,16 @@
         <v>0.4253</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.2115</v>
+        <v>-0.2088</v>
       </c>
       <c r="D632" t="n">
-        <v>0.1069</v>
+        <v>0.1083</v>
       </c>
       <c r="E632" t="n">
         <v>0.4253</v>
       </c>
       <c r="F632" t="n">
-        <v>-0.2115</v>
+        <v>-0.2088</v>
       </c>
       <c r="G632" t="n">
         <v>0.5974</v>
@@ -54137,7 +54137,7 @@
         <v>0.4486</v>
       </c>
       <c r="M632" t="n">
-        <v>0.2768</v>
+        <v>0.2849</v>
       </c>
     </row>
     <row r="633">
@@ -54150,16 +54150,16 @@
         <v>0.4192</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.1916</v>
+        <v>-0.1801</v>
       </c>
       <c r="D633" t="n">
-        <v>0.1138</v>
+        <v>0.1195</v>
       </c>
       <c r="E633" t="n">
         <v>0.4192</v>
       </c>
       <c r="F633" t="n">
-        <v>-0.1916</v>
+        <v>-0.1801</v>
       </c>
       <c r="G633" t="n">
         <v>0.5974</v>
@@ -54180,7 +54180,7 @@
         <v>0.4342</v>
       </c>
       <c r="M633" t="n">
-        <v>0.3401</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="634">
@@ -54193,16 +54193,16 @@
         <v>0.4602</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.169</v>
+        <v>-0.1712</v>
       </c>
       <c r="D634" t="n">
-        <v>0.1456</v>
+        <v>0.1445</v>
       </c>
       <c r="E634" t="n">
         <v>0.4602</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.169</v>
+        <v>-0.1712</v>
       </c>
       <c r="G634" t="n">
         <v>0.5974</v>
@@ -54223,7 +54223,7 @@
         <v>0.4206</v>
       </c>
       <c r="M634" t="n">
-        <v>0.4014</v>
+        <v>0.3948</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -4651,7 +4651,7 @@
         <v>-0.215</v>
       </c>
       <c r="K322" t="n">
-        <v>-0.138</v>
+        <v>-0.139</v>
       </c>
     </row>
     <row r="323">
@@ -5171,7 +5171,7 @@
         <v>-0.405</v>
       </c>
       <c r="K362" t="n">
-        <v>-0.374</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="363">
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.509</v>
+        <v>10.5</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.075</v>
+        <v>1.074</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -34435,10 +34435,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.0752</v>
+        <v>1.0744</v>
       </c>
       <c r="H634" t="n">
-        <v>10.5092</v>
+        <v>10.4998</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -38948,7 +38948,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.2717</v>
+        <v>-0.2718</v>
       </c>
       <c r="E230" t="n">
         <v>-0.6153999999999999</v>
@@ -39813,7 +39813,7 @@
         <v>-0.21</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.8439</v>
+        <v>-0.844</v>
       </c>
       <c r="D261" t="n">
         <v>-0.527</v>
@@ -39822,13 +39822,13 @@
         <v>-0.21</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.8439</v>
+        <v>-0.844</v>
       </c>
       <c r="G261" t="n">
         <v>-0.21</v>
       </c>
       <c r="M261" t="n">
-        <v>-0.8439</v>
+        <v>-0.844</v>
       </c>
     </row>
     <row r="262">
@@ -41717,7 +41717,7 @@
         <v>-0.1291</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0292</v>
+        <v>0.0291</v>
       </c>
       <c r="D329" t="n">
         <v>-0.05</v>
@@ -41726,13 +41726,13 @@
         <v>-0.1291</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0292</v>
+        <v>0.0291</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1291</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0292</v>
+        <v>0.0291</v>
       </c>
     </row>
     <row r="330">
@@ -41972,7 +41972,7 @@
         <v>-0.2473</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.1853</v>
+        <v>-0.1854</v>
       </c>
       <c r="E338" t="n">
         <v>-0.1234</v>
@@ -42830,7 +42830,7 @@
         <v>-0.1077</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.2918</v>
+        <v>-0.2919</v>
       </c>
       <c r="E368" t="n">
         <v>-0.476</v>
@@ -42982,7 +42982,7 @@
         <v>-0.5373</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2951</v>
+        <v>-0.2952</v>
       </c>
       <c r="D373" t="n">
         <v>-0.4162</v>
@@ -42991,7 +42991,7 @@
         <v>-0.5373</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2951</v>
+        <v>-0.2952</v>
       </c>
       <c r="G373" t="n">
         <v>0.1684</v>
@@ -43000,7 +43000,7 @@
         <v>-1.2431</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2951</v>
+        <v>-0.2952</v>
       </c>
     </row>
     <row r="374">
@@ -43013,7 +43013,7 @@
         <v>-0.5414</v>
       </c>
       <c r="C374" t="n">
-        <v>0.4905</v>
+        <v>0.4904</v>
       </c>
       <c r="D374" t="n">
         <v>-0.0255</v>
@@ -43022,7 +43022,7 @@
         <v>-0.5414</v>
       </c>
       <c r="F374" t="n">
-        <v>0.4905</v>
+        <v>0.4904</v>
       </c>
       <c r="G374" t="n">
         <v>0.3134</v>
@@ -43403,7 +43403,7 @@
         <v>-0.08</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.252</v>
+        <v>-0.2521</v>
       </c>
       <c r="E383" t="n">
         <v>-0.4241</v>
@@ -52245,7 +52245,7 @@
         <v>0.5526</v>
       </c>
       <c r="M588" t="n">
-        <v>-0.9604</v>
+        <v>-0.9605</v>
       </c>
     </row>
     <row r="589">
@@ -52890,7 +52890,7 @@
         <v>0.478</v>
       </c>
       <c r="M603" t="n">
-        <v>-0.4942</v>
+        <v>-0.4943</v>
       </c>
     </row>
     <row r="604">
@@ -53766,7 +53766,7 @@
         <v>-0.2482</v>
       </c>
       <c r="D624" t="n">
-        <v>0.1487</v>
+        <v>0.1486</v>
       </c>
       <c r="E624" t="n">
         <v>0.5455</v>
@@ -54193,16 +54193,16 @@
         <v>0.4495</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1703</v>
+        <v>-0.1701</v>
       </c>
       <c r="D634" t="n">
-        <v>0.1396</v>
+        <v>0.1397</v>
       </c>
       <c r="E634" t="n">
         <v>0.4495</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1703</v>
+        <v>-0.1701</v>
       </c>
       <c r="G634" t="n">
         <v>0.5548999999999999</v>
@@ -54223,7 +54223,7 @@
         <v>0.4206</v>
       </c>
       <c r="M634" t="n">
-        <v>0.3975</v>
+        <v>0.3981</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -2701,7 +2701,7 @@
         <v>-1.295</v>
       </c>
       <c r="K172" t="n">
-        <v>-1.931</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="173">
@@ -3728,7 +3728,7 @@
         <v>-0.386</v>
       </c>
       <c r="K251" t="n">
-        <v>-1.095</v>
+        <v>-1.096</v>
       </c>
     </row>
     <row r="252">
@@ -3962,7 +3962,7 @@
         <v>1.043</v>
       </c>
       <c r="K269" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="270">
@@ -4196,7 +4196,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="K287" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="288">
@@ -4313,7 +4313,7 @@
         <v>0.164</v>
       </c>
       <c r="K296" t="n">
-        <v>-1.576</v>
+        <v>-1.577</v>
       </c>
     </row>
     <row r="297">
@@ -4521,7 +4521,7 @@
         <v>0.099</v>
       </c>
       <c r="K312" t="n">
-        <v>0.804</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="313">
@@ -8603,7 +8603,7 @@
         <v>0.45</v>
       </c>
       <c r="K626" t="n">
-        <v>-0.17</v>
+        <v>-0.169</v>
       </c>
     </row>
   </sheetData>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.5</v>
+        <v>10.451</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="13">
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.074</v>
+        <v>1.072</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="14">
@@ -34435,10 +34435,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.0744</v>
+        <v>1.0722</v>
       </c>
       <c r="H634" t="n">
-        <v>10.4998</v>
+        <v>10.4513</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -37520,7 +37520,7 @@
         <v>-2.7855</v>
       </c>
       <c r="D179" t="n">
-        <v>-2.1128</v>
+        <v>-2.1129</v>
       </c>
       <c r="E179" t="n">
         <v>-1.4402</v>
@@ -37797,7 +37797,7 @@
         <v>-0.8015</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.4728</v>
+        <v>-0.4729</v>
       </c>
       <c r="D189" t="n">
         <v>-0.6372</v>
@@ -37806,13 +37806,13 @@
         <v>-0.8015</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.4728</v>
+        <v>-0.4729</v>
       </c>
       <c r="G189" t="n">
         <v>-0.8015</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.4728</v>
+        <v>-0.4729</v>
       </c>
     </row>
     <row r="190">
@@ -37965,7 +37965,7 @@
         <v>-1.3702</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7198</v>
+        <v>-0.7199</v>
       </c>
       <c r="D195" t="n">
         <v>-1.045</v>
@@ -37974,13 +37974,13 @@
         <v>-1.3702</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7198</v>
+        <v>-0.7199</v>
       </c>
       <c r="G195" t="n">
         <v>-1.3702</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7198</v>
+        <v>-0.7199</v>
       </c>
     </row>
     <row r="196">
@@ -37993,7 +37993,7 @@
         <v>-1.4857</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.8717</v>
+        <v>-0.8718</v>
       </c>
       <c r="D196" t="n">
         <v>-1.1787</v>
@@ -38002,13 +38002,13 @@
         <v>-1.4857</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.8717</v>
+        <v>-0.8718</v>
       </c>
       <c r="G196" t="n">
         <v>-1.4857</v>
       </c>
       <c r="M196" t="n">
-        <v>-0.8717</v>
+        <v>-0.8718</v>
       </c>
     </row>
     <row r="197">
@@ -38161,7 +38161,7 @@
         <v>-2.3232</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.442</v>
+        <v>-1.4421</v>
       </c>
       <c r="D202" t="n">
         <v>-1.8826</v>
@@ -38170,13 +38170,13 @@
         <v>-2.3232</v>
       </c>
       <c r="F202" t="n">
-        <v>-1.442</v>
+        <v>-1.4421</v>
       </c>
       <c r="G202" t="n">
         <v>-2.3232</v>
       </c>
       <c r="M202" t="n">
-        <v>-1.442</v>
+        <v>-1.4421</v>
       </c>
     </row>
     <row r="203">
@@ -38189,7 +38189,7 @@
         <v>-2.0213</v>
       </c>
       <c r="C203" t="n">
-        <v>-1.8399</v>
+        <v>-1.84</v>
       </c>
       <c r="D203" t="n">
         <v>-1.9306</v>
@@ -38198,13 +38198,13 @@
         <v>-2.0213</v>
       </c>
       <c r="F203" t="n">
-        <v>-1.8399</v>
+        <v>-1.84</v>
       </c>
       <c r="G203" t="n">
         <v>-2.0213</v>
       </c>
       <c r="M203" t="n">
-        <v>-1.8399</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="204">
@@ -38220,7 +38220,7 @@
         <v>-2.2709</v>
       </c>
       <c r="D204" t="n">
-        <v>-2.0975</v>
+        <v>-2.0976</v>
       </c>
       <c r="E204" t="n">
         <v>-1.9242</v>
@@ -38836,7 +38836,7 @@
         <v>-0.0032</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.2514</v>
+        <v>-0.2515</v>
       </c>
       <c r="E226" t="n">
         <v>-0.4997</v>
@@ -38973,7 +38973,7 @@
         <v>-0.4067</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="D231" t="n">
         <v>-0.2035</v>
@@ -38982,13 +38982,13 @@
         <v>-0.4067</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="G231" t="n">
         <v>-0.4067</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
     </row>
     <row r="232">
@@ -39060,7 +39060,7 @@
         <v>-0.3813</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.4964</v>
+        <v>-0.4965</v>
       </c>
       <c r="E234" t="n">
         <v>-0.6116</v>
@@ -39421,7 +39421,7 @@
         <v>-0.3548</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.2634</v>
+        <v>-1.2635</v>
       </c>
       <c r="D247" t="n">
         <v>-0.8091</v>
@@ -39430,13 +39430,13 @@
         <v>-0.3548</v>
       </c>
       <c r="F247" t="n">
-        <v>-1.2634</v>
+        <v>-1.2635</v>
       </c>
       <c r="G247" t="n">
         <v>-0.3548</v>
       </c>
       <c r="M247" t="n">
-        <v>-1.2634</v>
+        <v>-1.2635</v>
       </c>
     </row>
     <row r="248">
@@ -39564,7 +39564,7 @@
         <v>-1.0832</v>
       </c>
       <c r="D252" t="n">
-        <v>-0.8766</v>
+        <v>-0.8767</v>
       </c>
       <c r="E252" t="n">
         <v>-0.6701</v>
@@ -39785,7 +39785,7 @@
         <v>-0.2115</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.9983</v>
+        <v>-0.9984</v>
       </c>
       <c r="D260" t="n">
         <v>-0.6049</v>
@@ -39794,13 +39794,13 @@
         <v>-0.2115</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.9983</v>
+        <v>-0.9984</v>
       </c>
       <c r="G260" t="n">
         <v>-0.2115</v>
       </c>
       <c r="M260" t="n">
-        <v>-0.9983</v>
+        <v>-0.9984</v>
       </c>
     </row>
     <row r="261">
@@ -39897,7 +39897,7 @@
         <v>0.1101</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.8345</v>
+        <v>-0.8346</v>
       </c>
       <c r="D264" t="n">
         <v>-0.3622</v>
@@ -39906,13 +39906,13 @@
         <v>0.1101</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.8345</v>
+        <v>-0.8346</v>
       </c>
       <c r="G264" t="n">
         <v>0.1101</v>
       </c>
       <c r="M264" t="n">
-        <v>-0.8345</v>
+        <v>-0.8346</v>
       </c>
     </row>
     <row r="265">
@@ -40149,7 +40149,7 @@
         <v>0.1283</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1325</v>
+        <v>0.1324</v>
       </c>
       <c r="D273" t="n">
         <v>0.1304</v>
@@ -40158,13 +40158,13 @@
         <v>0.1283</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1325</v>
+        <v>0.1324</v>
       </c>
       <c r="G273" t="n">
         <v>0.1283</v>
       </c>
       <c r="M273" t="n">
-        <v>0.1325</v>
+        <v>0.1324</v>
       </c>
     </row>
     <row r="274">
@@ -40709,7 +40709,7 @@
         <v>0.1415</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.1256</v>
+        <v>-0.1257</v>
       </c>
       <c r="D293" t="n">
         <v>0.007900000000000001</v>
@@ -40718,13 +40718,13 @@
         <v>0.1415</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.1256</v>
+        <v>-0.1257</v>
       </c>
       <c r="G293" t="n">
         <v>0.1415</v>
       </c>
       <c r="M293" t="n">
-        <v>-0.1256</v>
+        <v>-0.1257</v>
       </c>
     </row>
     <row r="294">
@@ -40905,7 +40905,7 @@
         <v>0.0384</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.1947</v>
+        <v>-0.1948</v>
       </c>
       <c r="D300" t="n">
         <v>-0.07820000000000001</v>
@@ -40914,13 +40914,13 @@
         <v>0.0384</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.1947</v>
+        <v>-0.1948</v>
       </c>
       <c r="G300" t="n">
         <v>0.0384</v>
       </c>
       <c r="M300" t="n">
-        <v>-0.1947</v>
+        <v>-0.1948</v>
       </c>
     </row>
     <row r="301">
@@ -41157,7 +41157,7 @@
         <v>0.2206</v>
       </c>
       <c r="C309" t="n">
-        <v>-1.7387</v>
+        <v>-1.7388</v>
       </c>
       <c r="D309" t="n">
         <v>-0.7591</v>
@@ -41166,13 +41166,13 @@
         <v>0.2206</v>
       </c>
       <c r="F309" t="n">
-        <v>-1.7387</v>
+        <v>-1.7388</v>
       </c>
       <c r="G309" t="n">
         <v>0.2206</v>
       </c>
       <c r="M309" t="n">
-        <v>-1.7387</v>
+        <v>-1.7388</v>
       </c>
     </row>
     <row r="310">
@@ -41216,7 +41216,7 @@
         <v>-1.0248</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.4183</v>
+        <v>-0.4184</v>
       </c>
       <c r="E311" t="n">
         <v>0.1881</v>
@@ -41577,7 +41577,7 @@
         <v>-0.1751</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2105</v>
+        <v>0.2104</v>
       </c>
       <c r="D324" t="n">
         <v>0.0177</v>
@@ -41586,13 +41586,13 @@
         <v>-0.1751</v>
       </c>
       <c r="F324" t="n">
-        <v>0.2105</v>
+        <v>0.2104</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1751</v>
       </c>
       <c r="M324" t="n">
-        <v>0.2105</v>
+        <v>0.2104</v>
       </c>
     </row>
     <row r="325">
@@ -41748,7 +41748,7 @@
         <v>-0.1385</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.1767</v>
+        <v>-0.1768</v>
       </c>
       <c r="E330" t="n">
         <v>-0.215</v>
@@ -41885,22 +41885,22 @@
         <v>-0.0727</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2625</v>
+        <v>-0.2626</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.1676</v>
+        <v>-0.1677</v>
       </c>
       <c r="E335" t="n">
         <v>-0.0727</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2625</v>
+        <v>-0.2626</v>
       </c>
       <c r="G335" t="n">
         <v>-0.0727</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2625</v>
+        <v>-0.2626</v>
       </c>
     </row>
     <row r="336">
@@ -41913,7 +41913,7 @@
         <v>-0.1206</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.2049</v>
+        <v>-0.205</v>
       </c>
       <c r="D336" t="n">
         <v>-0.1628</v>
@@ -41922,13 +41922,13 @@
         <v>-0.1206</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.2049</v>
+        <v>-0.205</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1206</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.2049</v>
+        <v>-0.205</v>
       </c>
     </row>
     <row r="337">
@@ -41941,7 +41941,7 @@
         <v>-0.1706</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2841</v>
+        <v>-0.2842</v>
       </c>
       <c r="D337" t="n">
         <v>-0.2274</v>
@@ -41950,13 +41950,13 @@
         <v>-0.1706</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.2841</v>
+        <v>-0.2842</v>
       </c>
       <c r="G337" t="n">
         <v>-0.1706</v>
       </c>
       <c r="M337" t="n">
-        <v>-0.2841</v>
+        <v>-0.2842</v>
       </c>
     </row>
     <row r="338">
@@ -41997,22 +41997,22 @@
         <v>-0.1226</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2095</v>
+        <v>-0.2096</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.166</v>
+        <v>-0.1661</v>
       </c>
       <c r="E339" t="n">
         <v>-0.1226</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2095</v>
+        <v>-0.2096</v>
       </c>
       <c r="G339" t="n">
         <v>-0.1226</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2095</v>
+        <v>-0.2096</v>
       </c>
     </row>
     <row r="340">
@@ -42109,7 +42109,7 @@
         <v>-0.1207</v>
       </c>
       <c r="C343" t="n">
-        <v>0.3405</v>
+        <v>0.3404</v>
       </c>
       <c r="D343" t="n">
         <v>0.1099</v>
@@ -42118,13 +42118,13 @@
         <v>-0.1207</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3405</v>
+        <v>0.3404</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1207</v>
       </c>
       <c r="M343" t="n">
-        <v>0.3405</v>
+        <v>0.3404</v>
       </c>
     </row>
     <row r="344">
@@ -42165,7 +42165,7 @@
         <v>-0.1652</v>
       </c>
       <c r="C345" t="n">
-        <v>0.4443</v>
+        <v>0.4442</v>
       </c>
       <c r="D345" t="n">
         <v>0.1395</v>
@@ -42174,13 +42174,13 @@
         <v>-0.1652</v>
       </c>
       <c r="F345" t="n">
-        <v>0.4443</v>
+        <v>0.4442</v>
       </c>
       <c r="G345" t="n">
         <v>-0.1652</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4443</v>
+        <v>0.4442</v>
       </c>
     </row>
     <row r="346">
@@ -42193,7 +42193,7 @@
         <v>-0.1657</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5236</v>
       </c>
       <c r="D346" t="n">
         <v>0.179</v>
@@ -42202,13 +42202,13 @@
         <v>-0.1657</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5236</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1657</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5236</v>
       </c>
     </row>
     <row r="347">
@@ -42333,7 +42333,7 @@
         <v>-0.07480000000000001</v>
       </c>
       <c r="C351" t="n">
-        <v>0.9316</v>
+        <v>0.9315</v>
       </c>
       <c r="D351" t="n">
         <v>0.4284</v>
@@ -42342,13 +42342,13 @@
         <v>-0.07480000000000001</v>
       </c>
       <c r="F351" t="n">
-        <v>0.9316</v>
+        <v>0.9315</v>
       </c>
       <c r="G351" t="n">
         <v>-0.07480000000000001</v>
       </c>
       <c r="M351" t="n">
-        <v>0.9316</v>
+        <v>0.9315</v>
       </c>
     </row>
     <row r="352">
@@ -42364,7 +42364,7 @@
         <v>1.0241</v>
       </c>
       <c r="D352" t="n">
-        <v>0.4989</v>
+        <v>0.4988</v>
       </c>
       <c r="E352" t="n">
         <v>-0.0264</v>
@@ -42672,7 +42672,7 @@
         <v>-0.501</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.222</v>
+        <v>-0.2221</v>
       </c>
       <c r="D363" t="n">
         <v>-0.3615</v>
@@ -42681,7 +42681,7 @@
         <v>-0.501</v>
       </c>
       <c r="F363" t="n">
-        <v>-0.222</v>
+        <v>-0.2221</v>
       </c>
       <c r="G363" t="n">
         <v>0.2628</v>
@@ -42690,7 +42690,7 @@
         <v>-1.2649</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.222</v>
+        <v>-0.2221</v>
       </c>
     </row>
     <row r="364">
@@ -42734,7 +42734,7 @@
         <v>-0.529</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.2145</v>
+        <v>-0.2146</v>
       </c>
       <c r="D365" t="n">
         <v>-0.3718</v>
@@ -42743,7 +42743,7 @@
         <v>-0.529</v>
       </c>
       <c r="F365" t="n">
-        <v>-0.2145</v>
+        <v>-0.2146</v>
       </c>
       <c r="G365" t="n">
         <v>0.1665</v>
@@ -42752,7 +42752,7 @@
         <v>-1.2246</v>
       </c>
       <c r="M365" t="n">
-        <v>-0.2145</v>
+        <v>-0.2146</v>
       </c>
     </row>
     <row r="366">
@@ -42920,7 +42920,7 @@
         <v>-0.4532</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.3085</v>
+        <v>-0.3086</v>
       </c>
       <c r="D371" t="n">
         <v>-0.3809</v>
@@ -42929,7 +42929,7 @@
         <v>-0.4532</v>
       </c>
       <c r="F371" t="n">
-        <v>-0.3085</v>
+        <v>-0.3086</v>
       </c>
       <c r="G371" t="n">
         <v>0.2127</v>
@@ -42938,7 +42938,7 @@
         <v>-1.119</v>
       </c>
       <c r="M371" t="n">
-        <v>-0.3085</v>
+        <v>-0.3086</v>
       </c>
     </row>
     <row r="372">
@@ -42985,7 +42985,7 @@
         <v>-0.2952</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.4162</v>
+        <v>-0.4163</v>
       </c>
       <c r="E373" t="n">
         <v>-0.5373</v>
@@ -43185,16 +43185,16 @@
         <v>-0.5759</v>
       </c>
       <c r="C378" t="n">
-        <v>0.2295</v>
+        <v>0.2294</v>
       </c>
       <c r="D378" t="n">
-        <v>-0.1732</v>
+        <v>-0.1733</v>
       </c>
       <c r="E378" t="n">
         <v>-0.5759</v>
       </c>
       <c r="F378" t="n">
-        <v>0.2295</v>
+        <v>0.2294</v>
       </c>
       <c r="G378" t="n">
         <v>0.3131</v>
@@ -43314,7 +43314,7 @@
         <v>-0.4766</v>
       </c>
       <c r="C381" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="D381" t="n">
         <v>-0.2198</v>
@@ -43323,7 +43323,7 @@
         <v>-0.4766</v>
       </c>
       <c r="F381" t="n">
-        <v>0.0371</v>
+        <v>0.037</v>
       </c>
       <c r="G381" t="n">
         <v>0.1654</v>
@@ -43360,7 +43360,7 @@
         <v>-0.0217</v>
       </c>
       <c r="D382" t="n">
-        <v>-0.2548</v>
+        <v>-0.2549</v>
       </c>
       <c r="E382" t="n">
         <v>-0.488</v>
@@ -43473,7 +43473,7 @@
         <v>0.2207</v>
       </c>
       <c r="M384" t="n">
-        <v>0.7542</v>
+        <v>0.7541</v>
       </c>
     </row>
     <row r="385">
@@ -44088,7 +44088,7 @@
         <v>-0.8479</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.7155</v>
+        <v>-0.7156</v>
       </c>
       <c r="D399" t="n">
         <v>-0.7817</v>
@@ -44097,7 +44097,7 @@
         <v>-0.8479</v>
       </c>
       <c r="F399" t="n">
-        <v>-0.7155</v>
+        <v>-0.7156</v>
       </c>
       <c r="G399" t="n">
         <v>-0.0001</v>
@@ -44634,7 +44634,7 @@
         <v>-2.278</v>
       </c>
       <c r="M411" t="n">
-        <v>-0.3672</v>
+        <v>-0.3673</v>
       </c>
     </row>
     <row r="412">
@@ -44862,7 +44862,7 @@
         <v>0.0424</v>
       </c>
       <c r="C417" t="n">
-        <v>-1.3439</v>
+        <v>-1.344</v>
       </c>
       <c r="D417" t="n">
         <v>-0.6508</v>
@@ -44871,7 +44871,7 @@
         <v>0.0424</v>
       </c>
       <c r="F417" t="n">
-        <v>-1.3439</v>
+        <v>-1.344</v>
       </c>
       <c r="G417" t="n">
         <v>1.1201</v>
@@ -45034,7 +45034,7 @@
         <v>-0.4098</v>
       </c>
       <c r="C421" t="n">
-        <v>-1.1212</v>
+        <v>-1.1213</v>
       </c>
       <c r="D421" t="n">
         <v>-0.7655</v>
@@ -45043,7 +45043,7 @@
         <v>-0.4098</v>
       </c>
       <c r="F421" t="n">
-        <v>-1.1212</v>
+        <v>-1.1213</v>
       </c>
       <c r="G421" t="n">
         <v>-0.0741</v>
@@ -45666,7 +45666,7 @@
         <v>-0.0377</v>
       </c>
       <c r="M435" t="n">
-        <v>0.4091</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="436">
@@ -45980,7 +45980,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="C443" t="n">
-        <v>0.2955</v>
+        <v>0.2954</v>
       </c>
       <c r="D443" t="n">
         <v>-0.158</v>
@@ -45989,7 +45989,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="F443" t="n">
-        <v>0.2955</v>
+        <v>0.2954</v>
       </c>
       <c r="G443" t="n">
         <v>-0.1661</v>
@@ -46311,7 +46311,7 @@
         <v>0.2255</v>
       </c>
       <c r="M450" t="n">
-        <v>0.1824</v>
+        <v>0.1823</v>
       </c>
     </row>
     <row r="451">
@@ -46711,7 +46711,7 @@
         <v>-0.4726</v>
       </c>
       <c r="C460" t="n">
-        <v>0.2529</v>
+        <v>0.2528</v>
       </c>
       <c r="D460" t="n">
         <v>-0.1099</v>
@@ -46720,7 +46720,7 @@
         <v>-0.4726</v>
       </c>
       <c r="F460" t="n">
-        <v>0.2529</v>
+        <v>0.2528</v>
       </c>
       <c r="G460" t="n">
         <v>0.3203</v>
@@ -47257,7 +47257,7 @@
         <v>0.6002999999999999</v>
       </c>
       <c r="M472" t="n">
-        <v>0.2847</v>
+        <v>0.2846</v>
       </c>
     </row>
     <row r="473">
@@ -47356,7 +47356,7 @@
         <v>0.481</v>
       </c>
       <c r="C475" t="n">
-        <v>1.0086</v>
+        <v>1.0085</v>
       </c>
       <c r="D475" t="n">
         <v>0.7448</v>
@@ -47365,7 +47365,7 @@
         <v>0.481</v>
       </c>
       <c r="F475" t="n">
-        <v>1.0086</v>
+        <v>1.0085</v>
       </c>
       <c r="G475" t="n">
         <v>0.3734</v>
@@ -47472,7 +47472,7 @@
         <v>0.5770999999999999</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2795</v>
+        <v>0.2794</v>
       </c>
     </row>
     <row r="478">
@@ -47832,7 +47832,7 @@
         <v>1.0254</v>
       </c>
       <c r="D486" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="E486" t="n">
         <v>0.9735</v>
@@ -47872,7 +47872,7 @@
         <v>0.9488</v>
       </c>
       <c r="C487" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9631</v>
       </c>
       <c r="D487" t="n">
         <v>0.956</v>
@@ -47881,7 +47881,7 @@
         <v>0.9488</v>
       </c>
       <c r="F487" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9631</v>
       </c>
       <c r="G487" t="n">
         <v>1.7936</v>
@@ -48176,7 +48176,7 @@
         <v>0.8912</v>
       </c>
       <c r="D494" t="n">
-        <v>0.9164</v>
+        <v>0.9163</v>
       </c>
       <c r="E494" t="n">
         <v>0.9415</v>
@@ -48474,7 +48474,7 @@
         <v>0.6978</v>
       </c>
       <c r="C501" t="n">
-        <v>0.7879</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="D501" t="n">
         <v>0.7428</v>
@@ -48483,7 +48483,7 @@
         <v>0.6978</v>
       </c>
       <c r="F501" t="n">
-        <v>0.7879</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G501" t="n">
         <v>0.1528</v>
@@ -49493,7 +49493,7 @@
         <v>0.1594</v>
       </c>
       <c r="M524" t="n">
-        <v>0.4289</v>
+        <v>0.4288</v>
       </c>
     </row>
     <row r="525">
@@ -49549,7 +49549,7 @@
         <v>0.412</v>
       </c>
       <c r="C526" t="n">
-        <v>0.3036</v>
+        <v>0.3035</v>
       </c>
       <c r="D526" t="n">
         <v>0.3578</v>
@@ -49558,7 +49558,7 @@
         <v>0.412</v>
       </c>
       <c r="F526" t="n">
-        <v>0.3036</v>
+        <v>0.3035</v>
       </c>
       <c r="G526" t="n">
         <v>0.6449</v>
@@ -49767,7 +49767,7 @@
         <v>0.1715</v>
       </c>
       <c r="D531" t="n">
-        <v>0.2712</v>
+        <v>0.2711</v>
       </c>
       <c r="E531" t="n">
         <v>0.3708</v>
@@ -51871,7 +51871,7 @@
         <v>0.3093</v>
       </c>
       <c r="C580" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0767</v>
       </c>
       <c r="D580" t="n">
         <v>0.193</v>
@@ -51880,7 +51880,7 @@
         <v>0.3093</v>
       </c>
       <c r="F580" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0767</v>
       </c>
       <c r="G580" t="n">
         <v>0.6555</v>
@@ -52761,7 +52761,7 @@
         <v>0.5309</v>
       </c>
       <c r="M600" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.7224</v>
       </c>
     </row>
     <row r="601">
@@ -53492,7 +53492,7 @@
         <v>0.425</v>
       </c>
       <c r="M617" t="n">
-        <v>-0.1078</v>
+        <v>-0.1079</v>
       </c>
     </row>
     <row r="618">
@@ -53634,7 +53634,7 @@
         <v>0.484</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.242</v>
+        <v>-0.2421</v>
       </c>
       <c r="D621" t="n">
         <v>0.121</v>
@@ -53643,7 +53643,7 @@
         <v>0.484</v>
       </c>
       <c r="F621" t="n">
-        <v>-0.242</v>
+        <v>-0.2421</v>
       </c>
       <c r="G621" t="n">
         <v>1.2468</v>
@@ -53664,7 +53664,7 @@
         <v>0.4098</v>
       </c>
       <c r="M621" t="n">
-        <v>-0.105</v>
+        <v>-0.1051</v>
       </c>
     </row>
     <row r="622">
@@ -53750,7 +53750,7 @@
         <v>0.3654</v>
       </c>
       <c r="M623" t="n">
-        <v>-0.0876</v>
+        <v>-0.0877</v>
       </c>
     </row>
     <row r="624">
@@ -53793,7 +53793,7 @@
         <v>0.4504</v>
       </c>
       <c r="M624" t="n">
-        <v>-0.0601</v>
+        <v>-0.0602</v>
       </c>
     </row>
     <row r="625">
@@ -54008,7 +54008,7 @@
         <v>0.3526</v>
       </c>
       <c r="M629" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.06850000000000001</v>
       </c>
     </row>
     <row r="630">
@@ -54193,16 +54193,16 @@
         <v>0.4495</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1701</v>
+        <v>-0.1695</v>
       </c>
       <c r="D634" t="n">
-        <v>0.1397</v>
+        <v>0.14</v>
       </c>
       <c r="E634" t="n">
         <v>0.4495</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1701</v>
+        <v>-0.1695</v>
       </c>
       <c r="G634" t="n">
         <v>0.5548999999999999</v>
@@ -54223,7 +54223,7 @@
         <v>0.4206</v>
       </c>
       <c r="M634" t="n">
-        <v>0.3981</v>
+        <v>0.4001</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -3338,7 +3338,7 @@
         <v>-0.899</v>
       </c>
       <c r="K221" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="222">
@@ -3455,7 +3455,7 @@
         <v>-0.43</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.402</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="231">
@@ -6107,7 +6107,7 @@
         <v>-0.741</v>
       </c>
       <c r="K434" t="n">
-        <v>0.254</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="435">
@@ -6757,7 +6757,7 @@
         <v>0.97</v>
       </c>
       <c r="K484" t="n">
-        <v>0.881</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="485">
@@ -8603,7 +8603,7 @@
         <v>0.45</v>
       </c>
       <c r="K626" t="n">
-        <v>-0.169</v>
+        <v>-0.168</v>
       </c>
     </row>
   </sheetData>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.451</v>
+        <v>10.377</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="13">
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.072</v>
+        <v>1.068</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.87</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="14">
@@ -34435,10 +34435,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.0722</v>
+        <v>1.0685</v>
       </c>
       <c r="H634" t="n">
-        <v>10.4513</v>
+        <v>10.3774</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -37548,7 +37548,7 @@
         <v>-1.9315</v>
       </c>
       <c r="D180" t="n">
-        <v>-1.6134</v>
+        <v>-1.6135</v>
       </c>
       <c r="E180" t="n">
         <v>-1.2954</v>
@@ -37744,7 +37744,7 @@
         <v>-0.7324000000000001</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.7591</v>
+        <v>-0.7592</v>
       </c>
       <c r="E187" t="n">
         <v>-0.7859</v>
@@ -37940,7 +37940,7 @@
         <v>-0.7313</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.9952</v>
+        <v>-0.9953</v>
       </c>
       <c r="E194" t="n">
         <v>-1.2592</v>
@@ -38833,7 +38833,7 @@
         <v>-0.4997</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.0032</v>
+        <v>-0.0033</v>
       </c>
       <c r="D226" t="n">
         <v>-0.2515</v>
@@ -38842,13 +38842,13 @@
         <v>-0.4997</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.0032</v>
+        <v>-0.0033</v>
       </c>
       <c r="G226" t="n">
         <v>-0.4997</v>
       </c>
       <c r="M226" t="n">
-        <v>-0.0032</v>
+        <v>-0.0033</v>
       </c>
     </row>
     <row r="227">
@@ -38945,7 +38945,7 @@
         <v>-0.6153999999999999</v>
       </c>
       <c r="C230" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0718</v>
       </c>
       <c r="D230" t="n">
         <v>-0.2718</v>
@@ -38954,13 +38954,13 @@
         <v>-0.6153999999999999</v>
       </c>
       <c r="F230" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0718</v>
       </c>
       <c r="G230" t="n">
         <v>-0.6153999999999999</v>
       </c>
       <c r="M230" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="231">
@@ -39085,7 +39085,7 @@
         <v>-0.5919</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.3813</v>
+        <v>-0.3814</v>
       </c>
       <c r="D235" t="n">
         <v>-0.4866</v>
@@ -39094,13 +39094,13 @@
         <v>-0.5919</v>
       </c>
       <c r="F235" t="n">
-        <v>-0.3813</v>
+        <v>-0.3814</v>
       </c>
       <c r="G235" t="n">
         <v>-0.5919</v>
       </c>
       <c r="M235" t="n">
-        <v>-0.3813</v>
+        <v>-0.3814</v>
       </c>
     </row>
     <row r="236">
@@ -39113,7 +39113,7 @@
         <v>-0.5682</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.4532</v>
+        <v>-0.4533</v>
       </c>
       <c r="D236" t="n">
         <v>-0.5107</v>
@@ -39122,13 +39122,13 @@
         <v>-0.5682</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.4532</v>
+        <v>-0.4533</v>
       </c>
       <c r="G236" t="n">
         <v>-0.5682</v>
       </c>
       <c r="M236" t="n">
-        <v>-0.4532</v>
+        <v>-0.4533</v>
       </c>
     </row>
     <row r="237">
@@ -39200,7 +39200,7 @@
         <v>-0.4433</v>
       </c>
       <c r="D239" t="n">
-        <v>-0.3676</v>
+        <v>-0.3677</v>
       </c>
       <c r="E239" t="n">
         <v>-0.292</v>
@@ -39228,7 +39228,7 @@
         <v>-0.4706</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.3979</v>
+        <v>-0.398</v>
       </c>
       <c r="E240" t="n">
         <v>-0.3253</v>
@@ -39424,7 +39424,7 @@
         <v>-1.2635</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.8091</v>
+        <v>-0.8092</v>
       </c>
       <c r="E247" t="n">
         <v>-0.3548</v>
@@ -39592,7 +39592,7 @@
         <v>-0.8058999999999999</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.7951</v>
+        <v>-0.7952</v>
       </c>
       <c r="E253" t="n">
         <v>-0.7844</v>
@@ -39673,7 +39673,7 @@
         <v>-0.6083</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.7714</v>
+        <v>-0.7715</v>
       </c>
       <c r="D256" t="n">
         <v>-0.6899</v>
@@ -39682,13 +39682,13 @@
         <v>-0.6083</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.7714</v>
+        <v>-0.7715</v>
       </c>
       <c r="G256" t="n">
         <v>-0.6083</v>
       </c>
       <c r="M256" t="n">
-        <v>-0.7714</v>
+        <v>-0.7715</v>
       </c>
     </row>
     <row r="257">
@@ -39900,7 +39900,7 @@
         <v>-0.8346</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.3622</v>
+        <v>-0.3623</v>
       </c>
       <c r="E264" t="n">
         <v>0.1101</v>
@@ -40180,7 +40180,7 @@
         <v>0.2273</v>
       </c>
       <c r="D274" t="n">
-        <v>0.1937</v>
+        <v>0.1936</v>
       </c>
       <c r="E274" t="n">
         <v>0.16</v>
@@ -40233,7 +40233,7 @@
         <v>0.2691</v>
       </c>
       <c r="C276" t="n">
-        <v>0.1692</v>
+        <v>0.1691</v>
       </c>
       <c r="D276" t="n">
         <v>0.2191</v>
@@ -40242,13 +40242,13 @@
         <v>0.2691</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1692</v>
+        <v>0.1691</v>
       </c>
       <c r="G276" t="n">
         <v>0.2691</v>
       </c>
       <c r="M276" t="n">
-        <v>0.1692</v>
+        <v>0.1691</v>
       </c>
     </row>
     <row r="277">
@@ -40289,7 +40289,7 @@
         <v>0.3176</v>
       </c>
       <c r="C278" t="n">
-        <v>0.4116</v>
+        <v>0.4115</v>
       </c>
       <c r="D278" t="n">
         <v>0.3646</v>
@@ -40298,13 +40298,13 @@
         <v>0.3176</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4116</v>
+        <v>0.4115</v>
       </c>
       <c r="G278" t="n">
         <v>0.3176</v>
       </c>
       <c r="M278" t="n">
-        <v>0.4116</v>
+        <v>0.4115</v>
       </c>
     </row>
     <row r="279">
@@ -40345,7 +40345,7 @@
         <v>0.2961</v>
       </c>
       <c r="C280" t="n">
-        <v>0.5107</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="D280" t="n">
         <v>0.4034</v>
@@ -40354,13 +40354,13 @@
         <v>0.2961</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5107</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G280" t="n">
         <v>0.2961</v>
       </c>
       <c r="M280" t="n">
-        <v>0.5107</v>
+        <v>0.5106000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -40401,22 +40401,22 @@
         <v>0.9461000000000001</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="D282" t="n">
-        <v>0.4354</v>
+        <v>0.4353</v>
       </c>
       <c r="E282" t="n">
         <v>0.9461000000000001</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G282" t="n">
         <v>0.9461000000000001</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.07539999999999999</v>
       </c>
     </row>
     <row r="283">
@@ -40457,7 +40457,7 @@
         <v>0.9893</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0641</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="D284" t="n">
         <v>0.4626</v>
@@ -40466,13 +40466,13 @@
         <v>0.9893</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.0641</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G284" t="n">
         <v>0.9893</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.0641</v>
+        <v>-0.06419999999999999</v>
       </c>
     </row>
     <row r="285">
@@ -40513,7 +40513,7 @@
         <v>1.1511</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.0319</v>
+        <v>-0.032</v>
       </c>
       <c r="D286" t="n">
         <v>0.5596</v>
@@ -40522,13 +40522,13 @@
         <v>1.1511</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.0319</v>
+        <v>-0.032</v>
       </c>
       <c r="G286" t="n">
         <v>1.1511</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.0319</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="287">
@@ -40653,7 +40653,7 @@
         <v>0.8969</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.1329</v>
+        <v>-0.133</v>
       </c>
       <c r="D291" t="n">
         <v>0.382</v>
@@ -40662,13 +40662,13 @@
         <v>0.8969</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.1329</v>
+        <v>-0.133</v>
       </c>
       <c r="G291" t="n">
         <v>0.8969</v>
       </c>
       <c r="M291" t="n">
-        <v>-0.1329</v>
+        <v>-0.133</v>
       </c>
     </row>
     <row r="292">
@@ -40793,7 +40793,7 @@
         <v>0.0165</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1697</v>
+        <v>0.1696</v>
       </c>
       <c r="D296" t="n">
         <v>0.0931</v>
@@ -40802,13 +40802,13 @@
         <v>0.0165</v>
       </c>
       <c r="F296" t="n">
-        <v>0.1697</v>
+        <v>0.1696</v>
       </c>
       <c r="G296" t="n">
         <v>0.0165</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1697</v>
+        <v>0.1696</v>
       </c>
     </row>
     <row r="297">
@@ -40852,7 +40852,7 @@
         <v>-0.1634</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.1368</v>
+        <v>-0.1369</v>
       </c>
       <c r="E298" t="n">
         <v>-0.1103</v>
@@ -41020,7 +41020,7 @@
         <v>-1.5765</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.7064</v>
+        <v>-0.7065</v>
       </c>
       <c r="E304" t="n">
         <v>0.1636</v>
@@ -41045,7 +41045,7 @@
         <v>0.1752</v>
       </c>
       <c r="C305" t="n">
-        <v>-1.6607</v>
+        <v>-1.6608</v>
       </c>
       <c r="D305" t="n">
         <v>-0.7428</v>
@@ -41054,13 +41054,13 @@
         <v>0.1752</v>
       </c>
       <c r="F305" t="n">
-        <v>-1.6607</v>
+        <v>-1.6608</v>
       </c>
       <c r="G305" t="n">
         <v>0.1752</v>
       </c>
       <c r="M305" t="n">
-        <v>-1.6607</v>
+        <v>-1.6608</v>
       </c>
     </row>
     <row r="306">
@@ -41188,7 +41188,7 @@
         <v>-1.1231</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.4463</v>
+        <v>-0.4464</v>
       </c>
       <c r="E310" t="n">
         <v>0.2304</v>
@@ -41213,7 +41213,7 @@
         <v>0.1881</v>
       </c>
       <c r="C311" t="n">
-        <v>-1.0248</v>
+        <v>-1.0249</v>
       </c>
       <c r="D311" t="n">
         <v>-0.4184</v>
@@ -41222,13 +41222,13 @@
         <v>0.1881</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.0248</v>
+        <v>-1.0249</v>
       </c>
       <c r="G311" t="n">
         <v>0.1881</v>
       </c>
       <c r="M311" t="n">
-        <v>-1.0248</v>
+        <v>-1.0249</v>
       </c>
     </row>
     <row r="312">
@@ -41241,7 +41241,7 @@
         <v>0.1356</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.8728</v>
+        <v>-0.8729</v>
       </c>
       <c r="D312" t="n">
         <v>-0.3686</v>
@@ -41250,13 +41250,13 @@
         <v>0.1356</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.8728</v>
+        <v>-0.8729</v>
       </c>
       <c r="G312" t="n">
         <v>0.1356</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.8728</v>
+        <v>-0.8729</v>
       </c>
     </row>
     <row r="313">
@@ -41269,7 +41269,7 @@
         <v>0.1746</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.5012</v>
+        <v>-0.5013</v>
       </c>
       <c r="D313" t="n">
         <v>-0.1633</v>
@@ -41278,13 +41278,13 @@
         <v>0.1746</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.5012</v>
+        <v>-0.5013</v>
       </c>
       <c r="G313" t="n">
         <v>0.1746</v>
       </c>
       <c r="M313" t="n">
-        <v>-0.5012</v>
+        <v>-0.5013</v>
       </c>
     </row>
     <row r="314">
@@ -41297,7 +41297,7 @@
         <v>0.1261</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.1285</v>
+        <v>-0.1286</v>
       </c>
       <c r="D314" t="n">
         <v>-0.0012</v>
@@ -41306,13 +41306,13 @@
         <v>0.1261</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.1285</v>
+        <v>-0.1286</v>
       </c>
       <c r="G314" t="n">
         <v>0.1261</v>
       </c>
       <c r="M314" t="n">
-        <v>-0.1285</v>
+        <v>-0.1286</v>
       </c>
     </row>
     <row r="315">
@@ -41468,7 +41468,7 @@
         <v>0.8035</v>
       </c>
       <c r="D320" t="n">
-        <v>0.4515</v>
+        <v>0.4514</v>
       </c>
       <c r="E320" t="n">
         <v>0.0994</v>
@@ -41521,7 +41521,7 @@
         <v>-0.0863</v>
       </c>
       <c r="C322" t="n">
-        <v>0.7326</v>
+        <v>0.7325</v>
       </c>
       <c r="D322" t="n">
         <v>0.3231</v>
@@ -41530,13 +41530,13 @@
         <v>-0.0863</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7326</v>
+        <v>0.7325</v>
       </c>
       <c r="G322" t="n">
         <v>-0.0863</v>
       </c>
       <c r="M322" t="n">
-        <v>0.7326</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="323">
@@ -41605,7 +41605,7 @@
         <v>-0.1797</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1903</v>
+        <v>0.1902</v>
       </c>
       <c r="D325" t="n">
         <v>0.0053</v>
@@ -41614,13 +41614,13 @@
         <v>-0.1797</v>
       </c>
       <c r="F325" t="n">
-        <v>0.1903</v>
+        <v>0.1902</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1797</v>
       </c>
       <c r="M325" t="n">
-        <v>0.1903</v>
+        <v>0.1902</v>
       </c>
     </row>
     <row r="326">
@@ -41633,7 +41633,7 @@
         <v>-0.2563</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1847</v>
+        <v>0.1846</v>
       </c>
       <c r="D326" t="n">
         <v>-0.0358</v>
@@ -41642,13 +41642,13 @@
         <v>-0.2563</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1847</v>
+        <v>0.1846</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2563</v>
       </c>
       <c r="M326" t="n">
-        <v>0.1847</v>
+        <v>0.1846</v>
       </c>
     </row>
     <row r="327">
@@ -41661,7 +41661,7 @@
         <v>-0.2401</v>
       </c>
       <c r="C327" t="n">
-        <v>0.4105</v>
+        <v>0.4104</v>
       </c>
       <c r="D327" t="n">
         <v>0.0852</v>
@@ -41670,13 +41670,13 @@
         <v>-0.2401</v>
       </c>
       <c r="F327" t="n">
-        <v>0.4105</v>
+        <v>0.4104</v>
       </c>
       <c r="G327" t="n">
         <v>-0.2401</v>
       </c>
       <c r="M327" t="n">
-        <v>0.4105</v>
+        <v>0.4104</v>
       </c>
     </row>
     <row r="328">
@@ -41689,7 +41689,7 @@
         <v>-0.212</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4496</v>
+        <v>0.4495</v>
       </c>
       <c r="D328" t="n">
         <v>0.1188</v>
@@ -41698,13 +41698,13 @@
         <v>-0.212</v>
       </c>
       <c r="F328" t="n">
-        <v>0.4496</v>
+        <v>0.4495</v>
       </c>
       <c r="G328" t="n">
         <v>-0.212</v>
       </c>
       <c r="M328" t="n">
-        <v>0.4496</v>
+        <v>0.4495</v>
       </c>
     </row>
     <row r="329">
@@ -41745,7 +41745,7 @@
         <v>-0.215</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1385</v>
+        <v>-0.1386</v>
       </c>
       <c r="D330" t="n">
         <v>-0.1768</v>
@@ -41754,13 +41754,13 @@
         <v>-0.215</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1385</v>
+        <v>-0.1386</v>
       </c>
       <c r="G330" t="n">
         <v>-0.215</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1385</v>
+        <v>-0.1386</v>
       </c>
     </row>
     <row r="331">
@@ -41773,7 +41773,7 @@
         <v>-0.1669</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.1229</v>
+        <v>-0.123</v>
       </c>
       <c r="D331" t="n">
         <v>-0.1449</v>
@@ -41782,13 +41782,13 @@
         <v>-0.1669</v>
       </c>
       <c r="F331" t="n">
-        <v>-0.1229</v>
+        <v>-0.123</v>
       </c>
       <c r="G331" t="n">
         <v>-0.1669</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.1229</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="332">
@@ -41801,7 +41801,7 @@
         <v>-0.17</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.2562</v>
+        <v>-0.2563</v>
       </c>
       <c r="D332" t="n">
         <v>-0.2131</v>
@@ -41810,13 +41810,13 @@
         <v>-0.17</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2562</v>
+        <v>-0.2563</v>
       </c>
       <c r="G332" t="n">
         <v>-0.17</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.2562</v>
+        <v>-0.2563</v>
       </c>
     </row>
     <row r="333">
@@ -41969,7 +41969,7 @@
         <v>-0.1234</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2473</v>
+        <v>-0.2474</v>
       </c>
       <c r="D338" t="n">
         <v>-0.1854</v>
@@ -41978,13 +41978,13 @@
         <v>-0.1234</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2473</v>
+        <v>-0.2474</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1234</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2473</v>
+        <v>-0.2474</v>
       </c>
     </row>
     <row r="339">
@@ -42025,7 +42025,7 @@
         <v>-0.0746</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
       <c r="D340" t="n">
         <v>-0.0117</v>
@@ -42034,13 +42034,13 @@
         <v>-0.0746</v>
       </c>
       <c r="F340" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
       <c r="G340" t="n">
         <v>-0.0746</v>
       </c>
       <c r="M340" t="n">
-        <v>0.0513</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="341">
@@ -42053,7 +42053,7 @@
         <v>-0.1679</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1757</v>
+        <v>0.1756</v>
       </c>
       <c r="D341" t="n">
         <v>0.0039</v>
@@ -42062,13 +42062,13 @@
         <v>-0.1679</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1757</v>
+        <v>0.1756</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1679</v>
       </c>
       <c r="M341" t="n">
-        <v>0.1757</v>
+        <v>0.1756</v>
       </c>
     </row>
     <row r="342">
@@ -42081,7 +42081,7 @@
         <v>-0.1202</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2249</v>
+        <v>0.2248</v>
       </c>
       <c r="D342" t="n">
         <v>0.0523</v>
@@ -42090,13 +42090,13 @@
         <v>-0.1202</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2249</v>
+        <v>0.2248</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2249</v>
+        <v>0.2248</v>
       </c>
     </row>
     <row r="343">
@@ -42277,7 +42277,7 @@
         <v>-0.07140000000000001</v>
       </c>
       <c r="C349" t="n">
-        <v>0.5077</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="D349" t="n">
         <v>0.2181</v>
@@ -42286,13 +42286,13 @@
         <v>-0.07140000000000001</v>
       </c>
       <c r="F349" t="n">
-        <v>0.5077</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G349" t="n">
         <v>-0.07140000000000001</v>
       </c>
       <c r="M349" t="n">
-        <v>0.5077</v>
+        <v>0.5076000000000001</v>
       </c>
     </row>
     <row r="350">
@@ -42616,7 +42616,7 @@
         <v>0.0153</v>
       </c>
       <c r="D361" t="n">
-        <v>0.1391</v>
+        <v>0.139</v>
       </c>
       <c r="E361" t="n">
         <v>0.2628</v>
@@ -42641,7 +42641,7 @@
         <v>-0.5437</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0206</v>
+        <v>0.0205</v>
       </c>
       <c r="D362" t="n">
         <v>-0.2616</v>
@@ -42650,7 +42650,7 @@
         <v>-0.5437</v>
       </c>
       <c r="F362" t="n">
-        <v>0.0206</v>
+        <v>0.0205</v>
       </c>
       <c r="G362" t="n">
         <v>0.2146</v>
@@ -42659,7 +42659,7 @@
         <v>-1.302</v>
       </c>
       <c r="M362" t="n">
-        <v>0.0206</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="363">
@@ -42675,7 +42675,7 @@
         <v>-0.2221</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.3615</v>
+        <v>-0.3616</v>
       </c>
       <c r="E363" t="n">
         <v>-0.501</v>
@@ -42703,7 +42703,7 @@
         <v>-0.4827</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.0679</v>
+        <v>-0.068</v>
       </c>
       <c r="D364" t="n">
         <v>-0.2753</v>
@@ -42712,7 +42712,7 @@
         <v>-0.4827</v>
       </c>
       <c r="F364" t="n">
-        <v>-0.0679</v>
+        <v>-0.068</v>
       </c>
       <c r="G364" t="n">
         <v>0.2152</v>
@@ -42721,7 +42721,7 @@
         <v>-1.1806</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.0679</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="365">
@@ -42858,7 +42858,7 @@
         <v>-0.4497</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.4027</v>
+        <v>-0.4028</v>
       </c>
       <c r="D369" t="n">
         <v>-0.4262</v>
@@ -42867,7 +42867,7 @@
         <v>-0.4497</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.4027</v>
+        <v>-0.4028</v>
       </c>
       <c r="G369" t="n">
         <v>0.1637</v>
@@ -42876,7 +42876,7 @@
         <v>-1.063</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.4027</v>
+        <v>-0.4028</v>
       </c>
     </row>
     <row r="370">
@@ -42889,7 +42889,7 @@
         <v>-0.4053</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3745</v>
+        <v>-0.3746</v>
       </c>
       <c r="D370" t="n">
         <v>-0.3899</v>
@@ -42898,7 +42898,7 @@
         <v>-0.4053</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3745</v>
+        <v>-0.3746</v>
       </c>
       <c r="G370" t="n">
         <v>0.2608</v>
@@ -42907,7 +42907,7 @@
         <v>-1.0714</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3745</v>
+        <v>-0.3746</v>
       </c>
     </row>
     <row r="371">
@@ -42951,16 +42951,16 @@
         <v>-0.5491</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3361</v>
+        <v>-0.3362</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.4426</v>
+        <v>-0.4427</v>
       </c>
       <c r="E372" t="n">
         <v>-0.5491</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3361</v>
+        <v>-0.3362</v>
       </c>
       <c r="G372" t="n">
         <v>0.168</v>
@@ -42969,7 +42969,7 @@
         <v>-1.2662</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3361</v>
+        <v>-0.3362</v>
       </c>
     </row>
     <row r="373">
@@ -43056,7 +43056,7 @@
         <v>-0.5753</v>
       </c>
       <c r="C375" t="n">
-        <v>0.4563</v>
+        <v>0.4562</v>
       </c>
       <c r="D375" t="n">
         <v>-0.0595</v>
@@ -43065,7 +43065,7 @@
         <v>-0.5753</v>
       </c>
       <c r="F375" t="n">
-        <v>0.4563</v>
+        <v>0.4562</v>
       </c>
       <c r="G375" t="n">
         <v>0.1677</v>
@@ -43231,7 +43231,7 @@
         <v>0.1959</v>
       </c>
       <c r="D379" t="n">
-        <v>-0.1803</v>
+        <v>-0.1804</v>
       </c>
       <c r="E379" t="n">
         <v>-0.5566</v>
@@ -43357,7 +43357,7 @@
         <v>-0.488</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.0217</v>
+        <v>-0.0218</v>
       </c>
       <c r="D382" t="n">
         <v>-0.2549</v>
@@ -43366,7 +43366,7 @@
         <v>-0.488</v>
       </c>
       <c r="F382" t="n">
-        <v>-0.0217</v>
+        <v>-0.0218</v>
       </c>
       <c r="G382" t="n">
         <v>0.1639</v>
@@ -44075,7 +44075,7 @@
         <v>-1.0455</v>
       </c>
       <c r="M398" t="n">
-        <v>0.2702</v>
+        <v>0.2701</v>
       </c>
     </row>
     <row r="399">
@@ -44392,7 +44392,7 @@
         <v>-0.8405</v>
       </c>
       <c r="D406" t="n">
-        <v>-0.6607</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="E406" t="n">
         <v>-0.481</v>
@@ -44591,7 +44591,7 @@
         <v>-2.1231</v>
       </c>
       <c r="M410" t="n">
-        <v>-0.3739</v>
+        <v>-0.374</v>
       </c>
     </row>
     <row r="411">
@@ -44763,7 +44763,7 @@
         <v>-2.4944</v>
       </c>
       <c r="M414" t="n">
-        <v>-0.4855</v>
+        <v>-0.4856</v>
       </c>
     </row>
     <row r="415">
@@ -44935,7 +44935,7 @@
         <v>-2.9258</v>
       </c>
       <c r="M418" t="n">
-        <v>-0.669</v>
+        <v>-0.6691</v>
       </c>
     </row>
     <row r="419">
@@ -45236,7 +45236,7 @@
         <v>-1.2112</v>
       </c>
       <c r="M425" t="n">
-        <v>0.3129</v>
+        <v>0.3128</v>
       </c>
     </row>
     <row r="426">
@@ -45279,7 +45279,7 @@
         <v>-0.762</v>
       </c>
       <c r="M426" t="n">
-        <v>0.545</v>
+        <v>0.5449000000000001</v>
       </c>
     </row>
     <row r="427">
@@ -45682,7 +45682,7 @@
         <v>0.1894</v>
       </c>
       <c r="D436" t="n">
-        <v>-0.263</v>
+        <v>-0.2631</v>
       </c>
       <c r="E436" t="n">
         <v>-0.7155</v>
@@ -45838,7 +45838,7 @@
         <v>0.2502</v>
       </c>
       <c r="M439" t="n">
-        <v>0.3243</v>
+        <v>0.3242</v>
       </c>
     </row>
     <row r="440">
@@ -46096,7 +46096,7 @@
         <v>0.1918</v>
       </c>
       <c r="M445" t="n">
-        <v>0.1832</v>
+        <v>0.1831</v>
       </c>
     </row>
     <row r="446">
@@ -46139,7 +46139,7 @@
         <v>0.2401</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2392</v>
+        <v>0.2391</v>
       </c>
     </row>
     <row r="447">
@@ -46440,7 +46440,7 @@
         <v>0.143</v>
       </c>
       <c r="M453" t="n">
-        <v>0.1968</v>
+        <v>0.1967</v>
       </c>
     </row>
     <row r="454">
@@ -46655,7 +46655,7 @@
         <v>0.1919</v>
       </c>
       <c r="M458" t="n">
-        <v>0.389</v>
+        <v>0.3889</v>
       </c>
     </row>
     <row r="459">
@@ -47128,7 +47128,7 @@
         <v>0.4979</v>
       </c>
       <c r="M469" t="n">
-        <v>0.3935</v>
+        <v>0.3934</v>
       </c>
     </row>
     <row r="470">
@@ -47614,7 +47614,7 @@
         <v>1.0907</v>
       </c>
       <c r="C481" t="n">
-        <v>1.2862</v>
+        <v>1.2861</v>
       </c>
       <c r="D481" t="n">
         <v>1.1884</v>
@@ -47623,7 +47623,7 @@
         <v>1.0907</v>
       </c>
       <c r="F481" t="n">
-        <v>1.2862</v>
+        <v>1.2861</v>
       </c>
       <c r="G481" t="n">
         <v>1.5425</v>
@@ -47730,7 +47730,7 @@
         <v>0.61</v>
       </c>
       <c r="M483" t="n">
-        <v>0.228</v>
+        <v>0.2279</v>
       </c>
     </row>
     <row r="484">
@@ -47829,7 +47829,7 @@
         <v>0.9735</v>
       </c>
       <c r="C486" t="n">
-        <v>1.0254</v>
+        <v>1.0253</v>
       </c>
       <c r="D486" t="n">
         <v>0.9994</v>
@@ -47838,7 +47838,7 @@
         <v>0.9735</v>
       </c>
       <c r="F486" t="n">
-        <v>1.0254</v>
+        <v>1.0253</v>
       </c>
       <c r="G486" t="n">
         <v>1.7934</v>
@@ -47859,7 +47859,7 @@
         <v>0.5447</v>
       </c>
       <c r="M486" t="n">
-        <v>0.3384</v>
+        <v>0.3383</v>
       </c>
     </row>
     <row r="487">
@@ -47961,7 +47961,7 @@
         <v>0.9119</v>
       </c>
       <c r="D489" t="n">
-        <v>0.8887</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="E489" t="n">
         <v>0.8653999999999999</v>
@@ -48001,7 +48001,7 @@
         <v>0.8836000000000001</v>
       </c>
       <c r="C490" t="n">
-        <v>0.901</v>
+        <v>0.9009</v>
       </c>
       <c r="D490" t="n">
         <v>0.8923</v>
@@ -48010,7 +48010,7 @@
         <v>0.8836000000000001</v>
       </c>
       <c r="F490" t="n">
-        <v>0.901</v>
+        <v>0.9009</v>
       </c>
       <c r="G490" t="n">
         <v>1.6469</v>
@@ -48130,7 +48130,7 @@
         <v>0.7104</v>
       </c>
       <c r="C493" t="n">
-        <v>0.8657</v>
+        <v>0.8656</v>
       </c>
       <c r="D493" t="n">
         <v>0.788</v>
@@ -48139,7 +48139,7 @@
         <v>0.7104</v>
       </c>
       <c r="F493" t="n">
-        <v>0.8657</v>
+        <v>0.8656</v>
       </c>
       <c r="G493" t="n">
         <v>0.2521</v>
@@ -48160,7 +48160,7 @@
         <v>0.5299</v>
       </c>
       <c r="M493" t="n">
-        <v>0.3279</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="494">
@@ -49536,7 +49536,7 @@
         <v>0.1585</v>
       </c>
       <c r="M525" t="n">
-        <v>0.3921</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="526">
@@ -50009,7 +50009,7 @@
         <v>-0.0072</v>
       </c>
       <c r="M536" t="n">
-        <v>0.2575</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="537">
@@ -50151,7 +50151,7 @@
         <v>0.2944</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.0803</v>
+        <v>-0.0804</v>
       </c>
       <c r="D540" t="n">
         <v>0.107</v>
@@ -50160,7 +50160,7 @@
         <v>0.2944</v>
       </c>
       <c r="F540" t="n">
-        <v>-0.0803</v>
+        <v>-0.0804</v>
       </c>
       <c r="G540" t="n">
         <v>0.7401</v>
@@ -52331,7 +52331,7 @@
         <v>0.4095</v>
       </c>
       <c r="M590" t="n">
-        <v>-1.0747</v>
+        <v>-1.0748</v>
       </c>
     </row>
     <row r="591">
@@ -52804,7 +52804,7 @@
         <v>0.4849</v>
       </c>
       <c r="M601" t="n">
-        <v>-0.5678</v>
+        <v>-0.5679</v>
       </c>
     </row>
     <row r="602">
@@ -52903,7 +52903,7 @@
         <v>0.6262</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.1696</v>
+        <v>-0.1697</v>
       </c>
       <c r="D604" t="n">
         <v>0.2283</v>
@@ -52912,7 +52912,7 @@
         <v>0.6262</v>
       </c>
       <c r="F604" t="n">
-        <v>-0.1696</v>
+        <v>-0.1697</v>
       </c>
       <c r="G604" t="n">
         <v>1.4572</v>
@@ -52976,7 +52976,7 @@
         <v>0.4828</v>
       </c>
       <c r="M605" t="n">
-        <v>-0.3062</v>
+        <v>-0.3063</v>
       </c>
     </row>
     <row r="606">
@@ -53677,7 +53677,7 @@
         <v>0.4746</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.234</v>
+        <v>-0.2341</v>
       </c>
       <c r="D622" t="n">
         <v>0.1203</v>
@@ -53686,7 +53686,7 @@
         <v>0.4746</v>
       </c>
       <c r="F622" t="n">
-        <v>-0.234</v>
+        <v>-0.2341</v>
       </c>
       <c r="G622" t="n">
         <v>1.3681</v>
@@ -53720,7 +53720,7 @@
         <v>0.5212</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.2688</v>
+        <v>-0.2689</v>
       </c>
       <c r="D623" t="n">
         <v>0.1262</v>
@@ -53729,7 +53729,7 @@
         <v>0.5212</v>
       </c>
       <c r="F623" t="n">
-        <v>-0.2688</v>
+        <v>-0.2689</v>
       </c>
       <c r="G623" t="n">
         <v>1.3976</v>
@@ -53836,7 +53836,7 @@
         <v>0.3825</v>
       </c>
       <c r="M625" t="n">
-        <v>-0.0709</v>
+        <v>-0.07099999999999999</v>
       </c>
     </row>
     <row r="626">
@@ -53849,7 +53849,7 @@
         <v>0.4317</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.2655</v>
+        <v>-0.2656</v>
       </c>
       <c r="D626" t="n">
         <v>0.08309999999999999</v>
@@ -53858,7 +53858,7 @@
         <v>0.4317</v>
       </c>
       <c r="F626" t="n">
-        <v>-0.2655</v>
+        <v>-0.2656</v>
       </c>
       <c r="G626" t="n">
         <v>0.8129999999999999</v>
@@ -53879,7 +53879,7 @@
         <v>0.4379</v>
       </c>
       <c r="M626" t="n">
-        <v>-0.0413</v>
+        <v>-0.0414</v>
       </c>
     </row>
     <row r="627">
@@ -54137,7 +54137,7 @@
         <v>0.4486</v>
       </c>
       <c r="M632" t="n">
-        <v>0.2849</v>
+        <v>0.2848</v>
       </c>
     </row>
     <row r="633">
@@ -54180,7 +54180,7 @@
         <v>0.4342</v>
       </c>
       <c r="M633" t="n">
-        <v>0.3745</v>
+        <v>0.3744</v>
       </c>
     </row>
     <row r="634">
@@ -54193,16 +54193,16 @@
         <v>0.4495</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1695</v>
+        <v>-0.1684</v>
       </c>
       <c r="D634" t="n">
-        <v>0.14</v>
+        <v>0.1406</v>
       </c>
       <c r="E634" t="n">
         <v>0.4495</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1695</v>
+        <v>-0.1684</v>
       </c>
       <c r="G634" t="n">
         <v>0.5548999999999999</v>
@@ -54223,7 +54223,7 @@
         <v>0.4206</v>
       </c>
       <c r="M634" t="n">
-        <v>0.4001</v>
+        <v>0.4034</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -840,7 +840,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>-0.168</v>
       </c>
       <c r="K323" t="n">
-        <v>-0.123</v>
+        <v>-0.122</v>
       </c>
     </row>
     <row r="324">
@@ -4807,7 +4807,7 @@
         <v>-0.121</v>
       </c>
       <c r="K334" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="335">
@@ -4898,7 +4898,7 @@
         <v>-0.07199999999999999</v>
       </c>
       <c r="K341" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="342">
@@ -5171,7 +5171,7 @@
         <v>-0.407</v>
       </c>
       <c r="K362" t="n">
-        <v>-0.375</v>
+        <v>-0.374</v>
       </c>
     </row>
     <row r="363">
@@ -6432,7 +6432,7 @@
         <v>-0.258</v>
       </c>
       <c r="K459" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="460">
@@ -6445,7 +6445,7 @@
         <v>-0.349</v>
       </c>
       <c r="K460" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="461">
@@ -6536,7 +6536,7 @@
         <v>0.48</v>
       </c>
       <c r="K467" t="n">
-        <v>1.008</v>
+        <v>1.009</v>
       </c>
     </row>
     <row r="468">
@@ -6796,7 +6796,7 @@
         <v>0.91</v>
       </c>
       <c r="K487" t="n">
-        <v>0.848</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="488">
@@ -7407,7 +7407,7 @@
         <v>0.242</v>
       </c>
       <c r="K534" t="n">
-        <v>-0.136</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="535">
@@ -8291,7 +8291,7 @@
         <v>0.513</v>
       </c>
       <c r="K602" t="n">
-        <v>-0.164</v>
+        <v>-0.163</v>
       </c>
     </row>
     <row r="603">
@@ -8616,7 +8616,7 @@
         <v>0.436</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.158</v>
+        <v>-0.162</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9.878</v>
+        <v>9.879</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.03</v>
+        <v>1.054</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="14">
@@ -34490,7 +34490,7 @@
         <v>156.4171</v>
       </c>
       <c r="U634" t="n">
-        <v>0.977</v>
+        <v>1.043</v>
       </c>
       <c r="V634" t="n">
         <v>1.7921</v>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.03</v>
+        <v>1.054</v>
       </c>
       <c r="H635" t="n">
-        <v>9.877700000000001</v>
+        <v>9.8789</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -34560,7 +34560,7 @@
         <v>156.4171</v>
       </c>
       <c r="U635" t="n">
-        <v>0.977</v>
+        <v>1.043</v>
       </c>
       <c r="V635" t="n">
         <v>1.7921</v>
@@ -38048,7 +38048,7 @@
         <v>-1.372</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="D195" t="n">
         <v>-1.0466</v>
@@ -38057,13 +38057,13 @@
         <v>-1.372</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="G195" t="n">
         <v>-1.372</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7212</v>
       </c>
     </row>
     <row r="196">
@@ -41268,22 +41268,22 @@
         <v>0.2295</v>
       </c>
       <c r="C310" t="n">
-        <v>-1.1238</v>
+        <v>-1.1236</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.4471</v>
+        <v>-0.447</v>
       </c>
       <c r="E310" t="n">
         <v>0.2295</v>
       </c>
       <c r="F310" t="n">
-        <v>-1.1238</v>
+        <v>-1.1236</v>
       </c>
       <c r="G310" t="n">
         <v>0.2295</v>
       </c>
       <c r="M310" t="n">
-        <v>-1.1238</v>
+        <v>-1.1236</v>
       </c>
     </row>
     <row r="311">
@@ -41296,22 +41296,22 @@
         <v>0.1872</v>
       </c>
       <c r="C311" t="n">
-        <v>-1.0254</v>
+        <v>-1.0253</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.4191</v>
+        <v>-0.419</v>
       </c>
       <c r="E311" t="n">
         <v>0.1872</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.0254</v>
+        <v>-1.0253</v>
       </c>
       <c r="G311" t="n">
         <v>0.1872</v>
       </c>
       <c r="M311" t="n">
-        <v>-1.0254</v>
+        <v>-1.0253</v>
       </c>
     </row>
     <row r="312">
@@ -41324,22 +41324,22 @@
         <v>0.1347</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.8733</v>
+        <v>-0.8732</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3693</v>
+        <v>-0.3692</v>
       </c>
       <c r="E312" t="n">
         <v>0.1347</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.8733</v>
+        <v>-0.8732</v>
       </c>
       <c r="G312" t="n">
         <v>0.1347</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.8733</v>
+        <v>-0.8732</v>
       </c>
     </row>
     <row r="313">
@@ -41352,7 +41352,7 @@
         <v>0.1736</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.5013</v>
+        <v>-0.5012</v>
       </c>
       <c r="D313" t="n">
         <v>-0.1638</v>
@@ -41361,13 +41361,13 @@
         <v>0.1736</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.5013</v>
+        <v>-0.5012</v>
       </c>
       <c r="G313" t="n">
         <v>0.1736</v>
       </c>
       <c r="M313" t="n">
-        <v>-0.5013</v>
+        <v>-0.5012</v>
       </c>
     </row>
     <row r="314">
@@ -41380,22 +41380,22 @@
         <v>0.1252</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.1283</v>
+        <v>-0.1282</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.0016</v>
+        <v>-0.0015</v>
       </c>
       <c r="E314" t="n">
         <v>0.1252</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.1283</v>
+        <v>-0.1282</v>
       </c>
       <c r="G314" t="n">
         <v>0.1252</v>
       </c>
       <c r="M314" t="n">
-        <v>-0.1283</v>
+        <v>-0.1282</v>
       </c>
     </row>
     <row r="315">
@@ -41408,7 +41408,7 @@
         <v>0.1702</v>
       </c>
       <c r="C315" t="n">
-        <v>0.1322</v>
+        <v>0.1323</v>
       </c>
       <c r="D315" t="n">
         <v>0.1512</v>
@@ -41417,13 +41417,13 @@
         <v>0.1702</v>
       </c>
       <c r="F315" t="n">
-        <v>0.1322</v>
+        <v>0.1323</v>
       </c>
       <c r="G315" t="n">
         <v>0.1702</v>
       </c>
       <c r="M315" t="n">
-        <v>0.1322</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="316">
@@ -41464,7 +41464,7 @@
         <v>0.113</v>
       </c>
       <c r="C317" t="n">
-        <v>0.7672</v>
+        <v>0.7671</v>
       </c>
       <c r="D317" t="n">
         <v>0.4401</v>
@@ -41473,13 +41473,13 @@
         <v>0.113</v>
       </c>
       <c r="F317" t="n">
-        <v>0.7672</v>
+        <v>0.7671</v>
       </c>
       <c r="G317" t="n">
         <v>0.113</v>
       </c>
       <c r="M317" t="n">
-        <v>0.7672</v>
+        <v>0.7671</v>
       </c>
     </row>
     <row r="318">
@@ -41579,7 +41579,7 @@
         <v>0.8763</v>
       </c>
       <c r="D321" t="n">
-        <v>0.5104</v>
+        <v>0.5105</v>
       </c>
       <c r="E321" t="n">
         <v>0.1446</v>
@@ -41604,7 +41604,7 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="C322" t="n">
-        <v>0.7336</v>
+        <v>0.7337</v>
       </c>
       <c r="D322" t="n">
         <v>0.3231</v>
@@ -41613,13 +41613,13 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7336</v>
+        <v>0.7337</v>
       </c>
       <c r="G322" t="n">
         <v>-0.08740000000000001</v>
       </c>
       <c r="M322" t="n">
-        <v>0.7336</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="323">
@@ -41632,22 +41632,22 @@
         <v>-0.2268</v>
       </c>
       <c r="C323" t="n">
-        <v>0.303</v>
+        <v>0.3031</v>
       </c>
       <c r="D323" t="n">
-        <v>0.0381</v>
+        <v>0.0382</v>
       </c>
       <c r="E323" t="n">
         <v>-0.2268</v>
       </c>
       <c r="F323" t="n">
-        <v>0.303</v>
+        <v>0.3031</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2268</v>
       </c>
       <c r="M323" t="n">
-        <v>0.303</v>
+        <v>0.3031</v>
       </c>
     </row>
     <row r="324">
@@ -41660,22 +41660,22 @@
         <v>-0.1762</v>
       </c>
       <c r="C324" t="n">
-        <v>0.211</v>
+        <v>0.2112</v>
       </c>
       <c r="D324" t="n">
-        <v>0.0174</v>
+        <v>0.0175</v>
       </c>
       <c r="E324" t="n">
         <v>-0.1762</v>
       </c>
       <c r="F324" t="n">
-        <v>0.211</v>
+        <v>0.2112</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1762</v>
       </c>
       <c r="M324" t="n">
-        <v>0.211</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="325">
@@ -41688,22 +41688,22 @@
         <v>-0.1809</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1908</v>
+        <v>0.191</v>
       </c>
       <c r="D325" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="E325" t="n">
         <v>-0.1809</v>
       </c>
       <c r="F325" t="n">
-        <v>0.1908</v>
+        <v>0.191</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1809</v>
       </c>
       <c r="M325" t="n">
-        <v>0.1908</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="326">
@@ -41716,22 +41716,22 @@
         <v>-0.2575</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1852</v>
+        <v>0.1854</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.0361</v>
+        <v>-0.036</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2575</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1852</v>
+        <v>0.1854</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2575</v>
       </c>
       <c r="M326" t="n">
-        <v>0.1852</v>
+        <v>0.1854</v>
       </c>
     </row>
     <row r="327">
@@ -41744,7 +41744,7 @@
         <v>-0.2413</v>
       </c>
       <c r="C327" t="n">
-        <v>0.4112</v>
+        <v>0.4113</v>
       </c>
       <c r="D327" t="n">
         <v>0.08500000000000001</v>
@@ -41753,13 +41753,13 @@
         <v>-0.2413</v>
       </c>
       <c r="F327" t="n">
-        <v>0.4112</v>
+        <v>0.4113</v>
       </c>
       <c r="G327" t="n">
         <v>-0.2413</v>
       </c>
       <c r="M327" t="n">
-        <v>0.4112</v>
+        <v>0.4113</v>
       </c>
     </row>
     <row r="328">
@@ -41772,22 +41772,22 @@
         <v>-0.2131</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4503</v>
+        <v>0.4504</v>
       </c>
       <c r="D328" t="n">
-        <v>0.1186</v>
+        <v>0.1187</v>
       </c>
       <c r="E328" t="n">
         <v>-0.2131</v>
       </c>
       <c r="F328" t="n">
-        <v>0.4503</v>
+        <v>0.4504</v>
       </c>
       <c r="G328" t="n">
         <v>-0.2131</v>
       </c>
       <c r="M328" t="n">
-        <v>0.4503</v>
+        <v>0.4504</v>
       </c>
     </row>
     <row r="329">
@@ -41800,22 +41800,22 @@
         <v>-0.1302</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0295</v>
+        <v>0.0297</v>
       </c>
       <c r="D329" t="n">
-        <v>-0.0503</v>
+        <v>-0.0502</v>
       </c>
       <c r="E329" t="n">
         <v>-0.1302</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0295</v>
+        <v>0.0297</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1302</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0295</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="330">
@@ -41828,22 +41828,22 @@
         <v>-0.2161</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1383</v>
+        <v>-0.1381</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.1772</v>
+        <v>-0.1771</v>
       </c>
       <c r="E330" t="n">
         <v>-0.2161</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1383</v>
+        <v>-0.1381</v>
       </c>
       <c r="G330" t="n">
         <v>-0.2161</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1383</v>
+        <v>-0.1381</v>
       </c>
     </row>
     <row r="331">
@@ -41856,22 +41856,22 @@
         <v>-0.168</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.1227</v>
+        <v>-0.1225</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1453</v>
+        <v>-0.1452</v>
       </c>
       <c r="E331" t="n">
         <v>-0.168</v>
       </c>
       <c r="F331" t="n">
-        <v>-0.1227</v>
+        <v>-0.1225</v>
       </c>
       <c r="G331" t="n">
         <v>-0.168</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.1227</v>
+        <v>-0.1225</v>
       </c>
     </row>
     <row r="332">
@@ -41884,22 +41884,22 @@
         <v>-0.1711</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.2561</v>
+        <v>-0.2559</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.2136</v>
+        <v>-0.2135</v>
       </c>
       <c r="E332" t="n">
         <v>-0.1711</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2561</v>
+        <v>-0.2559</v>
       </c>
       <c r="G332" t="n">
         <v>-0.1711</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.2561</v>
+        <v>-0.2559</v>
       </c>
     </row>
     <row r="333">
@@ -41912,22 +41912,22 @@
         <v>-0.1727</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.241</v>
+        <v>-0.2408</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.2069</v>
+        <v>-0.2068</v>
       </c>
       <c r="E333" t="n">
         <v>-0.1727</v>
       </c>
       <c r="F333" t="n">
-        <v>-0.241</v>
+        <v>-0.2408</v>
       </c>
       <c r="G333" t="n">
         <v>-0.1727</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.241</v>
+        <v>-0.2408</v>
       </c>
     </row>
     <row r="334">
@@ -41940,22 +41940,22 @@
         <v>-0.1202</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1157</v>
+        <v>-0.1155</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1179</v>
+        <v>-0.1178</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1157</v>
+        <v>-0.1155</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1157</v>
+        <v>-0.1155</v>
       </c>
     </row>
     <row r="335">
@@ -41968,22 +41968,22 @@
         <v>-0.0738</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2624</v>
+        <v>-0.2622</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.1681</v>
+        <v>-0.168</v>
       </c>
       <c r="E335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2624</v>
+        <v>-0.2622</v>
       </c>
       <c r="G335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2624</v>
+        <v>-0.2622</v>
       </c>
     </row>
     <row r="336">
@@ -41996,22 +41996,22 @@
         <v>-0.1217</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.2048</v>
+        <v>-0.2046</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.1632</v>
+        <v>-0.1631</v>
       </c>
       <c r="E336" t="n">
         <v>-0.1217</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.2048</v>
+        <v>-0.2046</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1217</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.2048</v>
+        <v>-0.2046</v>
       </c>
     </row>
     <row r="337">
@@ -42024,22 +42024,22 @@
         <v>-0.1717</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2841</v>
+        <v>-0.2838</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.2279</v>
+        <v>-0.2278</v>
       </c>
       <c r="E337" t="n">
         <v>-0.1717</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.2841</v>
+        <v>-0.2838</v>
       </c>
       <c r="G337" t="n">
         <v>-0.1717</v>
       </c>
       <c r="M337" t="n">
-        <v>-0.2841</v>
+        <v>-0.2838</v>
       </c>
     </row>
     <row r="338">
@@ -42052,22 +42052,22 @@
         <v>-0.1245</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2472</v>
+        <v>-0.2469</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.1858</v>
+        <v>-0.1857</v>
       </c>
       <c r="E338" t="n">
         <v>-0.1245</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2472</v>
+        <v>-0.2469</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1245</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2472</v>
+        <v>-0.2469</v>
       </c>
     </row>
     <row r="339">
@@ -42080,22 +42080,22 @@
         <v>-0.1237</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2094</v>
+        <v>-0.2092</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.1665</v>
+        <v>-0.1664</v>
       </c>
       <c r="E339" t="n">
         <v>-0.1237</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2094</v>
+        <v>-0.2092</v>
       </c>
       <c r="G339" t="n">
         <v>-0.1237</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2094</v>
+        <v>-0.2092</v>
       </c>
     </row>
     <row r="340">
@@ -42108,22 +42108,22 @@
         <v>-0.0757</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0517</v>
+        <v>0.0519</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.012</v>
+        <v>-0.0119</v>
       </c>
       <c r="E340" t="n">
         <v>-0.0757</v>
       </c>
       <c r="F340" t="n">
-        <v>0.0517</v>
+        <v>0.0519</v>
       </c>
       <c r="G340" t="n">
         <v>-0.0757</v>
       </c>
       <c r="M340" t="n">
-        <v>0.0517</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="341">
@@ -42136,22 +42136,22 @@
         <v>-0.1691</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1762</v>
+        <v>0.1764</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0036</v>
+        <v>0.0037</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1691</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1762</v>
+        <v>0.1764</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1691</v>
       </c>
       <c r="M341" t="n">
-        <v>0.1762</v>
+        <v>0.1764</v>
       </c>
     </row>
     <row r="342">
@@ -42164,22 +42164,22 @@
         <v>-0.1213</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2255</v>
+        <v>0.2256</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0521</v>
+        <v>0.0522</v>
       </c>
       <c r="E342" t="n">
         <v>-0.1213</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2255</v>
+        <v>0.2256</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1213</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2255</v>
+        <v>0.2256</v>
       </c>
     </row>
     <row r="343">
@@ -42192,22 +42192,22 @@
         <v>-0.1218</v>
       </c>
       <c r="C343" t="n">
-        <v>0.3411</v>
+        <v>0.3413</v>
       </c>
       <c r="D343" t="n">
-        <v>0.1097</v>
+        <v>0.1098</v>
       </c>
       <c r="E343" t="n">
         <v>-0.1218</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3411</v>
+        <v>0.3413</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1218</v>
       </c>
       <c r="M343" t="n">
-        <v>0.3411</v>
+        <v>0.3413</v>
       </c>
     </row>
     <row r="344">
@@ -42220,7 +42220,7 @@
         <v>-0.1226</v>
       </c>
       <c r="C344" t="n">
-        <v>0.5609</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D344" t="n">
         <v>0.2192</v>
@@ -42229,13 +42229,13 @@
         <v>-0.1226</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5609</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G344" t="n">
         <v>-0.1226</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5609</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="345">
@@ -42248,7 +42248,7 @@
         <v>-0.1663</v>
       </c>
       <c r="C345" t="n">
-        <v>0.445</v>
+        <v>0.4452</v>
       </c>
       <c r="D345" t="n">
         <v>0.1394</v>
@@ -42257,13 +42257,13 @@
         <v>-0.1663</v>
       </c>
       <c r="F345" t="n">
-        <v>0.445</v>
+        <v>0.4452</v>
       </c>
       <c r="G345" t="n">
         <v>-0.1663</v>
       </c>
       <c r="M345" t="n">
-        <v>0.445</v>
+        <v>0.4452</v>
       </c>
     </row>
     <row r="346">
@@ -42276,7 +42276,7 @@
         <v>-0.1668</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5245</v>
+        <v>0.5246</v>
       </c>
       <c r="D346" t="n">
         <v>0.1789</v>
@@ -42285,13 +42285,13 @@
         <v>-0.1668</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5245</v>
+        <v>0.5246</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1668</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5245</v>
+        <v>0.5246</v>
       </c>
     </row>
     <row r="347">
@@ -42304,7 +42304,7 @@
         <v>-0.1669</v>
       </c>
       <c r="C347" t="n">
-        <v>0.351</v>
+        <v>0.3512</v>
       </c>
       <c r="D347" t="n">
         <v>0.0921</v>
@@ -42313,13 +42313,13 @@
         <v>-0.1669</v>
       </c>
       <c r="F347" t="n">
-        <v>0.351</v>
+        <v>0.3512</v>
       </c>
       <c r="G347" t="n">
         <v>-0.1669</v>
       </c>
       <c r="M347" t="n">
-        <v>0.351</v>
+        <v>0.3512</v>
       </c>
     </row>
     <row r="348">
@@ -42332,22 +42332,22 @@
         <v>-0.1199</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5125</v>
+        <v>0.5127</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1963</v>
+        <v>0.1964</v>
       </c>
       <c r="E348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5125</v>
+        <v>0.5127</v>
       </c>
       <c r="G348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5125</v>
+        <v>0.5127</v>
       </c>
     </row>
     <row r="349">
@@ -42360,22 +42360,22 @@
         <v>-0.0725</v>
       </c>
       <c r="C349" t="n">
-        <v>0.5085</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="D349" t="n">
-        <v>0.218</v>
+        <v>0.2181</v>
       </c>
       <c r="E349" t="n">
         <v>-0.0725</v>
       </c>
       <c r="F349" t="n">
-        <v>0.5085</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="G349" t="n">
         <v>-0.0725</v>
       </c>
       <c r="M349" t="n">
-        <v>0.5085</v>
+        <v>0.5086000000000001</v>
       </c>
     </row>
     <row r="350">
@@ -42556,22 +42556,22 @@
         <v>0.1672</v>
       </c>
       <c r="C356" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
       <c r="D356" t="n">
-        <v>0.2354</v>
+        <v>0.2355</v>
       </c>
       <c r="E356" t="n">
         <v>0.1672</v>
       </c>
       <c r="F356" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
       <c r="G356" t="n">
         <v>0.1672</v>
       </c>
       <c r="M356" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
     </row>
     <row r="357">
@@ -42584,22 +42584,22 @@
         <v>0.214</v>
       </c>
       <c r="C357" t="n">
-        <v>0.1632</v>
+        <v>0.1633</v>
       </c>
       <c r="D357" t="n">
-        <v>0.1886</v>
+        <v>0.1887</v>
       </c>
       <c r="E357" t="n">
         <v>0.214</v>
       </c>
       <c r="F357" t="n">
-        <v>0.1632</v>
+        <v>0.1633</v>
       </c>
       <c r="G357" t="n">
         <v>0.214</v>
       </c>
       <c r="M357" t="n">
-        <v>0.1632</v>
+        <v>0.1633</v>
       </c>
     </row>
     <row r="358">
@@ -42668,7 +42668,7 @@
         <v>0.213</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0184</v>
+        <v>-0.0183</v>
       </c>
       <c r="D360" t="n">
         <v>0.0973</v>
@@ -42677,13 +42677,13 @@
         <v>0.213</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.0184</v>
+        <v>-0.0183</v>
       </c>
       <c r="G360" t="n">
         <v>0.213</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.0184</v>
+        <v>-0.0183</v>
       </c>
     </row>
     <row r="361">
@@ -42724,7 +42724,7 @@
         <v>-0.5446</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
       <c r="D362" t="n">
         <v>-0.2618</v>
@@ -42733,7 +42733,7 @@
         <v>-0.5446</v>
       </c>
       <c r="F362" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
       <c r="G362" t="n">
         <v>0.2137</v>
@@ -42742,7 +42742,7 @@
         <v>-1.3029</v>
       </c>
       <c r="M362" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="363">
@@ -42755,7 +42755,7 @@
         <v>-0.502</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.2219</v>
+        <v>-0.2218</v>
       </c>
       <c r="D363" t="n">
         <v>-0.3619</v>
@@ -42764,7 +42764,7 @@
         <v>-0.502</v>
       </c>
       <c r="F363" t="n">
-        <v>-0.2219</v>
+        <v>-0.2218</v>
       </c>
       <c r="G363" t="n">
         <v>0.262</v>
@@ -42773,7 +42773,7 @@
         <v>-1.2659</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.2219</v>
+        <v>-0.2218</v>
       </c>
     </row>
     <row r="364">
@@ -42789,7 +42789,7 @@
         <v>-0.06759999999999999</v>
       </c>
       <c r="D364" t="n">
-        <v>-0.2758</v>
+        <v>-0.2757</v>
       </c>
       <c r="E364" t="n">
         <v>-0.4839</v>
@@ -42817,16 +42817,16 @@
         <v>-0.5301</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.2144</v>
+        <v>-0.2143</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.3723</v>
+        <v>-0.3722</v>
       </c>
       <c r="E365" t="n">
         <v>-0.5301</v>
       </c>
       <c r="F365" t="n">
-        <v>-0.2144</v>
+        <v>-0.2143</v>
       </c>
       <c r="G365" t="n">
         <v>0.1656</v>
@@ -42835,7 +42835,7 @@
         <v>-1.2258</v>
       </c>
       <c r="M365" t="n">
-        <v>-0.2144</v>
+        <v>-0.2143</v>
       </c>
     </row>
     <row r="366">
@@ -42848,7 +42848,7 @@
         <v>-0.445</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.2351</v>
+        <v>-0.2349</v>
       </c>
       <c r="D366" t="n">
         <v>-0.34</v>
@@ -42857,7 +42857,7 @@
         <v>-0.445</v>
       </c>
       <c r="F366" t="n">
-        <v>-0.2351</v>
+        <v>-0.2349</v>
       </c>
       <c r="G366" t="n">
         <v>0.117</v>
@@ -42866,7 +42866,7 @@
         <v>-1.0071</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.2351</v>
+        <v>-0.2349</v>
       </c>
     </row>
     <row r="367">
@@ -42879,7 +42879,7 @@
         <v>-0.4673</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
       <c r="D367" t="n">
         <v>-0.2865</v>
@@ -42888,7 +42888,7 @@
         <v>-0.4673</v>
       </c>
       <c r="F367" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
       <c r="G367" t="n">
         <v>0.2104</v>
@@ -42897,7 +42897,7 @@
         <v>-1.1451</v>
       </c>
       <c r="M367" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
     </row>
     <row r="368">
@@ -42910,16 +42910,16 @@
         <v>-0.4774</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.1074</v>
+        <v>-0.1073</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.2924</v>
+        <v>-0.2923</v>
       </c>
       <c r="E368" t="n">
         <v>-0.4774</v>
       </c>
       <c r="F368" t="n">
-        <v>-0.1074</v>
+        <v>-0.1073</v>
       </c>
       <c r="G368" t="n">
         <v>0.1595</v>
@@ -42928,7 +42928,7 @@
         <v>-1.1143</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.1074</v>
+        <v>-0.1073</v>
       </c>
     </row>
     <row r="369">
@@ -42941,16 +42941,16 @@
         <v>-0.4511</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.4027</v>
+        <v>-0.4026</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.4269</v>
+        <v>-0.4268</v>
       </c>
       <c r="E369" t="n">
         <v>-0.4511</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.4027</v>
+        <v>-0.4026</v>
       </c>
       <c r="G369" t="n">
         <v>0.1627</v>
@@ -42959,7 +42959,7 @@
         <v>-1.065</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.4027</v>
+        <v>-0.4026</v>
       </c>
     </row>
     <row r="370">
@@ -42972,16 +42972,16 @@
         <v>-0.4067</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3745</v>
+        <v>-0.3743</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.3906</v>
+        <v>-0.3905</v>
       </c>
       <c r="E370" t="n">
         <v>-0.4067</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3745</v>
+        <v>-0.3743</v>
       </c>
       <c r="G370" t="n">
         <v>0.2599</v>
@@ -42990,7 +42990,7 @@
         <v>-1.0733</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3745</v>
+        <v>-0.3743</v>
       </c>
     </row>
     <row r="371">
@@ -43003,16 +43003,16 @@
         <v>-0.4545</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.3085</v>
+        <v>-0.3083</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.3815</v>
+        <v>-0.3814</v>
       </c>
       <c r="E371" t="n">
         <v>-0.4545</v>
       </c>
       <c r="F371" t="n">
-        <v>-0.3085</v>
+        <v>-0.3083</v>
       </c>
       <c r="G371" t="n">
         <v>0.2118</v>
@@ -43021,7 +43021,7 @@
         <v>-1.1208</v>
       </c>
       <c r="M371" t="n">
-        <v>-0.3085</v>
+        <v>-0.3083</v>
       </c>
     </row>
     <row r="372">
@@ -43034,16 +43034,16 @@
         <v>-0.5501</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3361</v>
+        <v>-0.3359</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.4431</v>
+        <v>-0.443</v>
       </c>
       <c r="E372" t="n">
         <v>-0.5501</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3361</v>
+        <v>-0.3359</v>
       </c>
       <c r="G372" t="n">
         <v>0.167</v>
@@ -43052,7 +43052,7 @@
         <v>-1.2673</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3361</v>
+        <v>-0.3359</v>
       </c>
     </row>
     <row r="373">
@@ -43065,16 +43065,16 @@
         <v>-0.5384</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2951</v>
+        <v>-0.2949</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.4167</v>
+        <v>-0.4166</v>
       </c>
       <c r="E373" t="n">
         <v>-0.5384</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2951</v>
+        <v>-0.2949</v>
       </c>
       <c r="G373" t="n">
         <v>0.1675</v>
@@ -43083,7 +43083,7 @@
         <v>-1.2442</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2951</v>
+        <v>-0.2949</v>
       </c>
     </row>
     <row r="374">
@@ -43126,7 +43126,7 @@
         <v>1.051</v>
       </c>
       <c r="M374" t="n">
-        <v>0.8188</v>
+        <v>0.8189</v>
       </c>
     </row>
     <row r="375">
@@ -43169,7 +43169,7 @@
         <v>1.0309</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8123</v>
+        <v>0.8124</v>
       </c>
     </row>
     <row r="376">
@@ -43182,7 +43182,7 @@
         <v>-0.6566</v>
       </c>
       <c r="C376" t="n">
-        <v>0.3869</v>
+        <v>0.387</v>
       </c>
       <c r="D376" t="n">
         <v>-0.1348</v>
@@ -43191,7 +43191,7 @@
         <v>-0.6566</v>
       </c>
       <c r="F376" t="n">
-        <v>0.3869</v>
+        <v>0.387</v>
       </c>
       <c r="G376" t="n">
         <v>0.2151</v>
@@ -43255,7 +43255,7 @@
         <v>0.9013</v>
       </c>
       <c r="M377" t="n">
-        <v>0.8321</v>
+        <v>0.8322000000000001</v>
       </c>
     </row>
     <row r="378">
@@ -43298,7 +43298,7 @@
         <v>0.7295</v>
       </c>
       <c r="M378" t="n">
-        <v>0.7488</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="379">
@@ -43341,7 +43341,7 @@
         <v>0.7169</v>
       </c>
       <c r="M379" t="n">
-        <v>0.7417</v>
+        <v>0.7418</v>
       </c>
     </row>
     <row r="380">
@@ -43427,7 +43427,7 @@
         <v>0.4704</v>
       </c>
       <c r="M381" t="n">
-        <v>0.7165</v>
+        <v>0.7166</v>
       </c>
     </row>
     <row r="382">
@@ -43483,7 +43483,7 @@
         <v>-0.4242</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.079</v>
+        <v>-0.0789</v>
       </c>
       <c r="D383" t="n">
         <v>-0.2516</v>
@@ -43492,7 +43492,7 @@
         <v>-0.4242</v>
       </c>
       <c r="F383" t="n">
-        <v>-0.079</v>
+        <v>-0.0789</v>
       </c>
       <c r="G383" t="n">
         <v>0.2022</v>
@@ -43556,7 +43556,7 @@
         <v>0.2187</v>
       </c>
       <c r="M384" t="n">
-        <v>0.7523</v>
+        <v>0.7524</v>
       </c>
     </row>
     <row r="385">
@@ -43612,7 +43612,7 @@
         <v>-0.4496</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.272</v>
+        <v>-0.2719</v>
       </c>
       <c r="D386" t="n">
         <v>-0.3608</v>
@@ -43621,7 +43621,7 @@
         <v>-0.4496</v>
       </c>
       <c r="F386" t="n">
-        <v>-0.272</v>
+        <v>-0.2719</v>
       </c>
       <c r="G386" t="n">
         <v>0.1998</v>
@@ -43685,7 +43685,7 @@
         <v>-0.1281</v>
       </c>
       <c r="M387" t="n">
-        <v>0.8375</v>
+        <v>0.8376</v>
       </c>
     </row>
     <row r="388">
@@ -43943,7 +43943,7 @@
         <v>-0.652</v>
       </c>
       <c r="M393" t="n">
-        <v>0.4013</v>
+        <v>0.4014</v>
       </c>
     </row>
     <row r="394">
@@ -43986,7 +43986,7 @@
         <v>-0.6529</v>
       </c>
       <c r="M394" t="n">
-        <v>0.3742</v>
+        <v>0.3743</v>
       </c>
     </row>
     <row r="395">
@@ -44029,7 +44029,7 @@
         <v>-0.8083</v>
       </c>
       <c r="M395" t="n">
-        <v>0.3636</v>
+        <v>0.3637</v>
       </c>
     </row>
     <row r="396">
@@ -44045,7 +44045,7 @@
         <v>-0.6746</v>
       </c>
       <c r="D396" t="n">
-        <v>-0.793</v>
+        <v>-0.7929</v>
       </c>
       <c r="E396" t="n">
         <v>-0.9113</v>
@@ -44171,7 +44171,7 @@
         <v>-0.8489</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.7147</v>
+        <v>-0.7146</v>
       </c>
       <c r="D399" t="n">
         <v>-0.7818000000000001</v>
@@ -44180,7 +44180,7 @@
         <v>-0.8489</v>
       </c>
       <c r="F399" t="n">
-        <v>-0.7147</v>
+        <v>-0.7146</v>
       </c>
       <c r="G399" t="n">
         <v>-0.0011</v>
@@ -44260,7 +44260,7 @@
         <v>-0.6975</v>
       </c>
       <c r="D401" t="n">
-        <v>-0.7339</v>
+        <v>-0.7338</v>
       </c>
       <c r="E401" t="n">
         <v>-0.7702</v>
@@ -44416,7 +44416,7 @@
         <v>-1.671</v>
       </c>
       <c r="M404" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row r="405">
@@ -44472,7 +44472,7 @@
         <v>-0.482</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.84</v>
+        <v>-0.8399</v>
       </c>
       <c r="D406" t="n">
         <v>-0.661</v>
@@ -44481,7 +44481,7 @@
         <v>-0.482</v>
       </c>
       <c r="F406" t="n">
-        <v>-0.84</v>
+        <v>-0.8399</v>
       </c>
       <c r="G406" t="n">
         <v>-0.0582</v>
@@ -44588,7 +44588,7 @@
         <v>-1.9322</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.1736</v>
+        <v>-0.1735</v>
       </c>
     </row>
     <row r="409">
@@ -44674,7 +44674,7 @@
         <v>-2.128</v>
       </c>
       <c r="M410" t="n">
-        <v>-0.3736</v>
+        <v>-0.3735</v>
       </c>
     </row>
     <row r="411">
@@ -44687,7 +44687,7 @@
         <v>-0.2403</v>
       </c>
       <c r="C411" t="n">
-        <v>-1.0753</v>
+        <v>-1.0752</v>
       </c>
       <c r="D411" t="n">
         <v>-0.6578000000000001</v>
@@ -44696,7 +44696,7 @@
         <v>-0.2403</v>
       </c>
       <c r="F411" t="n">
-        <v>-1.0753</v>
+        <v>-1.0752</v>
       </c>
       <c r="G411" t="n">
         <v>0.5134</v>
@@ -44717,7 +44717,7 @@
         <v>-2.2831</v>
       </c>
       <c r="M411" t="n">
-        <v>-0.3669</v>
+        <v>-0.3668</v>
       </c>
     </row>
     <row r="412">
@@ -44760,7 +44760,7 @@
         <v>-2.3123</v>
       </c>
       <c r="M412" t="n">
-        <v>-0.6059</v>
+        <v>-0.6058</v>
       </c>
     </row>
     <row r="413">
@@ -44803,7 +44803,7 @@
         <v>-2.4555</v>
       </c>
       <c r="M413" t="n">
-        <v>-0.5271</v>
+        <v>-0.527</v>
       </c>
     </row>
     <row r="414">
@@ -44862,7 +44862,7 @@
         <v>-1.2376</v>
       </c>
       <c r="D415" t="n">
-        <v>-0.6412</v>
+        <v>-0.6411</v>
       </c>
       <c r="E415" t="n">
         <v>-0.0447</v>
@@ -44889,7 +44889,7 @@
         <v>-2.6249</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.622</v>
+        <v>-0.6219</v>
       </c>
     </row>
     <row r="416">
@@ -44932,7 +44932,7 @@
         <v>-2.7787</v>
       </c>
       <c r="M416" t="n">
-        <v>-0.6715</v>
+        <v>-0.6714</v>
       </c>
     </row>
     <row r="417">
@@ -45077,7 +45077,7 @@
         <v>-1.2631</v>
       </c>
       <c r="D420" t="n">
-        <v>-0.7437</v>
+        <v>-0.7436</v>
       </c>
       <c r="E420" t="n">
         <v>-0.2242</v>
@@ -45120,7 +45120,7 @@
         <v>-1.1211</v>
       </c>
       <c r="D421" t="n">
-        <v>-0.7655</v>
+        <v>-0.7654</v>
       </c>
       <c r="E421" t="n">
         <v>-0.4098</v>
@@ -45147,7 +45147,7 @@
         <v>-2.5794</v>
       </c>
       <c r="M421" t="n">
-        <v>-0.4442</v>
+        <v>-0.4441</v>
       </c>
     </row>
     <row r="422">
@@ -45362,7 +45362,7 @@
         <v>-0.7655</v>
       </c>
       <c r="M426" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="427">
@@ -45448,7 +45448,7 @@
         <v>-0.3802</v>
       </c>
       <c r="M428" t="n">
-        <v>0.6787</v>
+        <v>0.6788</v>
       </c>
     </row>
     <row r="429">
@@ -45491,7 +45491,7 @@
         <v>-0.3184</v>
       </c>
       <c r="M429" t="n">
-        <v>0.5555</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="430">
@@ -45534,7 +45534,7 @@
         <v>-0.2206</v>
       </c>
       <c r="M430" t="n">
-        <v>0.5225</v>
+        <v>0.5226</v>
       </c>
     </row>
     <row r="431">
@@ -45547,7 +45547,7 @@
         <v>-0.7841</v>
       </c>
       <c r="C431" t="n">
-        <v>0.0808</v>
+        <v>0.0809</v>
       </c>
       <c r="D431" t="n">
         <v>-0.3516</v>
@@ -45556,7 +45556,7 @@
         <v>-0.7841</v>
       </c>
       <c r="F431" t="n">
-        <v>0.0808</v>
+        <v>0.0809</v>
       </c>
       <c r="G431" t="n">
         <v>-0.8386</v>
@@ -45590,7 +45590,7 @@
         <v>-0.7226</v>
       </c>
       <c r="C432" t="n">
-        <v>0.0871</v>
+        <v>0.0872</v>
       </c>
       <c r="D432" t="n">
         <v>-0.3177</v>
@@ -45599,7 +45599,7 @@
         <v>-0.7226</v>
       </c>
       <c r="F432" t="n">
-        <v>0.0871</v>
+        <v>0.0872</v>
       </c>
       <c r="G432" t="n">
         <v>-0.5634</v>
@@ -45620,7 +45620,7 @@
         <v>-0.1602</v>
       </c>
       <c r="M432" t="n">
-        <v>0.4565</v>
+        <v>0.4566</v>
       </c>
     </row>
     <row r="433">
@@ -45679,7 +45679,7 @@
         <v>0.1466</v>
       </c>
       <c r="D434" t="n">
-        <v>-0.2082</v>
+        <v>-0.2081</v>
       </c>
       <c r="E434" t="n">
         <v>-0.5629</v>
@@ -45749,7 +45749,7 @@
         <v>-0.0399</v>
       </c>
       <c r="M435" t="n">
-        <v>0.408</v>
+        <v>0.4081</v>
       </c>
     </row>
     <row r="436">
@@ -45792,7 +45792,7 @@
         <v>0.0902</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4158</v>
+        <v>0.4159</v>
       </c>
     </row>
     <row r="437">
@@ -45805,7 +45805,7 @@
         <v>-0.641</v>
       </c>
       <c r="C437" t="n">
-        <v>0.2235</v>
+        <v>0.2236</v>
       </c>
       <c r="D437" t="n">
         <v>-0.2087</v>
@@ -45814,7 +45814,7 @@
         <v>-0.641</v>
       </c>
       <c r="F437" t="n">
-        <v>0.2235</v>
+        <v>0.2236</v>
       </c>
       <c r="G437" t="n">
         <v>-0.314</v>
@@ -45921,7 +45921,7 @@
         <v>0.2486</v>
       </c>
       <c r="M439" t="n">
-        <v>0.3235</v>
+        <v>0.3236</v>
       </c>
     </row>
     <row r="440">
@@ -46007,7 +46007,7 @@
         <v>0.2186</v>
       </c>
       <c r="M441" t="n">
-        <v>0.5135</v>
+        <v>0.5135999999999999</v>
       </c>
     </row>
     <row r="442">
@@ -46020,7 +46020,7 @@
         <v>-0.7393999999999999</v>
       </c>
       <c r="C442" t="n">
-        <v>0.2544</v>
+        <v>0.2545</v>
       </c>
       <c r="D442" t="n">
         <v>-0.2425</v>
@@ -46029,7 +46029,7 @@
         <v>-0.7393999999999999</v>
       </c>
       <c r="F442" t="n">
-        <v>0.2544</v>
+        <v>0.2545</v>
       </c>
       <c r="G442" t="n">
         <v>-0.3608</v>
@@ -46050,7 +46050,7 @@
         <v>0.2863</v>
       </c>
       <c r="M442" t="n">
-        <v>0.2319</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="443">
@@ -46093,7 +46093,7 @@
         <v>0.3248</v>
       </c>
       <c r="M443" t="n">
-        <v>0.2766</v>
+        <v>0.2767</v>
       </c>
     </row>
     <row r="444">
@@ -46106,7 +46106,7 @@
         <v>-0.609</v>
       </c>
       <c r="C444" t="n">
-        <v>0.2764</v>
+        <v>0.2765</v>
       </c>
       <c r="D444" t="n">
         <v>-0.1663</v>
@@ -46115,7 +46115,7 @@
         <v>-0.609</v>
       </c>
       <c r="F444" t="n">
-        <v>0.2764</v>
+        <v>0.2765</v>
       </c>
       <c r="G444" t="n">
         <v>-0.1725</v>
@@ -46152,7 +46152,7 @@
         <v>0.2383</v>
       </c>
       <c r="D445" t="n">
-        <v>-0.2138</v>
+        <v>-0.2137</v>
       </c>
       <c r="E445" t="n">
         <v>-0.6657999999999999</v>
@@ -46179,7 +46179,7 @@
         <v>0.1903</v>
       </c>
       <c r="M445" t="n">
-        <v>0.1828</v>
+        <v>0.1829</v>
       </c>
     </row>
     <row r="446">
@@ -46222,7 +46222,7 @@
         <v>0.2387</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2388</v>
+        <v>0.2389</v>
       </c>
     </row>
     <row r="447">
@@ -46351,7 +46351,7 @@
         <v>0.1753</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1532</v>
+        <v>0.1533</v>
       </c>
     </row>
     <row r="450">
@@ -46437,7 +46437,7 @@
         <v>0.1722</v>
       </c>
       <c r="M451" t="n">
-        <v>0.1678</v>
+        <v>0.1679</v>
       </c>
     </row>
     <row r="452">
@@ -46480,7 +46480,7 @@
         <v>0.1773</v>
       </c>
       <c r="M452" t="n">
-        <v>0.1851</v>
+        <v>0.1852</v>
       </c>
     </row>
     <row r="453">
@@ -46523,7 +46523,7 @@
         <v>0.1417</v>
       </c>
       <c r="M453" t="n">
-        <v>0.1963</v>
+        <v>0.1964</v>
       </c>
     </row>
     <row r="454">
@@ -46622,7 +46622,7 @@
         <v>-0.3844</v>
       </c>
       <c r="C456" t="n">
-        <v>0.3133</v>
+        <v>0.3134</v>
       </c>
       <c r="D456" t="n">
         <v>-0.0355</v>
@@ -46631,7 +46631,7 @@
         <v>-0.3844</v>
       </c>
       <c r="F456" t="n">
-        <v>0.3133</v>
+        <v>0.3134</v>
       </c>
       <c r="G456" t="n">
         <v>0.1237</v>
@@ -46781,7 +46781,7 @@
         <v>0.2417</v>
       </c>
       <c r="M459" t="n">
-        <v>0.4024</v>
+        <v>0.4025</v>
       </c>
     </row>
     <row r="460">
@@ -46824,7 +46824,7 @@
         <v>0.3094</v>
       </c>
       <c r="M460" t="n">
-        <v>0.3716</v>
+        <v>0.3717</v>
       </c>
     </row>
     <row r="461">
@@ -46837,7 +46837,7 @@
         <v>-0.4052</v>
       </c>
       <c r="C461" t="n">
-        <v>0.2693</v>
+        <v>0.2694</v>
       </c>
       <c r="D461" t="n">
         <v>-0.0679</v>
@@ -46846,7 +46846,7 @@
         <v>-0.4052</v>
       </c>
       <c r="F461" t="n">
-        <v>0.2693</v>
+        <v>0.2694</v>
       </c>
       <c r="G461" t="n">
         <v>0.3214</v>
@@ -46867,7 +46867,7 @@
         <v>0.3755</v>
       </c>
       <c r="M461" t="n">
-        <v>0.3927</v>
+        <v>0.3928</v>
       </c>
     </row>
     <row r="462">
@@ -46910,7 +46910,7 @@
         <v>0.3007</v>
       </c>
       <c r="M462" t="n">
-        <v>0.3901</v>
+        <v>0.3902</v>
       </c>
     </row>
     <row r="463">
@@ -46923,7 +46923,7 @@
         <v>-0.4251</v>
       </c>
       <c r="C463" t="n">
-        <v>0.2219</v>
+        <v>0.222</v>
       </c>
       <c r="D463" t="n">
         <v>-0.1016</v>
@@ -46932,7 +46932,7 @@
         <v>-0.4251</v>
       </c>
       <c r="F463" t="n">
-        <v>0.2219</v>
+        <v>0.222</v>
       </c>
       <c r="G463" t="n">
         <v>0.127</v>
@@ -46953,7 +46953,7 @@
         <v>0.4357</v>
       </c>
       <c r="M463" t="n">
-        <v>0.3317</v>
+        <v>0.3318</v>
       </c>
     </row>
     <row r="464">
@@ -46996,7 +46996,7 @@
         <v>0.3646</v>
       </c>
       <c r="M464" t="n">
-        <v>0.3705</v>
+        <v>0.3706</v>
       </c>
     </row>
     <row r="465">
@@ -47009,7 +47009,7 @@
         <v>-0.4815</v>
       </c>
       <c r="C465" t="n">
-        <v>0.3583</v>
+        <v>0.3584</v>
       </c>
       <c r="D465" t="n">
         <v>-0.0616</v>
@@ -47018,7 +47018,7 @@
         <v>-0.4815</v>
       </c>
       <c r="F465" t="n">
-        <v>0.3583</v>
+        <v>0.3584</v>
       </c>
       <c r="G465" t="n">
         <v>0.1255</v>
@@ -47039,7 +47039,7 @@
         <v>0.4487</v>
       </c>
       <c r="M465" t="n">
-        <v>0.3801</v>
+        <v>0.3802</v>
       </c>
     </row>
     <row r="466">
@@ -47082,7 +47082,7 @@
         <v>0.4637</v>
       </c>
       <c r="M466" t="n">
-        <v>0.3232</v>
+        <v>0.3233</v>
       </c>
     </row>
     <row r="467">
@@ -47125,7 +47125,7 @@
         <v>0.4398</v>
       </c>
       <c r="M467" t="n">
-        <v>0.3788</v>
+        <v>0.3789</v>
       </c>
     </row>
     <row r="468">
@@ -47141,7 +47141,7 @@
         <v>0.5625</v>
       </c>
       <c r="D468" t="n">
-        <v>0.1066</v>
+        <v>0.1067</v>
       </c>
       <c r="E468" t="n">
         <v>-0.3492</v>
@@ -47168,7 +47168,7 @@
         <v>0.5655</v>
       </c>
       <c r="M468" t="n">
-        <v>0.3634</v>
+        <v>0.3635</v>
       </c>
     </row>
     <row r="469">
@@ -47181,7 +47181,7 @@
         <v>-0.1419</v>
       </c>
       <c r="C469" t="n">
-        <v>0.6044</v>
+        <v>0.6045</v>
       </c>
       <c r="D469" t="n">
         <v>0.2313</v>
@@ -47190,7 +47190,7 @@
         <v>-0.1419</v>
       </c>
       <c r="F469" t="n">
-        <v>0.6044</v>
+        <v>0.6045</v>
       </c>
       <c r="G469" t="n">
         <v>0.5668</v>
@@ -47211,7 +47211,7 @@
         <v>0.4968</v>
       </c>
       <c r="M469" t="n">
-        <v>0.3922</v>
+        <v>0.3923</v>
       </c>
     </row>
     <row r="470">
@@ -47224,7 +47224,7 @@
         <v>-0.0474</v>
       </c>
       <c r="C470" t="n">
-        <v>0.6698</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="D470" t="n">
         <v>0.3112</v>
@@ -47233,7 +47233,7 @@
         <v>-0.0474</v>
       </c>
       <c r="F470" t="n">
-        <v>0.6698</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="G470" t="n">
         <v>0.0795</v>
@@ -47254,7 +47254,7 @@
         <v>0.5353</v>
       </c>
       <c r="M470" t="n">
-        <v>0.3814</v>
+        <v>0.3815</v>
       </c>
     </row>
     <row r="471">
@@ -47297,7 +47297,7 @@
         <v>0.6042999999999999</v>
       </c>
       <c r="M471" t="n">
-        <v>0.3017</v>
+        <v>0.3018</v>
       </c>
     </row>
     <row r="472">
@@ -47340,7 +47340,7 @@
         <v>0.5993000000000001</v>
       </c>
       <c r="M472" t="n">
-        <v>0.2832</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="473">
@@ -47396,16 +47396,16 @@
         <v>0.4419</v>
       </c>
       <c r="C474" t="n">
-        <v>0.9523</v>
+        <v>0.9524</v>
       </c>
       <c r="D474" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6972</v>
       </c>
       <c r="E474" t="n">
         <v>0.4419</v>
       </c>
       <c r="F474" t="n">
-        <v>0.9523</v>
+        <v>0.9524</v>
       </c>
       <c r="G474" t="n">
         <v>0.2241</v>
@@ -47512,7 +47512,7 @@
         <v>0.6837</v>
       </c>
       <c r="M476" t="n">
-        <v>0.3114</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="477">
@@ -47555,7 +47555,7 @@
         <v>0.576</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2778</v>
+        <v>0.2779</v>
       </c>
     </row>
     <row r="478">
@@ -47568,7 +47568,7 @@
         <v>0.71</v>
       </c>
       <c r="C478" t="n">
-        <v>1.112</v>
+        <v>1.1121</v>
       </c>
       <c r="D478" t="n">
         <v>0.911</v>
@@ -47577,7 +47577,7 @@
         <v>0.71</v>
       </c>
       <c r="F478" t="n">
-        <v>1.112</v>
+        <v>1.1121</v>
       </c>
       <c r="G478" t="n">
         <v>0.52</v>
@@ -47598,7 +47598,7 @@
         <v>0.6835</v>
       </c>
       <c r="M478" t="n">
-        <v>0.2116</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="479">
@@ -47641,7 +47641,7 @@
         <v>0.6918</v>
       </c>
       <c r="M479" t="n">
-        <v>0.2566</v>
+        <v>0.2567</v>
       </c>
     </row>
     <row r="480">
@@ -47684,7 +47684,7 @@
         <v>0.5768</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2469</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="481">
@@ -47700,7 +47700,7 @@
         <v>1.2857</v>
       </c>
       <c r="D481" t="n">
-        <v>1.1875</v>
+        <v>1.1876</v>
       </c>
       <c r="E481" t="n">
         <v>1.0894</v>
@@ -47727,7 +47727,7 @@
         <v>0.6427</v>
       </c>
       <c r="M481" t="n">
-        <v>0.2377</v>
+        <v>0.2378</v>
       </c>
     </row>
     <row r="482">
@@ -47770,7 +47770,7 @@
         <v>0.6854</v>
       </c>
       <c r="M482" t="n">
-        <v>0.2426</v>
+        <v>0.2427</v>
       </c>
     </row>
     <row r="483">
@@ -47829,7 +47829,7 @@
         <v>1.143</v>
       </c>
       <c r="D484" t="n">
-        <v>1.0397</v>
+        <v>1.0398</v>
       </c>
       <c r="E484" t="n">
         <v>0.9365</v>
@@ -47899,7 +47899,7 @@
         <v>0.6611</v>
       </c>
       <c r="M485" t="n">
-        <v>0.2088</v>
+        <v>0.2089</v>
       </c>
     </row>
     <row r="486">
@@ -47955,7 +47955,7 @@
         <v>0.9476</v>
       </c>
       <c r="C487" t="n">
-        <v>0.963</v>
+        <v>0.9631</v>
       </c>
       <c r="D487" t="n">
         <v>0.9553</v>
@@ -47964,7 +47964,7 @@
         <v>0.9476</v>
       </c>
       <c r="F487" t="n">
-        <v>0.963</v>
+        <v>0.9631</v>
       </c>
       <c r="G487" t="n">
         <v>1.7936</v>
@@ -47985,7 +47985,7 @@
         <v>0.5768</v>
       </c>
       <c r="M487" t="n">
-        <v>0.2594</v>
+        <v>0.2595</v>
       </c>
     </row>
     <row r="488">
@@ -48028,7 +48028,7 @@
         <v>0.5834</v>
       </c>
       <c r="M488" t="n">
-        <v>0.2459</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="489">
@@ -48071,7 +48071,7 @@
         <v>0.5085</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2653</v>
+        <v>0.2654</v>
       </c>
     </row>
     <row r="490">
@@ -48114,7 +48114,7 @@
         <v>0.5518</v>
       </c>
       <c r="M490" t="n">
-        <v>0.2423</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="491">
@@ -48157,7 +48157,7 @@
         <v>0.5944</v>
       </c>
       <c r="M491" t="n">
-        <v>0.241</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="492">
@@ -48200,7 +48200,7 @@
         <v>0.5242</v>
       </c>
       <c r="M492" t="n">
-        <v>0.3176</v>
+        <v>0.3177</v>
       </c>
     </row>
     <row r="493">
@@ -48213,7 +48213,7 @@
         <v>0.7083</v>
       </c>
       <c r="C493" t="n">
-        <v>0.8658</v>
+        <v>0.8659</v>
       </c>
       <c r="D493" t="n">
         <v>0.7871</v>
@@ -48222,7 +48222,7 @@
         <v>0.7083</v>
       </c>
       <c r="F493" t="n">
-        <v>0.8658</v>
+        <v>0.8659</v>
       </c>
       <c r="G493" t="n">
         <v>0.2513</v>
@@ -48243,7 +48243,7 @@
         <v>0.5293</v>
       </c>
       <c r="M493" t="n">
-        <v>0.3267</v>
+        <v>0.3268</v>
       </c>
     </row>
     <row r="494">
@@ -48372,7 +48372,7 @@
         <v>0.5276</v>
       </c>
       <c r="M496" t="n">
-        <v>0.7291</v>
+        <v>0.7292</v>
       </c>
     </row>
     <row r="497">
@@ -48415,7 +48415,7 @@
         <v>0.5363</v>
       </c>
       <c r="M497" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="498">
@@ -48501,7 +48501,7 @@
         <v>0.482</v>
       </c>
       <c r="M499" t="n">
-        <v>0.58</v>
+        <v>0.5800999999999999</v>
       </c>
     </row>
     <row r="500">
@@ -48544,7 +48544,7 @@
         <v>0.527</v>
       </c>
       <c r="M500" t="n">
-        <v>0.5957</v>
+        <v>0.5958</v>
       </c>
     </row>
     <row r="501">
@@ -48587,7 +48587,7 @@
         <v>0.4776</v>
       </c>
       <c r="M501" t="n">
-        <v>0.5432</v>
+        <v>0.5433</v>
       </c>
     </row>
     <row r="502">
@@ -48673,7 +48673,7 @@
         <v>0.4544</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4316</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="504">
@@ -48759,7 +48759,7 @@
         <v>0.4075</v>
       </c>
       <c r="M505" t="n">
-        <v>0.3721</v>
+        <v>0.3722</v>
       </c>
     </row>
     <row r="506">
@@ -48802,7 +48802,7 @@
         <v>0.4757</v>
       </c>
       <c r="M506" t="n">
-        <v>0.3125</v>
+        <v>0.3126</v>
       </c>
     </row>
     <row r="507">
@@ -48815,7 +48815,7 @@
         <v>0.4589</v>
       </c>
       <c r="C507" t="n">
-        <v>0.5868</v>
+        <v>0.5869</v>
       </c>
       <c r="D507" t="n">
         <v>0.5229</v>
@@ -48824,7 +48824,7 @@
         <v>0.4589</v>
       </c>
       <c r="F507" t="n">
-        <v>0.5868</v>
+        <v>0.5869</v>
       </c>
       <c r="G507" t="n">
         <v>0.2973</v>
@@ -48845,7 +48845,7 @@
         <v>0.401</v>
       </c>
       <c r="M507" t="n">
-        <v>0.3112</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="508">
@@ -49017,7 +49017,7 @@
         <v>0.3744</v>
       </c>
       <c r="M511" t="n">
-        <v>0.629</v>
+        <v>0.6289</v>
       </c>
     </row>
     <row r="512">
@@ -49232,7 +49232,7 @@
         <v>0.3077</v>
       </c>
       <c r="M516" t="n">
-        <v>0.5323</v>
+        <v>0.5322</v>
       </c>
     </row>
     <row r="517">
@@ -49331,7 +49331,7 @@
         <v>0.5201</v>
       </c>
       <c r="C519" t="n">
-        <v>0.4574</v>
+        <v>0.4575</v>
       </c>
       <c r="D519" t="n">
         <v>0.4888</v>
@@ -49340,7 +49340,7 @@
         <v>0.5201</v>
       </c>
       <c r="F519" t="n">
-        <v>0.4574</v>
+        <v>0.4575</v>
       </c>
       <c r="G519" t="n">
         <v>0.4301</v>
@@ -49361,7 +49361,7 @@
         <v>0.2866</v>
       </c>
       <c r="M519" t="n">
-        <v>0.4396</v>
+        <v>0.4397</v>
       </c>
     </row>
     <row r="520">
@@ -49503,7 +49503,7 @@
         <v>0.4349</v>
       </c>
       <c r="C523" t="n">
-        <v>0.4147</v>
+        <v>0.4148</v>
       </c>
       <c r="D523" t="n">
         <v>0.4248</v>
@@ -49512,7 +49512,7 @@
         <v>0.4349</v>
       </c>
       <c r="F523" t="n">
-        <v>0.4147</v>
+        <v>0.4148</v>
       </c>
       <c r="G523" t="n">
         <v>0.498</v>
@@ -49619,7 +49619,7 @@
         <v>0.1579</v>
       </c>
       <c r="M525" t="n">
-        <v>0.3896</v>
+        <v>0.3897</v>
       </c>
     </row>
     <row r="526">
@@ -50092,7 +50092,7 @@
         <v>-0.008399999999999999</v>
       </c>
       <c r="M536" t="n">
-        <v>0.2553</v>
+        <v>0.2554</v>
       </c>
     </row>
     <row r="537">
@@ -50135,7 +50135,7 @@
         <v>-0.0519</v>
       </c>
       <c r="M537" t="n">
-        <v>0.1858</v>
+        <v>0.1859</v>
       </c>
     </row>
     <row r="538">
@@ -50178,7 +50178,7 @@
         <v>-0.0247</v>
       </c>
       <c r="M538" t="n">
-        <v>0.1653</v>
+        <v>0.1654</v>
       </c>
     </row>
     <row r="539">
@@ -50264,7 +50264,7 @@
         <v>-0.0309</v>
       </c>
       <c r="M540" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="541">
@@ -50608,7 +50608,7 @@
         <v>-0.5876</v>
       </c>
       <c r="M548" t="n">
-        <v>-0.0606</v>
+        <v>-0.0607</v>
       </c>
     </row>
     <row r="549">
@@ -51339,7 +51339,7 @@
         <v>0.3191</v>
       </c>
       <c r="M565" t="n">
-        <v>-0.1465</v>
+        <v>-0.1464</v>
       </c>
     </row>
     <row r="566">
@@ -51640,7 +51640,7 @@
         <v>0.4803</v>
       </c>
       <c r="M572" t="n">
-        <v>0.0853</v>
+        <v>0.0854</v>
       </c>
     </row>
     <row r="573">
@@ -51914,7 +51914,7 @@
         <v>0.1301</v>
       </c>
       <c r="D579" t="n">
-        <v>0.189</v>
+        <v>0.1891</v>
       </c>
       <c r="E579" t="n">
         <v>0.248</v>
@@ -52040,7 +52040,7 @@
         <v>0.4612</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0427</v>
+        <v>0.0428</v>
       </c>
       <c r="D582" t="n">
         <v>0.252</v>
@@ -52049,7 +52049,7 @@
         <v>0.4612</v>
       </c>
       <c r="F582" t="n">
-        <v>0.0427</v>
+        <v>0.0428</v>
       </c>
       <c r="G582" t="n">
         <v>1.2718</v>
@@ -52083,7 +52083,7 @@
         <v>0.522</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.0399</v>
+        <v>-0.0398</v>
       </c>
       <c r="D583" t="n">
         <v>0.2411</v>
@@ -52092,7 +52092,7 @@
         <v>0.522</v>
       </c>
       <c r="F583" t="n">
-        <v>-0.0399</v>
+        <v>-0.0398</v>
       </c>
       <c r="G583" t="n">
         <v>1.3266</v>
@@ -52126,7 +52126,7 @@
         <v>0.5328000000000001</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.0712</v>
+        <v>-0.0711</v>
       </c>
       <c r="D584" t="n">
         <v>0.2308</v>
@@ -52135,7 +52135,7 @@
         <v>0.5328000000000001</v>
       </c>
       <c r="F584" t="n">
-        <v>-0.0712</v>
+        <v>-0.0711</v>
       </c>
       <c r="G584" t="n">
         <v>1.4156</v>
@@ -52172,7 +52172,7 @@
         <v>-0.1246</v>
       </c>
       <c r="D585" t="n">
-        <v>0.1951</v>
+        <v>0.1952</v>
       </c>
       <c r="E585" t="n">
         <v>0.5149</v>
@@ -52242,7 +52242,7 @@
         <v>0.6581</v>
       </c>
       <c r="M586" t="n">
-        <v>-0.7428</v>
+        <v>-0.7427</v>
       </c>
     </row>
     <row r="587">
@@ -52285,7 +52285,7 @@
         <v>0.53</v>
       </c>
       <c r="M587" t="n">
-        <v>-0.8623</v>
+        <v>-0.8622</v>
       </c>
     </row>
     <row r="588">
@@ -52328,7 +52328,7 @@
         <v>0.5521</v>
       </c>
       <c r="M588" t="n">
-        <v>-0.9629</v>
+        <v>-0.9628</v>
       </c>
     </row>
     <row r="589">
@@ -52371,7 +52371,7 @@
         <v>0.5172</v>
       </c>
       <c r="M589" t="n">
-        <v>-1.0472</v>
+        <v>-1.0471</v>
       </c>
     </row>
     <row r="590">
@@ -52457,7 +52457,7 @@
         <v>0.5151</v>
       </c>
       <c r="M591" t="n">
-        <v>-1.0619</v>
+        <v>-1.0618</v>
       </c>
     </row>
     <row r="592">
@@ -52500,7 +52500,7 @@
         <v>0.4581</v>
       </c>
       <c r="M592" t="n">
-        <v>-1.1679</v>
+        <v>-1.1678</v>
       </c>
     </row>
     <row r="593">
@@ -52556,7 +52556,7 @@
         <v>0.6217</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.4024</v>
+        <v>-0.4023</v>
       </c>
       <c r="D594" t="n">
         <v>0.1097</v>
@@ -52565,7 +52565,7 @@
         <v>0.6217</v>
       </c>
       <c r="F594" t="n">
-        <v>-0.4024</v>
+        <v>-0.4023</v>
       </c>
       <c r="G594" t="n">
         <v>1.7717</v>
@@ -52586,7 +52586,7 @@
         <v>0.4907</v>
       </c>
       <c r="M594" t="n">
-        <v>-1.0511</v>
+        <v>-1.051</v>
       </c>
     </row>
     <row r="595">
@@ -52672,7 +52672,7 @@
         <v>0.5352</v>
       </c>
       <c r="M596" t="n">
-        <v>-0.7734</v>
+        <v>-0.7733</v>
       </c>
     </row>
     <row r="597">
@@ -52685,7 +52685,7 @@
         <v>0.7344000000000001</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.3373</v>
+        <v>-0.3372</v>
       </c>
       <c r="D597" t="n">
         <v>0.1986</v>
@@ -52694,7 +52694,7 @@
         <v>0.7344000000000001</v>
       </c>
       <c r="F597" t="n">
-        <v>-0.3373</v>
+        <v>-0.3372</v>
       </c>
       <c r="G597" t="n">
         <v>1.7533</v>
@@ -52860,7 +52860,7 @@
         <v>-0.2475</v>
       </c>
       <c r="D601" t="n">
-        <v>0.2092</v>
+        <v>0.2093</v>
       </c>
       <c r="E601" t="n">
         <v>0.666</v>
@@ -52930,7 +52930,7 @@
         <v>0.4856</v>
       </c>
       <c r="M602" t="n">
-        <v>-0.5104</v>
+        <v>-0.5103</v>
       </c>
     </row>
     <row r="603">
@@ -52989,7 +52989,7 @@
         <v>-0.1688</v>
       </c>
       <c r="D604" t="n">
-        <v>0.227</v>
+        <v>0.2271</v>
       </c>
       <c r="E604" t="n">
         <v>0.6229</v>
@@ -53016,7 +53016,7 @@
         <v>0.4481</v>
       </c>
       <c r="M604" t="n">
-        <v>-0.3385</v>
+        <v>-0.3384</v>
       </c>
     </row>
     <row r="605">
@@ -53059,7 +53059,7 @@
         <v>0.4817</v>
       </c>
       <c r="M605" t="n">
-        <v>-0.3086</v>
+        <v>-0.3085</v>
       </c>
     </row>
     <row r="606">
@@ -53075,7 +53075,7 @@
         <v>-0.1349</v>
       </c>
       <c r="D606" t="n">
-        <v>0.2452</v>
+        <v>0.2453</v>
       </c>
       <c r="E606" t="n">
         <v>0.6254</v>
@@ -53102,7 +53102,7 @@
         <v>0.4796</v>
       </c>
       <c r="M606" t="n">
-        <v>-0.2808</v>
+        <v>-0.2807</v>
       </c>
     </row>
     <row r="607">
@@ -53115,16 +53115,16 @@
         <v>0.6499</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.1257</v>
+        <v>-0.1256</v>
       </c>
       <c r="D607" t="n">
-        <v>0.2621</v>
+        <v>0.2622</v>
       </c>
       <c r="E607" t="n">
         <v>0.6499</v>
       </c>
       <c r="F607" t="n">
-        <v>-0.1257</v>
+        <v>-0.1256</v>
       </c>
       <c r="G607" t="n">
         <v>1.4515</v>
@@ -53188,7 +53188,7 @@
         <v>0.4692</v>
       </c>
       <c r="M608" t="n">
-        <v>-0.292</v>
+        <v>-0.2919</v>
       </c>
     </row>
     <row r="609">
@@ -53201,7 +53201,7 @@
         <v>0.5876</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.1828</v>
+        <v>-0.1827</v>
       </c>
       <c r="D609" t="n">
         <v>0.2024</v>
@@ -53210,7 +53210,7 @@
         <v>0.5876</v>
       </c>
       <c r="F609" t="n">
-        <v>-0.1828</v>
+        <v>-0.1827</v>
       </c>
       <c r="G609" t="n">
         <v>1.4808</v>
@@ -53274,7 +53274,7 @@
         <v>0.4763</v>
       </c>
       <c r="M610" t="n">
-        <v>-0.2782</v>
+        <v>-0.2781</v>
       </c>
     </row>
     <row r="611">
@@ -53317,7 +53317,7 @@
         <v>0.46</v>
       </c>
       <c r="M611" t="n">
-        <v>-0.244</v>
+        <v>-0.2439</v>
       </c>
     </row>
     <row r="612">
@@ -53360,7 +53360,7 @@
         <v>0.4621</v>
       </c>
       <c r="M612" t="n">
-        <v>-0.1988</v>
+        <v>-0.1987</v>
       </c>
     </row>
     <row r="613">
@@ -53373,7 +53373,7 @@
         <v>0.5854</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.1639</v>
+        <v>-0.1638</v>
       </c>
       <c r="D613" t="n">
         <v>0.2108</v>
@@ -53382,7 +53382,7 @@
         <v>0.5854</v>
       </c>
       <c r="F613" t="n">
-        <v>-0.1639</v>
+        <v>-0.1638</v>
       </c>
       <c r="G613" t="n">
         <v>1.4019</v>
@@ -53403,7 +53403,7 @@
         <v>0.3813</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1054</v>
+        <v>-0.1053</v>
       </c>
     </row>
     <row r="614">
@@ -53446,7 +53446,7 @@
         <v>0.3886</v>
       </c>
       <c r="M614" t="n">
-        <v>-0.0404</v>
+        <v>-0.0403</v>
       </c>
     </row>
     <row r="615">
@@ -53532,7 +53532,7 @@
         <v>0.3747</v>
       </c>
       <c r="M616" t="n">
-        <v>0.0597</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="617">
@@ -53575,7 +53575,7 @@
         <v>0.4236</v>
       </c>
       <c r="M617" t="n">
-        <v>-0.1104</v>
+        <v>-0.1103</v>
       </c>
     </row>
     <row r="618">
@@ -53618,7 +53618,7 @@
         <v>0.4167</v>
       </c>
       <c r="M618" t="n">
-        <v>-0.1078</v>
+        <v>-0.1077</v>
       </c>
     </row>
     <row r="619">
@@ -53631,16 +53631,16 @@
         <v>0.5303</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.2199</v>
+        <v>-0.2198</v>
       </c>
       <c r="D619" t="n">
-        <v>0.1552</v>
+        <v>0.1553</v>
       </c>
       <c r="E619" t="n">
         <v>0.5303</v>
       </c>
       <c r="F619" t="n">
-        <v>-0.2199</v>
+        <v>-0.2198</v>
       </c>
       <c r="G619" t="n">
         <v>1.5796</v>
@@ -53661,7 +53661,7 @@
         <v>0.368</v>
       </c>
       <c r="M619" t="n">
-        <v>-0.1043</v>
+        <v>-0.1042</v>
       </c>
     </row>
     <row r="620">
@@ -53704,7 +53704,7 @@
         <v>0.3876</v>
       </c>
       <c r="M620" t="n">
-        <v>-0.1296</v>
+        <v>-0.1295</v>
       </c>
     </row>
     <row r="621">
@@ -53747,7 +53747,7 @@
         <v>0.4084</v>
       </c>
       <c r="M621" t="n">
-        <v>-0.1079</v>
+        <v>-0.1078</v>
       </c>
     </row>
     <row r="622">
@@ -53790,7 +53790,7 @@
         <v>0.4615</v>
       </c>
       <c r="M622" t="n">
-        <v>-0.1139</v>
+        <v>-0.1138</v>
       </c>
     </row>
     <row r="623">
@@ -53803,7 +53803,7 @@
         <v>0.5175999999999999</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.2681</v>
+        <v>-0.268</v>
       </c>
       <c r="D623" t="n">
         <v>0.1248</v>
@@ -53812,7 +53812,7 @@
         <v>0.5175999999999999</v>
       </c>
       <c r="F623" t="n">
-        <v>-0.2681</v>
+        <v>-0.268</v>
       </c>
       <c r="G623" t="n">
         <v>1.3975</v>
@@ -53833,7 +53833,7 @@
         <v>0.3639</v>
       </c>
       <c r="M623" t="n">
-        <v>-0.0906</v>
+        <v>-0.0905</v>
       </c>
     </row>
     <row r="624">
@@ -53849,7 +53849,7 @@
         <v>-0.2474</v>
       </c>
       <c r="D624" t="n">
-        <v>0.1472</v>
+        <v>0.1473</v>
       </c>
       <c r="E624" t="n">
         <v>0.5419</v>
@@ -53876,7 +53876,7 @@
         <v>0.449</v>
       </c>
       <c r="M624" t="n">
-        <v>-0.0631</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="625">
@@ -53919,7 +53919,7 @@
         <v>0.381</v>
       </c>
       <c r="M625" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0738</v>
       </c>
     </row>
     <row r="626">
@@ -53962,7 +53962,7 @@
         <v>0.4364</v>
       </c>
       <c r="M626" t="n">
-        <v>-0.0444</v>
+        <v>-0.0443</v>
       </c>
     </row>
     <row r="627">
@@ -54005,7 +54005,7 @@
         <v>0.3646</v>
       </c>
       <c r="M627" t="n">
-        <v>-0.0649</v>
+        <v>-0.0648</v>
       </c>
     </row>
     <row r="628">
@@ -54021,7 +54021,7 @@
         <v>-0.2767</v>
       </c>
       <c r="D628" t="n">
-        <v>0.074</v>
+        <v>0.0741</v>
       </c>
       <c r="E628" t="n">
         <v>0.4248</v>
@@ -54048,7 +54048,7 @@
         <v>0.4399</v>
       </c>
       <c r="M628" t="n">
-        <v>-0.0054</v>
+        <v>-0.0053</v>
       </c>
     </row>
     <row r="629">
@@ -54091,7 +54091,7 @@
         <v>0.3511</v>
       </c>
       <c r="M629" t="n">
-        <v>0.0654</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="630">
@@ -54134,7 +54134,7 @@
         <v>0.46</v>
       </c>
       <c r="M630" t="n">
-        <v>-0.0066</v>
+        <v>-0.0065</v>
       </c>
     </row>
     <row r="631">
@@ -54147,16 +54147,16 @@
         <v>0.3873</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.203</v>
+        <v>-0.2029</v>
       </c>
       <c r="D631" t="n">
-        <v>0.0921</v>
+        <v>0.0922</v>
       </c>
       <c r="E631" t="n">
         <v>0.3873</v>
       </c>
       <c r="F631" t="n">
-        <v>-0.203</v>
+        <v>-0.2029</v>
       </c>
       <c r="G631" t="n">
         <v>0.5188</v>
@@ -54177,7 +54177,7 @@
         <v>0.4838</v>
       </c>
       <c r="M631" t="n">
-        <v>0.2677</v>
+        <v>0.2678</v>
       </c>
     </row>
     <row r="632">
@@ -54220,7 +54220,7 @@
         <v>0.4472</v>
       </c>
       <c r="M632" t="n">
-        <v>0.2816</v>
+        <v>0.2817</v>
       </c>
     </row>
     <row r="633">
@@ -54306,7 +54306,7 @@
         <v>0.419</v>
       </c>
       <c r="M634" t="n">
-        <v>0.4024</v>
+        <v>0.4025</v>
       </c>
     </row>
     <row r="635">
@@ -54319,16 +54319,16 @@
         <v>0.4356</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1578</v>
+        <v>-0.162</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1389</v>
+        <v>0.1368</v>
       </c>
       <c r="E635" t="n">
         <v>0.4356</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1578</v>
+        <v>-0.162</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4293</v>
+        <v>0.4169</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -4170,7 +4170,7 @@
         <v>0.141</v>
       </c>
       <c r="K285" t="n">
-        <v>-0.126</v>
+        <v>-0.127</v>
       </c>
     </row>
     <row r="286">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9.879</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.054</v>
+        <v>1.053</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.054</v>
+        <v>1.0528</v>
       </c>
       <c r="H635" t="n">
-        <v>9.8789</v>
+        <v>9.8695</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -38048,7 +38048,7 @@
         <v>-1.372</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7212</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="D195" t="n">
         <v>-1.0466</v>
@@ -38057,13 +38057,13 @@
         <v>-1.372</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7212</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="G195" t="n">
         <v>-1.372</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7212</v>
+        <v>-0.7213000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -40232,7 +40232,7 @@
         <v>0.1273</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1319</v>
+        <v>0.1318</v>
       </c>
       <c r="D273" t="n">
         <v>0.1296</v>
@@ -40241,13 +40241,13 @@
         <v>0.1273</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1319</v>
+        <v>0.1318</v>
       </c>
       <c r="G273" t="n">
         <v>0.1273</v>
       </c>
       <c r="M273" t="n">
-        <v>0.1319</v>
+        <v>0.1318</v>
       </c>
     </row>
     <row r="274">
@@ -41719,7 +41719,7 @@
         <v>0.1854</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.036</v>
+        <v>-0.0361</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2575</v>
@@ -42052,7 +42052,7 @@
         <v>-0.1245</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2469</v>
+        <v>-0.247</v>
       </c>
       <c r="D338" t="n">
         <v>-0.1857</v>
@@ -42061,13 +42061,13 @@
         <v>-0.1245</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2469</v>
+        <v>-0.247</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1245</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2469</v>
+        <v>-0.247</v>
       </c>
     </row>
     <row r="339">
@@ -42668,7 +42668,7 @@
         <v>0.213</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0183</v>
+        <v>-0.0184</v>
       </c>
       <c r="D360" t="n">
         <v>0.0973</v>
@@ -42677,13 +42677,13 @@
         <v>0.213</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.0183</v>
+        <v>-0.0184</v>
       </c>
       <c r="G360" t="n">
         <v>0.213</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.0183</v>
+        <v>-0.0184</v>
       </c>
     </row>
     <row r="361">
@@ -42944,7 +42944,7 @@
         <v>-0.4026</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.4268</v>
+        <v>-0.4269</v>
       </c>
       <c r="E369" t="n">
         <v>-0.4511</v>
@@ -44862,7 +44862,7 @@
         <v>-1.2376</v>
       </c>
       <c r="D415" t="n">
-        <v>-0.6411</v>
+        <v>-0.6412</v>
       </c>
       <c r="E415" t="n">
         <v>-0.0447</v>
@@ -45534,7 +45534,7 @@
         <v>-0.2206</v>
       </c>
       <c r="M430" t="n">
-        <v>0.5226</v>
+        <v>0.5225</v>
       </c>
     </row>
     <row r="431">
@@ -46622,7 +46622,7 @@
         <v>-0.3844</v>
       </c>
       <c r="C456" t="n">
-        <v>0.3134</v>
+        <v>0.3133</v>
       </c>
       <c r="D456" t="n">
         <v>-0.0355</v>
@@ -46631,7 +46631,7 @@
         <v>-0.3844</v>
       </c>
       <c r="F456" t="n">
-        <v>0.3134</v>
+        <v>0.3133</v>
       </c>
       <c r="G456" t="n">
         <v>0.1237</v>
@@ -47082,7 +47082,7 @@
         <v>0.4637</v>
       </c>
       <c r="M466" t="n">
-        <v>0.3233</v>
+        <v>0.3232</v>
       </c>
     </row>
     <row r="467">
@@ -48501,7 +48501,7 @@
         <v>0.482</v>
       </c>
       <c r="M499" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="500">
@@ -48673,7 +48673,7 @@
         <v>0.4544</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4317</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="504">
@@ -53446,7 +53446,7 @@
         <v>0.3886</v>
       </c>
       <c r="M614" t="n">
-        <v>-0.0403</v>
+        <v>-0.0404</v>
       </c>
     </row>
     <row r="615">
@@ -53634,7 +53634,7 @@
         <v>-0.2198</v>
       </c>
       <c r="D619" t="n">
-        <v>0.1553</v>
+        <v>0.1552</v>
       </c>
       <c r="E619" t="n">
         <v>0.5303</v>
@@ -53661,7 +53661,7 @@
         <v>0.368</v>
       </c>
       <c r="M619" t="n">
-        <v>-0.1042</v>
+        <v>-0.1043</v>
       </c>
     </row>
     <row r="620">
@@ -54319,16 +54319,16 @@
         <v>0.4356</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.162</v>
+        <v>-0.1617</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1368</v>
+        <v>0.1369</v>
       </c>
       <c r="E635" t="n">
         <v>0.4356</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.162</v>
+        <v>-0.1617</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4169</v>
+        <v>0.4177</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -780,7 +780,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>+0.44  Mildly accommodative</t>
+          <t>+0.40  Mildly accommodative</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>+0.14  Broadly neutral</t>
+          <t>+0.12  Broadly neutral</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>-1.15</v>
+        <v>-1.28</v>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Monetary conditions score +0.44 (mildly accommodative) and liquidity conditions -0.16 (mildly restrictive); the combined index is +0.14 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-8.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
+          <t>Monetary conditions score +0.40 (mildly accommodative) and liquidity conditions -0.16 (mildly restrictive); the combined index is +0.12 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-10.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>-0.541</v>
+        <v>-0.54</v>
       </c>
       <c r="K366" t="n">
         <v>0.49</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>-0.575</v>
+        <v>-0.574</v>
       </c>
       <c r="K367" t="n">
         <v>0.456</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>-0.657</v>
+        <v>-0.656</v>
       </c>
       <c r="K368" t="n">
         <v>0.387</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>-0.541</v>
+        <v>-0.54</v>
       </c>
       <c r="K369" t="n">
         <v>0.354</v>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>-0.477</v>
+        <v>-0.476</v>
       </c>
       <c r="K373" t="n">
         <v>0.038</v>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="J376" t="n">
-        <v>-0.434</v>
+        <v>-0.433</v>
       </c>
       <c r="K376" t="n">
         <v>-0.131</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="J378" t="n">
-        <v>-0.45</v>
+        <v>-0.449</v>
       </c>
       <c r="K378" t="n">
         <v>-0.272</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>-0.572</v>
+        <v>-0.571</v>
       </c>
       <c r="K380" t="n">
         <v>-0.354</v>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>-0.697</v>
+        <v>-0.696</v>
       </c>
       <c r="K381" t="n">
         <v>-0.425</v>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>-0.855</v>
+        <v>-0.854</v>
       </c>
       <c r="K382" t="n">
         <v>-0.511</v>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>-0.9</v>
+        <v>-0.899</v>
       </c>
       <c r="K383" t="n">
         <v>-0.622</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="J384" t="n">
-        <v>-0.946</v>
+        <v>-0.945</v>
       </c>
       <c r="K384" t="n">
         <v>-0.627</v>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>-1.012</v>
+        <v>-1.011</v>
       </c>
       <c r="K385" t="n">
         <v>-0.696</v>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>-0.93</v>
+        <v>-0.929</v>
       </c>
       <c r="K387" t="n">
         <v>-0.6899999999999999</v>
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="J388" t="n">
-        <v>-0.911</v>
+        <v>-0.91</v>
       </c>
       <c r="K388" t="n">
         <v>-0.675</v>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="K389" t="n">
         <v>-0.678</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>-0.903</v>
+        <v>-0.902</v>
       </c>
       <c r="K390" t="n">
         <v>-0.6929999999999999</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>-0.849</v>
+        <v>-0.848</v>
       </c>
       <c r="K391" t="n">
         <v>-0.715</v>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>-0.898</v>
+        <v>-0.897</v>
       </c>
       <c r="K392" t="n">
         <v>-0.695</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>-0.77</v>
+        <v>-0.769</v>
       </c>
       <c r="K393" t="n">
         <v>-0.698</v>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>-0.553</v>
+        <v>-0.552</v>
       </c>
       <c r="K395" t="n">
         <v>-0.677</v>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>-0.429</v>
+        <v>-0.428</v>
       </c>
       <c r="K397" t="n">
         <v>-0.801</v>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>-0.482</v>
+        <v>-0.481</v>
       </c>
       <c r="K398" t="n">
         <v>-0.84</v>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="J399" t="n">
-        <v>-0.428</v>
+        <v>-0.427</v>
       </c>
       <c r="K399" t="n">
         <v>-0.914</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>-0.398</v>
+        <v>-0.397</v>
       </c>
       <c r="K400" t="n">
         <v>-0.912</v>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>-0.253</v>
+        <v>-0.252</v>
       </c>
       <c r="K401" t="n">
         <v>-0.961</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>-0.259</v>
+        <v>-0.258</v>
       </c>
       <c r="K402" t="n">
         <v>-1.029</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>-0.122</v>
+        <v>-0.121</v>
       </c>
       <c r="K406" t="n">
         <v>-1.157</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>-0.045</v>
+        <v>-0.044</v>
       </c>
       <c r="K407" t="n">
         <v>-1.238</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="K409" t="n">
         <v>-1.344</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>-0.079</v>
+        <v>-0.078</v>
       </c>
       <c r="K411" t="n">
         <v>-1.37</v>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>-0.581</v>
+        <v>-0.58</v>
       </c>
       <c r="K420" t="n">
         <v>0.044</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>-0.677</v>
+        <v>-0.676</v>
       </c>
       <c r="K422" t="n">
         <v>0.063</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>-0.723</v>
+        <v>-0.722</v>
       </c>
       <c r="K424" t="n">
         <v>0.08699999999999999</v>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>-0.715</v>
+        <v>-0.714</v>
       </c>
       <c r="K428" t="n">
         <v>0.19</v>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>-0.62</v>
+        <v>-0.619</v>
       </c>
       <c r="K430" t="n">
         <v>0.281</v>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>-0.666</v>
+        <v>-0.665</v>
       </c>
       <c r="K437" t="n">
         <v>0.238</v>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>-0.399</v>
+        <v>-0.398</v>
       </c>
       <c r="K442" t="n">
         <v>0.296</v>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>-0.344</v>
+        <v>-0.343</v>
       </c>
       <c r="K443" t="n">
         <v>0.283</v>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>-0.456</v>
+        <v>-0.455</v>
       </c>
       <c r="K450" t="n">
         <v>0.248</v>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="J451" t="n">
-        <v>-0.343</v>
+        <v>-0.342</v>
       </c>
       <c r="K451" t="n">
         <v>0.259</v>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="J458" t="n">
-        <v>-0.4</v>
+        <v>-0.399</v>
       </c>
       <c r="K458" t="n">
         <v>0.397</v>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>-0.017</v>
+        <v>-0.016</v>
       </c>
       <c r="K463" t="n">
         <v>0.727</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>0.653</v>
+        <v>0.652</v>
       </c>
       <c r="K469" t="n">
         <v>1.047</v>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>0.89</v>
+        <v>0.889</v>
       </c>
       <c r="K472" t="n">
         <v>1.202</v>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="K474" t="n">
         <v>1.24</v>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>1.037</v>
+        <v>1.036</v>
       </c>
       <c r="K477" t="n">
         <v>1.08</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>0.948</v>
+        <v>0.947</v>
       </c>
       <c r="K479" t="n">
         <v>0.963</v>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>0.918</v>
+        <v>0.917</v>
       </c>
       <c r="K480" t="n">
         <v>0.949</v>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>0.893</v>
+        <v>0.892</v>
       </c>
       <c r="K483" t="n">
         <v>0.892</v>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="K486" t="n">
         <v>0.891</v>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>0.91</v>
+        <v>0.909</v>
       </c>
       <c r="K487" t="n">
         <v>0.849</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="K489" t="n">
         <v>0.9330000000000001</v>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="K490" t="n">
         <v>0.9</v>
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="K491" t="n">
         <v>0.831</v>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="K492" t="n">
         <v>0.841</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>0.696</v>
+        <v>0.695</v>
       </c>
       <c r="K493" t="n">
         <v>0.788</v>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="K502" t="n">
         <v>0.618</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="K507" t="n">
         <v>0.528</v>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="K538" t="n">
         <v>-0.246</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>0.181</v>
+        <v>0.182</v>
       </c>
       <c r="K541" t="n">
         <v>-0.367</v>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="K546" t="n">
         <v>-0.451</v>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="K547" t="n">
         <v>-0.501</v>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="K549" t="n">
         <v>-0.449</v>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="K564" t="n">
         <v>0.334</v>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="J567" t="n">
-        <v>0.262</v>
+        <v>0.263</v>
       </c>
       <c r="K567" t="n">
         <v>0.23</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="J568" t="n">
-        <v>0.285</v>
+        <v>0.286</v>
       </c>
       <c r="K568" t="n">
         <v>0.244</v>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="K570" t="n">
         <v>0.148</v>
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="K574" t="n">
         <v>0.043</v>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="J578" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="K578" t="n">
         <v>-0.193</v>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="J580" t="n">
-        <v>0.642</v>
+        <v>0.643</v>
       </c>
       <c r="K580" t="n">
         <v>-0.316</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="J582" t="n">
-        <v>0.696</v>
+        <v>0.697</v>
       </c>
       <c r="K582" t="n">
         <v>-0.421</v>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
       <c r="K584" t="n">
         <v>-0.432</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="K589" t="n">
         <v>-0.337</v>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="K592" t="n">
         <v>-0.281</v>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="J597" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="K597" t="n">
         <v>-0.147</v>
@@ -8236,7 +8236,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>0.625</v>
+        <v>0.626</v>
       </c>
       <c r="K598" t="n">
         <v>-0.135</v>
@@ -8288,7 +8288,7 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>0.513</v>
+        <v>0.514</v>
       </c>
       <c r="K602" t="n">
         <v>-0.163</v>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="J605" t="n">
-        <v>0.585</v>
+        <v>0.586</v>
       </c>
       <c r="K605" t="n">
         <v>-0.164</v>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>0.624</v>
+        <v>0.625</v>
       </c>
       <c r="K606" t="n">
         <v>-0.148</v>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>0.554</v>
+        <v>0.555</v>
       </c>
       <c r="K607" t="n">
         <v>-0.143</v>
@@ -8379,7 +8379,7 @@
         </is>
       </c>
       <c r="J609" t="n">
-        <v>0.543</v>
+        <v>0.544</v>
       </c>
       <c r="K609" t="n">
         <v>-0.187</v>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="J611" t="n">
-        <v>0.53</v>
+        <v>0.531</v>
       </c>
       <c r="K611" t="n">
         <v>-0.22</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="J612" t="n">
-        <v>0.507</v>
+        <v>0.508</v>
       </c>
       <c r="K612" t="n">
         <v>-0.229</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="K614" t="n">
         <v>-0.233</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="J617" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="K617" t="n">
         <v>-0.277</v>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="K619" t="n">
         <v>-0.307</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="K621" t="n">
         <v>-0.289</v>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="K622" t="n">
         <v>-0.289</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="K623" t="n">
         <v>-0.203</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="K624" t="n">
         <v>-0.208</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="J625" t="n">
-        <v>0.404</v>
+        <v>0.405</v>
       </c>
       <c r="K625" t="n">
         <v>-0.179</v>
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>0.436</v>
+        <v>0.403</v>
       </c>
       <c r="K626" t="n">
         <v>-0.167</v>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>0.436</v>
+        <v>0.403</v>
       </c>
       <c r="K627" t="n">
         <v>-0.162</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-8.244</v>
+        <v>-10.169</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>-1.15</v>
+        <v>-1.28</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9.869999999999999</v>
+        <v>9.871</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.053</v>
+        <v>1.052</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>5.8</v>
       </c>
       <c r="C634" t="n">
-        <v>-8.243600000000001</v>
+        <v>-10.1694</v>
       </c>
       <c r="D634" t="n">
         <v>-14.5263</v>
@@ -34506,7 +34506,7 @@
         <v>5.8</v>
       </c>
       <c r="C635" t="n">
-        <v>-8.243600000000001</v>
+        <v>-10.1694</v>
       </c>
       <c r="D635" t="n">
         <v>-14.5263</v>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0528</v>
+        <v>1.0518</v>
       </c>
       <c r="H635" t="n">
-        <v>9.8695</v>
+        <v>9.8714</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -41327,7 +41327,7 @@
         <v>-0.8732</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3692</v>
+        <v>-0.3693</v>
       </c>
       <c r="E312" t="n">
         <v>0.1347</v>
@@ -41859,7 +41859,7 @@
         <v>-0.1225</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1452</v>
+        <v>-0.1453</v>
       </c>
       <c r="E331" t="n">
         <v>-0.168</v>
@@ -41940,22 +41940,22 @@
         <v>-0.1202</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1178</v>
+        <v>-0.1179</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
     </row>
     <row r="335">
@@ -42332,7 +42332,7 @@
         <v>-0.1199</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5127</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="D348" t="n">
         <v>0.1964</v>
@@ -42341,13 +42341,13 @@
         <v>-0.1199</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5127</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5127</v>
+        <v>0.5125999999999999</v>
       </c>
     </row>
     <row r="349">
@@ -43093,16 +43093,16 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>-0.5406</v>
+        <v>-0.5403</v>
       </c>
       <c r="C374" t="n">
         <v>0.4904</v>
       </c>
       <c r="D374" t="n">
-        <v>-0.0251</v>
+        <v>-0.025</v>
       </c>
       <c r="E374" t="n">
-        <v>-0.5406</v>
+        <v>-0.5403</v>
       </c>
       <c r="F374" t="n">
         <v>0.4904</v>
@@ -43117,7 +43117,7 @@
         <v>-1.2639</v>
       </c>
       <c r="J374" t="n">
-        <v>0.0332</v>
+        <v>0.0342</v>
       </c>
       <c r="K374" t="n">
         <v>-0.3987</v>
@@ -43136,16 +43136,16 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>-0.5747</v>
+        <v>-0.5744</v>
       </c>
       <c r="C375" t="n">
         <v>0.4563</v>
       </c>
       <c r="D375" t="n">
-        <v>-0.0592</v>
+        <v>-0.0591</v>
       </c>
       <c r="E375" t="n">
-        <v>-0.5747</v>
+        <v>-0.5744</v>
       </c>
       <c r="F375" t="n">
         <v>0.4563</v>
@@ -43160,7 +43160,7 @@
         <v>-1.1212</v>
       </c>
       <c r="J375" t="n">
-        <v>-0.0418</v>
+        <v>-0.0408</v>
       </c>
       <c r="K375" t="n">
         <v>-0.4742</v>
@@ -43169,7 +43169,7 @@
         <v>1.0309</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8124</v>
+        <v>0.8123</v>
       </c>
     </row>
     <row r="376">
@@ -43179,16 +43179,16 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>-0.6566</v>
+        <v>-0.6562</v>
       </c>
       <c r="C376" t="n">
         <v>0.387</v>
       </c>
       <c r="D376" t="n">
-        <v>-0.1348</v>
+        <v>-0.1346</v>
       </c>
       <c r="E376" t="n">
-        <v>-0.6566</v>
+        <v>-0.6562</v>
       </c>
       <c r="F376" t="n">
         <v>0.387</v>
@@ -43203,7 +43203,7 @@
         <v>-1.0882</v>
       </c>
       <c r="J376" t="n">
-        <v>-0.5252</v>
+        <v>-0.5235</v>
       </c>
       <c r="K376" t="n">
         <v>-0.5849</v>
@@ -43222,16 +43222,16 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>-0.5406</v>
+        <v>-0.5403</v>
       </c>
       <c r="C377" t="n">
         <v>0.3541</v>
       </c>
       <c r="D377" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0931</v>
       </c>
       <c r="E377" t="n">
-        <v>-0.5406</v>
+        <v>-0.5403</v>
       </c>
       <c r="F377" t="n">
         <v>0.3541</v>
@@ -43246,7 +43246,7 @@
         <v>-0.9927</v>
       </c>
       <c r="J377" t="n">
-        <v>-0.1211</v>
+        <v>-0.12</v>
       </c>
       <c r="K377" t="n">
         <v>-0.6711</v>
@@ -43265,16 +43265,16 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>-0.5755</v>
+        <v>-0.5752</v>
       </c>
       <c r="C378" t="n">
         <v>0.2302</v>
       </c>
       <c r="D378" t="n">
-        <v>-0.1726</v>
+        <v>-0.1725</v>
       </c>
       <c r="E378" t="n">
-        <v>-0.5755</v>
+        <v>-0.5752</v>
       </c>
       <c r="F378" t="n">
         <v>0.2302</v>
@@ -43289,7 +43289,7 @@
         <v>-1.045</v>
       </c>
       <c r="J378" t="n">
-        <v>-0.144</v>
+        <v>-0.1428</v>
       </c>
       <c r="K378" t="n">
         <v>-0.7877999999999999</v>
@@ -43308,16 +43308,16 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>-0.5563</v>
+        <v>-0.556</v>
       </c>
       <c r="C379" t="n">
         <v>0.1968</v>
       </c>
       <c r="D379" t="n">
-        <v>-0.1797</v>
+        <v>-0.1796</v>
       </c>
       <c r="E379" t="n">
-        <v>-0.5563</v>
+        <v>-0.556</v>
       </c>
       <c r="F379" t="n">
         <v>0.1968</v>
@@ -43332,7 +43332,7 @@
         <v>-0.9659</v>
       </c>
       <c r="J379" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.0887</v>
       </c>
       <c r="K379" t="n">
         <v>-0.8683</v>
@@ -43351,16 +43351,16 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>-0.4258</v>
+        <v>-0.4256</v>
       </c>
       <c r="C380" t="n">
         <v>0.1267</v>
       </c>
       <c r="D380" t="n">
-        <v>-0.1495</v>
+        <v>-0.1494</v>
       </c>
       <c r="E380" t="n">
-        <v>-0.4258</v>
+        <v>-0.4256</v>
       </c>
       <c r="F380" t="n">
         <v>0.1267</v>
@@ -43375,7 +43375,7 @@
         <v>-0.7965</v>
       </c>
       <c r="J380" t="n">
-        <v>0.2757</v>
+        <v>0.2763</v>
       </c>
       <c r="K380" t="n">
         <v>-0.9766</v>
@@ -43394,16 +43394,16 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>-0.4765</v>
+        <v>-0.4763</v>
       </c>
       <c r="C381" t="n">
         <v>0.038</v>
       </c>
       <c r="D381" t="n">
-        <v>-0.2193</v>
+        <v>-0.2192</v>
       </c>
       <c r="E381" t="n">
-        <v>-0.4765</v>
+        <v>-0.4763</v>
       </c>
       <c r="F381" t="n">
         <v>0.038</v>
@@ -43418,7 +43418,7 @@
         <v>-0.8143</v>
       </c>
       <c r="J381" t="n">
-        <v>0.0828</v>
+        <v>0.0837</v>
       </c>
       <c r="K381" t="n">
         <v>-1.0731</v>
@@ -43437,16 +43437,16 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>-0.4878</v>
+        <v>-0.4875</v>
       </c>
       <c r="C382" t="n">
         <v>-0.0207</v>
       </c>
       <c r="D382" t="n">
-        <v>-0.2543</v>
+        <v>-0.2541</v>
       </c>
       <c r="E382" t="n">
-        <v>-0.4878</v>
+        <v>-0.4875</v>
       </c>
       <c r="F382" t="n">
         <v>-0.0207</v>
@@ -43461,7 +43461,7 @@
         <v>-0.7847</v>
       </c>
       <c r="J382" t="n">
-        <v>-0.146</v>
+        <v>-0.1448</v>
       </c>
       <c r="K382" t="n">
         <v>-1.1946</v>
@@ -43480,16 +43480,16 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>-0.4242</v>
+        <v>-0.4239</v>
       </c>
       <c r="C383" t="n">
         <v>-0.0789</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.2516</v>
+        <v>-0.2514</v>
       </c>
       <c r="E383" t="n">
-        <v>-0.4242</v>
+        <v>-0.4239</v>
       </c>
       <c r="F383" t="n">
         <v>-0.0789</v>
@@ -43504,7 +43504,7 @@
         <v>-0.6076</v>
       </c>
       <c r="J383" t="n">
-        <v>-0.1089</v>
+        <v>-0.1078</v>
       </c>
       <c r="K383" t="n">
         <v>-1.2864</v>
@@ -43523,16 +43523,16 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>-0.4338</v>
+        <v>-0.4334</v>
       </c>
       <c r="C384" t="n">
         <v>-0.131</v>
       </c>
       <c r="D384" t="n">
-        <v>-0.2824</v>
+        <v>-0.2822</v>
       </c>
       <c r="E384" t="n">
-        <v>-0.4338</v>
+        <v>-0.4334</v>
       </c>
       <c r="F384" t="n">
         <v>-0.131</v>
@@ -43547,7 +43547,7 @@
         <v>-0.4421</v>
       </c>
       <c r="J384" t="n">
-        <v>-0.386</v>
+        <v>-0.3845</v>
       </c>
       <c r="K384" t="n">
         <v>-1.364</v>
@@ -43566,16 +43566,16 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>-0.366</v>
+        <v>-0.3657</v>
       </c>
       <c r="C385" t="n">
         <v>-0.207</v>
       </c>
       <c r="D385" t="n">
-        <v>-0.2865</v>
+        <v>-0.2864</v>
       </c>
       <c r="E385" t="n">
-        <v>-0.366</v>
+        <v>-0.3657</v>
       </c>
       <c r="F385" t="n">
         <v>-0.207</v>
@@ -43590,7 +43590,7 @@
         <v>-0.4187</v>
       </c>
       <c r="J385" t="n">
-        <v>-0.0469</v>
+        <v>-0.0458</v>
       </c>
       <c r="K385" t="n">
         <v>-1.4739</v>
@@ -43609,16 +43609,16 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>-0.4496</v>
+        <v>-0.4492</v>
       </c>
       <c r="C386" t="n">
         <v>-0.2719</v>
       </c>
       <c r="D386" t="n">
-        <v>-0.3608</v>
+        <v>-0.3606</v>
       </c>
       <c r="E386" t="n">
-        <v>-0.4496</v>
+        <v>-0.4492</v>
       </c>
       <c r="F386" t="n">
         <v>-0.2719</v>
@@ -43633,7 +43633,7 @@
         <v>-0.4997</v>
       </c>
       <c r="J386" t="n">
-        <v>-0.3185</v>
+        <v>-0.317</v>
       </c>
       <c r="K386" t="n">
         <v>-1.5711</v>
@@ -43652,16 +43652,16 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>-0.4621</v>
+        <v>-0.4617</v>
       </c>
       <c r="C387" t="n">
         <v>-0.3197</v>
       </c>
       <c r="D387" t="n">
-        <v>-0.3909</v>
+        <v>-0.3907</v>
       </c>
       <c r="E387" t="n">
-        <v>-0.4621</v>
+        <v>-0.4617</v>
       </c>
       <c r="F387" t="n">
         <v>-0.3197</v>
@@ -43676,7 +43676,7 @@
         <v>-0.3614</v>
       </c>
       <c r="J387" t="n">
-        <v>-0.5349</v>
+        <v>-0.5332</v>
       </c>
       <c r="K387" t="n">
         <v>-1.6685</v>
@@ -43695,16 +43695,16 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>-0.5717</v>
+        <v>-0.5712</v>
       </c>
       <c r="C388" t="n">
         <v>-0.3544</v>
       </c>
       <c r="D388" t="n">
-        <v>-0.463</v>
+        <v>-0.4628</v>
       </c>
       <c r="E388" t="n">
-        <v>-0.5717</v>
+        <v>-0.5712</v>
       </c>
       <c r="F388" t="n">
         <v>-0.3544</v>
@@ -43719,7 +43719,7 @@
         <v>-0.3928</v>
       </c>
       <c r="J388" t="n">
-        <v>-0.8386</v>
+        <v>-0.8366</v>
       </c>
       <c r="K388" t="n">
         <v>-1.7936</v>
@@ -43738,16 +43738,16 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>-0.697</v>
+        <v>-0.6963</v>
       </c>
       <c r="C389" t="n">
         <v>-0.4247</v>
       </c>
       <c r="D389" t="n">
-        <v>-0.5608</v>
+        <v>-0.5605</v>
       </c>
       <c r="E389" t="n">
-        <v>-0.697</v>
+        <v>-0.6963</v>
       </c>
       <c r="F389" t="n">
         <v>-0.4247</v>
@@ -43762,7 +43762,7 @@
         <v>-0.3572</v>
       </c>
       <c r="J389" t="n">
-        <v>-1.396</v>
+        <v>-1.3933</v>
       </c>
       <c r="K389" t="n">
         <v>-1.8552</v>
@@ -43781,16 +43781,16 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>-0.8552</v>
+        <v>-0.8544</v>
       </c>
       <c r="C390" t="n">
         <v>-0.5112</v>
       </c>
       <c r="D390" t="n">
-        <v>-0.6832</v>
+        <v>-0.6828</v>
       </c>
       <c r="E390" t="n">
-        <v>-0.8552</v>
+        <v>-0.8544</v>
       </c>
       <c r="F390" t="n">
         <v>-0.5112</v>
@@ -43805,7 +43805,7 @@
         <v>-0.5726</v>
       </c>
       <c r="J390" t="n">
-        <v>-1.7506</v>
+        <v>-1.7474</v>
       </c>
       <c r="K390" t="n">
         <v>-1.9648</v>
@@ -43824,16 +43824,16 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>-0.9004</v>
+        <v>-0.8995</v>
       </c>
       <c r="C391" t="n">
         <v>-0.622</v>
       </c>
       <c r="D391" t="n">
-        <v>-0.7612</v>
+        <v>-0.7607</v>
       </c>
       <c r="E391" t="n">
-        <v>-0.9004</v>
+        <v>-0.8995</v>
       </c>
       <c r="F391" t="n">
         <v>-0.622</v>
@@ -43848,7 +43848,7 @@
         <v>-0.4621</v>
       </c>
       <c r="J391" t="n">
-        <v>-2.0398</v>
+        <v>-2.0363</v>
       </c>
       <c r="K391" t="n">
         <v>-2.0825</v>
@@ -43867,16 +43867,16 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>-0.9463</v>
+        <v>-0.9454</v>
       </c>
       <c r="C392" t="n">
         <v>-0.6269</v>
       </c>
       <c r="D392" t="n">
-        <v>-0.7866</v>
+        <v>-0.7862</v>
       </c>
       <c r="E392" t="n">
-        <v>-0.9463</v>
+        <v>-0.9454</v>
       </c>
       <c r="F392" t="n">
         <v>-0.6269</v>
@@ -43891,7 +43891,7 @@
         <v>-0.3874</v>
       </c>
       <c r="J392" t="n">
-        <v>-2.067</v>
+        <v>-2.0635</v>
       </c>
       <c r="K392" t="n">
         <v>-1.9537</v>
@@ -43910,16 +43910,16 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>-1.0117</v>
+        <v>-1.0108</v>
       </c>
       <c r="C393" t="n">
         <v>-0.6963</v>
       </c>
       <c r="D393" t="n">
-        <v>-0.854</v>
+        <v>-0.8535</v>
       </c>
       <c r="E393" t="n">
-        <v>-1.0117</v>
+        <v>-1.0108</v>
       </c>
       <c r="F393" t="n">
         <v>-0.6963</v>
@@ -43934,7 +43934,7 @@
         <v>-0.3807</v>
       </c>
       <c r="J393" t="n">
-        <v>-2.3253</v>
+        <v>-2.3214</v>
       </c>
       <c r="K393" t="n">
         <v>-1.8382</v>
@@ -43953,16 +43953,16 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>-0.9105</v>
+        <v>-0.9096</v>
       </c>
       <c r="C394" t="n">
         <v>-0.6713</v>
       </c>
       <c r="D394" t="n">
-        <v>-0.7909</v>
+        <v>-0.7905</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.9105</v>
+        <v>-0.9096</v>
       </c>
       <c r="F394" t="n">
         <v>-0.6713</v>
@@ -43977,7 +43977,7 @@
         <v>-0.323</v>
       </c>
       <c r="J394" t="n">
-        <v>-2.0153</v>
+        <v>-2.0118</v>
       </c>
       <c r="K394" t="n">
         <v>-1.7354</v>
@@ -43996,16 +43996,16 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>-0.9297</v>
+        <v>-0.9288</v>
       </c>
       <c r="C395" t="n">
         <v>-0.6904</v>
       </c>
       <c r="D395" t="n">
-        <v>-0.8101</v>
+        <v>-0.8096</v>
       </c>
       <c r="E395" t="n">
-        <v>-0.9297</v>
+        <v>-0.9288</v>
       </c>
       <c r="F395" t="n">
         <v>-0.6904</v>
@@ -44020,7 +44020,7 @@
         <v>-0.2513</v>
       </c>
       <c r="J395" t="n">
-        <v>-2.107</v>
+        <v>-2.1033</v>
       </c>
       <c r="K395" t="n">
         <v>-1.6265</v>
@@ -44039,16 +44039,16 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>-0.9113</v>
+        <v>-0.9104</v>
       </c>
       <c r="C396" t="n">
         <v>-0.6746</v>
       </c>
       <c r="D396" t="n">
-        <v>-0.7929</v>
+        <v>-0.7925</v>
       </c>
       <c r="E396" t="n">
-        <v>-0.9113</v>
+        <v>-0.9104</v>
       </c>
       <c r="F396" t="n">
         <v>-0.6746</v>
@@ -44063,7 +44063,7 @@
         <v>-0.2528</v>
       </c>
       <c r="J396" t="n">
-        <v>-2.1044</v>
+        <v>-2.1008</v>
       </c>
       <c r="K396" t="n">
         <v>-1.5411</v>
@@ -44082,16 +44082,16 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>-0.9381</v>
+        <v>-0.9372</v>
       </c>
       <c r="C397" t="n">
         <v>-0.6784</v>
       </c>
       <c r="D397" t="n">
-        <v>-0.8082</v>
+        <v>-0.8078</v>
       </c>
       <c r="E397" t="n">
-        <v>-0.9381</v>
+        <v>-0.9372</v>
       </c>
       <c r="F397" t="n">
         <v>-0.6784</v>
@@ -44106,7 +44106,7 @@
         <v>-0.205</v>
       </c>
       <c r="J397" t="n">
-        <v>-2.3647</v>
+        <v>-2.3607</v>
       </c>
       <c r="K397" t="n">
         <v>-1.41</v>
@@ -44125,16 +44125,16 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>-0.9033</v>
+        <v>-0.9023</v>
       </c>
       <c r="C398" t="n">
         <v>-0.6934</v>
       </c>
       <c r="D398" t="n">
-        <v>-0.7983</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="E398" t="n">
-        <v>-0.9033</v>
+        <v>-0.9023</v>
       </c>
       <c r="F398" t="n">
         <v>-0.6934</v>
@@ -44149,7 +44149,7 @@
         <v>-0.0602</v>
       </c>
       <c r="J398" t="n">
-        <v>-2.3141</v>
+        <v>-2.3102</v>
       </c>
       <c r="K398" t="n">
         <v>-1.3008</v>
@@ -44168,16 +44168,16 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>-0.8489</v>
+        <v>-0.848</v>
       </c>
       <c r="C399" t="n">
         <v>-0.7146</v>
       </c>
       <c r="D399" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7813</v>
       </c>
       <c r="E399" t="n">
-        <v>-0.8489</v>
+        <v>-0.848</v>
       </c>
       <c r="F399" t="n">
         <v>-0.7146</v>
@@ -44192,7 +44192,7 @@
         <v>-0.0058</v>
       </c>
       <c r="J399" t="n">
-        <v>-2.1564</v>
+        <v>-2.1527</v>
       </c>
       <c r="K399" t="n">
         <v>-1.2048</v>
@@ -44211,16 +44211,16 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>-0.8983</v>
+        <v>-0.8974</v>
       </c>
       <c r="C400" t="n">
         <v>-0.6951000000000001</v>
       </c>
       <c r="D400" t="n">
-        <v>-0.7967</v>
+        <v>-0.7962</v>
       </c>
       <c r="E400" t="n">
-        <v>-0.8983</v>
+        <v>-0.8974</v>
       </c>
       <c r="F400" t="n">
         <v>-0.6951000000000001</v>
@@ -44235,7 +44235,7 @@
         <v>-0.1439</v>
       </c>
       <c r="J400" t="n">
-        <v>-2.1167</v>
+        <v>-2.1131</v>
       </c>
       <c r="K400" t="n">
         <v>-1.0672</v>
@@ -44254,16 +44254,16 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>-0.7702</v>
+        <v>-0.7693</v>
       </c>
       <c r="C401" t="n">
         <v>-0.6975</v>
       </c>
       <c r="D401" t="n">
-        <v>-0.7338</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="E401" t="n">
-        <v>-0.7702</v>
+        <v>-0.7693</v>
       </c>
       <c r="F401" t="n">
         <v>-0.6975</v>
@@ -44278,7 +44278,7 @@
         <v>-0.032</v>
       </c>
       <c r="J401" t="n">
-        <v>-1.8579</v>
+        <v>-1.8546</v>
       </c>
       <c r="K401" t="n">
         <v>-0.9696</v>
@@ -44297,16 +44297,16 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>-0.6234</v>
+        <v>-0.6227</v>
       </c>
       <c r="C402" t="n">
         <v>-0.6913</v>
       </c>
       <c r="D402" t="n">
-        <v>-0.6574</v>
+        <v>-0.657</v>
       </c>
       <c r="E402" t="n">
-        <v>-0.6234</v>
+        <v>-0.6227</v>
       </c>
       <c r="F402" t="n">
         <v>-0.6913</v>
@@ -44321,7 +44321,7 @@
         <v>0.0645</v>
       </c>
       <c r="J402" t="n">
-        <v>-1.4416</v>
+        <v>-1.4388</v>
       </c>
       <c r="K402" t="n">
         <v>-0.8647</v>
@@ -44340,16 +44340,16 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>-0.553</v>
+        <v>-0.5523</v>
       </c>
       <c r="C403" t="n">
         <v>-0.6768</v>
       </c>
       <c r="D403" t="n">
-        <v>-0.6149</v>
+        <v>-0.6146</v>
       </c>
       <c r="E403" t="n">
-        <v>-0.553</v>
+        <v>-0.5523</v>
       </c>
       <c r="F403" t="n">
         <v>-0.6768</v>
@@ -44364,7 +44364,7 @@
         <v>0.1618</v>
       </c>
       <c r="J403" t="n">
-        <v>-1.4169</v>
+        <v>-1.4141</v>
       </c>
       <c r="K403" t="n">
         <v>-0.7472</v>
@@ -44383,16 +44383,16 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>-0.4322</v>
+        <v>-0.4317</v>
       </c>
       <c r="C404" t="n">
         <v>-0.7622</v>
       </c>
       <c r="D404" t="n">
-        <v>-0.5972</v>
+        <v>-0.5969</v>
       </c>
       <c r="E404" t="n">
-        <v>-0.4322</v>
+        <v>-0.4317</v>
       </c>
       <c r="F404" t="n">
         <v>-0.7622</v>
@@ -44407,7 +44407,7 @@
         <v>0.1649</v>
       </c>
       <c r="J404" t="n">
-        <v>-1.0716</v>
+        <v>-1.0693</v>
       </c>
       <c r="K404" t="n">
         <v>-0.7096</v>
@@ -44426,16 +44426,16 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>-0.4286</v>
+        <v>-0.4281</v>
       </c>
       <c r="C405" t="n">
         <v>-0.8006</v>
       </c>
       <c r="D405" t="n">
-        <v>-0.6146</v>
+        <v>-0.6143</v>
       </c>
       <c r="E405" t="n">
-        <v>-0.4286</v>
+        <v>-0.4281</v>
       </c>
       <c r="F405" t="n">
         <v>-0.8006</v>
@@ -44450,7 +44450,7 @@
         <v>-0.07779999999999999</v>
       </c>
       <c r="J405" t="n">
-        <v>-0.7296</v>
+        <v>-0.7277</v>
       </c>
       <c r="K405" t="n">
         <v>-0.7179</v>
@@ -44469,16 +44469,16 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>-0.482</v>
+        <v>-0.4815</v>
       </c>
       <c r="C406" t="n">
         <v>-0.8399</v>
       </c>
       <c r="D406" t="n">
-        <v>-0.661</v>
+        <v>-0.6607</v>
       </c>
       <c r="E406" t="n">
-        <v>-0.482</v>
+        <v>-0.4815</v>
       </c>
       <c r="F406" t="n">
         <v>-0.8399</v>
@@ -44493,7 +44493,7 @@
         <v>-0.117</v>
       </c>
       <c r="J406" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.955</v>
       </c>
       <c r="K406" t="n">
         <v>-0.6819</v>
@@ -44512,16 +44512,16 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>-0.4276</v>
+        <v>-0.427</v>
       </c>
       <c r="C407" t="n">
         <v>-0.9137999999999999</v>
       </c>
       <c r="D407" t="n">
-        <v>-0.6707</v>
+        <v>-0.6704</v>
       </c>
       <c r="E407" t="n">
-        <v>-0.4276</v>
+        <v>-0.427</v>
       </c>
       <c r="F407" t="n">
         <v>-0.9137999999999999</v>
@@ -44536,7 +44536,7 @@
         <v>-0.0187</v>
       </c>
       <c r="J407" t="n">
-        <v>-1.0509</v>
+        <v>-1.0486</v>
       </c>
       <c r="K407" t="n">
         <v>-0.6617</v>
@@ -44555,16 +44555,16 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>-0.3976</v>
+        <v>-0.3971</v>
       </c>
       <c r="C408" t="n">
         <v>-0.9116</v>
       </c>
       <c r="D408" t="n">
-        <v>-0.6546</v>
+        <v>-0.6543</v>
       </c>
       <c r="E408" t="n">
-        <v>-0.3976</v>
+        <v>-0.3971</v>
       </c>
       <c r="F408" t="n">
         <v>-0.9116</v>
@@ -44579,7 +44579,7 @@
         <v>-0.1878</v>
       </c>
       <c r="J408" t="n">
-        <v>-0.9905</v>
+        <v>-0.9883</v>
       </c>
       <c r="K408" t="n">
         <v>-0.629</v>
@@ -44598,16 +44598,16 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>-0.2525</v>
+        <v>-0.252</v>
       </c>
       <c r="C409" t="n">
         <v>-0.9615</v>
       </c>
       <c r="D409" t="n">
-        <v>-0.607</v>
+        <v>-0.6068</v>
       </c>
       <c r="E409" t="n">
-        <v>-0.2525</v>
+        <v>-0.252</v>
       </c>
       <c r="F409" t="n">
         <v>-0.9615</v>
@@ -44622,7 +44622,7 @@
         <v>-0.1246</v>
       </c>
       <c r="J409" t="n">
-        <v>-0.8337</v>
+        <v>-0.8317</v>
       </c>
       <c r="K409" t="n">
         <v>-0.6002</v>
@@ -44641,16 +44641,16 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>-0.2588</v>
+        <v>-0.2583</v>
       </c>
       <c r="C410" t="n">
         <v>-1.0295</v>
       </c>
       <c r="D410" t="n">
-        <v>-0.6441</v>
+        <v>-0.6439</v>
       </c>
       <c r="E410" t="n">
-        <v>-0.2588</v>
+        <v>-0.2583</v>
       </c>
       <c r="F410" t="n">
         <v>-1.0295</v>
@@ -44665,7 +44665,7 @@
         <v>-0.2919</v>
       </c>
       <c r="J410" t="n">
-        <v>-0.6725</v>
+        <v>-0.6706</v>
       </c>
       <c r="K410" t="n">
         <v>-0.5869</v>
@@ -44684,16 +44684,16 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>-0.2403</v>
+        <v>-0.2398</v>
       </c>
       <c r="C411" t="n">
         <v>-1.0752</v>
       </c>
       <c r="D411" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.6575</v>
       </c>
       <c r="E411" t="n">
-        <v>-0.2403</v>
+        <v>-0.2398</v>
       </c>
       <c r="F411" t="n">
         <v>-1.0752</v>
@@ -44708,7 +44708,7 @@
         <v>-0.2619</v>
       </c>
       <c r="J411" t="n">
-        <v>-0.7812</v>
+        <v>-0.7792</v>
       </c>
       <c r="K411" t="n">
         <v>-0.5758</v>
@@ -44727,16 +44727,16 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>-0.2243</v>
+        <v>-0.2239</v>
       </c>
       <c r="C412" t="n">
         <v>-1.1508</v>
       </c>
       <c r="D412" t="n">
-        <v>-0.6876</v>
+        <v>-0.6873</v>
       </c>
       <c r="E412" t="n">
-        <v>-0.2243</v>
+        <v>-0.2239</v>
       </c>
       <c r="F412" t="n">
         <v>-1.1508</v>
@@ -44751,7 +44751,7 @@
         <v>-0.534</v>
       </c>
       <c r="J412" t="n">
-        <v>-0.5357</v>
+        <v>-0.5341</v>
       </c>
       <c r="K412" t="n">
         <v>-0.5341</v>
@@ -44770,16 +44770,16 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>-0.2385</v>
+        <v>-0.2381</v>
       </c>
       <c r="C413" t="n">
         <v>-1.1658</v>
       </c>
       <c r="D413" t="n">
-        <v>-0.7022</v>
+        <v>-0.7019</v>
       </c>
       <c r="E413" t="n">
-        <v>-0.2385</v>
+        <v>-0.2381</v>
       </c>
       <c r="F413" t="n">
         <v>-1.1658</v>
@@ -44794,7 +44794,7 @@
         <v>-0.3999</v>
       </c>
       <c r="J413" t="n">
-        <v>-0.4982</v>
+        <v>-0.4966</v>
       </c>
       <c r="K413" t="n">
         <v>-0.515</v>
@@ -44813,16 +44813,16 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>-0.1215</v>
+        <v>-0.1211</v>
       </c>
       <c r="C414" t="n">
         <v>-1.157</v>
       </c>
       <c r="D414" t="n">
-        <v>-0.6393</v>
+        <v>-0.6391</v>
       </c>
       <c r="E414" t="n">
-        <v>-0.1215</v>
+        <v>-0.1211</v>
       </c>
       <c r="F414" t="n">
         <v>-1.157</v>
@@ -44837,7 +44837,7 @@
         <v>-0.3494</v>
       </c>
       <c r="J414" t="n">
-        <v>-0.409</v>
+        <v>-0.4075</v>
       </c>
       <c r="K414" t="n">
         <v>-0.4864</v>
@@ -44856,16 +44856,16 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>-0.0447</v>
+        <v>-0.0443</v>
       </c>
       <c r="C415" t="n">
         <v>-1.2376</v>
       </c>
       <c r="D415" t="n">
-        <v>-0.6412</v>
+        <v>-0.6409</v>
       </c>
       <c r="E415" t="n">
-        <v>-0.0447</v>
+        <v>-0.0443</v>
       </c>
       <c r="F415" t="n">
         <v>-1.2376</v>
@@ -44880,7 +44880,7 @@
         <v>-0.2166</v>
       </c>
       <c r="J415" t="n">
-        <v>-0.4844</v>
+        <v>-0.4828</v>
       </c>
       <c r="K415" t="n">
         <v>-0.466</v>
@@ -44899,16 +44899,16 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.01</v>
+        <v>0.0104</v>
       </c>
       <c r="C416" t="n">
         <v>-1.3038</v>
       </c>
       <c r="D416" t="n">
-        <v>-0.6469</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="E416" t="n">
-        <v>0.01</v>
+        <v>0.0104</v>
       </c>
       <c r="F416" t="n">
         <v>-1.3038</v>
@@ -44923,7 +44923,7 @@
         <v>-0.1892</v>
       </c>
       <c r="J416" t="n">
-        <v>-0.5362</v>
+        <v>-0.5345</v>
       </c>
       <c r="K416" t="n">
         <v>-0.4612</v>
@@ -44942,16 +44942,16 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.0413</v>
+        <v>0.0417</v>
       </c>
       <c r="C417" t="n">
         <v>-1.3437</v>
       </c>
       <c r="D417" t="n">
-        <v>-0.6512</v>
+        <v>-0.651</v>
       </c>
       <c r="E417" t="n">
-        <v>0.0413</v>
+        <v>0.0417</v>
       </c>
       <c r="F417" t="n">
         <v>-1.3437</v>
@@ -44966,7 +44966,7 @@
         <v>-0.1524</v>
       </c>
       <c r="J417" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6328</v>
       </c>
       <c r="K417" t="n">
         <v>-0.4451</v>
@@ -44985,16 +44985,16 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>-0.0064</v>
+        <v>-0.006</v>
       </c>
       <c r="C418" t="n">
         <v>-1.3341</v>
       </c>
       <c r="D418" t="n">
-        <v>-0.6703</v>
+        <v>-0.6701</v>
       </c>
       <c r="E418" t="n">
-        <v>-0.0064</v>
+        <v>-0.006</v>
       </c>
       <c r="F418" t="n">
         <v>-1.3341</v>
@@ -45009,7 +45009,7 @@
         <v>-0.3562</v>
       </c>
       <c r="J418" t="n">
-        <v>-0.4844</v>
+        <v>-0.4828</v>
       </c>
       <c r="K418" t="n">
         <v>-0.4027</v>
@@ -45028,16 +45028,16 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>-0.0786</v>
+        <v>-0.0784</v>
       </c>
       <c r="C419" t="n">
         <v>-1.3699</v>
       </c>
       <c r="D419" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.7241</v>
       </c>
       <c r="E419" t="n">
-        <v>-0.0786</v>
+        <v>-0.0784</v>
       </c>
       <c r="F419" t="n">
         <v>-1.3699</v>
@@ -45052,7 +45052,7 @@
         <v>-0.8599</v>
       </c>
       <c r="J419" t="n">
-        <v>0.0334</v>
+        <v>0.0343</v>
       </c>
       <c r="K419" t="n">
         <v>-0.38</v>
@@ -45071,16 +45071,16 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>-0.2242</v>
+        <v>-0.2239</v>
       </c>
       <c r="C420" t="n">
         <v>-1.2631</v>
       </c>
       <c r="D420" t="n">
-        <v>-0.7436</v>
+        <v>-0.7435</v>
       </c>
       <c r="E420" t="n">
-        <v>-0.2242</v>
+        <v>-0.2239</v>
       </c>
       <c r="F420" t="n">
         <v>-1.2631</v>
@@ -45095,7 +45095,7 @@
         <v>-1.1295</v>
       </c>
       <c r="J420" t="n">
-        <v>0.0465</v>
+        <v>0.0475</v>
       </c>
       <c r="K420" t="n">
         <v>-0.3541</v>
@@ -45114,16 +45114,16 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>-0.4098</v>
+        <v>-0.4096</v>
       </c>
       <c r="C421" t="n">
         <v>-1.1211</v>
       </c>
       <c r="D421" t="n">
-        <v>-0.7654</v>
+        <v>-0.7653</v>
       </c>
       <c r="E421" t="n">
-        <v>-0.4098</v>
+        <v>-0.4096</v>
       </c>
       <c r="F421" t="n">
         <v>-1.1211</v>
@@ -45138,7 +45138,7 @@
         <v>-1.447</v>
       </c>
       <c r="J421" t="n">
-        <v>0.1384</v>
+        <v>0.1392</v>
       </c>
       <c r="K421" t="n">
         <v>-0.3399</v>
@@ -45157,16 +45157,16 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>-0.436</v>
+        <v>-0.4357</v>
       </c>
       <c r="C422" t="n">
         <v>-0.8888</v>
       </c>
       <c r="D422" t="n">
-        <v>-0.6624</v>
+        <v>-0.6622</v>
       </c>
       <c r="E422" t="n">
-        <v>-0.436</v>
+        <v>-0.4357</v>
       </c>
       <c r="F422" t="n">
         <v>-0.8888</v>
@@ -45181,7 +45181,7 @@
         <v>-1.4818</v>
       </c>
       <c r="J422" t="n">
-        <v>-0.1818</v>
+        <v>-0.1806</v>
       </c>
       <c r="K422" t="n">
         <v>-0.2949</v>
@@ -45200,16 +45200,16 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>-0.3868</v>
+        <v>-0.3866</v>
       </c>
       <c r="C423" t="n">
         <v>-0.7415</v>
       </c>
       <c r="D423" t="n">
-        <v>-0.5641</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E423" t="n">
-        <v>-0.3868</v>
+        <v>-0.3866</v>
       </c>
       <c r="F423" t="n">
         <v>-0.7415</v>
@@ -45224,7 +45224,7 @@
         <v>-1.3904</v>
       </c>
       <c r="J423" t="n">
-        <v>-0.0965</v>
+        <v>-0.0954</v>
       </c>
       <c r="K423" t="n">
         <v>-0.273</v>
@@ -45243,16 +45243,16 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>-0.2824</v>
+        <v>-0.2821</v>
       </c>
       <c r="C424" t="n">
         <v>-0.5429</v>
       </c>
       <c r="D424" t="n">
-        <v>-0.4126</v>
+        <v>-0.4125</v>
       </c>
       <c r="E424" t="n">
-        <v>-0.2824</v>
+        <v>-0.2821</v>
       </c>
       <c r="F424" t="n">
         <v>-0.5429</v>
@@ -45267,7 +45267,7 @@
         <v>-1.0802</v>
       </c>
       <c r="J424" t="n">
-        <v>0.0622</v>
+        <v>0.0631</v>
       </c>
       <c r="K424" t="n">
         <v>-0.2706</v>
@@ -45286,16 +45286,16 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>-0.2679</v>
+        <v>-0.2676</v>
       </c>
       <c r="C425" t="n">
         <v>-0.3867</v>
       </c>
       <c r="D425" t="n">
-        <v>-0.3273</v>
+        <v>-0.3271</v>
       </c>
       <c r="E425" t="n">
-        <v>-0.2679</v>
+        <v>-0.2676</v>
       </c>
       <c r="F425" t="n">
         <v>-0.3867</v>
@@ -45310,7 +45310,7 @@
         <v>-0.9503</v>
       </c>
       <c r="J425" t="n">
-        <v>-0.0876</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="K425" t="n">
         <v>-0.2569</v>
@@ -45329,16 +45329,16 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>-0.3771</v>
+        <v>-0.3769</v>
       </c>
       <c r="C426" t="n">
         <v>-0.1404</v>
       </c>
       <c r="D426" t="n">
-        <v>-0.2588</v>
+        <v>-0.2586</v>
       </c>
       <c r="E426" t="n">
-        <v>-0.3771</v>
+        <v>-0.3769</v>
       </c>
       <c r="F426" t="n">
         <v>-0.1404</v>
@@ -45353,7 +45353,7 @@
         <v>-0.976</v>
       </c>
       <c r="J426" t="n">
-        <v>-0.0316</v>
+        <v>-0.0305</v>
       </c>
       <c r="K426" t="n">
         <v>-0.1996</v>
@@ -45372,16 +45372,16 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>-0.4538</v>
+        <v>-0.4536</v>
       </c>
       <c r="C427" t="n">
         <v>-0.0102</v>
       </c>
       <c r="D427" t="n">
-        <v>-0.232</v>
+        <v>-0.2319</v>
       </c>
       <c r="E427" t="n">
-        <v>-0.4538</v>
+        <v>-0.4536</v>
       </c>
       <c r="F427" t="n">
         <v>-0.0102</v>
@@ -45396,7 +45396,7 @@
         <v>-0.9318</v>
       </c>
       <c r="J427" t="n">
-        <v>-0.0016</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K427" t="n">
         <v>-0.1858</v>
@@ -45415,16 +45415,16 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>-0.5806</v>
+        <v>-0.5803</v>
       </c>
       <c r="C428" t="n">
         <v>0.0439</v>
       </c>
       <c r="D428" t="n">
-        <v>-0.2683</v>
+        <v>-0.2682</v>
       </c>
       <c r="E428" t="n">
-        <v>-0.5806</v>
+        <v>-0.5803</v>
       </c>
       <c r="F428" t="n">
         <v>0.0439</v>
@@ -45439,7 +45439,7 @@
         <v>-1.0386</v>
       </c>
       <c r="J428" t="n">
-        <v>-0.17</v>
+        <v>-0.1688</v>
       </c>
       <c r="K428" t="n">
         <v>-0.1669</v>
@@ -45458,16 +45458,16 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.5829</v>
       </c>
       <c r="C429" t="n">
         <v>0.0348</v>
       </c>
       <c r="D429" t="n">
-        <v>-0.2742</v>
+        <v>-0.2741</v>
       </c>
       <c r="E429" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.5829</v>
       </c>
       <c r="F429" t="n">
         <v>0.0348</v>
@@ -45482,7 +45482,7 @@
         <v>-0.9852</v>
       </c>
       <c r="J429" t="n">
-        <v>-0.1171</v>
+        <v>-0.1159</v>
       </c>
       <c r="K429" t="n">
         <v>-0.1327</v>
@@ -45501,16 +45501,16 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>-0.6766</v>
+        <v>-0.6762</v>
       </c>
       <c r="C430" t="n">
         <v>0.0635</v>
       </c>
       <c r="D430" t="n">
-        <v>-0.3066</v>
+        <v>-0.3064</v>
       </c>
       <c r="E430" t="n">
-        <v>-0.6766</v>
+        <v>-0.6762</v>
       </c>
       <c r="F430" t="n">
         <v>0.0635</v>
@@ -45525,7 +45525,7 @@
         <v>-1.1501</v>
       </c>
       <c r="J430" t="n">
-        <v>-0.3438</v>
+        <v>-0.3424</v>
       </c>
       <c r="K430" t="n">
         <v>-0.1115</v>
@@ -45544,16 +45544,16 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>-0.7841</v>
+        <v>-0.7836</v>
       </c>
       <c r="C431" t="n">
         <v>0.0809</v>
       </c>
       <c r="D431" t="n">
-        <v>-0.3516</v>
+        <v>-0.3514</v>
       </c>
       <c r="E431" t="n">
-        <v>-0.7841</v>
+        <v>-0.7836</v>
       </c>
       <c r="F431" t="n">
         <v>0.0809</v>
@@ -45568,7 +45568,7 @@
         <v>-1.1452</v>
       </c>
       <c r="J431" t="n">
-        <v>-0.8989</v>
+        <v>-0.8968</v>
       </c>
       <c r="K431" t="n">
         <v>-0.0791</v>
@@ -45587,16 +45587,16 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>-0.7226</v>
+        <v>-0.722</v>
       </c>
       <c r="C432" t="n">
         <v>0.0872</v>
       </c>
       <c r="D432" t="n">
-        <v>-0.3177</v>
+        <v>-0.3174</v>
       </c>
       <c r="E432" t="n">
-        <v>-0.7226</v>
+        <v>-0.722</v>
       </c>
       <c r="F432" t="n">
         <v>0.0872</v>
@@ -45611,7 +45611,7 @@
         <v>-1.1861</v>
       </c>
       <c r="J432" t="n">
-        <v>-0.8195</v>
+        <v>-0.8174</v>
       </c>
       <c r="K432" t="n">
         <v>-0.0348</v>
@@ -45630,16 +45630,16 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>-0.6492</v>
+        <v>-0.6488</v>
       </c>
       <c r="C433" t="n">
         <v>0.1189</v>
       </c>
       <c r="D433" t="n">
-        <v>-0.2652</v>
+        <v>-0.2649</v>
       </c>
       <c r="E433" t="n">
-        <v>-0.6492</v>
+        <v>-0.6488</v>
       </c>
       <c r="F433" t="n">
         <v>0.1189</v>
@@ -45654,7 +45654,7 @@
         <v>-1.1439</v>
       </c>
       <c r="J433" t="n">
-        <v>-0.5913</v>
+        <v>-0.5896</v>
       </c>
       <c r="K433" t="n">
         <v>-0.0368</v>
@@ -45673,16 +45673,16 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>-0.5629</v>
+        <v>-0.5625</v>
       </c>
       <c r="C434" t="n">
         <v>0.1466</v>
       </c>
       <c r="D434" t="n">
-        <v>-0.2081</v>
+        <v>-0.208</v>
       </c>
       <c r="E434" t="n">
-        <v>-0.5629</v>
+        <v>-0.5625</v>
       </c>
       <c r="F434" t="n">
         <v>0.1466</v>
@@ -45697,7 +45697,7 @@
         <v>-1.0506</v>
       </c>
       <c r="J434" t="n">
-        <v>-0.4083</v>
+        <v>-0.4068</v>
       </c>
       <c r="K434" t="n">
         <v>0.0356</v>
@@ -45716,16 +45716,16 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>-0.597</v>
+        <v>-0.5966</v>
       </c>
       <c r="C435" t="n">
         <v>0.1372</v>
       </c>
       <c r="D435" t="n">
-        <v>-0.2299</v>
+        <v>-0.2297</v>
       </c>
       <c r="E435" t="n">
-        <v>-0.597</v>
+        <v>-0.5966</v>
       </c>
       <c r="F435" t="n">
         <v>0.1372</v>
@@ -45740,7 +45740,7 @@
         <v>-1.1399</v>
       </c>
       <c r="J435" t="n">
-        <v>-0.3169</v>
+        <v>-0.3155</v>
       </c>
       <c r="K435" t="n">
         <v>0.0433</v>
@@ -45759,16 +45759,16 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>-0.7148</v>
+        <v>-0.7144</v>
       </c>
       <c r="C436" t="n">
         <v>0.1902</v>
       </c>
       <c r="D436" t="n">
-        <v>-0.2623</v>
+        <v>-0.2621</v>
       </c>
       <c r="E436" t="n">
-        <v>-0.7148</v>
+        <v>-0.7144</v>
       </c>
       <c r="F436" t="n">
         <v>0.1902</v>
@@ -45783,7 +45783,7 @@
         <v>-1.0985</v>
       </c>
       <c r="J436" t="n">
-        <v>-0.6936</v>
+        <v>-0.6917</v>
       </c>
       <c r="K436" t="n">
         <v>0.0646</v>
@@ -45802,19 +45802,19 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>-0.641</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="C437" t="n">
-        <v>0.2236</v>
+        <v>0.2235</v>
       </c>
       <c r="D437" t="n">
-        <v>-0.2087</v>
+        <v>-0.2085</v>
       </c>
       <c r="E437" t="n">
-        <v>-0.641</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="F437" t="n">
-        <v>0.2236</v>
+        <v>0.2235</v>
       </c>
       <c r="G437" t="n">
         <v>-0.314</v>
@@ -45826,7 +45826,7 @@
         <v>-0.9045</v>
       </c>
       <c r="J437" t="n">
-        <v>-0.614</v>
+        <v>-0.6122</v>
       </c>
       <c r="K437" t="n">
         <v>0.09429999999999999</v>
@@ -45845,16 +45845,16 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>-0.6199</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="C438" t="n">
         <v>0.2809</v>
       </c>
       <c r="D438" t="n">
-        <v>-0.1695</v>
+        <v>-0.1693</v>
       </c>
       <c r="E438" t="n">
-        <v>-0.6199</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="F438" t="n">
         <v>0.2809</v>
@@ -45869,7 +45869,7 @@
         <v>-1.0681</v>
       </c>
       <c r="J438" t="n">
-        <v>-0.4517</v>
+        <v>-0.4501</v>
       </c>
       <c r="K438" t="n">
         <v>0.1207</v>
@@ -45888,16 +45888,16 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>-0.6594</v>
+        <v>-0.659</v>
       </c>
       <c r="C439" t="n">
         <v>0.2448</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.2073</v>
+        <v>-0.2071</v>
       </c>
       <c r="E439" t="n">
-        <v>-0.6594</v>
+        <v>-0.659</v>
       </c>
       <c r="F439" t="n">
         <v>0.2448</v>
@@ -45912,7 +45912,7 @@
         <v>-1.1758</v>
       </c>
       <c r="J439" t="n">
-        <v>-0.3637</v>
+        <v>-0.3622</v>
       </c>
       <c r="K439" t="n">
         <v>0.1622</v>
@@ -45931,16 +45931,16 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>-0.7373</v>
+        <v>-0.7369</v>
       </c>
       <c r="C440" t="n">
         <v>0.2835</v>
       </c>
       <c r="D440" t="n">
-        <v>-0.2269</v>
+        <v>-0.2267</v>
       </c>
       <c r="E440" t="n">
-        <v>-0.7373</v>
+        <v>-0.7369</v>
       </c>
       <c r="F440" t="n">
         <v>0.2835</v>
@@ -45955,7 +45955,7 @@
         <v>-1.3008</v>
       </c>
       <c r="J440" t="n">
-        <v>-0.4183</v>
+        <v>-0.4167</v>
       </c>
       <c r="K440" t="n">
         <v>0.1888</v>
@@ -45974,16 +45974,16 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>-0.6973</v>
+        <v>-0.697</v>
       </c>
       <c r="C441" t="n">
         <v>0.3252</v>
       </c>
       <c r="D441" t="n">
-        <v>-0.1861</v>
+        <v>-0.1859</v>
       </c>
       <c r="E441" t="n">
-        <v>-0.6973</v>
+        <v>-0.697</v>
       </c>
       <c r="F441" t="n">
         <v>0.3252</v>
@@ -45998,7 +45998,7 @@
         <v>-1.4006</v>
       </c>
       <c r="J441" t="n">
-        <v>-0.2311</v>
+        <v>-0.2298</v>
       </c>
       <c r="K441" t="n">
         <v>0.2434</v>
@@ -46017,16 +46017,16 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.739</v>
       </c>
       <c r="C442" t="n">
         <v>0.2545</v>
       </c>
       <c r="D442" t="n">
-        <v>-0.2425</v>
+        <v>-0.2423</v>
       </c>
       <c r="E442" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.739</v>
       </c>
       <c r="F442" t="n">
         <v>0.2545</v>
@@ -46041,7 +46041,7 @@
         <v>-1.4188</v>
       </c>
       <c r="J442" t="n">
-        <v>-0.3389</v>
+        <v>-0.3374</v>
       </c>
       <c r="K442" t="n">
         <v>0.2451</v>
@@ -46060,16 +46060,16 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>-0.6103</v>
+        <v>-0.61</v>
       </c>
       <c r="C443" t="n">
         <v>0.2964</v>
       </c>
       <c r="D443" t="n">
-        <v>-0.1569</v>
+        <v>-0.1568</v>
       </c>
       <c r="E443" t="n">
-        <v>-0.6103</v>
+        <v>-0.61</v>
       </c>
       <c r="F443" t="n">
         <v>0.2964</v>
@@ -46084,7 +46084,7 @@
         <v>-1.4929</v>
       </c>
       <c r="J443" t="n">
-        <v>0.0461</v>
+        <v>0.0471</v>
       </c>
       <c r="K443" t="n">
         <v>0.2878</v>
@@ -46103,16 +46103,16 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>-0.609</v>
+        <v>-0.6088</v>
       </c>
       <c r="C444" t="n">
         <v>0.2765</v>
       </c>
       <c r="D444" t="n">
-        <v>-0.1663</v>
+        <v>-0.1661</v>
       </c>
       <c r="E444" t="n">
-        <v>-0.609</v>
+        <v>-0.6088</v>
       </c>
       <c r="F444" t="n">
         <v>0.2765</v>
@@ -46127,7 +46127,7 @@
         <v>-1.4219</v>
       </c>
       <c r="J444" t="n">
-        <v>-0.0011</v>
+        <v>-0.0001</v>
       </c>
       <c r="K444" t="n">
         <v>0.3036</v>
@@ -46146,16 +46146,16 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6655</v>
       </c>
       <c r="C445" t="n">
         <v>0.2383</v>
       </c>
       <c r="D445" t="n">
-        <v>-0.2137</v>
+        <v>-0.2136</v>
       </c>
       <c r="E445" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6655</v>
       </c>
       <c r="F445" t="n">
         <v>0.2383</v>
@@ -46170,7 +46170,7 @@
         <v>-1.3708</v>
       </c>
       <c r="J445" t="n">
-        <v>-0.2281</v>
+        <v>-0.2268</v>
       </c>
       <c r="K445" t="n">
         <v>0.3418</v>
@@ -46189,16 +46189,16 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6766</v>
       </c>
       <c r="C446" t="n">
         <v>0.2781</v>
       </c>
       <c r="D446" t="n">
-        <v>-0.1994</v>
+        <v>-0.1993</v>
       </c>
       <c r="E446" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6766</v>
       </c>
       <c r="F446" t="n">
         <v>0.2781</v>
@@ -46213,7 +46213,7 @@
         <v>-1.3571</v>
       </c>
       <c r="J446" t="n">
-        <v>-0.2625</v>
+        <v>-0.2611</v>
       </c>
       <c r="K446" t="n">
         <v>0.3566</v>
@@ -46232,16 +46232,16 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>-0.6872</v>
+        <v>-0.6869</v>
       </c>
       <c r="C447" t="n">
         <v>0.2636</v>
       </c>
       <c r="D447" t="n">
-        <v>-0.2118</v>
+        <v>-0.2116</v>
       </c>
       <c r="E447" t="n">
-        <v>-0.6872</v>
+        <v>-0.6869</v>
       </c>
       <c r="F447" t="n">
         <v>0.2636</v>
@@ -46256,7 +46256,7 @@
         <v>-1.304</v>
       </c>
       <c r="J447" t="n">
-        <v>-0.3945</v>
+        <v>-0.393</v>
       </c>
       <c r="K447" t="n">
         <v>0.4021</v>
@@ -46275,7 +46275,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>-0.4019</v>
+        <v>-0.4018</v>
       </c>
       <c r="C448" t="n">
         <v>0.2413</v>
@@ -46284,7 +46284,7 @@
         <v>-0.0803</v>
       </c>
       <c r="E448" t="n">
-        <v>-0.4019</v>
+        <v>-0.4018</v>
       </c>
       <c r="F448" t="n">
         <v>0.2413</v>
@@ -46299,7 +46299,7 @@
         <v>-1.3311</v>
       </c>
       <c r="J448" t="n">
-        <v>0.5921</v>
+        <v>0.5924</v>
       </c>
       <c r="K448" t="n">
         <v>0.4044</v>
@@ -46342,7 +46342,7 @@
         <v>-1.1574</v>
       </c>
       <c r="J449" t="n">
-        <v>0.6629</v>
+        <v>0.6631</v>
       </c>
       <c r="K449" t="n">
         <v>0.4716</v>
@@ -46361,16 +46361,16 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>-0.3986</v>
+        <v>-0.3985</v>
       </c>
       <c r="C450" t="n">
         <v>0.2964</v>
       </c>
       <c r="D450" t="n">
-        <v>-0.0511</v>
+        <v>-0.051</v>
       </c>
       <c r="E450" t="n">
-        <v>-0.3986</v>
+        <v>-0.3985</v>
       </c>
       <c r="F450" t="n">
         <v>0.2964</v>
@@ -46385,7 +46385,7 @@
         <v>-1.2843</v>
       </c>
       <c r="J450" t="n">
-        <v>0.2346</v>
+        <v>0.2353</v>
       </c>
       <c r="K450" t="n">
         <v>0.483</v>
@@ -46404,16 +46404,16 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>-0.3436</v>
+        <v>-0.3434</v>
       </c>
       <c r="C451" t="n">
         <v>0.2832</v>
       </c>
       <c r="D451" t="n">
-        <v>-0.0302</v>
+        <v>-0.0301</v>
       </c>
       <c r="E451" t="n">
-        <v>-0.3436</v>
+        <v>-0.3434</v>
       </c>
       <c r="F451" t="n">
         <v>0.2832</v>
@@ -46428,7 +46428,7 @@
         <v>-1.3191</v>
       </c>
       <c r="J451" t="n">
-        <v>0.4242</v>
+        <v>0.4247</v>
       </c>
       <c r="K451" t="n">
         <v>0.5094</v>
@@ -46447,16 +46447,16 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>-0.3028</v>
+        <v>-0.3027</v>
       </c>
       <c r="C452" t="n">
         <v>0.2795</v>
       </c>
       <c r="D452" t="n">
-        <v>-0.0117</v>
+        <v>-0.0116</v>
       </c>
       <c r="E452" t="n">
-        <v>-0.3028</v>
+        <v>-0.3027</v>
       </c>
       <c r="F452" t="n">
         <v>0.2795</v>
@@ -46471,7 +46471,7 @@
         <v>-1.37</v>
       </c>
       <c r="J452" t="n">
-        <v>0.4331</v>
+        <v>0.4336</v>
       </c>
       <c r="K452" t="n">
         <v>0.476</v>
@@ -46490,16 +46490,16 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>-0.3312</v>
+        <v>-0.3311</v>
       </c>
       <c r="C453" t="n">
         <v>0.2512</v>
       </c>
       <c r="D453" t="n">
-        <v>-0.04</v>
+        <v>-0.0399</v>
       </c>
       <c r="E453" t="n">
-        <v>-0.3312</v>
+        <v>-0.3311</v>
       </c>
       <c r="F453" t="n">
         <v>0.2512</v>
@@ -46514,7 +46514,7 @@
         <v>-1.5231</v>
       </c>
       <c r="J453" t="n">
-        <v>0.4622</v>
+        <v>0.4626</v>
       </c>
       <c r="K453" t="n">
         <v>0.4155</v>
@@ -46533,16 +46533,16 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>-0.3571</v>
+        <v>-0.357</v>
       </c>
       <c r="C454" t="n">
         <v>0.276</v>
       </c>
       <c r="D454" t="n">
-        <v>-0.0406</v>
+        <v>-0.0405</v>
       </c>
       <c r="E454" t="n">
-        <v>-0.3571</v>
+        <v>-0.357</v>
       </c>
       <c r="F454" t="n">
         <v>0.276</v>
@@ -46557,7 +46557,7 @@
         <v>-1.6077</v>
       </c>
       <c r="J454" t="n">
-        <v>0.4231</v>
+        <v>0.4236</v>
       </c>
       <c r="K454" t="n">
         <v>0.3421</v>
@@ -46576,16 +46576,16 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>-0.4768</v>
+        <v>-0.4766</v>
       </c>
       <c r="C455" t="n">
         <v>0.2627</v>
       </c>
       <c r="D455" t="n">
-        <v>-0.1071</v>
+        <v>-0.1069</v>
       </c>
       <c r="E455" t="n">
-        <v>-0.4768</v>
+        <v>-0.4766</v>
       </c>
       <c r="F455" t="n">
         <v>0.2627</v>
@@ -46600,7 +46600,7 @@
         <v>-1.6449</v>
       </c>
       <c r="J455" t="n">
-        <v>0.0833</v>
+        <v>0.0842</v>
       </c>
       <c r="K455" t="n">
         <v>0.3111</v>
@@ -46619,7 +46619,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>-0.3844</v>
+        <v>-0.3843</v>
       </c>
       <c r="C456" t="n">
         <v>0.3133</v>
@@ -46628,7 +46628,7 @@
         <v>-0.0355</v>
       </c>
       <c r="E456" t="n">
-        <v>-0.3844</v>
+        <v>-0.3843</v>
       </c>
       <c r="F456" t="n">
         <v>0.3133</v>
@@ -46643,7 +46643,7 @@
         <v>-1.563</v>
       </c>
       <c r="J456" t="n">
-        <v>0.3048</v>
+        <v>0.3054</v>
       </c>
       <c r="K456" t="n">
         <v>0.2813</v>
@@ -46662,16 +46662,16 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>-0.3785</v>
+        <v>-0.3783</v>
       </c>
       <c r="C457" t="n">
         <v>0.2225</v>
       </c>
       <c r="D457" t="n">
-        <v>-0.078</v>
+        <v>-0.0779</v>
       </c>
       <c r="E457" t="n">
-        <v>-0.3785</v>
+        <v>-0.3783</v>
       </c>
       <c r="F457" t="n">
         <v>0.2225</v>
@@ -46686,7 +46686,7 @@
         <v>-1.5668</v>
       </c>
       <c r="J457" t="n">
-        <v>0.1937</v>
+        <v>0.1945</v>
       </c>
       <c r="K457" t="n">
         <v>0.1903</v>
@@ -46705,16 +46705,16 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>-0.4557</v>
+        <v>-0.4554</v>
       </c>
       <c r="C458" t="n">
         <v>0.2483</v>
       </c>
       <c r="D458" t="n">
-        <v>-0.1037</v>
+        <v>-0.1035</v>
       </c>
       <c r="E458" t="n">
-        <v>-0.4557</v>
+        <v>-0.4554</v>
       </c>
       <c r="F458" t="n">
         <v>0.2483</v>
@@ -46729,7 +46729,7 @@
         <v>-1.6108</v>
       </c>
       <c r="J458" t="n">
-        <v>-0.095</v>
+        <v>-0.0939</v>
       </c>
       <c r="K458" t="n">
         <v>0.1659</v>
@@ -46748,16 +46748,16 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>-0.3426</v>
+        <v>-0.3424</v>
       </c>
       <c r="C459" t="n">
         <v>0.2593</v>
       </c>
       <c r="D459" t="n">
-        <v>-0.0416</v>
+        <v>-0.0415</v>
       </c>
       <c r="E459" t="n">
-        <v>-0.3426</v>
+        <v>-0.3424</v>
       </c>
       <c r="F459" t="n">
         <v>0.2593</v>
@@ -46772,7 +46772,7 @@
         <v>-1.448</v>
       </c>
       <c r="J459" t="n">
-        <v>0.1755</v>
+        <v>0.1763</v>
       </c>
       <c r="K459" t="n">
         <v>0.1338</v>
@@ -46791,16 +46791,16 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>-0.472</v>
+        <v>-0.4715</v>
       </c>
       <c r="C460" t="n">
         <v>0.2539</v>
       </c>
       <c r="D460" t="n">
-        <v>-0.109</v>
+        <v>-0.1088</v>
       </c>
       <c r="E460" t="n">
-        <v>-0.472</v>
+        <v>-0.4715</v>
       </c>
       <c r="F460" t="n">
         <v>0.2539</v>
@@ -46815,7 +46815,7 @@
         <v>-1.1901</v>
       </c>
       <c r="J460" t="n">
-        <v>-0.7196</v>
+        <v>-0.7177</v>
       </c>
       <c r="K460" t="n">
         <v>0.0808</v>
@@ -46834,16 +46834,16 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>-0.4052</v>
+        <v>-0.4049</v>
       </c>
       <c r="C461" t="n">
         <v>0.2694</v>
       </c>
       <c r="D461" t="n">
-        <v>-0.0679</v>
+        <v>-0.0678</v>
       </c>
       <c r="E461" t="n">
-        <v>-0.4052</v>
+        <v>-0.4049</v>
       </c>
       <c r="F461" t="n">
         <v>0.2694</v>
@@ -46858,7 +46858,7 @@
         <v>-1.2692</v>
       </c>
       <c r="J461" t="n">
-        <v>-0.2385</v>
+        <v>-0.2371</v>
       </c>
       <c r="K461" t="n">
         <v>0.0398</v>
@@ -46877,16 +46877,16 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>-0.5032</v>
+        <v>-0.5029</v>
       </c>
       <c r="C462" t="n">
         <v>0.2196</v>
       </c>
       <c r="D462" t="n">
-        <v>-0.1418</v>
+        <v>-0.1416</v>
       </c>
       <c r="E462" t="n">
-        <v>-0.5032</v>
+        <v>-0.5029</v>
       </c>
       <c r="F462" t="n">
         <v>0.2196</v>
@@ -46901,7 +46901,7 @@
         <v>-1.4154</v>
       </c>
       <c r="J462" t="n">
-        <v>-0.1834</v>
+        <v>-0.1822</v>
       </c>
       <c r="K462" t="n">
         <v>-0.032</v>
@@ -46920,16 +46920,16 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>-0.4251</v>
+        <v>-0.4249</v>
       </c>
       <c r="C463" t="n">
         <v>0.222</v>
       </c>
       <c r="D463" t="n">
-        <v>-0.1016</v>
+        <v>-0.1015</v>
       </c>
       <c r="E463" t="n">
-        <v>-0.4251</v>
+        <v>-0.4249</v>
       </c>
       <c r="F463" t="n">
         <v>0.222</v>
@@ -46944,7 +46944,7 @@
         <v>-1.4755</v>
       </c>
       <c r="J463" t="n">
-        <v>0.1741</v>
+        <v>0.1749</v>
       </c>
       <c r="K463" t="n">
         <v>-0.1016</v>
@@ -46963,16 +46963,16 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>-0.4731</v>
+        <v>-0.4729</v>
       </c>
       <c r="C464" t="n">
         <v>0.2796</v>
       </c>
       <c r="D464" t="n">
-        <v>-0.0968</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="E464" t="n">
-        <v>-0.4731</v>
+        <v>-0.4729</v>
       </c>
       <c r="F464" t="n">
         <v>0.2796</v>
@@ -46987,7 +46987,7 @@
         <v>-1.4801</v>
       </c>
       <c r="J464" t="n">
-        <v>-0.0091</v>
+        <v>-0.0081</v>
       </c>
       <c r="K464" t="n">
         <v>0.1036</v>
@@ -47006,16 +47006,16 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>-0.4815</v>
+        <v>-0.4812</v>
       </c>
       <c r="C465" t="n">
         <v>0.3584</v>
       </c>
       <c r="D465" t="n">
-        <v>-0.0616</v>
+        <v>-0.0614</v>
       </c>
       <c r="E465" t="n">
-        <v>-0.4815</v>
+        <v>-0.4812</v>
       </c>
       <c r="F465" t="n">
         <v>0.3584</v>
@@ -47030,7 +47030,7 @@
         <v>-1.4674</v>
       </c>
       <c r="J465" t="n">
-        <v>-0.1618</v>
+        <v>-0.1606</v>
       </c>
       <c r="K465" t="n">
         <v>0.2462</v>
@@ -47049,16 +47049,16 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>-0.3995</v>
+        <v>-0.3993</v>
       </c>
       <c r="C466" t="n">
         <v>0.397</v>
       </c>
       <c r="D466" t="n">
-        <v>-0.0012</v>
+        <v>-0.0011</v>
       </c>
       <c r="E466" t="n">
-        <v>-0.3995</v>
+        <v>-0.3993</v>
       </c>
       <c r="F466" t="n">
         <v>0.397</v>
@@ -47073,7 +47073,7 @@
         <v>-1.4441</v>
       </c>
       <c r="J466" t="n">
-        <v>0.0386</v>
+        <v>0.0395</v>
       </c>
       <c r="K466" t="n">
         <v>0.4041</v>
@@ -47092,16 +47092,16 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>-0.2584</v>
+        <v>-0.2583</v>
       </c>
       <c r="C467" t="n">
         <v>0.4715</v>
       </c>
       <c r="D467" t="n">
-        <v>0.1065</v>
+        <v>0.1066</v>
       </c>
       <c r="E467" t="n">
-        <v>-0.2584</v>
+        <v>-0.2583</v>
       </c>
       <c r="F467" t="n">
         <v>0.4715</v>
@@ -47116,7 +47116,7 @@
         <v>-1.3593</v>
       </c>
       <c r="J467" t="n">
-        <v>0.5047</v>
+        <v>0.5051</v>
       </c>
       <c r="K467" t="n">
         <v>0.5958</v>
@@ -47135,16 +47135,16 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>-0.3492</v>
+        <v>-0.349</v>
       </c>
       <c r="C468" t="n">
         <v>0.5625</v>
       </c>
       <c r="D468" t="n">
-        <v>0.1067</v>
+        <v>0.1068</v>
       </c>
       <c r="E468" t="n">
-        <v>-0.3492</v>
+        <v>-0.349</v>
       </c>
       <c r="F468" t="n">
         <v>0.5625</v>
@@ -47159,7 +47159,7 @@
         <v>-1.2141</v>
       </c>
       <c r="J468" t="n">
-        <v>0.0594</v>
+        <v>0.0604</v>
       </c>
       <c r="K468" t="n">
         <v>0.7585</v>
@@ -47178,16 +47178,16 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>-0.1419</v>
+        <v>-0.1417</v>
       </c>
       <c r="C469" t="n">
         <v>0.6045</v>
       </c>
       <c r="D469" t="n">
-        <v>0.2313</v>
+        <v>0.2314</v>
       </c>
       <c r="E469" t="n">
-        <v>-0.1419</v>
+        <v>-0.1417</v>
       </c>
       <c r="F469" t="n">
         <v>0.6045</v>
@@ -47202,7 +47202,7 @@
         <v>-1.0105</v>
       </c>
       <c r="J469" t="n">
-        <v>0.1664</v>
+        <v>0.1673</v>
       </c>
       <c r="K469" t="n">
         <v>0.9243</v>
@@ -47227,7 +47227,7 @@
         <v>0.6699000000000001</v>
       </c>
       <c r="D470" t="n">
-        <v>0.3112</v>
+        <v>0.3113</v>
       </c>
       <c r="E470" t="n">
         <v>-0.0474</v>
@@ -47245,7 +47245,7 @@
         <v>-0.6746</v>
       </c>
       <c r="J470" t="n">
-        <v>0.582</v>
+        <v>0.5823</v>
       </c>
       <c r="K470" t="n">
         <v>1.0928</v>
@@ -47264,16 +47264,16 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>-0.0166</v>
+        <v>-0.0165</v>
       </c>
       <c r="C471" t="n">
         <v>0.727</v>
       </c>
       <c r="D471" t="n">
-        <v>0.3552</v>
+        <v>0.3553</v>
       </c>
       <c r="E471" t="n">
-        <v>-0.0166</v>
+        <v>-0.0165</v>
       </c>
       <c r="F471" t="n">
         <v>0.727</v>
@@ -47288,7 +47288,7 @@
         <v>-0.4319</v>
       </c>
       <c r="J471" t="n">
-        <v>0.35</v>
+        <v>0.3506</v>
       </c>
       <c r="K471" t="n">
         <v>1.2749</v>
@@ -47307,16 +47307,16 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.0735</v>
+        <v>0.0736</v>
       </c>
       <c r="C472" t="n">
         <v>0.7711</v>
       </c>
       <c r="D472" t="n">
-        <v>0.4223</v>
+        <v>0.4224</v>
       </c>
       <c r="E472" t="n">
-        <v>0.0735</v>
+        <v>0.0736</v>
       </c>
       <c r="F472" t="n">
         <v>0.7711</v>
@@ -47331,7 +47331,7 @@
         <v>-0.3739</v>
       </c>
       <c r="J472" t="n">
-        <v>0.6838</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K472" t="n">
         <v>1.4309</v>
@@ -47350,7 +47350,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.2295</v>
+        <v>0.2294</v>
       </c>
       <c r="C473" t="n">
         <v>0.9118000000000001</v>
@@ -47359,7 +47359,7 @@
         <v>0.5706</v>
       </c>
       <c r="E473" t="n">
-        <v>0.2295</v>
+        <v>0.2294</v>
       </c>
       <c r="F473" t="n">
         <v>0.9118000000000001</v>
@@ -47374,7 +47374,7 @@
         <v>-0.2202</v>
       </c>
       <c r="J473" t="n">
-        <v>1.0677</v>
+        <v>1.0674</v>
       </c>
       <c r="K473" t="n">
         <v>1.582</v>
@@ -47393,16 +47393,16 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.4419</v>
+        <v>0.4418</v>
       </c>
       <c r="C474" t="n">
         <v>0.9524</v>
       </c>
       <c r="D474" t="n">
-        <v>0.6972</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="E474" t="n">
-        <v>0.4419</v>
+        <v>0.4418</v>
       </c>
       <c r="F474" t="n">
         <v>0.9524</v>
@@ -47417,7 +47417,7 @@
         <v>-0.077</v>
       </c>
       <c r="J474" t="n">
-        <v>1.4381</v>
+        <v>1.4374</v>
       </c>
       <c r="K474" t="n">
         <v>1.7626</v>
@@ -47436,16 +47436,16 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.4801</v>
+        <v>0.4798</v>
       </c>
       <c r="C475" t="n">
         <v>1.0085</v>
       </c>
       <c r="D475" t="n">
-        <v>0.7443</v>
+        <v>0.7442</v>
       </c>
       <c r="E475" t="n">
-        <v>0.4801</v>
+        <v>0.4798</v>
       </c>
       <c r="F475" t="n">
         <v>1.0085</v>
@@ -47460,7 +47460,7 @@
         <v>-0.269</v>
       </c>
       <c r="J475" t="n">
-        <v>1.5211</v>
+        <v>1.5202</v>
       </c>
       <c r="K475" t="n">
         <v>1.9143</v>
@@ -47479,16 +47479,16 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.6313</v>
+        <v>0.631</v>
       </c>
       <c r="C476" t="n">
         <v>1.0339</v>
       </c>
       <c r="D476" t="n">
-        <v>0.8326</v>
+        <v>0.8325</v>
       </c>
       <c r="E476" t="n">
-        <v>0.6313</v>
+        <v>0.631</v>
       </c>
       <c r="F476" t="n">
         <v>1.0339</v>
@@ -47503,7 +47503,7 @@
         <v>-0.1687</v>
       </c>
       <c r="J476" t="n">
-        <v>1.8672</v>
+        <v>1.8659</v>
       </c>
       <c r="K476" t="n">
         <v>2.1066</v>
@@ -47522,16 +47522,16 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.6528</v>
+        <v>0.6525</v>
       </c>
       <c r="C477" t="n">
         <v>1.0467</v>
       </c>
       <c r="D477" t="n">
-        <v>0.8498</v>
+        <v>0.8496</v>
       </c>
       <c r="E477" t="n">
-        <v>0.6528</v>
+        <v>0.6525</v>
       </c>
       <c r="F477" t="n">
         <v>1.0467</v>
@@ -47546,7 +47546,7 @@
         <v>-0.2579</v>
       </c>
       <c r="J477" t="n">
-        <v>2.0007</v>
+        <v>1.9993</v>
       </c>
       <c r="K477" t="n">
         <v>2.2864</v>
@@ -47565,16 +47565,16 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.71</v>
+        <v>0.7096</v>
       </c>
       <c r="C478" t="n">
         <v>1.1121</v>
       </c>
       <c r="D478" t="n">
-        <v>0.911</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="E478" t="n">
-        <v>0.71</v>
+        <v>0.7096</v>
       </c>
       <c r="F478" t="n">
         <v>1.1121</v>
@@ -47589,7 +47589,7 @@
         <v>-0.1774</v>
       </c>
       <c r="J478" t="n">
-        <v>2.1504</v>
+        <v>2.1488</v>
       </c>
       <c r="K478" t="n">
         <v>2.441</v>
@@ -47608,16 +47608,16 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.767</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="C479" t="n">
         <v>1.1928</v>
       </c>
       <c r="D479" t="n">
-        <v>0.9799</v>
+        <v>0.9797</v>
       </c>
       <c r="E479" t="n">
-        <v>0.767</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="F479" t="n">
         <v>1.1928</v>
@@ -47632,7 +47632,7 @@
         <v>-0.2187</v>
       </c>
       <c r="J479" t="n">
-        <v>2.211</v>
+        <v>2.2093</v>
       </c>
       <c r="K479" t="n">
         <v>2.6299</v>
@@ -47651,16 +47651,16 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.8899</v>
+        <v>0.8894</v>
       </c>
       <c r="C480" t="n">
         <v>1.2021</v>
       </c>
       <c r="D480" t="n">
-        <v>1.046</v>
+        <v>1.0458</v>
       </c>
       <c r="E480" t="n">
-        <v>0.8899</v>
+        <v>0.8894</v>
       </c>
       <c r="F480" t="n">
         <v>1.2021</v>
@@ -47675,7 +47675,7 @@
         <v>-0.1237</v>
       </c>
       <c r="J480" t="n">
-        <v>2.4282</v>
+        <v>2.4262</v>
       </c>
       <c r="K480" t="n">
         <v>2.7826</v>
@@ -47694,16 +47694,16 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>1.0894</v>
+        <v>1.0889</v>
       </c>
       <c r="C481" t="n">
         <v>1.2857</v>
       </c>
       <c r="D481" t="n">
-        <v>1.1876</v>
+        <v>1.1873</v>
       </c>
       <c r="E481" t="n">
-        <v>1.0894</v>
+        <v>1.0889</v>
       </c>
       <c r="F481" t="n">
         <v>1.2857</v>
@@ -47718,7 +47718,7 @@
         <v>0.0405</v>
       </c>
       <c r="J481" t="n">
-        <v>2.3067</v>
+        <v>2.3049</v>
       </c>
       <c r="K481" t="n">
         <v>2.9767</v>
@@ -47737,16 +47737,16 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.9969</v>
+        <v>0.9963</v>
       </c>
       <c r="C482" t="n">
         <v>1.2402</v>
       </c>
       <c r="D482" t="n">
-        <v>1.1185</v>
+        <v>1.1183</v>
       </c>
       <c r="E482" t="n">
-        <v>0.9969</v>
+        <v>0.9963</v>
       </c>
       <c r="F482" t="n">
         <v>1.2402</v>
@@ -47761,7 +47761,7 @@
         <v>0.0581</v>
       </c>
       <c r="J482" t="n">
-        <v>2.5659</v>
+        <v>2.5637</v>
       </c>
       <c r="K482" t="n">
         <v>2.7926</v>
@@ -47780,16 +47780,16 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.9831</v>
+        <v>0.9825</v>
       </c>
       <c r="C483" t="n">
         <v>1.1602</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0717</v>
+        <v>1.0714</v>
       </c>
       <c r="E483" t="n">
-        <v>0.9831</v>
+        <v>0.9825</v>
       </c>
       <c r="F483" t="n">
         <v>1.1602</v>
@@ -47804,7 +47804,7 @@
         <v>-0.0182</v>
       </c>
       <c r="J483" t="n">
-        <v>2.6862</v>
+        <v>2.6839</v>
       </c>
       <c r="K483" t="n">
         <v>2.645</v>
@@ -47823,16 +47823,16 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.9365</v>
+        <v>0.9359</v>
       </c>
       <c r="C484" t="n">
         <v>1.143</v>
       </c>
       <c r="D484" t="n">
-        <v>1.0398</v>
+        <v>1.0395</v>
       </c>
       <c r="E484" t="n">
-        <v>0.9365</v>
+        <v>0.9359</v>
       </c>
       <c r="F484" t="n">
         <v>1.143</v>
@@ -47847,7 +47847,7 @@
         <v>-0.01</v>
       </c>
       <c r="J484" t="n">
-        <v>2.6545</v>
+        <v>2.6522</v>
       </c>
       <c r="K484" t="n">
         <v>2.5063</v>
@@ -47866,16 +47866,16 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>1.0367</v>
+        <v>1.0363</v>
       </c>
       <c r="C485" t="n">
         <v>1.0804</v>
       </c>
       <c r="D485" t="n">
-        <v>1.0586</v>
+        <v>1.0584</v>
       </c>
       <c r="E485" t="n">
-        <v>1.0367</v>
+        <v>1.0363</v>
       </c>
       <c r="F485" t="n">
         <v>1.0804</v>
@@ -47890,7 +47890,7 @@
         <v>-0.0622</v>
       </c>
       <c r="J485" t="n">
-        <v>2.2619</v>
+        <v>2.2601</v>
       </c>
       <c r="K485" t="n">
         <v>2.3713</v>
@@ -47909,16 +47909,16 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.9724</v>
+        <v>0.972</v>
       </c>
       <c r="C486" t="n">
         <v>1.0252</v>
       </c>
       <c r="D486" t="n">
-        <v>0.9988</v>
+        <v>0.9986</v>
       </c>
       <c r="E486" t="n">
-        <v>0.9724</v>
+        <v>0.972</v>
       </c>
       <c r="F486" t="n">
         <v>1.0252</v>
@@ -47933,7 +47933,7 @@
         <v>-0.1009</v>
       </c>
       <c r="J486" t="n">
-        <v>2.0463</v>
+        <v>2.0448</v>
       </c>
       <c r="K486" t="n">
         <v>2.1947</v>
@@ -47952,16 +47952,16 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.9476</v>
+        <v>0.9472</v>
       </c>
       <c r="C487" t="n">
         <v>0.9631</v>
       </c>
       <c r="D487" t="n">
-        <v>0.9553</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="E487" t="n">
-        <v>0.9476</v>
+        <v>0.9472</v>
       </c>
       <c r="F487" t="n">
         <v>0.9631</v>
@@ -47976,7 +47976,7 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="J487" t="n">
-        <v>2.0446</v>
+        <v>2.0431</v>
       </c>
       <c r="K487" t="n">
         <v>2.0529</v>
@@ -47995,16 +47995,16 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9175</v>
       </c>
       <c r="C488" t="n">
         <v>0.9493</v>
       </c>
       <c r="D488" t="n">
-        <v>0.9335</v>
+        <v>0.9334</v>
       </c>
       <c r="E488" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9175</v>
       </c>
       <c r="F488" t="n">
         <v>0.9493</v>
@@ -48019,7 +48019,7 @@
         <v>-0.098</v>
       </c>
       <c r="J488" t="n">
-        <v>1.9689</v>
+        <v>1.9675</v>
       </c>
       <c r="K488" t="n">
         <v>2.0185</v>
@@ -48038,16 +48038,16 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.8641</v>
+        <v>0.8638</v>
       </c>
       <c r="C489" t="n">
         <v>0.9119</v>
       </c>
       <c r="D489" t="n">
-        <v>0.888</v>
+        <v>0.8879</v>
       </c>
       <c r="E489" t="n">
-        <v>0.8641</v>
+        <v>0.8638</v>
       </c>
       <c r="F489" t="n">
         <v>0.9119</v>
@@ -48062,7 +48062,7 @@
         <v>-0.0528</v>
       </c>
       <c r="J489" t="n">
-        <v>1.7906</v>
+        <v>1.7894</v>
       </c>
       <c r="K489" t="n">
         <v>1.9618</v>
@@ -48071,7 +48071,7 @@
         <v>0.5085</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2654</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="490">
@@ -48081,16 +48081,16 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.8822</v>
+        <v>0.8819</v>
       </c>
       <c r="C490" t="n">
         <v>0.901</v>
       </c>
       <c r="D490" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8915</v>
       </c>
       <c r="E490" t="n">
-        <v>0.8822</v>
+        <v>0.8819</v>
       </c>
       <c r="F490" t="n">
         <v>0.901</v>
@@ -48105,7 +48105,7 @@
         <v>0.1227</v>
       </c>
       <c r="J490" t="n">
-        <v>1.6893</v>
+        <v>1.6883</v>
       </c>
       <c r="K490" t="n">
         <v>1.9088</v>
@@ -48124,16 +48124,16 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.8927</v>
+        <v>0.8925</v>
       </c>
       <c r="C491" t="n">
         <v>0.8921</v>
       </c>
       <c r="D491" t="n">
-        <v>0.8924</v>
+        <v>0.8923</v>
       </c>
       <c r="E491" t="n">
-        <v>0.8927</v>
+        <v>0.8925</v>
       </c>
       <c r="F491" t="n">
         <v>0.8921</v>
@@ -48148,7 +48148,7 @@
         <v>0.1364</v>
       </c>
       <c r="J491" t="n">
-        <v>1.7187</v>
+        <v>1.7176</v>
       </c>
       <c r="K491" t="n">
         <v>1.8409</v>
@@ -48167,16 +48167,16 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.9679</v>
+        <v>0.9677</v>
       </c>
       <c r="C492" t="n">
         <v>0.8806</v>
       </c>
       <c r="D492" t="n">
-        <v>0.9243</v>
+        <v>0.9241</v>
       </c>
       <c r="E492" t="n">
-        <v>0.9679</v>
+        <v>0.9677</v>
       </c>
       <c r="F492" t="n">
         <v>0.8806</v>
@@ -48191,7 +48191,7 @@
         <v>0.4661</v>
       </c>
       <c r="J492" t="n">
-        <v>1.6916</v>
+        <v>1.6906</v>
       </c>
       <c r="K492" t="n">
         <v>1.8</v>
@@ -48210,16 +48210,16 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.7083</v>
+        <v>0.708</v>
       </c>
       <c r="C493" t="n">
         <v>0.8659</v>
       </c>
       <c r="D493" t="n">
-        <v>0.7871</v>
+        <v>0.7869</v>
       </c>
       <c r="E493" t="n">
-        <v>0.7083</v>
+        <v>0.708</v>
       </c>
       <c r="F493" t="n">
         <v>0.8659</v>
@@ -48234,7 +48234,7 @@
         <v>0.5516</v>
       </c>
       <c r="J493" t="n">
-        <v>1.7753</v>
+        <v>1.7741</v>
       </c>
       <c r="K493" t="n">
         <v>1.7414</v>
@@ -48253,16 +48253,16 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.9396</v>
+        <v>0.9393</v>
       </c>
       <c r="C494" t="n">
         <v>0.8914</v>
       </c>
       <c r="D494" t="n">
-        <v>0.9155</v>
+        <v>0.9154</v>
       </c>
       <c r="E494" t="n">
-        <v>0.9396</v>
+        <v>0.9393</v>
       </c>
       <c r="F494" t="n">
         <v>0.8914</v>
@@ -48277,7 +48277,7 @@
         <v>0.4669</v>
       </c>
       <c r="J494" t="n">
-        <v>1.7832</v>
+        <v>1.782</v>
       </c>
       <c r="K494" t="n">
         <v>1.708</v>
@@ -48296,16 +48296,16 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.9095</v>
+        <v>0.9092</v>
       </c>
       <c r="C495" t="n">
         <v>0.8485</v>
       </c>
       <c r="D495" t="n">
-        <v>0.879</v>
+        <v>0.8789</v>
       </c>
       <c r="E495" t="n">
-        <v>0.9095</v>
+        <v>0.9092</v>
       </c>
       <c r="F495" t="n">
         <v>0.8485</v>
@@ -48320,7 +48320,7 @@
         <v>0.4859</v>
       </c>
       <c r="J495" t="n">
-        <v>1.7307</v>
+        <v>1.7296</v>
       </c>
       <c r="K495" t="n">
         <v>1.6499</v>
@@ -48339,16 +48339,16 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.9649</v>
+        <v>0.9646</v>
       </c>
       <c r="C496" t="n">
         <v>0.9478</v>
       </c>
       <c r="D496" t="n">
-        <v>0.9564</v>
+        <v>0.9562</v>
       </c>
       <c r="E496" t="n">
-        <v>0.9649</v>
+        <v>0.9646</v>
       </c>
       <c r="F496" t="n">
         <v>0.9478</v>
@@ -48363,7 +48363,7 @@
         <v>0.5178</v>
       </c>
       <c r="J496" t="n">
-        <v>1.778</v>
+        <v>1.7769</v>
       </c>
       <c r="K496" t="n">
         <v>1.5868</v>
@@ -48382,16 +48382,16 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7673</v>
       </c>
       <c r="C497" t="n">
         <v>0.9328</v>
       </c>
       <c r="D497" t="n">
-        <v>0.8502</v>
+        <v>0.8501</v>
       </c>
       <c r="E497" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7673</v>
       </c>
       <c r="F497" t="n">
         <v>0.9328</v>
@@ -48406,7 +48406,7 @@
         <v>0.4918</v>
       </c>
       <c r="J497" t="n">
-        <v>1.8645</v>
+        <v>1.8632</v>
       </c>
       <c r="K497" t="n">
         <v>1.5267</v>
@@ -48425,16 +48425,16 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.7916</v>
+        <v>0.7913</v>
       </c>
       <c r="C498" t="n">
         <v>0.9004</v>
       </c>
       <c r="D498" t="n">
-        <v>0.846</v>
+        <v>0.8458</v>
       </c>
       <c r="E498" t="n">
-        <v>0.7916</v>
+        <v>0.7913</v>
       </c>
       <c r="F498" t="n">
         <v>0.9004</v>
@@ -48449,7 +48449,7 @@
         <v>0.5543</v>
       </c>
       <c r="J498" t="n">
-        <v>1.8585</v>
+        <v>1.8572</v>
       </c>
       <c r="K498" t="n">
         <v>1.4968</v>
@@ -48468,16 +48468,16 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7794</v>
       </c>
       <c r="C499" t="n">
         <v>0.8308</v>
       </c>
       <c r="D499" t="n">
-        <v>0.8053</v>
+        <v>0.8051</v>
       </c>
       <c r="E499" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7794</v>
       </c>
       <c r="F499" t="n">
         <v>0.8308</v>
@@ -48492,7 +48492,7 @@
         <v>0.6677</v>
       </c>
       <c r="J499" t="n">
-        <v>1.7826</v>
+        <v>1.7814</v>
       </c>
       <c r="K499" t="n">
         <v>1.4305</v>
@@ -48511,16 +48511,16 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.7216</v>
+        <v>0.7214</v>
       </c>
       <c r="C500" t="n">
         <v>0.8414</v>
       </c>
       <c r="D500" t="n">
-        <v>0.7815</v>
+        <v>0.7814</v>
       </c>
       <c r="E500" t="n">
-        <v>0.7216</v>
+        <v>0.7214</v>
       </c>
       <c r="F500" t="n">
         <v>0.8414</v>
@@ -48535,7 +48535,7 @@
         <v>0.6322</v>
       </c>
       <c r="J500" t="n">
-        <v>1.6236</v>
+        <v>1.6226</v>
       </c>
       <c r="K500" t="n">
         <v>1.4015</v>
@@ -48554,16 +48554,16 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.6957</v>
+        <v>0.6955</v>
       </c>
       <c r="C501" t="n">
         <v>0.7879</v>
       </c>
       <c r="D501" t="n">
-        <v>0.7418</v>
+        <v>0.7417</v>
       </c>
       <c r="E501" t="n">
-        <v>0.6957</v>
+        <v>0.6955</v>
       </c>
       <c r="F501" t="n">
         <v>0.7879</v>
@@ -48578,7 +48578,7 @@
         <v>0.5779</v>
       </c>
       <c r="J501" t="n">
-        <v>1.5743</v>
+        <v>1.5734</v>
       </c>
       <c r="K501" t="n">
         <v>1.3428</v>
@@ -48597,16 +48597,16 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.6432</v>
+        <v>0.643</v>
       </c>
       <c r="C502" t="n">
         <v>0.7441</v>
       </c>
       <c r="D502" t="n">
-        <v>0.6937</v>
+        <v>0.6935</v>
       </c>
       <c r="E502" t="n">
-        <v>0.6432</v>
+        <v>0.643</v>
       </c>
       <c r="F502" t="n">
         <v>0.7441</v>
@@ -48621,7 +48621,7 @@
         <v>0.4396</v>
       </c>
       <c r="J502" t="n">
-        <v>1.6517</v>
+        <v>1.6507</v>
       </c>
       <c r="K502" t="n">
         <v>1.3025</v>
@@ -48640,16 +48640,16 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.5859</v>
+        <v>0.5857</v>
       </c>
       <c r="C503" t="n">
         <v>0.7181</v>
       </c>
       <c r="D503" t="n">
-        <v>0.652</v>
+        <v>0.6519</v>
       </c>
       <c r="E503" t="n">
-        <v>0.5859</v>
+        <v>0.5857</v>
       </c>
       <c r="F503" t="n">
         <v>0.7181</v>
@@ -48664,7 +48664,7 @@
         <v>0.4552</v>
       </c>
       <c r="J503" t="n">
-        <v>1.5201</v>
+        <v>1.5192</v>
       </c>
       <c r="K503" t="n">
         <v>1.2682</v>
@@ -48683,7 +48683,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.5704</v>
+        <v>0.5702</v>
       </c>
       <c r="C504" t="n">
         <v>0.6887</v>
@@ -48692,7 +48692,7 @@
         <v>0.6294999999999999</v>
       </c>
       <c r="E504" t="n">
-        <v>0.5704</v>
+        <v>0.5702</v>
       </c>
       <c r="F504" t="n">
         <v>0.6887</v>
@@ -48707,7 +48707,7 @@
         <v>0.5358000000000001</v>
       </c>
       <c r="J504" t="n">
-        <v>1.3795</v>
+        <v>1.3788</v>
       </c>
       <c r="K504" t="n">
         <v>1.1974</v>
@@ -48726,16 +48726,16 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.5413</v>
+        <v>0.5411</v>
       </c>
       <c r="C505" t="n">
         <v>0.6497000000000001</v>
       </c>
       <c r="D505" t="n">
-        <v>0.5955</v>
+        <v>0.5954</v>
       </c>
       <c r="E505" t="n">
-        <v>0.5413</v>
+        <v>0.5411</v>
       </c>
       <c r="F505" t="n">
         <v>0.6497000000000001</v>
@@ -48750,7 +48750,7 @@
         <v>0.4826</v>
       </c>
       <c r="J505" t="n">
-        <v>1.3383</v>
+        <v>1.3377</v>
       </c>
       <c r="K505" t="n">
         <v>1.1696</v>
@@ -48769,16 +48769,16 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.4879</v>
+        <v>0.4877</v>
       </c>
       <c r="C506" t="n">
         <v>0.6264999999999999</v>
       </c>
       <c r="D506" t="n">
-        <v>0.5572</v>
+        <v>0.5571</v>
       </c>
       <c r="E506" t="n">
-        <v>0.4879</v>
+        <v>0.4877</v>
       </c>
       <c r="F506" t="n">
         <v>0.6264999999999999</v>
@@ -48793,7 +48793,7 @@
         <v>0.311</v>
       </c>
       <c r="J506" t="n">
-        <v>1.3239</v>
+        <v>1.3233</v>
       </c>
       <c r="K506" t="n">
         <v>1.0912</v>
@@ -48812,16 +48812,16 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.4589</v>
+        <v>0.4588</v>
       </c>
       <c r="C507" t="n">
         <v>0.5869</v>
       </c>
       <c r="D507" t="n">
-        <v>0.5229</v>
+        <v>0.5228</v>
       </c>
       <c r="E507" t="n">
-        <v>0.4589</v>
+        <v>0.4588</v>
       </c>
       <c r="F507" t="n">
         <v>0.5869</v>
@@ -48836,7 +48836,7 @@
         <v>0.203</v>
       </c>
       <c r="J507" t="n">
-        <v>1.2271</v>
+        <v>1.2266</v>
       </c>
       <c r="K507" t="n">
         <v>1.0483</v>
@@ -48855,16 +48855,16 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.394</v>
+        <v>0.3939</v>
       </c>
       <c r="C508" t="n">
         <v>0.6283</v>
       </c>
       <c r="D508" t="n">
-        <v>0.5112</v>
+        <v>0.5111</v>
       </c>
       <c r="E508" t="n">
-        <v>0.394</v>
+        <v>0.3939</v>
       </c>
       <c r="F508" t="n">
         <v>0.6283</v>
@@ -48879,7 +48879,7 @@
         <v>0.1591</v>
       </c>
       <c r="J508" t="n">
-        <v>1.1818</v>
+        <v>1.1813</v>
       </c>
       <c r="K508" t="n">
         <v>0.9862</v>
@@ -48898,7 +48898,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.367</v>
+        <v>0.3669</v>
       </c>
       <c r="C509" t="n">
         <v>0.6291</v>
@@ -48907,7 +48907,7 @@
         <v>0.498</v>
       </c>
       <c r="E509" t="n">
-        <v>0.367</v>
+        <v>0.3669</v>
       </c>
       <c r="F509" t="n">
         <v>0.6291</v>
@@ -48922,7 +48922,7 @@
         <v>0.0411</v>
       </c>
       <c r="J509" t="n">
-        <v>1.1235</v>
+        <v>1.1231</v>
       </c>
       <c r="K509" t="n">
         <v>0.9238</v>
@@ -48947,7 +48947,7 @@
         <v>0.6182</v>
       </c>
       <c r="D510" t="n">
-        <v>0.4869</v>
+        <v>0.4868</v>
       </c>
       <c r="E510" t="n">
         <v>0.3555</v>
@@ -48965,7 +48965,7 @@
         <v>-0.0189</v>
       </c>
       <c r="J510" t="n">
-        <v>1.0912</v>
+        <v>1.0908</v>
       </c>
       <c r="K510" t="n">
         <v>0.8811</v>
@@ -48984,16 +48984,16 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.3329</v>
+        <v>0.3328</v>
       </c>
       <c r="C511" t="n">
         <v>0.615</v>
       </c>
       <c r="D511" t="n">
-        <v>0.474</v>
+        <v>0.4739</v>
       </c>
       <c r="E511" t="n">
-        <v>0.3329</v>
+        <v>0.3328</v>
       </c>
       <c r="F511" t="n">
         <v>0.615</v>
@@ -49008,7 +49008,7 @@
         <v>-0.1831</v>
       </c>
       <c r="J511" t="n">
-        <v>1.1763</v>
+        <v>1.1758</v>
       </c>
       <c r="K511" t="n">
         <v>0.8417</v>
@@ -49027,7 +49027,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.3156</v>
+        <v>0.3155</v>
       </c>
       <c r="C512" t="n">
         <v>0.6276</v>
@@ -49036,7 +49036,7 @@
         <v>0.4716</v>
       </c>
       <c r="E512" t="n">
-        <v>0.3156</v>
+        <v>0.3155</v>
       </c>
       <c r="F512" t="n">
         <v>0.6276</v>
@@ -49051,7 +49051,7 @@
         <v>-0.2536</v>
       </c>
       <c r="J512" t="n">
-        <v>1.1613</v>
+        <v>1.1608</v>
       </c>
       <c r="K512" t="n">
         <v>0.8044</v>
@@ -49070,16 +49070,16 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.2704</v>
+        <v>0.2703</v>
       </c>
       <c r="C513" t="n">
         <v>0.5883</v>
       </c>
       <c r="D513" t="n">
-        <v>0.4294</v>
+        <v>0.4293</v>
       </c>
       <c r="E513" t="n">
-        <v>0.2704</v>
+        <v>0.2703</v>
       </c>
       <c r="F513" t="n">
         <v>0.5883</v>
@@ -49094,7 +49094,7 @@
         <v>-0.3705</v>
       </c>
       <c r="J513" t="n">
-        <v>1.1792</v>
+        <v>1.1788</v>
       </c>
       <c r="K513" t="n">
         <v>0.8048</v>
@@ -49113,16 +49113,16 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.2953</v>
+        <v>0.2952</v>
       </c>
       <c r="C514" t="n">
         <v>0.5311</v>
       </c>
       <c r="D514" t="n">
-        <v>0.4132</v>
+        <v>0.4131</v>
       </c>
       <c r="E514" t="n">
-        <v>0.2953</v>
+        <v>0.2952</v>
       </c>
       <c r="F514" t="n">
         <v>0.5311</v>
@@ -49137,7 +49137,7 @@
         <v>-0.3394</v>
       </c>
       <c r="J514" t="n">
-        <v>1.1408</v>
+        <v>1.1404</v>
       </c>
       <c r="K514" t="n">
         <v>0.7744</v>
@@ -49156,16 +49156,16 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.3366</v>
+        <v>0.3365</v>
       </c>
       <c r="C515" t="n">
         <v>0.528</v>
       </c>
       <c r="D515" t="n">
-        <v>0.4323</v>
+        <v>0.4322</v>
       </c>
       <c r="E515" t="n">
-        <v>0.3366</v>
+        <v>0.3365</v>
       </c>
       <c r="F515" t="n">
         <v>0.528</v>
@@ -49180,7 +49180,7 @@
         <v>-0.2856</v>
       </c>
       <c r="J515" t="n">
-        <v>1.0911</v>
+        <v>1.0907</v>
       </c>
       <c r="K515" t="n">
         <v>0.7649</v>
@@ -49199,16 +49199,16 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.4019</v>
+        <v>0.4018</v>
       </c>
       <c r="C516" t="n">
         <v>0.5289</v>
       </c>
       <c r="D516" t="n">
-        <v>0.4654</v>
+        <v>0.4653</v>
       </c>
       <c r="E516" t="n">
-        <v>0.4019</v>
+        <v>0.4018</v>
       </c>
       <c r="F516" t="n">
         <v>0.5289</v>
@@ -49223,7 +49223,7 @@
         <v>-0.12</v>
       </c>
       <c r="J516" t="n">
-        <v>1.058</v>
+        <v>1.0577</v>
       </c>
       <c r="K516" t="n">
         <v>0.7467</v>
@@ -49242,7 +49242,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.593</v>
+        <v>0.5929</v>
       </c>
       <c r="C517" t="n">
         <v>0.4854</v>
@@ -49251,7 +49251,7 @@
         <v>0.5392</v>
       </c>
       <c r="E517" t="n">
-        <v>0.593</v>
+        <v>0.5929</v>
       </c>
       <c r="F517" t="n">
         <v>0.4854</v>
@@ -49266,7 +49266,7 @@
         <v>0.201</v>
       </c>
       <c r="J517" t="n">
-        <v>1.1138</v>
+        <v>1.1134</v>
       </c>
       <c r="K517" t="n">
         <v>0.7044</v>
@@ -49309,7 +49309,7 @@
         <v>0.1832</v>
       </c>
       <c r="J518" t="n">
-        <v>0.9193</v>
+        <v>0.9192</v>
       </c>
       <c r="K518" t="n">
         <v>0.7165</v>
@@ -49371,7 +49371,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.5006</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="C520" t="n">
         <v>0.4558</v>
@@ -49380,7 +49380,7 @@
         <v>0.4782</v>
       </c>
       <c r="E520" t="n">
-        <v>0.5006</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="F520" t="n">
         <v>0.4558</v>
@@ -49395,7 +49395,7 @@
         <v>0.1334</v>
       </c>
       <c r="J520" t="n">
-        <v>0.8667</v>
+        <v>0.8666</v>
       </c>
       <c r="K520" t="n">
         <v>0.6432</v>
@@ -49481,7 +49481,7 @@
         <v>0.1222</v>
       </c>
       <c r="J522" t="n">
-        <v>0.6469</v>
+        <v>0.6472</v>
       </c>
       <c r="K522" t="n">
         <v>0.6042999999999999</v>
@@ -49500,16 +49500,16 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.4349</v>
+        <v>0.435</v>
       </c>
       <c r="C523" t="n">
         <v>0.4148</v>
       </c>
       <c r="D523" t="n">
-        <v>0.4248</v>
+        <v>0.4249</v>
       </c>
       <c r="E523" t="n">
-        <v>0.4349</v>
+        <v>0.435</v>
       </c>
       <c r="F523" t="n">
         <v>0.4148</v>
@@ -49524,7 +49524,7 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="J523" t="n">
-        <v>0.5342</v>
+        <v>0.5345</v>
       </c>
       <c r="K523" t="n">
         <v>0.5856</v>
@@ -49543,16 +49543,16 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.4368</v>
+        <v>0.4369</v>
       </c>
       <c r="C524" t="n">
         <v>0.371</v>
       </c>
       <c r="D524" t="n">
-        <v>0.4039</v>
+        <v>0.404</v>
       </c>
       <c r="E524" t="n">
-        <v>0.4368</v>
+        <v>0.4369</v>
       </c>
       <c r="F524" t="n">
         <v>0.371</v>
@@ -49567,7 +49567,7 @@
         <v>0.1878</v>
       </c>
       <c r="J524" t="n">
-        <v>0.4006</v>
+        <v>0.4011</v>
       </c>
       <c r="K524" t="n">
         <v>0.5276999999999999</v>
@@ -49586,7 +49586,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.4166</v>
+        <v>0.4168</v>
       </c>
       <c r="C525" t="n">
         <v>0.3347</v>
@@ -49595,7 +49595,7 @@
         <v>0.3757</v>
       </c>
       <c r="E525" t="n">
-        <v>0.4166</v>
+        <v>0.4168</v>
       </c>
       <c r="F525" t="n">
         <v>0.3347</v>
@@ -49610,7 +49610,7 @@
         <v>0.1086</v>
       </c>
       <c r="J525" t="n">
-        <v>0.3199</v>
+        <v>0.3205</v>
       </c>
       <c r="K525" t="n">
         <v>0.4566</v>
@@ -49629,16 +49629,16 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.4105</v>
+        <v>0.4107</v>
       </c>
       <c r="C526" t="n">
         <v>0.304</v>
       </c>
       <c r="D526" t="n">
-        <v>0.3572</v>
+        <v>0.3573</v>
       </c>
       <c r="E526" t="n">
-        <v>0.4105</v>
+        <v>0.4107</v>
       </c>
       <c r="F526" t="n">
         <v>0.304</v>
@@ -49653,7 +49653,7 @@
         <v>0.1768</v>
       </c>
       <c r="J526" t="n">
-        <v>0.2825</v>
+        <v>0.2832</v>
       </c>
       <c r="K526" t="n">
         <v>0.3896</v>
@@ -49672,16 +49672,16 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.4322</v>
+        <v>0.4324</v>
       </c>
       <c r="C527" t="n">
         <v>0.3029</v>
       </c>
       <c r="D527" t="n">
-        <v>0.3676</v>
+        <v>0.3677</v>
       </c>
       <c r="E527" t="n">
-        <v>0.4322</v>
+        <v>0.4324</v>
       </c>
       <c r="F527" t="n">
         <v>0.3029</v>
@@ -49696,7 +49696,7 @@
         <v>0.2493</v>
       </c>
       <c r="J527" t="n">
-        <v>0.2406</v>
+        <v>0.2413</v>
       </c>
       <c r="K527" t="n">
         <v>0.3354</v>
@@ -49715,16 +49715,16 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.4263</v>
+        <v>0.4265</v>
       </c>
       <c r="C528" t="n">
         <v>0.2268</v>
       </c>
       <c r="D528" t="n">
-        <v>0.3266</v>
+        <v>0.3267</v>
       </c>
       <c r="E528" t="n">
-        <v>0.4263</v>
+        <v>0.4265</v>
       </c>
       <c r="F528" t="n">
         <v>0.2268</v>
@@ -49739,7 +49739,7 @@
         <v>0.2411</v>
       </c>
       <c r="J528" t="n">
-        <v>0.1693</v>
+        <v>0.1701</v>
       </c>
       <c r="K528" t="n">
         <v>0.2577</v>
@@ -49758,16 +49758,16 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.3868</v>
+        <v>0.387</v>
       </c>
       <c r="C529" t="n">
         <v>0.2213</v>
       </c>
       <c r="D529" t="n">
-        <v>0.304</v>
+        <v>0.3041</v>
       </c>
       <c r="E529" t="n">
-        <v>0.3868</v>
+        <v>0.387</v>
       </c>
       <c r="F529" t="n">
         <v>0.2213</v>
@@ -49782,7 +49782,7 @@
         <v>0.2615</v>
       </c>
       <c r="J529" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0772</v>
       </c>
       <c r="K529" t="n">
         <v>0.198</v>
@@ -49801,16 +49801,16 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.373</v>
+        <v>0.3733</v>
       </c>
       <c r="C530" t="n">
         <v>0.2245</v>
       </c>
       <c r="D530" t="n">
-        <v>0.2987</v>
+        <v>0.2989</v>
       </c>
       <c r="E530" t="n">
-        <v>0.373</v>
+        <v>0.3733</v>
       </c>
       <c r="F530" t="n">
         <v>0.2245</v>
@@ -49825,7 +49825,7 @@
         <v>0.2359</v>
       </c>
       <c r="J530" t="n">
-        <v>0.066</v>
+        <v>0.0669</v>
       </c>
       <c r="K530" t="n">
         <v>0.1582</v>
@@ -49844,16 +49844,16 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.3692</v>
+        <v>0.3695</v>
       </c>
       <c r="C531" t="n">
         <v>0.172</v>
       </c>
       <c r="D531" t="n">
-        <v>0.2706</v>
+        <v>0.2708</v>
       </c>
       <c r="E531" t="n">
-        <v>0.3692</v>
+        <v>0.3695</v>
       </c>
       <c r="F531" t="n">
         <v>0.172</v>
@@ -49868,7 +49868,7 @@
         <v>0.1518</v>
       </c>
       <c r="J531" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="K531" t="n">
         <v>0.0919</v>
@@ -49887,16 +49887,16 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.3027</v>
+        <v>0.303</v>
       </c>
       <c r="C532" t="n">
         <v>0.1211</v>
       </c>
       <c r="D532" t="n">
-        <v>0.2119</v>
+        <v>0.212</v>
       </c>
       <c r="E532" t="n">
-        <v>0.3027</v>
+        <v>0.303</v>
       </c>
       <c r="F532" t="n">
         <v>0.1211</v>
@@ -49911,7 +49911,7 @@
         <v>0.0664</v>
       </c>
       <c r="J532" t="n">
-        <v>-0.0371</v>
+        <v>-0.036</v>
       </c>
       <c r="K532" t="n">
         <v>0.007</v>
@@ -49930,16 +49930,16 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.2988</v>
+        <v>0.2991</v>
       </c>
       <c r="C533" t="n">
         <v>0.1016</v>
       </c>
       <c r="D533" t="n">
-        <v>0.2002</v>
+        <v>0.2004</v>
       </c>
       <c r="E533" t="n">
-        <v>0.2988</v>
+        <v>0.2991</v>
       </c>
       <c r="F533" t="n">
         <v>0.1016</v>
@@ -49954,7 +49954,7 @@
         <v>0.1391</v>
       </c>
       <c r="J533" t="n">
-        <v>-0.0578</v>
+        <v>-0.0567</v>
       </c>
       <c r="K533" t="n">
         <v>-0.0556</v>
@@ -49973,16 +49973,16 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.3062</v>
+        <v>0.3065</v>
       </c>
       <c r="C534" t="n">
         <v>0.0593</v>
       </c>
       <c r="D534" t="n">
-        <v>0.1828</v>
+        <v>0.1829</v>
       </c>
       <c r="E534" t="n">
-        <v>0.3062</v>
+        <v>0.3065</v>
       </c>
       <c r="F534" t="n">
         <v>0.0593</v>
@@ -49997,7 +49997,7 @@
         <v>0.1771</v>
       </c>
       <c r="J534" t="n">
-        <v>-0.0236</v>
+        <v>-0.0225</v>
       </c>
       <c r="K534" t="n">
         <v>-0.1363</v>
@@ -50016,16 +50016,16 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.296</v>
+        <v>0.2962</v>
       </c>
       <c r="C535" t="n">
         <v>0.057</v>
       </c>
       <c r="D535" t="n">
-        <v>0.1765</v>
+        <v>0.1766</v>
       </c>
       <c r="E535" t="n">
-        <v>0.296</v>
+        <v>0.2962</v>
       </c>
       <c r="F535" t="n">
         <v>0.057</v>
@@ -50040,7 +50040,7 @@
         <v>0.1653</v>
       </c>
       <c r="J535" t="n">
-        <v>-0.0954</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="K535" t="n">
         <v>-0.1823</v>
@@ -50059,16 +50059,16 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.3328</v>
+        <v>0.3331</v>
       </c>
       <c r="C536" t="n">
         <v>0.0231</v>
       </c>
       <c r="D536" t="n">
-        <v>0.1779</v>
+        <v>0.1781</v>
       </c>
       <c r="E536" t="n">
-        <v>0.3328</v>
+        <v>0.3331</v>
       </c>
       <c r="F536" t="n">
         <v>0.0231</v>
@@ -50083,7 +50083,7 @@
         <v>0.1807</v>
       </c>
       <c r="J536" t="n">
-        <v>-0.0185</v>
+        <v>-0.0175</v>
       </c>
       <c r="K536" t="n">
         <v>-0.1778</v>
@@ -50102,16 +50102,16 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.3048</v>
+        <v>0.305</v>
       </c>
       <c r="C537" t="n">
         <v>-0.0248</v>
       </c>
       <c r="D537" t="n">
-        <v>0.14</v>
+        <v>0.1401</v>
       </c>
       <c r="E537" t="n">
-        <v>0.3048</v>
+        <v>0.305</v>
       </c>
       <c r="F537" t="n">
         <v>-0.0248</v>
@@ -50126,7 +50126,7 @@
         <v>0.1188</v>
       </c>
       <c r="J537" t="n">
-        <v>-0.0441</v>
+        <v>-0.043</v>
       </c>
       <c r="K537" t="n">
         <v>-0.2084</v>
@@ -50145,16 +50145,16 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.2915</v>
+        <v>0.2918</v>
       </c>
       <c r="C538" t="n">
         <v>-0.0211</v>
       </c>
       <c r="D538" t="n">
-        <v>0.1352</v>
+        <v>0.1354</v>
       </c>
       <c r="E538" t="n">
-        <v>0.2915</v>
+        <v>0.2918</v>
       </c>
       <c r="F538" t="n">
         <v>-0.0211</v>
@@ -50169,7 +50169,7 @@
         <v>0.1706</v>
       </c>
       <c r="J538" t="n">
-        <v>-0.1425</v>
+        <v>-0.1413</v>
       </c>
       <c r="K538" t="n">
         <v>-0.2038</v>
@@ -50188,16 +50188,16 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.309</v>
+        <v>0.3093</v>
       </c>
       <c r="C539" t="n">
         <v>-0.0592</v>
       </c>
       <c r="D539" t="n">
-        <v>0.1249</v>
+        <v>0.1251</v>
       </c>
       <c r="E539" t="n">
-        <v>0.309</v>
+        <v>0.3093</v>
       </c>
       <c r="F539" t="n">
         <v>-0.0592</v>
@@ -50212,7 +50212,7 @@
         <v>0.1806</v>
       </c>
       <c r="J539" t="n">
-        <v>-0.1257</v>
+        <v>-0.1245</v>
       </c>
       <c r="K539" t="n">
         <v>-0.2481</v>
@@ -50231,16 +50231,16 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.2926</v>
+        <v>0.2929</v>
       </c>
       <c r="C540" t="n">
         <v>-0.0796</v>
       </c>
       <c r="D540" t="n">
-        <v>0.1065</v>
+        <v>0.1067</v>
       </c>
       <c r="E540" t="n">
-        <v>0.2926</v>
+        <v>0.2929</v>
       </c>
       <c r="F540" t="n">
         <v>-0.0796</v>
@@ -50255,7 +50255,7 @@
         <v>0.1959</v>
       </c>
       <c r="J540" t="n">
-        <v>-0.1306</v>
+        <v>-0.1294</v>
       </c>
       <c r="K540" t="n">
         <v>-0.2468</v>
@@ -50274,16 +50274,16 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.2428</v>
+        <v>0.2431</v>
       </c>
       <c r="C541" t="n">
         <v>-0.1213</v>
       </c>
       <c r="D541" t="n">
-        <v>0.0608</v>
+        <v>0.0609</v>
       </c>
       <c r="E541" t="n">
-        <v>0.2428</v>
+        <v>0.2431</v>
       </c>
       <c r="F541" t="n">
         <v>-0.1213</v>
@@ -50298,7 +50298,7 @@
         <v>0.1623</v>
       </c>
       <c r="J541" t="n">
-        <v>-0.1697</v>
+        <v>-0.1685</v>
       </c>
       <c r="K541" t="n">
         <v>-0.2719</v>
@@ -50317,16 +50317,16 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.2418</v>
+        <v>0.2421</v>
       </c>
       <c r="C542" t="n">
         <v>-0.1355</v>
       </c>
       <c r="D542" t="n">
-        <v>0.0532</v>
+        <v>0.0533</v>
       </c>
       <c r="E542" t="n">
-        <v>0.2418</v>
+        <v>0.2421</v>
       </c>
       <c r="F542" t="n">
         <v>-0.1355</v>
@@ -50341,7 +50341,7 @@
         <v>0.0434</v>
       </c>
       <c r="J542" t="n">
-        <v>-0.1798</v>
+        <v>-0.1786</v>
       </c>
       <c r="K542" t="n">
         <v>-0.2933</v>
@@ -50360,16 +50360,16 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.2377</v>
+        <v>0.238</v>
       </c>
       <c r="C543" t="n">
         <v>-0.1786</v>
       </c>
       <c r="D543" t="n">
-        <v>0.0295</v>
+        <v>0.0297</v>
       </c>
       <c r="E543" t="n">
-        <v>0.2377</v>
+        <v>0.238</v>
       </c>
       <c r="F543" t="n">
         <v>-0.1786</v>
@@ -50384,7 +50384,7 @@
         <v>0.1398</v>
       </c>
       <c r="J543" t="n">
-        <v>-0.2038</v>
+        <v>-0.2025</v>
       </c>
       <c r="K543" t="n">
         <v>-0.2983</v>
@@ -50403,16 +50403,16 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.262</v>
+        <v>0.2623</v>
       </c>
       <c r="C544" t="n">
         <v>-0.1826</v>
       </c>
       <c r="D544" t="n">
-        <v>0.0397</v>
+        <v>0.0399</v>
       </c>
       <c r="E544" t="n">
-        <v>0.262</v>
+        <v>0.2623</v>
       </c>
       <c r="F544" t="n">
         <v>-0.1826</v>
@@ -50427,7 +50427,7 @@
         <v>0.1734</v>
       </c>
       <c r="J544" t="n">
-        <v>-0.2004</v>
+        <v>-0.1991</v>
       </c>
       <c r="K544" t="n">
         <v>-0.2963</v>
@@ -50446,16 +50446,16 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.269</v>
+        <v>0.2694</v>
       </c>
       <c r="C545" t="n">
         <v>-0.2181</v>
       </c>
       <c r="D545" t="n">
-        <v>0.0255</v>
+        <v>0.0256</v>
       </c>
       <c r="E545" t="n">
-        <v>0.269</v>
+        <v>0.2694</v>
       </c>
       <c r="F545" t="n">
         <v>-0.2181</v>
@@ -50470,7 +50470,7 @@
         <v>0.1881</v>
       </c>
       <c r="J545" t="n">
-        <v>-0.2279</v>
+        <v>-0.2266</v>
       </c>
       <c r="K545" t="n">
         <v>-0.3212</v>
@@ -50489,16 +50489,16 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.2003</v>
+        <v>0.2006</v>
       </c>
       <c r="C546" t="n">
         <v>-0.2457</v>
       </c>
       <c r="D546" t="n">
-        <v>-0.0227</v>
+        <v>-0.0225</v>
       </c>
       <c r="E546" t="n">
-        <v>0.2003</v>
+        <v>0.2006</v>
       </c>
       <c r="F546" t="n">
         <v>-0.2457</v>
@@ -50513,7 +50513,7 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="J546" t="n">
-        <v>-0.2398</v>
+        <v>-0.2384</v>
       </c>
       <c r="K546" t="n">
         <v>-0.3415</v>
@@ -50532,16 +50532,16 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.1889</v>
+        <v>0.1892</v>
       </c>
       <c r="C547" t="n">
         <v>-0.2855</v>
       </c>
       <c r="D547" t="n">
-        <v>-0.0483</v>
+        <v>-0.0481</v>
       </c>
       <c r="E547" t="n">
-        <v>0.1889</v>
+        <v>0.1892</v>
       </c>
       <c r="F547" t="n">
         <v>-0.2855</v>
@@ -50556,7 +50556,7 @@
         <v>0.0103</v>
       </c>
       <c r="J547" t="n">
-        <v>-0.218</v>
+        <v>-0.2167</v>
       </c>
       <c r="K547" t="n">
         <v>-0.3499</v>
@@ -50575,16 +50575,16 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.1987</v>
+        <v>0.199</v>
       </c>
       <c r="C548" t="n">
         <v>-0.3266</v>
       </c>
       <c r="D548" t="n">
-        <v>-0.064</v>
+        <v>-0.0638</v>
       </c>
       <c r="E548" t="n">
-        <v>0.1987</v>
+        <v>0.199</v>
       </c>
       <c r="F548" t="n">
         <v>-0.3266</v>
@@ -50599,7 +50599,7 @@
         <v>0.0285</v>
       </c>
       <c r="J548" t="n">
-        <v>-0.2984</v>
+        <v>-0.297</v>
       </c>
       <c r="K548" t="n">
         <v>-0.3317</v>
@@ -50618,16 +50618,16 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.1813</v>
+        <v>0.1817</v>
       </c>
       <c r="C549" t="n">
         <v>-0.3673</v>
       </c>
       <c r="D549" t="n">
-        <v>-0.093</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="E549" t="n">
-        <v>0.1813</v>
+        <v>0.1817</v>
       </c>
       <c r="F549" t="n">
         <v>-0.3673</v>
@@ -50642,7 +50642,7 @@
         <v>-0.1183</v>
       </c>
       <c r="J549" t="n">
-        <v>-0.3035</v>
+        <v>-0.3021</v>
       </c>
       <c r="K549" t="n">
         <v>-0.3204</v>
@@ -50661,16 +50661,16 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.2259</v>
+        <v>0.2262</v>
       </c>
       <c r="C550" t="n">
         <v>-0.361</v>
       </c>
       <c r="D550" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0674</v>
       </c>
       <c r="E550" t="n">
-        <v>0.2259</v>
+        <v>0.2262</v>
       </c>
       <c r="F550" t="n">
         <v>-0.361</v>
@@ -50685,7 +50685,7 @@
         <v>-0.0578</v>
       </c>
       <c r="J550" t="n">
-        <v>-0.2709</v>
+        <v>-0.2695</v>
       </c>
       <c r="K550" t="n">
         <v>-0.2719</v>
@@ -50704,16 +50704,16 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.2496</v>
+        <v>0.2499</v>
       </c>
       <c r="C551" t="n">
         <v>-0.3955</v>
       </c>
       <c r="D551" t="n">
-        <v>-0.073</v>
+        <v>-0.0728</v>
       </c>
       <c r="E551" t="n">
-        <v>0.2496</v>
+        <v>0.2499</v>
       </c>
       <c r="F551" t="n">
         <v>-0.3955</v>
@@ -50728,7 +50728,7 @@
         <v>-0.0109</v>
       </c>
       <c r="J551" t="n">
-        <v>-0.2778</v>
+        <v>-0.2764</v>
       </c>
       <c r="K551" t="n">
         <v>-0.2401</v>
@@ -50747,16 +50747,16 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.3266</v>
+        <v>0.3269</v>
       </c>
       <c r="C552" t="n">
         <v>-0.3958</v>
       </c>
       <c r="D552" t="n">
-        <v>-0.0346</v>
+        <v>-0.0344</v>
       </c>
       <c r="E552" t="n">
-        <v>0.3266</v>
+        <v>0.3269</v>
       </c>
       <c r="F552" t="n">
         <v>-0.3958</v>
@@ -50771,7 +50771,7 @@
         <v>0.0418</v>
       </c>
       <c r="J552" t="n">
-        <v>-0.2902</v>
+        <v>-0.2888</v>
       </c>
       <c r="K552" t="n">
         <v>-0.2081</v>
@@ -50790,16 +50790,16 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.3285</v>
+        <v>0.3289</v>
       </c>
       <c r="C553" t="n">
         <v>-0.423</v>
       </c>
       <c r="D553" t="n">
-        <v>-0.0472</v>
+        <v>-0.047</v>
       </c>
       <c r="E553" t="n">
-        <v>0.3285</v>
+        <v>0.3289</v>
       </c>
       <c r="F553" t="n">
         <v>-0.423</v>
@@ -50814,7 +50814,7 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="J553" t="n">
-        <v>-0.3143</v>
+        <v>-0.3129</v>
       </c>
       <c r="K553" t="n">
         <v>-0.1918</v>
@@ -50833,16 +50833,16 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.4265</v>
+        <v>0.4268</v>
       </c>
       <c r="C554" t="n">
         <v>-0.4508</v>
       </c>
       <c r="D554" t="n">
-        <v>-0.0122</v>
+        <v>-0.012</v>
       </c>
       <c r="E554" t="n">
-        <v>0.4265</v>
+        <v>0.4268</v>
       </c>
       <c r="F554" t="n">
         <v>-0.4508</v>
@@ -50857,7 +50857,7 @@
         <v>0.1057</v>
       </c>
       <c r="J554" t="n">
-        <v>-0.311</v>
+        <v>-0.3096</v>
       </c>
       <c r="K554" t="n">
         <v>-0.1615</v>
@@ -50876,16 +50876,16 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.4524</v>
+        <v>0.4528</v>
       </c>
       <c r="C555" t="n">
         <v>-0.501</v>
       </c>
       <c r="D555" t="n">
-        <v>-0.0243</v>
+        <v>-0.0241</v>
       </c>
       <c r="E555" t="n">
-        <v>0.4524</v>
+        <v>0.4528</v>
       </c>
       <c r="F555" t="n">
         <v>-0.501</v>
@@ -50900,7 +50900,7 @@
         <v>0.1202</v>
       </c>
       <c r="J555" t="n">
-        <v>-0.2939</v>
+        <v>-0.2926</v>
       </c>
       <c r="K555" t="n">
         <v>-0.1403</v>
@@ -50919,16 +50919,16 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.5158</v>
+        <v>0.516</v>
       </c>
       <c r="C556" t="n">
         <v>-0.4863</v>
       </c>
       <c r="D556" t="n">
-        <v>0.0147</v>
+        <v>0.0149</v>
       </c>
       <c r="E556" t="n">
-        <v>0.5158</v>
+        <v>0.516</v>
       </c>
       <c r="F556" t="n">
         <v>-0.4863</v>
@@ -50943,7 +50943,7 @@
         <v>-0.05</v>
       </c>
       <c r="J556" t="n">
-        <v>0.0134</v>
+        <v>0.0144</v>
       </c>
       <c r="K556" t="n">
         <v>-0.1172</v>
@@ -50962,16 +50962,16 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.4905</v>
+        <v>0.4907</v>
       </c>
       <c r="C557" t="n">
         <v>-0.4493</v>
       </c>
       <c r="D557" t="n">
-        <v>0.0206</v>
+        <v>0.0207</v>
       </c>
       <c r="E557" t="n">
-        <v>0.4905</v>
+        <v>0.4907</v>
       </c>
       <c r="F557" t="n">
         <v>-0.4493</v>
@@ -50986,7 +50986,7 @@
         <v>-0.0979</v>
       </c>
       <c r="J557" t="n">
-        <v>0.1258</v>
+        <v>0.1267</v>
       </c>
       <c r="K557" t="n">
         <v>-0.0732</v>
@@ -51005,16 +51005,16 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.596</v>
+        <v>0.5961</v>
       </c>
       <c r="C558" t="n">
         <v>-0.3932</v>
       </c>
       <c r="D558" t="n">
-        <v>0.1014</v>
+        <v>0.1015</v>
       </c>
       <c r="E558" t="n">
-        <v>0.596</v>
+        <v>0.5961</v>
       </c>
       <c r="F558" t="n">
         <v>-0.3932</v>
@@ -51029,7 +51029,7 @@
         <v>-0.1218</v>
       </c>
       <c r="J558" t="n">
-        <v>0.2962</v>
+        <v>0.2968</v>
       </c>
       <c r="K558" t="n">
         <v>-0.0514</v>
@@ -51048,16 +51048,16 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.751</v>
+        <v>0.7511</v>
       </c>
       <c r="C559" t="n">
         <v>-0.3381</v>
       </c>
       <c r="D559" t="n">
-        <v>0.2064</v>
+        <v>0.2065</v>
       </c>
       <c r="E559" t="n">
-        <v>0.751</v>
+        <v>0.7511</v>
       </c>
       <c r="F559" t="n">
         <v>-0.3381</v>
@@ -51072,7 +51072,7 @@
         <v>-0.0345</v>
       </c>
       <c r="J559" t="n">
-        <v>0.455</v>
+        <v>0.4555</v>
       </c>
       <c r="K559" t="n">
         <v>-0.0105</v>
@@ -51091,7 +51091,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8121</v>
       </c>
       <c r="C560" t="n">
         <v>-0.2218</v>
@@ -51100,7 +51100,7 @@
         <v>0.2951</v>
       </c>
       <c r="E560" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8121</v>
       </c>
       <c r="F560" t="n">
         <v>-0.2218</v>
@@ -51115,7 +51115,7 @@
         <v>-0.039</v>
       </c>
       <c r="J560" t="n">
-        <v>0.6135</v>
+        <v>0.6138</v>
       </c>
       <c r="K560" t="n">
         <v>0.0813</v>
@@ -51158,7 +51158,7 @@
         <v>-0.0303</v>
       </c>
       <c r="J561" t="n">
-        <v>0.7571</v>
+        <v>0.7572</v>
       </c>
       <c r="K561" t="n">
         <v>0.1666</v>
@@ -51201,7 +51201,7 @@
         <v>-0.0222</v>
       </c>
       <c r="J562" t="n">
-        <v>0.8863</v>
+        <v>0.8862</v>
       </c>
       <c r="K562" t="n">
         <v>0.2379</v>
@@ -51220,7 +51220,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.8461</v>
+        <v>0.846</v>
       </c>
       <c r="C563" t="n">
         <v>0.07920000000000001</v>
@@ -51229,7 +51229,7 @@
         <v>0.4626</v>
       </c>
       <c r="E563" t="n">
-        <v>0.8461</v>
+        <v>0.846</v>
       </c>
       <c r="F563" t="n">
         <v>0.07920000000000001</v>
@@ -51244,7 +51244,7 @@
         <v>-0.0155</v>
       </c>
       <c r="J563" t="n">
-        <v>0.8995</v>
+        <v>0.8994</v>
       </c>
       <c r="K563" t="n">
         <v>0.3406</v>
@@ -51269,7 +51269,7 @@
         <v>0.1358</v>
       </c>
       <c r="D564" t="n">
-        <v>0.488</v>
+        <v>0.4879</v>
       </c>
       <c r="E564" t="n">
         <v>0.8401</v>
@@ -51287,7 +51287,7 @@
         <v>-0.0048</v>
       </c>
       <c r="J564" t="n">
-        <v>0.9428</v>
+        <v>0.9426</v>
       </c>
       <c r="K564" t="n">
         <v>0.4083</v>
@@ -51330,7 +51330,7 @@
         <v>0.029</v>
       </c>
       <c r="J565" t="n">
-        <v>0.9907</v>
+        <v>0.9905</v>
       </c>
       <c r="K565" t="n">
         <v>0.5086000000000001</v>
@@ -51373,7 +51373,7 @@
         <v>0.0429</v>
       </c>
       <c r="J566" t="n">
-        <v>0.9959</v>
+        <v>0.9957</v>
       </c>
       <c r="K566" t="n">
         <v>0.4955</v>
@@ -51416,7 +51416,7 @@
         <v>0.135</v>
       </c>
       <c r="J567" t="n">
-        <v>0.9369</v>
+        <v>0.9368</v>
       </c>
       <c r="K567" t="n">
         <v>0.515</v>
@@ -51459,7 +51459,7 @@
         <v>0.2425</v>
       </c>
       <c r="J568" t="n">
-        <v>0.6857</v>
+        <v>0.6859</v>
       </c>
       <c r="K568" t="n">
         <v>0.5058</v>
@@ -51502,7 +51502,7 @@
         <v>0.2879</v>
       </c>
       <c r="J569" t="n">
-        <v>0.5566</v>
+        <v>0.5569</v>
       </c>
       <c r="K569" t="n">
         <v>0.5053</v>
@@ -51521,16 +51521,16 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.5</v>
+        <v>0.5002</v>
       </c>
       <c r="C570" t="n">
         <v>0.3495</v>
       </c>
       <c r="D570" t="n">
-        <v>0.4247</v>
+        <v>0.4248</v>
       </c>
       <c r="E570" t="n">
-        <v>0.5</v>
+        <v>0.5002</v>
       </c>
       <c r="F570" t="n">
         <v>0.3495</v>
@@ -51545,7 +51545,7 @@
         <v>0.3157</v>
       </c>
       <c r="J570" t="n">
-        <v>0.3572</v>
+        <v>0.3578</v>
       </c>
       <c r="K570" t="n">
         <v>0.5169</v>
@@ -51564,16 +51564,16 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.3676</v>
+        <v>0.3678</v>
       </c>
       <c r="C571" t="n">
         <v>0.3719</v>
       </c>
       <c r="D571" t="n">
-        <v>0.3698</v>
+        <v>0.3699</v>
       </c>
       <c r="E571" t="n">
-        <v>0.3676</v>
+        <v>0.3678</v>
       </c>
       <c r="F571" t="n">
         <v>0.3719</v>
@@ -51588,7 +51588,7 @@
         <v>0.3562</v>
       </c>
       <c r="J571" t="n">
-        <v>0.1488</v>
+        <v>0.1496</v>
       </c>
       <c r="K571" t="n">
         <v>0.5288</v>
@@ -51607,16 +51607,16 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.3314</v>
+        <v>0.3316</v>
       </c>
       <c r="C572" t="n">
         <v>0.3337</v>
       </c>
       <c r="D572" t="n">
-        <v>0.3326</v>
+        <v>0.3327</v>
       </c>
       <c r="E572" t="n">
-        <v>0.3314</v>
+        <v>0.3316</v>
       </c>
       <c r="F572" t="n">
         <v>0.3337</v>
@@ -51631,7 +51631,7 @@
         <v>0.327</v>
       </c>
       <c r="J572" t="n">
-        <v>0.0167</v>
+        <v>0.0177</v>
       </c>
       <c r="K572" t="n">
         <v>0.4355</v>
@@ -51650,16 +51650,16 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.2829</v>
+        <v>0.2832</v>
       </c>
       <c r="C573" t="n">
         <v>0.3186</v>
       </c>
       <c r="D573" t="n">
-        <v>0.3008</v>
+        <v>0.3009</v>
       </c>
       <c r="E573" t="n">
-        <v>0.2829</v>
+        <v>0.2832</v>
       </c>
       <c r="F573" t="n">
         <v>0.3186</v>
@@ -51674,7 +51674,7 @@
         <v>0.312</v>
       </c>
       <c r="J573" t="n">
-        <v>-0.1327</v>
+        <v>-0.1315</v>
       </c>
       <c r="K573" t="n">
         <v>0.3682</v>
@@ -51693,16 +51693,16 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.2459</v>
+        <v>0.2463</v>
       </c>
       <c r="C574" t="n">
         <v>0.2615</v>
       </c>
       <c r="D574" t="n">
-        <v>0.2537</v>
+        <v>0.2539</v>
       </c>
       <c r="E574" t="n">
-        <v>0.2459</v>
+        <v>0.2463</v>
       </c>
       <c r="F574" t="n">
         <v>0.2615</v>
@@ -51717,7 +51717,7 @@
         <v>0.3271</v>
       </c>
       <c r="J574" t="n">
-        <v>-0.2357</v>
+        <v>-0.2344</v>
       </c>
       <c r="K574" t="n">
         <v>0.2881</v>
@@ -51736,16 +51736,16 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.2623</v>
+        <v>0.2627</v>
       </c>
       <c r="C575" t="n">
         <v>0.2303</v>
       </c>
       <c r="D575" t="n">
-        <v>0.2463</v>
+        <v>0.2465</v>
       </c>
       <c r="E575" t="n">
-        <v>0.2623</v>
+        <v>0.2627</v>
       </c>
       <c r="F575" t="n">
         <v>0.2303</v>
@@ -51760,7 +51760,7 @@
         <v>0.4651</v>
       </c>
       <c r="J575" t="n">
-        <v>-0.31</v>
+        <v>-0.3086</v>
       </c>
       <c r="K575" t="n">
         <v>0.1979</v>
@@ -51779,16 +51779,16 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.2852</v>
+        <v>0.2856</v>
       </c>
       <c r="C576" t="n">
         <v>0.2437</v>
       </c>
       <c r="D576" t="n">
-        <v>0.2645</v>
+        <v>0.2646</v>
       </c>
       <c r="E576" t="n">
-        <v>0.2852</v>
+        <v>0.2856</v>
       </c>
       <c r="F576" t="n">
         <v>0.2437</v>
@@ -51803,7 +51803,7 @@
         <v>0.4978</v>
       </c>
       <c r="J576" t="n">
-        <v>-0.3525</v>
+        <v>-0.351</v>
       </c>
       <c r="K576" t="n">
         <v>0.1389</v>
@@ -51822,16 +51822,16 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5624</v>
       </c>
       <c r="C577" t="n">
         <v>0.2027</v>
       </c>
       <c r="D577" t="n">
-        <v>0.3824</v>
+        <v>0.3825</v>
       </c>
       <c r="E577" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5624</v>
       </c>
       <c r="F577" t="n">
         <v>0.2027</v>
@@ -51846,7 +51846,7 @@
         <v>0.4899</v>
       </c>
       <c r="J577" t="n">
-        <v>-0.3687</v>
+        <v>-0.3672</v>
       </c>
       <c r="K577" t="n">
         <v>0.0349</v>
@@ -51865,16 +51865,16 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.2284</v>
+        <v>0.2288</v>
       </c>
       <c r="C578" t="n">
         <v>0.1485</v>
       </c>
       <c r="D578" t="n">
-        <v>0.1885</v>
+        <v>0.1886</v>
       </c>
       <c r="E578" t="n">
-        <v>0.2284</v>
+        <v>0.2288</v>
       </c>
       <c r="F578" t="n">
         <v>0.1485</v>
@@ -51889,7 +51889,7 @@
         <v>0.5427999999999999</v>
       </c>
       <c r="J578" t="n">
-        <v>-0.4248</v>
+        <v>-0.4233</v>
       </c>
       <c r="K578" t="n">
         <v>-0.032</v>
@@ -51908,16 +51908,16 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.248</v>
+        <v>0.2484</v>
       </c>
       <c r="C579" t="n">
         <v>0.1301</v>
       </c>
       <c r="D579" t="n">
-        <v>0.1891</v>
+        <v>0.1892</v>
       </c>
       <c r="E579" t="n">
-        <v>0.248</v>
+        <v>0.2484</v>
       </c>
       <c r="F579" t="n">
         <v>0.1301</v>
@@ -51932,7 +51932,7 @@
         <v>0.5749</v>
       </c>
       <c r="J579" t="n">
-        <v>-0.4031</v>
+        <v>-0.4016</v>
       </c>
       <c r="K579" t="n">
         <v>-0.1029</v>
@@ -51951,16 +51951,16 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.3076</v>
+        <v>0.3079</v>
       </c>
       <c r="C580" t="n">
         <v>0.0774</v>
       </c>
       <c r="D580" t="n">
-        <v>0.1925</v>
+        <v>0.1927</v>
       </c>
       <c r="E580" t="n">
-        <v>0.3076</v>
+        <v>0.3079</v>
       </c>
       <c r="F580" t="n">
         <v>0.0774</v>
@@ -51975,7 +51975,7 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="J580" t="n">
-        <v>-0.3672</v>
+        <v>-0.3657</v>
       </c>
       <c r="K580" t="n">
         <v>-0.2098</v>
@@ -51994,16 +51994,16 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.4981</v>
+        <v>0.4985</v>
       </c>
       <c r="C581" t="n">
         <v>0.0474</v>
       </c>
       <c r="D581" t="n">
-        <v>0.2728</v>
+        <v>0.2729</v>
       </c>
       <c r="E581" t="n">
-        <v>0.4981</v>
+        <v>0.4985</v>
       </c>
       <c r="F581" t="n">
         <v>0.0474</v>
@@ -52018,7 +52018,7 @@
         <v>0.9538</v>
       </c>
       <c r="J581" t="n">
-        <v>-0.4001</v>
+        <v>-0.3985</v>
       </c>
       <c r="K581" t="n">
         <v>-0.2864</v>
@@ -52037,16 +52037,16 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.4612</v>
+        <v>0.4616</v>
       </c>
       <c r="C582" t="n">
         <v>0.0428</v>
       </c>
       <c r="D582" t="n">
-        <v>0.252</v>
+        <v>0.2522</v>
       </c>
       <c r="E582" t="n">
-        <v>0.4612</v>
+        <v>0.4616</v>
       </c>
       <c r="F582" t="n">
         <v>0.0428</v>
@@ -52061,7 +52061,7 @@
         <v>0.9804</v>
       </c>
       <c r="J582" t="n">
-        <v>-0.4644</v>
+        <v>-0.4628</v>
       </c>
       <c r="K582" t="n">
         <v>-0.3587</v>
@@ -52080,16 +52080,16 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.522</v>
+        <v>0.5224</v>
       </c>
       <c r="C583" t="n">
         <v>-0.0398</v>
       </c>
       <c r="D583" t="n">
-        <v>0.2411</v>
+        <v>0.2413</v>
       </c>
       <c r="E583" t="n">
-        <v>0.522</v>
+        <v>0.5224</v>
       </c>
       <c r="F583" t="n">
         <v>-0.0398</v>
@@ -52104,7 +52104,7 @@
         <v>1.1727</v>
       </c>
       <c r="J583" t="n">
-        <v>-0.4247</v>
+        <v>-0.4231</v>
       </c>
       <c r="K583" t="n">
         <v>-0.4176</v>
@@ -52123,16 +52123,16 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5332</v>
       </c>
       <c r="C584" t="n">
         <v>-0.0711</v>
       </c>
       <c r="D584" t="n">
-        <v>0.2308</v>
+        <v>0.231</v>
       </c>
       <c r="E584" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5332</v>
       </c>
       <c r="F584" t="n">
         <v>-0.0711</v>
@@ -52147,7 +52147,7 @@
         <v>1.2242</v>
       </c>
       <c r="J584" t="n">
-        <v>-0.5547</v>
+        <v>-0.553</v>
       </c>
       <c r="K584" t="n">
         <v>-0.4417</v>
@@ -52166,16 +52166,16 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.5149</v>
+        <v>0.5154</v>
       </c>
       <c r="C585" t="n">
         <v>-0.1246</v>
       </c>
       <c r="D585" t="n">
-        <v>0.1952</v>
+        <v>0.1954</v>
       </c>
       <c r="E585" t="n">
-        <v>0.5149</v>
+        <v>0.5154</v>
       </c>
       <c r="F585" t="n">
         <v>-0.1246</v>
@@ -52190,7 +52190,7 @@
         <v>1.1579</v>
       </c>
       <c r="J585" t="n">
-        <v>-0.7447</v>
+        <v>-0.7427</v>
       </c>
       <c r="K585" t="n">
         <v>-0.4681</v>
@@ -52209,16 +52209,16 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5686</v>
       </c>
       <c r="C586" t="n">
         <v>-0.193</v>
       </c>
       <c r="D586" t="n">
-        <v>0.1875</v>
+        <v>0.1878</v>
       </c>
       <c r="E586" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5686</v>
       </c>
       <c r="F586" t="n">
         <v>-0.193</v>
@@ -52233,7 +52233,7 @@
         <v>1.3606</v>
       </c>
       <c r="J586" t="n">
-        <v>-0.9447</v>
+        <v>-0.9425</v>
       </c>
       <c r="K586" t="n">
         <v>-0.4944</v>
@@ -52252,16 +52252,16 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.6449</v>
+        <v>0.6454</v>
       </c>
       <c r="C587" t="n">
         <v>-0.2766</v>
       </c>
       <c r="D587" t="n">
-        <v>0.1841</v>
+        <v>0.1844</v>
       </c>
       <c r="E587" t="n">
-        <v>0.6449</v>
+        <v>0.6454</v>
       </c>
       <c r="F587" t="n">
         <v>-0.2766</v>
@@ -52276,7 +52276,7 @@
         <v>1.444</v>
       </c>
       <c r="J587" t="n">
-        <v>-0.8577</v>
+        <v>-0.8556</v>
       </c>
       <c r="K587" t="n">
         <v>-0.4977</v>
@@ -52295,16 +52295,16 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.642</v>
+        <v>0.6425</v>
       </c>
       <c r="C588" t="n">
         <v>-0.316</v>
       </c>
       <c r="D588" t="n">
-        <v>0.163</v>
+        <v>0.1633</v>
       </c>
       <c r="E588" t="n">
-        <v>0.642</v>
+        <v>0.6425</v>
       </c>
       <c r="F588" t="n">
         <v>-0.316</v>
@@ -52319,7 +52319,7 @@
         <v>1.3258</v>
       </c>
       <c r="J588" t="n">
-        <v>-0.8479</v>
+        <v>-0.8458</v>
       </c>
       <c r="K588" t="n">
         <v>-0.5372</v>
@@ -52338,16 +52338,16 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.5047</v>
+        <v>0.5052</v>
       </c>
       <c r="C589" t="n">
         <v>-0.3634</v>
       </c>
       <c r="D589" t="n">
-        <v>0.0707</v>
+        <v>0.0709</v>
       </c>
       <c r="E589" t="n">
-        <v>0.5047</v>
+        <v>0.5052</v>
       </c>
       <c r="F589" t="n">
         <v>-0.3634</v>
@@ -52362,7 +52362,7 @@
         <v>1.1332</v>
       </c>
       <c r="J589" t="n">
-        <v>-0.768</v>
+        <v>-0.766</v>
       </c>
       <c r="K589" t="n">
         <v>-0.5601</v>
@@ -52381,16 +52381,16 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.6964</v>
+        <v>0.6968</v>
       </c>
       <c r="C590" t="n">
         <v>-0.4211</v>
       </c>
       <c r="D590" t="n">
-        <v>0.1377</v>
+        <v>0.1379</v>
       </c>
       <c r="E590" t="n">
-        <v>0.6964</v>
+        <v>0.6968</v>
       </c>
       <c r="F590" t="n">
         <v>-0.4211</v>
@@ -52405,7 +52405,7 @@
         <v>1.0239</v>
       </c>
       <c r="J590" t="n">
-        <v>-0.4953</v>
+        <v>-0.4937</v>
       </c>
       <c r="K590" t="n">
         <v>-0.5951</v>
@@ -52424,16 +52424,16 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.5898</v>
+        <v>0.5903</v>
       </c>
       <c r="C591" t="n">
         <v>-0.3761</v>
       </c>
       <c r="D591" t="n">
-        <v>0.1069</v>
+        <v>0.1071</v>
       </c>
       <c r="E591" t="n">
-        <v>0.5898</v>
+        <v>0.5903</v>
       </c>
       <c r="F591" t="n">
         <v>-0.3761</v>
@@ -52448,7 +52448,7 @@
         <v>1.1217</v>
       </c>
       <c r="J591" t="n">
-        <v>-0.4922</v>
+        <v>-0.4906</v>
       </c>
       <c r="K591" t="n">
         <v>-0.5815</v>
@@ -52467,16 +52467,16 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5706</v>
       </c>
       <c r="C592" t="n">
         <v>-0.4315</v>
       </c>
       <c r="D592" t="n">
-        <v>0.0693</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E592" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5706</v>
       </c>
       <c r="F592" t="n">
         <v>-0.4315</v>
@@ -52491,7 +52491,7 @@
         <v>1.1199</v>
       </c>
       <c r="J592" t="n">
-        <v>-0.5886</v>
+        <v>-0.5869</v>
       </c>
       <c r="K592" t="n">
         <v>-0.5849</v>
@@ -52510,16 +52510,16 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.6057</v>
+        <v>0.6061</v>
       </c>
       <c r="C593" t="n">
         <v>-0.4141</v>
       </c>
       <c r="D593" t="n">
-        <v>0.0958</v>
+        <v>0.096</v>
       </c>
       <c r="E593" t="n">
-        <v>0.6057</v>
+        <v>0.6061</v>
       </c>
       <c r="F593" t="n">
         <v>-0.4141</v>
@@ -52534,7 +52534,7 @@
         <v>1.1165</v>
       </c>
       <c r="J593" t="n">
-        <v>-0.5649</v>
+        <v>-0.5632</v>
       </c>
       <c r="K593" t="n">
         <v>-0.6163</v>
@@ -52553,16 +52553,16 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.6217</v>
+        <v>0.6222</v>
       </c>
       <c r="C594" t="n">
         <v>-0.4023</v>
       </c>
       <c r="D594" t="n">
-        <v>0.1097</v>
+        <v>0.1099</v>
       </c>
       <c r="E594" t="n">
-        <v>0.6217</v>
+        <v>0.6222</v>
       </c>
       <c r="F594" t="n">
         <v>-0.4023</v>
@@ -52577,7 +52577,7 @@
         <v>1.2182</v>
       </c>
       <c r="J594" t="n">
-        <v>-0.4925</v>
+        <v>-0.4909</v>
       </c>
       <c r="K594" t="n">
         <v>-0.6467000000000001</v>
@@ -52596,16 +52596,16 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.6587</v>
+        <v>0.6591</v>
       </c>
       <c r="C595" t="n">
         <v>-0.3403</v>
       </c>
       <c r="D595" t="n">
-        <v>0.1592</v>
+        <v>0.1594</v>
       </c>
       <c r="E595" t="n">
-        <v>0.6587</v>
+        <v>0.6591</v>
       </c>
       <c r="F595" t="n">
         <v>-0.3403</v>
@@ -52620,7 +52620,7 @@
         <v>1.337</v>
       </c>
       <c r="J595" t="n">
-        <v>-0.577</v>
+        <v>-0.5753</v>
       </c>
       <c r="K595" t="n">
         <v>-0.6661</v>
@@ -52639,16 +52639,16 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.665</v>
+        <v>0.6654</v>
       </c>
       <c r="C596" t="n">
         <v>-0.2967</v>
       </c>
       <c r="D596" t="n">
-        <v>0.1841</v>
+        <v>0.1843</v>
       </c>
       <c r="E596" t="n">
-        <v>0.665</v>
+        <v>0.6654</v>
       </c>
       <c r="F596" t="n">
         <v>-0.2967</v>
@@ -52663,7 +52663,7 @@
         <v>1.3299</v>
       </c>
       <c r="J596" t="n">
-        <v>-0.4224</v>
+        <v>-0.4208</v>
       </c>
       <c r="K596" t="n">
         <v>-0.6519</v>
@@ -52672,7 +52672,7 @@
         <v>0.5352</v>
       </c>
       <c r="M596" t="n">
-        <v>-0.7733</v>
+        <v>-0.7734</v>
       </c>
     </row>
     <row r="597">
@@ -52682,16 +52682,16 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7348</v>
       </c>
       <c r="C597" t="n">
         <v>-0.3372</v>
       </c>
       <c r="D597" t="n">
-        <v>0.1986</v>
+        <v>0.1988</v>
       </c>
       <c r="E597" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7348</v>
       </c>
       <c r="F597" t="n">
         <v>-0.3372</v>
@@ -52706,7 +52706,7 @@
         <v>1.4318</v>
       </c>
       <c r="J597" t="n">
-        <v>-0.1935</v>
+        <v>-0.1922</v>
       </c>
       <c r="K597" t="n">
         <v>-0.6552</v>
@@ -52725,16 +52725,16 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.7442</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="C598" t="n">
         <v>-0.2526</v>
       </c>
       <c r="D598" t="n">
-        <v>0.2458</v>
+        <v>0.2459</v>
       </c>
       <c r="E598" t="n">
-        <v>0.7442</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="F598" t="n">
         <v>-0.2526</v>
@@ -52749,7 +52749,7 @@
         <v>1.502</v>
       </c>
       <c r="J598" t="n">
-        <v>-0.0143</v>
+        <v>-0.0132</v>
       </c>
       <c r="K598" t="n">
         <v>-0.6693</v>
@@ -52768,16 +52768,16 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7648</v>
       </c>
       <c r="C599" t="n">
         <v>-0.2279</v>
       </c>
       <c r="D599" t="n">
-        <v>0.2684</v>
+        <v>0.2685</v>
       </c>
       <c r="E599" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7648</v>
       </c>
       <c r="F599" t="n">
         <v>-0.2279</v>
@@ -52792,7 +52792,7 @@
         <v>1.5253</v>
       </c>
       <c r="J599" t="n">
-        <v>-0.0325</v>
+        <v>-0.0315</v>
       </c>
       <c r="K599" t="n">
         <v>-0.6399</v>
@@ -52811,16 +52811,16 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.7183</v>
+        <v>0.7186</v>
       </c>
       <c r="C600" t="n">
         <v>-0.2807</v>
       </c>
       <c r="D600" t="n">
-        <v>0.2188</v>
+        <v>0.219</v>
       </c>
       <c r="E600" t="n">
-        <v>0.7183</v>
+        <v>0.7186</v>
       </c>
       <c r="F600" t="n">
         <v>-0.2807</v>
@@ -52835,7 +52835,7 @@
         <v>1.5626</v>
       </c>
       <c r="J600" t="n">
-        <v>-0.0238</v>
+        <v>-0.0227</v>
       </c>
       <c r="K600" t="n">
         <v>-0.6473</v>
@@ -52854,16 +52854,16 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.666</v>
+        <v>0.6663</v>
       </c>
       <c r="C601" t="n">
         <v>-0.2475</v>
       </c>
       <c r="D601" t="n">
-        <v>0.2093</v>
+        <v>0.2094</v>
       </c>
       <c r="E601" t="n">
-        <v>0.666</v>
+        <v>0.6663</v>
       </c>
       <c r="F601" t="n">
         <v>-0.2475</v>
@@ -52878,7 +52878,7 @@
         <v>1.4113</v>
       </c>
       <c r="J601" t="n">
-        <v>-0.1242</v>
+        <v>-0.1231</v>
       </c>
       <c r="K601" t="n">
         <v>-0.6564</v>
@@ -52897,16 +52897,16 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.5496</v>
+        <v>0.55</v>
       </c>
       <c r="C602" t="n">
         <v>-0.224</v>
       </c>
       <c r="D602" t="n">
-        <v>0.1628</v>
+        <v>0.163</v>
       </c>
       <c r="E602" t="n">
-        <v>0.5496</v>
+        <v>0.55</v>
       </c>
       <c r="F602" t="n">
         <v>-0.224</v>
@@ -52921,7 +52921,7 @@
         <v>1.4742</v>
       </c>
       <c r="J602" t="n">
-        <v>-0.3636</v>
+        <v>-0.3622</v>
       </c>
       <c r="K602" t="n">
         <v>-0.6471</v>
@@ -52940,16 +52940,16 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.6545</v>
+        <v>0.6549</v>
       </c>
       <c r="C603" t="n">
         <v>-0.2141</v>
       </c>
       <c r="D603" t="n">
-        <v>0.2202</v>
+        <v>0.2204</v>
       </c>
       <c r="E603" t="n">
-        <v>0.6545</v>
+        <v>0.6549</v>
       </c>
       <c r="F603" t="n">
         <v>-0.2141</v>
@@ -52964,7 +52964,7 @@
         <v>1.5868</v>
       </c>
       <c r="J603" t="n">
-        <v>-0.3823</v>
+        <v>-0.3808</v>
       </c>
       <c r="K603" t="n">
         <v>-0.6225000000000001</v>
@@ -52983,16 +52983,16 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.6229</v>
+        <v>0.6233</v>
       </c>
       <c r="C604" t="n">
         <v>-0.1688</v>
       </c>
       <c r="D604" t="n">
-        <v>0.2271</v>
+        <v>0.2272</v>
       </c>
       <c r="E604" t="n">
-        <v>0.6229</v>
+        <v>0.6233</v>
       </c>
       <c r="F604" t="n">
         <v>-0.1688</v>
@@ -53007,7 +53007,7 @@
         <v>1.5843</v>
       </c>
       <c r="J604" t="n">
-        <v>-0.3768</v>
+        <v>-0.3753</v>
       </c>
       <c r="K604" t="n">
         <v>-0.6161</v>
@@ -53026,16 +53026,16 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.5772</v>
+        <v>0.5775</v>
       </c>
       <c r="C605" t="n">
         <v>-0.1467</v>
       </c>
       <c r="D605" t="n">
-        <v>0.2152</v>
+        <v>0.2154</v>
       </c>
       <c r="E605" t="n">
-        <v>0.5772</v>
+        <v>0.5775</v>
       </c>
       <c r="F605" t="n">
         <v>-0.1467</v>
@@ -53050,7 +53050,7 @@
         <v>1.6774</v>
       </c>
       <c r="J605" t="n">
-        <v>-0.4068</v>
+        <v>-0.4053</v>
       </c>
       <c r="K605" t="n">
         <v>-0.6133</v>
@@ -53069,16 +53069,16 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.6254</v>
+        <v>0.6258</v>
       </c>
       <c r="C606" t="n">
         <v>-0.1349</v>
       </c>
       <c r="D606" t="n">
-        <v>0.2453</v>
+        <v>0.2455</v>
       </c>
       <c r="E606" t="n">
-        <v>0.6254</v>
+        <v>0.6258</v>
       </c>
       <c r="F606" t="n">
         <v>-0.1349</v>
@@ -53093,7 +53093,7 @@
         <v>1.7417</v>
       </c>
       <c r="J606" t="n">
-        <v>-0.4333</v>
+        <v>-0.4318</v>
       </c>
       <c r="K606" t="n">
         <v>-0.6034</v>
@@ -53112,16 +53112,16 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.6499</v>
+        <v>0.6503</v>
       </c>
       <c r="C607" t="n">
         <v>-0.1256</v>
       </c>
       <c r="D607" t="n">
-        <v>0.2622</v>
+        <v>0.2623</v>
       </c>
       <c r="E607" t="n">
-        <v>0.6499</v>
+        <v>0.6503</v>
       </c>
       <c r="F607" t="n">
         <v>-0.1256</v>
@@ -53136,7 +53136,7 @@
         <v>1.7927</v>
       </c>
       <c r="J607" t="n">
-        <v>-0.3805</v>
+        <v>-0.3791</v>
       </c>
       <c r="K607" t="n">
         <v>-0.6027</v>
@@ -53155,16 +53155,16 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.6796</v>
+        <v>0.68</v>
       </c>
       <c r="C608" t="n">
         <v>-0.157</v>
       </c>
       <c r="D608" t="n">
-        <v>0.2613</v>
+        <v>0.2615</v>
       </c>
       <c r="E608" t="n">
-        <v>0.6796</v>
+        <v>0.68</v>
       </c>
       <c r="F608" t="n">
         <v>-0.157</v>
@@ -53179,7 +53179,7 @@
         <v>1.7907</v>
       </c>
       <c r="J608" t="n">
-        <v>-0.3898</v>
+        <v>-0.3883</v>
       </c>
       <c r="K608" t="n">
         <v>-0.6482</v>
@@ -53198,16 +53198,16 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.5876</v>
+        <v>0.588</v>
       </c>
       <c r="C609" t="n">
         <v>-0.1827</v>
       </c>
       <c r="D609" t="n">
-        <v>0.2024</v>
+        <v>0.2026</v>
       </c>
       <c r="E609" t="n">
-        <v>0.5876</v>
+        <v>0.588</v>
       </c>
       <c r="F609" t="n">
         <v>-0.1827</v>
@@ -53222,7 +53222,7 @@
         <v>1.4683</v>
       </c>
       <c r="J609" t="n">
-        <v>-0.427</v>
+        <v>-0.4255</v>
       </c>
       <c r="K609" t="n">
         <v>-0.6542</v>
@@ -53241,16 +53241,16 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.5131</v>
+        <v>0.5135</v>
       </c>
       <c r="C610" t="n">
         <v>-0.1635</v>
       </c>
       <c r="D610" t="n">
-        <v>0.1748</v>
+        <v>0.175</v>
       </c>
       <c r="E610" t="n">
-        <v>0.5131</v>
+        <v>0.5135</v>
       </c>
       <c r="F610" t="n">
         <v>-0.1635</v>
@@ -53265,7 +53265,7 @@
         <v>1.3983</v>
       </c>
       <c r="J610" t="n">
-        <v>-0.4674</v>
+        <v>-0.4658</v>
       </c>
       <c r="K610" t="n">
         <v>-0.6886</v>
@@ -53284,16 +53284,16 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.5269</v>
+        <v>0.5273</v>
       </c>
       <c r="C611" t="n">
         <v>-0.1745</v>
       </c>
       <c r="D611" t="n">
-        <v>0.1762</v>
+        <v>0.1764</v>
       </c>
       <c r="E611" t="n">
-        <v>0.5269</v>
+        <v>0.5273</v>
       </c>
       <c r="F611" t="n">
         <v>-0.1745</v>
@@ -53308,7 +53308,7 @@
         <v>1.5804</v>
       </c>
       <c r="J611" t="n">
-        <v>-0.5205</v>
+        <v>-0.5188</v>
       </c>
       <c r="K611" t="n">
         <v>-0.7396</v>
@@ -53327,16 +53327,16 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5775</v>
       </c>
       <c r="C612" t="n">
         <v>-0.1589</v>
       </c>
       <c r="D612" t="n">
-        <v>0.2091</v>
+        <v>0.2093</v>
       </c>
       <c r="E612" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5775</v>
       </c>
       <c r="F612" t="n">
         <v>-0.1589</v>
@@ -53351,7 +53351,7 @@
         <v>1.643</v>
       </c>
       <c r="J612" t="n">
-        <v>-0.5395</v>
+        <v>-0.5379</v>
       </c>
       <c r="K612" t="n">
         <v>-0.7401</v>
@@ -53370,16 +53370,16 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.5854</v>
+        <v>0.5858</v>
       </c>
       <c r="C613" t="n">
         <v>-0.1638</v>
       </c>
       <c r="D613" t="n">
-        <v>0.2108</v>
+        <v>0.211</v>
       </c>
       <c r="E613" t="n">
-        <v>0.5854</v>
+        <v>0.5858</v>
       </c>
       <c r="F613" t="n">
         <v>-0.1638</v>
@@ -53394,7 +53394,7 @@
         <v>1.6211</v>
       </c>
       <c r="J613" t="n">
-        <v>-0.5962</v>
+        <v>-0.5944</v>
       </c>
       <c r="K613" t="n">
         <v>-0.7674</v>
@@ -53403,7 +53403,7 @@
         <v>0.3813</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1053</v>
+        <v>-0.1054</v>
       </c>
     </row>
     <row r="614">
@@ -53413,16 +53413,16 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.624</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="C614" t="n">
         <v>-0.1478</v>
       </c>
       <c r="D614" t="n">
-        <v>0.2381</v>
+        <v>0.2383</v>
       </c>
       <c r="E614" t="n">
-        <v>0.624</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="F614" t="n">
         <v>-0.1478</v>
@@ -53437,7 +53437,7 @@
         <v>1.6792</v>
       </c>
       <c r="J614" t="n">
-        <v>-0.6888</v>
+        <v>-0.6869</v>
       </c>
       <c r="K614" t="n">
         <v>-0.7917</v>
@@ -53456,16 +53456,16 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.5544</v>
+        <v>0.5548</v>
       </c>
       <c r="C615" t="n">
         <v>-0.1428</v>
       </c>
       <c r="D615" t="n">
-        <v>0.2058</v>
+        <v>0.206</v>
       </c>
       <c r="E615" t="n">
-        <v>0.5544</v>
+        <v>0.5548</v>
       </c>
       <c r="F615" t="n">
         <v>-0.1428</v>
@@ -53480,7 +53480,7 @@
         <v>1.5615</v>
       </c>
       <c r="J615" t="n">
-        <v>-0.7</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="K615" t="n">
         <v>-0.8374</v>
@@ -53499,16 +53499,16 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.5336</v>
+        <v>0.5342</v>
       </c>
       <c r="C616" t="n">
         <v>-0.1406</v>
       </c>
       <c r="D616" t="n">
-        <v>0.1965</v>
+        <v>0.1968</v>
       </c>
       <c r="E616" t="n">
-        <v>0.5336</v>
+        <v>0.5342</v>
       </c>
       <c r="F616" t="n">
         <v>-0.1406</v>
@@ -53523,7 +53523,7 @@
         <v>1.4947</v>
       </c>
       <c r="J616" t="n">
-        <v>-0.8225</v>
+        <v>-0.8204</v>
       </c>
       <c r="K616" t="n">
         <v>-0.8561</v>
@@ -53532,7 +53532,7 @@
         <v>0.3747</v>
       </c>
       <c r="M616" t="n">
-        <v>0.0598</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="617">
@@ -53542,16 +53542,16 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.5432</v>
+        <v>0.5437</v>
       </c>
       <c r="C617" t="n">
         <v>-0.1866</v>
       </c>
       <c r="D617" t="n">
-        <v>0.1783</v>
+        <v>0.1786</v>
       </c>
       <c r="E617" t="n">
-        <v>0.5432</v>
+        <v>0.5437</v>
       </c>
       <c r="F617" t="n">
         <v>-0.1866</v>
@@ -53566,7 +53566,7 @@
         <v>1.341</v>
       </c>
       <c r="J617" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.824</v>
       </c>
       <c r="K617" t="n">
         <v>-0.873</v>
@@ -53585,16 +53585,16 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.5738</v>
+        <v>0.5743</v>
       </c>
       <c r="C618" t="n">
         <v>-0.1973</v>
       </c>
       <c r="D618" t="n">
-        <v>0.1882</v>
+        <v>0.1885</v>
       </c>
       <c r="E618" t="n">
-        <v>0.5738</v>
+        <v>0.5743</v>
       </c>
       <c r="F618" t="n">
         <v>-0.1973</v>
@@ -53609,7 +53609,7 @@
         <v>1.3979</v>
       </c>
       <c r="J618" t="n">
-        <v>-0.8285</v>
+        <v>-0.8265</v>
       </c>
       <c r="K618" t="n">
         <v>-0.901</v>
@@ -53628,16 +53628,16 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.5303</v>
+        <v>0.5309</v>
       </c>
       <c r="C619" t="n">
         <v>-0.2198</v>
       </c>
       <c r="D619" t="n">
-        <v>0.1552</v>
+        <v>0.1555</v>
       </c>
       <c r="E619" t="n">
-        <v>0.5303</v>
+        <v>0.5309</v>
       </c>
       <c r="F619" t="n">
         <v>-0.2198</v>
@@ -53652,7 +53652,7 @@
         <v>1.4194</v>
       </c>
       <c r="J619" t="n">
-        <v>-0.911</v>
+        <v>-0.9089</v>
       </c>
       <c r="K619" t="n">
         <v>-0.9232</v>
@@ -53671,16 +53671,16 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.5072</v>
+        <v>0.5077</v>
       </c>
       <c r="C620" t="n">
         <v>-0.2287</v>
       </c>
       <c r="D620" t="n">
-        <v>0.1392</v>
+        <v>0.1395</v>
       </c>
       <c r="E620" t="n">
-        <v>0.5072</v>
+        <v>0.5077</v>
       </c>
       <c r="F620" t="n">
         <v>-0.2287</v>
@@ -53695,7 +53695,7 @@
         <v>1.512</v>
       </c>
       <c r="J620" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.9429</v>
       </c>
       <c r="K620" t="n">
         <v>-0.9443</v>
@@ -53714,16 +53714,16 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.4806</v>
+        <v>0.4811</v>
       </c>
       <c r="C621" t="n">
         <v>-0.2412</v>
       </c>
       <c r="D621" t="n">
-        <v>0.1197</v>
+        <v>0.12</v>
       </c>
       <c r="E621" t="n">
-        <v>0.4806</v>
+        <v>0.4811</v>
       </c>
       <c r="F621" t="n">
         <v>-0.2412</v>
@@ -53738,7 +53738,7 @@
         <v>1.519</v>
       </c>
       <c r="J621" t="n">
-        <v>-0.948</v>
+        <v>-0.9458</v>
       </c>
       <c r="K621" t="n">
         <v>-1.0242</v>
@@ -53757,16 +53757,16 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.4712</v>
+        <v>0.4718</v>
       </c>
       <c r="C622" t="n">
         <v>-0.2332</v>
       </c>
       <c r="D622" t="n">
-        <v>0.119</v>
+        <v>0.1193</v>
       </c>
       <c r="E622" t="n">
-        <v>0.4712</v>
+        <v>0.4718</v>
       </c>
       <c r="F622" t="n">
         <v>-0.2332</v>
@@ -53781,7 +53781,7 @@
         <v>1.545</v>
       </c>
       <c r="J622" t="n">
-        <v>-1.1078</v>
+        <v>-1.1054</v>
       </c>
       <c r="K622" t="n">
         <v>-1.0474</v>
@@ -53800,16 +53800,16 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5182</v>
       </c>
       <c r="C623" t="n">
         <v>-0.268</v>
       </c>
       <c r="D623" t="n">
-        <v>0.1248</v>
+        <v>0.1251</v>
       </c>
       <c r="E623" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5182</v>
       </c>
       <c r="F623" t="n">
         <v>-0.268</v>
@@ -53824,7 +53824,7 @@
         <v>1.6322</v>
       </c>
       <c r="J623" t="n">
-        <v>-1.1328</v>
+        <v>-1.1304</v>
       </c>
       <c r="K623" t="n">
         <v>-1.0774</v>
@@ -53843,16 +53843,16 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.5419</v>
+        <v>0.5425</v>
       </c>
       <c r="C624" t="n">
         <v>-0.2474</v>
       </c>
       <c r="D624" t="n">
-        <v>0.1473</v>
+        <v>0.1476</v>
       </c>
       <c r="E624" t="n">
-        <v>0.5419</v>
+        <v>0.5425</v>
       </c>
       <c r="F624" t="n">
         <v>-0.2474</v>
@@ -53867,7 +53867,7 @@
         <v>1.7296</v>
       </c>
       <c r="J624" t="n">
-        <v>-1.1442</v>
+        <v>-1.1417</v>
       </c>
       <c r="K624" t="n">
         <v>-1.128</v>
@@ -53886,16 +53886,16 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.2284</v>
+        <v>0.229</v>
       </c>
       <c r="C625" t="n">
         <v>-0.2769</v>
       </c>
       <c r="D625" t="n">
-        <v>-0.0243</v>
+        <v>-0.0239</v>
       </c>
       <c r="E625" t="n">
-        <v>0.2284</v>
+        <v>0.229</v>
       </c>
       <c r="F625" t="n">
         <v>-0.2769</v>
@@ -53910,7 +53910,7 @@
         <v>1.7803</v>
       </c>
       <c r="J625" t="n">
-        <v>-1.2294</v>
+        <v>-1.2268</v>
       </c>
       <c r="K625" t="n">
         <v>-1.1379</v>
@@ -53929,16 +53929,16 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.4278</v>
+        <v>0.4285</v>
       </c>
       <c r="C626" t="n">
         <v>-0.2647</v>
       </c>
       <c r="D626" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="E626" t="n">
-        <v>0.4278</v>
+        <v>0.4285</v>
       </c>
       <c r="F626" t="n">
         <v>-0.2647</v>
@@ -53953,7 +53953,7 @@
         <v>1.816</v>
       </c>
       <c r="J626" t="n">
-        <v>-1.1511</v>
+        <v>-1.1486</v>
       </c>
       <c r="K626" t="n">
         <v>-1.1862</v>
@@ -53972,16 +53972,16 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.3819</v>
+        <v>0.3825</v>
       </c>
       <c r="C627" t="n">
         <v>-0.3068</v>
       </c>
       <c r="D627" t="n">
-        <v>0.0376</v>
+        <v>0.0379</v>
       </c>
       <c r="E627" t="n">
-        <v>0.3819</v>
+        <v>0.3825</v>
       </c>
       <c r="F627" t="n">
         <v>-0.3068</v>
@@ -53996,7 +53996,7 @@
         <v>1.8189</v>
       </c>
       <c r="J627" t="n">
-        <v>-1.1658</v>
+        <v>-1.1633</v>
       </c>
       <c r="K627" t="n">
         <v>-1.2201</v>
@@ -54015,16 +54015,16 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.4248</v>
+        <v>0.4254</v>
       </c>
       <c r="C628" t="n">
         <v>-0.2767</v>
       </c>
       <c r="D628" t="n">
-        <v>0.0741</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="E628" t="n">
-        <v>0.4248</v>
+        <v>0.4254</v>
       </c>
       <c r="F628" t="n">
         <v>-0.2767</v>
@@ -54039,7 +54039,7 @@
         <v>1.8932</v>
       </c>
       <c r="J628" t="n">
-        <v>-1.2126</v>
+        <v>-1.2101</v>
       </c>
       <c r="K628" t="n">
         <v>-1.2646</v>
@@ -54058,16 +54058,16 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.3865</v>
+        <v>0.3871</v>
       </c>
       <c r="C629" t="n">
         <v>-0.2893</v>
       </c>
       <c r="D629" t="n">
-        <v>0.0486</v>
+        <v>0.0489</v>
       </c>
       <c r="E629" t="n">
-        <v>0.3865</v>
+        <v>0.3871</v>
       </c>
       <c r="F629" t="n">
         <v>-0.2893</v>
@@ -54082,7 +54082,7 @@
         <v>1.9247</v>
       </c>
       <c r="J629" t="n">
-        <v>-1.2228</v>
+        <v>-1.2203</v>
       </c>
       <c r="K629" t="n">
         <v>-1.2844</v>
@@ -54101,16 +54101,16 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.3831</v>
+        <v>0.3837</v>
       </c>
       <c r="C630" t="n">
         <v>-0.2891</v>
       </c>
       <c r="D630" t="n">
-        <v>0.047</v>
+        <v>0.0473</v>
       </c>
       <c r="E630" t="n">
-        <v>0.3831</v>
+        <v>0.3837</v>
       </c>
       <c r="F630" t="n">
         <v>-0.2891</v>
@@ -54125,7 +54125,7 @@
         <v>1.8936</v>
       </c>
       <c r="J630" t="n">
-        <v>-1.2329</v>
+        <v>-1.2304</v>
       </c>
       <c r="K630" t="n">
         <v>-1.3207</v>
@@ -54144,16 +54144,16 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.3873</v>
+        <v>0.3879</v>
       </c>
       <c r="C631" t="n">
         <v>-0.2029</v>
       </c>
       <c r="D631" t="n">
-        <v>0.0922</v>
+        <v>0.0925</v>
       </c>
       <c r="E631" t="n">
-        <v>0.3873</v>
+        <v>0.3879</v>
       </c>
       <c r="F631" t="n">
         <v>-0.2029</v>
@@ -54168,7 +54168,7 @@
         <v>1.9551</v>
       </c>
       <c r="J631" t="n">
-        <v>-1.3318</v>
+        <v>-1.3291</v>
       </c>
       <c r="K631" t="n">
         <v>-1.3604</v>
@@ -54187,16 +54187,16 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.4212</v>
+        <v>0.4218</v>
       </c>
       <c r="C632" t="n">
         <v>-0.2079</v>
       </c>
       <c r="D632" t="n">
-        <v>0.1066</v>
+        <v>0.107</v>
       </c>
       <c r="E632" t="n">
-        <v>0.4212</v>
+        <v>0.4218</v>
       </c>
       <c r="F632" t="n">
         <v>-0.2079</v>
@@ -54211,7 +54211,7 @@
         <v>1.9922</v>
       </c>
       <c r="J632" t="n">
-        <v>-1.3197</v>
+        <v>-1.3171</v>
       </c>
       <c r="K632" t="n">
         <v>-1.3525</v>
@@ -54230,16 +54230,16 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.4043</v>
+        <v>0.405</v>
       </c>
       <c r="C633" t="n">
         <v>-0.1793</v>
       </c>
       <c r="D633" t="n">
-        <v>0.1125</v>
+        <v>0.1129</v>
       </c>
       <c r="E633" t="n">
-        <v>0.4043</v>
+        <v>0.405</v>
       </c>
       <c r="F633" t="n">
         <v>-0.1793</v>
@@ -54254,7 +54254,7 @@
         <v>2.0019</v>
       </c>
       <c r="J633" t="n">
-        <v>-1.3387</v>
+        <v>-1.336</v>
       </c>
       <c r="K633" t="n">
         <v>-1.3418</v>
@@ -54273,16 +54273,16 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.4356</v>
+        <v>0.4028</v>
       </c>
       <c r="C634" t="n">
         <v>-0.1668</v>
       </c>
       <c r="D634" t="n">
-        <v>0.1344</v>
+        <v>0.118</v>
       </c>
       <c r="E634" t="n">
-        <v>0.4356</v>
+        <v>0.4028</v>
       </c>
       <c r="F634" t="n">
         <v>-0.1668</v>
@@ -54297,7 +54297,7 @@
         <v>1.9448</v>
       </c>
       <c r="J634" t="n">
-        <v>-1.15</v>
+        <v>-1.281</v>
       </c>
       <c r="K634" t="n">
         <v>-1.3218</v>
@@ -54316,19 +54316,19 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.4356</v>
+        <v>0.4028</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1617</v>
+        <v>-0.1616</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1369</v>
+        <v>0.1206</v>
       </c>
       <c r="E635" t="n">
-        <v>0.4356</v>
+        <v>0.4028</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1617</v>
+        <v>-0.1616</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54340,7 +54340,7 @@
         <v>1.9448</v>
       </c>
       <c r="J635" t="n">
-        <v>-1.15</v>
+        <v>-1.281</v>
       </c>
       <c r="K635" t="n">
         <v>-1.3218</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4177</v>
+        <v>0.4182</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -4170,7 +4170,7 @@
         <v>0.141</v>
       </c>
       <c r="K285" t="n">
-        <v>-0.127</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="286">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9.871</v>
+        <v>9.888999999999999</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.052</v>
+        <v>1.053</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0518</v>
+        <v>1.0527</v>
       </c>
       <c r="H635" t="n">
-        <v>9.8714</v>
+        <v>9.8886</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37432,7 +37432,7 @@
         <v>-1.2168</v>
       </c>
       <c r="C173" t="n">
-        <v>-4.1782</v>
+        <v>-4.1783</v>
       </c>
       <c r="D173" t="n">
         <v>-2.6975</v>
@@ -37441,13 +37441,13 @@
         <v>-1.2168</v>
       </c>
       <c r="F173" t="n">
-        <v>-4.1782</v>
+        <v>-4.1783</v>
       </c>
       <c r="G173" t="n">
         <v>-1.2168</v>
       </c>
       <c r="M173" t="n">
-        <v>-4.1782</v>
+        <v>-4.1783</v>
       </c>
     </row>
     <row r="174">
@@ -38048,7 +38048,7 @@
         <v>-1.372</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="D195" t="n">
         <v>-1.0466</v>
@@ -38057,13 +38057,13 @@
         <v>-1.372</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="G195" t="n">
         <v>-1.372</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7212</v>
       </c>
     </row>
     <row r="196">
@@ -39087,7 +39087,7 @@
         <v>-0.0032</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.1971</v>
+        <v>-0.197</v>
       </c>
       <c r="E232" t="n">
         <v>-0.3909</v>
@@ -40232,7 +40232,7 @@
         <v>0.1273</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1318</v>
+        <v>0.1319</v>
       </c>
       <c r="D273" t="n">
         <v>0.1296</v>
@@ -40241,13 +40241,13 @@
         <v>0.1273</v>
       </c>
       <c r="F273" t="n">
-        <v>0.1318</v>
+        <v>0.1319</v>
       </c>
       <c r="G273" t="n">
         <v>0.1273</v>
       </c>
       <c r="M273" t="n">
-        <v>0.1318</v>
+        <v>0.1319</v>
       </c>
     </row>
     <row r="274">
@@ -40431,7 +40431,7 @@
         <v>0.5104</v>
       </c>
       <c r="D280" t="n">
-        <v>0.4028</v>
+        <v>0.4029</v>
       </c>
       <c r="E280" t="n">
         <v>0.2953</v>
@@ -41327,7 +41327,7 @@
         <v>-0.8732</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3693</v>
+        <v>-0.3692</v>
       </c>
       <c r="E312" t="n">
         <v>0.1347</v>
@@ -41719,7 +41719,7 @@
         <v>0.1854</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.0361</v>
+        <v>-0.036</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2575</v>
@@ -41859,7 +41859,7 @@
         <v>-0.1225</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1453</v>
+        <v>-0.1452</v>
       </c>
       <c r="E331" t="n">
         <v>-0.168</v>
@@ -41940,22 +41940,22 @@
         <v>-0.1202</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1156</v>
+        <v>-0.1155</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1179</v>
+        <v>-0.1178</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1156</v>
+        <v>-0.1155</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1156</v>
+        <v>-0.1155</v>
       </c>
     </row>
     <row r="335">
@@ -42332,7 +42332,7 @@
         <v>-0.1199</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5127</v>
       </c>
       <c r="D348" t="n">
         <v>0.1964</v>
@@ -42341,13 +42341,13 @@
         <v>-0.1199</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5127</v>
       </c>
       <c r="G348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5127</v>
       </c>
     </row>
     <row r="349">
@@ -43169,7 +43169,7 @@
         <v>1.0309</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8123</v>
+        <v>0.8124</v>
       </c>
     </row>
     <row r="376">
@@ -45805,7 +45805,7 @@
         <v>-0.6405999999999999</v>
       </c>
       <c r="C437" t="n">
-        <v>0.2235</v>
+        <v>0.2236</v>
       </c>
       <c r="D437" t="n">
         <v>-0.2085</v>
@@ -45814,7 +45814,7 @@
         <v>-0.6405999999999999</v>
       </c>
       <c r="F437" t="n">
-        <v>0.2235</v>
+        <v>0.2236</v>
       </c>
       <c r="G437" t="n">
         <v>-0.314</v>
@@ -48071,7 +48071,7 @@
         <v>0.5085</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2653</v>
+        <v>0.2654</v>
       </c>
     </row>
     <row r="490">
@@ -48673,7 +48673,7 @@
         <v>0.4544</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4316</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="504">
@@ -52672,7 +52672,7 @@
         <v>0.5352</v>
       </c>
       <c r="M596" t="n">
-        <v>-0.7734</v>
+        <v>-0.7733</v>
       </c>
     </row>
     <row r="597">
@@ -53403,7 +53403,7 @@
         <v>0.3813</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1054</v>
+        <v>-0.1053</v>
       </c>
     </row>
     <row r="614">
@@ -53532,7 +53532,7 @@
         <v>0.3747</v>
       </c>
       <c r="M616" t="n">
-        <v>0.0597</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="617">
@@ -54319,16 +54319,16 @@
         <v>0.4028</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1616</v>
+        <v>-0.1618</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1206</v>
+        <v>0.1205</v>
       </c>
       <c r="E635" t="n">
         <v>0.4028</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1616</v>
+        <v>-0.1618</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4182</v>
+        <v>0.4174</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9.888999999999999</v>
+        <v>9.909000000000001</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.053</v>
+        <v>1.052</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="14">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0527</v>
+        <v>1.0517</v>
       </c>
       <c r="H635" t="n">
-        <v>9.8886</v>
+        <v>9.9091</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -39840,7 +39840,7 @@
         <v>-0.3872</v>
       </c>
       <c r="C259" t="n">
-        <v>-1.0973</v>
+        <v>-1.0972</v>
       </c>
       <c r="D259" t="n">
         <v>-0.7422</v>
@@ -39849,13 +39849,13 @@
         <v>-0.3872</v>
       </c>
       <c r="F259" t="n">
-        <v>-1.0973</v>
+        <v>-1.0972</v>
       </c>
       <c r="G259" t="n">
         <v>-0.3872</v>
       </c>
       <c r="M259" t="n">
-        <v>-1.0973</v>
+        <v>-1.0972</v>
       </c>
     </row>
     <row r="260">
@@ -40148,7 +40148,7 @@
         <v>0.0435</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.3345</v>
+        <v>-0.3344</v>
       </c>
       <c r="D270" t="n">
         <v>-0.1455</v>
@@ -40157,13 +40157,13 @@
         <v>0.0435</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.3345</v>
+        <v>-0.3344</v>
       </c>
       <c r="G270" t="n">
         <v>0.0435</v>
       </c>
       <c r="M270" t="n">
-        <v>-0.3345</v>
+        <v>-0.3344</v>
       </c>
     </row>
     <row r="271">
@@ -40179,7 +40179,7 @@
         <v>-0.0424</v>
       </c>
       <c r="D271" t="n">
-        <v>0.0331</v>
+        <v>0.0332</v>
       </c>
       <c r="E271" t="n">
         <v>0.1087</v>
@@ -40456,7 +40456,7 @@
         <v>0.9434</v>
       </c>
       <c r="C281" t="n">
-        <v>0.5726</v>
+        <v>0.5727</v>
       </c>
       <c r="D281" t="n">
         <v>0.758</v>
@@ -40465,13 +40465,13 @@
         <v>0.9434</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5726</v>
+        <v>0.5727</v>
       </c>
       <c r="G281" t="n">
         <v>0.9434</v>
       </c>
       <c r="M281" t="n">
-        <v>0.5726</v>
+        <v>0.5727</v>
       </c>
     </row>
     <row r="282">
@@ -41159,7 +41159,7 @@
         <v>-1.6395</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.7008</v>
+        <v>-0.7007</v>
       </c>
       <c r="E306" t="n">
         <v>0.238</v>
@@ -41327,7 +41327,7 @@
         <v>-0.8732</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3692</v>
+        <v>-0.3693</v>
       </c>
       <c r="E312" t="n">
         <v>0.1347</v>
@@ -41719,7 +41719,7 @@
         <v>0.1854</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.036</v>
+        <v>-0.0361</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2575</v>
@@ -41940,22 +41940,22 @@
         <v>-0.1202</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1178</v>
+        <v>-0.1179</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
     </row>
     <row r="335">
@@ -43169,7 +43169,7 @@
         <v>1.0309</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8124</v>
+        <v>0.8123</v>
       </c>
     </row>
     <row r="376">
@@ -43827,7 +43827,7 @@
         <v>-0.8995</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.622</v>
+        <v>-0.6219</v>
       </c>
       <c r="D391" t="n">
         <v>-0.7607</v>
@@ -43836,7 +43836,7 @@
         <v>-0.8995</v>
       </c>
       <c r="F391" t="n">
-        <v>-0.622</v>
+        <v>-0.6219</v>
       </c>
       <c r="G391" t="n">
         <v>0.2407</v>
@@ -44373,7 +44373,7 @@
         <v>-1.4948</v>
       </c>
       <c r="M403" t="n">
-        <v>0.2116</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="404">
@@ -48071,7 +48071,7 @@
         <v>0.5085</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2654</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="490">
@@ -48673,7 +48673,7 @@
         <v>0.4544</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4317</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="504">
@@ -49232,7 +49232,7 @@
         <v>0.3077</v>
       </c>
       <c r="M516" t="n">
-        <v>0.5322</v>
+        <v>0.5323</v>
       </c>
     </row>
     <row r="517">
@@ -53403,7 +53403,7 @@
         <v>0.3813</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1053</v>
+        <v>-0.1054</v>
       </c>
     </row>
     <row r="614">
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4174</v>
+        <v>0.4175</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>-1.284</v>
       </c>
       <c r="K158" t="n">
-        <v>-3.205</v>
+        <v>-3.206</v>
       </c>
     </row>
     <row r="159">
@@ -4404,7 +4404,7 @@
         <v>0.187</v>
       </c>
       <c r="K303" t="n">
-        <v>-1.025</v>
+        <v>-1.026</v>
       </c>
     </row>
     <row r="304">
@@ -4430,7 +4430,7 @@
         <v>0.174</v>
       </c>
       <c r="K305" t="n">
-        <v>-0.501</v>
+        <v>-0.502</v>
       </c>
     </row>
     <row r="306">
@@ -4638,7 +4638,7 @@
         <v>-0.13</v>
       </c>
       <c r="K321" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="322">
@@ -4651,7 +4651,7 @@
         <v>-0.216</v>
       </c>
       <c r="K322" t="n">
-        <v>-0.138</v>
+        <v>-0.139</v>
       </c>
     </row>
     <row r="323">
@@ -4664,7 +4664,7 @@
         <v>-0.168</v>
       </c>
       <c r="K323" t="n">
-        <v>-0.122</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="324">
@@ -4716,7 +4716,7 @@
         <v>-0.074</v>
       </c>
       <c r="K327" t="n">
-        <v>-0.262</v>
+        <v>-0.263</v>
       </c>
     </row>
     <row r="328">
@@ -4768,7 +4768,7 @@
         <v>-0.124</v>
       </c>
       <c r="K331" t="n">
-        <v>-0.209</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="332">
@@ -4781,7 +4781,7 @@
         <v>-0.076</v>
       </c>
       <c r="K332" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="333">
@@ -4807,7 +4807,7 @@
         <v>-0.121</v>
       </c>
       <c r="K334" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="335">
@@ -4859,7 +4859,7 @@
         <v>-0.167</v>
       </c>
       <c r="K338" t="n">
-        <v>0.525</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="339">
@@ -4885,7 +4885,7 @@
         <v>-0.12</v>
       </c>
       <c r="K340" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="341">
@@ -4898,7 +4898,7 @@
         <v>-0.07199999999999999</v>
       </c>
       <c r="K341" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="342">
@@ -5041,7 +5041,7 @@
         <v>0.213</v>
       </c>
       <c r="K352" t="n">
-        <v>-0.018</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="353">
@@ -5106,7 +5106,7 @@
         <v>-0.53</v>
       </c>
       <c r="K357" t="n">
-        <v>-0.214</v>
+        <v>-0.215</v>
       </c>
     </row>
     <row r="358">
@@ -5145,7 +5145,7 @@
         <v>-0.477</v>
       </c>
       <c r="K360" t="n">
-        <v>-0.107</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="361">
@@ -5171,7 +5171,7 @@
         <v>-0.407</v>
       </c>
       <c r="K362" t="n">
-        <v>-0.374</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="363">
@@ -5184,7 +5184,7 @@
         <v>-0.454</v>
       </c>
       <c r="K363" t="n">
-        <v>-0.308</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="364">
@@ -5678,7 +5678,7 @@
         <v>-0.252</v>
       </c>
       <c r="K401" t="n">
-        <v>-0.961</v>
+        <v>-0.962</v>
       </c>
     </row>
     <row r="402">
@@ -5691,7 +5691,7 @@
         <v>-0.258</v>
       </c>
       <c r="K402" t="n">
-        <v>-1.029</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="403">
@@ -6081,7 +6081,7 @@
         <v>-0.737</v>
       </c>
       <c r="K432" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="433">
@@ -6302,7 +6302,7 @@
         <v>-0.378</v>
       </c>
       <c r="K449" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="450">
@@ -6432,7 +6432,7 @@
         <v>-0.258</v>
       </c>
       <c r="K459" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="460">
@@ -6445,7 +6445,7 @@
         <v>-0.349</v>
       </c>
       <c r="K460" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="461">
@@ -6536,7 +6536,7 @@
         <v>0.48</v>
       </c>
       <c r="K467" t="n">
-        <v>1.009</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="468">
@@ -6796,7 +6796,7 @@
         <v>0.909</v>
       </c>
       <c r="K487" t="n">
-        <v>0.849</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="488">
@@ -7407,7 +7407,7 @@
         <v>0.242</v>
       </c>
       <c r="K534" t="n">
-        <v>-0.135</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="535">
@@ -8291,7 +8291,7 @@
         <v>0.514</v>
       </c>
       <c r="K602" t="n">
-        <v>-0.163</v>
+        <v>-0.164</v>
       </c>
     </row>
     <row r="603">
@@ -8603,7 +8603,7 @@
         <v>0.403</v>
       </c>
       <c r="K626" t="n">
-        <v>-0.167</v>
+        <v>-0.156</v>
       </c>
     </row>
     <row r="627">
@@ -8616,7 +8616,7 @@
         <v>0.403</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.162</v>
+        <v>-0.163</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9.909000000000001</v>
+        <v>10.081</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="13">
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="14">
@@ -34448,10 +34448,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.0657</v>
+        <v>1.0079</v>
       </c>
       <c r="H634" t="n">
-        <v>10.3303</v>
+        <v>10.1724</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0517</v>
+        <v>1.0523</v>
       </c>
       <c r="H635" t="n">
-        <v>9.9091</v>
+        <v>10.0809</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -41268,22 +41268,22 @@
         <v>0.2295</v>
       </c>
       <c r="C310" t="n">
-        <v>-1.1236</v>
+        <v>-1.124</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.447</v>
+        <v>-0.4473</v>
       </c>
       <c r="E310" t="n">
         <v>0.2295</v>
       </c>
       <c r="F310" t="n">
-        <v>-1.1236</v>
+        <v>-1.124</v>
       </c>
       <c r="G310" t="n">
         <v>0.2295</v>
       </c>
       <c r="M310" t="n">
-        <v>-1.1236</v>
+        <v>-1.124</v>
       </c>
     </row>
     <row r="311">
@@ -41296,22 +41296,22 @@
         <v>0.1872</v>
       </c>
       <c r="C311" t="n">
-        <v>-1.0253</v>
+        <v>-1.0257</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.419</v>
+        <v>-0.4192</v>
       </c>
       <c r="E311" t="n">
         <v>0.1872</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.0253</v>
+        <v>-1.0257</v>
       </c>
       <c r="G311" t="n">
         <v>0.1872</v>
       </c>
       <c r="M311" t="n">
-        <v>-1.0253</v>
+        <v>-1.0257</v>
       </c>
     </row>
     <row r="312">
@@ -41324,22 +41324,22 @@
         <v>0.1347</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.8732</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3693</v>
+        <v>-0.3694</v>
       </c>
       <c r="E312" t="n">
         <v>0.1347</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.8732</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="G312" t="n">
         <v>0.1347</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.8732</v>
+        <v>-0.8735000000000001</v>
       </c>
     </row>
     <row r="313">
@@ -41352,22 +41352,22 @@
         <v>0.1736</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.5012</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.1638</v>
+        <v>-0.1639</v>
       </c>
       <c r="E313" t="n">
         <v>0.1736</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.5012</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="G313" t="n">
         <v>0.1736</v>
       </c>
       <c r="M313" t="n">
-        <v>-0.5012</v>
+        <v>-0.5014999999999999</v>
       </c>
     </row>
     <row r="314">
@@ -41380,22 +41380,22 @@
         <v>0.1252</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.1282</v>
+        <v>-0.1284</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.0015</v>
+        <v>-0.0016</v>
       </c>
       <c r="E314" t="n">
         <v>0.1252</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.1282</v>
+        <v>-0.1284</v>
       </c>
       <c r="G314" t="n">
         <v>0.1252</v>
       </c>
       <c r="M314" t="n">
-        <v>-0.1282</v>
+        <v>-0.1284</v>
       </c>
     </row>
     <row r="315">
@@ -41408,7 +41408,7 @@
         <v>0.1702</v>
       </c>
       <c r="C315" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
       <c r="D315" t="n">
         <v>0.1512</v>
@@ -41417,13 +41417,13 @@
         <v>0.1702</v>
       </c>
       <c r="F315" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
       <c r="G315" t="n">
         <v>0.1702</v>
       </c>
       <c r="M315" t="n">
-        <v>0.1323</v>
+        <v>0.1322</v>
       </c>
     </row>
     <row r="316">
@@ -41436,7 +41436,7 @@
         <v>0.1172</v>
       </c>
       <c r="C316" t="n">
-        <v>0.5027</v>
+        <v>0.5028</v>
       </c>
       <c r="D316" t="n">
         <v>0.31</v>
@@ -41445,13 +41445,13 @@
         <v>0.1172</v>
       </c>
       <c r="F316" t="n">
-        <v>0.5027</v>
+        <v>0.5028</v>
       </c>
       <c r="G316" t="n">
         <v>0.1172</v>
       </c>
       <c r="M316" t="n">
-        <v>0.5027</v>
+        <v>0.5028</v>
       </c>
     </row>
     <row r="317">
@@ -41464,7 +41464,7 @@
         <v>0.113</v>
       </c>
       <c r="C317" t="n">
-        <v>0.7671</v>
+        <v>0.7673</v>
       </c>
       <c r="D317" t="n">
         <v>0.4401</v>
@@ -41473,13 +41473,13 @@
         <v>0.113</v>
       </c>
       <c r="F317" t="n">
-        <v>0.7671</v>
+        <v>0.7673</v>
       </c>
       <c r="G317" t="n">
         <v>0.113</v>
       </c>
       <c r="M317" t="n">
-        <v>0.7671</v>
+        <v>0.7673</v>
       </c>
     </row>
     <row r="318">
@@ -41579,7 +41579,7 @@
         <v>0.8763</v>
       </c>
       <c r="D321" t="n">
-        <v>0.5105</v>
+        <v>0.5104</v>
       </c>
       <c r="E321" t="n">
         <v>0.1446</v>
@@ -41604,7 +41604,7 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="C322" t="n">
-        <v>0.7337</v>
+        <v>0.7335</v>
       </c>
       <c r="D322" t="n">
         <v>0.3231</v>
@@ -41613,13 +41613,13 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7337</v>
+        <v>0.7335</v>
       </c>
       <c r="G322" t="n">
         <v>-0.08740000000000001</v>
       </c>
       <c r="M322" t="n">
-        <v>0.7337</v>
+        <v>0.7335</v>
       </c>
     </row>
     <row r="323">
@@ -41632,22 +41632,22 @@
         <v>-0.2268</v>
       </c>
       <c r="C323" t="n">
-        <v>0.3031</v>
+        <v>0.3027</v>
       </c>
       <c r="D323" t="n">
-        <v>0.0382</v>
+        <v>0.038</v>
       </c>
       <c r="E323" t="n">
         <v>-0.2268</v>
       </c>
       <c r="F323" t="n">
-        <v>0.3031</v>
+        <v>0.3027</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2268</v>
       </c>
       <c r="M323" t="n">
-        <v>0.3031</v>
+        <v>0.3027</v>
       </c>
     </row>
     <row r="324">
@@ -41660,22 +41660,22 @@
         <v>-0.1762</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2112</v>
+        <v>0.2108</v>
       </c>
       <c r="D324" t="n">
-        <v>0.0175</v>
+        <v>0.0173</v>
       </c>
       <c r="E324" t="n">
         <v>-0.1762</v>
       </c>
       <c r="F324" t="n">
-        <v>0.2112</v>
+        <v>0.2108</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1762</v>
       </c>
       <c r="M324" t="n">
-        <v>0.2112</v>
+        <v>0.2108</v>
       </c>
     </row>
     <row r="325">
@@ -41688,22 +41688,22 @@
         <v>-0.1809</v>
       </c>
       <c r="C325" t="n">
-        <v>0.191</v>
+        <v>0.1906</v>
       </c>
       <c r="D325" t="n">
-        <v>0.0051</v>
+        <v>0.0049</v>
       </c>
       <c r="E325" t="n">
         <v>-0.1809</v>
       </c>
       <c r="F325" t="n">
-        <v>0.191</v>
+        <v>0.1906</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1809</v>
       </c>
       <c r="M325" t="n">
-        <v>0.191</v>
+        <v>0.1906</v>
       </c>
     </row>
     <row r="326">
@@ -41716,22 +41716,22 @@
         <v>-0.2575</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1854</v>
+        <v>0.185</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.0361</v>
+        <v>-0.0362</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2575</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1854</v>
+        <v>0.185</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2575</v>
       </c>
       <c r="M326" t="n">
-        <v>0.1854</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="327">
@@ -41744,22 +41744,22 @@
         <v>-0.2413</v>
       </c>
       <c r="C327" t="n">
-        <v>0.4113</v>
+        <v>0.411</v>
       </c>
       <c r="D327" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="E327" t="n">
         <v>-0.2413</v>
       </c>
       <c r="F327" t="n">
-        <v>0.4113</v>
+        <v>0.411</v>
       </c>
       <c r="G327" t="n">
         <v>-0.2413</v>
       </c>
       <c r="M327" t="n">
-        <v>0.4113</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="328">
@@ -41772,22 +41772,22 @@
         <v>-0.2131</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4504</v>
+        <v>0.4502</v>
       </c>
       <c r="D328" t="n">
-        <v>0.1187</v>
+        <v>0.1186</v>
       </c>
       <c r="E328" t="n">
         <v>-0.2131</v>
       </c>
       <c r="F328" t="n">
-        <v>0.4504</v>
+        <v>0.4502</v>
       </c>
       <c r="G328" t="n">
         <v>-0.2131</v>
       </c>
       <c r="M328" t="n">
-        <v>0.4504</v>
+        <v>0.4502</v>
       </c>
     </row>
     <row r="329">
@@ -41800,22 +41800,22 @@
         <v>-0.1302</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0297</v>
+        <v>0.0293</v>
       </c>
       <c r="D329" t="n">
-        <v>-0.0502</v>
+        <v>-0.0504</v>
       </c>
       <c r="E329" t="n">
         <v>-0.1302</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0297</v>
+        <v>0.0293</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1302</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0297</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="330">
@@ -41828,22 +41828,22 @@
         <v>-0.2161</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1381</v>
+        <v>-0.1386</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.1771</v>
+        <v>-0.1773</v>
       </c>
       <c r="E330" t="n">
         <v>-0.2161</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1381</v>
+        <v>-0.1386</v>
       </c>
       <c r="G330" t="n">
         <v>-0.2161</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1381</v>
+        <v>-0.1386</v>
       </c>
     </row>
     <row r="331">
@@ -41856,22 +41856,22 @@
         <v>-0.168</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.1225</v>
+        <v>-0.1229</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1452</v>
+        <v>-0.1455</v>
       </c>
       <c r="E331" t="n">
         <v>-0.168</v>
       </c>
       <c r="F331" t="n">
-        <v>-0.1225</v>
+        <v>-0.1229</v>
       </c>
       <c r="G331" t="n">
         <v>-0.168</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.1225</v>
+        <v>-0.1229</v>
       </c>
     </row>
     <row r="332">
@@ -41884,22 +41884,22 @@
         <v>-0.1711</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.2559</v>
+        <v>-0.2564</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.2135</v>
+        <v>-0.2137</v>
       </c>
       <c r="E332" t="n">
         <v>-0.1711</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2559</v>
+        <v>-0.2564</v>
       </c>
       <c r="G332" t="n">
         <v>-0.1711</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.2559</v>
+        <v>-0.2564</v>
       </c>
     </row>
     <row r="333">
@@ -41912,22 +41912,22 @@
         <v>-0.1727</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.2408</v>
+        <v>-0.2413</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.2068</v>
+        <v>-0.207</v>
       </c>
       <c r="E333" t="n">
         <v>-0.1727</v>
       </c>
       <c r="F333" t="n">
-        <v>-0.2408</v>
+        <v>-0.2413</v>
       </c>
       <c r="G333" t="n">
         <v>-0.1727</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.2408</v>
+        <v>-0.2413</v>
       </c>
     </row>
     <row r="334">
@@ -41940,22 +41940,22 @@
         <v>-0.1202</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1156</v>
+        <v>-0.116</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1179</v>
+        <v>-0.1181</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1156</v>
+        <v>-0.116</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1156</v>
+        <v>-0.116</v>
       </c>
     </row>
     <row r="335">
@@ -41968,22 +41968,22 @@
         <v>-0.0738</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2622</v>
+        <v>-0.2628</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.168</v>
+        <v>-0.1683</v>
       </c>
       <c r="E335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2622</v>
+        <v>-0.2628</v>
       </c>
       <c r="G335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2622</v>
+        <v>-0.2628</v>
       </c>
     </row>
     <row r="336">
@@ -41996,22 +41996,22 @@
         <v>-0.1217</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.2046</v>
+        <v>-0.2051</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.1631</v>
+        <v>-0.1634</v>
       </c>
       <c r="E336" t="n">
         <v>-0.1217</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.2046</v>
+        <v>-0.2051</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1217</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.2046</v>
+        <v>-0.2051</v>
       </c>
     </row>
     <row r="337">
@@ -42024,22 +42024,22 @@
         <v>-0.1717</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2838</v>
+        <v>-0.2844</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.2278</v>
+        <v>-0.2281</v>
       </c>
       <c r="E337" t="n">
         <v>-0.1717</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.2838</v>
+        <v>-0.2844</v>
       </c>
       <c r="G337" t="n">
         <v>-0.1717</v>
       </c>
       <c r="M337" t="n">
-        <v>-0.2838</v>
+        <v>-0.2844</v>
       </c>
     </row>
     <row r="338">
@@ -42052,22 +42052,22 @@
         <v>-0.1245</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.247</v>
+        <v>-0.2475</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.1857</v>
+        <v>-0.186</v>
       </c>
       <c r="E338" t="n">
         <v>-0.1245</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.247</v>
+        <v>-0.2475</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1245</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.247</v>
+        <v>-0.2475</v>
       </c>
     </row>
     <row r="339">
@@ -42080,22 +42080,22 @@
         <v>-0.1237</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2092</v>
+        <v>-0.2097</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.1664</v>
+        <v>-0.1667</v>
       </c>
       <c r="E339" t="n">
         <v>-0.1237</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2092</v>
+        <v>-0.2097</v>
       </c>
       <c r="G339" t="n">
         <v>-0.1237</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2092</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="340">
@@ -42108,22 +42108,22 @@
         <v>-0.0757</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0519</v>
+        <v>0.0514</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.0119</v>
+        <v>-0.0121</v>
       </c>
       <c r="E340" t="n">
         <v>-0.0757</v>
       </c>
       <c r="F340" t="n">
-        <v>0.0519</v>
+        <v>0.0514</v>
       </c>
       <c r="G340" t="n">
         <v>-0.0757</v>
       </c>
       <c r="M340" t="n">
-        <v>0.0519</v>
+        <v>0.0514</v>
       </c>
     </row>
     <row r="341">
@@ -42136,22 +42136,22 @@
         <v>-0.1691</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1764</v>
+        <v>0.176</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1691</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1764</v>
+        <v>0.176</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1691</v>
       </c>
       <c r="M341" t="n">
-        <v>0.1764</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="342">
@@ -42164,22 +42164,22 @@
         <v>-0.1213</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2256</v>
+        <v>0.2252</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0522</v>
+        <v>0.052</v>
       </c>
       <c r="E342" t="n">
         <v>-0.1213</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2256</v>
+        <v>0.2252</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1213</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2256</v>
+        <v>0.2252</v>
       </c>
     </row>
     <row r="343">
@@ -42192,22 +42192,22 @@
         <v>-0.1218</v>
       </c>
       <c r="C343" t="n">
-        <v>0.3413</v>
+        <v>0.3409</v>
       </c>
       <c r="D343" t="n">
-        <v>0.1098</v>
+        <v>0.1096</v>
       </c>
       <c r="E343" t="n">
         <v>-0.1218</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3413</v>
+        <v>0.3409</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1218</v>
       </c>
       <c r="M343" t="n">
-        <v>0.3413</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="344">
@@ -42220,22 +42220,22 @@
         <v>-0.1226</v>
       </c>
       <c r="C344" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5607</v>
       </c>
       <c r="D344" t="n">
-        <v>0.2192</v>
+        <v>0.2191</v>
       </c>
       <c r="E344" t="n">
         <v>-0.1226</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5607</v>
       </c>
       <c r="G344" t="n">
         <v>-0.1226</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5607</v>
       </c>
     </row>
     <row r="345">
@@ -42248,22 +42248,22 @@
         <v>-0.1663</v>
       </c>
       <c r="C345" t="n">
-        <v>0.4452</v>
+        <v>0.4448</v>
       </c>
       <c r="D345" t="n">
-        <v>0.1394</v>
+        <v>0.1393</v>
       </c>
       <c r="E345" t="n">
         <v>-0.1663</v>
       </c>
       <c r="F345" t="n">
-        <v>0.4452</v>
+        <v>0.4448</v>
       </c>
       <c r="G345" t="n">
         <v>-0.1663</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4452</v>
+        <v>0.4448</v>
       </c>
     </row>
     <row r="346">
@@ -42276,22 +42276,22 @@
         <v>-0.1668</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5246</v>
+        <v>0.5243</v>
       </c>
       <c r="D346" t="n">
-        <v>0.1789</v>
+        <v>0.1788</v>
       </c>
       <c r="E346" t="n">
         <v>-0.1668</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5246</v>
+        <v>0.5243</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1668</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5246</v>
+        <v>0.5243</v>
       </c>
     </row>
     <row r="347">
@@ -42304,22 +42304,22 @@
         <v>-0.1669</v>
       </c>
       <c r="C347" t="n">
-        <v>0.3512</v>
+        <v>0.3508</v>
       </c>
       <c r="D347" t="n">
-        <v>0.0921</v>
+        <v>0.0919</v>
       </c>
       <c r="E347" t="n">
         <v>-0.1669</v>
       </c>
       <c r="F347" t="n">
-        <v>0.3512</v>
+        <v>0.3508</v>
       </c>
       <c r="G347" t="n">
         <v>-0.1669</v>
       </c>
       <c r="M347" t="n">
-        <v>0.3512</v>
+        <v>0.3508</v>
       </c>
     </row>
     <row r="348">
@@ -42332,22 +42332,22 @@
         <v>-0.1199</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5127</v>
+        <v>0.5124</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1964</v>
+        <v>0.1962</v>
       </c>
       <c r="E348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5127</v>
+        <v>0.5124</v>
       </c>
       <c r="G348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5127</v>
+        <v>0.5124</v>
       </c>
     </row>
     <row r="349">
@@ -42360,22 +42360,22 @@
         <v>-0.0725</v>
       </c>
       <c r="C349" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5083</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2181</v>
+        <v>0.2179</v>
       </c>
       <c r="E349" t="n">
         <v>-0.0725</v>
       </c>
       <c r="F349" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5083</v>
       </c>
       <c r="G349" t="n">
         <v>-0.0725</v>
       </c>
       <c r="M349" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="350">
@@ -42388,22 +42388,22 @@
         <v>-0.1226</v>
       </c>
       <c r="C350" t="n">
-        <v>0.8066</v>
+        <v>0.8065</v>
       </c>
       <c r="D350" t="n">
-        <v>0.342</v>
+        <v>0.3419</v>
       </c>
       <c r="E350" t="n">
         <v>-0.1226</v>
       </c>
       <c r="F350" t="n">
-        <v>0.8066</v>
+        <v>0.8065</v>
       </c>
       <c r="G350" t="n">
         <v>-0.1226</v>
       </c>
       <c r="M350" t="n">
-        <v>0.8066</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="351">
@@ -42416,22 +42416,22 @@
         <v>-0.07580000000000001</v>
       </c>
       <c r="C351" t="n">
-        <v>0.9328</v>
+        <v>0.9327</v>
       </c>
       <c r="D351" t="n">
-        <v>0.4285</v>
+        <v>0.4284</v>
       </c>
       <c r="E351" t="n">
         <v>-0.07580000000000001</v>
       </c>
       <c r="F351" t="n">
-        <v>0.9328</v>
+        <v>0.9327</v>
       </c>
       <c r="G351" t="n">
         <v>-0.07580000000000001</v>
       </c>
       <c r="M351" t="n">
-        <v>0.9328</v>
+        <v>0.9327</v>
       </c>
     </row>
     <row r="352">
@@ -42475,7 +42475,7 @@
         <v>1.2357</v>
       </c>
       <c r="D353" t="n">
-        <v>0.6516</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="E353" t="n">
         <v>0.06759999999999999</v>
@@ -42503,7 +42503,7 @@
         <v>1.2553</v>
       </c>
       <c r="D354" t="n">
-        <v>0.663</v>
+        <v>0.6631</v>
       </c>
       <c r="E354" t="n">
         <v>0.0708</v>
@@ -42556,22 +42556,22 @@
         <v>0.1672</v>
       </c>
       <c r="C356" t="n">
-        <v>0.3037</v>
+        <v>0.3036</v>
       </c>
       <c r="D356" t="n">
-        <v>0.2355</v>
+        <v>0.2354</v>
       </c>
       <c r="E356" t="n">
         <v>0.1672</v>
       </c>
       <c r="F356" t="n">
-        <v>0.3037</v>
+        <v>0.3036</v>
       </c>
       <c r="G356" t="n">
         <v>0.1672</v>
       </c>
       <c r="M356" t="n">
-        <v>0.3037</v>
+        <v>0.3036</v>
       </c>
     </row>
     <row r="357">
@@ -42584,22 +42584,22 @@
         <v>0.214</v>
       </c>
       <c r="C357" t="n">
-        <v>0.1633</v>
+        <v>0.1631</v>
       </c>
       <c r="D357" t="n">
-        <v>0.1887</v>
+        <v>0.1886</v>
       </c>
       <c r="E357" t="n">
         <v>0.214</v>
       </c>
       <c r="F357" t="n">
-        <v>0.1633</v>
+        <v>0.1631</v>
       </c>
       <c r="G357" t="n">
         <v>0.214</v>
       </c>
       <c r="M357" t="n">
-        <v>0.1633</v>
+        <v>0.1631</v>
       </c>
     </row>
     <row r="358">
@@ -42612,7 +42612,7 @@
         <v>0.2085</v>
       </c>
       <c r="C358" t="n">
-        <v>0.2659</v>
+        <v>0.2658</v>
       </c>
       <c r="D358" t="n">
         <v>0.2372</v>
@@ -42621,13 +42621,13 @@
         <v>0.2085</v>
       </c>
       <c r="F358" t="n">
-        <v>0.2659</v>
+        <v>0.2658</v>
       </c>
       <c r="G358" t="n">
         <v>0.2085</v>
       </c>
       <c r="M358" t="n">
-        <v>0.2659</v>
+        <v>0.2658</v>
       </c>
     </row>
     <row r="359">
@@ -42640,22 +42640,22 @@
         <v>0.3073</v>
       </c>
       <c r="C359" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0665</v>
       </c>
       <c r="D359" t="n">
-        <v>0.187</v>
+        <v>0.1869</v>
       </c>
       <c r="E359" t="n">
         <v>0.3073</v>
       </c>
       <c r="F359" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0665</v>
       </c>
       <c r="G359" t="n">
         <v>0.3073</v>
       </c>
       <c r="M359" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="360">
@@ -42668,22 +42668,22 @@
         <v>0.213</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0184</v>
+        <v>-0.0185</v>
       </c>
       <c r="D360" t="n">
-        <v>0.0973</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="E360" t="n">
         <v>0.213</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.0184</v>
+        <v>-0.0185</v>
       </c>
       <c r="G360" t="n">
         <v>0.213</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.0184</v>
+        <v>-0.0185</v>
       </c>
     </row>
     <row r="361">
@@ -42696,7 +42696,7 @@
         <v>0.2619</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0157</v>
+        <v>0.0156</v>
       </c>
       <c r="D361" t="n">
         <v>0.1388</v>
@@ -42705,13 +42705,13 @@
         <v>0.2619</v>
       </c>
       <c r="F361" t="n">
-        <v>0.0157</v>
+        <v>0.0156</v>
       </c>
       <c r="G361" t="n">
         <v>0.2619</v>
       </c>
       <c r="M361" t="n">
-        <v>0.0157</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="362">
@@ -42724,16 +42724,16 @@
         <v>-0.5446</v>
       </c>
       <c r="C362" t="n">
-        <v>0.021</v>
+        <v>0.0208</v>
       </c>
       <c r="D362" t="n">
-        <v>-0.2618</v>
+        <v>-0.2619</v>
       </c>
       <c r="E362" t="n">
         <v>-0.5446</v>
       </c>
       <c r="F362" t="n">
-        <v>0.021</v>
+        <v>0.0208</v>
       </c>
       <c r="G362" t="n">
         <v>0.2137</v>
@@ -42742,7 +42742,7 @@
         <v>-1.3029</v>
       </c>
       <c r="M362" t="n">
-        <v>0.021</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="363">
@@ -42755,16 +42755,16 @@
         <v>-0.502</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.2218</v>
+        <v>-0.2221</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.3619</v>
+        <v>-0.362</v>
       </c>
       <c r="E363" t="n">
         <v>-0.502</v>
       </c>
       <c r="F363" t="n">
-        <v>-0.2218</v>
+        <v>-0.2221</v>
       </c>
       <c r="G363" t="n">
         <v>0.262</v>
@@ -42773,7 +42773,7 @@
         <v>-1.2659</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.2218</v>
+        <v>-0.2221</v>
       </c>
     </row>
     <row r="364">
@@ -42786,16 +42786,16 @@
         <v>-0.4839</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0678</v>
       </c>
       <c r="D364" t="n">
-        <v>-0.2757</v>
+        <v>-0.2758</v>
       </c>
       <c r="E364" t="n">
         <v>-0.4839</v>
       </c>
       <c r="F364" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0678</v>
       </c>
       <c r="G364" t="n">
         <v>0.2143</v>
@@ -42804,7 +42804,7 @@
         <v>-1.1821</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0678</v>
       </c>
     </row>
     <row r="365">
@@ -42817,16 +42817,16 @@
         <v>-0.5301</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.2143</v>
+        <v>-0.2146</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.3722</v>
+        <v>-0.3724</v>
       </c>
       <c r="E365" t="n">
         <v>-0.5301</v>
       </c>
       <c r="F365" t="n">
-        <v>-0.2143</v>
+        <v>-0.2146</v>
       </c>
       <c r="G365" t="n">
         <v>0.1656</v>
@@ -42835,7 +42835,7 @@
         <v>-1.2258</v>
       </c>
       <c r="M365" t="n">
-        <v>-0.2143</v>
+        <v>-0.2146</v>
       </c>
     </row>
     <row r="366">
@@ -42848,16 +42848,16 @@
         <v>-0.445</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.2349</v>
+        <v>-0.2353</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.34</v>
+        <v>-0.3401</v>
       </c>
       <c r="E366" t="n">
         <v>-0.445</v>
       </c>
       <c r="F366" t="n">
-        <v>-0.2349</v>
+        <v>-0.2353</v>
       </c>
       <c r="G366" t="n">
         <v>0.117</v>
@@ -42866,7 +42866,7 @@
         <v>-1.0071</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.2349</v>
+        <v>-0.2353</v>
       </c>
     </row>
     <row r="367">
@@ -42879,16 +42879,16 @@
         <v>-0.4673</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.1057</v>
+        <v>-0.1059</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.2865</v>
+        <v>-0.2866</v>
       </c>
       <c r="E367" t="n">
         <v>-0.4673</v>
       </c>
       <c r="F367" t="n">
-        <v>-0.1057</v>
+        <v>-0.1059</v>
       </c>
       <c r="G367" t="n">
         <v>0.2104</v>
@@ -42897,7 +42897,7 @@
         <v>-1.1451</v>
       </c>
       <c r="M367" t="n">
-        <v>-0.1057</v>
+        <v>-0.1059</v>
       </c>
     </row>
     <row r="368">
@@ -42910,16 +42910,16 @@
         <v>-0.4774</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.1073</v>
+        <v>-0.1076</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.2923</v>
+        <v>-0.2925</v>
       </c>
       <c r="E368" t="n">
         <v>-0.4774</v>
       </c>
       <c r="F368" t="n">
-        <v>-0.1073</v>
+        <v>-0.1076</v>
       </c>
       <c r="G368" t="n">
         <v>0.1595</v>
@@ -42928,7 +42928,7 @@
         <v>-1.1143</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.1073</v>
+        <v>-0.1076</v>
       </c>
     </row>
     <row r="369">
@@ -42941,16 +42941,16 @@
         <v>-0.4511</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.4026</v>
+        <v>-0.403</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.4269</v>
+        <v>-0.4271</v>
       </c>
       <c r="E369" t="n">
         <v>-0.4511</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.4026</v>
+        <v>-0.403</v>
       </c>
       <c r="G369" t="n">
         <v>0.1627</v>
@@ -42959,7 +42959,7 @@
         <v>-1.065</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.4026</v>
+        <v>-0.403</v>
       </c>
     </row>
     <row r="370">
@@ -42972,16 +42972,16 @@
         <v>-0.4067</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3743</v>
+        <v>-0.3748</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.3905</v>
+        <v>-0.3908</v>
       </c>
       <c r="E370" t="n">
         <v>-0.4067</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3743</v>
+        <v>-0.3748</v>
       </c>
       <c r="G370" t="n">
         <v>0.2599</v>
@@ -42990,7 +42990,7 @@
         <v>-1.0733</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3743</v>
+        <v>-0.3748</v>
       </c>
     </row>
     <row r="371">
@@ -43003,16 +43003,16 @@
         <v>-0.4545</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.3083</v>
+        <v>-0.3087</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.3814</v>
+        <v>-0.3816</v>
       </c>
       <c r="E371" t="n">
         <v>-0.4545</v>
       </c>
       <c r="F371" t="n">
-        <v>-0.3083</v>
+        <v>-0.3087</v>
       </c>
       <c r="G371" t="n">
         <v>0.2118</v>
@@ -43021,7 +43021,7 @@
         <v>-1.1208</v>
       </c>
       <c r="M371" t="n">
-        <v>-0.3083</v>
+        <v>-0.3087</v>
       </c>
     </row>
     <row r="372">
@@ -43034,16 +43034,16 @@
         <v>-0.5501</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3359</v>
+        <v>-0.3363</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.443</v>
+        <v>-0.4432</v>
       </c>
       <c r="E372" t="n">
         <v>-0.5501</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3359</v>
+        <v>-0.3363</v>
       </c>
       <c r="G372" t="n">
         <v>0.167</v>
@@ -43052,7 +43052,7 @@
         <v>-1.2673</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3359</v>
+        <v>-0.3363</v>
       </c>
     </row>
     <row r="373">
@@ -43065,16 +43065,16 @@
         <v>-0.5384</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2949</v>
+        <v>-0.2953</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.4166</v>
+        <v>-0.4168</v>
       </c>
       <c r="E373" t="n">
         <v>-0.5384</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2949</v>
+        <v>-0.2953</v>
       </c>
       <c r="G373" t="n">
         <v>0.1675</v>
@@ -43083,7 +43083,7 @@
         <v>-1.2442</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2949</v>
+        <v>-0.2953</v>
       </c>
     </row>
     <row r="374">
@@ -43096,7 +43096,7 @@
         <v>-0.5403</v>
       </c>
       <c r="C374" t="n">
-        <v>0.4904</v>
+        <v>0.4903</v>
       </c>
       <c r="D374" t="n">
         <v>-0.025</v>
@@ -43105,7 +43105,7 @@
         <v>-0.5403</v>
       </c>
       <c r="F374" t="n">
-        <v>0.4904</v>
+        <v>0.4903</v>
       </c>
       <c r="G374" t="n">
         <v>0.3126</v>
@@ -43126,7 +43126,7 @@
         <v>1.051</v>
       </c>
       <c r="M374" t="n">
-        <v>0.8189</v>
+        <v>0.8186</v>
       </c>
     </row>
     <row r="375">
@@ -43169,7 +43169,7 @@
         <v>1.0309</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8123</v>
+        <v>0.8122</v>
       </c>
     </row>
     <row r="376">
@@ -43182,7 +43182,7 @@
         <v>-0.6562</v>
       </c>
       <c r="C376" t="n">
-        <v>0.387</v>
+        <v>0.3869</v>
       </c>
       <c r="D376" t="n">
         <v>-0.1346</v>
@@ -43191,7 +43191,7 @@
         <v>-0.6562</v>
       </c>
       <c r="F376" t="n">
-        <v>0.387</v>
+        <v>0.3869</v>
       </c>
       <c r="G376" t="n">
         <v>0.2151</v>
@@ -43212,7 +43212,7 @@
         <v>0.8955</v>
       </c>
       <c r="M376" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8502</v>
       </c>
     </row>
     <row r="377">
@@ -43255,7 +43255,7 @@
         <v>0.9013</v>
       </c>
       <c r="M377" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="378">
@@ -43298,7 +43298,7 @@
         <v>0.7295</v>
       </c>
       <c r="M378" t="n">
-        <v>0.7489</v>
+        <v>0.7487</v>
       </c>
     </row>
     <row r="379">
@@ -43311,7 +43311,7 @@
         <v>-0.556</v>
       </c>
       <c r="C379" t="n">
-        <v>0.1968</v>
+        <v>0.1967</v>
       </c>
       <c r="D379" t="n">
         <v>-0.1796</v>
@@ -43320,7 +43320,7 @@
         <v>-0.556</v>
       </c>
       <c r="F379" t="n">
-        <v>0.1968</v>
+        <v>0.1967</v>
       </c>
       <c r="G379" t="n">
         <v>0.1671</v>
@@ -43341,7 +43341,7 @@
         <v>0.7169</v>
       </c>
       <c r="M379" t="n">
-        <v>0.7418</v>
+        <v>0.7416</v>
       </c>
     </row>
     <row r="380">
@@ -43357,7 +43357,7 @@
         <v>0.1267</v>
       </c>
       <c r="D380" t="n">
-        <v>-0.1494</v>
+        <v>-0.1495</v>
       </c>
       <c r="E380" t="n">
         <v>-0.4256</v>
@@ -43384,7 +43384,7 @@
         <v>0.5988</v>
       </c>
       <c r="M380" t="n">
-        <v>0.758</v>
+        <v>0.7578</v>
       </c>
     </row>
     <row r="381">
@@ -43397,7 +43397,7 @@
         <v>-0.4763</v>
       </c>
       <c r="C381" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="D381" t="n">
         <v>-0.2192</v>
@@ -43406,7 +43406,7 @@
         <v>-0.4763</v>
       </c>
       <c r="F381" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="G381" t="n">
         <v>0.1645</v>
@@ -43427,7 +43427,7 @@
         <v>0.4704</v>
       </c>
       <c r="M381" t="n">
-        <v>0.7166</v>
+        <v>0.7164</v>
       </c>
     </row>
     <row r="382">
@@ -43440,7 +43440,7 @@
         <v>-0.4875</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.0207</v>
+        <v>-0.0208</v>
       </c>
       <c r="D382" t="n">
         <v>-0.2541</v>
@@ -43449,7 +43449,7 @@
         <v>-0.4875</v>
       </c>
       <c r="F382" t="n">
-        <v>-0.0207</v>
+        <v>-0.0208</v>
       </c>
       <c r="G382" t="n">
         <v>0.163</v>
@@ -43470,7 +43470,7 @@
         <v>0.3495</v>
       </c>
       <c r="M382" t="n">
-        <v>0.7829</v>
+        <v>0.7828000000000001</v>
       </c>
     </row>
     <row r="383">
@@ -43483,16 +43483,16 @@
         <v>-0.4239</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.0789</v>
+        <v>-0.079</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.2514</v>
+        <v>-0.2515</v>
       </c>
       <c r="E383" t="n">
         <v>-0.4239</v>
       </c>
       <c r="F383" t="n">
-        <v>-0.0789</v>
+        <v>-0.079</v>
       </c>
       <c r="G383" t="n">
         <v>0.2022</v>
@@ -43513,7 +43513,7 @@
         <v>0.2889</v>
       </c>
       <c r="M383" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.7605</v>
       </c>
     </row>
     <row r="384">
@@ -43556,7 +43556,7 @@
         <v>0.2187</v>
       </c>
       <c r="M384" t="n">
-        <v>0.7524</v>
+        <v>0.7522</v>
       </c>
     </row>
     <row r="385">
@@ -43569,7 +43569,7 @@
         <v>-0.3657</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.207</v>
+        <v>-0.2071</v>
       </c>
       <c r="D385" t="n">
         <v>-0.2864</v>
@@ -43578,7 +43578,7 @@
         <v>-0.3657</v>
       </c>
       <c r="F385" t="n">
-        <v>-0.207</v>
+        <v>-0.2071</v>
       </c>
       <c r="G385" t="n">
         <v>0.1989</v>
@@ -43599,7 +43599,7 @@
         <v>0.14</v>
       </c>
       <c r="M385" t="n">
-        <v>0.7129</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="386">
@@ -43612,7 +43612,7 @@
         <v>-0.4492</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.2719</v>
+        <v>-0.272</v>
       </c>
       <c r="D386" t="n">
         <v>-0.3606</v>
@@ -43621,7 +43621,7 @@
         <v>-0.4492</v>
       </c>
       <c r="F386" t="n">
-        <v>-0.2719</v>
+        <v>-0.272</v>
       </c>
       <c r="G386" t="n">
         <v>0.1998</v>
@@ -43642,7 +43642,7 @@
         <v>-0.0242</v>
       </c>
       <c r="M386" t="n">
-        <v>0.7795</v>
+        <v>0.7794</v>
       </c>
     </row>
     <row r="387">
@@ -43685,7 +43685,7 @@
         <v>-0.1281</v>
       </c>
       <c r="M387" t="n">
-        <v>0.8376</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="388">
@@ -43827,7 +43827,7 @@
         <v>-0.8995</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.6219</v>
+        <v>-0.622</v>
       </c>
       <c r="D391" t="n">
         <v>-0.7607</v>
@@ -43836,7 +43836,7 @@
         <v>-0.8995</v>
       </c>
       <c r="F391" t="n">
-        <v>-0.6219</v>
+        <v>-0.622</v>
       </c>
       <c r="G391" t="n">
         <v>0.2407</v>
@@ -43943,7 +43943,7 @@
         <v>-0.652</v>
       </c>
       <c r="M393" t="n">
-        <v>0.4014</v>
+        <v>0.4013</v>
       </c>
     </row>
     <row r="394">
@@ -43986,7 +43986,7 @@
         <v>-0.6529</v>
       </c>
       <c r="M394" t="n">
-        <v>0.3743</v>
+        <v>0.3742</v>
       </c>
     </row>
     <row r="395">
@@ -44029,7 +44029,7 @@
         <v>-0.8083</v>
       </c>
       <c r="M395" t="n">
-        <v>0.3637</v>
+        <v>0.3636</v>
       </c>
     </row>
     <row r="396">
@@ -44171,7 +44171,7 @@
         <v>-0.848</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.7146</v>
+        <v>-0.7147</v>
       </c>
       <c r="D399" t="n">
         <v>-0.7813</v>
@@ -44180,7 +44180,7 @@
         <v>-0.848</v>
       </c>
       <c r="F399" t="n">
-        <v>-0.7146</v>
+        <v>-0.7147</v>
       </c>
       <c r="G399" t="n">
         <v>-0.0011</v>
@@ -44257,7 +44257,7 @@
         <v>-0.7693</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.6975</v>
+        <v>-0.6976</v>
       </c>
       <c r="D401" t="n">
         <v>-0.7334000000000001</v>
@@ -44266,7 +44266,7 @@
         <v>-0.7693</v>
       </c>
       <c r="F401" t="n">
-        <v>-0.6975</v>
+        <v>-0.6976</v>
       </c>
       <c r="G401" t="n">
         <v>-0.0488</v>
@@ -44389,7 +44389,7 @@
         <v>-0.7622</v>
       </c>
       <c r="D404" t="n">
-        <v>-0.5969</v>
+        <v>-0.597</v>
       </c>
       <c r="E404" t="n">
         <v>-0.4317</v>
@@ -44416,7 +44416,7 @@
         <v>-1.671</v>
       </c>
       <c r="M404" t="n">
-        <v>0.0939</v>
+        <v>0.09379999999999999</v>
       </c>
     </row>
     <row r="405">
@@ -44459,7 +44459,7 @@
         <v>-1.6817</v>
       </c>
       <c r="M405" t="n">
-        <v>-0.0021</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="406">
@@ -44472,7 +44472,7 @@
         <v>-0.4815</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.8399</v>
+        <v>-0.84</v>
       </c>
       <c r="D406" t="n">
         <v>-0.6607</v>
@@ -44481,7 +44481,7 @@
         <v>-0.4815</v>
       </c>
       <c r="F406" t="n">
-        <v>-0.8399</v>
+        <v>-0.84</v>
       </c>
       <c r="G406" t="n">
         <v>-0.0582</v>
@@ -44545,7 +44545,7 @@
         <v>-1.9155</v>
       </c>
       <c r="M407" t="n">
-        <v>-0.1641</v>
+        <v>-0.1642</v>
       </c>
     </row>
     <row r="408">
@@ -44588,7 +44588,7 @@
         <v>-1.9322</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.1735</v>
+        <v>-0.1736</v>
       </c>
     </row>
     <row r="409">
@@ -44631,7 +44631,7 @@
         <v>-2.0019</v>
       </c>
       <c r="M409" t="n">
-        <v>-0.2824</v>
+        <v>-0.2825</v>
       </c>
     </row>
     <row r="410">
@@ -44674,7 +44674,7 @@
         <v>-2.128</v>
       </c>
       <c r="M410" t="n">
-        <v>-0.3735</v>
+        <v>-0.3737</v>
       </c>
     </row>
     <row r="411">
@@ -44687,16 +44687,16 @@
         <v>-0.2398</v>
       </c>
       <c r="C411" t="n">
-        <v>-1.0752</v>
+        <v>-1.0753</v>
       </c>
       <c r="D411" t="n">
-        <v>-0.6575</v>
+        <v>-0.6576</v>
       </c>
       <c r="E411" t="n">
         <v>-0.2398</v>
       </c>
       <c r="F411" t="n">
-        <v>-1.0752</v>
+        <v>-1.0753</v>
       </c>
       <c r="G411" t="n">
         <v>0.5134</v>
@@ -44717,7 +44717,7 @@
         <v>-2.2831</v>
       </c>
       <c r="M411" t="n">
-        <v>-0.3668</v>
+        <v>-0.367</v>
       </c>
     </row>
     <row r="412">
@@ -44733,7 +44733,7 @@
         <v>-1.1508</v>
       </c>
       <c r="D412" t="n">
-        <v>-0.6873</v>
+        <v>-0.6874</v>
       </c>
       <c r="E412" t="n">
         <v>-0.2239</v>
@@ -44760,7 +44760,7 @@
         <v>-2.3123</v>
       </c>
       <c r="M412" t="n">
-        <v>-0.6058</v>
+        <v>-0.6061</v>
       </c>
     </row>
     <row r="413">
@@ -44773,16 +44773,16 @@
         <v>-0.2381</v>
       </c>
       <c r="C413" t="n">
-        <v>-1.1658</v>
+        <v>-1.1659</v>
       </c>
       <c r="D413" t="n">
-        <v>-0.7019</v>
+        <v>-0.702</v>
       </c>
       <c r="E413" t="n">
         <v>-0.2381</v>
       </c>
       <c r="F413" t="n">
-        <v>-1.1658</v>
+        <v>-1.1659</v>
       </c>
       <c r="G413" t="n">
         <v>0.4525</v>
@@ -44803,7 +44803,7 @@
         <v>-2.4555</v>
       </c>
       <c r="M413" t="n">
-        <v>-0.527</v>
+        <v>-0.5271</v>
       </c>
     </row>
     <row r="414">
@@ -44846,7 +44846,7 @@
         <v>-2.4996</v>
       </c>
       <c r="M414" t="n">
-        <v>-0.4849</v>
+        <v>-0.485</v>
       </c>
     </row>
     <row r="415">
@@ -44859,16 +44859,16 @@
         <v>-0.0443</v>
       </c>
       <c r="C415" t="n">
-        <v>-1.2376</v>
+        <v>-1.2377</v>
       </c>
       <c r="D415" t="n">
-        <v>-0.6409</v>
+        <v>-0.641</v>
       </c>
       <c r="E415" t="n">
         <v>-0.0443</v>
       </c>
       <c r="F415" t="n">
-        <v>-1.2376</v>
+        <v>-1.2377</v>
       </c>
       <c r="G415" t="n">
         <v>0.8522999999999999</v>
@@ -44889,7 +44889,7 @@
         <v>-2.6249</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.6219</v>
+        <v>-0.6221</v>
       </c>
     </row>
     <row r="416">
@@ -44932,7 +44932,7 @@
         <v>-2.7787</v>
       </c>
       <c r="M416" t="n">
-        <v>-0.6714</v>
+        <v>-0.6716</v>
       </c>
     </row>
     <row r="417">
@@ -44975,7 +44975,7 @@
         <v>-2.8637</v>
       </c>
       <c r="M417" t="n">
-        <v>-0.7222</v>
+        <v>-0.7223000000000001</v>
       </c>
     </row>
     <row r="418">
@@ -44988,7 +44988,7 @@
         <v>-0.006</v>
       </c>
       <c r="C418" t="n">
-        <v>-1.3341</v>
+        <v>-1.3342</v>
       </c>
       <c r="D418" t="n">
         <v>-0.6701</v>
@@ -44997,7 +44997,7 @@
         <v>-0.006</v>
       </c>
       <c r="F418" t="n">
-        <v>-1.3341</v>
+        <v>-1.3342</v>
       </c>
       <c r="G418" t="n">
         <v>1.0705</v>
@@ -45018,7 +45018,7 @@
         <v>-2.9316</v>
       </c>
       <c r="M418" t="n">
-        <v>-0.6681</v>
+        <v>-0.6682</v>
       </c>
     </row>
     <row r="419">
@@ -45034,7 +45034,7 @@
         <v>-1.3699</v>
       </c>
       <c r="D419" t="n">
-        <v>-0.7241</v>
+        <v>-0.7242</v>
       </c>
       <c r="E419" t="n">
         <v>-0.0784</v>
@@ -45061,7 +45061,7 @@
         <v>-3.0006</v>
       </c>
       <c r="M419" t="n">
-        <v>-0.7291</v>
+        <v>-0.7292</v>
       </c>
     </row>
     <row r="420">
@@ -45104,7 +45104,7 @@
         <v>-2.8123</v>
       </c>
       <c r="M420" t="n">
-        <v>-0.6229</v>
+        <v>-0.623</v>
       </c>
     </row>
     <row r="421">
@@ -45117,16 +45117,16 @@
         <v>-0.4096</v>
       </c>
       <c r="C421" t="n">
-        <v>-1.1211</v>
+        <v>-1.1212</v>
       </c>
       <c r="D421" t="n">
-        <v>-0.7653</v>
+        <v>-0.7654</v>
       </c>
       <c r="E421" t="n">
         <v>-0.4096</v>
       </c>
       <c r="F421" t="n">
-        <v>-1.1211</v>
+        <v>-1.1212</v>
       </c>
       <c r="G421" t="n">
         <v>-0.0752</v>
@@ -45147,7 +45147,7 @@
         <v>-2.5794</v>
       </c>
       <c r="M421" t="n">
-        <v>-0.4441</v>
+        <v>-0.4442</v>
       </c>
     </row>
     <row r="422">
@@ -45190,7 +45190,7 @@
         <v>-2.1771</v>
       </c>
       <c r="M422" t="n">
-        <v>-0.1943</v>
+        <v>-0.1944</v>
       </c>
     </row>
     <row r="423">
@@ -45233,7 +45233,7 @@
         <v>-1.9019</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.0494</v>
+        <v>-0.0495</v>
       </c>
     </row>
     <row r="424">
@@ -45276,7 +45276,7 @@
         <v>-1.4944</v>
       </c>
       <c r="M424" t="n">
-        <v>0.1363</v>
+        <v>0.1362</v>
       </c>
     </row>
     <row r="425">
@@ -45319,7 +45319,7 @@
         <v>-1.2153</v>
       </c>
       <c r="M425" t="n">
-        <v>0.3121</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="426">
@@ -45362,7 +45362,7 @@
         <v>-0.7655</v>
       </c>
       <c r="M426" t="n">
-        <v>0.544</v>
+        <v>0.5439000000000001</v>
       </c>
     </row>
     <row r="427">
@@ -45405,7 +45405,7 @@
         <v>-0.4699</v>
       </c>
       <c r="M427" t="n">
-        <v>0.6252</v>
+        <v>0.6251</v>
       </c>
     </row>
     <row r="428">
@@ -45448,7 +45448,7 @@
         <v>-0.3802</v>
       </c>
       <c r="M428" t="n">
-        <v>0.6788</v>
+        <v>0.6787</v>
       </c>
     </row>
     <row r="429">
@@ -45491,7 +45491,7 @@
         <v>-0.3184</v>
       </c>
       <c r="M429" t="n">
-        <v>0.5556</v>
+        <v>0.5554</v>
       </c>
     </row>
     <row r="430">
@@ -45504,7 +45504,7 @@
         <v>-0.6762</v>
       </c>
       <c r="C430" t="n">
-        <v>0.0635</v>
+        <v>0.0634</v>
       </c>
       <c r="D430" t="n">
         <v>-0.3064</v>
@@ -45513,7 +45513,7 @@
         <v>-0.6762</v>
       </c>
       <c r="F430" t="n">
-        <v>0.0635</v>
+        <v>0.0634</v>
       </c>
       <c r="G430" t="n">
         <v>-0.8811</v>
@@ -45534,7 +45534,7 @@
         <v>-0.2206</v>
       </c>
       <c r="M430" t="n">
-        <v>0.5225</v>
+        <v>0.5224</v>
       </c>
     </row>
     <row r="431">
@@ -45547,7 +45547,7 @@
         <v>-0.7836</v>
       </c>
       <c r="C431" t="n">
-        <v>0.0809</v>
+        <v>0.0808</v>
       </c>
       <c r="D431" t="n">
         <v>-0.3514</v>
@@ -45556,7 +45556,7 @@
         <v>-0.7836</v>
       </c>
       <c r="F431" t="n">
-        <v>0.0809</v>
+        <v>0.0808</v>
       </c>
       <c r="G431" t="n">
         <v>-0.8386</v>
@@ -45577,7 +45577,7 @@
         <v>-0.2436</v>
       </c>
       <c r="M431" t="n">
-        <v>0.5652</v>
+        <v>0.5651</v>
       </c>
     </row>
     <row r="432">
@@ -45590,16 +45590,16 @@
         <v>-0.722</v>
       </c>
       <c r="C432" t="n">
-        <v>0.0872</v>
+        <v>0.0871</v>
       </c>
       <c r="D432" t="n">
-        <v>-0.3174</v>
+        <v>-0.3175</v>
       </c>
       <c r="E432" t="n">
         <v>-0.722</v>
       </c>
       <c r="F432" t="n">
-        <v>0.0872</v>
+        <v>0.0871</v>
       </c>
       <c r="G432" t="n">
         <v>-0.5634</v>
@@ -45620,7 +45620,7 @@
         <v>-0.1602</v>
       </c>
       <c r="M432" t="n">
-        <v>0.4566</v>
+        <v>0.4564</v>
       </c>
     </row>
     <row r="433">
@@ -45633,16 +45633,16 @@
         <v>-0.6488</v>
       </c>
       <c r="C433" t="n">
-        <v>0.1189</v>
+        <v>0.1188</v>
       </c>
       <c r="D433" t="n">
-        <v>-0.2649</v>
+        <v>-0.265</v>
       </c>
       <c r="E433" t="n">
         <v>-0.6488</v>
       </c>
       <c r="F433" t="n">
-        <v>0.1189</v>
+        <v>0.1188</v>
       </c>
       <c r="G433" t="n">
         <v>-0.4118</v>
@@ -45663,7 +45663,7 @@
         <v>-0.1164</v>
       </c>
       <c r="M433" t="n">
-        <v>0.5098</v>
+        <v>0.5097</v>
       </c>
     </row>
     <row r="434">
@@ -45706,7 +45706,7 @@
         <v>-0.0469</v>
       </c>
       <c r="M434" t="n">
-        <v>0.4512</v>
+        <v>0.4511</v>
       </c>
     </row>
     <row r="435">
@@ -45719,7 +45719,7 @@
         <v>-0.5966</v>
       </c>
       <c r="C435" t="n">
-        <v>0.1372</v>
+        <v>0.1371</v>
       </c>
       <c r="D435" t="n">
         <v>-0.2297</v>
@@ -45728,7 +45728,7 @@
         <v>-0.5966</v>
       </c>
       <c r="F435" t="n">
-        <v>0.1372</v>
+        <v>0.1371</v>
       </c>
       <c r="G435" t="n">
         <v>-0.2189</v>
@@ -45749,7 +45749,7 @@
         <v>-0.0399</v>
       </c>
       <c r="M435" t="n">
-        <v>0.4081</v>
+        <v>0.4079</v>
       </c>
     </row>
     <row r="436">
@@ -45792,7 +45792,7 @@
         <v>0.0902</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4159</v>
+        <v>0.4157</v>
       </c>
     </row>
     <row r="437">
@@ -45805,7 +45805,7 @@
         <v>-0.6405999999999999</v>
       </c>
       <c r="C437" t="n">
-        <v>0.2236</v>
+        <v>0.2235</v>
       </c>
       <c r="D437" t="n">
         <v>-0.2085</v>
@@ -45814,7 +45814,7 @@
         <v>-0.6405999999999999</v>
       </c>
       <c r="F437" t="n">
-        <v>0.2236</v>
+        <v>0.2235</v>
       </c>
       <c r="G437" t="n">
         <v>-0.314</v>
@@ -45835,7 +45835,7 @@
         <v>0.1695</v>
       </c>
       <c r="M437" t="n">
-        <v>0.4068</v>
+        <v>0.4067</v>
       </c>
     </row>
     <row r="438">
@@ -45848,7 +45848,7 @@
         <v>-0.6195000000000001</v>
       </c>
       <c r="C438" t="n">
-        <v>0.2809</v>
+        <v>0.2808</v>
       </c>
       <c r="D438" t="n">
         <v>-0.1693</v>
@@ -45857,7 +45857,7 @@
         <v>-0.6195000000000001</v>
       </c>
       <c r="F438" t="n">
-        <v>0.2809</v>
+        <v>0.2808</v>
       </c>
       <c r="G438" t="n">
         <v>-0.2191</v>
@@ -45878,7 +45878,7 @@
         <v>0.2591</v>
       </c>
       <c r="M438" t="n">
-        <v>0.4628</v>
+        <v>0.4627</v>
       </c>
     </row>
     <row r="439">
@@ -45921,7 +45921,7 @@
         <v>0.2486</v>
       </c>
       <c r="M439" t="n">
-        <v>0.3236</v>
+        <v>0.3234</v>
       </c>
     </row>
     <row r="440">
@@ -45964,7 +45964,7 @@
         <v>0.2602</v>
       </c>
       <c r="M440" t="n">
-        <v>0.4016</v>
+        <v>0.4015</v>
       </c>
     </row>
     <row r="441">
@@ -46007,7 +46007,7 @@
         <v>0.2186</v>
       </c>
       <c r="M441" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="442">
@@ -46020,7 +46020,7 @@
         <v>-0.739</v>
       </c>
       <c r="C442" t="n">
-        <v>0.2545</v>
+        <v>0.2544</v>
       </c>
       <c r="D442" t="n">
         <v>-0.2423</v>
@@ -46029,7 +46029,7 @@
         <v>-0.739</v>
       </c>
       <c r="F442" t="n">
-        <v>0.2545</v>
+        <v>0.2544</v>
       </c>
       <c r="G442" t="n">
         <v>-0.3608</v>
@@ -46050,7 +46050,7 @@
         <v>0.2863</v>
       </c>
       <c r="M442" t="n">
-        <v>0.232</v>
+        <v>0.2318</v>
       </c>
     </row>
     <row r="443">
@@ -46093,7 +46093,7 @@
         <v>0.3248</v>
       </c>
       <c r="M443" t="n">
-        <v>0.2767</v>
+        <v>0.2765</v>
       </c>
     </row>
     <row r="444">
@@ -46106,16 +46106,16 @@
         <v>-0.6088</v>
       </c>
       <c r="C444" t="n">
-        <v>0.2765</v>
+        <v>0.2764</v>
       </c>
       <c r="D444" t="n">
-        <v>-0.1661</v>
+        <v>-0.1662</v>
       </c>
       <c r="E444" t="n">
         <v>-0.6088</v>
       </c>
       <c r="F444" t="n">
-        <v>0.2765</v>
+        <v>0.2764</v>
       </c>
       <c r="G444" t="n">
         <v>-0.1725</v>
@@ -46136,7 +46136,7 @@
         <v>0.2365</v>
       </c>
       <c r="M444" t="n">
-        <v>0.2892</v>
+        <v>0.2891</v>
       </c>
     </row>
     <row r="445">
@@ -46179,7 +46179,7 @@
         <v>0.1903</v>
       </c>
       <c r="M445" t="n">
-        <v>0.1829</v>
+        <v>0.1827</v>
       </c>
     </row>
     <row r="446">
@@ -46192,7 +46192,7 @@
         <v>-0.6766</v>
       </c>
       <c r="C446" t="n">
-        <v>0.2781</v>
+        <v>0.278</v>
       </c>
       <c r="D446" t="n">
         <v>-0.1993</v>
@@ -46201,7 +46201,7 @@
         <v>-0.6766</v>
       </c>
       <c r="F446" t="n">
-        <v>0.2781</v>
+        <v>0.278</v>
       </c>
       <c r="G446" t="n">
         <v>-0.1755</v>
@@ -46222,7 +46222,7 @@
         <v>0.2387</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2389</v>
+        <v>0.2388</v>
       </c>
     </row>
     <row r="447">
@@ -46235,16 +46235,16 @@
         <v>-0.6869</v>
       </c>
       <c r="C447" t="n">
-        <v>0.2636</v>
+        <v>0.2635</v>
       </c>
       <c r="D447" t="n">
-        <v>-0.2116</v>
+        <v>-0.2117</v>
       </c>
       <c r="E447" t="n">
         <v>-0.6869</v>
       </c>
       <c r="F447" t="n">
-        <v>0.2636</v>
+        <v>0.2635</v>
       </c>
       <c r="G447" t="n">
         <v>-0.182</v>
@@ -46265,7 +46265,7 @@
         <v>0.2031</v>
       </c>
       <c r="M447" t="n">
-        <v>0.1855</v>
+        <v>0.1854</v>
       </c>
     </row>
     <row r="448">
@@ -46278,7 +46278,7 @@
         <v>-0.4018</v>
       </c>
       <c r="C448" t="n">
-        <v>0.2413</v>
+        <v>0.2412</v>
       </c>
       <c r="D448" t="n">
         <v>-0.0803</v>
@@ -46287,7 +46287,7 @@
         <v>-0.4018</v>
       </c>
       <c r="F448" t="n">
-        <v>0.2413</v>
+        <v>0.2412</v>
       </c>
       <c r="G448" t="n">
         <v>-0.0823</v>
@@ -46308,7 +46308,7 @@
         <v>0.1996</v>
       </c>
       <c r="M448" t="n">
-        <v>0.1198</v>
+        <v>0.1197</v>
       </c>
     </row>
     <row r="449">
@@ -46351,7 +46351,7 @@
         <v>0.1753</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1533</v>
+        <v>0.1531</v>
       </c>
     </row>
     <row r="450">
@@ -46394,7 +46394,7 @@
         <v>0.2242</v>
       </c>
       <c r="M450" t="n">
-        <v>0.1821</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="451">
@@ -46407,16 +46407,16 @@
         <v>-0.3434</v>
       </c>
       <c r="C451" t="n">
-        <v>0.2832</v>
+        <v>0.2831</v>
       </c>
       <c r="D451" t="n">
-        <v>-0.0301</v>
+        <v>-0.0302</v>
       </c>
       <c r="E451" t="n">
         <v>-0.3434</v>
       </c>
       <c r="F451" t="n">
-        <v>0.2832</v>
+        <v>0.2831</v>
       </c>
       <c r="G451" t="n">
         <v>0.1223</v>
@@ -46437,7 +46437,7 @@
         <v>0.1722</v>
       </c>
       <c r="M451" t="n">
-        <v>0.1679</v>
+        <v>0.1677</v>
       </c>
     </row>
     <row r="452">
@@ -46450,7 +46450,7 @@
         <v>-0.3027</v>
       </c>
       <c r="C452" t="n">
-        <v>0.2795</v>
+        <v>0.2794</v>
       </c>
       <c r="D452" t="n">
         <v>-0.0116</v>
@@ -46459,7 +46459,7 @@
         <v>-0.3027</v>
       </c>
       <c r="F452" t="n">
-        <v>0.2795</v>
+        <v>0.2794</v>
       </c>
       <c r="G452" t="n">
         <v>0.2703</v>
@@ -46480,7 +46480,7 @@
         <v>0.1773</v>
       </c>
       <c r="M452" t="n">
-        <v>0.1852</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="453">
@@ -46493,16 +46493,16 @@
         <v>-0.3311</v>
       </c>
       <c r="C453" t="n">
-        <v>0.2512</v>
+        <v>0.2511</v>
       </c>
       <c r="D453" t="n">
-        <v>-0.0399</v>
+        <v>-0.04</v>
       </c>
       <c r="E453" t="n">
         <v>-0.3311</v>
       </c>
       <c r="F453" t="n">
-        <v>0.2512</v>
+        <v>0.2511</v>
       </c>
       <c r="G453" t="n">
         <v>0.3181</v>
@@ -46523,7 +46523,7 @@
         <v>0.1417</v>
       </c>
       <c r="M453" t="n">
-        <v>0.1964</v>
+        <v>0.1962</v>
       </c>
     </row>
     <row r="454">
@@ -46536,7 +46536,7 @@
         <v>-0.357</v>
       </c>
       <c r="C454" t="n">
-        <v>0.276</v>
+        <v>0.2759</v>
       </c>
       <c r="D454" t="n">
         <v>-0.0405</v>
@@ -46545,7 +46545,7 @@
         <v>-0.357</v>
       </c>
       <c r="F454" t="n">
-        <v>0.276</v>
+        <v>0.2759</v>
       </c>
       <c r="G454" t="n">
         <v>0.3194</v>
@@ -46566,7 +46566,7 @@
         <v>0.2311</v>
       </c>
       <c r="M454" t="n">
-        <v>0.2547</v>
+        <v>0.2546</v>
       </c>
     </row>
     <row r="455">
@@ -46579,16 +46579,16 @@
         <v>-0.4766</v>
       </c>
       <c r="C455" t="n">
-        <v>0.2627</v>
+        <v>0.2626</v>
       </c>
       <c r="D455" t="n">
-        <v>-0.1069</v>
+        <v>-0.107</v>
       </c>
       <c r="E455" t="n">
         <v>-0.4766</v>
       </c>
       <c r="F455" t="n">
-        <v>0.2627</v>
+        <v>0.2626</v>
       </c>
       <c r="G455" t="n">
         <v>0.1727</v>
@@ -46609,7 +46609,7 @@
         <v>0.1664</v>
       </c>
       <c r="M455" t="n">
-        <v>0.3105</v>
+        <v>0.3104</v>
       </c>
     </row>
     <row r="456">
@@ -46652,7 +46652,7 @@
         <v>0.2672</v>
       </c>
       <c r="M456" t="n">
-        <v>0.3915</v>
+        <v>0.3914</v>
       </c>
     </row>
     <row r="457">
@@ -46695,7 +46695,7 @@
         <v>0.1266</v>
       </c>
       <c r="M457" t="n">
-        <v>0.3506</v>
+        <v>0.3505</v>
       </c>
     </row>
     <row r="458">
@@ -46711,7 +46711,7 @@
         <v>0.2483</v>
       </c>
       <c r="D458" t="n">
-        <v>-0.1035</v>
+        <v>-0.1036</v>
       </c>
       <c r="E458" t="n">
         <v>-0.4554</v>
@@ -46738,7 +46738,7 @@
         <v>0.1907</v>
       </c>
       <c r="M458" t="n">
-        <v>0.3884</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="459">
@@ -46754,7 +46754,7 @@
         <v>0.2593</v>
       </c>
       <c r="D459" t="n">
-        <v>-0.0415</v>
+        <v>-0.0416</v>
       </c>
       <c r="E459" t="n">
         <v>-0.3424</v>
@@ -46781,7 +46781,7 @@
         <v>0.2417</v>
       </c>
       <c r="M459" t="n">
-        <v>0.4025</v>
+        <v>0.4023</v>
       </c>
     </row>
     <row r="460">
@@ -46824,7 +46824,7 @@
         <v>0.3094</v>
       </c>
       <c r="M460" t="n">
-        <v>0.3717</v>
+        <v>0.3715</v>
       </c>
     </row>
     <row r="461">
@@ -46837,7 +46837,7 @@
         <v>-0.4049</v>
       </c>
       <c r="C461" t="n">
-        <v>0.2694</v>
+        <v>0.2693</v>
       </c>
       <c r="D461" t="n">
         <v>-0.0678</v>
@@ -46846,7 +46846,7 @@
         <v>-0.4049</v>
       </c>
       <c r="F461" t="n">
-        <v>0.2694</v>
+        <v>0.2693</v>
       </c>
       <c r="G461" t="n">
         <v>0.3214</v>
@@ -46867,7 +46867,7 @@
         <v>0.3755</v>
       </c>
       <c r="M461" t="n">
-        <v>0.3928</v>
+        <v>0.3926</v>
       </c>
     </row>
     <row r="462">
@@ -46883,7 +46883,7 @@
         <v>0.2196</v>
       </c>
       <c r="D462" t="n">
-        <v>-0.1416</v>
+        <v>-0.1417</v>
       </c>
       <c r="E462" t="n">
         <v>-0.5029</v>
@@ -46910,7 +46910,7 @@
         <v>0.3007</v>
       </c>
       <c r="M462" t="n">
-        <v>0.3902</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="463">
@@ -46923,7 +46923,7 @@
         <v>-0.4249</v>
       </c>
       <c r="C463" t="n">
-        <v>0.222</v>
+        <v>0.2219</v>
       </c>
       <c r="D463" t="n">
         <v>-0.1015</v>
@@ -46932,7 +46932,7 @@
         <v>-0.4249</v>
       </c>
       <c r="F463" t="n">
-        <v>0.222</v>
+        <v>0.2219</v>
       </c>
       <c r="G463" t="n">
         <v>0.127</v>
@@ -46953,7 +46953,7 @@
         <v>0.4357</v>
       </c>
       <c r="M463" t="n">
-        <v>0.3318</v>
+        <v>0.3316</v>
       </c>
     </row>
     <row r="464">
@@ -46966,16 +46966,16 @@
         <v>-0.4729</v>
       </c>
       <c r="C464" t="n">
-        <v>0.2796</v>
+        <v>0.2795</v>
       </c>
       <c r="D464" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="E464" t="n">
         <v>-0.4729</v>
       </c>
       <c r="F464" t="n">
-        <v>0.2796</v>
+        <v>0.2795</v>
       </c>
       <c r="G464" t="n">
         <v>0.076</v>
@@ -46996,7 +46996,7 @@
         <v>0.3646</v>
       </c>
       <c r="M464" t="n">
-        <v>0.3706</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="465">
@@ -47009,7 +47009,7 @@
         <v>-0.4812</v>
       </c>
       <c r="C465" t="n">
-        <v>0.3584</v>
+        <v>0.3583</v>
       </c>
       <c r="D465" t="n">
         <v>-0.0614</v>
@@ -47018,7 +47018,7 @@
         <v>-0.4812</v>
       </c>
       <c r="F465" t="n">
-        <v>0.3584</v>
+        <v>0.3583</v>
       </c>
       <c r="G465" t="n">
         <v>0.1255</v>
@@ -47039,7 +47039,7 @@
         <v>0.4487</v>
       </c>
       <c r="M465" t="n">
-        <v>0.3802</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="466">
@@ -47082,7 +47082,7 @@
         <v>0.4637</v>
       </c>
       <c r="M466" t="n">
-        <v>0.3232</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="467">
@@ -47095,16 +47095,16 @@
         <v>-0.2583</v>
       </c>
       <c r="C467" t="n">
-        <v>0.4715</v>
+        <v>0.4714</v>
       </c>
       <c r="D467" t="n">
-        <v>0.1066</v>
+        <v>0.1065</v>
       </c>
       <c r="E467" t="n">
         <v>-0.2583</v>
       </c>
       <c r="F467" t="n">
-        <v>0.4715</v>
+        <v>0.4714</v>
       </c>
       <c r="G467" t="n">
         <v>0.2235</v>
@@ -47125,7 +47125,7 @@
         <v>0.4398</v>
       </c>
       <c r="M467" t="n">
-        <v>0.3789</v>
+        <v>0.3786</v>
       </c>
     </row>
     <row r="468">
@@ -47138,16 +47138,16 @@
         <v>-0.349</v>
       </c>
       <c r="C468" t="n">
-        <v>0.5625</v>
+        <v>0.5624</v>
       </c>
       <c r="D468" t="n">
-        <v>0.1068</v>
+        <v>0.1067</v>
       </c>
       <c r="E468" t="n">
         <v>-0.349</v>
       </c>
       <c r="F468" t="n">
-        <v>0.5625</v>
+        <v>0.5624</v>
       </c>
       <c r="G468" t="n">
         <v>0.2234</v>
@@ -47168,7 +47168,7 @@
         <v>0.5655</v>
       </c>
       <c r="M468" t="n">
-        <v>0.3635</v>
+        <v>0.3633</v>
       </c>
     </row>
     <row r="469">
@@ -47181,7 +47181,7 @@
         <v>-0.1417</v>
       </c>
       <c r="C469" t="n">
-        <v>0.6045</v>
+        <v>0.6044</v>
       </c>
       <c r="D469" t="n">
         <v>0.2314</v>
@@ -47190,7 +47190,7 @@
         <v>-0.1417</v>
       </c>
       <c r="F469" t="n">
-        <v>0.6045</v>
+        <v>0.6044</v>
       </c>
       <c r="G469" t="n">
         <v>0.5668</v>
@@ -47211,7 +47211,7 @@
         <v>0.4968</v>
       </c>
       <c r="M469" t="n">
-        <v>0.3923</v>
+        <v>0.3921</v>
       </c>
     </row>
     <row r="470">
@@ -47224,16 +47224,16 @@
         <v>-0.0474</v>
       </c>
       <c r="C470" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6698</v>
       </c>
       <c r="D470" t="n">
-        <v>0.3113</v>
+        <v>0.3112</v>
       </c>
       <c r="E470" t="n">
         <v>-0.0474</v>
       </c>
       <c r="F470" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6698</v>
       </c>
       <c r="G470" t="n">
         <v>0.0795</v>
@@ -47254,7 +47254,7 @@
         <v>0.5353</v>
       </c>
       <c r="M470" t="n">
-        <v>0.3815</v>
+        <v>0.3812</v>
       </c>
     </row>
     <row r="471">
@@ -47267,16 +47267,16 @@
         <v>-0.0165</v>
       </c>
       <c r="C471" t="n">
-        <v>0.727</v>
+        <v>0.7269</v>
       </c>
       <c r="D471" t="n">
-        <v>0.3553</v>
+        <v>0.3552</v>
       </c>
       <c r="E471" t="n">
         <v>-0.0165</v>
       </c>
       <c r="F471" t="n">
-        <v>0.727</v>
+        <v>0.7269</v>
       </c>
       <c r="G471" t="n">
         <v>0.0834</v>
@@ -47297,7 +47297,7 @@
         <v>0.6042999999999999</v>
       </c>
       <c r="M471" t="n">
-        <v>0.3018</v>
+        <v>0.3016</v>
       </c>
     </row>
     <row r="472">
@@ -47313,7 +47313,7 @@
         <v>0.7711</v>
       </c>
       <c r="D472" t="n">
-        <v>0.4224</v>
+        <v>0.4223</v>
       </c>
       <c r="E472" t="n">
         <v>0.0736</v>
@@ -47340,7 +47340,7 @@
         <v>0.5993000000000001</v>
       </c>
       <c r="M472" t="n">
-        <v>0.2833</v>
+        <v>0.2831</v>
       </c>
     </row>
     <row r="473">
@@ -47383,7 +47383,7 @@
         <v>0.6619</v>
       </c>
       <c r="M473" t="n">
-        <v>0.4915</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="474">
@@ -47396,16 +47396,16 @@
         <v>0.4418</v>
       </c>
       <c r="C474" t="n">
-        <v>0.9524</v>
+        <v>0.9523</v>
       </c>
       <c r="D474" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="E474" t="n">
         <v>0.4418</v>
       </c>
       <c r="F474" t="n">
-        <v>0.9524</v>
+        <v>0.9523</v>
       </c>
       <c r="G474" t="n">
         <v>0.2241</v>
@@ -47426,7 +47426,7 @@
         <v>0.6924</v>
       </c>
       <c r="M474" t="n">
-        <v>0.4021</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="475">
@@ -47469,7 +47469,7 @@
         <v>0.7369</v>
       </c>
       <c r="M475" t="n">
-        <v>0.3744</v>
+        <v>0.3743</v>
       </c>
     </row>
     <row r="476">
@@ -47485,7 +47485,7 @@
         <v>1.0339</v>
       </c>
       <c r="D476" t="n">
-        <v>0.8325</v>
+        <v>0.8324</v>
       </c>
       <c r="E476" t="n">
         <v>0.631</v>
@@ -47512,7 +47512,7 @@
         <v>0.6837</v>
       </c>
       <c r="M476" t="n">
-        <v>0.3115</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="477">
@@ -47555,7 +47555,7 @@
         <v>0.576</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2779</v>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="478">
@@ -47568,7 +47568,7 @@
         <v>0.7096</v>
       </c>
       <c r="C478" t="n">
-        <v>1.1121</v>
+        <v>1.112</v>
       </c>
       <c r="D478" t="n">
         <v>0.9108000000000001</v>
@@ -47577,7 +47577,7 @@
         <v>0.7096</v>
       </c>
       <c r="F478" t="n">
-        <v>1.1121</v>
+        <v>1.112</v>
       </c>
       <c r="G478" t="n">
         <v>0.52</v>
@@ -47598,7 +47598,7 @@
         <v>0.6835</v>
       </c>
       <c r="M478" t="n">
-        <v>0.2117</v>
+        <v>0.2115</v>
       </c>
     </row>
     <row r="479">
@@ -47611,7 +47611,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="C479" t="n">
-        <v>1.1928</v>
+        <v>1.1927</v>
       </c>
       <c r="D479" t="n">
         <v>0.9797</v>
@@ -47620,7 +47620,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="F479" t="n">
-        <v>1.1928</v>
+        <v>1.1927</v>
       </c>
       <c r="G479" t="n">
         <v>0.6215000000000001</v>
@@ -47641,7 +47641,7 @@
         <v>0.6918</v>
       </c>
       <c r="M479" t="n">
-        <v>0.2567</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="480">
@@ -47684,7 +47684,7 @@
         <v>0.5768</v>
       </c>
       <c r="M480" t="n">
-        <v>0.247</v>
+        <v>0.2468</v>
       </c>
     </row>
     <row r="481">
@@ -47727,7 +47727,7 @@
         <v>0.6427</v>
       </c>
       <c r="M481" t="n">
-        <v>0.2378</v>
+        <v>0.2376</v>
       </c>
     </row>
     <row r="482">
@@ -47743,7 +47743,7 @@
         <v>1.2402</v>
       </c>
       <c r="D482" t="n">
-        <v>1.1183</v>
+        <v>1.1182</v>
       </c>
       <c r="E482" t="n">
         <v>0.9963</v>
@@ -47770,7 +47770,7 @@
         <v>0.6854</v>
       </c>
       <c r="M482" t="n">
-        <v>0.2427</v>
+        <v>0.2425</v>
       </c>
     </row>
     <row r="483">
@@ -47786,7 +47786,7 @@
         <v>1.1602</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0714</v>
+        <v>1.0713</v>
       </c>
       <c r="E483" t="n">
         <v>0.9825</v>
@@ -47813,7 +47813,7 @@
         <v>0.6092</v>
       </c>
       <c r="M483" t="n">
-        <v>0.2265</v>
+        <v>0.2264</v>
       </c>
     </row>
     <row r="484">
@@ -47829,7 +47829,7 @@
         <v>1.143</v>
       </c>
       <c r="D484" t="n">
-        <v>1.0395</v>
+        <v>1.0394</v>
       </c>
       <c r="E484" t="n">
         <v>0.9359</v>
@@ -47856,7 +47856,7 @@
         <v>0.6831</v>
       </c>
       <c r="M484" t="n">
-        <v>0.2396</v>
+        <v>0.2394</v>
       </c>
     </row>
     <row r="485">
@@ -47872,7 +47872,7 @@
         <v>1.0804</v>
       </c>
       <c r="D485" t="n">
-        <v>1.0584</v>
+        <v>1.0583</v>
       </c>
       <c r="E485" t="n">
         <v>1.0363</v>
@@ -47899,7 +47899,7 @@
         <v>0.6611</v>
       </c>
       <c r="M485" t="n">
-        <v>0.2089</v>
+        <v>0.2087</v>
       </c>
     </row>
     <row r="486">
@@ -47912,16 +47912,16 @@
         <v>0.972</v>
       </c>
       <c r="C486" t="n">
-        <v>1.0252</v>
+        <v>1.0251</v>
       </c>
       <c r="D486" t="n">
-        <v>0.9986</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="E486" t="n">
         <v>0.972</v>
       </c>
       <c r="F486" t="n">
-        <v>1.0252</v>
+        <v>1.0251</v>
       </c>
       <c r="G486" t="n">
         <v>1.7935</v>
@@ -47942,7 +47942,7 @@
         <v>0.5438</v>
       </c>
       <c r="M486" t="n">
-        <v>0.337</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="487">
@@ -47955,7 +47955,7 @@
         <v>0.9472</v>
       </c>
       <c r="C487" t="n">
-        <v>0.9631</v>
+        <v>0.963</v>
       </c>
       <c r="D487" t="n">
         <v>0.9550999999999999</v>
@@ -47964,7 +47964,7 @@
         <v>0.9472</v>
       </c>
       <c r="F487" t="n">
-        <v>0.9631</v>
+        <v>0.963</v>
       </c>
       <c r="G487" t="n">
         <v>1.7936</v>
@@ -47985,7 +47985,7 @@
         <v>0.5768</v>
       </c>
       <c r="M487" t="n">
-        <v>0.2595</v>
+        <v>0.2593</v>
       </c>
     </row>
     <row r="488">
@@ -47998,16 +47998,16 @@
         <v>0.9175</v>
       </c>
       <c r="C488" t="n">
-        <v>0.9493</v>
+        <v>0.9492</v>
       </c>
       <c r="D488" t="n">
-        <v>0.9334</v>
+        <v>0.9333</v>
       </c>
       <c r="E488" t="n">
         <v>0.9175</v>
       </c>
       <c r="F488" t="n">
-        <v>0.9493</v>
+        <v>0.9492</v>
       </c>
       <c r="G488" t="n">
         <v>1.7972</v>
@@ -48028,7 +48028,7 @@
         <v>0.5834</v>
       </c>
       <c r="M488" t="n">
-        <v>0.246</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="489">
@@ -48041,16 +48041,16 @@
         <v>0.8638</v>
       </c>
       <c r="C489" t="n">
-        <v>0.9119</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="D489" t="n">
-        <v>0.8879</v>
+        <v>0.8878</v>
       </c>
       <c r="E489" t="n">
         <v>0.8638</v>
       </c>
       <c r="F489" t="n">
-        <v>0.9119</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="G489" t="n">
         <v>1.695</v>
@@ -48071,7 +48071,7 @@
         <v>0.5085</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2653</v>
+        <v>0.2651</v>
       </c>
     </row>
     <row r="490">
@@ -48084,16 +48084,16 @@
         <v>0.8819</v>
       </c>
       <c r="C490" t="n">
-        <v>0.901</v>
+        <v>0.9009</v>
       </c>
       <c r="D490" t="n">
-        <v>0.8915</v>
+        <v>0.8914</v>
       </c>
       <c r="E490" t="n">
         <v>0.8819</v>
       </c>
       <c r="F490" t="n">
-        <v>0.901</v>
+        <v>0.9009</v>
       </c>
       <c r="G490" t="n">
         <v>1.6469</v>
@@ -48114,7 +48114,7 @@
         <v>0.5518</v>
       </c>
       <c r="M490" t="n">
-        <v>0.2424</v>
+        <v>0.2422</v>
       </c>
     </row>
     <row r="491">
@@ -48127,7 +48127,7 @@
         <v>0.8925</v>
       </c>
       <c r="C491" t="n">
-        <v>0.8921</v>
+        <v>0.892</v>
       </c>
       <c r="D491" t="n">
         <v>0.8923</v>
@@ -48136,7 +48136,7 @@
         <v>0.8925</v>
       </c>
       <c r="F491" t="n">
-        <v>0.8921</v>
+        <v>0.892</v>
       </c>
       <c r="G491" t="n">
         <v>1.6023</v>
@@ -48157,7 +48157,7 @@
         <v>0.5944</v>
       </c>
       <c r="M491" t="n">
-        <v>0.2411</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="492">
@@ -48200,7 +48200,7 @@
         <v>0.5242</v>
       </c>
       <c r="M492" t="n">
-        <v>0.3177</v>
+        <v>0.3175</v>
       </c>
     </row>
     <row r="493">
@@ -48213,7 +48213,7 @@
         <v>0.708</v>
       </c>
       <c r="C493" t="n">
-        <v>0.8659</v>
+        <v>0.8658</v>
       </c>
       <c r="D493" t="n">
         <v>0.7869</v>
@@ -48222,7 +48222,7 @@
         <v>0.708</v>
       </c>
       <c r="F493" t="n">
-        <v>0.8659</v>
+        <v>0.8658</v>
       </c>
       <c r="G493" t="n">
         <v>0.2513</v>
@@ -48243,7 +48243,7 @@
         <v>0.5293</v>
       </c>
       <c r="M493" t="n">
-        <v>0.3268</v>
+        <v>0.3266</v>
       </c>
     </row>
     <row r="494">
@@ -48259,7 +48259,7 @@
         <v>0.8914</v>
       </c>
       <c r="D494" t="n">
-        <v>0.9154</v>
+        <v>0.9153</v>
       </c>
       <c r="E494" t="n">
         <v>0.9393</v>
@@ -48286,7 +48286,7 @@
         <v>0.5121</v>
       </c>
       <c r="M494" t="n">
-        <v>0.4541</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="495">
@@ -48302,7 +48302,7 @@
         <v>0.8485</v>
       </c>
       <c r="D495" t="n">
-        <v>0.8789</v>
+        <v>0.8788</v>
       </c>
       <c r="E495" t="n">
         <v>0.9092</v>
@@ -48329,7 +48329,7 @@
         <v>0.5881</v>
       </c>
       <c r="M495" t="n">
-        <v>0.3076</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="496">
@@ -48372,7 +48372,7 @@
         <v>0.5276</v>
       </c>
       <c r="M496" t="n">
-        <v>0.7292</v>
+        <v>0.7291</v>
       </c>
     </row>
     <row r="497">
@@ -48388,7 +48388,7 @@
         <v>0.9328</v>
       </c>
       <c r="D497" t="n">
-        <v>0.8501</v>
+        <v>0.85</v>
       </c>
       <c r="E497" t="n">
         <v>0.7673</v>
@@ -48415,7 +48415,7 @@
         <v>0.5363</v>
       </c>
       <c r="M497" t="n">
-        <v>0.7355</v>
+        <v>0.7353</v>
       </c>
     </row>
     <row r="498">
@@ -48428,7 +48428,7 @@
         <v>0.7913</v>
       </c>
       <c r="C498" t="n">
-        <v>0.9004</v>
+        <v>0.9003</v>
       </c>
       <c r="D498" t="n">
         <v>0.8458</v>
@@ -48437,7 +48437,7 @@
         <v>0.7913</v>
       </c>
       <c r="F498" t="n">
-        <v>0.9004</v>
+        <v>0.9003</v>
       </c>
       <c r="G498" t="n">
         <v>0.3435</v>
@@ -48458,7 +48458,7 @@
         <v>0.5165</v>
       </c>
       <c r="M498" t="n">
-        <v>0.6878</v>
+        <v>0.6877</v>
       </c>
     </row>
     <row r="499">
@@ -48501,7 +48501,7 @@
         <v>0.482</v>
       </c>
       <c r="M499" t="n">
-        <v>0.58</v>
+        <v>0.5799</v>
       </c>
     </row>
     <row r="500">
@@ -48544,7 +48544,7 @@
         <v>0.527</v>
       </c>
       <c r="M500" t="n">
-        <v>0.5958</v>
+        <v>0.5957</v>
       </c>
     </row>
     <row r="501">
@@ -48557,7 +48557,7 @@
         <v>0.6955</v>
       </c>
       <c r="C501" t="n">
-        <v>0.7879</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="D501" t="n">
         <v>0.7417</v>
@@ -48566,7 +48566,7 @@
         <v>0.6955</v>
       </c>
       <c r="F501" t="n">
-        <v>0.7879</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G501" t="n">
         <v>0.1519</v>
@@ -48587,7 +48587,7 @@
         <v>0.4776</v>
       </c>
       <c r="M501" t="n">
-        <v>0.5433</v>
+        <v>0.5431</v>
       </c>
     </row>
     <row r="502">
@@ -48600,7 +48600,7 @@
         <v>0.643</v>
       </c>
       <c r="C502" t="n">
-        <v>0.7441</v>
+        <v>0.744</v>
       </c>
       <c r="D502" t="n">
         <v>0.6935</v>
@@ -48609,7 +48609,7 @@
         <v>0.643</v>
       </c>
       <c r="F502" t="n">
-        <v>0.7441</v>
+        <v>0.744</v>
       </c>
       <c r="G502" t="n">
         <v>0.1525</v>
@@ -48630,7 +48630,7 @@
         <v>0.4746</v>
       </c>
       <c r="M502" t="n">
-        <v>0.4551</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="503">
@@ -48643,7 +48643,7 @@
         <v>0.5857</v>
       </c>
       <c r="C503" t="n">
-        <v>0.7181</v>
+        <v>0.718</v>
       </c>
       <c r="D503" t="n">
         <v>0.6519</v>
@@ -48652,7 +48652,7 @@
         <v>0.5857</v>
       </c>
       <c r="F503" t="n">
-        <v>0.7181</v>
+        <v>0.718</v>
       </c>
       <c r="G503" t="n">
         <v>0.1059</v>
@@ -48673,7 +48673,7 @@
         <v>0.4544</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4316</v>
+        <v>0.4315</v>
       </c>
     </row>
     <row r="504">
@@ -48689,7 +48689,7 @@
         <v>0.6887</v>
       </c>
       <c r="D504" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6294</v>
       </c>
       <c r="E504" t="n">
         <v>0.5702</v>
@@ -48716,7 +48716,7 @@
         <v>0.447</v>
       </c>
       <c r="M504" t="n">
-        <v>0.4217</v>
+        <v>0.4216</v>
       </c>
     </row>
     <row r="505">
@@ -48759,7 +48759,7 @@
         <v>0.4075</v>
       </c>
       <c r="M505" t="n">
-        <v>0.3722</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="506">
@@ -48772,7 +48772,7 @@
         <v>0.4877</v>
       </c>
       <c r="C506" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6264</v>
       </c>
       <c r="D506" t="n">
         <v>0.5571</v>
@@ -48781,7 +48781,7 @@
         <v>0.4877</v>
       </c>
       <c r="F506" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6264</v>
       </c>
       <c r="G506" t="n">
         <v>0.2557</v>
@@ -48802,7 +48802,7 @@
         <v>0.4757</v>
       </c>
       <c r="M506" t="n">
-        <v>0.3126</v>
+        <v>0.3124</v>
       </c>
     </row>
     <row r="507">
@@ -48815,7 +48815,7 @@
         <v>0.4588</v>
       </c>
       <c r="C507" t="n">
-        <v>0.5869</v>
+        <v>0.5868</v>
       </c>
       <c r="D507" t="n">
         <v>0.5228</v>
@@ -48824,7 +48824,7 @@
         <v>0.4588</v>
       </c>
       <c r="F507" t="n">
-        <v>0.5869</v>
+        <v>0.5868</v>
       </c>
       <c r="G507" t="n">
         <v>0.2973</v>
@@ -48845,7 +48845,7 @@
         <v>0.401</v>
       </c>
       <c r="M507" t="n">
-        <v>0.3113</v>
+        <v>0.3111</v>
       </c>
     </row>
     <row r="508">
@@ -49017,7 +49017,7 @@
         <v>0.3744</v>
       </c>
       <c r="M511" t="n">
-        <v>0.6289</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="512">
@@ -49060,7 +49060,7 @@
         <v>0.4369</v>
       </c>
       <c r="M512" t="n">
-        <v>0.6415</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="513">
@@ -49331,16 +49331,16 @@
         <v>0.5201</v>
       </c>
       <c r="C519" t="n">
-        <v>0.4575</v>
+        <v>0.4574</v>
       </c>
       <c r="D519" t="n">
-        <v>0.4888</v>
+        <v>0.4887</v>
       </c>
       <c r="E519" t="n">
         <v>0.5201</v>
       </c>
       <c r="F519" t="n">
-        <v>0.4575</v>
+        <v>0.4574</v>
       </c>
       <c r="G519" t="n">
         <v>0.4301</v>
@@ -49361,7 +49361,7 @@
         <v>0.2866</v>
       </c>
       <c r="M519" t="n">
-        <v>0.4397</v>
+        <v>0.4396</v>
       </c>
     </row>
     <row r="520">
@@ -49503,7 +49503,7 @@
         <v>0.435</v>
       </c>
       <c r="C523" t="n">
-        <v>0.4148</v>
+        <v>0.4147</v>
       </c>
       <c r="D523" t="n">
         <v>0.4249</v>
@@ -49512,7 +49512,7 @@
         <v>0.435</v>
       </c>
       <c r="F523" t="n">
-        <v>0.4148</v>
+        <v>0.4147</v>
       </c>
       <c r="G523" t="n">
         <v>0.498</v>
@@ -49533,7 +49533,7 @@
         <v>0.2033</v>
       </c>
       <c r="M523" t="n">
-        <v>0.4554</v>
+        <v>0.4553</v>
       </c>
     </row>
     <row r="524">
@@ -49619,7 +49619,7 @@
         <v>0.1579</v>
       </c>
       <c r="M525" t="n">
-        <v>0.3897</v>
+        <v>0.3896</v>
       </c>
     </row>
     <row r="526">
@@ -49632,7 +49632,7 @@
         <v>0.4107</v>
       </c>
       <c r="C526" t="n">
-        <v>0.304</v>
+        <v>0.3039</v>
       </c>
       <c r="D526" t="n">
         <v>0.3573</v>
@@ -49641,7 +49641,7 @@
         <v>0.4107</v>
       </c>
       <c r="F526" t="n">
-        <v>0.304</v>
+        <v>0.3039</v>
       </c>
       <c r="G526" t="n">
         <v>0.6443</v>
@@ -49705,7 +49705,7 @@
         <v>0.2096</v>
       </c>
       <c r="M527" t="n">
-        <v>0.3638</v>
+        <v>0.3637</v>
       </c>
     </row>
     <row r="528">
@@ -49721,7 +49721,7 @@
         <v>0.2268</v>
       </c>
       <c r="D528" t="n">
-        <v>0.3267</v>
+        <v>0.3266</v>
       </c>
       <c r="E528" t="n">
         <v>0.4265</v>
@@ -49748,7 +49748,7 @@
         <v>0.0638</v>
       </c>
       <c r="M528" t="n">
-        <v>0.3589</v>
+        <v>0.3588</v>
       </c>
     </row>
     <row r="529">
@@ -49761,7 +49761,7 @@
         <v>0.387</v>
       </c>
       <c r="C529" t="n">
-        <v>0.2213</v>
+        <v>0.2212</v>
       </c>
       <c r="D529" t="n">
         <v>0.3041</v>
@@ -49770,7 +49770,7 @@
         <v>0.387</v>
       </c>
       <c r="F529" t="n">
-        <v>0.2213</v>
+        <v>0.2212</v>
       </c>
       <c r="G529" t="n">
         <v>0.6857</v>
@@ -49791,7 +49791,7 @@
         <v>0.1201</v>
       </c>
       <c r="M529" t="n">
-        <v>0.3457</v>
+        <v>0.3456</v>
       </c>
     </row>
     <row r="530">
@@ -49804,7 +49804,7 @@
         <v>0.3733</v>
       </c>
       <c r="C530" t="n">
-        <v>0.2245</v>
+        <v>0.2244</v>
       </c>
       <c r="D530" t="n">
         <v>0.2989</v>
@@ -49813,7 +49813,7 @@
         <v>0.3733</v>
       </c>
       <c r="F530" t="n">
-        <v>0.2245</v>
+        <v>0.2244</v>
       </c>
       <c r="G530" t="n">
         <v>0.6844</v>
@@ -49850,7 +49850,7 @@
         <v>0.172</v>
       </c>
       <c r="D531" t="n">
-        <v>0.2708</v>
+        <v>0.2707</v>
       </c>
       <c r="E531" t="n">
         <v>0.3695</v>
@@ -49920,7 +49920,7 @@
         <v>0.0463</v>
       </c>
       <c r="M532" t="n">
-        <v>0.3099</v>
+        <v>0.3098</v>
       </c>
     </row>
     <row r="533">
@@ -49936,7 +49936,7 @@
         <v>0.1016</v>
       </c>
       <c r="D533" t="n">
-        <v>0.2004</v>
+        <v>0.2003</v>
       </c>
       <c r="E533" t="n">
         <v>0.2991</v>
@@ -49963,7 +49963,7 @@
         <v>0.015</v>
       </c>
       <c r="M533" t="n">
-        <v>0.3455</v>
+        <v>0.3454</v>
       </c>
     </row>
     <row r="534">
@@ -50062,7 +50062,7 @@
         <v>0.3331</v>
       </c>
       <c r="C536" t="n">
-        <v>0.0231</v>
+        <v>0.023</v>
       </c>
       <c r="D536" t="n">
         <v>0.1781</v>
@@ -50071,7 +50071,7 @@
         <v>0.3331</v>
       </c>
       <c r="F536" t="n">
-        <v>0.0231</v>
+        <v>0.023</v>
       </c>
       <c r="G536" t="n">
         <v>0.6886</v>
@@ -50092,7 +50092,7 @@
         <v>-0.008399999999999999</v>
       </c>
       <c r="M536" t="n">
-        <v>0.2554</v>
+        <v>0.2553</v>
       </c>
     </row>
     <row r="537">
@@ -50135,7 +50135,7 @@
         <v>-0.0519</v>
       </c>
       <c r="M537" t="n">
-        <v>0.1859</v>
+        <v>0.1858</v>
       </c>
     </row>
     <row r="538">
@@ -50178,7 +50178,7 @@
         <v>-0.0247</v>
       </c>
       <c r="M538" t="n">
-        <v>0.1654</v>
+        <v>0.1653</v>
       </c>
     </row>
     <row r="539">
@@ -50194,7 +50194,7 @@
         <v>-0.0592</v>
       </c>
       <c r="D539" t="n">
-        <v>0.1251</v>
+        <v>0.125</v>
       </c>
       <c r="E539" t="n">
         <v>0.3093</v>
@@ -50264,7 +50264,7 @@
         <v>-0.0309</v>
       </c>
       <c r="M540" t="n">
-        <v>0.039</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="541">
@@ -50608,7 +50608,7 @@
         <v>-0.5876</v>
       </c>
       <c r="M548" t="n">
-        <v>-0.0607</v>
+        <v>-0.0606</v>
       </c>
     </row>
     <row r="549">
@@ -50823,7 +50823,7 @@
         <v>-0.8757</v>
       </c>
       <c r="M553" t="n">
-        <v>-0.2014</v>
+        <v>-0.2013</v>
       </c>
     </row>
     <row r="554">
@@ -51339,7 +51339,7 @@
         <v>0.3191</v>
       </c>
       <c r="M565" t="n">
-        <v>-0.1464</v>
+        <v>-0.1465</v>
       </c>
     </row>
     <row r="566">
@@ -51640,7 +51640,7 @@
         <v>0.4803</v>
       </c>
       <c r="M572" t="n">
-        <v>0.0854</v>
+        <v>0.0853</v>
       </c>
     </row>
     <row r="573">
@@ -51769,7 +51769,7 @@
         <v>0.472</v>
       </c>
       <c r="M575" t="n">
-        <v>0.021</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="576">
@@ -52027,7 +52027,7 @@
         <v>0.5796</v>
       </c>
       <c r="M581" t="n">
-        <v>-0.151</v>
+        <v>-0.1511</v>
       </c>
     </row>
     <row r="582">
@@ -52040,7 +52040,7 @@
         <v>0.4616</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0428</v>
+        <v>0.0427</v>
       </c>
       <c r="D582" t="n">
         <v>0.2522</v>
@@ -52049,7 +52049,7 @@
         <v>0.4616</v>
       </c>
       <c r="F582" t="n">
-        <v>0.0428</v>
+        <v>0.0427</v>
       </c>
       <c r="G582" t="n">
         <v>1.2718</v>
@@ -52070,7 +52070,7 @@
         <v>0.6644</v>
       </c>
       <c r="M582" t="n">
-        <v>-0.1775</v>
+        <v>-0.1776</v>
       </c>
     </row>
     <row r="583">
@@ -52083,16 +52083,16 @@
         <v>0.5224</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.0398</v>
+        <v>-0.0399</v>
       </c>
       <c r="D583" t="n">
-        <v>0.2413</v>
+        <v>0.2412</v>
       </c>
       <c r="E583" t="n">
         <v>0.5224</v>
       </c>
       <c r="F583" t="n">
-        <v>-0.0398</v>
+        <v>-0.0399</v>
       </c>
       <c r="G583" t="n">
         <v>1.3266</v>
@@ -52113,7 +52113,7 @@
         <v>0.6334</v>
       </c>
       <c r="M583" t="n">
-        <v>-0.3353</v>
+        <v>-0.3354</v>
       </c>
     </row>
     <row r="584">
@@ -52126,7 +52126,7 @@
         <v>0.5332</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.0711</v>
+        <v>-0.0712</v>
       </c>
       <c r="D584" t="n">
         <v>0.231</v>
@@ -52135,7 +52135,7 @@
         <v>0.5332</v>
       </c>
       <c r="F584" t="n">
-        <v>-0.0711</v>
+        <v>-0.0712</v>
       </c>
       <c r="G584" t="n">
         <v>1.4156</v>
@@ -52156,7 +52156,7 @@
         <v>0.6971000000000001</v>
       </c>
       <c r="M584" t="n">
-        <v>-0.4688</v>
+        <v>-0.4689</v>
       </c>
     </row>
     <row r="585">
@@ -52169,7 +52169,7 @@
         <v>0.5154</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.1246</v>
+        <v>-0.1247</v>
       </c>
       <c r="D585" t="n">
         <v>0.1954</v>
@@ -52178,7 +52178,7 @@
         <v>0.5154</v>
       </c>
       <c r="F585" t="n">
-        <v>-0.1246</v>
+        <v>-0.1247</v>
       </c>
       <c r="G585" t="n">
         <v>1.5593</v>
@@ -52199,7 +52199,7 @@
         <v>0.5825</v>
       </c>
       <c r="M585" t="n">
-        <v>-0.4882</v>
+        <v>-0.4883</v>
       </c>
     </row>
     <row r="586">
@@ -52212,16 +52212,16 @@
         <v>0.5686</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.193</v>
+        <v>-0.1931</v>
       </c>
       <c r="D586" t="n">
-        <v>0.1878</v>
+        <v>0.1877</v>
       </c>
       <c r="E586" t="n">
         <v>0.5686</v>
       </c>
       <c r="F586" t="n">
-        <v>-0.193</v>
+        <v>-0.1931</v>
       </c>
       <c r="G586" t="n">
         <v>1.7537</v>
@@ -52242,7 +52242,7 @@
         <v>0.6581</v>
       </c>
       <c r="M586" t="n">
-        <v>-0.7427</v>
+        <v>-0.7429</v>
       </c>
     </row>
     <row r="587">
@@ -52255,7 +52255,7 @@
         <v>0.6454</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.2766</v>
+        <v>-0.2767</v>
       </c>
       <c r="D587" t="n">
         <v>0.1844</v>
@@ -52264,7 +52264,7 @@
         <v>0.6454</v>
       </c>
       <c r="F587" t="n">
-        <v>-0.2766</v>
+        <v>-0.2767</v>
       </c>
       <c r="G587" t="n">
         <v>1.9347</v>
@@ -52285,7 +52285,7 @@
         <v>0.53</v>
       </c>
       <c r="M587" t="n">
-        <v>-0.8622</v>
+        <v>-0.8624000000000001</v>
       </c>
     </row>
     <row r="588">
@@ -52298,16 +52298,16 @@
         <v>0.6425</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.316</v>
+        <v>-0.3161</v>
       </c>
       <c r="D588" t="n">
-        <v>0.1633</v>
+        <v>0.1632</v>
       </c>
       <c r="E588" t="n">
         <v>0.6425</v>
       </c>
       <c r="F588" t="n">
-        <v>-0.316</v>
+        <v>-0.3161</v>
       </c>
       <c r="G588" t="n">
         <v>2.0245</v>
@@ -52328,7 +52328,7 @@
         <v>0.5521</v>
       </c>
       <c r="M588" t="n">
-        <v>-0.9628</v>
+        <v>-0.963</v>
       </c>
     </row>
     <row r="589">
@@ -52371,7 +52371,7 @@
         <v>0.5172</v>
       </c>
       <c r="M589" t="n">
-        <v>-1.0471</v>
+        <v>-1.0473</v>
       </c>
     </row>
     <row r="590">
@@ -52387,7 +52387,7 @@
         <v>-0.4211</v>
       </c>
       <c r="D590" t="n">
-        <v>0.1379</v>
+        <v>0.1378</v>
       </c>
       <c r="E590" t="n">
         <v>0.6968</v>
@@ -52414,7 +52414,7 @@
         <v>0.4088</v>
       </c>
       <c r="M590" t="n">
-        <v>-1.077</v>
+        <v>-1.0771</v>
       </c>
     </row>
     <row r="591">
@@ -52457,7 +52457,7 @@
         <v>0.5151</v>
       </c>
       <c r="M591" t="n">
-        <v>-1.0618</v>
+        <v>-1.062</v>
       </c>
     </row>
     <row r="592">
@@ -52470,7 +52470,7 @@
         <v>0.5706</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.4315</v>
+        <v>-0.4316</v>
       </c>
       <c r="D592" t="n">
         <v>0.06950000000000001</v>
@@ -52479,7 +52479,7 @@
         <v>0.5706</v>
       </c>
       <c r="F592" t="n">
-        <v>-0.4315</v>
+        <v>-0.4316</v>
       </c>
       <c r="G592" t="n">
         <v>1.7695</v>
@@ -52500,7 +52500,7 @@
         <v>0.4581</v>
       </c>
       <c r="M592" t="n">
-        <v>-1.1678</v>
+        <v>-1.168</v>
       </c>
     </row>
     <row r="593">
@@ -52513,7 +52513,7 @@
         <v>0.6061</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.4141</v>
+        <v>-0.4142</v>
       </c>
       <c r="D593" t="n">
         <v>0.096</v>
@@ -52522,7 +52522,7 @@
         <v>0.6061</v>
       </c>
       <c r="F593" t="n">
-        <v>-0.4141</v>
+        <v>-0.4142</v>
       </c>
       <c r="G593" t="n">
         <v>1.8545</v>
@@ -52543,7 +52543,7 @@
         <v>0.5243</v>
       </c>
       <c r="M593" t="n">
-        <v>-1.1504</v>
+        <v>-1.1505</v>
       </c>
     </row>
     <row r="594">
@@ -52556,7 +52556,7 @@
         <v>0.6222</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.4023</v>
+        <v>-0.4024</v>
       </c>
       <c r="D594" t="n">
         <v>0.1099</v>
@@ -52565,7 +52565,7 @@
         <v>0.6222</v>
       </c>
       <c r="F594" t="n">
-        <v>-0.4023</v>
+        <v>-0.4024</v>
       </c>
       <c r="G594" t="n">
         <v>1.7717</v>
@@ -52586,7 +52586,7 @@
         <v>0.4907</v>
       </c>
       <c r="M594" t="n">
-        <v>-1.051</v>
+        <v>-1.0511</v>
       </c>
     </row>
     <row r="595">
@@ -52629,7 +52629,7 @@
         <v>0.4905</v>
       </c>
       <c r="M595" t="n">
-        <v>-0.8452</v>
+        <v>-0.8453000000000001</v>
       </c>
     </row>
     <row r="596">
@@ -52672,7 +52672,7 @@
         <v>0.5352</v>
       </c>
       <c r="M596" t="n">
-        <v>-0.7733</v>
+        <v>-0.7734</v>
       </c>
     </row>
     <row r="597">
@@ -52685,16 +52685,16 @@
         <v>0.7348</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.3372</v>
+        <v>-0.3373</v>
       </c>
       <c r="D597" t="n">
-        <v>0.1988</v>
+        <v>0.1987</v>
       </c>
       <c r="E597" t="n">
         <v>0.7348</v>
       </c>
       <c r="F597" t="n">
-        <v>-0.3372</v>
+        <v>-0.3373</v>
       </c>
       <c r="G597" t="n">
         <v>1.7533</v>
@@ -52715,7 +52715,7 @@
         <v>0.446</v>
       </c>
       <c r="M597" t="n">
-        <v>-0.8025</v>
+        <v>-0.8026</v>
       </c>
     </row>
     <row r="598">
@@ -52801,7 +52801,7 @@
         <v>0.5211</v>
       </c>
       <c r="M599" t="n">
-        <v>-0.5648</v>
+        <v>-0.5649</v>
       </c>
     </row>
     <row r="600">
@@ -52817,7 +52817,7 @@
         <v>-0.2807</v>
       </c>
       <c r="D600" t="n">
-        <v>0.219</v>
+        <v>0.2189</v>
       </c>
       <c r="E600" t="n">
         <v>0.7186</v>
@@ -52844,7 +52844,7 @@
         <v>0.53</v>
       </c>
       <c r="M600" t="n">
-        <v>-0.7247</v>
+        <v>-0.7248</v>
       </c>
     </row>
     <row r="601">
@@ -52857,7 +52857,7 @@
         <v>0.6663</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.2475</v>
+        <v>-0.2476</v>
       </c>
       <c r="D601" t="n">
         <v>0.2094</v>
@@ -52866,7 +52866,7 @@
         <v>0.6663</v>
       </c>
       <c r="F601" t="n">
-        <v>-0.2475</v>
+        <v>-0.2476</v>
       </c>
       <c r="G601" t="n">
         <v>1.5079</v>
@@ -52887,7 +52887,7 @@
         <v>0.4839</v>
       </c>
       <c r="M601" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.5702</v>
       </c>
     </row>
     <row r="602">
@@ -52930,7 +52930,7 @@
         <v>0.4856</v>
       </c>
       <c r="M602" t="n">
-        <v>-0.5103</v>
+        <v>-0.5104</v>
       </c>
     </row>
     <row r="603">
@@ -52973,7 +52973,7 @@
         <v>0.4768</v>
       </c>
       <c r="M603" t="n">
-        <v>-0.4966</v>
+        <v>-0.4967</v>
       </c>
     </row>
     <row r="604">
@@ -53016,7 +53016,7 @@
         <v>0.4481</v>
       </c>
       <c r="M604" t="n">
-        <v>-0.3384</v>
+        <v>-0.3385</v>
       </c>
     </row>
     <row r="605">
@@ -53029,7 +53029,7 @@
         <v>0.5775</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.1467</v>
+        <v>-0.1468</v>
       </c>
       <c r="D605" t="n">
         <v>0.2154</v>
@@ -53038,7 +53038,7 @@
         <v>0.5775</v>
       </c>
       <c r="F605" t="n">
-        <v>-0.1467</v>
+        <v>-0.1468</v>
       </c>
       <c r="G605" t="n">
         <v>1.2533</v>
@@ -53059,7 +53059,7 @@
         <v>0.4817</v>
       </c>
       <c r="M605" t="n">
-        <v>-0.3085</v>
+        <v>-0.3086</v>
       </c>
     </row>
     <row r="606">
@@ -53075,7 +53075,7 @@
         <v>-0.1349</v>
       </c>
       <c r="D606" t="n">
-        <v>0.2455</v>
+        <v>0.2454</v>
       </c>
       <c r="E606" t="n">
         <v>0.6258</v>
@@ -53102,7 +53102,7 @@
         <v>0.4796</v>
       </c>
       <c r="M606" t="n">
-        <v>-0.2807</v>
+        <v>-0.2808</v>
       </c>
     </row>
     <row r="607">
@@ -53115,7 +53115,7 @@
         <v>0.6503</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.1256</v>
+        <v>-0.1257</v>
       </c>
       <c r="D607" t="n">
         <v>0.2623</v>
@@ -53124,7 +53124,7 @@
         <v>0.6503</v>
       </c>
       <c r="F607" t="n">
-        <v>-0.1256</v>
+        <v>-0.1257</v>
       </c>
       <c r="G607" t="n">
         <v>1.4515</v>
@@ -53145,7 +53145,7 @@
         <v>0.4832</v>
       </c>
       <c r="M607" t="n">
-        <v>-0.2574</v>
+        <v>-0.2575</v>
       </c>
     </row>
     <row r="608">
@@ -53188,7 +53188,7 @@
         <v>0.4692</v>
       </c>
       <c r="M608" t="n">
-        <v>-0.2919</v>
+        <v>-0.2921</v>
       </c>
     </row>
     <row r="609">
@@ -53201,7 +53201,7 @@
         <v>0.588</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.1827</v>
+        <v>-0.1828</v>
       </c>
       <c r="D609" t="n">
         <v>0.2026</v>
@@ -53210,7 +53210,7 @@
         <v>0.588</v>
       </c>
       <c r="F609" t="n">
-        <v>-0.1827</v>
+        <v>-0.1828</v>
       </c>
       <c r="G609" t="n">
         <v>1.4808</v>
@@ -53231,7 +53231,7 @@
         <v>0.4727</v>
       </c>
       <c r="M609" t="n">
-        <v>-0.3668</v>
+        <v>-0.3669</v>
       </c>
     </row>
     <row r="610">
@@ -53274,7 +53274,7 @@
         <v>0.4763</v>
       </c>
       <c r="M610" t="n">
-        <v>-0.2781</v>
+        <v>-0.2783</v>
       </c>
     </row>
     <row r="611">
@@ -53287,7 +53287,7 @@
         <v>0.5273</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.1745</v>
+        <v>-0.1746</v>
       </c>
       <c r="D611" t="n">
         <v>0.1764</v>
@@ -53296,7 +53296,7 @@
         <v>0.5273</v>
       </c>
       <c r="F611" t="n">
-        <v>-0.1745</v>
+        <v>-0.1746</v>
       </c>
       <c r="G611" t="n">
         <v>1.2023</v>
@@ -53317,7 +53317,7 @@
         <v>0.46</v>
       </c>
       <c r="M611" t="n">
-        <v>-0.2439</v>
+        <v>-0.2441</v>
       </c>
     </row>
     <row r="612">
@@ -53330,7 +53330,7 @@
         <v>0.5775</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.1589</v>
+        <v>-0.159</v>
       </c>
       <c r="D612" t="n">
         <v>0.2093</v>
@@ -53339,7 +53339,7 @@
         <v>0.5775</v>
       </c>
       <c r="F612" t="n">
-        <v>-0.1589</v>
+        <v>-0.159</v>
       </c>
       <c r="G612" t="n">
         <v>1.3456</v>
@@ -53360,7 +53360,7 @@
         <v>0.4621</v>
       </c>
       <c r="M612" t="n">
-        <v>-0.1987</v>
+        <v>-0.1989</v>
       </c>
     </row>
     <row r="613">
@@ -53373,7 +53373,7 @@
         <v>0.5858</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.1638</v>
+        <v>-0.1639</v>
       </c>
       <c r="D613" t="n">
         <v>0.211</v>
@@ -53382,7 +53382,7 @@
         <v>0.5858</v>
       </c>
       <c r="F613" t="n">
-        <v>-0.1638</v>
+        <v>-0.1639</v>
       </c>
       <c r="G613" t="n">
         <v>1.4019</v>
@@ -53403,7 +53403,7 @@
         <v>0.3813</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1054</v>
+        <v>-0.1055</v>
       </c>
     </row>
     <row r="614">
@@ -53416,7 +53416,7 @@
         <v>0.6245000000000001</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.1478</v>
+        <v>-0.1479</v>
       </c>
       <c r="D614" t="n">
         <v>0.2383</v>
@@ -53425,7 +53425,7 @@
         <v>0.6245000000000001</v>
       </c>
       <c r="F614" t="n">
-        <v>-0.1478</v>
+        <v>-0.1479</v>
       </c>
       <c r="G614" t="n">
         <v>1.5712</v>
@@ -53446,7 +53446,7 @@
         <v>0.3886</v>
       </c>
       <c r="M614" t="n">
-        <v>-0.0404</v>
+        <v>-0.0405</v>
       </c>
     </row>
     <row r="615">
@@ -53459,7 +53459,7 @@
         <v>0.5548</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.1428</v>
+        <v>-0.1429</v>
       </c>
       <c r="D615" t="n">
         <v>0.206</v>
@@ -53468,7 +53468,7 @@
         <v>0.5548</v>
       </c>
       <c r="F615" t="n">
-        <v>-0.1428</v>
+        <v>-0.1429</v>
       </c>
       <c r="G615" t="n">
         <v>1.4183</v>
@@ -53489,7 +53489,7 @@
         <v>0.3955</v>
       </c>
       <c r="M615" t="n">
-        <v>0.0135</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="616">
@@ -53532,7 +53532,7 @@
         <v>0.3747</v>
       </c>
       <c r="M616" t="n">
-        <v>0.0598</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="617">
@@ -53545,16 +53545,16 @@
         <v>0.5437</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.1866</v>
+        <v>-0.1867</v>
       </c>
       <c r="D617" t="n">
-        <v>0.1786</v>
+        <v>0.1785</v>
       </c>
       <c r="E617" t="n">
         <v>0.5437</v>
       </c>
       <c r="F617" t="n">
-        <v>-0.1866</v>
+        <v>-0.1867</v>
       </c>
       <c r="G617" t="n">
         <v>1.6838</v>
@@ -53575,7 +53575,7 @@
         <v>0.4236</v>
       </c>
       <c r="M617" t="n">
-        <v>-0.1103</v>
+        <v>-0.1105</v>
       </c>
     </row>
     <row r="618">
@@ -53588,7 +53588,7 @@
         <v>0.5743</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.1973</v>
+        <v>-0.1974</v>
       </c>
       <c r="D618" t="n">
         <v>0.1885</v>
@@ -53597,7 +53597,7 @@
         <v>0.5743</v>
       </c>
       <c r="F618" t="n">
-        <v>-0.1973</v>
+        <v>-0.1974</v>
       </c>
       <c r="G618" t="n">
         <v>1.716</v>
@@ -53618,7 +53618,7 @@
         <v>0.4167</v>
       </c>
       <c r="M618" t="n">
-        <v>-0.1077</v>
+        <v>-0.1079</v>
       </c>
     </row>
     <row r="619">
@@ -53631,7 +53631,7 @@
         <v>0.5309</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.2198</v>
+        <v>-0.2199</v>
       </c>
       <c r="D619" t="n">
         <v>0.1555</v>
@@ -53640,7 +53640,7 @@
         <v>0.5309</v>
       </c>
       <c r="F619" t="n">
-        <v>-0.2198</v>
+        <v>-0.2199</v>
       </c>
       <c r="G619" t="n">
         <v>1.5796</v>
@@ -53661,7 +53661,7 @@
         <v>0.368</v>
       </c>
       <c r="M619" t="n">
-        <v>-0.1043</v>
+        <v>-0.1045</v>
       </c>
     </row>
     <row r="620">
@@ -53674,7 +53674,7 @@
         <v>0.5077</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.2287</v>
+        <v>-0.2288</v>
       </c>
       <c r="D620" t="n">
         <v>0.1395</v>
@@ -53683,7 +53683,7 @@
         <v>0.5077</v>
       </c>
       <c r="F620" t="n">
-        <v>-0.2287</v>
+        <v>-0.2288</v>
       </c>
       <c r="G620" t="n">
         <v>1.4321</v>
@@ -53704,7 +53704,7 @@
         <v>0.3876</v>
       </c>
       <c r="M620" t="n">
-        <v>-0.1295</v>
+        <v>-0.1297</v>
       </c>
     </row>
     <row r="621">
@@ -53717,16 +53717,16 @@
         <v>0.4811</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.2412</v>
+        <v>-0.2413</v>
       </c>
       <c r="D621" t="n">
-        <v>0.12</v>
+        <v>0.1199</v>
       </c>
       <c r="E621" t="n">
         <v>0.4811</v>
       </c>
       <c r="F621" t="n">
-        <v>-0.2412</v>
+        <v>-0.2413</v>
       </c>
       <c r="G621" t="n">
         <v>1.2465</v>
@@ -53747,7 +53747,7 @@
         <v>0.4084</v>
       </c>
       <c r="M621" t="n">
-        <v>-0.1078</v>
+        <v>-0.1081</v>
       </c>
     </row>
     <row r="622">
@@ -53760,7 +53760,7 @@
         <v>0.4718</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.2332</v>
+        <v>-0.2333</v>
       </c>
       <c r="D622" t="n">
         <v>0.1193</v>
@@ -53769,7 +53769,7 @@
         <v>0.4718</v>
       </c>
       <c r="F622" t="n">
-        <v>-0.2332</v>
+        <v>-0.2333</v>
       </c>
       <c r="G622" t="n">
         <v>1.3679</v>
@@ -53790,7 +53790,7 @@
         <v>0.4615</v>
       </c>
       <c r="M622" t="n">
-        <v>-0.1138</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="623">
@@ -53803,7 +53803,7 @@
         <v>0.5182</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.268</v>
+        <v>-0.2681</v>
       </c>
       <c r="D623" t="n">
         <v>0.1251</v>
@@ -53812,7 +53812,7 @@
         <v>0.5182</v>
       </c>
       <c r="F623" t="n">
-        <v>-0.268</v>
+        <v>-0.2681</v>
       </c>
       <c r="G623" t="n">
         <v>1.3975</v>
@@ -53833,7 +53833,7 @@
         <v>0.3639</v>
       </c>
       <c r="M623" t="n">
-        <v>-0.0905</v>
+        <v>-0.09080000000000001</v>
       </c>
     </row>
     <row r="624">
@@ -53849,7 +53849,7 @@
         <v>-0.2474</v>
       </c>
       <c r="D624" t="n">
-        <v>0.1476</v>
+        <v>0.1475</v>
       </c>
       <c r="E624" t="n">
         <v>0.5425</v>
@@ -53876,7 +53876,7 @@
         <v>0.449</v>
       </c>
       <c r="M624" t="n">
-        <v>-0.063</v>
+        <v>-0.0633</v>
       </c>
     </row>
     <row r="625">
@@ -53889,16 +53889,16 @@
         <v>0.229</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.2769</v>
+        <v>-0.277</v>
       </c>
       <c r="D625" t="n">
-        <v>-0.0239</v>
+        <v>-0.024</v>
       </c>
       <c r="E625" t="n">
         <v>0.229</v>
       </c>
       <c r="F625" t="n">
-        <v>-0.2769</v>
+        <v>-0.277</v>
       </c>
       <c r="G625" t="n">
         <v>0.1551</v>
@@ -53919,7 +53919,7 @@
         <v>0.381</v>
       </c>
       <c r="M625" t="n">
-        <v>-0.0738</v>
+        <v>-0.074</v>
       </c>
     </row>
     <row r="626">
@@ -53962,7 +53962,7 @@
         <v>0.4364</v>
       </c>
       <c r="M626" t="n">
-        <v>-0.0443</v>
+        <v>-0.0445</v>
       </c>
     </row>
     <row r="627">
@@ -53978,7 +53978,7 @@
         <v>-0.3068</v>
       </c>
       <c r="D627" t="n">
-        <v>0.0379</v>
+        <v>0.0378</v>
       </c>
       <c r="E627" t="n">
         <v>0.3825</v>
@@ -54005,7 +54005,7 @@
         <v>0.3646</v>
       </c>
       <c r="M627" t="n">
-        <v>-0.0648</v>
+        <v>-0.065</v>
       </c>
     </row>
     <row r="628">
@@ -54021,7 +54021,7 @@
         <v>-0.2767</v>
       </c>
       <c r="D628" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0743</v>
       </c>
       <c r="E628" t="n">
         <v>0.4254</v>
@@ -54048,7 +54048,7 @@
         <v>0.4399</v>
       </c>
       <c r="M628" t="n">
-        <v>-0.0053</v>
+        <v>-0.0055</v>
       </c>
     </row>
     <row r="629">
@@ -54091,7 +54091,7 @@
         <v>0.3511</v>
       </c>
       <c r="M629" t="n">
-        <v>0.0655</v>
+        <v>0.0653</v>
       </c>
     </row>
     <row r="630">
@@ -54134,7 +54134,7 @@
         <v>0.46</v>
       </c>
       <c r="M630" t="n">
-        <v>-0.0065</v>
+        <v>-0.0067</v>
       </c>
     </row>
     <row r="631">
@@ -54147,7 +54147,7 @@
         <v>0.3879</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.2029</v>
+        <v>-0.203</v>
       </c>
       <c r="D631" t="n">
         <v>0.0925</v>
@@ -54156,7 +54156,7 @@
         <v>0.3879</v>
       </c>
       <c r="F631" t="n">
-        <v>-0.2029</v>
+        <v>-0.203</v>
       </c>
       <c r="G631" t="n">
         <v>0.5188</v>
@@ -54177,7 +54177,7 @@
         <v>0.4838</v>
       </c>
       <c r="M631" t="n">
-        <v>0.2678</v>
+        <v>0.2676</v>
       </c>
     </row>
     <row r="632">
@@ -54193,7 +54193,7 @@
         <v>-0.2079</v>
       </c>
       <c r="D632" t="n">
-        <v>0.107</v>
+        <v>0.1069</v>
       </c>
       <c r="E632" t="n">
         <v>0.4218</v>
@@ -54220,7 +54220,7 @@
         <v>0.4472</v>
       </c>
       <c r="M632" t="n">
-        <v>0.2817</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="633">
@@ -54263,7 +54263,7 @@
         <v>0.4328</v>
       </c>
       <c r="M633" t="n">
-        <v>0.3712</v>
+        <v>0.3711</v>
       </c>
     </row>
     <row r="634">
@@ -54276,16 +54276,16 @@
         <v>0.4028</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1668</v>
+        <v>-0.1559</v>
       </c>
       <c r="D634" t="n">
-        <v>0.118</v>
+        <v>0.1235</v>
       </c>
       <c r="E634" t="n">
         <v>0.4028</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1668</v>
+        <v>-0.1559</v>
       </c>
       <c r="G634" t="n">
         <v>0.5542</v>
@@ -54306,7 +54306,7 @@
         <v>0.419</v>
       </c>
       <c r="M634" t="n">
-        <v>0.4025</v>
+        <v>0.4353</v>
       </c>
     </row>
     <row r="635">
@@ -54319,16 +54319,16 @@
         <v>0.4028</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1618</v>
+        <v>-0.163</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1205</v>
+        <v>0.1199</v>
       </c>
       <c r="E635" t="n">
         <v>0.4028</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1618</v>
+        <v>-0.163</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4175</v>
+        <v>0.4139</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -3156,7 +3156,7 @@
         <v>-1.535</v>
       </c>
       <c r="K207" t="n">
-        <v>-0.677</v>
+        <v>-0.676</v>
       </c>
     </row>
     <row r="208">
@@ -4430,7 +4430,7 @@
         <v>0.174</v>
       </c>
       <c r="K305" t="n">
-        <v>-0.502</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="306">
@@ -8616,7 +8616,7 @@
         <v>0.403</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.163</v>
+        <v>-0.164</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.081</v>
+        <v>10.185</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.052</v>
+        <v>1.055</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="14">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0523</v>
+        <v>1.0547</v>
       </c>
       <c r="H635" t="n">
-        <v>10.0809</v>
+        <v>10.1847</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37404,7 +37404,7 @@
         <v>-1.1932</v>
       </c>
       <c r="C172" t="n">
-        <v>-4.3103</v>
+        <v>-4.3104</v>
       </c>
       <c r="D172" t="n">
         <v>-2.7518</v>
@@ -37413,13 +37413,13 @@
         <v>-1.1932</v>
       </c>
       <c r="F172" t="n">
-        <v>-4.3103</v>
+        <v>-4.3104</v>
       </c>
       <c r="G172" t="n">
         <v>-1.1932</v>
       </c>
       <c r="M172" t="n">
-        <v>-4.3103</v>
+        <v>-4.3104</v>
       </c>
     </row>
     <row r="173">
@@ -37684,7 +37684,7 @@
         <v>-1.258</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.0216</v>
+        <v>-1.0215</v>
       </c>
       <c r="D182" t="n">
         <v>-1.1398</v>
@@ -37693,13 +37693,13 @@
         <v>-1.258</v>
       </c>
       <c r="F182" t="n">
-        <v>-1.0216</v>
+        <v>-1.0215</v>
       </c>
       <c r="G182" t="n">
         <v>-1.258</v>
       </c>
       <c r="M182" t="n">
-        <v>-1.0216</v>
+        <v>-1.0215</v>
       </c>
     </row>
     <row r="183">
@@ -37768,7 +37768,7 @@
         <v>-0.7049</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.8907</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="D185" t="n">
         <v>-0.7978</v>
@@ -37777,13 +37777,13 @@
         <v>-0.7049</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.8907</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="G185" t="n">
         <v>-0.7049</v>
       </c>
       <c r="M185" t="n">
-        <v>-0.8907</v>
+        <v>-0.8905999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -37852,22 +37852,22 @@
         <v>-0.7726</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.4749</v>
+        <v>-0.4748</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.6238</v>
+        <v>-0.6237</v>
       </c>
       <c r="E188" t="n">
         <v>-0.7726</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.4749</v>
+        <v>-0.4748</v>
       </c>
       <c r="G188" t="n">
         <v>-0.7726</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.4749</v>
+        <v>-0.4748</v>
       </c>
     </row>
     <row r="189">
@@ -37908,7 +37908,7 @@
         <v>-0.8621</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3764</v>
+        <v>-0.3763</v>
       </c>
       <c r="D190" t="n">
         <v>-0.6192</v>
@@ -37917,13 +37917,13 @@
         <v>-0.8621</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.3764</v>
+        <v>-0.3763</v>
       </c>
       <c r="G190" t="n">
         <v>-0.8621</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.3764</v>
+        <v>-0.3763</v>
       </c>
     </row>
     <row r="191">
@@ -38524,7 +38524,7 @@
         <v>-1.6605</v>
       </c>
       <c r="C212" t="n">
-        <v>-1.9829</v>
+        <v>-1.9828</v>
       </c>
       <c r="D212" t="n">
         <v>-1.8217</v>
@@ -38533,13 +38533,13 @@
         <v>-1.6605</v>
       </c>
       <c r="F212" t="n">
-        <v>-1.9829</v>
+        <v>-1.9828</v>
       </c>
       <c r="G212" t="n">
         <v>-1.6605</v>
       </c>
       <c r="M212" t="n">
-        <v>-1.9829</v>
+        <v>-1.9828</v>
       </c>
     </row>
     <row r="213">
@@ -38552,7 +38552,7 @@
         <v>-1.6244</v>
       </c>
       <c r="C213" t="n">
-        <v>-1.3171</v>
+        <v>-1.317</v>
       </c>
       <c r="D213" t="n">
         <v>-1.4707</v>
@@ -38561,13 +38561,13 @@
         <v>-1.6244</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.3171</v>
+        <v>-1.317</v>
       </c>
       <c r="G213" t="n">
         <v>-1.6244</v>
       </c>
       <c r="M213" t="n">
-        <v>-1.3171</v>
+        <v>-1.317</v>
       </c>
     </row>
     <row r="214">
@@ -38748,7 +38748,7 @@
         <v>-1.1315</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.0153</v>
+        <v>-0.0152</v>
       </c>
       <c r="D220" t="n">
         <v>-0.5734</v>
@@ -38757,13 +38757,13 @@
         <v>-1.1315</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.0153</v>
+        <v>-0.0152</v>
       </c>
       <c r="G220" t="n">
         <v>-1.1315</v>
       </c>
       <c r="M220" t="n">
-        <v>-0.0153</v>
+        <v>-0.0152</v>
       </c>
     </row>
     <row r="221">
@@ -38779,7 +38779,7 @@
         <v>-0.1359</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.403</v>
+        <v>-0.4029</v>
       </c>
       <c r="E221" t="n">
         <v>-0.67</v>
@@ -38807,7 +38807,7 @@
         <v>-0.1525</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.4384</v>
+        <v>-0.4383</v>
       </c>
       <c r="E222" t="n">
         <v>-0.7242</v>
@@ -38916,7 +38916,7 @@
         <v>-0.501</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
       <c r="D226" t="n">
         <v>-0.2525</v>
@@ -38925,13 +38925,13 @@
         <v>-0.501</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
       <c r="G226" t="n">
         <v>-0.501</v>
       </c>
       <c r="M226" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
     </row>
     <row r="227">
@@ -39003,7 +39003,7 @@
         <v>0.0238</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.4382</v>
+        <v>-0.4381</v>
       </c>
       <c r="E229" t="n">
         <v>-0.9001</v>
@@ -39056,7 +39056,7 @@
         <v>-0.408</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.001</v>
+        <v>-0.0009</v>
       </c>
       <c r="D231" t="n">
         <v>-0.2045</v>
@@ -39065,13 +39065,13 @@
         <v>-0.408</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.001</v>
+        <v>-0.0009</v>
       </c>
       <c r="G231" t="n">
         <v>-0.408</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.001</v>
+        <v>-0.0009</v>
       </c>
     </row>
     <row r="232">
@@ -39171,7 +39171,7 @@
         <v>-0.3824</v>
       </c>
       <c r="D235" t="n">
-        <v>-0.4879</v>
+        <v>-0.4878</v>
       </c>
       <c r="E235" t="n">
         <v>-0.5933</v>
@@ -39364,7 +39364,7 @@
         <v>-0.2555</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.7225</v>
+        <v>-0.7224</v>
       </c>
       <c r="D242" t="n">
         <v>-0.489</v>
@@ -39373,13 +39373,13 @@
         <v>-0.2555</v>
       </c>
       <c r="F242" t="n">
-        <v>-0.7225</v>
+        <v>-0.7224</v>
       </c>
       <c r="G242" t="n">
         <v>-0.2555</v>
       </c>
       <c r="M242" t="n">
-        <v>-0.7225</v>
+        <v>-0.7224</v>
       </c>
     </row>
     <row r="243">
@@ -39392,7 +39392,7 @@
         <v>-0.3314</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.9379</v>
+        <v>-0.9378</v>
       </c>
       <c r="D243" t="n">
         <v>-0.6346000000000001</v>
@@ -39401,13 +39401,13 @@
         <v>-0.3314</v>
       </c>
       <c r="F243" t="n">
-        <v>-0.9379</v>
+        <v>-0.9378</v>
       </c>
       <c r="G243" t="n">
         <v>-0.3314</v>
       </c>
       <c r="M243" t="n">
-        <v>-0.9379</v>
+        <v>-0.9378</v>
       </c>
     </row>
     <row r="244">
@@ -39451,7 +39451,7 @@
         <v>-1.1941</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.776</v>
+        <v>-0.7759</v>
       </c>
       <c r="E245" t="n">
         <v>-0.3578</v>
@@ -39479,7 +39479,7 @@
         <v>-1.0767</v>
       </c>
       <c r="D246" t="n">
-        <v>-0.6624</v>
+        <v>-0.6623</v>
       </c>
       <c r="E246" t="n">
         <v>-0.248</v>
@@ -39504,7 +39504,7 @@
         <v>-0.3561</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.2654</v>
+        <v>-1.2653</v>
       </c>
       <c r="D247" t="n">
         <v>-0.8107</v>
@@ -39513,13 +39513,13 @@
         <v>-0.3561</v>
       </c>
       <c r="F247" t="n">
-        <v>-1.2654</v>
+        <v>-1.2653</v>
       </c>
       <c r="G247" t="n">
         <v>-0.3561</v>
       </c>
       <c r="M247" t="n">
-        <v>-1.2654</v>
+        <v>-1.2653</v>
       </c>
     </row>
     <row r="248">
@@ -39980,7 +39980,7 @@
         <v>0.1091</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.8361</v>
+        <v>-0.836</v>
       </c>
       <c r="D264" t="n">
         <v>-0.3635</v>
@@ -39989,13 +39989,13 @@
         <v>0.1091</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.8361</v>
+        <v>-0.836</v>
       </c>
       <c r="G264" t="n">
         <v>0.1091</v>
       </c>
       <c r="M264" t="n">
-        <v>-0.8361</v>
+        <v>-0.836</v>
       </c>
     </row>
     <row r="265">
@@ -40008,7 +40008,7 @@
         <v>0.2193</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.8708</v>
+        <v>-0.8707</v>
       </c>
       <c r="D265" t="n">
         <v>-0.3257</v>
@@ -40017,13 +40017,13 @@
         <v>0.2193</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.8708</v>
+        <v>-0.8707</v>
       </c>
       <c r="G265" t="n">
         <v>0.2193</v>
       </c>
       <c r="M265" t="n">
-        <v>-0.8708</v>
+        <v>-0.8707</v>
       </c>
     </row>
     <row r="266">
@@ -40036,7 +40036,7 @@
         <v>-0.0429</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.0178</v>
+        <v>-1.0177</v>
       </c>
       <c r="D266" t="n">
         <v>-0.5303</v>
@@ -40045,13 +40045,13 @@
         <v>-0.0429</v>
       </c>
       <c r="F266" t="n">
-        <v>-1.0178</v>
+        <v>-1.0177</v>
       </c>
       <c r="G266" t="n">
         <v>-0.0429</v>
       </c>
       <c r="M266" t="n">
-        <v>-1.0178</v>
+        <v>-1.0177</v>
       </c>
     </row>
     <row r="267">
@@ -40176,7 +40176,7 @@
         <v>0.1087</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.0424</v>
+        <v>-0.0423</v>
       </c>
       <c r="D271" t="n">
         <v>0.0332</v>
@@ -40185,13 +40185,13 @@
         <v>0.1087</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.0424</v>
+        <v>-0.0423</v>
       </c>
       <c r="G271" t="n">
         <v>0.1087</v>
       </c>
       <c r="M271" t="n">
-        <v>-0.0424</v>
+        <v>-0.0423</v>
       </c>
     </row>
     <row r="272">
@@ -40263,7 +40263,7 @@
         <v>0.2268</v>
       </c>
       <c r="D274" t="n">
-        <v>0.1929</v>
+        <v>0.193</v>
       </c>
       <c r="E274" t="n">
         <v>0.1591</v>
@@ -40288,22 +40288,22 @@
         <v>0.1667</v>
       </c>
       <c r="C275" t="n">
-        <v>0.1652</v>
+        <v>0.1653</v>
       </c>
       <c r="D275" t="n">
-        <v>0.1659</v>
+        <v>0.166</v>
       </c>
       <c r="E275" t="n">
         <v>0.1667</v>
       </c>
       <c r="F275" t="n">
-        <v>0.1652</v>
+        <v>0.1653</v>
       </c>
       <c r="G275" t="n">
         <v>0.1667</v>
       </c>
       <c r="M275" t="n">
-        <v>0.1652</v>
+        <v>0.1653</v>
       </c>
     </row>
     <row r="276">
@@ -40344,7 +40344,7 @@
         <v>1.0425</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1519</v>
+        <v>0.152</v>
       </c>
       <c r="D277" t="n">
         <v>0.5972</v>
@@ -40353,13 +40353,13 @@
         <v>1.0425</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1519</v>
+        <v>0.152</v>
       </c>
       <c r="G277" t="n">
         <v>1.0425</v>
       </c>
       <c r="M277" t="n">
-        <v>0.1519</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="278">
@@ -40372,7 +40372,7 @@
         <v>0.3167</v>
       </c>
       <c r="C278" t="n">
-        <v>0.4112</v>
+        <v>0.4113</v>
       </c>
       <c r="D278" t="n">
         <v>0.364</v>
@@ -40381,13 +40381,13 @@
         <v>0.3167</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4112</v>
+        <v>0.4113</v>
       </c>
       <c r="G278" t="n">
         <v>0.3167</v>
       </c>
       <c r="M278" t="n">
-        <v>0.4112</v>
+        <v>0.4113</v>
       </c>
     </row>
     <row r="279">
@@ -40599,7 +40599,7 @@
         <v>-0.0327</v>
       </c>
       <c r="D286" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5591</v>
       </c>
       <c r="E286" t="n">
         <v>1.1508</v>
@@ -40683,7 +40683,7 @@
         <v>-0.1117</v>
       </c>
       <c r="D289" t="n">
-        <v>0.0461</v>
+        <v>0.0462</v>
       </c>
       <c r="E289" t="n">
         <v>0.204</v>
@@ -40764,7 +40764,7 @@
         <v>0.9152</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1417</v>
+        <v>-0.1416</v>
       </c>
       <c r="D292" t="n">
         <v>0.3868</v>
@@ -40773,13 +40773,13 @@
         <v>0.9152</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.1417</v>
+        <v>-0.1416</v>
       </c>
       <c r="G292" t="n">
         <v>0.9152</v>
       </c>
       <c r="M292" t="n">
-        <v>-0.1417</v>
+        <v>-0.1416</v>
       </c>
     </row>
     <row r="293">
@@ -40795,7 +40795,7 @@
         <v>-0.1265</v>
       </c>
       <c r="D293" t="n">
-        <v>0.007</v>
+        <v>0.0071</v>
       </c>
       <c r="E293" t="n">
         <v>0.1406</v>
@@ -40820,7 +40820,7 @@
         <v>0.075</v>
       </c>
       <c r="C294" t="n">
-        <v>0.3806</v>
+        <v>0.3807</v>
       </c>
       <c r="D294" t="n">
         <v>0.2278</v>
@@ -40829,13 +40829,13 @@
         <v>0.075</v>
       </c>
       <c r="F294" t="n">
-        <v>0.3806</v>
+        <v>0.3807</v>
       </c>
       <c r="G294" t="n">
         <v>0.075</v>
       </c>
       <c r="M294" t="n">
-        <v>0.3806</v>
+        <v>0.3807</v>
       </c>
     </row>
     <row r="295">
@@ -40848,22 +40848,22 @@
         <v>0.0675</v>
       </c>
       <c r="C295" t="n">
-        <v>0.3801</v>
+        <v>0.3802</v>
       </c>
       <c r="D295" t="n">
-        <v>0.2238</v>
+        <v>0.2239</v>
       </c>
       <c r="E295" t="n">
         <v>0.0675</v>
       </c>
       <c r="F295" t="n">
-        <v>0.3801</v>
+        <v>0.3802</v>
       </c>
       <c r="G295" t="n">
         <v>0.0675</v>
       </c>
       <c r="M295" t="n">
-        <v>0.3801</v>
+        <v>0.3802</v>
       </c>
     </row>
     <row r="296">
@@ -40904,7 +40904,7 @@
         <v>0.0212</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1648</v>
+        <v>0.1649</v>
       </c>
       <c r="D297" t="n">
         <v>0.093</v>
@@ -40913,13 +40913,13 @@
         <v>0.0212</v>
       </c>
       <c r="F297" t="n">
-        <v>0.1648</v>
+        <v>0.1649</v>
       </c>
       <c r="G297" t="n">
         <v>0.0212</v>
       </c>
       <c r="M297" t="n">
-        <v>0.1648</v>
+        <v>0.1649</v>
       </c>
     </row>
     <row r="298">
@@ -40960,7 +40960,7 @@
         <v>-0.037</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.1287</v>
+        <v>-0.1286</v>
       </c>
       <c r="D299" t="n">
         <v>-0.0828</v>
@@ -40969,13 +40969,13 @@
         <v>-0.037</v>
       </c>
       <c r="F299" t="n">
-        <v>-0.1287</v>
+        <v>-0.1286</v>
       </c>
       <c r="G299" t="n">
         <v>-0.037</v>
       </c>
       <c r="M299" t="n">
-        <v>-0.1287</v>
+        <v>-0.1286</v>
       </c>
     </row>
     <row r="300">
@@ -40988,7 +40988,7 @@
         <v>0.0374</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.1957</v>
+        <v>-0.1956</v>
       </c>
       <c r="D300" t="n">
         <v>-0.0791</v>
@@ -40997,13 +40997,13 @@
         <v>0.0374</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.1957</v>
+        <v>-0.1956</v>
       </c>
       <c r="G300" t="n">
         <v>0.0374</v>
       </c>
       <c r="M300" t="n">
-        <v>-0.1957</v>
+        <v>-0.1956</v>
       </c>
     </row>
     <row r="301">
@@ -41016,7 +41016,7 @@
         <v>-0.0268</v>
       </c>
       <c r="C301" t="n">
-        <v>-1.0474</v>
+        <v>-1.0473</v>
       </c>
       <c r="D301" t="n">
         <v>-0.5371</v>
@@ -41025,13 +41025,13 @@
         <v>-0.0268</v>
       </c>
       <c r="F301" t="n">
-        <v>-1.0474</v>
+        <v>-1.0473</v>
       </c>
       <c r="G301" t="n">
         <v>-0.0268</v>
       </c>
       <c r="M301" t="n">
-        <v>-1.0474</v>
+        <v>-1.0473</v>
       </c>
     </row>
     <row r="302">
@@ -41271,7 +41271,7 @@
         <v>-1.124</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.4473</v>
+        <v>-0.4472</v>
       </c>
       <c r="E310" t="n">
         <v>0.2295</v>
@@ -41632,7 +41632,7 @@
         <v>-0.2268</v>
       </c>
       <c r="C323" t="n">
-        <v>0.3027</v>
+        <v>0.3028</v>
       </c>
       <c r="D323" t="n">
         <v>0.038</v>
@@ -41641,13 +41641,13 @@
         <v>-0.2268</v>
       </c>
       <c r="F323" t="n">
-        <v>0.3027</v>
+        <v>0.3028</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2268</v>
       </c>
       <c r="M323" t="n">
-        <v>0.3027</v>
+        <v>0.3028</v>
       </c>
     </row>
     <row r="324">
@@ -41744,7 +41744,7 @@
         <v>-0.2413</v>
       </c>
       <c r="C327" t="n">
-        <v>0.411</v>
+        <v>0.4111</v>
       </c>
       <c r="D327" t="n">
         <v>0.0849</v>
@@ -41753,13 +41753,13 @@
         <v>-0.2413</v>
       </c>
       <c r="F327" t="n">
-        <v>0.411</v>
+        <v>0.4111</v>
       </c>
       <c r="G327" t="n">
         <v>-0.2413</v>
       </c>
       <c r="M327" t="n">
-        <v>0.411</v>
+        <v>0.4111</v>
       </c>
     </row>
     <row r="328">
@@ -41828,7 +41828,7 @@
         <v>-0.2161</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1386</v>
+        <v>-0.1385</v>
       </c>
       <c r="D330" t="n">
         <v>-0.1773</v>
@@ -41837,13 +41837,13 @@
         <v>-0.2161</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1386</v>
+        <v>-0.1385</v>
       </c>
       <c r="G330" t="n">
         <v>-0.2161</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1386</v>
+        <v>-0.1385</v>
       </c>
     </row>
     <row r="331">
@@ -41968,7 +41968,7 @@
         <v>-0.0738</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2628</v>
+        <v>-0.2627</v>
       </c>
       <c r="D335" t="n">
         <v>-0.1683</v>
@@ -41977,13 +41977,13 @@
         <v>-0.0738</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2628</v>
+        <v>-0.2627</v>
       </c>
       <c r="G335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2628</v>
+        <v>-0.2627</v>
       </c>
     </row>
     <row r="336">
@@ -41996,7 +41996,7 @@
         <v>-0.1217</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.2051</v>
+        <v>-0.205</v>
       </c>
       <c r="D336" t="n">
         <v>-0.1634</v>
@@ -42005,13 +42005,13 @@
         <v>-0.1217</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.2051</v>
+        <v>-0.205</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1217</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.2051</v>
+        <v>-0.205</v>
       </c>
     </row>
     <row r="337">
@@ -42027,7 +42027,7 @@
         <v>-0.2844</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.2281</v>
+        <v>-0.228</v>
       </c>
       <c r="E337" t="n">
         <v>-0.1717</v>
@@ -42108,7 +42108,7 @@
         <v>-0.0757</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0514</v>
+        <v>0.0515</v>
       </c>
       <c r="D340" t="n">
         <v>-0.0121</v>
@@ -42117,13 +42117,13 @@
         <v>-0.0757</v>
       </c>
       <c r="F340" t="n">
-        <v>0.0514</v>
+        <v>0.0515</v>
       </c>
       <c r="G340" t="n">
         <v>-0.0757</v>
       </c>
       <c r="M340" t="n">
-        <v>0.0514</v>
+        <v>0.0515</v>
       </c>
     </row>
     <row r="341">
@@ -42164,7 +42164,7 @@
         <v>-0.1213</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="D342" t="n">
         <v>0.052</v>
@@ -42173,13 +42173,13 @@
         <v>-0.1213</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1213</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
     </row>
     <row r="343">
@@ -42220,7 +42220,7 @@
         <v>-0.1226</v>
       </c>
       <c r="C344" t="n">
-        <v>0.5607</v>
+        <v>0.5608</v>
       </c>
       <c r="D344" t="n">
         <v>0.2191</v>
@@ -42229,13 +42229,13 @@
         <v>-0.1226</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5607</v>
+        <v>0.5608</v>
       </c>
       <c r="G344" t="n">
         <v>-0.1226</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5607</v>
+        <v>0.5608</v>
       </c>
     </row>
     <row r="345">
@@ -42248,7 +42248,7 @@
         <v>-0.1663</v>
       </c>
       <c r="C345" t="n">
-        <v>0.4448</v>
+        <v>0.4449</v>
       </c>
       <c r="D345" t="n">
         <v>0.1393</v>
@@ -42257,13 +42257,13 @@
         <v>-0.1663</v>
       </c>
       <c r="F345" t="n">
-        <v>0.4448</v>
+        <v>0.4449</v>
       </c>
       <c r="G345" t="n">
         <v>-0.1663</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4448</v>
+        <v>0.4449</v>
       </c>
     </row>
     <row r="346">
@@ -42276,7 +42276,7 @@
         <v>-0.1668</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5243</v>
+        <v>0.5244</v>
       </c>
       <c r="D346" t="n">
         <v>0.1788</v>
@@ -42285,13 +42285,13 @@
         <v>-0.1668</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5243</v>
+        <v>0.5244</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1668</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5243</v>
+        <v>0.5244</v>
       </c>
     </row>
     <row r="347">
@@ -42307,7 +42307,7 @@
         <v>0.3508</v>
       </c>
       <c r="D347" t="n">
-        <v>0.0919</v>
+        <v>0.092</v>
       </c>
       <c r="E347" t="n">
         <v>-0.1669</v>
@@ -42360,7 +42360,7 @@
         <v>-0.0725</v>
       </c>
       <c r="C349" t="n">
-        <v>0.5083</v>
+        <v>0.5084</v>
       </c>
       <c r="D349" t="n">
         <v>0.2179</v>
@@ -42369,13 +42369,13 @@
         <v>-0.0725</v>
       </c>
       <c r="F349" t="n">
-        <v>0.5083</v>
+        <v>0.5084</v>
       </c>
       <c r="G349" t="n">
         <v>-0.0725</v>
       </c>
       <c r="M349" t="n">
-        <v>0.5083</v>
+        <v>0.5084</v>
       </c>
     </row>
     <row r="350">
@@ -42391,7 +42391,7 @@
         <v>0.8065</v>
       </c>
       <c r="D350" t="n">
-        <v>0.3419</v>
+        <v>0.342</v>
       </c>
       <c r="E350" t="n">
         <v>-0.1226</v>
@@ -42419,7 +42419,7 @@
         <v>0.9327</v>
       </c>
       <c r="D351" t="n">
-        <v>0.4284</v>
+        <v>0.4285</v>
       </c>
       <c r="E351" t="n">
         <v>-0.07580000000000001</v>
@@ -42584,7 +42584,7 @@
         <v>0.214</v>
       </c>
       <c r="C357" t="n">
-        <v>0.1631</v>
+        <v>0.1632</v>
       </c>
       <c r="D357" t="n">
         <v>0.1886</v>
@@ -42593,13 +42593,13 @@
         <v>0.214</v>
       </c>
       <c r="F357" t="n">
-        <v>0.1631</v>
+        <v>0.1632</v>
       </c>
       <c r="G357" t="n">
         <v>0.214</v>
       </c>
       <c r="M357" t="n">
-        <v>0.1631</v>
+        <v>0.1632</v>
       </c>
     </row>
     <row r="358">
@@ -42612,7 +42612,7 @@
         <v>0.2085</v>
       </c>
       <c r="C358" t="n">
-        <v>0.2658</v>
+        <v>0.2659</v>
       </c>
       <c r="D358" t="n">
         <v>0.2372</v>
@@ -42621,13 +42621,13 @@
         <v>0.2085</v>
       </c>
       <c r="F358" t="n">
-        <v>0.2658</v>
+        <v>0.2659</v>
       </c>
       <c r="G358" t="n">
         <v>0.2085</v>
       </c>
       <c r="M358" t="n">
-        <v>0.2658</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="359">
@@ -42786,7 +42786,7 @@
         <v>-0.4839</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.0678</v>
+        <v>-0.0677</v>
       </c>
       <c r="D364" t="n">
         <v>-0.2758</v>
@@ -42795,7 +42795,7 @@
         <v>-0.4839</v>
       </c>
       <c r="F364" t="n">
-        <v>-0.0678</v>
+        <v>-0.0677</v>
       </c>
       <c r="G364" t="n">
         <v>0.2143</v>
@@ -42804,7 +42804,7 @@
         <v>-1.1821</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.0678</v>
+        <v>-0.0677</v>
       </c>
     </row>
     <row r="365">
@@ -42817,16 +42817,16 @@
         <v>-0.5301</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.2146</v>
+        <v>-0.2145</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.3724</v>
+        <v>-0.3723</v>
       </c>
       <c r="E365" t="n">
         <v>-0.5301</v>
       </c>
       <c r="F365" t="n">
-        <v>-0.2146</v>
+        <v>-0.2145</v>
       </c>
       <c r="G365" t="n">
         <v>0.1656</v>
@@ -42835,7 +42835,7 @@
         <v>-1.2258</v>
       </c>
       <c r="M365" t="n">
-        <v>-0.2146</v>
+        <v>-0.2145</v>
       </c>
     </row>
     <row r="366">
@@ -42848,7 +42848,7 @@
         <v>-0.445</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.2353</v>
+        <v>-0.2352</v>
       </c>
       <c r="D366" t="n">
         <v>-0.3401</v>
@@ -42857,7 +42857,7 @@
         <v>-0.445</v>
       </c>
       <c r="F366" t="n">
-        <v>-0.2353</v>
+        <v>-0.2352</v>
       </c>
       <c r="G366" t="n">
         <v>0.117</v>
@@ -42866,7 +42866,7 @@
         <v>-1.0071</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.2353</v>
+        <v>-0.2352</v>
       </c>
     </row>
     <row r="367">
@@ -42975,7 +42975,7 @@
         <v>-0.3748</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.3908</v>
+        <v>-0.3907</v>
       </c>
       <c r="E370" t="n">
         <v>-0.4067</v>
@@ -43126,7 +43126,7 @@
         <v>1.051</v>
       </c>
       <c r="M374" t="n">
-        <v>0.8186</v>
+        <v>0.8187</v>
       </c>
     </row>
     <row r="375">
@@ -43384,7 +43384,7 @@
         <v>0.5988</v>
       </c>
       <c r="M380" t="n">
-        <v>0.7578</v>
+        <v>0.7579</v>
       </c>
     </row>
     <row r="381">
@@ -43569,7 +43569,7 @@
         <v>-0.3657</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.2071</v>
+        <v>-0.207</v>
       </c>
       <c r="D385" t="n">
         <v>-0.2864</v>
@@ -43578,7 +43578,7 @@
         <v>-0.3657</v>
       </c>
       <c r="F385" t="n">
-        <v>-0.2071</v>
+        <v>-0.207</v>
       </c>
       <c r="G385" t="n">
         <v>0.1989</v>
@@ -43827,7 +43827,7 @@
         <v>-0.8995</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.622</v>
+        <v>-0.6219</v>
       </c>
       <c r="D391" t="n">
         <v>-0.7607</v>
@@ -43836,7 +43836,7 @@
         <v>-0.8995</v>
       </c>
       <c r="F391" t="n">
-        <v>-0.622</v>
+        <v>-0.6219</v>
       </c>
       <c r="G391" t="n">
         <v>0.2407</v>
@@ -44389,7 +44389,7 @@
         <v>-0.7622</v>
       </c>
       <c r="D404" t="n">
-        <v>-0.597</v>
+        <v>-0.5969</v>
       </c>
       <c r="E404" t="n">
         <v>-0.4317</v>
@@ -44674,7 +44674,7 @@
         <v>-2.128</v>
       </c>
       <c r="M410" t="n">
-        <v>-0.3737</v>
+        <v>-0.3736</v>
       </c>
     </row>
     <row r="411">
@@ -44717,7 +44717,7 @@
         <v>-2.2831</v>
       </c>
       <c r="M411" t="n">
-        <v>-0.367</v>
+        <v>-0.3669</v>
       </c>
     </row>
     <row r="412">
@@ -44760,7 +44760,7 @@
         <v>-2.3123</v>
       </c>
       <c r="M412" t="n">
-        <v>-0.6061</v>
+        <v>-0.606</v>
       </c>
     </row>
     <row r="413">
@@ -44846,7 +44846,7 @@
         <v>-2.4996</v>
       </c>
       <c r="M414" t="n">
-        <v>-0.485</v>
+        <v>-0.4849</v>
       </c>
     </row>
     <row r="415">
@@ -44932,7 +44932,7 @@
         <v>-2.7787</v>
       </c>
       <c r="M416" t="n">
-        <v>-0.6716</v>
+        <v>-0.6715</v>
       </c>
     </row>
     <row r="417">
@@ -45276,7 +45276,7 @@
         <v>-1.4944</v>
       </c>
       <c r="M424" t="n">
-        <v>0.1362</v>
+        <v>0.1363</v>
       </c>
     </row>
     <row r="425">
@@ -45749,7 +45749,7 @@
         <v>-0.0399</v>
       </c>
       <c r="M435" t="n">
-        <v>0.4079</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="436">
@@ -45792,7 +45792,7 @@
         <v>0.0902</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4157</v>
+        <v>0.4158</v>
       </c>
     </row>
     <row r="437">
@@ -47138,7 +47138,7 @@
         <v>-0.349</v>
       </c>
       <c r="C468" t="n">
-        <v>0.5624</v>
+        <v>0.5625</v>
       </c>
       <c r="D468" t="n">
         <v>0.1067</v>
@@ -47147,7 +47147,7 @@
         <v>-0.349</v>
       </c>
       <c r="F468" t="n">
-        <v>0.5624</v>
+        <v>0.5625</v>
       </c>
       <c r="G468" t="n">
         <v>0.2234</v>
@@ -47267,7 +47267,7 @@
         <v>-0.0165</v>
       </c>
       <c r="C471" t="n">
-        <v>0.7269</v>
+        <v>0.727</v>
       </c>
       <c r="D471" t="n">
         <v>0.3552</v>
@@ -47276,7 +47276,7 @@
         <v>-0.0165</v>
       </c>
       <c r="F471" t="n">
-        <v>0.7269</v>
+        <v>0.727</v>
       </c>
       <c r="G471" t="n">
         <v>0.0834</v>
@@ -47786,7 +47786,7 @@
         <v>1.1602</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0713</v>
+        <v>1.0714</v>
       </c>
       <c r="E483" t="n">
         <v>0.9825</v>
@@ -47856,7 +47856,7 @@
         <v>0.6831</v>
       </c>
       <c r="M484" t="n">
-        <v>0.2394</v>
+        <v>0.2395</v>
       </c>
     </row>
     <row r="485">
@@ -47915,7 +47915,7 @@
         <v>1.0251</v>
       </c>
       <c r="D486" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="E486" t="n">
         <v>0.972</v>
@@ -48028,7 +48028,7 @@
         <v>0.5834</v>
       </c>
       <c r="M488" t="n">
-        <v>0.2457</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="489">
@@ -48259,7 +48259,7 @@
         <v>0.8914</v>
       </c>
       <c r="D494" t="n">
-        <v>0.9153</v>
+        <v>0.9154</v>
       </c>
       <c r="E494" t="n">
         <v>0.9393</v>
@@ -48329,7 +48329,7 @@
         <v>0.5881</v>
       </c>
       <c r="M495" t="n">
-        <v>0.3074</v>
+        <v>0.3075</v>
       </c>
     </row>
     <row r="496">
@@ -49334,7 +49334,7 @@
         <v>0.4574</v>
       </c>
       <c r="D519" t="n">
-        <v>0.4887</v>
+        <v>0.4888</v>
       </c>
       <c r="E519" t="n">
         <v>0.5201</v>
@@ -49533,7 +49533,7 @@
         <v>0.2033</v>
       </c>
       <c r="M523" t="n">
-        <v>0.4553</v>
+        <v>0.4554</v>
       </c>
     </row>
     <row r="524">
@@ -49791,7 +49791,7 @@
         <v>0.1201</v>
       </c>
       <c r="M529" t="n">
-        <v>0.3456</v>
+        <v>0.3457</v>
       </c>
     </row>
     <row r="530">
@@ -49963,7 +49963,7 @@
         <v>0.015</v>
       </c>
       <c r="M533" t="n">
-        <v>0.3454</v>
+        <v>0.3455</v>
       </c>
     </row>
     <row r="534">
@@ -51769,7 +51769,7 @@
         <v>0.472</v>
       </c>
       <c r="M575" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="576">
@@ -52070,7 +52070,7 @@
         <v>0.6644</v>
       </c>
       <c r="M582" t="n">
-        <v>-0.1776</v>
+        <v>-0.1775</v>
       </c>
     </row>
     <row r="583">
@@ -52215,7 +52215,7 @@
         <v>-0.1931</v>
       </c>
       <c r="D586" t="n">
-        <v>0.1877</v>
+        <v>0.1878</v>
       </c>
       <c r="E586" t="n">
         <v>0.5686</v>
@@ -52457,7 +52457,7 @@
         <v>0.5151</v>
       </c>
       <c r="M591" t="n">
-        <v>-1.062</v>
+        <v>-1.0619</v>
       </c>
     </row>
     <row r="592">
@@ -52500,7 +52500,7 @@
         <v>0.4581</v>
       </c>
       <c r="M592" t="n">
-        <v>-1.168</v>
+        <v>-1.1679</v>
       </c>
     </row>
     <row r="593">
@@ -52801,7 +52801,7 @@
         <v>0.5211</v>
       </c>
       <c r="M599" t="n">
-        <v>-0.5649</v>
+        <v>-0.5648</v>
       </c>
     </row>
     <row r="600">
@@ -53747,7 +53747,7 @@
         <v>0.4084</v>
       </c>
       <c r="M621" t="n">
-        <v>-0.1081</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="622">
@@ -53978,7 +53978,7 @@
         <v>-0.3068</v>
       </c>
       <c r="D627" t="n">
-        <v>0.0378</v>
+        <v>0.0379</v>
       </c>
       <c r="E627" t="n">
         <v>0.3825</v>
@@ -54319,16 +54319,16 @@
         <v>0.4028</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.163</v>
+        <v>-0.164</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1199</v>
+        <v>0.1194</v>
       </c>
       <c r="E635" t="n">
         <v>0.4028</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.163</v>
+        <v>-0.164</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4139</v>
+        <v>0.4108</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -2519,7 +2519,7 @@
         <v>-1.284</v>
       </c>
       <c r="K158" t="n">
-        <v>-3.206</v>
+        <v>-3.205</v>
       </c>
     </row>
     <row r="159">
@@ -4651,7 +4651,7 @@
         <v>-0.216</v>
       </c>
       <c r="K322" t="n">
-        <v>-0.139</v>
+        <v>-0.138</v>
       </c>
     </row>
     <row r="323">
@@ -8616,7 +8616,7 @@
         <v>0.403</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.164</v>
+        <v>-0.165</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.185</v>
+        <v>10.269</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.055</v>
+        <v>1.057</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="14">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0547</v>
+        <v>1.0572</v>
       </c>
       <c r="H635" t="n">
-        <v>10.1847</v>
+        <v>10.2686</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37740,7 +37740,7 @@
         <v>-1.288</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.9137</v>
       </c>
       <c r="D184" t="n">
         <v>-1.1009</v>
@@ -37749,13 +37749,13 @@
         <v>-1.288</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.9137</v>
       </c>
       <c r="G184" t="n">
         <v>-1.288</v>
       </c>
       <c r="M184" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.9137</v>
       </c>
     </row>
     <row r="185">
@@ -37796,22 +37796,22 @@
         <v>-0.6958</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.7713</v>
+        <v>-0.7712</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.7336</v>
+        <v>-0.7335</v>
       </c>
       <c r="E186" t="n">
         <v>-0.6958</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.7713</v>
+        <v>-0.7712</v>
       </c>
       <c r="G186" t="n">
         <v>-0.6958</v>
       </c>
       <c r="M186" t="n">
-        <v>-0.7713</v>
+        <v>-0.7712</v>
       </c>
     </row>
     <row r="187">
@@ -38104,7 +38104,7 @@
         <v>-2.0781</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.8215</v>
+        <v>-0.8214</v>
       </c>
       <c r="D197" t="n">
         <v>-1.4498</v>
@@ -38113,13 +38113,13 @@
         <v>-2.0781</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.8215</v>
+        <v>-0.8214</v>
       </c>
       <c r="G197" t="n">
         <v>-2.0781</v>
       </c>
       <c r="M197" t="n">
-        <v>-0.8215</v>
+        <v>-0.8214</v>
       </c>
     </row>
     <row r="198">
@@ -38216,7 +38216,7 @@
         <v>-2.239</v>
       </c>
       <c r="C201" t="n">
-        <v>-1.4058</v>
+        <v>-1.4057</v>
       </c>
       <c r="D201" t="n">
         <v>-1.8224</v>
@@ -38225,13 +38225,13 @@
         <v>-2.239</v>
       </c>
       <c r="F201" t="n">
-        <v>-1.4058</v>
+        <v>-1.4057</v>
       </c>
       <c r="G201" t="n">
         <v>-2.239</v>
       </c>
       <c r="M201" t="n">
-        <v>-1.4058</v>
+        <v>-1.4057</v>
       </c>
     </row>
     <row r="202">
@@ -38247,7 +38247,7 @@
         <v>-1.4441</v>
       </c>
       <c r="D202" t="n">
-        <v>-1.8849</v>
+        <v>-1.8848</v>
       </c>
       <c r="E202" t="n">
         <v>-2.3256</v>
@@ -38356,7 +38356,7 @@
         <v>-1.7537</v>
       </c>
       <c r="C206" t="n">
-        <v>-2.3622</v>
+        <v>-2.3621</v>
       </c>
       <c r="D206" t="n">
         <v>-2.0579</v>
@@ -38365,13 +38365,13 @@
         <v>-1.7537</v>
       </c>
       <c r="F206" t="n">
-        <v>-2.3622</v>
+        <v>-2.3621</v>
       </c>
       <c r="G206" t="n">
         <v>-1.7537</v>
       </c>
       <c r="M206" t="n">
-        <v>-2.3622</v>
+        <v>-2.3621</v>
       </c>
     </row>
     <row r="207">
@@ -38496,7 +38496,7 @@
         <v>-1.8361</v>
       </c>
       <c r="C211" t="n">
-        <v>-2.0885</v>
+        <v>-2.0884</v>
       </c>
       <c r="D211" t="n">
         <v>-1.9623</v>
@@ -38505,13 +38505,13 @@
         <v>-1.8361</v>
       </c>
       <c r="F211" t="n">
-        <v>-2.0885</v>
+        <v>-2.0884</v>
       </c>
       <c r="G211" t="n">
         <v>-1.8361</v>
       </c>
       <c r="M211" t="n">
-        <v>-2.0885</v>
+        <v>-2.0884</v>
       </c>
     </row>
     <row r="212">
@@ -38804,7 +38804,7 @@
         <v>-0.7242</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.1525</v>
+        <v>-0.1524</v>
       </c>
       <c r="D222" t="n">
         <v>-0.4383</v>
@@ -38813,13 +38813,13 @@
         <v>-0.7242</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.1525</v>
+        <v>-0.1524</v>
       </c>
       <c r="G222" t="n">
         <v>-0.7242</v>
       </c>
       <c r="M222" t="n">
-        <v>-0.1525</v>
+        <v>-0.1524</v>
       </c>
     </row>
     <row r="223">
@@ -38919,7 +38919,7 @@
         <v>-0.0039</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.2525</v>
+        <v>-0.2524</v>
       </c>
       <c r="E226" t="n">
         <v>-0.501</v>
@@ -38972,7 +38972,7 @@
         <v>-0.4445</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0168</v>
+        <v>0.0169</v>
       </c>
       <c r="D228" t="n">
         <v>-0.2138</v>
@@ -38981,13 +38981,13 @@
         <v>-0.4445</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0168</v>
+        <v>0.0169</v>
       </c>
       <c r="G228" t="n">
         <v>-0.4445</v>
       </c>
       <c r="M228" t="n">
-        <v>0.0168</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="229">
@@ -39000,7 +39000,7 @@
         <v>-0.9001</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
       <c r="D229" t="n">
         <v>-0.4381</v>
@@ -39009,13 +39009,13 @@
         <v>-0.9001</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
       <c r="G229" t="n">
         <v>-0.9001</v>
       </c>
       <c r="M229" t="n">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="230">
@@ -39028,7 +39028,7 @@
         <v>-0.6168</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0712</v>
+        <v>0.0713</v>
       </c>
       <c r="D230" t="n">
         <v>-0.2728</v>
@@ -39037,13 +39037,13 @@
         <v>-0.6168</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0712</v>
+        <v>0.0713</v>
       </c>
       <c r="G230" t="n">
         <v>-0.6168</v>
       </c>
       <c r="M230" t="n">
-        <v>0.0712</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="231">
@@ -39084,7 +39084,7 @@
         <v>-0.3909</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.0032</v>
+        <v>-0.0031</v>
       </c>
       <c r="D232" t="n">
         <v>-0.197</v>
@@ -39093,13 +39093,13 @@
         <v>-0.3909</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.0032</v>
+        <v>-0.0031</v>
       </c>
       <c r="G232" t="n">
         <v>-0.3909</v>
       </c>
       <c r="M232" t="n">
-        <v>-0.0032</v>
+        <v>-0.0031</v>
       </c>
     </row>
     <row r="233">
@@ -39140,7 +39140,7 @@
         <v>-0.613</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.3824</v>
+        <v>-0.3823</v>
       </c>
       <c r="D234" t="n">
         <v>-0.4977</v>
@@ -39149,13 +39149,13 @@
         <v>-0.613</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.3824</v>
+        <v>-0.3823</v>
       </c>
       <c r="G234" t="n">
         <v>-0.613</v>
       </c>
       <c r="M234" t="n">
-        <v>-0.3824</v>
+        <v>-0.3823</v>
       </c>
     </row>
     <row r="235">
@@ -39252,7 +39252,7 @@
         <v>-0.4317</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.4036</v>
+        <v>-0.4035</v>
       </c>
       <c r="D238" t="n">
         <v>-0.4176</v>
@@ -39261,13 +39261,13 @@
         <v>-0.4317</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.4036</v>
+        <v>-0.4035</v>
       </c>
       <c r="G238" t="n">
         <v>-0.4317</v>
       </c>
       <c r="M238" t="n">
-        <v>-0.4036</v>
+        <v>-0.4035</v>
       </c>
     </row>
     <row r="239">
@@ -39308,7 +39308,7 @@
         <v>-0.3265</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.4718</v>
+        <v>-0.4717</v>
       </c>
       <c r="D240" t="n">
         <v>-0.3991</v>
@@ -39317,13 +39317,13 @@
         <v>-0.3265</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.4718</v>
+        <v>-0.4717</v>
       </c>
       <c r="G240" t="n">
         <v>-0.3265</v>
       </c>
       <c r="M240" t="n">
-        <v>-0.4718</v>
+        <v>-0.4717</v>
       </c>
     </row>
     <row r="241">
@@ -39420,7 +39420,7 @@
         <v>-0.3512</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.2466</v>
+        <v>-1.2465</v>
       </c>
       <c r="D244" t="n">
         <v>-0.7989000000000001</v>
@@ -39429,13 +39429,13 @@
         <v>-0.3512</v>
       </c>
       <c r="F244" t="n">
-        <v>-1.2466</v>
+        <v>-1.2465</v>
       </c>
       <c r="G244" t="n">
         <v>-0.3512</v>
       </c>
       <c r="M244" t="n">
-        <v>-1.2466</v>
+        <v>-1.2465</v>
       </c>
     </row>
     <row r="245">
@@ -39700,7 +39700,7 @@
         <v>-0.5684</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.7802</v>
+        <v>-0.7801</v>
       </c>
       <c r="D254" t="n">
         <v>-0.6743</v>
@@ -39709,13 +39709,13 @@
         <v>-0.5684</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.7802</v>
+        <v>-0.7801</v>
       </c>
       <c r="G254" t="n">
         <v>-0.5684</v>
       </c>
       <c r="M254" t="n">
-        <v>-0.7802</v>
+        <v>-0.7801</v>
       </c>
     </row>
     <row r="255">
@@ -39756,7 +39756,7 @@
         <v>-0.6097</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.7729</v>
+        <v>-0.7728</v>
       </c>
       <c r="D256" t="n">
         <v>-0.6913</v>
@@ -39765,13 +39765,13 @@
         <v>-0.6097</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.7729</v>
+        <v>-0.7728</v>
       </c>
       <c r="G256" t="n">
         <v>-0.6097</v>
       </c>
       <c r="M256" t="n">
-        <v>-0.7729</v>
+        <v>-0.7728</v>
       </c>
     </row>
     <row r="257">
@@ -39896,7 +39896,7 @@
         <v>-0.2111</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.8455</v>
+        <v>-0.8454</v>
       </c>
       <c r="D261" t="n">
         <v>-0.5283</v>
@@ -39905,13 +39905,13 @@
         <v>-0.2111</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.8455</v>
+        <v>-0.8454</v>
       </c>
       <c r="G261" t="n">
         <v>-0.2111</v>
       </c>
       <c r="M261" t="n">
-        <v>-0.8455</v>
+        <v>-0.8454</v>
       </c>
     </row>
     <row r="262">
@@ -40092,7 +40092,7 @@
         <v>0.0412</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.891</v>
+        <v>-0.8909</v>
       </c>
       <c r="D268" t="n">
         <v>-0.4249</v>
@@ -40101,13 +40101,13 @@
         <v>0.0412</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.891</v>
+        <v>-0.8909</v>
       </c>
       <c r="G268" t="n">
         <v>0.0412</v>
       </c>
       <c r="M268" t="n">
-        <v>-0.891</v>
+        <v>-0.8909</v>
       </c>
     </row>
     <row r="269">
@@ -40120,7 +40120,7 @@
         <v>0.0533</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.4219</v>
+        <v>-0.4218</v>
       </c>
       <c r="D269" t="n">
         <v>-0.1843</v>
@@ -40129,13 +40129,13 @@
         <v>0.0533</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.4219</v>
+        <v>-0.4218</v>
       </c>
       <c r="G269" t="n">
         <v>0.0533</v>
       </c>
       <c r="M269" t="n">
-        <v>-0.4219</v>
+        <v>-0.4218</v>
       </c>
     </row>
     <row r="270">
@@ -40260,7 +40260,7 @@
         <v>0.1591</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2268</v>
+        <v>0.2269</v>
       </c>
       <c r="D274" t="n">
         <v>0.193</v>
@@ -40269,13 +40269,13 @@
         <v>0.1591</v>
       </c>
       <c r="F274" t="n">
-        <v>0.2268</v>
+        <v>0.2269</v>
       </c>
       <c r="G274" t="n">
         <v>0.1591</v>
       </c>
       <c r="M274" t="n">
-        <v>0.2268</v>
+        <v>0.2269</v>
       </c>
     </row>
     <row r="275">
@@ -40316,7 +40316,7 @@
         <v>0.2682</v>
       </c>
       <c r="C276" t="n">
-        <v>0.1686</v>
+        <v>0.1687</v>
       </c>
       <c r="D276" t="n">
         <v>0.2184</v>
@@ -40325,13 +40325,13 @@
         <v>0.2682</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1686</v>
+        <v>0.1687</v>
       </c>
       <c r="G276" t="n">
         <v>0.2682</v>
       </c>
       <c r="M276" t="n">
-        <v>0.1686</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="277">
@@ -40428,7 +40428,7 @@
         <v>0.2953</v>
       </c>
       <c r="C280" t="n">
-        <v>0.5104</v>
+        <v>0.5105</v>
       </c>
       <c r="D280" t="n">
         <v>0.4029</v>
@@ -40437,13 +40437,13 @@
         <v>0.2953</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5104</v>
+        <v>0.5105</v>
       </c>
       <c r="G280" t="n">
         <v>0.2953</v>
       </c>
       <c r="M280" t="n">
-        <v>0.5104</v>
+        <v>0.5105</v>
       </c>
     </row>
     <row r="281">
@@ -40487,7 +40487,7 @@
         <v>-0.0761</v>
       </c>
       <c r="D282" t="n">
-        <v>0.4347</v>
+        <v>0.4348</v>
       </c>
       <c r="E282" t="n">
         <v>0.9456</v>
@@ -40512,7 +40512,7 @@
         <v>0.9067</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.0722</v>
+        <v>-0.0721</v>
       </c>
       <c r="D283" t="n">
         <v>0.4173</v>
@@ -40521,13 +40521,13 @@
         <v>0.9067</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.0722</v>
+        <v>-0.0721</v>
       </c>
       <c r="G283" t="n">
         <v>0.9067</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.0722</v>
+        <v>-0.0721</v>
       </c>
     </row>
     <row r="284">
@@ -40568,7 +40568,7 @@
         <v>1.0579</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.1007</v>
+        <v>-0.1006</v>
       </c>
       <c r="D285" t="n">
         <v>0.4786</v>
@@ -40577,13 +40577,13 @@
         <v>1.0579</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.1007</v>
+        <v>-0.1006</v>
       </c>
       <c r="G285" t="n">
         <v>1.0579</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.1007</v>
+        <v>-0.1006</v>
       </c>
     </row>
     <row r="286">
@@ -40596,7 +40596,7 @@
         <v>1.1508</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.0327</v>
+        <v>-0.0326</v>
       </c>
       <c r="D286" t="n">
         <v>0.5591</v>
@@ -40605,13 +40605,13 @@
         <v>1.1508</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.0327</v>
+        <v>-0.0326</v>
       </c>
       <c r="G286" t="n">
         <v>1.1508</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.0327</v>
+        <v>-0.0326</v>
       </c>
     </row>
     <row r="287">
@@ -40624,7 +40624,7 @@
         <v>1.1549</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.1082</v>
+        <v>-0.1081</v>
       </c>
       <c r="D287" t="n">
         <v>0.5234</v>
@@ -40633,13 +40633,13 @@
         <v>1.1549</v>
       </c>
       <c r="F287" t="n">
-        <v>-0.1082</v>
+        <v>-0.1081</v>
       </c>
       <c r="G287" t="n">
         <v>1.1549</v>
       </c>
       <c r="M287" t="n">
-        <v>-0.1082</v>
+        <v>-0.1081</v>
       </c>
     </row>
     <row r="288">
@@ -40736,7 +40736,7 @@
         <v>0.8964</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.1338</v>
+        <v>-0.1337</v>
       </c>
       <c r="D291" t="n">
         <v>0.3813</v>
@@ -40745,13 +40745,13 @@
         <v>0.8964</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.1338</v>
+        <v>-0.1337</v>
       </c>
       <c r="G291" t="n">
         <v>0.8964</v>
       </c>
       <c r="M291" t="n">
-        <v>-0.1338</v>
+        <v>-0.1337</v>
       </c>
     </row>
     <row r="292">
@@ -40792,7 +40792,7 @@
         <v>0.1406</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.1265</v>
+        <v>-0.1264</v>
       </c>
       <c r="D293" t="n">
         <v>0.0071</v>
@@ -40801,13 +40801,13 @@
         <v>0.1406</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.1265</v>
+        <v>-0.1264</v>
       </c>
       <c r="G293" t="n">
         <v>0.1406</v>
       </c>
       <c r="M293" t="n">
-        <v>-0.1265</v>
+        <v>-0.1264</v>
       </c>
     </row>
     <row r="294">
@@ -40876,7 +40876,7 @@
         <v>0.0155</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1691</v>
+        <v>0.1692</v>
       </c>
       <c r="D296" t="n">
         <v>0.09229999999999999</v>
@@ -40885,13 +40885,13 @@
         <v>0.0155</v>
       </c>
       <c r="F296" t="n">
-        <v>0.1691</v>
+        <v>0.1692</v>
       </c>
       <c r="G296" t="n">
         <v>0.0155</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1691</v>
+        <v>0.1692</v>
       </c>
     </row>
     <row r="297">
@@ -40932,7 +40932,7 @@
         <v>-0.1114</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.1643</v>
+        <v>-0.1642</v>
       </c>
       <c r="D298" t="n">
         <v>-0.1378</v>
@@ -40941,13 +40941,13 @@
         <v>-0.1114</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.1643</v>
+        <v>-0.1642</v>
       </c>
       <c r="G298" t="n">
         <v>-0.1114</v>
       </c>
       <c r="M298" t="n">
-        <v>-0.1643</v>
+        <v>-0.1642</v>
       </c>
     </row>
     <row r="299">
@@ -41296,7 +41296,7 @@
         <v>0.1872</v>
       </c>
       <c r="C311" t="n">
-        <v>-1.0257</v>
+        <v>-1.0256</v>
       </c>
       <c r="D311" t="n">
         <v>-0.4192</v>
@@ -41305,13 +41305,13 @@
         <v>0.1872</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.0257</v>
+        <v>-1.0256</v>
       </c>
       <c r="G311" t="n">
         <v>0.1872</v>
       </c>
       <c r="M311" t="n">
-        <v>-1.0257</v>
+        <v>-1.0256</v>
       </c>
     </row>
     <row r="312">
@@ -41324,7 +41324,7 @@
         <v>0.1347</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.8734</v>
       </c>
       <c r="D312" t="n">
         <v>-0.3694</v>
@@ -41333,13 +41333,13 @@
         <v>0.1347</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.8734</v>
       </c>
       <c r="G312" t="n">
         <v>0.1347</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.8734</v>
       </c>
     </row>
     <row r="313">
@@ -41520,7 +41520,7 @@
         <v>0.1115</v>
       </c>
       <c r="C319" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9038</v>
       </c>
       <c r="D319" t="n">
         <v>0.5076000000000001</v>
@@ -41529,13 +41529,13 @@
         <v>0.1115</v>
       </c>
       <c r="F319" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9038</v>
       </c>
       <c r="G319" t="n">
         <v>0.1115</v>
       </c>
       <c r="M319" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="320">
@@ -41604,7 +41604,7 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="C322" t="n">
-        <v>0.7335</v>
+        <v>0.7336</v>
       </c>
       <c r="D322" t="n">
         <v>0.3231</v>
@@ -41613,13 +41613,13 @@
         <v>-0.08740000000000001</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7335</v>
+        <v>0.7336</v>
       </c>
       <c r="G322" t="n">
         <v>-0.08740000000000001</v>
       </c>
       <c r="M322" t="n">
-        <v>0.7335</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="323">
@@ -41688,7 +41688,7 @@
         <v>-0.1809</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1906</v>
+        <v>0.1907</v>
       </c>
       <c r="D325" t="n">
         <v>0.0049</v>
@@ -41697,13 +41697,13 @@
         <v>-0.1809</v>
       </c>
       <c r="F325" t="n">
-        <v>0.1906</v>
+        <v>0.1907</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1809</v>
       </c>
       <c r="M325" t="n">
-        <v>0.1906</v>
+        <v>0.1907</v>
       </c>
     </row>
     <row r="326">
@@ -41772,7 +41772,7 @@
         <v>-0.2131</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4502</v>
+        <v>0.4503</v>
       </c>
       <c r="D328" t="n">
         <v>0.1186</v>
@@ -41781,13 +41781,13 @@
         <v>-0.2131</v>
       </c>
       <c r="F328" t="n">
-        <v>0.4502</v>
+        <v>0.4503</v>
       </c>
       <c r="G328" t="n">
         <v>-0.2131</v>
       </c>
       <c r="M328" t="n">
-        <v>0.4502</v>
+        <v>0.4503</v>
       </c>
     </row>
     <row r="329">
@@ -41800,7 +41800,7 @@
         <v>-0.1302</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0293</v>
+        <v>0.0294</v>
       </c>
       <c r="D329" t="n">
         <v>-0.0504</v>
@@ -41809,13 +41809,13 @@
         <v>-0.1302</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0293</v>
+        <v>0.0294</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1302</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0293</v>
+        <v>0.0294</v>
       </c>
     </row>
     <row r="330">
@@ -41859,7 +41859,7 @@
         <v>-0.1229</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1455</v>
+        <v>-0.1454</v>
       </c>
       <c r="E331" t="n">
         <v>-0.168</v>
@@ -41884,7 +41884,7 @@
         <v>-0.1711</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.2564</v>
+        <v>-0.2563</v>
       </c>
       <c r="D332" t="n">
         <v>-0.2137</v>
@@ -41893,13 +41893,13 @@
         <v>-0.1711</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2564</v>
+        <v>-0.2563</v>
       </c>
       <c r="G332" t="n">
         <v>-0.1711</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.2564</v>
+        <v>-0.2563</v>
       </c>
     </row>
     <row r="333">
@@ -41940,22 +41940,22 @@
         <v>-0.1202</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.116</v>
+        <v>-0.1159</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.1181</v>
+        <v>-0.118</v>
       </c>
       <c r="E334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.116</v>
+        <v>-0.1159</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1202</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.116</v>
+        <v>-0.1159</v>
       </c>
     </row>
     <row r="335">
@@ -41999,7 +41999,7 @@
         <v>-0.205</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.1634</v>
+        <v>-0.1633</v>
       </c>
       <c r="E336" t="n">
         <v>-0.1217</v>
@@ -42024,7 +42024,7 @@
         <v>-0.1717</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2844</v>
+        <v>-0.2843</v>
       </c>
       <c r="D337" t="n">
         <v>-0.228</v>
@@ -42033,13 +42033,13 @@
         <v>-0.1717</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.2844</v>
+        <v>-0.2843</v>
       </c>
       <c r="G337" t="n">
         <v>-0.1717</v>
       </c>
       <c r="M337" t="n">
-        <v>-0.2844</v>
+        <v>-0.2843</v>
       </c>
     </row>
     <row r="338">
@@ -42052,7 +42052,7 @@
         <v>-0.1245</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2475</v>
+        <v>-0.2474</v>
       </c>
       <c r="D338" t="n">
         <v>-0.186</v>
@@ -42061,13 +42061,13 @@
         <v>-0.1245</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2475</v>
+        <v>-0.2474</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1245</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2475</v>
+        <v>-0.2474</v>
       </c>
     </row>
     <row r="339">
@@ -42080,22 +42080,22 @@
         <v>-0.1237</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2097</v>
+        <v>-0.2096</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.1667</v>
+        <v>-0.1666</v>
       </c>
       <c r="E339" t="n">
         <v>-0.1237</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2097</v>
+        <v>-0.2096</v>
       </c>
       <c r="G339" t="n">
         <v>-0.1237</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2097</v>
+        <v>-0.2096</v>
       </c>
     </row>
     <row r="340">
@@ -42192,7 +42192,7 @@
         <v>-0.1218</v>
       </c>
       <c r="C343" t="n">
-        <v>0.3409</v>
+        <v>0.341</v>
       </c>
       <c r="D343" t="n">
         <v>0.1096</v>
@@ -42201,13 +42201,13 @@
         <v>-0.1218</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3409</v>
+        <v>0.341</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1218</v>
       </c>
       <c r="M343" t="n">
-        <v>0.3409</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="344">
@@ -42304,7 +42304,7 @@
         <v>-0.1669</v>
       </c>
       <c r="C347" t="n">
-        <v>0.3508</v>
+        <v>0.3509</v>
       </c>
       <c r="D347" t="n">
         <v>0.092</v>
@@ -42313,13 +42313,13 @@
         <v>-0.1669</v>
       </c>
       <c r="F347" t="n">
-        <v>0.3508</v>
+        <v>0.3509</v>
       </c>
       <c r="G347" t="n">
         <v>-0.1669</v>
       </c>
       <c r="M347" t="n">
-        <v>0.3508</v>
+        <v>0.3509</v>
       </c>
     </row>
     <row r="348">
@@ -42335,7 +42335,7 @@
         <v>0.5124</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1962</v>
+        <v>0.1963</v>
       </c>
       <c r="E348" t="n">
         <v>-0.1199</v>
@@ -42363,7 +42363,7 @@
         <v>0.5084</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2179</v>
+        <v>0.218</v>
       </c>
       <c r="E349" t="n">
         <v>-0.0725</v>
@@ -42388,7 +42388,7 @@
         <v>-0.1226</v>
       </c>
       <c r="C350" t="n">
-        <v>0.8065</v>
+        <v>0.8066</v>
       </c>
       <c r="D350" t="n">
         <v>0.342</v>
@@ -42397,13 +42397,13 @@
         <v>-0.1226</v>
       </c>
       <c r="F350" t="n">
-        <v>0.8065</v>
+        <v>0.8066</v>
       </c>
       <c r="G350" t="n">
         <v>-0.1226</v>
       </c>
       <c r="M350" t="n">
-        <v>0.8065</v>
+        <v>0.8066</v>
       </c>
     </row>
     <row r="351">
@@ -42500,7 +42500,7 @@
         <v>0.0708</v>
       </c>
       <c r="C354" t="n">
-        <v>1.2553</v>
+        <v>1.2554</v>
       </c>
       <c r="D354" t="n">
         <v>0.6631</v>
@@ -42509,13 +42509,13 @@
         <v>0.0708</v>
       </c>
       <c r="F354" t="n">
-        <v>1.2553</v>
+        <v>1.2554</v>
       </c>
       <c r="G354" t="n">
         <v>0.0708</v>
       </c>
       <c r="M354" t="n">
-        <v>1.2553</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="355">
@@ -42724,7 +42724,7 @@
         <v>-0.5446</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0208</v>
+        <v>0.0209</v>
       </c>
       <c r="D362" t="n">
         <v>-0.2619</v>
@@ -42733,7 +42733,7 @@
         <v>-0.5446</v>
       </c>
       <c r="F362" t="n">
-        <v>0.0208</v>
+        <v>0.0209</v>
       </c>
       <c r="G362" t="n">
         <v>0.2137</v>
@@ -42742,7 +42742,7 @@
         <v>-1.3029</v>
       </c>
       <c r="M362" t="n">
-        <v>0.0208</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="363">
@@ -42755,7 +42755,7 @@
         <v>-0.502</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.2221</v>
+        <v>-0.222</v>
       </c>
       <c r="D363" t="n">
         <v>-0.362</v>
@@ -42764,7 +42764,7 @@
         <v>-0.502</v>
       </c>
       <c r="F363" t="n">
-        <v>-0.2221</v>
+        <v>-0.222</v>
       </c>
       <c r="G363" t="n">
         <v>0.262</v>
@@ -42773,7 +42773,7 @@
         <v>-1.2659</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.2221</v>
+        <v>-0.222</v>
       </c>
     </row>
     <row r="364">
@@ -42944,7 +42944,7 @@
         <v>-0.403</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.4271</v>
+        <v>-0.427</v>
       </c>
       <c r="E369" t="n">
         <v>-0.4511</v>
@@ -42972,7 +42972,7 @@
         <v>-0.4067</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3748</v>
+        <v>-0.3747</v>
       </c>
       <c r="D370" t="n">
         <v>-0.3907</v>
@@ -42981,7 +42981,7 @@
         <v>-0.4067</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3748</v>
+        <v>-0.3747</v>
       </c>
       <c r="G370" t="n">
         <v>0.2599</v>
@@ -42990,7 +42990,7 @@
         <v>-1.0733</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3748</v>
+        <v>-0.3747</v>
       </c>
     </row>
     <row r="371">
@@ -43298,7 +43298,7 @@
         <v>0.7295</v>
       </c>
       <c r="M378" t="n">
-        <v>0.7487</v>
+        <v>0.7488</v>
       </c>
     </row>
     <row r="379">
@@ -43357,7 +43357,7 @@
         <v>0.1267</v>
       </c>
       <c r="D380" t="n">
-        <v>-0.1495</v>
+        <v>-0.1494</v>
       </c>
       <c r="E380" t="n">
         <v>-0.4256</v>
@@ -43486,7 +43486,7 @@
         <v>-0.079</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.2515</v>
+        <v>-0.2514</v>
       </c>
       <c r="E383" t="n">
         <v>-0.4239</v>
@@ -43857,7 +43857,7 @@
         <v>-0.4923</v>
       </c>
       <c r="M391" t="n">
-        <v>0.7089</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="392">
@@ -44690,7 +44690,7 @@
         <v>-1.0753</v>
       </c>
       <c r="D411" t="n">
-        <v>-0.6576</v>
+        <v>-0.6575</v>
       </c>
       <c r="E411" t="n">
         <v>-0.2398</v>
@@ -44859,7 +44859,7 @@
         <v>-0.0443</v>
       </c>
       <c r="C415" t="n">
-        <v>-1.2377</v>
+        <v>-1.2376</v>
       </c>
       <c r="D415" t="n">
         <v>-0.641</v>
@@ -44868,7 +44868,7 @@
         <v>-0.0443</v>
       </c>
       <c r="F415" t="n">
-        <v>-1.2377</v>
+        <v>-1.2376</v>
       </c>
       <c r="G415" t="n">
         <v>0.8522999999999999</v>
@@ -44988,7 +44988,7 @@
         <v>-0.006</v>
       </c>
       <c r="C418" t="n">
-        <v>-1.3342</v>
+        <v>-1.3341</v>
       </c>
       <c r="D418" t="n">
         <v>-0.6701</v>
@@ -44997,7 +44997,7 @@
         <v>-0.006</v>
       </c>
       <c r="F418" t="n">
-        <v>-1.3342</v>
+        <v>-1.3341</v>
       </c>
       <c r="G418" t="n">
         <v>1.0705</v>
@@ -45018,7 +45018,7 @@
         <v>-2.9316</v>
       </c>
       <c r="M418" t="n">
-        <v>-0.6682</v>
+        <v>-0.6681</v>
       </c>
     </row>
     <row r="419">
@@ -45504,7 +45504,7 @@
         <v>-0.6762</v>
       </c>
       <c r="C430" t="n">
-        <v>0.0634</v>
+        <v>0.0635</v>
       </c>
       <c r="D430" t="n">
         <v>-0.3064</v>
@@ -45513,7 +45513,7 @@
         <v>-0.6762</v>
       </c>
       <c r="F430" t="n">
-        <v>0.0634</v>
+        <v>0.0635</v>
       </c>
       <c r="G430" t="n">
         <v>-0.8811</v>
@@ -45577,7 +45577,7 @@
         <v>-0.2436</v>
       </c>
       <c r="M431" t="n">
-        <v>0.5651</v>
+        <v>0.5652</v>
       </c>
     </row>
     <row r="432">
@@ -45633,7 +45633,7 @@
         <v>-0.6488</v>
       </c>
       <c r="C433" t="n">
-        <v>0.1188</v>
+        <v>0.1189</v>
       </c>
       <c r="D433" t="n">
         <v>-0.265</v>
@@ -45642,7 +45642,7 @@
         <v>-0.6488</v>
       </c>
       <c r="F433" t="n">
-        <v>0.1188</v>
+        <v>0.1189</v>
       </c>
       <c r="G433" t="n">
         <v>-0.4118</v>
@@ -46278,7 +46278,7 @@
         <v>-0.4018</v>
       </c>
       <c r="C448" t="n">
-        <v>0.2412</v>
+        <v>0.2413</v>
       </c>
       <c r="D448" t="n">
         <v>-0.0803</v>
@@ -46287,7 +46287,7 @@
         <v>-0.4018</v>
       </c>
       <c r="F448" t="n">
-        <v>0.2412</v>
+        <v>0.2413</v>
       </c>
       <c r="G448" t="n">
         <v>-0.0823</v>
@@ -46450,7 +46450,7 @@
         <v>-0.3027</v>
       </c>
       <c r="C452" t="n">
-        <v>0.2794</v>
+        <v>0.2795</v>
       </c>
       <c r="D452" t="n">
         <v>-0.0116</v>
@@ -46459,7 +46459,7 @@
         <v>-0.3027</v>
       </c>
       <c r="F452" t="n">
-        <v>0.2794</v>
+        <v>0.2795</v>
       </c>
       <c r="G452" t="n">
         <v>0.2703</v>
@@ -46480,7 +46480,7 @@
         <v>0.1773</v>
       </c>
       <c r="M452" t="n">
-        <v>0.185</v>
+        <v>0.1851</v>
       </c>
     </row>
     <row r="453">
@@ -46523,7 +46523,7 @@
         <v>0.1417</v>
       </c>
       <c r="M453" t="n">
-        <v>0.1962</v>
+        <v>0.1963</v>
       </c>
     </row>
     <row r="454">
@@ -46867,7 +46867,7 @@
         <v>0.3755</v>
       </c>
       <c r="M461" t="n">
-        <v>0.3926</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="462">
@@ -47082,7 +47082,7 @@
         <v>0.4637</v>
       </c>
       <c r="M466" t="n">
-        <v>0.323</v>
+        <v>0.3231</v>
       </c>
     </row>
     <row r="467">
@@ -47125,7 +47125,7 @@
         <v>0.4398</v>
       </c>
       <c r="M467" t="n">
-        <v>0.3786</v>
+        <v>0.3787</v>
       </c>
     </row>
     <row r="468">
@@ -47254,7 +47254,7 @@
         <v>0.5353</v>
       </c>
       <c r="M470" t="n">
-        <v>0.3812</v>
+        <v>0.3813</v>
       </c>
     </row>
     <row r="471">
@@ -47512,7 +47512,7 @@
         <v>0.6837</v>
       </c>
       <c r="M476" t="n">
-        <v>0.3113</v>
+        <v>0.3114</v>
       </c>
     </row>
     <row r="477">
@@ -47743,7 +47743,7 @@
         <v>1.2402</v>
       </c>
       <c r="D482" t="n">
-        <v>1.1182</v>
+        <v>1.1183</v>
       </c>
       <c r="E482" t="n">
         <v>0.9963</v>
@@ -47899,7 +47899,7 @@
         <v>0.6611</v>
       </c>
       <c r="M485" t="n">
-        <v>0.2087</v>
+        <v>0.2088</v>
       </c>
     </row>
     <row r="486">
@@ -47942,7 +47942,7 @@
         <v>0.5438</v>
       </c>
       <c r="M486" t="n">
-        <v>0.3368</v>
+        <v>0.3369</v>
       </c>
     </row>
     <row r="487">
@@ -48071,7 +48071,7 @@
         <v>0.5085</v>
       </c>
       <c r="M489" t="n">
-        <v>0.2651</v>
+        <v>0.2652</v>
       </c>
     </row>
     <row r="490">
@@ -48127,7 +48127,7 @@
         <v>0.8925</v>
       </c>
       <c r="C491" t="n">
-        <v>0.892</v>
+        <v>0.8921</v>
       </c>
       <c r="D491" t="n">
         <v>0.8923</v>
@@ -48136,7 +48136,7 @@
         <v>0.8925</v>
       </c>
       <c r="F491" t="n">
-        <v>0.892</v>
+        <v>0.8921</v>
       </c>
       <c r="G491" t="n">
         <v>1.6023</v>
@@ -48243,7 +48243,7 @@
         <v>0.5293</v>
       </c>
       <c r="M493" t="n">
-        <v>0.3266</v>
+        <v>0.3267</v>
       </c>
     </row>
     <row r="494">
@@ -48415,7 +48415,7 @@
         <v>0.5363</v>
       </c>
       <c r="M497" t="n">
-        <v>0.7353</v>
+        <v>0.7354000000000001</v>
       </c>
     </row>
     <row r="498">
@@ -48557,7 +48557,7 @@
         <v>0.6955</v>
       </c>
       <c r="C501" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7879</v>
       </c>
       <c r="D501" t="n">
         <v>0.7417</v>
@@ -48566,7 +48566,7 @@
         <v>0.6955</v>
       </c>
       <c r="F501" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7879</v>
       </c>
       <c r="G501" t="n">
         <v>0.1519</v>
@@ -48587,7 +48587,7 @@
         <v>0.4776</v>
       </c>
       <c r="M501" t="n">
-        <v>0.5431</v>
+        <v>0.5432</v>
       </c>
     </row>
     <row r="502">
@@ -48802,7 +48802,7 @@
         <v>0.4757</v>
       </c>
       <c r="M506" t="n">
-        <v>0.3124</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="507">
@@ -49189,7 +49189,7 @@
         <v>0.2755</v>
       </c>
       <c r="M515" t="n">
-        <v>0.5434</v>
+        <v>0.5435</v>
       </c>
     </row>
     <row r="516">
@@ -49804,7 +49804,7 @@
         <v>0.3733</v>
       </c>
       <c r="C530" t="n">
-        <v>0.2244</v>
+        <v>0.2245</v>
       </c>
       <c r="D530" t="n">
         <v>0.2989</v>
@@ -49813,7 +49813,7 @@
         <v>0.3733</v>
       </c>
       <c r="F530" t="n">
-        <v>0.2244</v>
+        <v>0.2245</v>
       </c>
       <c r="G530" t="n">
         <v>0.6844</v>
@@ -50062,7 +50062,7 @@
         <v>0.3331</v>
       </c>
       <c r="C536" t="n">
-        <v>0.023</v>
+        <v>0.0231</v>
       </c>
       <c r="D536" t="n">
         <v>0.1781</v>
@@ -50071,7 +50071,7 @@
         <v>0.3331</v>
       </c>
       <c r="F536" t="n">
-        <v>0.023</v>
+        <v>0.0231</v>
       </c>
       <c r="G536" t="n">
         <v>0.6886</v>
@@ -50194,7 +50194,7 @@
         <v>-0.0592</v>
       </c>
       <c r="D539" t="n">
-        <v>0.125</v>
+        <v>0.1251</v>
       </c>
       <c r="E539" t="n">
         <v>0.3093</v>
@@ -50565,7 +50565,7 @@
         <v>-0.4584</v>
       </c>
       <c r="M547" t="n">
-        <v>-0.0482</v>
+        <v>-0.0481</v>
       </c>
     </row>
     <row r="548">
@@ -51339,7 +51339,7 @@
         <v>0.3191</v>
       </c>
       <c r="M565" t="n">
-        <v>-0.1465</v>
+        <v>-0.1464</v>
       </c>
     </row>
     <row r="566">
@@ -51871,7 +51871,7 @@
         <v>0.1485</v>
       </c>
       <c r="D578" t="n">
-        <v>0.1886</v>
+        <v>0.1887</v>
       </c>
       <c r="E578" t="n">
         <v>0.2288</v>
@@ -52169,7 +52169,7 @@
         <v>0.5154</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.1247</v>
+        <v>-0.1246</v>
       </c>
       <c r="D585" t="n">
         <v>0.1954</v>
@@ -52178,7 +52178,7 @@
         <v>0.5154</v>
       </c>
       <c r="F585" t="n">
-        <v>-0.1247</v>
+        <v>-0.1246</v>
       </c>
       <c r="G585" t="n">
         <v>1.5593</v>
@@ -52298,7 +52298,7 @@
         <v>0.6425</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.3161</v>
+        <v>-0.316</v>
       </c>
       <c r="D588" t="n">
         <v>0.1632</v>
@@ -52307,7 +52307,7 @@
         <v>0.6425</v>
       </c>
       <c r="F588" t="n">
-        <v>-0.3161</v>
+        <v>-0.316</v>
       </c>
       <c r="G588" t="n">
         <v>2.0245</v>
@@ -52371,7 +52371,7 @@
         <v>0.5172</v>
       </c>
       <c r="M589" t="n">
-        <v>-1.0473</v>
+        <v>-1.0472</v>
       </c>
     </row>
     <row r="590">
@@ -52513,7 +52513,7 @@
         <v>0.6061</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.4142</v>
+        <v>-0.4141</v>
       </c>
       <c r="D593" t="n">
         <v>0.096</v>
@@ -52522,7 +52522,7 @@
         <v>0.6061</v>
       </c>
       <c r="F593" t="n">
-        <v>-0.4142</v>
+        <v>-0.4141</v>
       </c>
       <c r="G593" t="n">
         <v>1.8545</v>
@@ -52629,7 +52629,7 @@
         <v>0.4905</v>
       </c>
       <c r="M595" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.8452</v>
       </c>
     </row>
     <row r="596">
@@ -53029,7 +53029,7 @@
         <v>0.5775</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.1468</v>
+        <v>-0.1467</v>
       </c>
       <c r="D605" t="n">
         <v>0.2154</v>
@@ -53038,7 +53038,7 @@
         <v>0.5775</v>
       </c>
       <c r="F605" t="n">
-        <v>-0.1468</v>
+        <v>-0.1467</v>
       </c>
       <c r="G605" t="n">
         <v>1.2533</v>
@@ -53188,7 +53188,7 @@
         <v>0.4692</v>
       </c>
       <c r="M608" t="n">
-        <v>-0.2921</v>
+        <v>-0.292</v>
       </c>
     </row>
     <row r="609">
@@ -53459,7 +53459,7 @@
         <v>0.5548</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.1429</v>
+        <v>-0.1428</v>
       </c>
       <c r="D615" t="n">
         <v>0.206</v>
@@ -53468,7 +53468,7 @@
         <v>0.5548</v>
       </c>
       <c r="F615" t="n">
-        <v>-0.1429</v>
+        <v>-0.1428</v>
       </c>
       <c r="G615" t="n">
         <v>1.4183</v>
@@ -53545,7 +53545,7 @@
         <v>0.5437</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.1867</v>
+        <v>-0.1866</v>
       </c>
       <c r="D617" t="n">
         <v>0.1785</v>
@@ -53554,7 +53554,7 @@
         <v>0.5437</v>
       </c>
       <c r="F617" t="n">
-        <v>-0.1867</v>
+        <v>-0.1866</v>
       </c>
       <c r="G617" t="n">
         <v>1.6838</v>
@@ -53876,7 +53876,7 @@
         <v>0.449</v>
       </c>
       <c r="M624" t="n">
-        <v>-0.0633</v>
+        <v>-0.06320000000000001</v>
       </c>
     </row>
     <row r="625">
@@ -54276,7 +54276,7 @@
         <v>0.4028</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1559</v>
+        <v>-0.1558</v>
       </c>
       <c r="D634" t="n">
         <v>0.1235</v>
@@ -54285,7 +54285,7 @@
         <v>0.4028</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1559</v>
+        <v>-0.1558</v>
       </c>
       <c r="G634" t="n">
         <v>0.5542</v>
@@ -54319,16 +54319,16 @@
         <v>0.4028</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.164</v>
+        <v>-0.165</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1194</v>
+        <v>0.1189</v>
       </c>
       <c r="E635" t="n">
         <v>0.4028</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.164</v>
+        <v>-0.165</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4108</v>
+        <v>0.4079</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>-0.16  Mildly restrictive</t>
+          <t>-0.17  Mildly restrictive</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Monetary conditions score +0.40 (mildly accommodative) and liquidity conditions -0.16 (mildly restrictive); the combined index is +0.12 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-10.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
+          <t>Monetary conditions score +0.40 (mildly accommodative) and liquidity conditions -0.17 (mildly restrictive); the combined index is +0.12 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-10.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4781,7 +4781,7 @@
         <v>-0.076</v>
       </c>
       <c r="K332" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="333">
@@ -5041,7 +5041,7 @@
         <v>0.213</v>
       </c>
       <c r="K352" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="353">
@@ -5106,7 +5106,7 @@
         <v>-0.53</v>
       </c>
       <c r="K357" t="n">
-        <v>-0.215</v>
+        <v>-0.214</v>
       </c>
     </row>
     <row r="358">
@@ -5691,7 +5691,7 @@
         <v>-0.258</v>
       </c>
       <c r="K402" t="n">
-        <v>-1.03</v>
+        <v>-1.029</v>
       </c>
     </row>
     <row r="403">
@@ -8616,7 +8616,7 @@
         <v>0.403</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.165</v>
+        <v>-0.166</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.269</v>
+        <v>10.362</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.057</v>
+        <v>1.06</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0572</v>
+        <v>1.0602</v>
       </c>
       <c r="H635" t="n">
-        <v>10.2686</v>
+        <v>10.3619</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37824,7 +37824,7 @@
         <v>-0.7874</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.7338</v>
+        <v>-0.7337</v>
       </c>
       <c r="D187" t="n">
         <v>-0.7606000000000001</v>
@@ -37833,13 +37833,13 @@
         <v>-0.7874</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.7338</v>
+        <v>-0.7337</v>
       </c>
       <c r="G187" t="n">
         <v>-0.7874</v>
       </c>
       <c r="M187" t="n">
-        <v>-0.7338</v>
+        <v>-0.7337</v>
       </c>
     </row>
     <row r="188">
@@ -37992,7 +37992,7 @@
         <v>-1.4169</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0891</v>
+        <v>0.0892</v>
       </c>
       <c r="D193" t="n">
         <v>-0.6639</v>
@@ -38001,13 +38001,13 @@
         <v>-1.4169</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0891</v>
+        <v>0.0892</v>
       </c>
       <c r="G193" t="n">
         <v>-1.4169</v>
       </c>
       <c r="M193" t="n">
-        <v>0.0891</v>
+        <v>0.0892</v>
       </c>
     </row>
     <row r="194">
@@ -38020,7 +38020,7 @@
         <v>-1.261</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.7327</v>
+        <v>-0.7326</v>
       </c>
       <c r="D194" t="n">
         <v>-0.9968</v>
@@ -38029,13 +38029,13 @@
         <v>-1.261</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.7327</v>
+        <v>-0.7326</v>
       </c>
       <c r="G194" t="n">
         <v>-1.261</v>
       </c>
       <c r="M194" t="n">
-        <v>-0.7327</v>
+        <v>-0.7326</v>
       </c>
     </row>
     <row r="195">
@@ -38076,7 +38076,7 @@
         <v>-1.4876</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.8733</v>
+        <v>-0.8732</v>
       </c>
       <c r="D196" t="n">
         <v>-1.1804</v>
@@ -38085,13 +38085,13 @@
         <v>-1.4876</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.8733</v>
+        <v>-0.8732</v>
       </c>
       <c r="G196" t="n">
         <v>-1.4876</v>
       </c>
       <c r="M196" t="n">
-        <v>-0.8733</v>
+        <v>-0.8732</v>
       </c>
     </row>
     <row r="197">
@@ -38219,7 +38219,7 @@
         <v>-1.4057</v>
       </c>
       <c r="D201" t="n">
-        <v>-1.8224</v>
+        <v>-1.8223</v>
       </c>
       <c r="E201" t="n">
         <v>-2.239</v>
@@ -38300,7 +38300,7 @@
         <v>-1.9264</v>
       </c>
       <c r="C204" t="n">
-        <v>-2.2738</v>
+        <v>-2.2737</v>
       </c>
       <c r="D204" t="n">
         <v>-2.1001</v>
@@ -38309,13 +38309,13 @@
         <v>-1.9264</v>
       </c>
       <c r="F204" t="n">
-        <v>-2.2738</v>
+        <v>-2.2737</v>
       </c>
       <c r="G204" t="n">
         <v>-1.9264</v>
       </c>
       <c r="M204" t="n">
-        <v>-2.2738</v>
+        <v>-2.2737</v>
       </c>
     </row>
     <row r="205">
@@ -38499,7 +38499,7 @@
         <v>-2.0884</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.9623</v>
+        <v>-1.9622</v>
       </c>
       <c r="E211" t="n">
         <v>-1.8361</v>
@@ -38580,7 +38580,7 @@
         <v>-1.5043</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.7345</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="D214" t="n">
         <v>-1.1194</v>
@@ -38589,13 +38589,13 @@
         <v>-1.5043</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.7345</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="G214" t="n">
         <v>-1.5043</v>
       </c>
       <c r="M214" t="n">
-        <v>-0.7345</v>
+        <v>-0.7344000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -38636,7 +38636,7 @@
         <v>-1.4442</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.5063</v>
+        <v>-0.5062</v>
       </c>
       <c r="D216" t="n">
         <v>-0.9752</v>
@@ -38645,13 +38645,13 @@
         <v>-1.4442</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.5063</v>
+        <v>-0.5062</v>
       </c>
       <c r="G216" t="n">
         <v>-1.4442</v>
       </c>
       <c r="M216" t="n">
-        <v>-0.5063</v>
+        <v>-0.5062</v>
       </c>
     </row>
     <row r="217">
@@ -38695,7 +38695,7 @@
         <v>-0.1513</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.6513</v>
+        <v>-0.6512</v>
       </c>
       <c r="E218" t="n">
         <v>-1.1512</v>
@@ -38720,7 +38720,7 @@
         <v>-1.0927</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.2087</v>
+        <v>-0.2086</v>
       </c>
       <c r="D219" t="n">
         <v>-0.6506999999999999</v>
@@ -38729,13 +38729,13 @@
         <v>-1.0927</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.2087</v>
+        <v>-0.2086</v>
       </c>
       <c r="G219" t="n">
         <v>-1.0927</v>
       </c>
       <c r="M219" t="n">
-        <v>-0.2087</v>
+        <v>-0.2086</v>
       </c>
     </row>
     <row r="220">
@@ -38751,7 +38751,7 @@
         <v>-0.0152</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.5734</v>
+        <v>-0.5733</v>
       </c>
       <c r="E220" t="n">
         <v>-1.1315</v>
@@ -38776,7 +38776,7 @@
         <v>-0.67</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.1359</v>
+        <v>-0.1358</v>
       </c>
       <c r="D221" t="n">
         <v>-0.4029</v>
@@ -38785,13 +38785,13 @@
         <v>-0.67</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.1359</v>
+        <v>-0.1358</v>
       </c>
       <c r="G221" t="n">
         <v>-0.67</v>
       </c>
       <c r="M221" t="n">
-        <v>-0.1359</v>
+        <v>-0.1358</v>
       </c>
     </row>
     <row r="222">
@@ -38888,22 +38888,22 @@
         <v>-0.5007</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.0818</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.2913</v>
+        <v>-0.2912</v>
       </c>
       <c r="E225" t="n">
         <v>-0.5007</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.0818</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="G225" t="n">
         <v>-0.5007</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.0818</v>
+        <v>-0.08169999999999999</v>
       </c>
     </row>
     <row r="226">
@@ -38944,7 +38944,7 @@
         <v>-0.4974</v>
       </c>
       <c r="C227" t="n">
-        <v>0.0042</v>
+        <v>0.0043</v>
       </c>
       <c r="D227" t="n">
         <v>-0.2466</v>
@@ -38953,13 +38953,13 @@
         <v>-0.4974</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0042</v>
+        <v>0.0043</v>
       </c>
       <c r="G227" t="n">
         <v>-0.4974</v>
       </c>
       <c r="M227" t="n">
-        <v>0.0042</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="228">
@@ -39031,7 +39031,7 @@
         <v>0.0713</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.2728</v>
+        <v>-0.2727</v>
       </c>
       <c r="E230" t="n">
         <v>-0.6168</v>
@@ -39059,7 +39059,7 @@
         <v>-0.0009</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.2045</v>
+        <v>-0.2044</v>
       </c>
       <c r="E231" t="n">
         <v>-0.408</v>
@@ -39196,22 +39196,22 @@
         <v>-0.5696</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.4544</v>
+        <v>-0.4543</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.512</v>
+        <v>-0.5119</v>
       </c>
       <c r="E236" t="n">
         <v>-0.5696</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.4544</v>
+        <v>-0.4543</v>
       </c>
       <c r="G236" t="n">
         <v>-0.5696</v>
       </c>
       <c r="M236" t="n">
-        <v>-0.4544</v>
+        <v>-0.4543</v>
       </c>
     </row>
     <row r="237">
@@ -39280,7 +39280,7 @@
         <v>-0.2932</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.4444</v>
+        <v>-0.4443</v>
       </c>
       <c r="D239" t="n">
         <v>-0.3688</v>
@@ -39289,13 +39289,13 @@
         <v>-0.2932</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.4444</v>
+        <v>-0.4443</v>
       </c>
       <c r="G239" t="n">
         <v>-0.2932</v>
       </c>
       <c r="M239" t="n">
-        <v>-0.4444</v>
+        <v>-0.4443</v>
       </c>
     </row>
     <row r="240">
@@ -39336,22 +39336,22 @@
         <v>-0.4334</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.5119</v>
+        <v>-0.5118</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.4727</v>
+        <v>-0.4726</v>
       </c>
       <c r="E241" t="n">
         <v>-0.4334</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.5119</v>
+        <v>-0.5118</v>
       </c>
       <c r="G241" t="n">
         <v>-0.4334</v>
       </c>
       <c r="M241" t="n">
-        <v>-0.5119</v>
+        <v>-0.5118</v>
       </c>
     </row>
     <row r="242">
@@ -39423,7 +39423,7 @@
         <v>-1.2465</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.7988</v>
       </c>
       <c r="E244" t="n">
         <v>-0.3512</v>
@@ -39731,7 +39731,7 @@
         <v>-0.6909999999999999</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.6431</v>
+        <v>-0.643</v>
       </c>
       <c r="E255" t="n">
         <v>-0.5951</v>
@@ -39927,7 +39927,7 @@
         <v>-0.8856000000000001</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.4059</v>
+        <v>-0.4058</v>
       </c>
       <c r="E262" t="n">
         <v>0.07389999999999999</v>
@@ -40123,7 +40123,7 @@
         <v>-0.4218</v>
       </c>
       <c r="D269" t="n">
-        <v>-0.1843</v>
+        <v>-0.1842</v>
       </c>
       <c r="E269" t="n">
         <v>0.0533</v>
@@ -40151,7 +40151,7 @@
         <v>-0.3344</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.1455</v>
+        <v>-0.1454</v>
       </c>
       <c r="E270" t="n">
         <v>0.0435</v>
@@ -40204,7 +40204,7 @@
         <v>0.129</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.0184</v>
+        <v>-0.0183</v>
       </c>
       <c r="D272" t="n">
         <v>0.0553</v>
@@ -40213,13 +40213,13 @@
         <v>0.129</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.0184</v>
+        <v>-0.0183</v>
       </c>
       <c r="G272" t="n">
         <v>0.129</v>
       </c>
       <c r="M272" t="n">
-        <v>-0.0184</v>
+        <v>-0.0183</v>
       </c>
     </row>
     <row r="273">
@@ -40540,7 +40540,7 @@
         <v>0.9889</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0649</v>
+        <v>-0.0648</v>
       </c>
       <c r="D284" t="n">
         <v>0.462</v>
@@ -40549,13 +40549,13 @@
         <v>0.9889</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.0649</v>
+        <v>-0.0648</v>
       </c>
       <c r="G284" t="n">
         <v>0.9889</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.0649</v>
+        <v>-0.0648</v>
       </c>
     </row>
     <row r="285">
@@ -40652,22 +40652,22 @@
         <v>1.0711</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.1086</v>
+        <v>-0.1085</v>
       </c>
       <c r="D288" t="n">
-        <v>0.4812</v>
+        <v>0.4813</v>
       </c>
       <c r="E288" t="n">
         <v>1.0711</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.1086</v>
+        <v>-0.1085</v>
       </c>
       <c r="G288" t="n">
         <v>1.0711</v>
       </c>
       <c r="M288" t="n">
-        <v>-0.1086</v>
+        <v>-0.1085</v>
       </c>
     </row>
     <row r="289">
@@ -40680,7 +40680,7 @@
         <v>0.204</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.1117</v>
+        <v>-0.1116</v>
       </c>
       <c r="D289" t="n">
         <v>0.0462</v>
@@ -40689,13 +40689,13 @@
         <v>0.204</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.1117</v>
+        <v>-0.1116</v>
       </c>
       <c r="G289" t="n">
         <v>0.204</v>
       </c>
       <c r="M289" t="n">
-        <v>-0.1117</v>
+        <v>-0.1116</v>
       </c>
     </row>
     <row r="290">
@@ -40708,22 +40708,22 @@
         <v>0.9966</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.1253</v>
+        <v>-0.1252</v>
       </c>
       <c r="D290" t="n">
-        <v>0.4356</v>
+        <v>0.4357</v>
       </c>
       <c r="E290" t="n">
         <v>0.9966</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.1253</v>
+        <v>-0.1252</v>
       </c>
       <c r="G290" t="n">
         <v>0.9966</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.1253</v>
+        <v>-0.1252</v>
       </c>
     </row>
     <row r="291">
@@ -40823,7 +40823,7 @@
         <v>0.3807</v>
       </c>
       <c r="D294" t="n">
-        <v>0.2278</v>
+        <v>0.2279</v>
       </c>
       <c r="E294" t="n">
         <v>0.075</v>
@@ -41215,7 +41215,7 @@
         <v>-1.7698</v>
       </c>
       <c r="D308" t="n">
-        <v>-0.7763</v>
+        <v>-0.7762</v>
       </c>
       <c r="E308" t="n">
         <v>0.2173</v>
@@ -41352,7 +41352,7 @@
         <v>0.1736</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5014</v>
       </c>
       <c r="D313" t="n">
         <v>-0.1639</v>
@@ -41361,13 +41361,13 @@
         <v>0.1736</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5014</v>
       </c>
       <c r="G313" t="n">
         <v>0.1736</v>
       </c>
       <c r="M313" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5014</v>
       </c>
     </row>
     <row r="314">
@@ -41579,7 +41579,7 @@
         <v>0.8763</v>
       </c>
       <c r="D321" t="n">
-        <v>0.5104</v>
+        <v>0.5105</v>
       </c>
       <c r="E321" t="n">
         <v>0.1446</v>
@@ -41660,7 +41660,7 @@
         <v>-0.1762</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2108</v>
+        <v>0.2109</v>
       </c>
       <c r="D324" t="n">
         <v>0.0173</v>
@@ -41669,13 +41669,13 @@
         <v>-0.1762</v>
       </c>
       <c r="F324" t="n">
-        <v>0.2108</v>
+        <v>0.2109</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1762</v>
       </c>
       <c r="M324" t="n">
-        <v>0.2108</v>
+        <v>0.2109</v>
       </c>
     </row>
     <row r="325">
@@ -41716,7 +41716,7 @@
         <v>-0.2575</v>
       </c>
       <c r="C326" t="n">
-        <v>0.185</v>
+        <v>0.1851</v>
       </c>
       <c r="D326" t="n">
         <v>-0.0362</v>
@@ -41725,13 +41725,13 @@
         <v>-0.2575</v>
       </c>
       <c r="F326" t="n">
-        <v>0.185</v>
+        <v>0.1851</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2575</v>
       </c>
       <c r="M326" t="n">
-        <v>0.185</v>
+        <v>0.1851</v>
       </c>
     </row>
     <row r="327">
@@ -41856,7 +41856,7 @@
         <v>-0.168</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.1229</v>
+        <v>-0.1228</v>
       </c>
       <c r="D331" t="n">
         <v>-0.1454</v>
@@ -41865,13 +41865,13 @@
         <v>-0.168</v>
       </c>
       <c r="F331" t="n">
-        <v>-0.1229</v>
+        <v>-0.1228</v>
       </c>
       <c r="G331" t="n">
         <v>-0.168</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.1229</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="332">
@@ -41912,7 +41912,7 @@
         <v>-0.1727</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.2413</v>
+        <v>-0.2412</v>
       </c>
       <c r="D333" t="n">
         <v>-0.207</v>
@@ -41921,13 +41921,13 @@
         <v>-0.1727</v>
       </c>
       <c r="F333" t="n">
-        <v>-0.2413</v>
+        <v>-0.2412</v>
       </c>
       <c r="G333" t="n">
         <v>-0.1727</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.2413</v>
+        <v>-0.2412</v>
       </c>
     </row>
     <row r="334">
@@ -41968,22 +41968,22 @@
         <v>-0.0738</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2627</v>
+        <v>-0.2626</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.1683</v>
+        <v>-0.1682</v>
       </c>
       <c r="E335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2627</v>
+        <v>-0.2626</v>
       </c>
       <c r="G335" t="n">
         <v>-0.0738</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2627</v>
+        <v>-0.2626</v>
       </c>
     </row>
     <row r="336">
@@ -42055,7 +42055,7 @@
         <v>-0.2474</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.186</v>
+        <v>-0.1859</v>
       </c>
       <c r="E338" t="n">
         <v>-0.1245</v>
@@ -42136,7 +42136,7 @@
         <v>-0.1691</v>
       </c>
       <c r="C341" t="n">
-        <v>0.176</v>
+        <v>0.1761</v>
       </c>
       <c r="D341" t="n">
         <v>0.0035</v>
@@ -42145,13 +42145,13 @@
         <v>-0.1691</v>
       </c>
       <c r="F341" t="n">
-        <v>0.176</v>
+        <v>0.1761</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1691</v>
       </c>
       <c r="M341" t="n">
-        <v>0.176</v>
+        <v>0.1761</v>
       </c>
     </row>
     <row r="342">
@@ -42332,7 +42332,7 @@
         <v>-0.1199</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5124</v>
+        <v>0.5125</v>
       </c>
       <c r="D348" t="n">
         <v>0.1963</v>
@@ -42341,13 +42341,13 @@
         <v>-0.1199</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5124</v>
+        <v>0.5125</v>
       </c>
       <c r="G348" t="n">
         <v>-0.1199</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5124</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="349">
@@ -42416,7 +42416,7 @@
         <v>-0.07580000000000001</v>
       </c>
       <c r="C351" t="n">
-        <v>0.9327</v>
+        <v>0.9328</v>
       </c>
       <c r="D351" t="n">
         <v>0.4285</v>
@@ -42425,13 +42425,13 @@
         <v>-0.07580000000000001</v>
       </c>
       <c r="F351" t="n">
-        <v>0.9327</v>
+        <v>0.9328</v>
       </c>
       <c r="G351" t="n">
         <v>-0.07580000000000001</v>
       </c>
       <c r="M351" t="n">
-        <v>0.9327</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="352">
@@ -42472,7 +42472,7 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="C353" t="n">
-        <v>1.2357</v>
+        <v>1.2358</v>
       </c>
       <c r="D353" t="n">
         <v>0.6516999999999999</v>
@@ -42481,13 +42481,13 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="F353" t="n">
-        <v>1.2357</v>
+        <v>1.2358</v>
       </c>
       <c r="G353" t="n">
         <v>0.06759999999999999</v>
       </c>
       <c r="M353" t="n">
-        <v>1.2357</v>
+        <v>1.2358</v>
       </c>
     </row>
     <row r="354">
@@ -42531,7 +42531,7 @@
         <v>1.0938</v>
       </c>
       <c r="D355" t="n">
-        <v>0.5825</v>
+        <v>0.5826</v>
       </c>
       <c r="E355" t="n">
         <v>0.0713</v>
@@ -42640,7 +42640,7 @@
         <v>0.3073</v>
       </c>
       <c r="C359" t="n">
-        <v>0.0665</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="D359" t="n">
         <v>0.1869</v>
@@ -42649,13 +42649,13 @@
         <v>0.3073</v>
       </c>
       <c r="F359" t="n">
-        <v>0.0665</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="G359" t="n">
         <v>0.3073</v>
       </c>
       <c r="M359" t="n">
-        <v>0.0665</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="360">
@@ -42879,7 +42879,7 @@
         <v>-0.4673</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.1059</v>
+        <v>-0.1058</v>
       </c>
       <c r="D367" t="n">
         <v>-0.2866</v>
@@ -42888,7 +42888,7 @@
         <v>-0.4673</v>
       </c>
       <c r="F367" t="n">
-        <v>-0.1059</v>
+        <v>-0.1058</v>
       </c>
       <c r="G367" t="n">
         <v>0.2104</v>
@@ -42897,7 +42897,7 @@
         <v>-1.1451</v>
       </c>
       <c r="M367" t="n">
-        <v>-0.1059</v>
+        <v>-0.1058</v>
       </c>
     </row>
     <row r="368">
@@ -42941,7 +42941,7 @@
         <v>-0.4511</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.403</v>
+        <v>-0.4029</v>
       </c>
       <c r="D369" t="n">
         <v>-0.427</v>
@@ -42950,7 +42950,7 @@
         <v>-0.4511</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.403</v>
+        <v>-0.4029</v>
       </c>
       <c r="G369" t="n">
         <v>0.1627</v>
@@ -42959,7 +42959,7 @@
         <v>-1.065</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.403</v>
+        <v>-0.4029</v>
       </c>
     </row>
     <row r="370">
@@ -43003,7 +43003,7 @@
         <v>-0.4545</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.3087</v>
+        <v>-0.3086</v>
       </c>
       <c r="D371" t="n">
         <v>-0.3816</v>
@@ -43012,7 +43012,7 @@
         <v>-0.4545</v>
       </c>
       <c r="F371" t="n">
-        <v>-0.3087</v>
+        <v>-0.3086</v>
       </c>
       <c r="G371" t="n">
         <v>0.2118</v>
@@ -43021,7 +43021,7 @@
         <v>-1.1208</v>
       </c>
       <c r="M371" t="n">
-        <v>-0.3087</v>
+        <v>-0.3086</v>
       </c>
     </row>
     <row r="372">
@@ -43034,7 +43034,7 @@
         <v>-0.5501</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3363</v>
+        <v>-0.3362</v>
       </c>
       <c r="D372" t="n">
         <v>-0.4432</v>
@@ -43043,7 +43043,7 @@
         <v>-0.5501</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3363</v>
+        <v>-0.3362</v>
       </c>
       <c r="G372" t="n">
         <v>0.167</v>
@@ -43052,7 +43052,7 @@
         <v>-1.2673</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3363</v>
+        <v>-0.3362</v>
       </c>
     </row>
     <row r="373">
@@ -43065,7 +43065,7 @@
         <v>-0.5384</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2953</v>
+        <v>-0.2952</v>
       </c>
       <c r="D373" t="n">
         <v>-0.4168</v>
@@ -43074,7 +43074,7 @@
         <v>-0.5384</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2953</v>
+        <v>-0.2952</v>
       </c>
       <c r="G373" t="n">
         <v>0.1675</v>
@@ -43083,7 +43083,7 @@
         <v>-1.2442</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2953</v>
+        <v>-0.2952</v>
       </c>
     </row>
     <row r="374">
@@ -43311,7 +43311,7 @@
         <v>-0.556</v>
       </c>
       <c r="C379" t="n">
-        <v>0.1967</v>
+        <v>0.1968</v>
       </c>
       <c r="D379" t="n">
         <v>-0.1796</v>
@@ -43320,7 +43320,7 @@
         <v>-0.556</v>
       </c>
       <c r="F379" t="n">
-        <v>0.1967</v>
+        <v>0.1968</v>
       </c>
       <c r="G379" t="n">
         <v>0.1671</v>
@@ -43341,7 +43341,7 @@
         <v>0.7169</v>
       </c>
       <c r="M379" t="n">
-        <v>0.7416</v>
+        <v>0.7417</v>
       </c>
     </row>
     <row r="380">
@@ -43440,7 +43440,7 @@
         <v>-0.4875</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.0208</v>
+        <v>-0.0207</v>
       </c>
       <c r="D382" t="n">
         <v>-0.2541</v>
@@ -43449,7 +43449,7 @@
         <v>-0.4875</v>
       </c>
       <c r="F382" t="n">
-        <v>-0.0208</v>
+        <v>-0.0207</v>
       </c>
       <c r="G382" t="n">
         <v>0.163</v>
@@ -43556,7 +43556,7 @@
         <v>0.2187</v>
       </c>
       <c r="M384" t="n">
-        <v>0.7522</v>
+        <v>0.7523</v>
       </c>
     </row>
     <row r="385">
@@ -43728,7 +43728,7 @@
         <v>-0.1761</v>
       </c>
       <c r="M388" t="n">
-        <v>0.9065</v>
+        <v>0.9066</v>
       </c>
     </row>
     <row r="389">
@@ -44257,7 +44257,7 @@
         <v>-0.7693</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.6976</v>
+        <v>-0.6975</v>
       </c>
       <c r="D401" t="n">
         <v>-0.7334000000000001</v>
@@ -44266,7 +44266,7 @@
         <v>-0.7693</v>
       </c>
       <c r="F401" t="n">
-        <v>-0.6976</v>
+        <v>-0.6975</v>
       </c>
       <c r="G401" t="n">
         <v>-0.0488</v>
@@ -44631,7 +44631,7 @@
         <v>-2.0019</v>
       </c>
       <c r="M409" t="n">
-        <v>-0.2825</v>
+        <v>-0.2824</v>
       </c>
     </row>
     <row r="410">
@@ -44889,7 +44889,7 @@
         <v>-2.6249</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.6221</v>
+        <v>-0.622</v>
       </c>
     </row>
     <row r="416">
@@ -45319,7 +45319,7 @@
         <v>-1.2153</v>
       </c>
       <c r="M425" t="n">
-        <v>0.312</v>
+        <v>0.3121</v>
       </c>
     </row>
     <row r="426">
@@ -45848,7 +45848,7 @@
         <v>-0.6195000000000001</v>
       </c>
       <c r="C438" t="n">
-        <v>0.2808</v>
+        <v>0.2809</v>
       </c>
       <c r="D438" t="n">
         <v>-0.1693</v>
@@ -45857,7 +45857,7 @@
         <v>-0.6195000000000001</v>
       </c>
       <c r="F438" t="n">
-        <v>0.2808</v>
+        <v>0.2809</v>
       </c>
       <c r="G438" t="n">
         <v>-0.2191</v>
@@ -45878,7 +45878,7 @@
         <v>0.2591</v>
       </c>
       <c r="M438" t="n">
-        <v>0.4627</v>
+        <v>0.4628</v>
       </c>
     </row>
     <row r="439">
@@ -45964,7 +45964,7 @@
         <v>0.2602</v>
       </c>
       <c r="M440" t="n">
-        <v>0.4015</v>
+        <v>0.4016</v>
       </c>
     </row>
     <row r="441">
@@ -46050,7 +46050,7 @@
         <v>0.2863</v>
       </c>
       <c r="M442" t="n">
-        <v>0.2318</v>
+        <v>0.2319</v>
       </c>
     </row>
     <row r="443">
@@ -46192,7 +46192,7 @@
         <v>-0.6766</v>
       </c>
       <c r="C446" t="n">
-        <v>0.278</v>
+        <v>0.2781</v>
       </c>
       <c r="D446" t="n">
         <v>-0.1993</v>
@@ -46201,7 +46201,7 @@
         <v>-0.6766</v>
       </c>
       <c r="F446" t="n">
-        <v>0.278</v>
+        <v>0.2781</v>
       </c>
       <c r="G446" t="n">
         <v>-0.1755</v>
@@ -46235,16 +46235,16 @@
         <v>-0.6869</v>
       </c>
       <c r="C447" t="n">
-        <v>0.2635</v>
+        <v>0.2636</v>
       </c>
       <c r="D447" t="n">
-        <v>-0.2117</v>
+        <v>-0.2116</v>
       </c>
       <c r="E447" t="n">
         <v>-0.6869</v>
       </c>
       <c r="F447" t="n">
-        <v>0.2635</v>
+        <v>0.2636</v>
       </c>
       <c r="G447" t="n">
         <v>-0.182</v>
@@ -46351,7 +46351,7 @@
         <v>0.1753</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1531</v>
+        <v>0.1532</v>
       </c>
     </row>
     <row r="450">
@@ -46437,7 +46437,7 @@
         <v>0.1722</v>
       </c>
       <c r="M451" t="n">
-        <v>0.1677</v>
+        <v>0.1678</v>
       </c>
     </row>
     <row r="452">
@@ -46754,7 +46754,7 @@
         <v>0.2593</v>
       </c>
       <c r="D459" t="n">
-        <v>-0.0416</v>
+        <v>-0.0415</v>
       </c>
       <c r="E459" t="n">
         <v>-0.3424</v>
@@ -46824,7 +46824,7 @@
         <v>0.3094</v>
       </c>
       <c r="M460" t="n">
-        <v>0.3715</v>
+        <v>0.3716</v>
       </c>
     </row>
     <row r="461">
@@ -46996,7 +46996,7 @@
         <v>0.3646</v>
       </c>
       <c r="M464" t="n">
-        <v>0.3704</v>
+        <v>0.3705</v>
       </c>
     </row>
     <row r="465">
@@ -47098,7 +47098,7 @@
         <v>0.4714</v>
       </c>
       <c r="D467" t="n">
-        <v>0.1065</v>
+        <v>0.1066</v>
       </c>
       <c r="E467" t="n">
         <v>-0.2583</v>
@@ -47141,7 +47141,7 @@
         <v>0.5625</v>
       </c>
       <c r="D468" t="n">
-        <v>0.1067</v>
+        <v>0.1068</v>
       </c>
       <c r="E468" t="n">
         <v>-0.349</v>
@@ -47270,7 +47270,7 @@
         <v>0.727</v>
       </c>
       <c r="D471" t="n">
-        <v>0.3552</v>
+        <v>0.3553</v>
       </c>
       <c r="E471" t="n">
         <v>-0.0165</v>
@@ -47611,7 +47611,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="C479" t="n">
-        <v>1.1927</v>
+        <v>1.1928</v>
       </c>
       <c r="D479" t="n">
         <v>0.9797</v>
@@ -47620,7 +47620,7 @@
         <v>0.7665999999999999</v>
       </c>
       <c r="F479" t="n">
-        <v>1.1927</v>
+        <v>1.1928</v>
       </c>
       <c r="G479" t="n">
         <v>0.6215000000000001</v>
@@ -47684,7 +47684,7 @@
         <v>0.5768</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2468</v>
+        <v>0.2469</v>
       </c>
     </row>
     <row r="481">
@@ -47727,7 +47727,7 @@
         <v>0.6427</v>
       </c>
       <c r="M481" t="n">
-        <v>0.2376</v>
+        <v>0.2377</v>
       </c>
     </row>
     <row r="482">
@@ -47770,7 +47770,7 @@
         <v>0.6854</v>
       </c>
       <c r="M482" t="n">
-        <v>0.2425</v>
+        <v>0.2426</v>
       </c>
     </row>
     <row r="483">
@@ -47829,7 +47829,7 @@
         <v>1.143</v>
       </c>
       <c r="D484" t="n">
-        <v>1.0394</v>
+        <v>1.0395</v>
       </c>
       <c r="E484" t="n">
         <v>0.9359</v>
@@ -48428,7 +48428,7 @@
         <v>0.7913</v>
       </c>
       <c r="C498" t="n">
-        <v>0.9003</v>
+        <v>0.9004</v>
       </c>
       <c r="D498" t="n">
         <v>0.8458</v>
@@ -48437,7 +48437,7 @@
         <v>0.7913</v>
       </c>
       <c r="F498" t="n">
-        <v>0.9003</v>
+        <v>0.9004</v>
       </c>
       <c r="G498" t="n">
         <v>0.3435</v>
@@ -48759,7 +48759,7 @@
         <v>0.4075</v>
       </c>
       <c r="M505" t="n">
-        <v>0.372</v>
+        <v>0.3721</v>
       </c>
     </row>
     <row r="506">
@@ -48845,7 +48845,7 @@
         <v>0.401</v>
       </c>
       <c r="M507" t="n">
-        <v>0.3111</v>
+        <v>0.3112</v>
       </c>
     </row>
     <row r="508">
@@ -49632,7 +49632,7 @@
         <v>0.4107</v>
       </c>
       <c r="C526" t="n">
-        <v>0.3039</v>
+        <v>0.304</v>
       </c>
       <c r="D526" t="n">
         <v>0.3573</v>
@@ -49641,7 +49641,7 @@
         <v>0.4107</v>
       </c>
       <c r="F526" t="n">
-        <v>0.3039</v>
+        <v>0.304</v>
       </c>
       <c r="G526" t="n">
         <v>0.6443</v>
@@ -49721,7 +49721,7 @@
         <v>0.2268</v>
       </c>
       <c r="D528" t="n">
-        <v>0.3266</v>
+        <v>0.3267</v>
       </c>
       <c r="E528" t="n">
         <v>0.4265</v>
@@ -49748,7 +49748,7 @@
         <v>0.0638</v>
       </c>
       <c r="M528" t="n">
-        <v>0.3588</v>
+        <v>0.3589</v>
       </c>
     </row>
     <row r="529">
@@ -49761,7 +49761,7 @@
         <v>0.387</v>
       </c>
       <c r="C529" t="n">
-        <v>0.2212</v>
+        <v>0.2213</v>
       </c>
       <c r="D529" t="n">
         <v>0.3041</v>
@@ -49770,7 +49770,7 @@
         <v>0.387</v>
       </c>
       <c r="F529" t="n">
-        <v>0.2212</v>
+        <v>0.2213</v>
       </c>
       <c r="G529" t="n">
         <v>0.6857</v>
@@ -49920,7 +49920,7 @@
         <v>0.0463</v>
       </c>
       <c r="M532" t="n">
-        <v>0.3098</v>
+        <v>0.3099</v>
       </c>
     </row>
     <row r="533">
@@ -52086,7 +52086,7 @@
         <v>-0.0399</v>
       </c>
       <c r="D583" t="n">
-        <v>0.2412</v>
+        <v>0.2413</v>
       </c>
       <c r="E583" t="n">
         <v>0.5224</v>
@@ -52212,7 +52212,7 @@
         <v>0.5686</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.1931</v>
+        <v>-0.193</v>
       </c>
       <c r="D586" t="n">
         <v>0.1878</v>
@@ -52221,7 +52221,7 @@
         <v>0.5686</v>
       </c>
       <c r="F586" t="n">
-        <v>-0.1931</v>
+        <v>-0.193</v>
       </c>
       <c r="G586" t="n">
         <v>1.7537</v>
@@ -52242,7 +52242,7 @@
         <v>0.6581</v>
       </c>
       <c r="M586" t="n">
-        <v>-0.7429</v>
+        <v>-0.7428</v>
       </c>
     </row>
     <row r="587">
@@ -52285,7 +52285,7 @@
         <v>0.53</v>
       </c>
       <c r="M587" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.8623</v>
       </c>
     </row>
     <row r="588">
@@ -52470,7 +52470,7 @@
         <v>0.5706</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.4316</v>
+        <v>-0.4315</v>
       </c>
       <c r="D592" t="n">
         <v>0.06950000000000001</v>
@@ -52479,7 +52479,7 @@
         <v>0.5706</v>
       </c>
       <c r="F592" t="n">
-        <v>-0.4316</v>
+        <v>-0.4315</v>
       </c>
       <c r="G592" t="n">
         <v>1.7695</v>
@@ -52857,7 +52857,7 @@
         <v>0.6663</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.2476</v>
+        <v>-0.2475</v>
       </c>
       <c r="D601" t="n">
         <v>0.2094</v>
@@ -52866,7 +52866,7 @@
         <v>0.6663</v>
       </c>
       <c r="F601" t="n">
-        <v>-0.2476</v>
+        <v>-0.2475</v>
       </c>
       <c r="G601" t="n">
         <v>1.5079</v>
@@ -53274,7 +53274,7 @@
         <v>0.4763</v>
       </c>
       <c r="M610" t="n">
-        <v>-0.2783</v>
+        <v>-0.2782</v>
       </c>
     </row>
     <row r="611">
@@ -53532,7 +53532,7 @@
         <v>0.3747</v>
       </c>
       <c r="M616" t="n">
-        <v>0.0596</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="617">
@@ -53618,7 +53618,7 @@
         <v>0.4167</v>
       </c>
       <c r="M618" t="n">
-        <v>-0.1079</v>
+        <v>-0.1078</v>
       </c>
     </row>
     <row r="619">
@@ -53661,7 +53661,7 @@
         <v>0.368</v>
       </c>
       <c r="M619" t="n">
-        <v>-0.1045</v>
+        <v>-0.1044</v>
       </c>
     </row>
     <row r="620">
@@ -53833,7 +53833,7 @@
         <v>0.3639</v>
       </c>
       <c r="M623" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0907</v>
       </c>
     </row>
     <row r="624">
@@ -54177,7 +54177,7 @@
         <v>0.4838</v>
       </c>
       <c r="M631" t="n">
-        <v>0.2676</v>
+        <v>0.2677</v>
       </c>
     </row>
     <row r="632">
@@ -54220,7 +54220,7 @@
         <v>0.4472</v>
       </c>
       <c r="M632" t="n">
-        <v>0.2815</v>
+        <v>0.2816</v>
       </c>
     </row>
     <row r="633">
@@ -54319,16 +54319,16 @@
         <v>0.4028</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.165</v>
+        <v>-0.1661</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1189</v>
+        <v>0.1184</v>
       </c>
       <c r="E635" t="n">
         <v>0.4028</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.165</v>
+        <v>-0.1661</v>
       </c>
       <c r="G635" t="n">
         <v>0.5542</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4079</v>
+        <v>0.4047</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -3533,7 +3533,7 @@
         <v>-0.351</v>
       </c>
       <c r="K236" t="n">
-        <v>-1.247</v>
+        <v>-1.246</v>
       </c>
     </row>
     <row r="237">
@@ -3988,7 +3988,7 @@
         <v>0.268</v>
       </c>
       <c r="K271" t="n">
-        <v>0.501</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="272">
@@ -4885,7 +4885,7 @@
         <v>-0.12</v>
       </c>
       <c r="K340" t="n">
-        <v>0.512</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="341">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.536</v>
+        <v>10.619</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.06</v>
+        <v>1.059</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0603</v>
+        <v>1.0588</v>
       </c>
       <c r="H635" t="n">
-        <v>10.5361</v>
+        <v>10.6189</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37183,7 +37183,7 @@
         <v>-2.8744</v>
       </c>
       <c r="D164" t="n">
-        <v>-2.045</v>
+        <v>-2.0449</v>
       </c>
       <c r="E164" t="n">
         <v>-1.2155</v>
@@ -37379,7 +37379,7 @@
         <v>-4.4218</v>
       </c>
       <c r="D171" t="n">
-        <v>-2.8057</v>
+        <v>-2.8058</v>
       </c>
       <c r="E171" t="n">
         <v>-1.1897</v>
@@ -37603,7 +37603,7 @@
         <v>-2.7889</v>
       </c>
       <c r="D179" t="n">
-        <v>-2.1155</v>
+        <v>-2.1154</v>
       </c>
       <c r="E179" t="n">
         <v>-1.442</v>
@@ -37908,7 +37908,7 @@
         <v>-0.8622</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3763</v>
+        <v>-0.3762</v>
       </c>
       <c r="D190" t="n">
         <v>-0.6192</v>
@@ -37917,13 +37917,13 @@
         <v>-0.8622</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.3763</v>
+        <v>-0.3762</v>
       </c>
       <c r="G190" t="n">
         <v>-0.8622</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.3763</v>
+        <v>-0.3762</v>
       </c>
     </row>
     <row r="191">
@@ -37995,7 +37995,7 @@
         <v>0.0892</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.6639</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="E193" t="n">
         <v>-1.4169</v>
@@ -38048,7 +38048,7 @@
         <v>-1.372</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7212</v>
+        <v>-0.7211</v>
       </c>
       <c r="D195" t="n">
         <v>-1.0466</v>
@@ -38057,13 +38057,13 @@
         <v>-1.372</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7212</v>
+        <v>-0.7211</v>
       </c>
       <c r="G195" t="n">
         <v>-1.372</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7212</v>
+        <v>-0.7211</v>
       </c>
     </row>
     <row r="196">
@@ -38132,7 +38132,7 @@
         <v>-2.0205</v>
       </c>
       <c r="C198" t="n">
-        <v>-1.1546</v>
+        <v>-1.1545</v>
       </c>
       <c r="D198" t="n">
         <v>-1.5875</v>
@@ -38141,13 +38141,13 @@
         <v>-2.0205</v>
       </c>
       <c r="F198" t="n">
-        <v>-1.1546</v>
+        <v>-1.1545</v>
       </c>
       <c r="G198" t="n">
         <v>-2.0205</v>
       </c>
       <c r="M198" t="n">
-        <v>-1.1546</v>
+        <v>-1.1545</v>
       </c>
     </row>
     <row r="199">
@@ -38272,7 +38272,7 @@
         <v>-2.0234</v>
       </c>
       <c r="C203" t="n">
-        <v>-1.8424</v>
+        <v>-1.8423</v>
       </c>
       <c r="D203" t="n">
         <v>-1.9329</v>
@@ -38281,13 +38281,13 @@
         <v>-2.0234</v>
       </c>
       <c r="F203" t="n">
-        <v>-1.8424</v>
+        <v>-1.8423</v>
       </c>
       <c r="G203" t="n">
         <v>-2.0234</v>
       </c>
       <c r="M203" t="n">
-        <v>-1.8424</v>
+        <v>-1.8423</v>
       </c>
     </row>
     <row r="204">
@@ -38748,7 +38748,7 @@
         <v>-1.1315</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.0152</v>
+        <v>-0.0151</v>
       </c>
       <c r="D220" t="n">
         <v>-0.5733</v>
@@ -38757,13 +38757,13 @@
         <v>-1.1315</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.0152</v>
+        <v>-0.0151</v>
       </c>
       <c r="G220" t="n">
         <v>-1.1315</v>
       </c>
       <c r="M220" t="n">
-        <v>-0.0152</v>
+        <v>-0.0151</v>
       </c>
     </row>
     <row r="221">
@@ -38916,7 +38916,7 @@
         <v>-0.5012</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.0039</v>
+        <v>-0.0038</v>
       </c>
       <c r="D226" t="n">
         <v>-0.2525</v>
@@ -38925,13 +38925,13 @@
         <v>-0.5012</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.0039</v>
+        <v>-0.0038</v>
       </c>
       <c r="G226" t="n">
         <v>-0.5012</v>
       </c>
       <c r="M226" t="n">
-        <v>-0.0039</v>
+        <v>-0.0038</v>
       </c>
     </row>
     <row r="227">
@@ -39143,7 +39143,7 @@
         <v>-0.3823</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.4978</v>
+        <v>-0.4977</v>
       </c>
       <c r="E234" t="n">
         <v>-0.6132</v>
@@ -39560,7 +39560,7 @@
         <v>-0.4626</v>
       </c>
       <c r="C249" t="n">
-        <v>-1.363</v>
+        <v>-1.3629</v>
       </c>
       <c r="D249" t="n">
         <v>-0.9127999999999999</v>
@@ -39569,13 +39569,13 @@
         <v>-0.4626</v>
       </c>
       <c r="F249" t="n">
-        <v>-1.363</v>
+        <v>-1.3629</v>
       </c>
       <c r="G249" t="n">
         <v>-0.4626</v>
       </c>
       <c r="M249" t="n">
-        <v>-1.363</v>
+        <v>-1.3629</v>
       </c>
     </row>
     <row r="250">
@@ -39644,7 +39644,7 @@
         <v>-0.6718</v>
       </c>
       <c r="C252" t="n">
-        <v>-1.0849</v>
+        <v>-1.0848</v>
       </c>
       <c r="D252" t="n">
         <v>-0.8783</v>
@@ -39653,13 +39653,13 @@
         <v>-0.6718</v>
       </c>
       <c r="F252" t="n">
-        <v>-1.0849</v>
+        <v>-1.0848</v>
       </c>
       <c r="G252" t="n">
         <v>-0.6718</v>
       </c>
       <c r="M252" t="n">
-        <v>-1.0849</v>
+        <v>-1.0848</v>
       </c>
     </row>
     <row r="253">
@@ -39728,22 +39728,22 @@
         <v>-0.5954</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6909</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.6432</v>
+        <v>-0.6431</v>
       </c>
       <c r="E255" t="n">
         <v>-0.5954</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6909</v>
       </c>
       <c r="G255" t="n">
         <v>-0.5954</v>
       </c>
       <c r="M255" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6909</v>
       </c>
     </row>
     <row r="256">
@@ -39759,7 +39759,7 @@
         <v>-0.7728</v>
       </c>
       <c r="D256" t="n">
-        <v>-0.6914</v>
+        <v>-0.6913</v>
       </c>
       <c r="E256" t="n">
         <v>-0.6099</v>
@@ -39784,7 +39784,7 @@
         <v>-0.4634</v>
       </c>
       <c r="C257" t="n">
-        <v>-1.1877</v>
+        <v>-1.1876</v>
       </c>
       <c r="D257" t="n">
         <v>-0.8255</v>
@@ -39793,13 +39793,13 @@
         <v>-0.4634</v>
       </c>
       <c r="F257" t="n">
-        <v>-1.1877</v>
+        <v>-1.1876</v>
       </c>
       <c r="G257" t="n">
         <v>-0.4634</v>
       </c>
       <c r="M257" t="n">
-        <v>-1.1877</v>
+        <v>-1.1876</v>
       </c>
     </row>
     <row r="258">
@@ -39812,7 +39812,7 @@
         <v>-0.473</v>
       </c>
       <c r="C258" t="n">
-        <v>-1.1961</v>
+        <v>-1.196</v>
       </c>
       <c r="D258" t="n">
         <v>-0.8345</v>
@@ -39821,13 +39821,13 @@
         <v>-0.473</v>
       </c>
       <c r="F258" t="n">
-        <v>-1.1961</v>
+        <v>-1.196</v>
       </c>
       <c r="G258" t="n">
         <v>-0.473</v>
       </c>
       <c r="M258" t="n">
-        <v>-1.1961</v>
+        <v>-1.196</v>
       </c>
     </row>
     <row r="259">
@@ -40148,7 +40148,7 @@
         <v>0.0431</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.3344</v>
+        <v>-0.3343</v>
       </c>
       <c r="D270" t="n">
         <v>-0.1456</v>
@@ -40157,13 +40157,13 @@
         <v>0.0431</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.3344</v>
+        <v>-0.3343</v>
       </c>
       <c r="G270" t="n">
         <v>0.0431</v>
       </c>
       <c r="M270" t="n">
-        <v>-0.3344</v>
+        <v>-0.3343</v>
       </c>
     </row>
     <row r="271">
@@ -40176,7 +40176,7 @@
         <v>0.1082</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.0423</v>
+        <v>-0.0422</v>
       </c>
       <c r="D271" t="n">
         <v>0.033</v>
@@ -40185,13 +40185,13 @@
         <v>0.1082</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.0423</v>
+        <v>-0.0422</v>
       </c>
       <c r="G271" t="n">
         <v>0.1082</v>
       </c>
       <c r="M271" t="n">
-        <v>-0.0423</v>
+        <v>-0.0422</v>
       </c>
     </row>
     <row r="272">
@@ -40344,7 +40344,7 @@
         <v>1.0418</v>
       </c>
       <c r="C277" t="n">
-        <v>0.152</v>
+        <v>0.1521</v>
       </c>
       <c r="D277" t="n">
         <v>0.5969</v>
@@ -40353,13 +40353,13 @@
         <v>1.0418</v>
       </c>
       <c r="F277" t="n">
-        <v>0.152</v>
+        <v>0.1521</v>
       </c>
       <c r="G277" t="n">
         <v>1.0418</v>
       </c>
       <c r="M277" t="n">
-        <v>0.152</v>
+        <v>0.1521</v>
       </c>
     </row>
     <row r="278">
@@ -40372,7 +40372,7 @@
         <v>0.3162</v>
       </c>
       <c r="C278" t="n">
-        <v>0.4113</v>
+        <v>0.4114</v>
       </c>
       <c r="D278" t="n">
         <v>0.3638</v>
@@ -40381,13 +40381,13 @@
         <v>0.3162</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4113</v>
+        <v>0.4114</v>
       </c>
       <c r="G278" t="n">
         <v>0.3162</v>
       </c>
       <c r="M278" t="n">
-        <v>0.4113</v>
+        <v>0.4114</v>
       </c>
     </row>
     <row r="279">
@@ -40428,7 +40428,7 @@
         <v>0.2948</v>
       </c>
       <c r="C280" t="n">
-        <v>0.5105</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="D280" t="n">
         <v>0.4027</v>
@@ -40437,13 +40437,13 @@
         <v>0.2948</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5105</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G280" t="n">
         <v>0.2948</v>
       </c>
       <c r="M280" t="n">
-        <v>0.5105</v>
+        <v>0.5106000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -40764,7 +40764,7 @@
         <v>0.9145</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1416</v>
+        <v>-0.1415</v>
       </c>
       <c r="D292" t="n">
         <v>0.3865</v>
@@ -40773,13 +40773,13 @@
         <v>0.9145</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.1416</v>
+        <v>-0.1415</v>
       </c>
       <c r="G292" t="n">
         <v>0.9145</v>
       </c>
       <c r="M292" t="n">
-        <v>-0.1416</v>
+        <v>-0.1415</v>
       </c>
     </row>
     <row r="293">
@@ -40879,7 +40879,7 @@
         <v>0.1692</v>
       </c>
       <c r="D296" t="n">
-        <v>0.0921</v>
+        <v>0.0922</v>
       </c>
       <c r="E296" t="n">
         <v>0.0151</v>
@@ -40904,7 +40904,7 @@
         <v>0.0208</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1649</v>
+        <v>0.165</v>
       </c>
       <c r="D297" t="n">
         <v>0.0929</v>
@@ -40913,13 +40913,13 @@
         <v>0.0208</v>
       </c>
       <c r="F297" t="n">
-        <v>0.1649</v>
+        <v>0.165</v>
       </c>
       <c r="G297" t="n">
         <v>0.0208</v>
       </c>
       <c r="M297" t="n">
-        <v>0.1649</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="298">
@@ -40960,7 +40960,7 @@
         <v>-0.0374</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.1286</v>
+        <v>-0.1285</v>
       </c>
       <c r="D299" t="n">
         <v>-0.083</v>
@@ -40969,13 +40969,13 @@
         <v>-0.0374</v>
       </c>
       <c r="F299" t="n">
-        <v>-0.1286</v>
+        <v>-0.1285</v>
       </c>
       <c r="G299" t="n">
         <v>-0.0374</v>
       </c>
       <c r="M299" t="n">
-        <v>-0.1286</v>
+        <v>-0.1285</v>
       </c>
     </row>
     <row r="300">
@@ -40988,7 +40988,7 @@
         <v>0.037</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.1956</v>
+        <v>-0.1955</v>
       </c>
       <c r="D300" t="n">
         <v>-0.0793</v>
@@ -40997,13 +40997,13 @@
         <v>0.037</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.1956</v>
+        <v>-0.1955</v>
       </c>
       <c r="G300" t="n">
         <v>0.037</v>
       </c>
       <c r="M300" t="n">
-        <v>-0.1956</v>
+        <v>-0.1955</v>
       </c>
     </row>
     <row r="301">
@@ -41212,7 +41212,7 @@
         <v>0.2168</v>
       </c>
       <c r="C308" t="n">
-        <v>-1.7698</v>
+        <v>-1.7697</v>
       </c>
       <c r="D308" t="n">
         <v>-0.7765</v>
@@ -41221,13 +41221,13 @@
         <v>0.2168</v>
       </c>
       <c r="F308" t="n">
-        <v>-1.7698</v>
+        <v>-1.7697</v>
       </c>
       <c r="G308" t="n">
         <v>0.2168</v>
       </c>
       <c r="M308" t="n">
-        <v>-1.7698</v>
+        <v>-1.7697</v>
       </c>
     </row>
     <row r="309">
@@ -41240,7 +41240,7 @@
         <v>0.2192</v>
       </c>
       <c r="C309" t="n">
-        <v>-1.7411</v>
+        <v>-1.741</v>
       </c>
       <c r="D309" t="n">
         <v>-0.7609</v>
@@ -41249,13 +41249,13 @@
         <v>0.2192</v>
       </c>
       <c r="F309" t="n">
-        <v>-1.7411</v>
+        <v>-1.741</v>
       </c>
       <c r="G309" t="n">
         <v>0.2192</v>
       </c>
       <c r="M309" t="n">
-        <v>-1.7411</v>
+        <v>-1.741</v>
       </c>
     </row>
     <row r="310">
@@ -41271,7 +41271,7 @@
         <v>-1.124</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.4474</v>
+        <v>-0.4475</v>
       </c>
       <c r="E310" t="n">
         <v>0.2291</v>
@@ -41548,7 +41548,7 @@
         <v>0.098</v>
       </c>
       <c r="C320" t="n">
-        <v>0.8046</v>
+        <v>0.8047</v>
       </c>
       <c r="D320" t="n">
         <v>0.4513</v>
@@ -41557,13 +41557,13 @@
         <v>0.098</v>
       </c>
       <c r="F320" t="n">
-        <v>0.8046</v>
+        <v>0.8047</v>
       </c>
       <c r="G320" t="n">
         <v>0.098</v>
       </c>
       <c r="M320" t="n">
-        <v>0.8046</v>
+        <v>0.8047</v>
       </c>
     </row>
     <row r="321">
@@ -41576,7 +41576,7 @@
         <v>0.1441</v>
       </c>
       <c r="C321" t="n">
-        <v>0.8763</v>
+        <v>0.8764</v>
       </c>
       <c r="D321" t="n">
         <v>0.5102</v>
@@ -41585,13 +41585,13 @@
         <v>0.1441</v>
       </c>
       <c r="F321" t="n">
-        <v>0.8763</v>
+        <v>0.8764</v>
       </c>
       <c r="G321" t="n">
         <v>0.1441</v>
       </c>
       <c r="M321" t="n">
-        <v>0.8763</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="322">
@@ -41632,7 +41632,7 @@
         <v>-0.2272</v>
       </c>
       <c r="C323" t="n">
-        <v>0.3028</v>
+        <v>0.3029</v>
       </c>
       <c r="D323" t="n">
         <v>0.0378</v>
@@ -41641,13 +41641,13 @@
         <v>-0.2272</v>
       </c>
       <c r="F323" t="n">
-        <v>0.3028</v>
+        <v>0.3029</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2272</v>
       </c>
       <c r="M323" t="n">
-        <v>0.3028</v>
+        <v>0.3029</v>
       </c>
     </row>
     <row r="324">
@@ -42223,7 +42223,7 @@
         <v>0.5609</v>
       </c>
       <c r="D344" t="n">
-        <v>0.2189</v>
+        <v>0.219</v>
       </c>
       <c r="E344" t="n">
         <v>-0.123</v>
@@ -42276,7 +42276,7 @@
         <v>-0.1672</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5244</v>
+        <v>0.5245</v>
       </c>
       <c r="D346" t="n">
         <v>0.1786</v>
@@ -42285,13 +42285,13 @@
         <v>-0.1672</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5244</v>
+        <v>0.5245</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1672</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5244</v>
+        <v>0.5245</v>
       </c>
     </row>
     <row r="347">
@@ -42360,7 +42360,7 @@
         <v>-0.07290000000000001</v>
       </c>
       <c r="C349" t="n">
-        <v>0.5084</v>
+        <v>0.5085</v>
       </c>
       <c r="D349" t="n">
         <v>0.2178</v>
@@ -42369,13 +42369,13 @@
         <v>-0.07290000000000001</v>
       </c>
       <c r="F349" t="n">
-        <v>0.5084</v>
+        <v>0.5085</v>
       </c>
       <c r="G349" t="n">
         <v>-0.07290000000000001</v>
       </c>
       <c r="M349" t="n">
-        <v>0.5084</v>
+        <v>0.5085</v>
       </c>
     </row>
     <row r="350">
@@ -42556,7 +42556,7 @@
         <v>0.1668</v>
       </c>
       <c r="C356" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
       <c r="D356" t="n">
         <v>0.2352</v>
@@ -42565,13 +42565,13 @@
         <v>0.1668</v>
       </c>
       <c r="F356" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
       <c r="G356" t="n">
         <v>0.1668</v>
       </c>
       <c r="M356" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
     </row>
     <row r="357">
@@ -42696,22 +42696,22 @@
         <v>0.2614</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0156</v>
+        <v>0.0157</v>
       </c>
       <c r="D361" t="n">
-        <v>0.1385</v>
+        <v>0.1386</v>
       </c>
       <c r="E361" t="n">
         <v>0.2614</v>
       </c>
       <c r="F361" t="n">
-        <v>0.0156</v>
+        <v>0.0157</v>
       </c>
       <c r="G361" t="n">
         <v>0.2614</v>
       </c>
       <c r="M361" t="n">
-        <v>0.0156</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="362">
@@ -46652,7 +46652,7 @@
         <v>0.2672</v>
       </c>
       <c r="M456" t="n">
-        <v>0.3914</v>
+        <v>0.3915</v>
       </c>
     </row>
     <row r="457">
@@ -50694,7 +50694,7 @@
         <v>-0.6632</v>
       </c>
       <c r="M550" t="n">
-        <v>-0.1479</v>
+        <v>-0.1478</v>
       </c>
     </row>
     <row r="551">
@@ -52516,7 +52516,7 @@
         <v>-0.4141</v>
       </c>
       <c r="D593" t="n">
-        <v>0.0958</v>
+        <v>0.0959</v>
       </c>
       <c r="E593" t="n">
         <v>0.6058</v>
@@ -54091,7 +54091,7 @@
         <v>0.3511</v>
       </c>
       <c r="M629" t="n">
-        <v>0.0654</v>
+        <v>0.0653</v>
       </c>
     </row>
     <row r="630">
@@ -54319,16 +54319,16 @@
         <v>0.4308</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1671</v>
+        <v>-0.1674</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1319</v>
+        <v>0.1317</v>
       </c>
       <c r="E635" t="n">
         <v>0.4308</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1671</v>
+        <v>-0.1674</v>
       </c>
       <c r="G635" t="n">
         <v>0.6662</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4014</v>
+        <v>0.4006</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -3273,7 +3273,7 @@
         <v>-0.715</v>
       </c>
       <c r="K216" t="n">
-        <v>-0.045</v>
+        <v>-0.044</v>
       </c>
     </row>
     <row r="217">
@@ -5678,7 +5678,7 @@
         <v>-0.252</v>
       </c>
       <c r="K401" t="n">
-        <v>-0.962</v>
+        <v>-0.961</v>
       </c>
     </row>
     <row r="402">
@@ -6302,7 +6302,7 @@
         <v>-0.378</v>
       </c>
       <c r="K449" t="n">
-        <v>0.222</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="450">
@@ -8616,7 +8616,7 @@
         <v>0.431</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.167</v>
+        <v>-0.168</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.619</v>
+        <v>10.752</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0588</v>
+        <v>1.0593</v>
       </c>
       <c r="H635" t="n">
-        <v>10.6189</v>
+        <v>10.7519</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37544,7 +37544,7 @@
         <v>-1.5359</v>
       </c>
       <c r="C177" t="n">
-        <v>-2.9541</v>
+        <v>-2.954</v>
       </c>
       <c r="D177" t="n">
         <v>-2.245</v>
@@ -37553,13 +37553,13 @@
         <v>-1.5359</v>
       </c>
       <c r="F177" t="n">
-        <v>-2.9541</v>
+        <v>-2.954</v>
       </c>
       <c r="G177" t="n">
         <v>-1.5359</v>
       </c>
       <c r="M177" t="n">
-        <v>-2.9541</v>
+        <v>-2.954</v>
       </c>
     </row>
     <row r="178">
@@ -37572,7 +37572,7 @@
         <v>-1.4887</v>
       </c>
       <c r="C178" t="n">
-        <v>-2.7641</v>
+        <v>-2.764</v>
       </c>
       <c r="D178" t="n">
         <v>-2.1264</v>
@@ -37581,13 +37581,13 @@
         <v>-1.4887</v>
       </c>
       <c r="F178" t="n">
-        <v>-2.7641</v>
+        <v>-2.764</v>
       </c>
       <c r="G178" t="n">
         <v>-1.4887</v>
       </c>
       <c r="M178" t="n">
-        <v>-2.7641</v>
+        <v>-2.764</v>
       </c>
     </row>
     <row r="179">
@@ -37600,7 +37600,7 @@
         <v>-1.442</v>
       </c>
       <c r="C179" t="n">
-        <v>-2.7889</v>
+        <v>-2.7888</v>
       </c>
       <c r="D179" t="n">
         <v>-2.1154</v>
@@ -37609,13 +37609,13 @@
         <v>-1.442</v>
       </c>
       <c r="F179" t="n">
-        <v>-2.7889</v>
+        <v>-2.7888</v>
       </c>
       <c r="G179" t="n">
         <v>-1.442</v>
       </c>
       <c r="M179" t="n">
-        <v>-2.7889</v>
+        <v>-2.7888</v>
       </c>
     </row>
     <row r="180">
@@ -37684,7 +37684,7 @@
         <v>-1.2581</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.0215</v>
+        <v>-1.0214</v>
       </c>
       <c r="D182" t="n">
         <v>-1.1398</v>
@@ -37693,13 +37693,13 @@
         <v>-1.2581</v>
       </c>
       <c r="F182" t="n">
-        <v>-1.0215</v>
+        <v>-1.0214</v>
       </c>
       <c r="G182" t="n">
         <v>-1.2581</v>
       </c>
       <c r="M182" t="n">
-        <v>-1.0215</v>
+        <v>-1.0214</v>
       </c>
     </row>
     <row r="183">
@@ -37768,7 +37768,7 @@
         <v>-0.7052</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.8905</v>
       </c>
       <c r="D185" t="n">
         <v>-0.7979000000000001</v>
@@ -37777,13 +37777,13 @@
         <v>-0.7052</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.8905</v>
       </c>
       <c r="G185" t="n">
         <v>-0.7052</v>
       </c>
       <c r="M185" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.8905</v>
       </c>
     </row>
     <row r="186">
@@ -37852,7 +37852,7 @@
         <v>-0.7728</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.4748</v>
+        <v>-0.4747</v>
       </c>
       <c r="D188" t="n">
         <v>-0.6238</v>
@@ -37861,13 +37861,13 @@
         <v>-0.7728</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.4748</v>
+        <v>-0.4747</v>
       </c>
       <c r="G188" t="n">
         <v>-0.7728</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.4748</v>
+        <v>-0.4747</v>
       </c>
     </row>
     <row r="189">
@@ -38107,7 +38107,7 @@
         <v>-0.8214</v>
       </c>
       <c r="D197" t="n">
-        <v>-1.4497</v>
+        <v>-1.4496</v>
       </c>
       <c r="E197" t="n">
         <v>-2.0779</v>
@@ -38163,7 +38163,7 @@
         <v>-1.1531</v>
       </c>
       <c r="D199" t="n">
-        <v>-1.6157</v>
+        <v>-1.6156</v>
       </c>
       <c r="E199" t="n">
         <v>-2.0782</v>
@@ -38188,7 +38188,7 @@
         <v>-2.1588</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.0857</v>
+        <v>-1.0856</v>
       </c>
       <c r="D200" t="n">
         <v>-1.6222</v>
@@ -38197,13 +38197,13 @@
         <v>-2.1588</v>
       </c>
       <c r="F200" t="n">
-        <v>-1.0857</v>
+        <v>-1.0856</v>
       </c>
       <c r="G200" t="n">
         <v>-2.1588</v>
       </c>
       <c r="M200" t="n">
-        <v>-1.0857</v>
+        <v>-1.0856</v>
       </c>
     </row>
     <row r="201">
@@ -38244,7 +38244,7 @@
         <v>-2.3253</v>
       </c>
       <c r="C202" t="n">
-        <v>-1.4441</v>
+        <v>-1.444</v>
       </c>
       <c r="D202" t="n">
         <v>-1.8847</v>
@@ -38253,13 +38253,13 @@
         <v>-2.3253</v>
       </c>
       <c r="F202" t="n">
-        <v>-1.4441</v>
+        <v>-1.444</v>
       </c>
       <c r="G202" t="n">
         <v>-2.3253</v>
       </c>
       <c r="M202" t="n">
-        <v>-1.4441</v>
+        <v>-1.444</v>
       </c>
     </row>
     <row r="203">
@@ -38499,7 +38499,7 @@
         <v>-2.0884</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.9622</v>
+        <v>-1.9621</v>
       </c>
       <c r="E211" t="n">
         <v>-1.8359</v>
@@ -38804,7 +38804,7 @@
         <v>-0.7244</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.1524</v>
+        <v>-0.1523</v>
       </c>
       <c r="D222" t="n">
         <v>-0.4384</v>
@@ -38813,13 +38813,13 @@
         <v>-0.7244</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.1524</v>
+        <v>-0.1523</v>
       </c>
       <c r="G222" t="n">
         <v>-0.7244</v>
       </c>
       <c r="M222" t="n">
-        <v>-0.1524</v>
+        <v>-0.1523</v>
       </c>
     </row>
     <row r="223">
@@ -38863,7 +38863,7 @@
         <v>-0.0445</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.3796</v>
+        <v>-0.3795</v>
       </c>
       <c r="E224" t="n">
         <v>-0.7146</v>
@@ -38972,7 +38972,7 @@
         <v>-0.4447</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
       <c r="D228" t="n">
         <v>-0.2139</v>
@@ -38981,13 +38981,13 @@
         <v>-0.4447</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
       <c r="G228" t="n">
         <v>-0.4447</v>
       </c>
       <c r="M228" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="229">
@@ -39000,22 +39000,22 @@
         <v>-0.9002</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.4382</v>
+        <v>-0.4381</v>
       </c>
       <c r="E229" t="n">
         <v>-0.9002</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
       <c r="G229" t="n">
         <v>-0.9002</v>
       </c>
       <c r="M229" t="n">
-        <v>0.0239</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="230">
@@ -39028,7 +39028,7 @@
         <v>-0.617</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0713</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="D230" t="n">
         <v>-0.2728</v>
@@ -39037,13 +39037,13 @@
         <v>-0.617</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0713</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="G230" t="n">
         <v>-0.617</v>
       </c>
       <c r="M230" t="n">
-        <v>0.0713</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="231">
@@ -39056,22 +39056,22 @@
         <v>-0.4083</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.0009</v>
+        <v>-0.0008</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.2046</v>
+        <v>-0.2045</v>
       </c>
       <c r="E231" t="n">
         <v>-0.4083</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0009</v>
+        <v>-0.0008</v>
       </c>
       <c r="G231" t="n">
         <v>-0.4083</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.0009</v>
+        <v>-0.0008</v>
       </c>
     </row>
     <row r="232">
@@ -39084,7 +39084,7 @@
         <v>-0.3912</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.0031</v>
+        <v>-0.003</v>
       </c>
       <c r="D232" t="n">
         <v>-0.1971</v>
@@ -39093,13 +39093,13 @@
         <v>-0.3912</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.0031</v>
+        <v>-0.003</v>
       </c>
       <c r="G232" t="n">
         <v>-0.3912</v>
       </c>
       <c r="M232" t="n">
-        <v>-0.0031</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="233">
@@ -39140,7 +39140,7 @@
         <v>-0.6132</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.3823</v>
+        <v>-0.3822</v>
       </c>
       <c r="D234" t="n">
         <v>-0.4977</v>
@@ -39149,13 +39149,13 @@
         <v>-0.6132</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.3823</v>
+        <v>-0.3822</v>
       </c>
       <c r="G234" t="n">
         <v>-0.6132</v>
       </c>
       <c r="M234" t="n">
-        <v>-0.3823</v>
+        <v>-0.3822</v>
       </c>
     </row>
     <row r="235">
@@ -39252,7 +39252,7 @@
         <v>-0.4319</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.4035</v>
+        <v>-0.4034</v>
       </c>
       <c r="D238" t="n">
         <v>-0.4177</v>
@@ -39261,13 +39261,13 @@
         <v>-0.4319</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.4035</v>
+        <v>-0.4034</v>
       </c>
       <c r="G238" t="n">
         <v>-0.4319</v>
       </c>
       <c r="M238" t="n">
-        <v>-0.4035</v>
+        <v>-0.4034</v>
       </c>
     </row>
     <row r="239">
@@ -39339,7 +39339,7 @@
         <v>-0.5118</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.4728</v>
+        <v>-0.4727</v>
       </c>
       <c r="E241" t="n">
         <v>-0.4337</v>
@@ -39364,7 +39364,7 @@
         <v>-0.2558</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.7224</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="D242" t="n">
         <v>-0.4891</v>
@@ -39373,13 +39373,13 @@
         <v>-0.2558</v>
       </c>
       <c r="F242" t="n">
-        <v>-0.7224</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="G242" t="n">
         <v>-0.2558</v>
       </c>
       <c r="M242" t="n">
-        <v>-0.7224</v>
+        <v>-0.7223000000000001</v>
       </c>
     </row>
     <row r="243">
@@ -39392,7 +39392,7 @@
         <v>-0.3317</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.9378</v>
+        <v>-0.9377</v>
       </c>
       <c r="D243" t="n">
         <v>-0.6347</v>
@@ -39401,13 +39401,13 @@
         <v>-0.3317</v>
       </c>
       <c r="F243" t="n">
-        <v>-0.9378</v>
+        <v>-0.9377</v>
       </c>
       <c r="G243" t="n">
         <v>-0.3317</v>
       </c>
       <c r="M243" t="n">
-        <v>-0.9378</v>
+        <v>-0.9377</v>
       </c>
     </row>
     <row r="244">
@@ -39532,7 +39532,7 @@
         <v>-0.3836</v>
       </c>
       <c r="C248" t="n">
-        <v>-1.1783</v>
+        <v>-1.1782</v>
       </c>
       <c r="D248" t="n">
         <v>-0.7809</v>
@@ -39541,13 +39541,13 @@
         <v>-0.3836</v>
       </c>
       <c r="F248" t="n">
-        <v>-1.1783</v>
+        <v>-1.1782</v>
       </c>
       <c r="G248" t="n">
         <v>-0.3836</v>
       </c>
       <c r="M248" t="n">
-        <v>-1.1783</v>
+        <v>-1.1782</v>
       </c>
     </row>
     <row r="249">
@@ -39563,7 +39563,7 @@
         <v>-1.3629</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.9127</v>
       </c>
       <c r="E249" t="n">
         <v>-0.4626</v>
@@ -39588,7 +39588,7 @@
         <v>-0.5951</v>
       </c>
       <c r="C250" t="n">
-        <v>-1.3084</v>
+        <v>-1.3083</v>
       </c>
       <c r="D250" t="n">
         <v>-0.9517</v>
@@ -39597,13 +39597,13 @@
         <v>-0.5951</v>
       </c>
       <c r="F250" t="n">
-        <v>-1.3084</v>
+        <v>-1.3083</v>
       </c>
       <c r="G250" t="n">
         <v>-0.5951</v>
       </c>
       <c r="M250" t="n">
-        <v>-1.3084</v>
+        <v>-1.3083</v>
       </c>
     </row>
     <row r="251">
@@ -39619,7 +39619,7 @@
         <v>-1.1943</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.9341</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="E251" t="n">
         <v>-0.6738</v>
@@ -39840,7 +39840,7 @@
         <v>-0.3875</v>
       </c>
       <c r="C259" t="n">
-        <v>-1.0972</v>
+        <v>-1.0971</v>
       </c>
       <c r="D259" t="n">
         <v>-0.7423</v>
@@ -39849,13 +39849,13 @@
         <v>-0.3875</v>
       </c>
       <c r="F259" t="n">
-        <v>-1.0972</v>
+        <v>-1.0971</v>
       </c>
       <c r="G259" t="n">
         <v>-0.3875</v>
       </c>
       <c r="M259" t="n">
-        <v>-1.0972</v>
+        <v>-1.0971</v>
       </c>
     </row>
     <row r="260">
@@ -39980,22 +39980,22 @@
         <v>0.1087</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.836</v>
+        <v>-0.8359</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.3637</v>
+        <v>-0.3636</v>
       </c>
       <c r="E264" t="n">
         <v>0.1087</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.836</v>
+        <v>-0.8359</v>
       </c>
       <c r="G264" t="n">
         <v>0.1087</v>
       </c>
       <c r="M264" t="n">
-        <v>-0.836</v>
+        <v>-0.8359</v>
       </c>
     </row>
     <row r="265">
@@ -40008,7 +40008,7 @@
         <v>0.2189</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.8707</v>
+        <v>-0.8706</v>
       </c>
       <c r="D265" t="n">
         <v>-0.3259</v>
@@ -40017,13 +40017,13 @@
         <v>0.2189</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.8707</v>
+        <v>-0.8706</v>
       </c>
       <c r="G265" t="n">
         <v>0.2189</v>
       </c>
       <c r="M265" t="n">
-        <v>-0.8707</v>
+        <v>-0.8706</v>
       </c>
     </row>
     <row r="266">
@@ -40095,7 +40095,7 @@
         <v>-0.8909</v>
       </c>
       <c r="D268" t="n">
-        <v>-0.4251</v>
+        <v>-0.425</v>
       </c>
       <c r="E268" t="n">
         <v>0.0408</v>
@@ -40260,7 +40260,7 @@
         <v>0.1586</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2269</v>
+        <v>0.227</v>
       </c>
       <c r="D274" t="n">
         <v>0.1928</v>
@@ -40269,13 +40269,13 @@
         <v>0.1586</v>
       </c>
       <c r="F274" t="n">
-        <v>0.2269</v>
+        <v>0.227</v>
       </c>
       <c r="G274" t="n">
         <v>0.1586</v>
       </c>
       <c r="M274" t="n">
-        <v>0.2269</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="275">
@@ -40316,22 +40316,22 @@
         <v>0.2677</v>
       </c>
       <c r="C276" t="n">
-        <v>0.1687</v>
+        <v>0.1688</v>
       </c>
       <c r="D276" t="n">
-        <v>0.2182</v>
+        <v>0.2183</v>
       </c>
       <c r="E276" t="n">
         <v>0.2677</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1687</v>
+        <v>0.1688</v>
       </c>
       <c r="G276" t="n">
         <v>0.2677</v>
       </c>
       <c r="M276" t="n">
-        <v>0.1687</v>
+        <v>0.1688</v>
       </c>
     </row>
     <row r="277">
@@ -40403,7 +40403,7 @@
         <v>0.5014999999999999</v>
       </c>
       <c r="D279" t="n">
-        <v>0.3847</v>
+        <v>0.3848</v>
       </c>
       <c r="E279" t="n">
         <v>0.268</v>
@@ -40487,7 +40487,7 @@
         <v>-0.076</v>
       </c>
       <c r="D282" t="n">
-        <v>0.4344</v>
+        <v>0.4345</v>
       </c>
       <c r="E282" t="n">
         <v>0.9449</v>
@@ -40512,7 +40512,7 @@
         <v>0.906</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.0721</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="D283" t="n">
         <v>0.417</v>
@@ -40521,13 +40521,13 @@
         <v>0.906</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.0721</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G283" t="n">
         <v>0.906</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.0721</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="284">
@@ -40568,7 +40568,7 @@
         <v>1.0571</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.1006</v>
+        <v>-0.1005</v>
       </c>
       <c r="D285" t="n">
         <v>0.4783</v>
@@ -40577,13 +40577,13 @@
         <v>1.0571</v>
       </c>
       <c r="F285" t="n">
-        <v>-0.1006</v>
+        <v>-0.1005</v>
       </c>
       <c r="G285" t="n">
         <v>1.0571</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.1006</v>
+        <v>-0.1005</v>
       </c>
     </row>
     <row r="286">
@@ -40596,7 +40596,7 @@
         <v>1.15</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.0326</v>
+        <v>-0.0325</v>
       </c>
       <c r="D286" t="n">
         <v>0.5587</v>
@@ -40605,13 +40605,13 @@
         <v>1.15</v>
       </c>
       <c r="F286" t="n">
-        <v>-0.0326</v>
+        <v>-0.0325</v>
       </c>
       <c r="G286" t="n">
         <v>1.15</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.0326</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="287">
@@ -40624,22 +40624,22 @@
         <v>1.1542</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.1081</v>
+        <v>-0.108</v>
       </c>
       <c r="D287" t="n">
-        <v>0.523</v>
+        <v>0.5231</v>
       </c>
       <c r="E287" t="n">
         <v>1.1542</v>
       </c>
       <c r="F287" t="n">
-        <v>-0.1081</v>
+        <v>-0.108</v>
       </c>
       <c r="G287" t="n">
         <v>1.1542</v>
       </c>
       <c r="M287" t="n">
-        <v>-0.1081</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="288">
@@ -40652,7 +40652,7 @@
         <v>1.0703</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.1085</v>
+        <v>-0.1084</v>
       </c>
       <c r="D288" t="n">
         <v>0.4809</v>
@@ -40661,13 +40661,13 @@
         <v>1.0703</v>
       </c>
       <c r="F288" t="n">
-        <v>-0.1085</v>
+        <v>-0.1084</v>
       </c>
       <c r="G288" t="n">
         <v>1.0703</v>
       </c>
       <c r="M288" t="n">
-        <v>-0.1085</v>
+        <v>-0.1084</v>
       </c>
     </row>
     <row r="289">
@@ -40736,7 +40736,7 @@
         <v>0.8957000000000001</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.1337</v>
+        <v>-0.1336</v>
       </c>
       <c r="D291" t="n">
         <v>0.381</v>
@@ -40745,13 +40745,13 @@
         <v>0.8957000000000001</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.1337</v>
+        <v>-0.1336</v>
       </c>
       <c r="G291" t="n">
         <v>0.8957000000000001</v>
       </c>
       <c r="M291" t="n">
-        <v>-0.1337</v>
+        <v>-0.1336</v>
       </c>
     </row>
     <row r="292">
@@ -40792,7 +40792,7 @@
         <v>0.1401</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.1264</v>
+        <v>-0.1263</v>
       </c>
       <c r="D293" t="n">
         <v>0.0069</v>
@@ -40801,13 +40801,13 @@
         <v>0.1401</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.1264</v>
+        <v>-0.1263</v>
       </c>
       <c r="G293" t="n">
         <v>0.1401</v>
       </c>
       <c r="M293" t="n">
-        <v>-0.1264</v>
+        <v>-0.1263</v>
       </c>
     </row>
     <row r="294">
@@ -40876,7 +40876,7 @@
         <v>0.0151</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1692</v>
+        <v>0.1693</v>
       </c>
       <c r="D296" t="n">
         <v>0.0922</v>
@@ -40885,13 +40885,13 @@
         <v>0.0151</v>
       </c>
       <c r="F296" t="n">
-        <v>0.1692</v>
+        <v>0.1693</v>
       </c>
       <c r="G296" t="n">
         <v>0.0151</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1692</v>
+        <v>0.1693</v>
       </c>
     </row>
     <row r="297">
@@ -40932,22 +40932,22 @@
         <v>-0.1118</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.1642</v>
+        <v>-0.1641</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.138</v>
+        <v>-0.1379</v>
       </c>
       <c r="E298" t="n">
         <v>-0.1118</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.1642</v>
+        <v>-0.1641</v>
       </c>
       <c r="G298" t="n">
         <v>-0.1118</v>
       </c>
       <c r="M298" t="n">
-        <v>-0.1642</v>
+        <v>-0.1641</v>
       </c>
     </row>
     <row r="299">
@@ -40963,7 +40963,7 @@
         <v>-0.1285</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.083</v>
+        <v>-0.0829</v>
       </c>
       <c r="E299" t="n">
         <v>-0.0374</v>
@@ -41072,7 +41072,7 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="C303" t="n">
-        <v>-1.4312</v>
+        <v>-1.4311</v>
       </c>
       <c r="D303" t="n">
         <v>-0.6697</v>
@@ -41081,13 +41081,13 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="F303" t="n">
-        <v>-1.4312</v>
+        <v>-1.4311</v>
       </c>
       <c r="G303" t="n">
         <v>0.09180000000000001</v>
       </c>
       <c r="M303" t="n">
-        <v>-1.4312</v>
+        <v>-1.4311</v>
       </c>
     </row>
     <row r="304">
@@ -41128,7 +41128,7 @@
         <v>0.1738</v>
       </c>
       <c r="C305" t="n">
-        <v>-1.663</v>
+        <v>-1.6629</v>
       </c>
       <c r="D305" t="n">
         <v>-0.7446</v>
@@ -41137,13 +41137,13 @@
         <v>0.1738</v>
       </c>
       <c r="F305" t="n">
-        <v>-1.663</v>
+        <v>-1.6629</v>
       </c>
       <c r="G305" t="n">
         <v>0.1738</v>
       </c>
       <c r="M305" t="n">
-        <v>-1.663</v>
+        <v>-1.6629</v>
       </c>
     </row>
     <row r="306">
@@ -41268,22 +41268,22 @@
         <v>0.2291</v>
       </c>
       <c r="C310" t="n">
-        <v>-1.124</v>
+        <v>-1.1239</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.4475</v>
+        <v>-0.4474</v>
       </c>
       <c r="E310" t="n">
         <v>0.2291</v>
       </c>
       <c r="F310" t="n">
-        <v>-1.124</v>
+        <v>-1.1239</v>
       </c>
       <c r="G310" t="n">
         <v>0.2291</v>
       </c>
       <c r="M310" t="n">
-        <v>-1.124</v>
+        <v>-1.1239</v>
       </c>
     </row>
     <row r="311">
@@ -41635,7 +41635,7 @@
         <v>0.3029</v>
       </c>
       <c r="D323" t="n">
-        <v>0.0378</v>
+        <v>0.0379</v>
       </c>
       <c r="E323" t="n">
         <v>-0.2272</v>
@@ -41663,7 +41663,7 @@
         <v>0.2109</v>
       </c>
       <c r="D324" t="n">
-        <v>0.0171</v>
+        <v>0.0172</v>
       </c>
       <c r="E324" t="n">
         <v>-0.1766</v>
@@ -41688,22 +41688,22 @@
         <v>-0.1812</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1907</v>
+        <v>0.1908</v>
       </c>
       <c r="D325" t="n">
-        <v>0.0047</v>
+        <v>0.0048</v>
       </c>
       <c r="E325" t="n">
         <v>-0.1812</v>
       </c>
       <c r="F325" t="n">
-        <v>0.1907</v>
+        <v>0.1908</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1812</v>
       </c>
       <c r="M325" t="n">
-        <v>0.1907</v>
+        <v>0.1908</v>
       </c>
     </row>
     <row r="326">
@@ -41719,7 +41719,7 @@
         <v>0.1851</v>
       </c>
       <c r="D326" t="n">
-        <v>-0.0364</v>
+        <v>-0.0363</v>
       </c>
       <c r="E326" t="n">
         <v>-0.2578</v>
@@ -41744,7 +41744,7 @@
         <v>-0.2416</v>
       </c>
       <c r="C327" t="n">
-        <v>0.4111</v>
+        <v>0.4112</v>
       </c>
       <c r="D327" t="n">
         <v>0.0848</v>
@@ -41753,13 +41753,13 @@
         <v>-0.2416</v>
       </c>
       <c r="F327" t="n">
-        <v>0.4111</v>
+        <v>0.4112</v>
       </c>
       <c r="G327" t="n">
         <v>-0.2416</v>
       </c>
       <c r="M327" t="n">
-        <v>0.4111</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="328">
@@ -41831,7 +41831,7 @@
         <v>-0.1384</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.1775</v>
+        <v>-0.1774</v>
       </c>
       <c r="E330" t="n">
         <v>-0.2165</v>
@@ -41887,7 +41887,7 @@
         <v>-0.2563</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.2139</v>
+        <v>-0.2138</v>
       </c>
       <c r="E332" t="n">
         <v>-0.1714</v>
@@ -41940,7 +41940,7 @@
         <v>-0.1205</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1159</v>
+        <v>-0.1158</v>
       </c>
       <c r="D334" t="n">
         <v>-0.1182</v>
@@ -41949,13 +41949,13 @@
         <v>-0.1205</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1159</v>
+        <v>-0.1158</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1205</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1159</v>
+        <v>-0.1158</v>
       </c>
     </row>
     <row r="335">
@@ -42052,7 +42052,7 @@
         <v>-0.1249</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2474</v>
+        <v>-0.2473</v>
       </c>
       <c r="D338" t="n">
         <v>-0.1861</v>
@@ -42061,13 +42061,13 @@
         <v>-0.1249</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2474</v>
+        <v>-0.2473</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1249</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2474</v>
+        <v>-0.2473</v>
       </c>
     </row>
     <row r="339">
@@ -42080,7 +42080,7 @@
         <v>-0.124</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2096</v>
+        <v>-0.2095</v>
       </c>
       <c r="D339" t="n">
         <v>-0.1668</v>
@@ -42089,13 +42089,13 @@
         <v>-0.124</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.2096</v>
+        <v>-0.2095</v>
       </c>
       <c r="G339" t="n">
         <v>-0.124</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.2096</v>
+        <v>-0.2095</v>
       </c>
     </row>
     <row r="340">
@@ -42164,7 +42164,7 @@
         <v>-0.1217</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2253</v>
+        <v>0.2254</v>
       </c>
       <c r="D342" t="n">
         <v>0.0518</v>
@@ -42173,13 +42173,13 @@
         <v>-0.1217</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2253</v>
+        <v>0.2254</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1217</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2253</v>
+        <v>0.2254</v>
       </c>
     </row>
     <row r="343">
@@ -42192,22 +42192,22 @@
         <v>-0.1222</v>
       </c>
       <c r="C343" t="n">
-        <v>0.341</v>
+        <v>0.3411</v>
       </c>
       <c r="D343" t="n">
-        <v>0.1094</v>
+        <v>0.1095</v>
       </c>
       <c r="E343" t="n">
         <v>-0.1222</v>
       </c>
       <c r="F343" t="n">
-        <v>0.341</v>
+        <v>0.3411</v>
       </c>
       <c r="G343" t="n">
         <v>-0.1222</v>
       </c>
       <c r="M343" t="n">
-        <v>0.341</v>
+        <v>0.3411</v>
       </c>
     </row>
     <row r="344">
@@ -42248,22 +42248,22 @@
         <v>-0.1667</v>
       </c>
       <c r="C345" t="n">
-        <v>0.4449</v>
+        <v>0.445</v>
       </c>
       <c r="D345" t="n">
-        <v>0.1391</v>
+        <v>0.1392</v>
       </c>
       <c r="E345" t="n">
         <v>-0.1667</v>
       </c>
       <c r="F345" t="n">
-        <v>0.4449</v>
+        <v>0.445</v>
       </c>
       <c r="G345" t="n">
         <v>-0.1667</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4449</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="346">
@@ -42279,7 +42279,7 @@
         <v>0.5245</v>
       </c>
       <c r="D346" t="n">
-        <v>0.1786</v>
+        <v>0.1787</v>
       </c>
       <c r="E346" t="n">
         <v>-0.1672</v>
@@ -42304,7 +42304,7 @@
         <v>-0.1673</v>
       </c>
       <c r="C347" t="n">
-        <v>0.3509</v>
+        <v>0.351</v>
       </c>
       <c r="D347" t="n">
         <v>0.09180000000000001</v>
@@ -42313,13 +42313,13 @@
         <v>-0.1673</v>
       </c>
       <c r="F347" t="n">
-        <v>0.3509</v>
+        <v>0.351</v>
       </c>
       <c r="G347" t="n">
         <v>-0.1673</v>
       </c>
       <c r="M347" t="n">
-        <v>0.3509</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="348">
@@ -42615,7 +42615,7 @@
         <v>0.2659</v>
       </c>
       <c r="D358" t="n">
-        <v>0.2369</v>
+        <v>0.237</v>
       </c>
       <c r="E358" t="n">
         <v>0.208</v>
@@ -42668,7 +42668,7 @@
         <v>0.2125</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0185</v>
+        <v>-0.0184</v>
       </c>
       <c r="D360" t="n">
         <v>0.097</v>
@@ -42677,13 +42677,13 @@
         <v>0.2125</v>
       </c>
       <c r="F360" t="n">
-        <v>-0.0185</v>
+        <v>-0.0184</v>
       </c>
       <c r="G360" t="n">
         <v>0.2125</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.0185</v>
+        <v>-0.0184</v>
       </c>
     </row>
     <row r="361">
@@ -42972,7 +42972,7 @@
         <v>-0.407</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.3747</v>
+        <v>-0.3746</v>
       </c>
       <c r="D370" t="n">
         <v>-0.3908</v>
@@ -42981,7 +42981,7 @@
         <v>-0.407</v>
       </c>
       <c r="F370" t="n">
-        <v>-0.3747</v>
+        <v>-0.3746</v>
       </c>
       <c r="G370" t="n">
         <v>0.2594</v>
@@ -42990,7 +42990,7 @@
         <v>-1.0733</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.3747</v>
+        <v>-0.3746</v>
       </c>
     </row>
     <row r="371">
@@ -43513,7 +43513,7 @@
         <v>0.2889</v>
       </c>
       <c r="M383" t="n">
-        <v>0.7605</v>
+        <v>0.7606000000000001</v>
       </c>
     </row>
     <row r="384">
@@ -43599,7 +43599,7 @@
         <v>0.14</v>
       </c>
       <c r="M385" t="n">
-        <v>0.7128</v>
+        <v>0.7129</v>
       </c>
     </row>
     <row r="386">
@@ -43685,7 +43685,7 @@
         <v>-0.1281</v>
       </c>
       <c r="M387" t="n">
-        <v>0.8375</v>
+        <v>0.8376</v>
       </c>
     </row>
     <row r="388">
@@ -44416,7 +44416,7 @@
         <v>-1.671</v>
       </c>
       <c r="M404" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0939</v>
       </c>
     </row>
     <row r="405">
@@ -44773,7 +44773,7 @@
         <v>-0.2382</v>
       </c>
       <c r="C413" t="n">
-        <v>-1.1659</v>
+        <v>-1.1658</v>
       </c>
       <c r="D413" t="n">
         <v>-0.702</v>
@@ -44782,7 +44782,7 @@
         <v>-0.2382</v>
       </c>
       <c r="F413" t="n">
-        <v>-1.1659</v>
+        <v>-1.1658</v>
       </c>
       <c r="G413" t="n">
         <v>0.452</v>
@@ -45061,7 +45061,7 @@
         <v>-3.0006</v>
       </c>
       <c r="M419" t="n">
-        <v>-0.7292</v>
+        <v>-0.7291</v>
       </c>
     </row>
     <row r="420">
@@ -45233,7 +45233,7 @@
         <v>-1.9019</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.0495</v>
+        <v>-0.0494</v>
       </c>
     </row>
     <row r="424">
@@ -45362,7 +45362,7 @@
         <v>-0.7655</v>
       </c>
       <c r="M426" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="427">
@@ -45491,7 +45491,7 @@
         <v>-0.3184</v>
       </c>
       <c r="M429" t="n">
-        <v>0.5554</v>
+        <v>0.5555</v>
       </c>
     </row>
     <row r="430">
@@ -45534,7 +45534,7 @@
         <v>-0.2206</v>
       </c>
       <c r="M430" t="n">
-        <v>0.5224</v>
+        <v>0.5225</v>
       </c>
     </row>
     <row r="431">
@@ -45851,7 +45851,7 @@
         <v>0.2809</v>
       </c>
       <c r="D438" t="n">
-        <v>-0.1694</v>
+        <v>-0.1693</v>
       </c>
       <c r="E438" t="n">
         <v>-0.6196</v>
@@ -46493,7 +46493,7 @@
         <v>-0.3312</v>
       </c>
       <c r="C453" t="n">
-        <v>0.2511</v>
+        <v>0.2512</v>
       </c>
       <c r="D453" t="n">
         <v>-0.04</v>
@@ -46502,7 +46502,7 @@
         <v>-0.3312</v>
       </c>
       <c r="F453" t="n">
-        <v>0.2511</v>
+        <v>0.2512</v>
       </c>
       <c r="G453" t="n">
         <v>0.3176</v>
@@ -46579,7 +46579,7 @@
         <v>-0.4767</v>
       </c>
       <c r="C455" t="n">
-        <v>0.2626</v>
+        <v>0.2627</v>
       </c>
       <c r="D455" t="n">
         <v>-0.107</v>
@@ -46588,7 +46588,7 @@
         <v>-0.4767</v>
       </c>
       <c r="F455" t="n">
-        <v>0.2626</v>
+        <v>0.2627</v>
       </c>
       <c r="G455" t="n">
         <v>0.1722</v>
@@ -46953,7 +46953,7 @@
         <v>0.4357</v>
       </c>
       <c r="M463" t="n">
-        <v>0.3316</v>
+        <v>0.3317</v>
       </c>
     </row>
     <row r="464">
@@ -47039,7 +47039,7 @@
         <v>0.4487</v>
       </c>
       <c r="M465" t="n">
-        <v>0.38</v>
+        <v>0.3801</v>
       </c>
     </row>
     <row r="466">
@@ -47297,7 +47297,7 @@
         <v>0.6042999999999999</v>
       </c>
       <c r="M471" t="n">
-        <v>0.3016</v>
+        <v>0.3017</v>
       </c>
     </row>
     <row r="472">
@@ -47426,7 +47426,7 @@
         <v>0.6924</v>
       </c>
       <c r="M474" t="n">
-        <v>0.402</v>
+        <v>0.4021</v>
       </c>
     </row>
     <row r="475">
@@ -48643,7 +48643,7 @@
         <v>0.5856</v>
       </c>
       <c r="C503" t="n">
-        <v>0.718</v>
+        <v>0.7181</v>
       </c>
       <c r="D503" t="n">
         <v>0.6518</v>
@@ -48652,7 +48652,7 @@
         <v>0.5856</v>
       </c>
       <c r="F503" t="n">
-        <v>0.718</v>
+        <v>0.7181</v>
       </c>
       <c r="G503" t="n">
         <v>0.1054</v>
@@ -48673,7 +48673,7 @@
         <v>0.4544</v>
       </c>
       <c r="M503" t="n">
-        <v>0.4315</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="504">
@@ -48974,7 +48974,7 @@
         <v>0.4044</v>
       </c>
       <c r="M510" t="n">
-        <v>0.569</v>
+        <v>0.5691000000000001</v>
       </c>
     </row>
     <row r="511">
@@ -49103,7 +49103,7 @@
         <v>0.3663</v>
       </c>
       <c r="M513" t="n">
-        <v>0.5938</v>
+        <v>0.5939</v>
       </c>
     </row>
     <row r="514">
@@ -49503,7 +49503,7 @@
         <v>0.4349</v>
       </c>
       <c r="C523" t="n">
-        <v>0.4147</v>
+        <v>0.4148</v>
       </c>
       <c r="D523" t="n">
         <v>0.4248</v>
@@ -49512,7 +49512,7 @@
         <v>0.4349</v>
       </c>
       <c r="F523" t="n">
-        <v>0.4147</v>
+        <v>0.4148</v>
       </c>
       <c r="G523" t="n">
         <v>0.4974</v>
@@ -50135,7 +50135,7 @@
         <v>-0.0519</v>
       </c>
       <c r="M537" t="n">
-        <v>0.1858</v>
+        <v>0.1859</v>
       </c>
     </row>
     <row r="538">
@@ -50178,7 +50178,7 @@
         <v>-0.0247</v>
       </c>
       <c r="M538" t="n">
-        <v>0.1653</v>
+        <v>0.1654</v>
       </c>
     </row>
     <row r="539">
@@ -50264,7 +50264,7 @@
         <v>-0.0309</v>
       </c>
       <c r="M540" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="541">
@@ -51124,7 +51124,7 @@
         <v>-0.4763</v>
       </c>
       <c r="M560" t="n">
-        <v>-0.2704</v>
+        <v>-0.2703</v>
       </c>
     </row>
     <row r="561">
@@ -51511,7 +51511,7 @@
         <v>0.439</v>
       </c>
       <c r="M569" t="n">
-        <v>0.057</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="570">
@@ -51683,7 +51683,7 @@
         <v>0.4779</v>
       </c>
       <c r="M573" t="n">
-        <v>0.1098</v>
+        <v>0.1099</v>
       </c>
     </row>
     <row r="574">
@@ -52156,7 +52156,7 @@
         <v>0.6971000000000001</v>
       </c>
       <c r="M584" t="n">
-        <v>-0.4689</v>
+        <v>-0.4688</v>
       </c>
     </row>
     <row r="585">
@@ -52973,7 +52973,7 @@
         <v>0.4768</v>
       </c>
       <c r="M603" t="n">
-        <v>-0.4967</v>
+        <v>-0.4966</v>
       </c>
     </row>
     <row r="604">
@@ -53446,7 +53446,7 @@
         <v>0.3886</v>
       </c>
       <c r="M614" t="n">
-        <v>-0.0405</v>
+        <v>-0.0404</v>
       </c>
     </row>
     <row r="615">
@@ -53489,7 +53489,7 @@
         <v>0.3955</v>
       </c>
       <c r="M615" t="n">
-        <v>0.0134</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="616">
@@ -54091,7 +54091,7 @@
         <v>0.3511</v>
       </c>
       <c r="M629" t="n">
-        <v>0.0653</v>
+        <v>0.0654</v>
       </c>
     </row>
     <row r="630">
@@ -54319,16 +54319,16 @@
         <v>0.4308</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1674</v>
+        <v>-0.1683</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1317</v>
+        <v>0.1313</v>
       </c>
       <c r="E635" t="n">
         <v>0.4308</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1674</v>
+        <v>-0.1683</v>
       </c>
       <c r="G635" t="n">
         <v>0.6662</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.4006</v>
+        <v>0.3979</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -2935,7 +2935,7 @@
         <v>-2.021</v>
       </c>
       <c r="K190" t="n">
-        <v>-1.155</v>
+        <v>-1.154</v>
       </c>
     </row>
     <row r="191">
@@ -3767,7 +3767,7 @@
         <v>0.073</v>
       </c>
       <c r="K254" t="n">
-        <v>-0.886</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="255">
@@ -4157,7 +4157,7 @@
         <v>0.915</v>
       </c>
       <c r="K284" t="n">
-        <v>-0.142</v>
+        <v>-0.141</v>
       </c>
     </row>
     <row r="285">
@@ -4248,7 +4248,7 @@
         <v>-0.037</v>
       </c>
       <c r="K291" t="n">
-        <v>-0.129</v>
+        <v>-0.128</v>
       </c>
     </row>
     <row r="292">
@@ -4261,7 +4261,7 @@
         <v>0.037</v>
       </c>
       <c r="K292" t="n">
-        <v>-0.196</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="293">
@@ -4937,7 +4937,7 @@
         <v>-0.028</v>
       </c>
       <c r="K344" t="n">
-        <v>1.025</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="345">
@@ -5145,7 +5145,7 @@
         <v>-0.478</v>
       </c>
       <c r="K360" t="n">
-        <v>-0.108</v>
+        <v>-0.107</v>
       </c>
     </row>
     <row r="361">
@@ -6081,7 +6081,7 @@
         <v>-0.737</v>
       </c>
       <c r="K432" t="n">
-        <v>0.283</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="433">
@@ -8616,7 +8616,7 @@
         <v>0.431</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.168</v>
+        <v>-0.169</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.752</v>
+        <v>10.885</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="13">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0593</v>
+        <v>1.0594</v>
       </c>
       <c r="H635" t="n">
-        <v>10.7519</v>
+        <v>10.8851</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37656,7 +37656,7 @@
         <v>-0.2916</v>
       </c>
       <c r="C181" t="n">
-        <v>-1.9569</v>
+        <v>-1.9568</v>
       </c>
       <c r="D181" t="n">
         <v>-1.1242</v>
@@ -37665,13 +37665,13 @@
         <v>-0.2916</v>
       </c>
       <c r="F181" t="n">
-        <v>-1.9569</v>
+        <v>-1.9568</v>
       </c>
       <c r="G181" t="n">
         <v>-0.2916</v>
       </c>
       <c r="M181" t="n">
-        <v>-1.9569</v>
+        <v>-1.9568</v>
       </c>
     </row>
     <row r="182">
@@ -37687,7 +37687,7 @@
         <v>-1.0214</v>
       </c>
       <c r="D182" t="n">
-        <v>-1.1398</v>
+        <v>-1.1397</v>
       </c>
       <c r="E182" t="n">
         <v>-1.2581</v>
@@ -37740,7 +37740,7 @@
         <v>-1.2881</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.9137</v>
+        <v>-0.9136</v>
       </c>
       <c r="D184" t="n">
         <v>-1.1009</v>
@@ -37749,13 +37749,13 @@
         <v>-1.2881</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.9137</v>
+        <v>-0.9136</v>
       </c>
       <c r="G184" t="n">
         <v>-1.2881</v>
       </c>
       <c r="M184" t="n">
-        <v>-0.9137</v>
+        <v>-0.9136</v>
       </c>
     </row>
     <row r="185">
@@ -37771,7 +37771,7 @@
         <v>-0.8905</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7978</v>
       </c>
       <c r="E185" t="n">
         <v>-0.7052</v>
@@ -37796,7 +37796,7 @@
         <v>-0.6961000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.7712</v>
+        <v>-0.7711</v>
       </c>
       <c r="D186" t="n">
         <v>-0.7336</v>
@@ -37805,13 +37805,13 @@
         <v>-0.6961000000000001</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.7712</v>
+        <v>-0.7711</v>
       </c>
       <c r="G186" t="n">
         <v>-0.6961000000000001</v>
       </c>
       <c r="M186" t="n">
-        <v>-0.7712</v>
+        <v>-0.7711</v>
       </c>
     </row>
     <row r="187">
@@ -37883,7 +37883,7 @@
         <v>-0.4739</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6385</v>
       </c>
       <c r="E189" t="n">
         <v>-0.8032</v>
@@ -37936,7 +37936,7 @@
         <v>-1.0616</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.2029</v>
+        <v>-0.2028</v>
       </c>
       <c r="D191" t="n">
         <v>-0.6322</v>
@@ -37945,13 +37945,13 @@
         <v>-1.0616</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.2029</v>
+        <v>-0.2028</v>
       </c>
       <c r="G191" t="n">
         <v>-1.0616</v>
       </c>
       <c r="M191" t="n">
-        <v>-0.2029</v>
+        <v>-0.2028</v>
       </c>
     </row>
     <row r="192">
@@ -37992,7 +37992,7 @@
         <v>-1.4169</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0892</v>
+        <v>0.0893</v>
       </c>
       <c r="D193" t="n">
         <v>-0.6637999999999999</v>
@@ -38001,13 +38001,13 @@
         <v>-1.4169</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0892</v>
+        <v>0.0893</v>
       </c>
       <c r="G193" t="n">
         <v>-1.4169</v>
       </c>
       <c r="M193" t="n">
-        <v>0.0892</v>
+        <v>0.0893</v>
       </c>
     </row>
     <row r="194">
@@ -38020,7 +38020,7 @@
         <v>-1.261</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.7326</v>
+        <v>-0.7325</v>
       </c>
       <c r="D194" t="n">
         <v>-0.9968</v>
@@ -38029,13 +38029,13 @@
         <v>-1.261</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.7326</v>
+        <v>-0.7325</v>
       </c>
       <c r="G194" t="n">
         <v>-1.261</v>
       </c>
       <c r="M194" t="n">
-        <v>-0.7326</v>
+        <v>-0.7325</v>
       </c>
     </row>
     <row r="195">
@@ -38104,7 +38104,7 @@
         <v>-2.0779</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.8214</v>
+        <v>-0.8213</v>
       </c>
       <c r="D197" t="n">
         <v>-1.4496</v>
@@ -38113,13 +38113,13 @@
         <v>-2.0779</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.8214</v>
+        <v>-0.8213</v>
       </c>
       <c r="G197" t="n">
         <v>-2.0779</v>
       </c>
       <c r="M197" t="n">
-        <v>-0.8214</v>
+        <v>-0.8213</v>
       </c>
     </row>
     <row r="198">
@@ -38275,7 +38275,7 @@
         <v>-1.8423</v>
       </c>
       <c r="D203" t="n">
-        <v>-1.9329</v>
+        <v>-1.9328</v>
       </c>
       <c r="E203" t="n">
         <v>-2.0234</v>
@@ -38443,7 +38443,7 @@
         <v>-2.2285</v>
       </c>
       <c r="D209" t="n">
-        <v>-2.0701</v>
+        <v>-2.07</v>
       </c>
       <c r="E209" t="n">
         <v>-1.9116</v>
@@ -38552,7 +38552,7 @@
         <v>-1.6243</v>
       </c>
       <c r="C213" t="n">
-        <v>-1.317</v>
+        <v>-1.3169</v>
       </c>
       <c r="D213" t="n">
         <v>-1.4706</v>
@@ -38561,13 +38561,13 @@
         <v>-1.6243</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.317</v>
+        <v>-1.3169</v>
       </c>
       <c r="G213" t="n">
         <v>-1.6243</v>
       </c>
       <c r="M213" t="n">
-        <v>-1.317</v>
+        <v>-1.3169</v>
       </c>
     </row>
     <row r="214">
@@ -38580,7 +38580,7 @@
         <v>-1.5042</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7343</v>
       </c>
       <c r="D214" t="n">
         <v>-1.1193</v>
@@ -38589,13 +38589,13 @@
         <v>-1.5042</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7343</v>
       </c>
       <c r="G214" t="n">
         <v>-1.5042</v>
       </c>
       <c r="M214" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7343</v>
       </c>
     </row>
     <row r="215">
@@ -38636,22 +38636,22 @@
         <v>-1.4441</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.5062</v>
+        <v>-0.5061</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.9752</v>
+        <v>-0.9751</v>
       </c>
       <c r="E216" t="n">
         <v>-1.4441</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.5062</v>
+        <v>-0.5061</v>
       </c>
       <c r="G216" t="n">
         <v>-1.4441</v>
       </c>
       <c r="M216" t="n">
-        <v>-0.5062</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="217">
@@ -38664,7 +38664,7 @@
         <v>-1.438</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.0907</v>
+        <v>-0.0906</v>
       </c>
       <c r="D217" t="n">
         <v>-0.7643</v>
@@ -38673,13 +38673,13 @@
         <v>-1.438</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.0907</v>
+        <v>-0.0906</v>
       </c>
       <c r="G217" t="n">
         <v>-1.438</v>
       </c>
       <c r="M217" t="n">
-        <v>-0.0907</v>
+        <v>-0.0906</v>
       </c>
     </row>
     <row r="218">
@@ -38720,22 +38720,22 @@
         <v>-1.0928</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.2086</v>
+        <v>-0.2085</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.6506</v>
       </c>
       <c r="E219" t="n">
         <v>-1.0928</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.2086</v>
+        <v>-0.2085</v>
       </c>
       <c r="G219" t="n">
         <v>-1.0928</v>
       </c>
       <c r="M219" t="n">
-        <v>-0.2086</v>
+        <v>-0.2085</v>
       </c>
     </row>
     <row r="220">
@@ -38776,7 +38776,7 @@
         <v>-0.6702</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.1358</v>
+        <v>-0.1357</v>
       </c>
       <c r="D221" t="n">
         <v>-0.403</v>
@@ -38785,13 +38785,13 @@
         <v>-0.6702</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.1358</v>
+        <v>-0.1357</v>
       </c>
       <c r="G221" t="n">
         <v>-0.6702</v>
       </c>
       <c r="M221" t="n">
-        <v>-0.1358</v>
+        <v>-0.1357</v>
       </c>
     </row>
     <row r="222">
@@ -38832,7 +38832,7 @@
         <v>-0.7167</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
       <c r="D223" t="n">
         <v>-0.3603</v>
@@ -38841,13 +38841,13 @@
         <v>-0.7167</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
       <c r="G223" t="n">
         <v>-0.7167</v>
       </c>
       <c r="M223" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
     </row>
     <row r="224">
@@ -38888,7 +38888,7 @@
         <v>-0.501</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="D225" t="n">
         <v>-0.2913</v>
@@ -38897,13 +38897,13 @@
         <v>-0.501</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="G225" t="n">
         <v>-0.501</v>
       </c>
       <c r="M225" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.08160000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -38944,22 +38944,22 @@
         <v>-0.4977</v>
       </c>
       <c r="C227" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.2467</v>
+        <v>-0.2466</v>
       </c>
       <c r="E227" t="n">
         <v>-0.4977</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="G227" t="n">
         <v>-0.4977</v>
       </c>
       <c r="M227" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
     </row>
     <row r="228">
@@ -39196,7 +39196,7 @@
         <v>-0.5698</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.4543</v>
+        <v>-0.4542</v>
       </c>
       <c r="D236" t="n">
         <v>-0.512</v>
@@ -39205,13 +39205,13 @@
         <v>-0.5698</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.4543</v>
+        <v>-0.4542</v>
       </c>
       <c r="G236" t="n">
         <v>-0.5698</v>
       </c>
       <c r="M236" t="n">
-        <v>-0.4543</v>
+        <v>-0.4542</v>
       </c>
     </row>
     <row r="237">
@@ -39224,7 +39224,7 @@
         <v>-0.5076000000000001</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.3546</v>
+        <v>-0.3545</v>
       </c>
       <c r="D237" t="n">
         <v>-0.4311</v>
@@ -39233,13 +39233,13 @@
         <v>-0.5076000000000001</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.3546</v>
+        <v>-0.3545</v>
       </c>
       <c r="G237" t="n">
         <v>-0.5076000000000001</v>
       </c>
       <c r="M237" t="n">
-        <v>-0.3546</v>
+        <v>-0.3545</v>
       </c>
     </row>
     <row r="238">
@@ -39280,7 +39280,7 @@
         <v>-0.2935</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.4443</v>
+        <v>-0.4442</v>
       </c>
       <c r="D239" t="n">
         <v>-0.3689</v>
@@ -39289,13 +39289,13 @@
         <v>-0.2935</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.4443</v>
+        <v>-0.4442</v>
       </c>
       <c r="G239" t="n">
         <v>-0.2935</v>
       </c>
       <c r="M239" t="n">
-        <v>-0.4443</v>
+        <v>-0.4442</v>
       </c>
     </row>
     <row r="240">
@@ -39308,7 +39308,7 @@
         <v>-0.3268</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.4717</v>
+        <v>-0.4716</v>
       </c>
       <c r="D240" t="n">
         <v>-0.3992</v>
@@ -39317,13 +39317,13 @@
         <v>-0.3268</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.4717</v>
+        <v>-0.4716</v>
       </c>
       <c r="G240" t="n">
         <v>-0.3268</v>
       </c>
       <c r="M240" t="n">
-        <v>-0.4717</v>
+        <v>-0.4716</v>
       </c>
     </row>
     <row r="241">
@@ -39336,7 +39336,7 @@
         <v>-0.4337</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.5118</v>
+        <v>-0.5117</v>
       </c>
       <c r="D241" t="n">
         <v>-0.4727</v>
@@ -39345,13 +39345,13 @@
         <v>-0.4337</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.5118</v>
+        <v>-0.5117</v>
       </c>
       <c r="G241" t="n">
         <v>-0.4337</v>
       </c>
       <c r="M241" t="n">
-        <v>-0.5118</v>
+        <v>-0.5117</v>
       </c>
     </row>
     <row r="242">
@@ -39420,7 +39420,7 @@
         <v>-0.3515</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.2465</v>
+        <v>-1.2464</v>
       </c>
       <c r="D244" t="n">
         <v>-0.799</v>
@@ -39429,13 +39429,13 @@
         <v>-0.3515</v>
       </c>
       <c r="F244" t="n">
-        <v>-1.2465</v>
+        <v>-1.2464</v>
       </c>
       <c r="G244" t="n">
         <v>-0.3515</v>
       </c>
       <c r="M244" t="n">
-        <v>-1.2465</v>
+        <v>-1.2464</v>
       </c>
     </row>
     <row r="245">
@@ -39504,7 +39504,7 @@
         <v>-0.3564</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.2653</v>
+        <v>-1.2652</v>
       </c>
       <c r="D247" t="n">
         <v>-0.8108</v>
@@ -39513,13 +39513,13 @@
         <v>-0.3564</v>
       </c>
       <c r="F247" t="n">
-        <v>-1.2653</v>
+        <v>-1.2652</v>
       </c>
       <c r="G247" t="n">
         <v>-0.3564</v>
       </c>
       <c r="M247" t="n">
-        <v>-1.2653</v>
+        <v>-1.2652</v>
       </c>
     </row>
     <row r="248">
@@ -39700,7 +39700,7 @@
         <v>-0.5687</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.7801</v>
+        <v>-0.78</v>
       </c>
       <c r="D254" t="n">
         <v>-0.6744</v>
@@ -39709,13 +39709,13 @@
         <v>-0.5687</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.7801</v>
+        <v>-0.78</v>
       </c>
       <c r="G254" t="n">
         <v>-0.5687</v>
       </c>
       <c r="M254" t="n">
-        <v>-0.7801</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="255">
@@ -39756,7 +39756,7 @@
         <v>-0.6099</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.7728</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="D256" t="n">
         <v>-0.6913</v>
@@ -39765,13 +39765,13 @@
         <v>-0.6099</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.7728</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="G256" t="n">
         <v>-0.6099</v>
       </c>
       <c r="M256" t="n">
-        <v>-0.7728</v>
+        <v>-0.7727000000000001</v>
       </c>
     </row>
     <row r="257">
@@ -39896,7 +39896,7 @@
         <v>-0.2115</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.8454</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="D261" t="n">
         <v>-0.5284</v>
@@ -39905,13 +39905,13 @@
         <v>-0.2115</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.8454</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="G261" t="n">
         <v>-0.2115</v>
       </c>
       <c r="M261" t="n">
-        <v>-0.8454</v>
+        <v>-0.8453000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -40036,7 +40036,7 @@
         <v>-0.0433</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.0177</v>
+        <v>-1.0176</v>
       </c>
       <c r="D266" t="n">
         <v>-0.5305</v>
@@ -40045,13 +40045,13 @@
         <v>-0.0433</v>
       </c>
       <c r="F266" t="n">
-        <v>-1.0177</v>
+        <v>-1.0176</v>
       </c>
       <c r="G266" t="n">
         <v>-0.0433</v>
       </c>
       <c r="M266" t="n">
-        <v>-1.0177</v>
+        <v>-1.0176</v>
       </c>
     </row>
     <row r="267">
@@ -40067,7 +40067,7 @@
         <v>-1.0881</v>
       </c>
       <c r="D267" t="n">
-        <v>-0.5322</v>
+        <v>-0.5321</v>
       </c>
       <c r="E267" t="n">
         <v>0.0238</v>
@@ -40092,7 +40092,7 @@
         <v>0.0408</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.8909</v>
+        <v>-0.8908</v>
       </c>
       <c r="D268" t="n">
         <v>-0.425</v>
@@ -40101,13 +40101,13 @@
         <v>0.0408</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.8909</v>
+        <v>-0.8908</v>
       </c>
       <c r="G268" t="n">
         <v>0.0408</v>
       </c>
       <c r="M268" t="n">
-        <v>-0.8909</v>
+        <v>-0.8908</v>
       </c>
     </row>
     <row r="269">
@@ -40120,7 +40120,7 @@
         <v>0.0529</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.4218</v>
+        <v>-0.4217</v>
       </c>
       <c r="D269" t="n">
         <v>-0.1844</v>
@@ -40129,13 +40129,13 @@
         <v>0.0529</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.4218</v>
+        <v>-0.4217</v>
       </c>
       <c r="G269" t="n">
         <v>0.0529</v>
       </c>
       <c r="M269" t="n">
-        <v>-0.4218</v>
+        <v>-0.4217</v>
       </c>
     </row>
     <row r="270">
@@ -40204,22 +40204,22 @@
         <v>0.1285</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.0183</v>
+        <v>-0.0182</v>
       </c>
       <c r="D272" t="n">
-        <v>0.0551</v>
+        <v>0.0552</v>
       </c>
       <c r="E272" t="n">
         <v>0.1285</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.0183</v>
+        <v>-0.0182</v>
       </c>
       <c r="G272" t="n">
         <v>0.1285</v>
       </c>
       <c r="M272" t="n">
-        <v>-0.0183</v>
+        <v>-0.0182</v>
       </c>
     </row>
     <row r="273">
@@ -40235,7 +40235,7 @@
         <v>0.132</v>
       </c>
       <c r="D273" t="n">
-        <v>0.1294</v>
+        <v>0.1295</v>
       </c>
       <c r="E273" t="n">
         <v>0.1269</v>
@@ -40400,7 +40400,7 @@
         <v>0.268</v>
       </c>
       <c r="C279" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5016</v>
       </c>
       <c r="D279" t="n">
         <v>0.3848</v>
@@ -40409,13 +40409,13 @@
         <v>0.268</v>
       </c>
       <c r="F279" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5016</v>
       </c>
       <c r="G279" t="n">
         <v>0.268</v>
       </c>
       <c r="M279" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5016</v>
       </c>
     </row>
     <row r="280">
@@ -40456,22 +40456,22 @@
         <v>0.9427</v>
       </c>
       <c r="C281" t="n">
-        <v>0.5728</v>
+        <v>0.5729</v>
       </c>
       <c r="D281" t="n">
-        <v>0.7577</v>
+        <v>0.7578</v>
       </c>
       <c r="E281" t="n">
         <v>0.9427</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5728</v>
+        <v>0.5729</v>
       </c>
       <c r="G281" t="n">
         <v>0.9427</v>
       </c>
       <c r="M281" t="n">
-        <v>0.5728</v>
+        <v>0.5729</v>
       </c>
     </row>
     <row r="282">
@@ -40540,7 +40540,7 @@
         <v>0.9882</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.0648</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="D284" t="n">
         <v>0.4617</v>
@@ -40549,13 +40549,13 @@
         <v>0.9882</v>
       </c>
       <c r="F284" t="n">
-        <v>-0.0648</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G284" t="n">
         <v>0.9882</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.0648</v>
+        <v>-0.06469999999999999</v>
       </c>
     </row>
     <row r="285">
@@ -40599,7 +40599,7 @@
         <v>-0.0325</v>
       </c>
       <c r="D286" t="n">
-        <v>0.5587</v>
+        <v>0.5588</v>
       </c>
       <c r="E286" t="n">
         <v>1.15</v>
@@ -40655,7 +40655,7 @@
         <v>-0.1084</v>
       </c>
       <c r="D288" t="n">
-        <v>0.4809</v>
+        <v>0.481</v>
       </c>
       <c r="E288" t="n">
         <v>1.0703</v>
@@ -40680,7 +40680,7 @@
         <v>0.2035</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.1116</v>
+        <v>-0.1115</v>
       </c>
       <c r="D289" t="n">
         <v>0.046</v>
@@ -40689,13 +40689,13 @@
         <v>0.2035</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.1116</v>
+        <v>-0.1115</v>
       </c>
       <c r="G289" t="n">
         <v>0.2035</v>
       </c>
       <c r="M289" t="n">
-        <v>-0.1116</v>
+        <v>-0.1115</v>
       </c>
     </row>
     <row r="290">
@@ -40708,22 +40708,22 @@
         <v>0.9959</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.1252</v>
+        <v>-0.1251</v>
       </c>
       <c r="D290" t="n">
-        <v>0.4353</v>
+        <v>0.4354</v>
       </c>
       <c r="E290" t="n">
         <v>0.9959</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.1252</v>
+        <v>-0.1251</v>
       </c>
       <c r="G290" t="n">
         <v>0.9959</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.1252</v>
+        <v>-0.1251</v>
       </c>
     </row>
     <row r="291">
@@ -40991,7 +40991,7 @@
         <v>-0.1955</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.0793</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="E300" t="n">
         <v>0.037</v>
@@ -41016,22 +41016,22 @@
         <v>-0.0272</v>
       </c>
       <c r="C301" t="n">
-        <v>-1.0473</v>
+        <v>-1.0472</v>
       </c>
       <c r="D301" t="n">
-        <v>-0.5373</v>
+        <v>-0.5372</v>
       </c>
       <c r="E301" t="n">
         <v>-0.0272</v>
       </c>
       <c r="F301" t="n">
-        <v>-1.0473</v>
+        <v>-1.0472</v>
       </c>
       <c r="G301" t="n">
         <v>-0.0272</v>
       </c>
       <c r="M301" t="n">
-        <v>-1.0473</v>
+        <v>-1.0472</v>
       </c>
     </row>
     <row r="302">
@@ -41159,7 +41159,7 @@
         <v>-1.6394</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.701</v>
+        <v>-0.7009</v>
       </c>
       <c r="E306" t="n">
         <v>0.2375</v>
@@ -41184,7 +41184,7 @@
         <v>0.2308</v>
       </c>
       <c r="C307" t="n">
-        <v>-1.7982</v>
+        <v>-1.7981</v>
       </c>
       <c r="D307" t="n">
         <v>-0.7837</v>
@@ -41193,13 +41193,13 @@
         <v>0.2308</v>
       </c>
       <c r="F307" t="n">
-        <v>-1.7982</v>
+        <v>-1.7981</v>
       </c>
       <c r="G307" t="n">
         <v>0.2308</v>
       </c>
       <c r="M307" t="n">
-        <v>-1.7982</v>
+        <v>-1.7981</v>
       </c>
     </row>
     <row r="308">
@@ -41436,7 +41436,7 @@
         <v>0.1168</v>
       </c>
       <c r="C316" t="n">
-        <v>0.5028</v>
+        <v>0.5029</v>
       </c>
       <c r="D316" t="n">
         <v>0.3098</v>
@@ -41445,13 +41445,13 @@
         <v>0.1168</v>
       </c>
       <c r="F316" t="n">
-        <v>0.5028</v>
+        <v>0.5029</v>
       </c>
       <c r="G316" t="n">
         <v>0.1168</v>
       </c>
       <c r="M316" t="n">
-        <v>0.5028</v>
+        <v>0.5029</v>
       </c>
     </row>
     <row r="317">
@@ -41579,7 +41579,7 @@
         <v>0.8764</v>
       </c>
       <c r="D321" t="n">
-        <v>0.5102</v>
+        <v>0.5103</v>
       </c>
       <c r="E321" t="n">
         <v>0.1441</v>
@@ -41604,7 +41604,7 @@
         <v>-0.0878</v>
       </c>
       <c r="C322" t="n">
-        <v>0.7336</v>
+        <v>0.7337</v>
       </c>
       <c r="D322" t="n">
         <v>0.3229</v>
@@ -41613,13 +41613,13 @@
         <v>-0.0878</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7336</v>
+        <v>0.7337</v>
       </c>
       <c r="G322" t="n">
         <v>-0.0878</v>
       </c>
       <c r="M322" t="n">
-        <v>0.7336</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="323">
@@ -41772,22 +41772,22 @@
         <v>-0.2135</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4503</v>
+        <v>0.4504</v>
       </c>
       <c r="D328" t="n">
-        <v>0.1184</v>
+        <v>0.1185</v>
       </c>
       <c r="E328" t="n">
         <v>-0.2135</v>
       </c>
       <c r="F328" t="n">
-        <v>0.4503</v>
+        <v>0.4504</v>
       </c>
       <c r="G328" t="n">
         <v>-0.2135</v>
       </c>
       <c r="M328" t="n">
-        <v>0.4503</v>
+        <v>0.4504</v>
       </c>
     </row>
     <row r="329">
@@ -41800,22 +41800,22 @@
         <v>-0.1305</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0294</v>
+        <v>0.0295</v>
       </c>
       <c r="D329" t="n">
-        <v>-0.0506</v>
+        <v>-0.0505</v>
       </c>
       <c r="E329" t="n">
         <v>-0.1305</v>
       </c>
       <c r="F329" t="n">
-        <v>0.0294</v>
+        <v>0.0295</v>
       </c>
       <c r="G329" t="n">
         <v>-0.1305</v>
       </c>
       <c r="M329" t="n">
-        <v>0.0294</v>
+        <v>0.0295</v>
       </c>
     </row>
     <row r="330">
@@ -41884,7 +41884,7 @@
         <v>-0.1714</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.2563</v>
+        <v>-0.2562</v>
       </c>
       <c r="D332" t="n">
         <v>-0.2138</v>
@@ -41893,13 +41893,13 @@
         <v>-0.1714</v>
       </c>
       <c r="F332" t="n">
-        <v>-0.2563</v>
+        <v>-0.2562</v>
       </c>
       <c r="G332" t="n">
         <v>-0.1714</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.2563</v>
+        <v>-0.2562</v>
       </c>
     </row>
     <row r="333">
@@ -42027,7 +42027,7 @@
         <v>-0.2842</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.2282</v>
+        <v>-0.2281</v>
       </c>
       <c r="E337" t="n">
         <v>-0.1721</v>
@@ -42111,7 +42111,7 @@
         <v>0.0516</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.0123</v>
+        <v>-0.0122</v>
       </c>
       <c r="E340" t="n">
         <v>-0.0761</v>
@@ -42136,22 +42136,22 @@
         <v>-0.1694</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1761</v>
+        <v>0.1762</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0033</v>
+        <v>0.0034</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1694</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1761</v>
+        <v>0.1762</v>
       </c>
       <c r="G341" t="n">
         <v>-0.1694</v>
       </c>
       <c r="M341" t="n">
-        <v>0.1761</v>
+        <v>0.1762</v>
       </c>
     </row>
     <row r="342">
@@ -42167,7 +42167,7 @@
         <v>0.2254</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0518</v>
+        <v>0.0519</v>
       </c>
       <c r="E342" t="n">
         <v>-0.1217</v>
@@ -42307,7 +42307,7 @@
         <v>0.351</v>
       </c>
       <c r="D347" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0919</v>
       </c>
       <c r="E347" t="n">
         <v>-0.1673</v>
@@ -42388,7 +42388,7 @@
         <v>-0.123</v>
       </c>
       <c r="C350" t="n">
-        <v>0.8066</v>
+        <v>0.8067</v>
       </c>
       <c r="D350" t="n">
         <v>0.3418</v>
@@ -42397,13 +42397,13 @@
         <v>-0.123</v>
       </c>
       <c r="F350" t="n">
-        <v>0.8066</v>
+        <v>0.8067</v>
       </c>
       <c r="G350" t="n">
         <v>-0.123</v>
       </c>
       <c r="M350" t="n">
-        <v>0.8066</v>
+        <v>0.8067</v>
       </c>
     </row>
     <row r="351">
@@ -42500,7 +42500,7 @@
         <v>0.0703</v>
       </c>
       <c r="C354" t="n">
-        <v>1.2554</v>
+        <v>1.2555</v>
       </c>
       <c r="D354" t="n">
         <v>0.6629</v>
@@ -42509,13 +42509,13 @@
         <v>0.0703</v>
       </c>
       <c r="F354" t="n">
-        <v>1.2554</v>
+        <v>1.2555</v>
       </c>
       <c r="G354" t="n">
         <v>0.0703</v>
       </c>
       <c r="M354" t="n">
-        <v>1.2554</v>
+        <v>1.2555</v>
       </c>
     </row>
     <row r="355">
@@ -42584,7 +42584,7 @@
         <v>0.2135</v>
       </c>
       <c r="C357" t="n">
-        <v>0.1632</v>
+        <v>0.1633</v>
       </c>
       <c r="D357" t="n">
         <v>0.1884</v>
@@ -42593,13 +42593,13 @@
         <v>0.2135</v>
       </c>
       <c r="F357" t="n">
-        <v>0.1632</v>
+        <v>0.1633</v>
       </c>
       <c r="G357" t="n">
         <v>0.2135</v>
       </c>
       <c r="M357" t="n">
-        <v>0.1632</v>
+        <v>0.1633</v>
       </c>
     </row>
     <row r="358">
@@ -42786,7 +42786,7 @@
         <v>-0.4841</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.0677</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="D364" t="n">
         <v>-0.2759</v>
@@ -42795,7 +42795,7 @@
         <v>-0.4841</v>
       </c>
       <c r="F364" t="n">
-        <v>-0.0677</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="G364" t="n">
         <v>0.2138</v>
@@ -42804,7 +42804,7 @@
         <v>-1.1821</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.0677</v>
+        <v>-0.06759999999999999</v>
       </c>
     </row>
     <row r="365">
@@ -42817,7 +42817,7 @@
         <v>-0.5304</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.2145</v>
+        <v>-0.2144</v>
       </c>
       <c r="D365" t="n">
         <v>-0.3724</v>
@@ -42826,7 +42826,7 @@
         <v>-0.5304</v>
       </c>
       <c r="F365" t="n">
-        <v>-0.2145</v>
+        <v>-0.2144</v>
       </c>
       <c r="G365" t="n">
         <v>0.1651</v>
@@ -42835,7 +42835,7 @@
         <v>-1.2258</v>
       </c>
       <c r="M365" t="n">
-        <v>-0.2145</v>
+        <v>-0.2144</v>
       </c>
     </row>
     <row r="366">
@@ -42913,7 +42913,7 @@
         <v>-0.1075</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.2926</v>
+        <v>-0.2925</v>
       </c>
       <c r="E368" t="n">
         <v>-0.4776</v>
@@ -43814,7 +43814,7 @@
         <v>-0.3017</v>
       </c>
       <c r="M390" t="n">
-        <v>0.7329</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="391">
@@ -43986,7 +43986,7 @@
         <v>-0.6529</v>
       </c>
       <c r="M394" t="n">
-        <v>0.3742</v>
+        <v>0.3743</v>
       </c>
     </row>
     <row r="395">
@@ -44330,7 +44330,7 @@
         <v>-1.4656</v>
       </c>
       <c r="M402" t="n">
-        <v>0.2564</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="403">
@@ -44459,7 +44459,7 @@
         <v>-1.6817</v>
       </c>
       <c r="M405" t="n">
-        <v>-0.0022</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="406">
@@ -44472,7 +44472,7 @@
         <v>-0.4816</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.84</v>
+        <v>-0.8399</v>
       </c>
       <c r="D406" t="n">
         <v>-0.6608000000000001</v>
@@ -44481,7 +44481,7 @@
         <v>-0.4816</v>
       </c>
       <c r="F406" t="n">
-        <v>-0.84</v>
+        <v>-0.8399</v>
       </c>
       <c r="G406" t="n">
         <v>-0.0586</v>
@@ -45117,7 +45117,7 @@
         <v>-0.4097</v>
       </c>
       <c r="C421" t="n">
-        <v>-1.1212</v>
+        <v>-1.1211</v>
       </c>
       <c r="D421" t="n">
         <v>-0.7654</v>
@@ -45126,7 +45126,7 @@
         <v>-0.4097</v>
       </c>
       <c r="F421" t="n">
-        <v>-1.1212</v>
+        <v>-1.1211</v>
       </c>
       <c r="G421" t="n">
         <v>-0.0756</v>
@@ -45719,7 +45719,7 @@
         <v>-0.5967</v>
       </c>
       <c r="C435" t="n">
-        <v>0.1371</v>
+        <v>0.1372</v>
       </c>
       <c r="D435" t="n">
         <v>-0.2298</v>
@@ -45728,7 +45728,7 @@
         <v>-0.5967</v>
       </c>
       <c r="F435" t="n">
-        <v>0.1371</v>
+        <v>0.1372</v>
       </c>
       <c r="G435" t="n">
         <v>-0.2192</v>
@@ -46093,7 +46093,7 @@
         <v>0.3248</v>
       </c>
       <c r="M443" t="n">
-        <v>0.2765</v>
+        <v>0.2766</v>
       </c>
     </row>
     <row r="444">
@@ -48114,7 +48114,7 @@
         <v>0.5518</v>
       </c>
       <c r="M490" t="n">
-        <v>0.2422</v>
+        <v>0.2423</v>
       </c>
     </row>
     <row r="491">
@@ -48600,7 +48600,7 @@
         <v>0.6429</v>
       </c>
       <c r="C502" t="n">
-        <v>0.744</v>
+        <v>0.7441</v>
       </c>
       <c r="D502" t="n">
         <v>0.6935</v>
@@ -48609,7 +48609,7 @@
         <v>0.6429</v>
       </c>
       <c r="F502" t="n">
-        <v>0.744</v>
+        <v>0.7441</v>
       </c>
       <c r="G502" t="n">
         <v>0.1521</v>
@@ -48732,7 +48732,7 @@
         <v>0.6497000000000001</v>
       </c>
       <c r="D505" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5954</v>
       </c>
       <c r="E505" t="n">
         <v>0.541</v>
@@ -49146,7 +49146,7 @@
         <v>0.3236</v>
       </c>
       <c r="M514" t="n">
-        <v>0.4952</v>
+        <v>0.4953</v>
       </c>
     </row>
     <row r="515">
@@ -50866,7 +50866,7 @@
         <v>-0.9617</v>
       </c>
       <c r="M554" t="n">
-        <v>-0.2292</v>
+        <v>-0.2291</v>
       </c>
     </row>
     <row r="555">
@@ -50995,7 +50995,7 @@
         <v>-0.9447</v>
       </c>
       <c r="M557" t="n">
-        <v>-0.3299</v>
+        <v>-0.3298</v>
       </c>
     </row>
     <row r="558">
@@ -51253,7 +51253,7 @@
         <v>0.0631</v>
       </c>
       <c r="M563" t="n">
-        <v>-0.1662</v>
+        <v>-0.1661</v>
       </c>
     </row>
     <row r="564">
@@ -51855,7 +51855,7 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="M577" t="n">
-        <v>-0.0302</v>
+        <v>-0.0301</v>
       </c>
     </row>
     <row r="578">
@@ -52199,7 +52199,7 @@
         <v>0.5825</v>
       </c>
       <c r="M585" t="n">
-        <v>-0.4883</v>
+        <v>-0.4882</v>
       </c>
     </row>
     <row r="586">
@@ -52328,7 +52328,7 @@
         <v>0.5521</v>
       </c>
       <c r="M588" t="n">
-        <v>-0.963</v>
+        <v>-0.9629</v>
       </c>
     </row>
     <row r="589">
@@ -52430,7 +52430,7 @@
         <v>-0.3761</v>
       </c>
       <c r="D591" t="n">
-        <v>0.1069</v>
+        <v>0.107</v>
       </c>
       <c r="E591" t="n">
         <v>0.59</v>
@@ -52543,7 +52543,7 @@
         <v>0.5243</v>
       </c>
       <c r="M593" t="n">
-        <v>-1.1505</v>
+        <v>-1.1504</v>
       </c>
     </row>
     <row r="594">
@@ -53360,7 +53360,7 @@
         <v>0.4621</v>
       </c>
       <c r="M612" t="n">
-        <v>-0.1989</v>
+        <v>-0.1988</v>
       </c>
     </row>
     <row r="613">
@@ -54134,7 +54134,7 @@
         <v>0.46</v>
       </c>
       <c r="M630" t="n">
-        <v>-0.0067</v>
+        <v>-0.0066</v>
       </c>
     </row>
     <row r="631">
@@ -54319,16 +54319,16 @@
         <v>0.4308</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1683</v>
+        <v>-0.1691</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1313</v>
+        <v>0.1309</v>
       </c>
       <c r="E635" t="n">
         <v>0.4308</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1683</v>
+        <v>-0.1691</v>
       </c>
       <c r="G635" t="n">
         <v>0.6662</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.3979</v>
+        <v>0.3955</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>-0.705</v>
       </c>
       <c r="K177" t="n">
-        <v>-0.891</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="178">
@@ -3078,7 +3078,7 @@
         <v>-1.912</v>
       </c>
       <c r="K201" t="n">
-        <v>-2.229</v>
+        <v>-2.228</v>
       </c>
     </row>
     <row r="202">
@@ -3208,7 +3208,7 @@
         <v>-1.093</v>
       </c>
       <c r="K211" t="n">
-        <v>-0.209</v>
+        <v>-0.208</v>
       </c>
     </row>
     <row r="212">
@@ -4066,7 +4066,7 @@
         <v>1.057</v>
       </c>
       <c r="K277" t="n">
-        <v>-0.101</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="278">
@@ -4079,7 +4079,7 @@
         <v>1.15</v>
       </c>
       <c r="K278" t="n">
-        <v>-0.033</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="279">
@@ -4118,7 +4118,7 @@
         <v>0.204</v>
       </c>
       <c r="K281" t="n">
-        <v>-0.112</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="282">
@@ -4768,7 +4768,7 @@
         <v>-0.124</v>
       </c>
       <c r="K331" t="n">
-        <v>-0.21</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="332">
@@ -4859,7 +4859,7 @@
         <v>-0.167</v>
       </c>
       <c r="K338" t="n">
-        <v>0.524</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="339">
@@ -4898,7 +4898,7 @@
         <v>-0.073</v>
       </c>
       <c r="K341" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="342">
@@ -8616,7 +8616,7 @@
         <v>0.431</v>
       </c>
       <c r="K627" t="n">
-        <v>-0.169</v>
+        <v>-0.171</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.885</v>
+        <v>11.089</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.059</v>
+        <v>1.06</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0594</v>
+        <v>1.0605</v>
       </c>
       <c r="H635" t="n">
-        <v>10.8851</v>
+        <v>11.0888</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37180,7 +37180,7 @@
         <v>-1.2155</v>
       </c>
       <c r="C164" t="n">
-        <v>-2.8744</v>
+        <v>-2.8743</v>
       </c>
       <c r="D164" t="n">
         <v>-2.0449</v>
@@ -37189,13 +37189,13 @@
         <v>-1.2155</v>
       </c>
       <c r="F164" t="n">
-        <v>-2.8744</v>
+        <v>-2.8743</v>
       </c>
       <c r="G164" t="n">
         <v>-1.2155</v>
       </c>
       <c r="M164" t="n">
-        <v>-2.8744</v>
+        <v>-2.8743</v>
       </c>
     </row>
     <row r="165">
@@ -37208,7 +37208,7 @@
         <v>-1.1524</v>
       </c>
       <c r="C165" t="n">
-        <v>-3.1342</v>
+        <v>-3.1341</v>
       </c>
       <c r="D165" t="n">
         <v>-2.1433</v>
@@ -37217,13 +37217,13 @@
         <v>-1.1524</v>
       </c>
       <c r="F165" t="n">
-        <v>-3.1342</v>
+        <v>-3.1341</v>
       </c>
       <c r="G165" t="n">
         <v>-1.1524</v>
       </c>
       <c r="M165" t="n">
-        <v>-3.1342</v>
+        <v>-3.1341</v>
       </c>
     </row>
     <row r="166">
@@ -37267,7 +37267,7 @@
         <v>-3.1765</v>
       </c>
       <c r="D167" t="n">
-        <v>-2.2982</v>
+        <v>-2.2981</v>
       </c>
       <c r="E167" t="n">
         <v>-1.4198</v>
@@ -37323,7 +37323,7 @@
         <v>-3.8966</v>
       </c>
       <c r="D169" t="n">
-        <v>-2.5928</v>
+        <v>-2.5927</v>
       </c>
       <c r="E169" t="n">
         <v>-1.2889</v>
@@ -37379,7 +37379,7 @@
         <v>-4.4218</v>
       </c>
       <c r="D171" t="n">
-        <v>-2.8058</v>
+        <v>-2.8057</v>
       </c>
       <c r="E171" t="n">
         <v>-1.1897</v>
@@ -37575,7 +37575,7 @@
         <v>-2.764</v>
       </c>
       <c r="D178" t="n">
-        <v>-2.1264</v>
+        <v>-2.1263</v>
       </c>
       <c r="E178" t="n">
         <v>-1.4887</v>
@@ -37628,7 +37628,7 @@
         <v>-1.2972</v>
       </c>
       <c r="C180" t="n">
-        <v>-1.934</v>
+        <v>-1.9339</v>
       </c>
       <c r="D180" t="n">
         <v>-1.6156</v>
@@ -37637,13 +37637,13 @@
         <v>-1.2972</v>
       </c>
       <c r="F180" t="n">
-        <v>-1.934</v>
+        <v>-1.9339</v>
       </c>
       <c r="G180" t="n">
         <v>-1.2972</v>
       </c>
       <c r="M180" t="n">
-        <v>-1.934</v>
+        <v>-1.9339</v>
       </c>
     </row>
     <row r="181">
@@ -37712,7 +37712,7 @@
         <v>-1.2693</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.9811</v>
+        <v>-0.981</v>
       </c>
       <c r="D183" t="n">
         <v>-1.1252</v>
@@ -37721,13 +37721,13 @@
         <v>-1.2693</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.9811</v>
+        <v>-0.981</v>
       </c>
       <c r="G183" t="n">
         <v>-1.2693</v>
       </c>
       <c r="M183" t="n">
-        <v>-0.9811</v>
+        <v>-0.981</v>
       </c>
     </row>
     <row r="184">
@@ -37743,7 +37743,7 @@
         <v>-0.9136</v>
       </c>
       <c r="D184" t="n">
-        <v>-1.1009</v>
+        <v>-1.1008</v>
       </c>
       <c r="E184" t="n">
         <v>-1.2881</v>
@@ -37824,7 +37824,7 @@
         <v>-0.7876</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.7337</v>
+        <v>-0.7336</v>
       </c>
       <c r="D187" t="n">
         <v>-0.7606000000000001</v>
@@ -37833,13 +37833,13 @@
         <v>-0.7876</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.7337</v>
+        <v>-0.7336</v>
       </c>
       <c r="G187" t="n">
         <v>-0.7876</v>
       </c>
       <c r="M187" t="n">
-        <v>-0.7337</v>
+        <v>-0.7336</v>
       </c>
     </row>
     <row r="188">
@@ -37855,7 +37855,7 @@
         <v>-0.4747</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.6238</v>
+        <v>-0.6237</v>
       </c>
       <c r="E188" t="n">
         <v>-0.7728</v>
@@ -37880,7 +37880,7 @@
         <v>-0.8032</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.4739</v>
+        <v>-0.4738</v>
       </c>
       <c r="D189" t="n">
         <v>-0.6385</v>
@@ -37889,13 +37889,13 @@
         <v>-0.8032</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.4739</v>
+        <v>-0.4738</v>
       </c>
       <c r="G189" t="n">
         <v>-0.8032</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.4739</v>
+        <v>-0.4738</v>
       </c>
     </row>
     <row r="190">
@@ -37908,7 +37908,7 @@
         <v>-0.8622</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3762</v>
+        <v>-0.3761</v>
       </c>
       <c r="D190" t="n">
         <v>-0.6192</v>
@@ -37917,13 +37917,13 @@
         <v>-0.8622</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.3762</v>
+        <v>-0.3761</v>
       </c>
       <c r="G190" t="n">
         <v>-0.8622</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.3762</v>
+        <v>-0.3761</v>
       </c>
     </row>
     <row r="191">
@@ -37964,22 +37964,22 @@
         <v>-1.2352</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.0977</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.6665</v>
+        <v>-0.6664</v>
       </c>
       <c r="E192" t="n">
         <v>-1.2352</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.0977</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="G192" t="n">
         <v>-1.2352</v>
       </c>
       <c r="M192" t="n">
-        <v>-0.0977</v>
+        <v>-0.09760000000000001</v>
       </c>
     </row>
     <row r="193">
@@ -38051,7 +38051,7 @@
         <v>-0.7211</v>
       </c>
       <c r="D195" t="n">
-        <v>-1.0466</v>
+        <v>-1.0465</v>
       </c>
       <c r="E195" t="n">
         <v>-1.372</v>
@@ -38076,7 +38076,7 @@
         <v>-1.4876</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.8732</v>
+        <v>-0.8731</v>
       </c>
       <c r="D196" t="n">
         <v>-1.1804</v>
@@ -38085,13 +38085,13 @@
         <v>-1.4876</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.8732</v>
+        <v>-0.8731</v>
       </c>
       <c r="G196" t="n">
         <v>-1.4876</v>
       </c>
       <c r="M196" t="n">
-        <v>-0.8732</v>
+        <v>-0.8731</v>
       </c>
     </row>
     <row r="197">
@@ -38160,7 +38160,7 @@
         <v>-2.0782</v>
       </c>
       <c r="C199" t="n">
-        <v>-1.1531</v>
+        <v>-1.153</v>
       </c>
       <c r="D199" t="n">
         <v>-1.6156</v>
@@ -38169,13 +38169,13 @@
         <v>-2.0782</v>
       </c>
       <c r="F199" t="n">
-        <v>-1.1531</v>
+        <v>-1.153</v>
       </c>
       <c r="G199" t="n">
         <v>-2.0782</v>
       </c>
       <c r="M199" t="n">
-        <v>-1.1531</v>
+        <v>-1.153</v>
       </c>
     </row>
     <row r="200">
@@ -38216,7 +38216,7 @@
         <v>-2.2387</v>
       </c>
       <c r="C201" t="n">
-        <v>-1.4057</v>
+        <v>-1.4056</v>
       </c>
       <c r="D201" t="n">
         <v>-1.8222</v>
@@ -38225,13 +38225,13 @@
         <v>-2.2387</v>
       </c>
       <c r="F201" t="n">
-        <v>-1.4057</v>
+        <v>-1.4056</v>
       </c>
       <c r="G201" t="n">
         <v>-2.2387</v>
       </c>
       <c r="M201" t="n">
-        <v>-1.4057</v>
+        <v>-1.4056</v>
       </c>
     </row>
     <row r="202">
@@ -38303,7 +38303,7 @@
         <v>-2.2737</v>
       </c>
       <c r="D204" t="n">
-        <v>-2.1</v>
+        <v>-2.0999</v>
       </c>
       <c r="E204" t="n">
         <v>-1.9262</v>
@@ -38412,7 +38412,7 @@
         <v>-1.8551</v>
       </c>
       <c r="C208" t="n">
-        <v>-2.2337</v>
+        <v>-2.2336</v>
       </c>
       <c r="D208" t="n">
         <v>-2.0444</v>
@@ -38421,13 +38421,13 @@
         <v>-1.8551</v>
       </c>
       <c r="F208" t="n">
-        <v>-2.2337</v>
+        <v>-2.2336</v>
       </c>
       <c r="G208" t="n">
         <v>-1.8551</v>
       </c>
       <c r="M208" t="n">
-        <v>-2.2337</v>
+        <v>-2.2336</v>
       </c>
     </row>
     <row r="209">
@@ -38524,7 +38524,7 @@
         <v>-1.6604</v>
       </c>
       <c r="C212" t="n">
-        <v>-1.9828</v>
+        <v>-1.9827</v>
       </c>
       <c r="D212" t="n">
         <v>-1.8216</v>
@@ -38533,13 +38533,13 @@
         <v>-1.6604</v>
       </c>
       <c r="F212" t="n">
-        <v>-1.9828</v>
+        <v>-1.9827</v>
       </c>
       <c r="G212" t="n">
         <v>-1.6604</v>
       </c>
       <c r="M212" t="n">
-        <v>-1.9828</v>
+        <v>-1.9827</v>
       </c>
     </row>
     <row r="213">
@@ -38608,7 +38608,7 @@
         <v>-1.5344</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.6764</v>
+        <v>-0.6763</v>
       </c>
       <c r="D215" t="n">
         <v>-1.1054</v>
@@ -38617,13 +38617,13 @@
         <v>-1.5344</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.6764</v>
+        <v>-0.6763</v>
       </c>
       <c r="G215" t="n">
         <v>-1.5344</v>
       </c>
       <c r="M215" t="n">
-        <v>-0.6764</v>
+        <v>-0.6763</v>
       </c>
     </row>
     <row r="216">
@@ -38692,7 +38692,7 @@
         <v>-1.1513</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1512</v>
+        <v>-0.1511</v>
       </c>
       <c r="D218" t="n">
         <v>-0.6512</v>
@@ -38701,13 +38701,13 @@
         <v>-1.1513</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.1512</v>
+        <v>-0.1511</v>
       </c>
       <c r="G218" t="n">
         <v>-1.1513</v>
       </c>
       <c r="M218" t="n">
-        <v>-0.1512</v>
+        <v>-0.1511</v>
       </c>
     </row>
     <row r="219">
@@ -38748,7 +38748,7 @@
         <v>-1.1315</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.0151</v>
+        <v>-0.015</v>
       </c>
       <c r="D220" t="n">
         <v>-0.5733</v>
@@ -38757,13 +38757,13 @@
         <v>-1.1315</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.0151</v>
+        <v>-0.015</v>
       </c>
       <c r="G220" t="n">
         <v>-1.1315</v>
       </c>
       <c r="M220" t="n">
-        <v>-0.0151</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="221">
@@ -38860,7 +38860,7 @@
         <v>-0.7146</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.0445</v>
+        <v>-0.0444</v>
       </c>
       <c r="D224" t="n">
         <v>-0.3795</v>
@@ -38869,13 +38869,13 @@
         <v>-0.7146</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.0445</v>
+        <v>-0.0444</v>
       </c>
       <c r="G224" t="n">
         <v>-0.7146</v>
       </c>
       <c r="M224" t="n">
-        <v>-0.0445</v>
+        <v>-0.0444</v>
       </c>
     </row>
     <row r="225">
@@ -38916,7 +38916,7 @@
         <v>-0.5012</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.0038</v>
+        <v>-0.0037</v>
       </c>
       <c r="D226" t="n">
         <v>-0.2525</v>
@@ -38925,13 +38925,13 @@
         <v>-0.5012</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.0038</v>
+        <v>-0.0037</v>
       </c>
       <c r="G226" t="n">
         <v>-0.5012</v>
       </c>
       <c r="M226" t="n">
-        <v>-0.0038</v>
+        <v>-0.0037</v>
       </c>
     </row>
     <row r="227">
@@ -38972,22 +38972,22 @@
         <v>-0.4447</v>
       </c>
       <c r="C228" t="n">
-        <v>0.017</v>
+        <v>0.0171</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.2139</v>
+        <v>-0.2138</v>
       </c>
       <c r="E228" t="n">
         <v>-0.4447</v>
       </c>
       <c r="F228" t="n">
-        <v>0.017</v>
+        <v>0.0171</v>
       </c>
       <c r="G228" t="n">
         <v>-0.4447</v>
       </c>
       <c r="M228" t="n">
-        <v>0.017</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="229">
@@ -39056,7 +39056,7 @@
         <v>-0.4083</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.0008</v>
+        <v>-0.0007</v>
       </c>
       <c r="D231" t="n">
         <v>-0.2045</v>
@@ -39065,13 +39065,13 @@
         <v>-0.4083</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0008</v>
+        <v>-0.0007</v>
       </c>
       <c r="G231" t="n">
         <v>-0.4083</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.0008</v>
+        <v>-0.0007</v>
       </c>
     </row>
     <row r="232">
@@ -39112,22 +39112,22 @@
         <v>-0.5596</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.1157</v>
+        <v>-0.1156</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.3377</v>
+        <v>-0.3376</v>
       </c>
       <c r="E233" t="n">
         <v>-0.5596</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.1157</v>
+        <v>-0.1156</v>
       </c>
       <c r="G233" t="n">
         <v>-0.5596</v>
       </c>
       <c r="M233" t="n">
-        <v>-0.1157</v>
+        <v>-0.1156</v>
       </c>
     </row>
     <row r="234">
@@ -39168,7 +39168,7 @@
         <v>-0.5935</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.3823</v>
+        <v>-0.3822</v>
       </c>
       <c r="D235" t="n">
         <v>-0.4879</v>
@@ -39177,13 +39177,13 @@
         <v>-0.5935</v>
       </c>
       <c r="F235" t="n">
-        <v>-0.3823</v>
+        <v>-0.3822</v>
       </c>
       <c r="G235" t="n">
         <v>-0.5935</v>
       </c>
       <c r="M235" t="n">
-        <v>-0.3823</v>
+        <v>-0.3822</v>
       </c>
     </row>
     <row r="236">
@@ -39227,7 +39227,7 @@
         <v>-0.3545</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.4311</v>
+        <v>-0.431</v>
       </c>
       <c r="E237" t="n">
         <v>-0.5076000000000001</v>
@@ -39423,7 +39423,7 @@
         <v>-1.2464</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.799</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="E244" t="n">
         <v>-0.3515</v>
@@ -39451,7 +39451,7 @@
         <v>-1.194</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.7761</v>
+        <v>-0.776</v>
       </c>
       <c r="E245" t="n">
         <v>-0.3581</v>
@@ -39476,22 +39476,22 @@
         <v>-0.2484</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.0766</v>
+        <v>-1.0765</v>
       </c>
       <c r="D246" t="n">
-        <v>-0.6625</v>
+        <v>-0.6624</v>
       </c>
       <c r="E246" t="n">
         <v>-0.2484</v>
       </c>
       <c r="F246" t="n">
-        <v>-1.0766</v>
+        <v>-1.0765</v>
       </c>
       <c r="G246" t="n">
         <v>-0.2484</v>
       </c>
       <c r="M246" t="n">
-        <v>-1.0766</v>
+        <v>-1.0765</v>
       </c>
     </row>
     <row r="247">
@@ -39672,22 +39672,22 @@
         <v>-0.7861</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.8073</v>
+        <v>-0.8072</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.7967</v>
+        <v>-0.7966</v>
       </c>
       <c r="E253" t="n">
         <v>-0.7861</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.8073</v>
+        <v>-0.8072</v>
       </c>
       <c r="G253" t="n">
         <v>-0.7861</v>
       </c>
       <c r="M253" t="n">
-        <v>-0.8073</v>
+        <v>-0.8072</v>
       </c>
     </row>
     <row r="254">
@@ -39703,7 +39703,7 @@
         <v>-0.78</v>
       </c>
       <c r="D254" t="n">
-        <v>-0.6744</v>
+        <v>-0.6743</v>
       </c>
       <c r="E254" t="n">
         <v>-0.5687</v>
@@ -39728,7 +39728,7 @@
         <v>-0.5954</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.6909</v>
+        <v>-0.6908</v>
       </c>
       <c r="D255" t="n">
         <v>-0.6431</v>
@@ -39737,13 +39737,13 @@
         <v>-0.5954</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.6909</v>
+        <v>-0.6908</v>
       </c>
       <c r="G255" t="n">
         <v>-0.5954</v>
       </c>
       <c r="M255" t="n">
-        <v>-0.6909</v>
+        <v>-0.6908</v>
       </c>
     </row>
     <row r="256">
@@ -39868,7 +39868,7 @@
         <v>-0.2129</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.9999</v>
+        <v>-0.9998</v>
       </c>
       <c r="D260" t="n">
         <v>-0.6064000000000001</v>
@@ -39877,13 +39877,13 @@
         <v>-0.2129</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.9999</v>
+        <v>-0.9998</v>
       </c>
       <c r="G260" t="n">
         <v>-0.2129</v>
       </c>
       <c r="M260" t="n">
-        <v>-0.9999</v>
+        <v>-0.9998</v>
       </c>
     </row>
     <row r="261">
@@ -39924,7 +39924,7 @@
         <v>0.0735</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.8855</v>
+        <v>-0.8854</v>
       </c>
       <c r="D262" t="n">
         <v>-0.406</v>
@@ -39933,13 +39933,13 @@
         <v>0.0735</v>
       </c>
       <c r="F262" t="n">
-        <v>-0.8855</v>
+        <v>-0.8854</v>
       </c>
       <c r="G262" t="n">
         <v>0.0735</v>
       </c>
       <c r="M262" t="n">
-        <v>-0.8855</v>
+        <v>-0.8854</v>
       </c>
     </row>
     <row r="263">
@@ -39952,7 +39952,7 @@
         <v>0.1547</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.7617</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="D263" t="n">
         <v>-0.3035</v>
@@ -39961,13 +39961,13 @@
         <v>0.1547</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.7617</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="G263" t="n">
         <v>0.1547</v>
       </c>
       <c r="M263" t="n">
-        <v>-0.7617</v>
+        <v>-0.7616000000000001</v>
       </c>
     </row>
     <row r="264">
@@ -40064,7 +40064,7 @@
         <v>0.0238</v>
       </c>
       <c r="C267" t="n">
-        <v>-1.0881</v>
+        <v>-1.088</v>
       </c>
       <c r="D267" t="n">
         <v>-0.5321</v>
@@ -40073,13 +40073,13 @@
         <v>0.0238</v>
       </c>
       <c r="F267" t="n">
-        <v>-1.0881</v>
+        <v>-1.088</v>
       </c>
       <c r="G267" t="n">
         <v>0.0238</v>
       </c>
       <c r="M267" t="n">
-        <v>-1.0881</v>
+        <v>-1.088</v>
       </c>
     </row>
     <row r="268">
@@ -40148,7 +40148,7 @@
         <v>0.0431</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.3343</v>
+        <v>-0.3342</v>
       </c>
       <c r="D270" t="n">
         <v>-0.1456</v>
@@ -40157,13 +40157,13 @@
         <v>0.0431</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.3343</v>
+        <v>-0.3342</v>
       </c>
       <c r="G270" t="n">
         <v>0.0431</v>
       </c>
       <c r="M270" t="n">
-        <v>-0.3343</v>
+        <v>-0.3342</v>
       </c>
     </row>
     <row r="271">
@@ -40176,7 +40176,7 @@
         <v>0.1082</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.0422</v>
+        <v>-0.0421</v>
       </c>
       <c r="D271" t="n">
         <v>0.033</v>
@@ -40185,13 +40185,13 @@
         <v>0.1082</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.0422</v>
+        <v>-0.0421</v>
       </c>
       <c r="G271" t="n">
         <v>0.1082</v>
       </c>
       <c r="M271" t="n">
-        <v>-0.0422</v>
+        <v>-0.0421</v>
       </c>
     </row>
     <row r="272">
@@ -40232,7 +40232,7 @@
         <v>0.1269</v>
       </c>
       <c r="C273" t="n">
-        <v>0.132</v>
+        <v>0.1321</v>
       </c>
       <c r="D273" t="n">
         <v>0.1295</v>
@@ -40241,13 +40241,13 @@
         <v>0.1269</v>
       </c>
       <c r="F273" t="n">
-        <v>0.132</v>
+        <v>0.1321</v>
       </c>
       <c r="G273" t="n">
         <v>0.1269</v>
       </c>
       <c r="M273" t="n">
-        <v>0.132</v>
+        <v>0.1321</v>
       </c>
     </row>
     <row r="274">
@@ -40288,7 +40288,7 @@
         <v>0.1662</v>
       </c>
       <c r="C275" t="n">
-        <v>0.1654</v>
+        <v>0.1655</v>
       </c>
       <c r="D275" t="n">
         <v>0.1658</v>
@@ -40297,13 +40297,13 @@
         <v>0.1662</v>
       </c>
       <c r="F275" t="n">
-        <v>0.1654</v>
+        <v>0.1655</v>
       </c>
       <c r="G275" t="n">
         <v>0.1662</v>
       </c>
       <c r="M275" t="n">
-        <v>0.1654</v>
+        <v>0.1655</v>
       </c>
     </row>
     <row r="276">
@@ -40344,22 +40344,22 @@
         <v>1.0418</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1521</v>
+        <v>0.1522</v>
       </c>
       <c r="D277" t="n">
-        <v>0.5969</v>
+        <v>0.597</v>
       </c>
       <c r="E277" t="n">
         <v>1.0418</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1521</v>
+        <v>0.1522</v>
       </c>
       <c r="G277" t="n">
         <v>1.0418</v>
       </c>
       <c r="M277" t="n">
-        <v>0.1521</v>
+        <v>0.1522</v>
       </c>
     </row>
     <row r="278">
@@ -40372,22 +40372,22 @@
         <v>0.3162</v>
       </c>
       <c r="C278" t="n">
-        <v>0.4114</v>
+        <v>0.4115</v>
       </c>
       <c r="D278" t="n">
-        <v>0.3638</v>
+        <v>0.3639</v>
       </c>
       <c r="E278" t="n">
         <v>0.3162</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4114</v>
+        <v>0.4115</v>
       </c>
       <c r="G278" t="n">
         <v>0.3162</v>
       </c>
       <c r="M278" t="n">
-        <v>0.4114</v>
+        <v>0.4115</v>
       </c>
     </row>
     <row r="279">
@@ -40428,7 +40428,7 @@
         <v>0.2948</v>
       </c>
       <c r="C280" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="D280" t="n">
         <v>0.4027</v>
@@ -40437,13 +40437,13 @@
         <v>0.2948</v>
       </c>
       <c r="F280" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="G280" t="n">
         <v>0.2948</v>
       </c>
       <c r="M280" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5107</v>
       </c>
     </row>
     <row r="281">
@@ -40484,7 +40484,7 @@
         <v>0.9449</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.076</v>
+        <v>-0.0759</v>
       </c>
       <c r="D282" t="n">
         <v>0.4345</v>
@@ -40493,13 +40493,13 @@
         <v>0.9449</v>
       </c>
       <c r="F282" t="n">
-        <v>-0.076</v>
+        <v>-0.0759</v>
       </c>
       <c r="G282" t="n">
         <v>0.9449</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.076</v>
+        <v>-0.0759</v>
       </c>
     </row>
     <row r="283">
@@ -40543,7 +40543,7 @@
         <v>-0.06469999999999999</v>
       </c>
       <c r="D284" t="n">
-        <v>0.4617</v>
+        <v>0.4618</v>
       </c>
       <c r="E284" t="n">
         <v>0.9882</v>
@@ -40739,7 +40739,7 @@
         <v>-0.1336</v>
       </c>
       <c r="D291" t="n">
-        <v>0.381</v>
+        <v>0.3811</v>
       </c>
       <c r="E291" t="n">
         <v>0.8957000000000001</v>
@@ -40764,7 +40764,7 @@
         <v>0.9145</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.1415</v>
+        <v>-0.1414</v>
       </c>
       <c r="D292" t="n">
         <v>0.3865</v>
@@ -40773,13 +40773,13 @@
         <v>0.9145</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.1415</v>
+        <v>-0.1414</v>
       </c>
       <c r="G292" t="n">
         <v>0.9145</v>
       </c>
       <c r="M292" t="n">
-        <v>-0.1415</v>
+        <v>-0.1414</v>
       </c>
     </row>
     <row r="293">
@@ -40820,7 +40820,7 @@
         <v>0.0746</v>
       </c>
       <c r="C294" t="n">
-        <v>0.3808</v>
+        <v>0.3809</v>
       </c>
       <c r="D294" t="n">
         <v>0.2277</v>
@@ -40829,13 +40829,13 @@
         <v>0.0746</v>
       </c>
       <c r="F294" t="n">
-        <v>0.3808</v>
+        <v>0.3809</v>
       </c>
       <c r="G294" t="n">
         <v>0.0746</v>
       </c>
       <c r="M294" t="n">
-        <v>0.3808</v>
+        <v>0.3809</v>
       </c>
     </row>
     <row r="295">
@@ -40848,7 +40848,7 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="C295" t="n">
-        <v>0.3803</v>
+        <v>0.3804</v>
       </c>
       <c r="D295" t="n">
         <v>0.2237</v>
@@ -40857,13 +40857,13 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="F295" t="n">
-        <v>0.3803</v>
+        <v>0.3804</v>
       </c>
       <c r="G295" t="n">
         <v>0.06710000000000001</v>
       </c>
       <c r="M295" t="n">
-        <v>0.3803</v>
+        <v>0.3804</v>
       </c>
     </row>
     <row r="296">
@@ -40904,7 +40904,7 @@
         <v>0.0208</v>
       </c>
       <c r="C297" t="n">
-        <v>0.165</v>
+        <v>0.1651</v>
       </c>
       <c r="D297" t="n">
         <v>0.0929</v>
@@ -40913,13 +40913,13 @@
         <v>0.0208</v>
       </c>
       <c r="F297" t="n">
-        <v>0.165</v>
+        <v>0.1651</v>
       </c>
       <c r="G297" t="n">
         <v>0.0208</v>
       </c>
       <c r="M297" t="n">
-        <v>0.165</v>
+        <v>0.1651</v>
       </c>
     </row>
     <row r="298">
@@ -40960,7 +40960,7 @@
         <v>-0.0374</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.1285</v>
+        <v>-0.1284</v>
       </c>
       <c r="D299" t="n">
         <v>-0.0829</v>
@@ -40969,13 +40969,13 @@
         <v>-0.0374</v>
       </c>
       <c r="F299" t="n">
-        <v>-0.1285</v>
+        <v>-0.1284</v>
       </c>
       <c r="G299" t="n">
         <v>-0.0374</v>
       </c>
       <c r="M299" t="n">
-        <v>-0.1285</v>
+        <v>-0.1284</v>
       </c>
     </row>
     <row r="300">
@@ -40988,7 +40988,7 @@
         <v>0.037</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.1955</v>
+        <v>-0.1954</v>
       </c>
       <c r="D300" t="n">
         <v>-0.07920000000000001</v>
@@ -40997,13 +40997,13 @@
         <v>0.037</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.1955</v>
+        <v>-0.1954</v>
       </c>
       <c r="G300" t="n">
         <v>0.037</v>
       </c>
       <c r="M300" t="n">
-        <v>-0.1955</v>
+        <v>-0.1954</v>
       </c>
     </row>
     <row r="301">
@@ -41044,7 +41044,7 @@
         <v>0.0553</v>
       </c>
       <c r="C302" t="n">
-        <v>-1.3603</v>
+        <v>-1.3602</v>
       </c>
       <c r="D302" t="n">
         <v>-0.6525</v>
@@ -41053,13 +41053,13 @@
         <v>0.0553</v>
       </c>
       <c r="F302" t="n">
-        <v>-1.3603</v>
+        <v>-1.3602</v>
       </c>
       <c r="G302" t="n">
         <v>0.0553</v>
       </c>
       <c r="M302" t="n">
-        <v>-1.3603</v>
+        <v>-1.3602</v>
       </c>
     </row>
     <row r="303">
@@ -41215,7 +41215,7 @@
         <v>-1.7697</v>
       </c>
       <c r="D308" t="n">
-        <v>-0.7765</v>
+        <v>-0.7764</v>
       </c>
       <c r="E308" t="n">
         <v>0.2168</v>
@@ -41296,7 +41296,7 @@
         <v>0.1868</v>
       </c>
       <c r="C311" t="n">
-        <v>-1.0256</v>
+        <v>-1.0255</v>
       </c>
       <c r="D311" t="n">
         <v>-0.4194</v>
@@ -41305,13 +41305,13 @@
         <v>0.1868</v>
       </c>
       <c r="F311" t="n">
-        <v>-1.0256</v>
+        <v>-1.0255</v>
       </c>
       <c r="G311" t="n">
         <v>0.1868</v>
       </c>
       <c r="M311" t="n">
-        <v>-1.0256</v>
+        <v>-1.0255</v>
       </c>
     </row>
     <row r="312">
@@ -41464,22 +41464,22 @@
         <v>0.1126</v>
       </c>
       <c r="C317" t="n">
-        <v>0.7673</v>
+        <v>0.7674</v>
       </c>
       <c r="D317" t="n">
-        <v>0.4399</v>
+        <v>0.44</v>
       </c>
       <c r="E317" t="n">
         <v>0.1126</v>
       </c>
       <c r="F317" t="n">
-        <v>0.7673</v>
+        <v>0.7674</v>
       </c>
       <c r="G317" t="n">
         <v>0.1126</v>
       </c>
       <c r="M317" t="n">
-        <v>0.7673</v>
+        <v>0.7674</v>
       </c>
     </row>
     <row r="318">
@@ -41520,7 +41520,7 @@
         <v>0.111</v>
       </c>
       <c r="C319" t="n">
-        <v>0.9038</v>
+        <v>0.9039</v>
       </c>
       <c r="D319" t="n">
         <v>0.5074</v>
@@ -41529,13 +41529,13 @@
         <v>0.111</v>
       </c>
       <c r="F319" t="n">
-        <v>0.9038</v>
+        <v>0.9039</v>
       </c>
       <c r="G319" t="n">
         <v>0.111</v>
       </c>
       <c r="M319" t="n">
-        <v>0.9038</v>
+        <v>0.9039</v>
       </c>
     </row>
     <row r="320">
@@ -41551,7 +41551,7 @@
         <v>0.8047</v>
       </c>
       <c r="D320" t="n">
-        <v>0.4513</v>
+        <v>0.4514</v>
       </c>
       <c r="E320" t="n">
         <v>0.098</v>
@@ -41660,7 +41660,7 @@
         <v>-0.1766</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2109</v>
+        <v>0.211</v>
       </c>
       <c r="D324" t="n">
         <v>0.0172</v>
@@ -41669,13 +41669,13 @@
         <v>-0.1766</v>
       </c>
       <c r="F324" t="n">
-        <v>0.2109</v>
+        <v>0.211</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1766</v>
       </c>
       <c r="M324" t="n">
-        <v>0.2109</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="325">
@@ -41716,7 +41716,7 @@
         <v>-0.2578</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1851</v>
+        <v>0.1852</v>
       </c>
       <c r="D326" t="n">
         <v>-0.0363</v>
@@ -41725,13 +41725,13 @@
         <v>-0.2578</v>
       </c>
       <c r="F326" t="n">
-        <v>0.1851</v>
+        <v>0.1852</v>
       </c>
       <c r="G326" t="n">
         <v>-0.2578</v>
       </c>
       <c r="M326" t="n">
-        <v>0.1851</v>
+        <v>0.1852</v>
       </c>
     </row>
     <row r="327">
@@ -41856,7 +41856,7 @@
         <v>-0.1684</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.1228</v>
+        <v>-0.1227</v>
       </c>
       <c r="D331" t="n">
         <v>-0.1456</v>
@@ -41865,13 +41865,13 @@
         <v>-0.1684</v>
       </c>
       <c r="F331" t="n">
-        <v>-0.1228</v>
+        <v>-0.1227</v>
       </c>
       <c r="G331" t="n">
         <v>-0.1684</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.1228</v>
+        <v>-0.1227</v>
       </c>
     </row>
     <row r="332">
@@ -41912,7 +41912,7 @@
         <v>-0.1731</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.2412</v>
+        <v>-0.2411</v>
       </c>
       <c r="D333" t="n">
         <v>-0.2071</v>
@@ -41921,13 +41921,13 @@
         <v>-0.1731</v>
       </c>
       <c r="F333" t="n">
-        <v>-0.2412</v>
+        <v>-0.2411</v>
       </c>
       <c r="G333" t="n">
         <v>-0.1731</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.2412</v>
+        <v>-0.2411</v>
       </c>
     </row>
     <row r="334">
@@ -41968,7 +41968,7 @@
         <v>-0.0742</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2626</v>
+        <v>-0.2625</v>
       </c>
       <c r="D335" t="n">
         <v>-0.1684</v>
@@ -41977,13 +41977,13 @@
         <v>-0.0742</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.2626</v>
+        <v>-0.2625</v>
       </c>
       <c r="G335" t="n">
         <v>-0.0742</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.2626</v>
+        <v>-0.2625</v>
       </c>
     </row>
     <row r="336">
@@ -42332,7 +42332,7 @@
         <v>-0.1203</v>
       </c>
       <c r="C348" t="n">
-        <v>0.5125</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="D348" t="n">
         <v>0.1961</v>
@@ -42341,13 +42341,13 @@
         <v>-0.1203</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5125</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G348" t="n">
         <v>-0.1203</v>
       </c>
       <c r="M348" t="n">
-        <v>0.5125</v>
+        <v>0.5125999999999999</v>
       </c>
     </row>
     <row r="349">
@@ -42416,7 +42416,7 @@
         <v>-0.0762</v>
       </c>
       <c r="C351" t="n">
-        <v>0.9328</v>
+        <v>0.9329</v>
       </c>
       <c r="D351" t="n">
         <v>0.4283</v>
@@ -42425,13 +42425,13 @@
         <v>-0.0762</v>
       </c>
       <c r="F351" t="n">
-        <v>0.9328</v>
+        <v>0.9329</v>
       </c>
       <c r="G351" t="n">
         <v>-0.0762</v>
       </c>
       <c r="M351" t="n">
-        <v>0.9328</v>
+        <v>0.9329</v>
       </c>
     </row>
     <row r="352">
@@ -42472,7 +42472,7 @@
         <v>0.0672</v>
       </c>
       <c r="C353" t="n">
-        <v>1.2358</v>
+        <v>1.2359</v>
       </c>
       <c r="D353" t="n">
         <v>0.6515</v>
@@ -42481,13 +42481,13 @@
         <v>0.0672</v>
       </c>
       <c r="F353" t="n">
-        <v>1.2358</v>
+        <v>1.2359</v>
       </c>
       <c r="G353" t="n">
         <v>0.0672</v>
       </c>
       <c r="M353" t="n">
-        <v>1.2358</v>
+        <v>1.2359</v>
       </c>
     </row>
     <row r="354">
@@ -42612,7 +42612,7 @@
         <v>0.208</v>
       </c>
       <c r="C358" t="n">
-        <v>0.2659</v>
+        <v>0.266</v>
       </c>
       <c r="D358" t="n">
         <v>0.237</v>
@@ -42621,13 +42621,13 @@
         <v>0.208</v>
       </c>
       <c r="F358" t="n">
-        <v>0.2659</v>
+        <v>0.266</v>
       </c>
       <c r="G358" t="n">
         <v>0.208</v>
       </c>
       <c r="M358" t="n">
-        <v>0.2659</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="359">
@@ -42640,7 +42640,7 @@
         <v>0.3068</v>
       </c>
       <c r="C359" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="D359" t="n">
         <v>0.1867</v>
@@ -42649,13 +42649,13 @@
         <v>0.3068</v>
       </c>
       <c r="F359" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="G359" t="n">
         <v>0.3068</v>
       </c>
       <c r="M359" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="360">
@@ -42724,16 +42724,16 @@
         <v>-0.5449000000000001</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
       <c r="D362" t="n">
-        <v>-0.262</v>
+        <v>-0.2619</v>
       </c>
       <c r="E362" t="n">
         <v>-0.5449000000000001</v>
       </c>
       <c r="F362" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
       <c r="G362" t="n">
         <v>0.2132</v>
@@ -42742,7 +42742,7 @@
         <v>-1.3029</v>
       </c>
       <c r="M362" t="n">
-        <v>0.0209</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="363">
@@ -42755,7 +42755,7 @@
         <v>-0.5022</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.222</v>
+        <v>-0.2219</v>
       </c>
       <c r="D363" t="n">
         <v>-0.3621</v>
@@ -42764,7 +42764,7 @@
         <v>-0.5022</v>
       </c>
       <c r="F363" t="n">
-        <v>-0.222</v>
+        <v>-0.2219</v>
       </c>
       <c r="G363" t="n">
         <v>0.2615</v>
@@ -42773,7 +42773,7 @@
         <v>-1.2659</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.222</v>
+        <v>-0.2219</v>
       </c>
     </row>
     <row r="364">
@@ -42879,7 +42879,7 @@
         <v>-0.4676</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
       <c r="D367" t="n">
         <v>-0.2867</v>
@@ -42888,7 +42888,7 @@
         <v>-0.4676</v>
       </c>
       <c r="F367" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
       <c r="G367" t="n">
         <v>0.2099</v>
@@ -42897,7 +42897,7 @@
         <v>-1.1451</v>
       </c>
       <c r="M367" t="n">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
     </row>
     <row r="368">
@@ -42941,7 +42941,7 @@
         <v>-0.4514</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.4029</v>
+        <v>-0.4028</v>
       </c>
       <c r="D369" t="n">
         <v>-0.4271</v>
@@ -42950,7 +42950,7 @@
         <v>-0.4514</v>
       </c>
       <c r="F369" t="n">
-        <v>-0.4029</v>
+        <v>-0.4028</v>
       </c>
       <c r="G369" t="n">
         <v>0.1623</v>
@@ -42959,7 +42959,7 @@
         <v>-1.065</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.4029</v>
+        <v>-0.4028</v>
       </c>
     </row>
     <row r="370">
@@ -43003,16 +43003,16 @@
         <v>-0.4547</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.3086</v>
+        <v>-0.3085</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.3817</v>
+        <v>-0.3816</v>
       </c>
       <c r="E371" t="n">
         <v>-0.4547</v>
       </c>
       <c r="F371" t="n">
-        <v>-0.3086</v>
+        <v>-0.3085</v>
       </c>
       <c r="G371" t="n">
         <v>0.2113</v>
@@ -43021,7 +43021,7 @@
         <v>-1.1208</v>
       </c>
       <c r="M371" t="n">
-        <v>-0.3086</v>
+        <v>-0.3085</v>
       </c>
     </row>
     <row r="372">
@@ -43034,16 +43034,16 @@
         <v>-0.5503</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.3362</v>
+        <v>-0.3361</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.4433</v>
+        <v>-0.4432</v>
       </c>
       <c r="E372" t="n">
         <v>-0.5503</v>
       </c>
       <c r="F372" t="n">
-        <v>-0.3362</v>
+        <v>-0.3361</v>
       </c>
       <c r="G372" t="n">
         <v>0.1666</v>
@@ -43052,7 +43052,7 @@
         <v>-1.2673</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.3362</v>
+        <v>-0.3361</v>
       </c>
     </row>
     <row r="373">
@@ -43065,7 +43065,7 @@
         <v>-0.5386</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.2952</v>
+        <v>-0.2951</v>
       </c>
       <c r="D373" t="n">
         <v>-0.4169</v>
@@ -43074,7 +43074,7 @@
         <v>-0.5386</v>
       </c>
       <c r="F373" t="n">
-        <v>-0.2952</v>
+        <v>-0.2951</v>
       </c>
       <c r="G373" t="n">
         <v>0.1671</v>
@@ -43083,7 +43083,7 @@
         <v>-1.2442</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.2952</v>
+        <v>-0.2951</v>
       </c>
     </row>
     <row r="374">
@@ -43096,7 +43096,7 @@
         <v>-0.5405</v>
       </c>
       <c r="C374" t="n">
-        <v>0.4903</v>
+        <v>0.4904</v>
       </c>
       <c r="D374" t="n">
         <v>-0.0251</v>
@@ -43105,7 +43105,7 @@
         <v>-0.5405</v>
       </c>
       <c r="F374" t="n">
-        <v>0.4903</v>
+        <v>0.4904</v>
       </c>
       <c r="G374" t="n">
         <v>0.3121</v>
@@ -43255,7 +43255,7 @@
         <v>0.9013</v>
       </c>
       <c r="M377" t="n">
-        <v>0.832</v>
+        <v>0.8321</v>
       </c>
     </row>
     <row r="378">
@@ -43612,7 +43612,7 @@
         <v>-0.4493</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.272</v>
+        <v>-0.2719</v>
       </c>
       <c r="D386" t="n">
         <v>-0.3606</v>
@@ -43621,7 +43621,7 @@
         <v>-0.4493</v>
       </c>
       <c r="F386" t="n">
-        <v>-0.272</v>
+        <v>-0.2719</v>
       </c>
       <c r="G386" t="n">
         <v>0.1993</v>
@@ -43943,7 +43943,7 @@
         <v>-0.652</v>
       </c>
       <c r="M393" t="n">
-        <v>0.4013</v>
+        <v>0.4014</v>
       </c>
     </row>
     <row r="394">
@@ -44171,7 +44171,7 @@
         <v>-0.8481</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.7147</v>
+        <v>-0.7146</v>
       </c>
       <c r="D399" t="n">
         <v>-0.7814</v>
@@ -44180,7 +44180,7 @@
         <v>-0.8481</v>
       </c>
       <c r="F399" t="n">
-        <v>-0.7147</v>
+        <v>-0.7146</v>
       </c>
       <c r="G399" t="n">
         <v>-0.0015</v>
@@ -44975,7 +44975,7 @@
         <v>-2.8637</v>
       </c>
       <c r="M417" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.7222</v>
       </c>
     </row>
     <row r="418">
@@ -45104,7 +45104,7 @@
         <v>-2.8123</v>
       </c>
       <c r="M420" t="n">
-        <v>-0.623</v>
+        <v>-0.6229</v>
       </c>
     </row>
     <row r="421">
@@ -45663,7 +45663,7 @@
         <v>-0.1164</v>
       </c>
       <c r="M433" t="n">
-        <v>0.5097</v>
+        <v>0.5098</v>
       </c>
     </row>
     <row r="434">
@@ -45706,7 +45706,7 @@
         <v>-0.0469</v>
       </c>
       <c r="M434" t="n">
-        <v>0.4511</v>
+        <v>0.4512</v>
       </c>
     </row>
     <row r="435">
@@ -46007,7 +46007,7 @@
         <v>0.2186</v>
       </c>
       <c r="M441" t="n">
-        <v>0.5135</v>
+        <v>0.5135999999999999</v>
       </c>
     </row>
     <row r="442">
@@ -46136,7 +46136,7 @@
         <v>0.2365</v>
       </c>
       <c r="M444" t="n">
-        <v>0.2891</v>
+        <v>0.2892</v>
       </c>
     </row>
     <row r="445">
@@ -46308,7 +46308,7 @@
         <v>0.1996</v>
       </c>
       <c r="M448" t="n">
-        <v>0.1197</v>
+        <v>0.1198</v>
       </c>
     </row>
     <row r="449">
@@ -46324,7 +46324,7 @@
         <v>0.2667</v>
       </c>
       <c r="D449" t="n">
-        <v>-0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="E449" t="n">
         <v>-0.2788</v>
@@ -46566,7 +46566,7 @@
         <v>0.2311</v>
       </c>
       <c r="M454" t="n">
-        <v>0.2546</v>
+        <v>0.2547</v>
       </c>
     </row>
     <row r="455">
@@ -46609,7 +46609,7 @@
         <v>0.1664</v>
       </c>
       <c r="M455" t="n">
-        <v>0.3104</v>
+        <v>0.3105</v>
       </c>
     </row>
     <row r="456">
@@ -46738,7 +46738,7 @@
         <v>0.1907</v>
       </c>
       <c r="M458" t="n">
-        <v>0.3883</v>
+        <v>0.3884</v>
       </c>
     </row>
     <row r="459">
@@ -46840,7 +46840,7 @@
         <v>0.2693</v>
       </c>
       <c r="D461" t="n">
-        <v>-0.0679</v>
+        <v>-0.0678</v>
       </c>
       <c r="E461" t="n">
         <v>-0.405</v>
@@ -47340,7 +47340,7 @@
         <v>0.5993000000000001</v>
       </c>
       <c r="M472" t="n">
-        <v>0.2831</v>
+        <v>0.2832</v>
       </c>
     </row>
     <row r="473">
@@ -47383,7 +47383,7 @@
         <v>0.6619</v>
       </c>
       <c r="M473" t="n">
-        <v>0.4914</v>
+        <v>0.4915</v>
       </c>
     </row>
     <row r="474">
@@ -47985,7 +47985,7 @@
         <v>0.5768</v>
       </c>
       <c r="M487" t="n">
-        <v>0.2593</v>
+        <v>0.2594</v>
       </c>
     </row>
     <row r="488">
@@ -48084,7 +48084,7 @@
         <v>0.8817</v>
       </c>
       <c r="C490" t="n">
-        <v>0.9009</v>
+        <v>0.901</v>
       </c>
       <c r="D490" t="n">
         <v>0.8913</v>
@@ -48093,7 +48093,7 @@
         <v>0.8817</v>
       </c>
       <c r="F490" t="n">
-        <v>0.9009</v>
+        <v>0.901</v>
       </c>
       <c r="G490" t="n">
         <v>1.646</v>
@@ -48157,7 +48157,7 @@
         <v>0.5944</v>
       </c>
       <c r="M491" t="n">
-        <v>0.2409</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="492">
@@ -48200,7 +48200,7 @@
         <v>0.5242</v>
       </c>
       <c r="M492" t="n">
-        <v>0.3175</v>
+        <v>0.3176</v>
       </c>
     </row>
     <row r="493">
@@ -48286,7 +48286,7 @@
         <v>0.5121</v>
       </c>
       <c r="M494" t="n">
-        <v>0.454</v>
+        <v>0.4541</v>
       </c>
     </row>
     <row r="495">
@@ -48716,7 +48716,7 @@
         <v>0.447</v>
       </c>
       <c r="M504" t="n">
-        <v>0.4216</v>
+        <v>0.4217</v>
       </c>
     </row>
     <row r="505">
@@ -48772,7 +48772,7 @@
         <v>0.4876</v>
       </c>
       <c r="C506" t="n">
-        <v>0.6264</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="D506" t="n">
         <v>0.5570000000000001</v>
@@ -48781,7 +48781,7 @@
         <v>0.4876</v>
       </c>
       <c r="F506" t="n">
-        <v>0.6264</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="G506" t="n">
         <v>0.2552</v>
@@ -48888,7 +48888,7 @@
         <v>0.4586</v>
       </c>
       <c r="M508" t="n">
-        <v>0.44</v>
+        <v>0.4401</v>
       </c>
     </row>
     <row r="509">
@@ -48931,7 +48931,7 @@
         <v>0.4169</v>
       </c>
       <c r="M509" t="n">
-        <v>0.5465</v>
+        <v>0.5466</v>
       </c>
     </row>
     <row r="510">
@@ -48987,7 +48987,7 @@
         <v>0.3327</v>
       </c>
       <c r="C511" t="n">
-        <v>0.615</v>
+        <v>0.6151</v>
       </c>
       <c r="D511" t="n">
         <v>0.4739</v>
@@ -48996,7 +48996,7 @@
         <v>0.3327</v>
       </c>
       <c r="F511" t="n">
-        <v>0.615</v>
+        <v>0.6151</v>
       </c>
       <c r="G511" t="n">
         <v>0.1507</v>
@@ -49275,7 +49275,7 @@
         <v>0.2767</v>
       </c>
       <c r="M517" t="n">
-        <v>0.475</v>
+        <v>0.4751</v>
       </c>
     </row>
     <row r="518">
@@ -49361,7 +49361,7 @@
         <v>0.2866</v>
       </c>
       <c r="M519" t="n">
-        <v>0.4396</v>
+        <v>0.4397</v>
       </c>
     </row>
     <row r="520">
@@ -49933,7 +49933,7 @@
         <v>0.2989</v>
       </c>
       <c r="C533" t="n">
-        <v>0.1016</v>
+        <v>0.1017</v>
       </c>
       <c r="D533" t="n">
         <v>0.2003</v>
@@ -49942,7 +49942,7 @@
         <v>0.2989</v>
       </c>
       <c r="F533" t="n">
-        <v>0.1016</v>
+        <v>0.1017</v>
       </c>
       <c r="G533" t="n">
         <v>0.6424</v>
@@ -50006,7 +50006,7 @@
         <v>0.0319</v>
       </c>
       <c r="M534" t="n">
-        <v>0.2822</v>
+        <v>0.2823</v>
       </c>
     </row>
     <row r="535">
@@ -50148,7 +50148,7 @@
         <v>0.2917</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.0211</v>
+        <v>-0.021</v>
       </c>
       <c r="D538" t="n">
         <v>0.1353</v>
@@ -50157,7 +50157,7 @@
         <v>0.2917</v>
       </c>
       <c r="F538" t="n">
-        <v>-0.0211</v>
+        <v>-0.021</v>
       </c>
       <c r="G538" t="n">
         <v>0.7296</v>
@@ -51038,7 +51038,7 @@
         <v>-0.8535</v>
       </c>
       <c r="M558" t="n">
-        <v>-0.2747</v>
+        <v>-0.2746</v>
       </c>
     </row>
     <row r="559">
@@ -51054,7 +51054,7 @@
         <v>-0.3381</v>
       </c>
       <c r="D559" t="n">
-        <v>0.2064</v>
+        <v>0.2065</v>
       </c>
       <c r="E559" t="n">
         <v>0.751</v>
@@ -51183,7 +51183,7 @@
         <v>-0.066</v>
       </c>
       <c r="D562" t="n">
-        <v>0.404</v>
+        <v>0.4041</v>
       </c>
       <c r="E562" t="n">
         <v>0.8741</v>
@@ -51696,16 +51696,16 @@
         <v>0.2461</v>
       </c>
       <c r="C574" t="n">
-        <v>0.2615</v>
+        <v>0.2616</v>
       </c>
       <c r="D574" t="n">
-        <v>0.2538</v>
+        <v>0.2539</v>
       </c>
       <c r="E574" t="n">
         <v>0.2461</v>
       </c>
       <c r="F574" t="n">
-        <v>0.2615</v>
+        <v>0.2616</v>
       </c>
       <c r="G574" t="n">
         <v>0.3436</v>
@@ -52040,7 +52040,7 @@
         <v>0.4614</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0427</v>
+        <v>0.0428</v>
       </c>
       <c r="D582" t="n">
         <v>0.2521</v>
@@ -52049,7 +52049,7 @@
         <v>0.4614</v>
       </c>
       <c r="F582" t="n">
-        <v>0.0427</v>
+        <v>0.0428</v>
       </c>
       <c r="G582" t="n">
         <v>1.271</v>
@@ -52113,7 +52113,7 @@
         <v>0.6334</v>
       </c>
       <c r="M583" t="n">
-        <v>-0.3354</v>
+        <v>-0.3353</v>
       </c>
     </row>
     <row r="584">
@@ -52258,7 +52258,7 @@
         <v>-0.2767</v>
       </c>
       <c r="D587" t="n">
-        <v>0.1842</v>
+        <v>0.1843</v>
       </c>
       <c r="E587" t="n">
         <v>0.6452</v>
@@ -52672,7 +52672,7 @@
         <v>0.5352</v>
       </c>
       <c r="M596" t="n">
-        <v>-0.7734</v>
+        <v>-0.7733</v>
       </c>
     </row>
     <row r="597">
@@ -53704,7 +53704,7 @@
         <v>0.3876</v>
       </c>
       <c r="M620" t="n">
-        <v>-0.1297</v>
+        <v>-0.1296</v>
       </c>
     </row>
     <row r="621">
@@ -53720,7 +53720,7 @@
         <v>-0.2412</v>
       </c>
       <c r="D621" t="n">
-        <v>0.1198</v>
+        <v>0.1199</v>
       </c>
       <c r="E621" t="n">
         <v>0.4809</v>
@@ -53790,7 +53790,7 @@
         <v>0.4615</v>
       </c>
       <c r="M622" t="n">
-        <v>-0.114</v>
+        <v>-0.1139</v>
       </c>
     </row>
     <row r="623">
@@ -53919,7 +53919,7 @@
         <v>0.381</v>
       </c>
       <c r="M625" t="n">
-        <v>-0.074</v>
+        <v>-0.07389999999999999</v>
       </c>
     </row>
     <row r="626">
@@ -54048,7 +54048,7 @@
         <v>0.4399</v>
       </c>
       <c r="M628" t="n">
-        <v>-0.0055</v>
+        <v>-0.0054</v>
       </c>
     </row>
     <row r="629">
@@ -54319,16 +54319,16 @@
         <v>0.4308</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1691</v>
+        <v>-0.1706</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1309</v>
+        <v>0.1301</v>
       </c>
       <c r="E635" t="n">
         <v>0.4308</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1691</v>
+        <v>-0.1706</v>
       </c>
       <c r="G635" t="n">
         <v>0.6662</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.3955</v>
+        <v>0.3911</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -2532,7 +2532,7 @@
         <v>-1.42</v>
       </c>
       <c r="K159" t="n">
-        <v>-3.177</v>
+        <v>-3.176</v>
       </c>
     </row>
     <row r="160">
@@ -2883,7 +2883,7 @@
         <v>-1.261</v>
       </c>
       <c r="K186" t="n">
-        <v>-0.733</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="187">
@@ -3442,7 +3442,7 @@
         <v>-0.508</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.355</v>
+        <v>-0.354</v>
       </c>
     </row>
     <row r="230">
@@ -4638,7 +4638,7 @@
         <v>-0.131</v>
       </c>
       <c r="K321" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="322">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>11.089</v>
+        <v>11.16</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>0.75</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="13">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.06</v>
+        <v>1.061</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="14">
@@ -34518,10 +34518,10 @@
         <v>0.0141</v>
       </c>
       <c r="G635" t="n">
-        <v>1.0605</v>
+        <v>1.0614</v>
       </c>
       <c r="H635" t="n">
-        <v>11.0888</v>
+        <v>11.1596</v>
       </c>
       <c r="I635" t="n">
         <v>1.2932</v>
@@ -37547,7 +37547,7 @@
         <v>-2.954</v>
       </c>
       <c r="D177" t="n">
-        <v>-2.245</v>
+        <v>-2.2449</v>
       </c>
       <c r="E177" t="n">
         <v>-1.5359</v>
@@ -38048,7 +38048,7 @@
         <v>-1.372</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.7211</v>
+        <v>-0.721</v>
       </c>
       <c r="D195" t="n">
         <v>-1.0465</v>
@@ -38057,13 +38057,13 @@
         <v>-1.372</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.7211</v>
+        <v>-0.721</v>
       </c>
       <c r="G195" t="n">
         <v>-1.372</v>
       </c>
       <c r="M195" t="n">
-        <v>-0.7211</v>
+        <v>-0.721</v>
       </c>
     </row>
     <row r="196">
@@ -38471,7 +38471,7 @@
         <v>-2.0739</v>
       </c>
       <c r="D210" t="n">
-        <v>-1.9804</v>
+        <v>-1.9803</v>
       </c>
       <c r="E210" t="n">
         <v>-1.8868</v>
@@ -38583,7 +38583,7 @@
         <v>-0.7343</v>
       </c>
       <c r="D214" t="n">
-        <v>-1.1193</v>
+        <v>-1.1192</v>
       </c>
       <c r="E214" t="n">
         <v>-1.5042</v>
@@ -38779,7 +38779,7 @@
         <v>-0.1357</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.403</v>
+        <v>-0.4029</v>
       </c>
       <c r="E221" t="n">
         <v>-0.6702</v>
@@ -38804,22 +38804,22 @@
         <v>-0.7244</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.1523</v>
+        <v>-0.1522</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.4384</v>
+        <v>-0.4383</v>
       </c>
       <c r="E222" t="n">
         <v>-0.7244</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.1523</v>
+        <v>-0.1522</v>
       </c>
       <c r="G222" t="n">
         <v>-0.7244</v>
       </c>
       <c r="M222" t="n">
-        <v>-0.1523</v>
+        <v>-0.1522</v>
       </c>
     </row>
     <row r="223">
@@ -39000,7 +39000,7 @@
         <v>-0.9002</v>
       </c>
       <c r="C229" t="n">
-        <v>0.024</v>
+        <v>0.0241</v>
       </c>
       <c r="D229" t="n">
         <v>-0.4381</v>
@@ -39009,13 +39009,13 @@
         <v>-0.9002</v>
       </c>
       <c r="F229" t="n">
-        <v>0.024</v>
+        <v>0.0241</v>
       </c>
       <c r="G229" t="n">
         <v>-0.9002</v>
       </c>
       <c r="M229" t="n">
-        <v>0.024</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="230">
@@ -39028,7 +39028,7 @@
         <v>-0.617</v>
       </c>
       <c r="C230" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="D230" t="n">
         <v>-0.2728</v>
@@ -39037,13 +39037,13 @@
         <v>-0.617</v>
       </c>
       <c r="F230" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="G230" t="n">
         <v>-0.617</v>
       </c>
       <c r="M230" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -39084,7 +39084,7 @@
         <v>-0.3912</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.003</v>
+        <v>-0.0029</v>
       </c>
       <c r="D232" t="n">
         <v>-0.1971</v>
@@ -39093,13 +39093,13 @@
         <v>-0.3912</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.003</v>
+        <v>-0.0029</v>
       </c>
       <c r="G232" t="n">
         <v>-0.3912</v>
       </c>
       <c r="M232" t="n">
-        <v>-0.003</v>
+        <v>-0.0029</v>
       </c>
     </row>
     <row r="233">
@@ -39367,7 +39367,7 @@
         <v>-0.7223000000000001</v>
       </c>
       <c r="D242" t="n">
-        <v>-0.4891</v>
+        <v>-0.489</v>
       </c>
       <c r="E242" t="n">
         <v>-0.2558</v>
@@ -39448,7 +39448,7 @@
         <v>-0.3581</v>
       </c>
       <c r="C245" t="n">
-        <v>-1.194</v>
+        <v>-1.1939</v>
       </c>
       <c r="D245" t="n">
         <v>-0.776</v>
@@ -39457,13 +39457,13 @@
         <v>-0.3581</v>
       </c>
       <c r="F245" t="n">
-        <v>-1.194</v>
+        <v>-1.1939</v>
       </c>
       <c r="G245" t="n">
         <v>-0.3581</v>
       </c>
       <c r="M245" t="n">
-        <v>-1.194</v>
+        <v>-1.1939</v>
       </c>
     </row>
     <row r="246">
@@ -39616,7 +39616,7 @@
         <v>-0.6738</v>
       </c>
       <c r="C251" t="n">
-        <v>-1.1943</v>
+        <v>-1.1942</v>
       </c>
       <c r="D251" t="n">
         <v>-0.9340000000000001</v>
@@ -39625,13 +39625,13 @@
         <v>-0.6738</v>
       </c>
       <c r="F251" t="n">
-        <v>-1.1943</v>
+        <v>-1.1942</v>
       </c>
       <c r="G251" t="n">
         <v>-0.6738</v>
       </c>
       <c r="M251" t="n">
-        <v>-1.1943</v>
+        <v>-1.1942</v>
       </c>
     </row>
     <row r="252">
@@ -39784,7 +39784,7 @@
         <v>-0.4634</v>
       </c>
       <c r="C257" t="n">
-        <v>-1.1876</v>
+        <v>-1.1875</v>
       </c>
       <c r="D257" t="n">
         <v>-0.8255</v>
@@ -39793,13 +39793,13 @@
         <v>-0.4634</v>
       </c>
       <c r="F257" t="n">
-        <v>-1.1876</v>
+        <v>-1.1875</v>
       </c>
       <c r="G257" t="n">
         <v>-0.4634</v>
       </c>
       <c r="M257" t="n">
-        <v>-1.1876</v>
+        <v>-1.1875</v>
       </c>
     </row>
     <row r="258">
@@ -40039,7 +40039,7 @@
         <v>-1.0176</v>
       </c>
       <c r="D266" t="n">
-        <v>-0.5305</v>
+        <v>-0.5304</v>
       </c>
       <c r="E266" t="n">
         <v>-0.0433</v>
@@ -40260,7 +40260,7 @@
         <v>0.1586</v>
       </c>
       <c r="C274" t="n">
-        <v>0.227</v>
+        <v>0.2271</v>
       </c>
       <c r="D274" t="n">
         <v>0.1928</v>
@@ -40269,13 +40269,13 @@
         <v>0.1586</v>
       </c>
       <c r="F274" t="n">
-        <v>0.227</v>
+        <v>0.2271</v>
       </c>
       <c r="G274" t="n">
         <v>0.1586</v>
       </c>
       <c r="M274" t="n">
-        <v>0.227</v>
+        <v>0.2271</v>
       </c>
     </row>
     <row r="275">
@@ -40316,7 +40316,7 @@
         <v>0.2677</v>
       </c>
       <c r="C276" t="n">
-        <v>0.1688</v>
+        <v>0.1689</v>
       </c>
       <c r="D276" t="n">
         <v>0.2183</v>
@@ -40325,13 +40325,13 @@
         <v>0.2677</v>
       </c>
       <c r="F276" t="n">
-        <v>0.1688</v>
+        <v>0.1689</v>
       </c>
       <c r="G276" t="n">
         <v>0.2677</v>
       </c>
       <c r="M276" t="n">
-        <v>0.1688</v>
+        <v>0.1689</v>
       </c>
     </row>
     <row r="277">
@@ -40512,7 +40512,7 @@
         <v>0.906</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="D283" t="n">
         <v>0.417</v>
@@ -40521,13 +40521,13 @@
         <v>0.906</v>
       </c>
       <c r="F283" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="G283" t="n">
         <v>0.906</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07190000000000001</v>
       </c>
     </row>
     <row r="284">
@@ -40767,7 +40767,7 @@
         <v>-0.1414</v>
       </c>
       <c r="D292" t="n">
-        <v>0.3865</v>
+        <v>0.3866</v>
       </c>
       <c r="E292" t="n">
         <v>0.9145</v>
@@ -40851,7 +40851,7 @@
         <v>0.3804</v>
       </c>
       <c r="D295" t="n">
-        <v>0.2237</v>
+        <v>0.2238</v>
       </c>
       <c r="E295" t="n">
         <v>0.06710000000000001</v>
@@ -40876,7 +40876,7 @@
         <v>0.0151</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1693</v>
+        <v>0.1694</v>
       </c>
       <c r="D296" t="n">
         <v>0.0922</v>
@@ -40885,13 +40885,13 @@
         <v>0.0151</v>
       </c>
       <c r="F296" t="n">
-        <v>0.1693</v>
+        <v>0.1694</v>
       </c>
       <c r="G296" t="n">
         <v>0.0151</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1693</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="297">
@@ -40932,7 +40932,7 @@
         <v>-0.1118</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.1641</v>
+        <v>-0.164</v>
       </c>
       <c r="D298" t="n">
         <v>-0.1379</v>
@@ -40941,13 +40941,13 @@
         <v>-0.1118</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.1641</v>
+        <v>-0.164</v>
       </c>
       <c r="G298" t="n">
         <v>-0.1118</v>
       </c>
       <c r="M298" t="n">
-        <v>-0.1641</v>
+        <v>-0.164</v>
       </c>
     </row>
     <row r="299">
@@ -41075,7 +41075,7 @@
         <v>-1.4311</v>
       </c>
       <c r="D303" t="n">
-        <v>-0.6697</v>
+        <v>-0.6696</v>
       </c>
       <c r="E303" t="n">
         <v>0.09180000000000001</v>
@@ -41156,7 +41156,7 @@
         <v>0.2375</v>
       </c>
       <c r="C306" t="n">
-        <v>-1.6394</v>
+        <v>-1.6393</v>
       </c>
       <c r="D306" t="n">
         <v>-0.7009</v>
@@ -41165,13 +41165,13 @@
         <v>0.2375</v>
       </c>
       <c r="F306" t="n">
-        <v>-1.6394</v>
+        <v>-1.6393</v>
       </c>
       <c r="G306" t="n">
         <v>0.2375</v>
       </c>
       <c r="M306" t="n">
-        <v>-1.6394</v>
+        <v>-1.6393</v>
       </c>
     </row>
     <row r="307">
@@ -41324,7 +41324,7 @@
         <v>0.1342</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.8734</v>
+        <v>-0.8733</v>
       </c>
       <c r="D312" t="n">
         <v>-0.3696</v>
@@ -41333,13 +41333,13 @@
         <v>0.1342</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.8734</v>
+        <v>-0.8733</v>
       </c>
       <c r="G312" t="n">
         <v>0.1342</v>
       </c>
       <c r="M312" t="n">
-        <v>-0.8734</v>
+        <v>-0.8733</v>
       </c>
     </row>
     <row r="313">
@@ -41632,7 +41632,7 @@
         <v>-0.2272</v>
       </c>
       <c r="C323" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
       <c r="D323" t="n">
         <v>0.0379</v>
@@ -41641,13 +41641,13 @@
         <v>-0.2272</v>
       </c>
       <c r="F323" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
       <c r="G323" t="n">
         <v>-0.2272</v>
       </c>
       <c r="M323" t="n">
-        <v>0.3029</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="324">
@@ -41828,7 +41828,7 @@
         <v>-0.2165</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.1384</v>
+        <v>-0.1383</v>
       </c>
       <c r="D330" t="n">
         <v>-0.1774</v>
@@ -41837,13 +41837,13 @@
         <v>-0.2165</v>
       </c>
       <c r="F330" t="n">
-        <v>-0.1384</v>
+        <v>-0.1383</v>
       </c>
       <c r="G330" t="n">
         <v>-0.2165</v>
       </c>
       <c r="M330" t="n">
-        <v>-0.1384</v>
+        <v>-0.1383</v>
       </c>
     </row>
     <row r="331">
@@ -41859,7 +41859,7 @@
         <v>-0.1227</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.1456</v>
+        <v>-0.1455</v>
       </c>
       <c r="E331" t="n">
         <v>-0.1684</v>
@@ -41996,7 +41996,7 @@
         <v>-0.1221</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.2049</v>
+        <v>-0.2048</v>
       </c>
       <c r="D336" t="n">
         <v>-0.1635</v>
@@ -42005,13 +42005,13 @@
         <v>-0.1221</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.2049</v>
+        <v>-0.2048</v>
       </c>
       <c r="G336" t="n">
         <v>-0.1221</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.2049</v>
+        <v>-0.2048</v>
       </c>
     </row>
     <row r="337">
@@ -42024,7 +42024,7 @@
         <v>-0.1721</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2842</v>
+        <v>-0.2841</v>
       </c>
       <c r="D337" t="n">
         <v>-0.2281</v>
@@ -42033,13 +42033,13 @@
         <v>-0.1721</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.2842</v>
+        <v>-0.2841</v>
       </c>
       <c r="G337" t="n">
         <v>-0.1721</v>
       </c>
       <c r="M337" t="n">
-        <v>-0.2842</v>
+        <v>-0.2841</v>
       </c>
     </row>
     <row r="338">
@@ -42083,7 +42083,7 @@
         <v>-0.2095</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.1668</v>
+        <v>-0.1667</v>
       </c>
       <c r="E339" t="n">
         <v>-0.124</v>
@@ -42108,7 +42108,7 @@
         <v>-0.0761</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0516</v>
+        <v>0.0517</v>
       </c>
       <c r="D340" t="n">
         <v>-0.0122</v>
@@ -42117,13 +42117,13 @@
         <v>-0.0761</v>
       </c>
       <c r="F340" t="n">
-        <v>0.0516</v>
+        <v>0.0517</v>
       </c>
       <c r="G340" t="n">
         <v>-0.0761</v>
       </c>
       <c r="M340" t="n">
-        <v>0.0516</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="341">
@@ -42164,7 +42164,7 @@
         <v>-0.1217</v>
       </c>
       <c r="C342" t="n">
-        <v>0.2254</v>
+        <v>0.2255</v>
       </c>
       <c r="D342" t="n">
         <v>0.0519</v>
@@ -42173,13 +42173,13 @@
         <v>-0.1217</v>
       </c>
       <c r="F342" t="n">
-        <v>0.2254</v>
+        <v>0.2255</v>
       </c>
       <c r="G342" t="n">
         <v>-0.1217</v>
       </c>
       <c r="M342" t="n">
-        <v>0.2254</v>
+        <v>0.2255</v>
       </c>
     </row>
     <row r="343">
@@ -42220,7 +42220,7 @@
         <v>-0.123</v>
       </c>
       <c r="C344" t="n">
-        <v>0.5609</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D344" t="n">
         <v>0.219</v>
@@ -42229,13 +42229,13 @@
         <v>-0.123</v>
       </c>
       <c r="F344" t="n">
-        <v>0.5609</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G344" t="n">
         <v>-0.123</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5609</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="345">
@@ -42276,7 +42276,7 @@
         <v>-0.1672</v>
       </c>
       <c r="C346" t="n">
-        <v>0.5245</v>
+        <v>0.5246</v>
       </c>
       <c r="D346" t="n">
         <v>0.1787</v>
@@ -42285,13 +42285,13 @@
         <v>-0.1672</v>
       </c>
       <c r="F346" t="n">
-        <v>0.5245</v>
+        <v>0.5246</v>
       </c>
       <c r="G346" t="n">
         <v>-0.1672</v>
       </c>
       <c r="M346" t="n">
-        <v>0.5245</v>
+        <v>0.5246</v>
       </c>
     </row>
     <row r="347">
@@ -42444,22 +42444,22 @@
         <v>-0.0278</v>
       </c>
       <c r="C352" t="n">
-        <v>1.0255</v>
+        <v>1.0256</v>
       </c>
       <c r="D352" t="n">
-        <v>0.4988</v>
+        <v>0.4989</v>
       </c>
       <c r="E352" t="n">
         <v>-0.0278</v>
       </c>
       <c r="F352" t="n">
-        <v>1.0255</v>
+        <v>1.0256</v>
       </c>
       <c r="G352" t="n">
         <v>-0.0278</v>
       </c>
       <c r="M352" t="n">
-        <v>1.0255</v>
+        <v>1.0256</v>
       </c>
     </row>
     <row r="353">
@@ -42528,7 +42528,7 @@
         <v>0.0709</v>
       </c>
       <c r="C355" t="n">
-        <v>1.0939</v>
+        <v>1.094</v>
       </c>
       <c r="D355" t="n">
         <v>0.5824</v>
@@ -42537,13 +42537,13 @@
         <v>0.0709</v>
       </c>
       <c r="F355" t="n">
-        <v>1.0939</v>
+        <v>1.094</v>
       </c>
       <c r="G355" t="n">
         <v>0.0709</v>
       </c>
       <c r="M355" t="n">
-        <v>1.0939</v>
+        <v>1.094</v>
       </c>
     </row>
     <row r="356">
@@ -42559,7 +42559,7 @@
         <v>0.3037</v>
       </c>
       <c r="D356" t="n">
-        <v>0.2352</v>
+        <v>0.2353</v>
       </c>
       <c r="E356" t="n">
         <v>0.1668</v>
@@ -42851,7 +42851,7 @@
         <v>-0.2351</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.3402</v>
+        <v>-0.3401</v>
       </c>
       <c r="E366" t="n">
         <v>-0.4452</v>
@@ -42882,7 +42882,7 @@
         <v>-0.1057</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.2867</v>
+        <v>-0.2866</v>
       </c>
       <c r="E367" t="n">
         <v>-0.4676</v>
@@ -42910,7 +42910,7 @@
         <v>-0.4776</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.1075</v>
+        <v>-0.1074</v>
       </c>
       <c r="D368" t="n">
         <v>-0.2925</v>
@@ -42919,7 +42919,7 @@
         <v>-0.4776</v>
       </c>
       <c r="F368" t="n">
-        <v>-0.1075</v>
+        <v>-0.1074</v>
       </c>
       <c r="G368" t="n">
         <v>0.159</v>
@@ -42928,7 +42928,7 @@
         <v>-1.1143</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.1075</v>
+        <v>-0.1074</v>
       </c>
     </row>
     <row r="369">
@@ -43099,7 +43099,7 @@
         <v>0.4904</v>
       </c>
       <c r="D374" t="n">
-        <v>-0.0251</v>
+        <v>-0.025</v>
       </c>
       <c r="E374" t="n">
         <v>-0.5405</v>
@@ -43169,7 +43169,7 @@
         <v>1.0309</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8122</v>
+        <v>0.8123</v>
       </c>
     </row>
     <row r="376">
@@ -43228,7 +43228,7 @@
         <v>0.3541</v>
       </c>
       <c r="D377" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0931</v>
       </c>
       <c r="E377" t="n">
         <v>-0.5404</v>
@@ -43470,7 +43470,7 @@
         <v>0.3495</v>
       </c>
       <c r="M382" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7829</v>
       </c>
     </row>
     <row r="383">
@@ -44029,7 +44029,7 @@
         <v>-0.8083</v>
       </c>
       <c r="M395" t="n">
-        <v>0.3636</v>
+        <v>0.3637</v>
       </c>
     </row>
     <row r="396">
@@ -44518,7 +44518,7 @@
         <v>-0.9137999999999999</v>
       </c>
       <c r="D407" t="n">
-        <v>-0.6705</v>
+        <v>-0.6704</v>
       </c>
       <c r="E407" t="n">
         <v>-0.4271</v>
@@ -45448,7 +45448,7 @@
         <v>-0.3802</v>
       </c>
       <c r="M428" t="n">
-        <v>0.6787</v>
+        <v>0.6788</v>
       </c>
     </row>
     <row r="429">
@@ -45835,7 +45835,7 @@
         <v>0.1695</v>
       </c>
       <c r="M437" t="n">
-        <v>0.4067</v>
+        <v>0.4068</v>
       </c>
     </row>
     <row r="438">
@@ -46394,7 +46394,7 @@
         <v>0.2242</v>
       </c>
       <c r="M450" t="n">
-        <v>0.182</v>
+        <v>0.1821</v>
       </c>
     </row>
     <row r="451">
@@ -46407,7 +46407,7 @@
         <v>-0.3436</v>
       </c>
       <c r="C451" t="n">
-        <v>0.2831</v>
+        <v>0.2832</v>
       </c>
       <c r="D451" t="n">
         <v>-0.0302</v>
@@ -46416,7 +46416,7 @@
         <v>-0.3436</v>
       </c>
       <c r="F451" t="n">
-        <v>0.2831</v>
+        <v>0.2832</v>
       </c>
       <c r="G451" t="n">
         <v>0.1219</v>
@@ -46695,7 +46695,7 @@
         <v>0.1266</v>
       </c>
       <c r="M457" t="n">
-        <v>0.3505</v>
+        <v>0.3506</v>
       </c>
     </row>
     <row r="458">
@@ -47555,7 +47555,7 @@
         <v>0.576</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2777</v>
+        <v>0.2778</v>
       </c>
     </row>
     <row r="478">
@@ -47912,7 +47912,7 @@
         <v>0.9717</v>
       </c>
       <c r="C486" t="n">
-        <v>1.0251</v>
+        <v>1.0252</v>
       </c>
       <c r="D486" t="n">
         <v>0.9984</v>
@@ -47921,7 +47921,7 @@
         <v>0.9717</v>
       </c>
       <c r="F486" t="n">
-        <v>1.0251</v>
+        <v>1.0252</v>
       </c>
       <c r="G486" t="n">
         <v>1.7925</v>
@@ -48028,7 +48028,7 @@
         <v>0.5834</v>
       </c>
       <c r="M488" t="n">
-        <v>0.2458</v>
+        <v>0.2459</v>
       </c>
     </row>
     <row r="489">
@@ -50780,7 +50780,7 @@
         <v>-0.7475000000000001</v>
       </c>
       <c r="M552" t="n">
-        <v>-0.2318</v>
+        <v>-0.2317</v>
       </c>
     </row>
     <row r="553">
@@ -50909,7 +50909,7 @@
         <v>-1.0435</v>
       </c>
       <c r="M555" t="n">
-        <v>-0.3194</v>
+        <v>-0.3193</v>
       </c>
     </row>
     <row r="556">
@@ -51167,7 +51167,7 @@
         <v>-0.2666</v>
       </c>
       <c r="M561" t="n">
-        <v>-0.1874</v>
+        <v>-0.1873</v>
       </c>
     </row>
     <row r="562">
@@ -51812,7 +51812,7 @@
         <v>0.5733</v>
       </c>
       <c r="M576" t="n">
-        <v>0.0189</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="577">
@@ -52083,7 +52083,7 @@
         <v>0.5222</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.0399</v>
+        <v>-0.0398</v>
       </c>
       <c r="D583" t="n">
         <v>0.2412</v>
@@ -52092,7 +52092,7 @@
         <v>0.5222</v>
       </c>
       <c r="F583" t="n">
-        <v>-0.0399</v>
+        <v>-0.0398</v>
       </c>
       <c r="G583" t="n">
         <v>1.3258</v>
@@ -53317,7 +53317,7 @@
         <v>0.46</v>
       </c>
       <c r="M611" t="n">
-        <v>-0.2441</v>
+        <v>-0.244</v>
       </c>
     </row>
     <row r="612">
@@ -53403,7 +53403,7 @@
         <v>0.3813</v>
       </c>
       <c r="M613" t="n">
-        <v>-0.1055</v>
+        <v>-0.1054</v>
       </c>
     </row>
     <row r="614">
@@ -54263,7 +54263,7 @@
         <v>0.4328</v>
       </c>
       <c r="M633" t="n">
-        <v>0.3711</v>
+        <v>0.3712</v>
       </c>
     </row>
     <row r="634">
@@ -54319,16 +54319,16 @@
         <v>0.4308</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.1706</v>
+        <v>-0.1712</v>
       </c>
       <c r="D635" t="n">
-        <v>0.1301</v>
+        <v>0.1298</v>
       </c>
       <c r="E635" t="n">
         <v>0.4308</v>
       </c>
       <c r="F635" t="n">
-        <v>-0.1706</v>
+        <v>-0.1712</v>
       </c>
       <c r="G635" t="n">
         <v>0.6662</v>
@@ -54349,7 +54349,7 @@
         <v>0.419</v>
       </c>
       <c r="M635" t="n">
-        <v>0.3911</v>
+        <v>0.3893</v>
       </c>
     </row>
   </sheetData>
